--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026/09/05 22:01:25</t>
+          <t>2026/09/05 23:01:38</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>165:59:47</t>
+          <t>167:00:00</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -855,7 +855,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026/09/05 22:31:21</t>
+          <t>2026/09/05 23:31:38</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>166:16:53</t>
+          <t>167:17:10</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -914,7 +914,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/09/05 22:23:42</t>
+          <t>2026/09/05 23:23:13</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>166:00:02</t>
+          <t>166:59:33</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/09/05 22:42:06</t>
+          <t>2026/09/05 23:42:06</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>165:59:35</t>
+          <t>166:59:35</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026/09/05 22:56:11</t>
+          <t>2026/09/05 23:56:11</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>165:59:35</t>
+          <t>166:59:35</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026/09/05 21:04:45</t>
+          <t>2026/09/05 23:04:45</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>164:00:00</t>
+          <t>166:00:00</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026/09/05 22:11:40</t>
+          <t>2026/09/05 23:11:21</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>125:27:26</t>
+          <t>126:27:07</t>
         </is>
       </c>
       <c r="L86" t="n">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026/09/05 22:46:44</t>
+          <t>2026/09/05 23:46:38</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>83:06:03</t>
+          <t>84:05:57</t>
         </is>
       </c>
       <c r="L133" t="n">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026/09/05 22:39:21</t>
+          <t>2026/09/05 23:39:21</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>32:35:22</t>
+          <t>33:35:22</t>
         </is>
       </c>
       <c r="L172" t="n">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026/09/05 22:55:09</t>
+          <t>2026/09/05 23:55:35</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>30:00:16</t>
+          <t>31:00:42</t>
         </is>
       </c>
       <c r="L178" t="n">
@@ -10944,26 +10944,26 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026/09/05 22:34:33</t>
+          <t>2026/09/05 23:04:45</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>-32.788598, -70.912005</t>
+          <t>-32.838394, -70.955539</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>-32.78860, -70.91200</t>
+          <t>-32.83839, -70.95554</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>24:30:46</t>
+          <t>25:00:58</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>22.07</v>
+        <v>28.94</v>
       </c>
       <c r="M180" t="n">
         <v>0</v>
@@ -11216,7 +11216,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1062.24</v>
+        <v>1069.11</v>
       </c>
       <c r="C3" t="n">
         <v>10</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N186"/>
+  <dimension ref="A1:N187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,7 +560,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026/09/06 22:01:38</t>
+          <t>2026/09/06 23:01:21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>166:00:16</t>
+          <t>166:59:59</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -914,7 +914,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/09/06 22:23:43</t>
+          <t>2026/09/06 23:22:46</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>166:01:05</t>
+          <t>167:00:08</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/09/06 22:40:43</t>
+          <t>2026/09/06 23:40:43</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>165:58:12</t>
+          <t>166:58:12</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/09/06 22:31:20</t>
+          <t>2026/09/06 23:31:38</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>165:47:12</t>
+          <t>166:47:30</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/09/06 22:56:06</t>
+          <t>2026/09/06 23:56:06</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>165:59:30</t>
+          <t>166:59:30</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026/09/06 21:04:45</t>
+          <t>2026/09/06 23:04:45</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>164:00:00</t>
+          <t>166:00:00</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026/09/06 22:12:08</t>
+          <t>2026/09/06 23:12:11</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>149:27:54</t>
+          <t>150:27:57</t>
         </is>
       </c>
       <c r="L93" t="n">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026/09/06 22:46:25</t>
+          <t>2026/09/06 23:46:38</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>107:05:44</t>
+          <t>108:05:57</t>
         </is>
       </c>
       <c r="L140" t="n">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026/09/06 22:39:31</t>
+          <t>2026/09/06 23:39:20</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>56:35:32</t>
+          <t>57:35:21</t>
         </is>
       </c>
       <c r="L176" t="n">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026/09/06 21:38:57</t>
+          <t>2026/09/06 23:38:57</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11195,7 +11195,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>04:00:00</t>
+          <t>06:00:00</t>
         </is>
       </c>
       <c r="L184" t="n">
@@ -11323,6 +11323,65 @@
         <v>0</v>
       </c>
       <c r="N186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>CHANGAN HUNTER TKCS-53</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>4</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>2026/09/06 21:06:07</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>-33.0873016, -71.3623533</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-33.08730, -71.36235</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>2026/09/06 23:06:53</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>-33.0872433, -71.3622583</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>-33.08724, -71.36226</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>02:00:46</t>
+        </is>
+      </c>
+      <c r="L187" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M187" t="n">
+        <v>0</v>
+      </c>
+      <c r="N187" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11412,13 +11471,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>588.4299999999999</v>
+        <v>588.35</v>
       </c>
       <c r="C4" t="n">
         <v>78</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>140</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -855,7 +855,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026/09/07 22:40:43</t>
+          <t>2026/09/07 23:40:43</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>165:58:58</t>
+          <t>166:58:58</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -886,7 +886,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>LPR20251V02900023-LL</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -904,48 +904,48 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-34.205437, -70.677295</t>
+          <t>-33.899904, -71.429498</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-34.20544, -70.67730</t>
+          <t>-33.89990, -71.42950</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/09/02 08:55:46</t>
+          <t>2026/09/07 23:31:38</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-34.205342, -70.680134</t>
+          <t>-33.89982, -71.429438</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-34.20534, -70.68013</t>
+          <t>-33.89982, -71.42944</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>32:11:39</t>
+          <t>166:47:31</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.28</v>
+        <v>0.04</v>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LPR20251V02900023-LL</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -953,7 +953,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -963,42 +963,42 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-33.899904, -71.429498</t>
+          <t>-34.205437, -70.677295</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-33.89990, -71.42950</t>
+          <t>-34.20544, -70.67730</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026/09/07 22:31:21</t>
+          <t>2026/09/02 08:55:46</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-33.89982, -71.429438</t>
+          <t>-34.205342, -70.680134</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-33.89982, -71.42944</t>
+          <t>-34.20534, -70.68013</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>165:47:14</t>
+          <t>32:11:39</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.04</v>
+        <v>0.28</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026/09/07 22:12:08</t>
+          <t>2026/09/07 23:11:45</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>165:24:39</t>
+          <t>166:24:16</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/09/07 22:56:06</t>
+          <t>2026/09/07 23:56:06</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>165:59:14</t>
+          <t>166:59:14</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026/09/07 22:39:21</t>
+          <t>2026/09/07 23:39:21</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>80:35:22</t>
+          <t>81:35:22</t>
         </is>
       </c>
       <c r="L150" t="n">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026/09/07 22:14:09</t>
+          <t>2026/09/07 23:14:08</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>07:01:17</t>
+          <t>08:01:16</t>
         </is>
       </c>
       <c r="L166" t="n">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026/09/07 21:21:38</t>
+          <t>2026/09/07 23:21:38</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>06:00:04</t>
+          <t>08:00:04</t>
         </is>
       </c>
       <c r="L167" t="n">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026/09/07 21:54:08</t>
+          <t>2026/09/07 23:54:08</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>04:01:06</t>
+          <t>06:01:06</t>
         </is>
       </c>
       <c r="L168" t="n">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026/09/07 21:15:37</t>
+          <t>2026/09/07 23:15:37</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>02:01:00</t>
+          <t>04:01:00</t>
         </is>
       </c>
       <c r="L170" t="n">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026/09/07 21:48:03</t>
+          <t>2026/09/07 23:48:03</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>01:49:03</t>
+          <t>03:49:03</t>
         </is>
       </c>
       <c r="L172" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -886,7 +886,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LPR20251V02900023-LL</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -904,48 +904,48 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-33.899904, -71.429498</t>
+          <t>-34.205437, -70.677295</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-33.89990, -71.42950</t>
+          <t>-34.20544, -70.67730</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/09/07 23:31:38</t>
+          <t>2026/09/02 08:55:46</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-33.89982, -71.429438</t>
+          <t>-34.205342, -70.680134</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-33.89982, -71.42944</t>
+          <t>-34.20534, -70.68013</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>166:47:31</t>
+          <t>32:11:39</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.04</v>
+        <v>0.28</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>LPR20251V02900023-LL</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -953,7 +953,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -963,42 +963,42 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-34.205437, -70.677295</t>
+          <t>-33.899904, -71.429498</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-34.20544, -70.67730</t>
+          <t>-33.89990, -71.42950</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026/09/02 08:55:46</t>
+          <t>2026/09/07 23:31:38</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-34.205342, -70.680134</t>
+          <t>-33.89982, -71.429438</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-34.20534, -70.68013</t>
+          <t>-33.89982, -71.42944</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>32:11:39</t>
+          <t>166:47:31</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.28</v>
+        <v>0.04</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/09/08 22:40:35</t>
+          <t>2026/09/08 23:40:35</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>165:58:50</t>
+          <t>166:58:50</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/09/08 22:31:38</t>
+          <t>2026/09/08 23:31:21</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>165:47:38</t>
+          <t>166:47:21</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/09/08 22:08:45</t>
+          <t>2026/09/08 23:09:09</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>165:24:13</t>
+          <t>166:24:37</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026/09/08 22:56:11</t>
+          <t>2026/09/08 23:56:11</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>165:59:19</t>
+          <t>166:59:19</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026/09/08 22:13:38</t>
+          <t>2026/09/08 23:13:18</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>104:09:39</t>
+          <t>105:09:19</t>
         </is>
       </c>
       <c r="L146" t="n">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026/09/08 22:46:52</t>
+          <t>2026/09/08 23:46:52</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>43:00:24</t>
+          <t>44:00:24</t>
         </is>
       </c>
       <c r="L153" t="n">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026/09/08 22:35:23</t>
+          <t>2026/09/08 23:35:23</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>09:45:07</t>
+          <t>10:45:07</t>
         </is>
       </c>
       <c r="L170" t="n">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026/09/08 22:57:30</t>
+          <t>2026/09/08 23:57:30</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>09:01:08</t>
+          <t>10:01:08</t>
         </is>
       </c>
       <c r="L174" t="n">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026/09/08 22:28:01</t>
+          <t>2026/09/08 23:28:01</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>07:01:16</t>
+          <t>08:01:16</t>
         </is>
       </c>
       <c r="L175" t="n">
@@ -10885,7 +10885,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026/09/08 21:09:50</t>
+          <t>2026/09/08 23:09:50</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>02:00:58</t>
+          <t>04:00:58</t>
         </is>
       </c>
       <c r="L179" t="n">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026/09/08 21:31:52</t>
+          <t>2026/09/08 23:31:52</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>02:00:02</t>
+          <t>04:00:02</t>
         </is>
       </c>
       <c r="L181" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N155"/>
+  <dimension ref="A1:N156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/09/09 22:31:21</t>
+          <t>2026/09/09 23:31:25</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>166:00:00</t>
+          <t>167:00:04</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026/09/09 22:40:35</t>
+          <t>2026/09/09 23:40:35</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>165:58:54</t>
+          <t>166:58:54</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/09/09 22:56:11</t>
+          <t>2026/09/09 23:56:11</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>166:00:02</t>
+          <t>167:00:02</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -8702,7 +8702,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026/09/09 22:35:22</t>
+          <t>2026/09/09 23:35:03</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>33:45:06</t>
+          <t>34:44:47</t>
         </is>
       </c>
       <c r="L142" t="n">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026/09/09 22:54:33</t>
+          <t>2026/09/09 23:54:22</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>32:58:11</t>
+          <t>33:58:00</t>
         </is>
       </c>
       <c r="L146" t="n">
@@ -8997,7 +8997,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026/09/09 22:25:00</t>
+          <t>2026/09/09 23:24:47</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>30:58:15</t>
+          <t>31:58:02</t>
         </is>
       </c>
       <c r="L147" t="n">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026/09/09 21:34:28</t>
+          <t>2026/09/09 23:34:28</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L154" t="n">
@@ -9494,6 +9494,65 @@
         <v>0</v>
       </c>
       <c r="N155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>MITSUBISHI L200 PHZF-89</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>5</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>2026/09/09 21:27:13</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>-33.4366466, -70.6296616</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>-33.43665, -70.62966</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>2026/09/09 23:29:06</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>-33.4366466, -70.6296616</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>-33.43665, -70.62966</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>02:01:53</t>
+        </is>
+      </c>
+      <c r="L156" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" t="n">
+        <v>0</v>
+      </c>
+      <c r="N156" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9792,13 +9851,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>392.32</v>
+        <v>392.28</v>
       </c>
       <c r="C15" t="n">
         <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>138</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026/09/10 22:06:21</t>
+          <t>2026/09/10 23:06:36</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>165:54:42</t>
+          <t>166:54:57</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026/09/10 22:31:52</t>
+          <t>2026/09/10 23:31:30</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>166:00:31</t>
+          <t>167:00:09</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -914,7 +914,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/09/10 22:41:02</t>
+          <t>2026/09/10 23:41:02</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>165:59:21</t>
+          <t>166:59:21</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/09/10 22:56:10</t>
+          <t>2026/09/10 23:56:10</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>166:00:01</t>
+          <t>167:00:01</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026/09/10 22:34:38</t>
+          <t>2026/09/10 23:34:47</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>57:44:22</t>
+          <t>58:44:31</t>
         </is>
       </c>
       <c r="L125" t="n">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026/09/10 22:54:30</t>
+          <t>2026/09/10 23:54:17</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>56:58:08</t>
+          <t>57:57:55</t>
         </is>
       </c>
       <c r="L130" t="n">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026/09/10 22:09:33</t>
+          <t>2026/09/10 23:09:54</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8363,7 +8363,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>30:44:56</t>
+          <t>31:45:17</t>
         </is>
       </c>
       <c r="L136" t="n">
@@ -8407,7 +8407,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026/09/10 21:42:06</t>
+          <t>2026/09/10 23:42:06</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>10:00:44</t>
+          <t>12:00:44</t>
         </is>
       </c>
       <c r="L137" t="n">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026/09/10 21:37:12</t>
+          <t>2026/09/10 23:37:12</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>04:00:17</t>
+          <t>06:00:17</t>
         </is>
       </c>
       <c r="L138" t="n">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026/09/10 21:47:06</t>
+          <t>2026/09/10 23:47:06</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>04:00:00</t>
+          <t>06:00:00</t>
         </is>
       </c>
       <c r="L139" t="n">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026/09/10 21:40:33</t>
+          <t>2026/09/10 23:40:33</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>02:00:20</t>
+          <t>04:00:20</t>
         </is>
       </c>
       <c r="L140" t="n">
@@ -8643,7 +8643,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026/09/10 21:43:06</t>
+          <t>2026/09/10 23:43:06</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>02:00:35</t>
+          <t>04:00:35</t>
         </is>
       </c>
       <c r="L141" t="n">
@@ -8702,7 +8702,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026/09/10 21:54:59</t>
+          <t>2026/09/10 23:54:59</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>02:01:24</t>
+          <t>04:01:24</t>
         </is>
       </c>
       <c r="L142" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,13 +446,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N143"/>
+  <dimension ref="A1:N125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Desde : 2026/09/04 04:00:00   Hasta : 2026/09/11 03:59:59</t>
+          <t>Desde : 2026/09/05 04:00:00   Hasta : 2026/09/12 03:59:59</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026/09/04 00:01:38</t>
+          <t>2026/09/05 00:01:19</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>85:44:28</t>
+          <t>61:44:47</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -591,7 +591,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -604,47 +604,47 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026/09/04 00:09:11</t>
+          <t>2026/09/05 00:01:57</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-34.579653, -70.961421</t>
+          <t>-33.4363316, -70.628895</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-34.57965, -70.96142</t>
+          <t>-33.43633, -70.62889</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026/09/04 11:41:54</t>
+          <t>2026/09/06 09:42:38</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-34.579653, -70.961427</t>
+          <t>-33.4359749, -70.6299933</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-34.57965, -70.96143</t>
+          <t>-33.43597, -70.62999</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>11:32:43</t>
+          <t>33:40:41</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.14</v>
+        <v>55.39</v>
       </c>
       <c r="M5" t="n">
-        <v>5</v>
+        <v>138</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6">
@@ -663,22 +663,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026/09/04 00:11:39</t>
+          <t>2026/09/05 00:11:38</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-34.205439, -70.677158</t>
+          <t>-34.205312, -70.677304</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-34.20544, -70.67716</t>
+          <t>-34.20531, -70.67730</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026/09/10 23:06:36</t>
+          <t>2026/09/11 23:06:39</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -693,11 +693,11 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>166:54:57</t>
+          <t>166:55:01</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -722,7 +722,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026/09/04 00:23:09</t>
+          <t>2026/09/05 00:23:37</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>73:01:46</t>
+          <t>49:01:18</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LPR20251V02900023-LL</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -781,53 +781,53 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026/09/04 00:31:21</t>
+          <t>2026/09/05 00:25:37</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-33.899721, -71.429341</t>
+          <t>-33.359994, -70.807041</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-33.89972, -71.42934</t>
+          <t>-33.35999, -70.80704</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026/09/10 23:31:30</t>
+          <t>2026/09/09 14:27:06</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-33.899886, -71.429534</t>
+          <t>-33.359994, -70.807053</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-33.89989, -71.42953</t>
+          <t>-33.35999, -70.80705</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>167:00:09</t>
+          <t>110:01:29</t>
         </is>
       </c>
       <c r="L8" t="n">
         <v>0.03</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>LPR20251V02900023-LL</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -835,58 +835,58 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026/09/04 00:36:14</t>
+          <t>2026/09/05 00:31:37</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-34.1678533, -70.7329816</t>
+          <t>-33.899796, -71.429428</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-34.16785, -70.73298</t>
+          <t>-33.89980, -71.42943</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026/09/04 08:32:57</t>
+          <t>2026/09/11 22:31:27</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-34.20428, -70.6791333</t>
+          <t>-33.899886, -71.429534</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-34.20428, -70.67913</t>
+          <t>-33.89989, -71.42953</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>07:56:43</t>
+          <t>165:59:50</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>7.59</v>
+        <v>0.01</v>
       </c>
       <c r="M9" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LPR20251E02900022</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -894,58 +894,58 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026/09/04 00:41:41</t>
+          <t>2026/09/05 00:32:53</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-33.367545, -70.69663</t>
+          <t>-32.7430849, -70.7297799</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-33.36754, -70.69663</t>
+          <t>-32.74308, -70.72978</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/09/10 23:41:02</t>
+          <t>2026/09/06 18:18:51</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-33.36765, -70.697163</t>
+          <t>-32.7431899, -70.7296433</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-33.36765, -70.69716</t>
+          <t>-32.74319, -70.72964</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>166:59:21</t>
+          <t>41:45:58</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.05</v>
+        <v>0.44</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -958,53 +958,53 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026/09/04 00:44:06</t>
+          <t>2026/09/05 00:33:21</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-33.360018, -70.807049</t>
+          <t>-32.779806, -70.979927</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-33.36002, -70.80705</t>
+          <t>-32.77981, -70.97993</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026/09/04 08:08:22</t>
+          <t>2026/09/06 20:51:33</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-33.36037, -70.810194</t>
+          <t>-32.785413, -70.895182</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-33.36037, -70.81019</t>
+          <t>-32.78541, -70.89518</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>07:24:16</t>
+          <t>44:18:12</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.35</v>
+        <v>30.79</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1012,58 +1012,58 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026/09/04 00:46:32</t>
+          <t>2026/09/05 00:39:42</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-34.20537, -70.677421</t>
+          <t>-32.8792316, -70.6088916</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-34.20537, -70.67742</t>
+          <t>-32.87923, -70.60889</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026/09/07 02:49:01</t>
+          <t>2026/09/05 13:30:06</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-34.205421, -70.677247</t>
+          <t>-32.8321399, -70.6228783</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-34.20542, -70.67725</t>
+          <t>-32.83214, -70.62288</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>74:02:29</t>
+          <t>12:50:24</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.03</v>
+        <v>8.27</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1076,53 +1076,53 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026/09/04 00:47:46</t>
+          <t>2026/09/05 00:40:53</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-34.1677083, -70.7330066</t>
+          <t>-33.087275, -71.3622416</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-34.16771, -70.73301</t>
+          <t>-33.08727, -71.36224</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026/09/04 08:45:53</t>
+          <t>2026/09/05 12:26:55</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-34.2051983, -70.6775183</t>
+          <t>-33.0873233, -71.3623383</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-34.20520, -70.67752</t>
+          <t>-33.08732, -71.36234</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>07:58:07</t>
+          <t>11:46:02</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>8.710000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="M13" t="n">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="N13" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>LPR20251E02900022</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1130,58 +1130,58 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026/09/04 00:49:02</t>
+          <t>2026/09/05 00:42:06</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-34.16777, -70.7330183</t>
+          <t>-33.36765, -70.697163</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-34.16777, -70.73302</t>
+          <t>-33.36765, -70.69716</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/09/04 08:45:07</t>
+          <t>2026/09/11 22:41:02</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-34.205345, -70.6803566</t>
+          <t>-33.36765, -70.697163</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-34.20535, -70.68036</t>
+          <t>-33.36765, -70.69716</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>07:56:05</t>
+          <t>165:58:56</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8.69</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1189,58 +1189,58 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026/09/04 00:55:51</t>
+          <t>2026/09/05 00:46:27</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-32.879205, -70.6087949</t>
+          <t>-34.20537, -70.677421</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-32.87920, -70.60879</t>
+          <t>-34.20537, -70.67742</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/09/04 07:58:41</t>
+          <t>2026/09/07 02:49:01</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-32.8791833, -70.6088016</t>
+          <t>-34.205421, -70.677247</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-32.87918, -70.60880</t>
+          <t>-34.20542, -70.67725</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>07:02:50</t>
+          <t>50:02:34</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>10.17</v>
+        <v>0.03</v>
       </c>
       <c r="M15" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LPR20251T02800022</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1253,37 +1253,37 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026/09/04 00:56:09</t>
+          <t>2026/09/05 00:55:26</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-33.367244, -70.69677</t>
+          <t>-34.042677, -70.681769</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-33.36724, -70.69677</t>
+          <t>-34.04268, -70.68177</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/09/10 23:56:10</t>
+          <t>2026/09/06 00:59:49</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-33.367244, -70.69677</t>
+          <t>-34.042702, -70.681741</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-33.36724, -70.69677</t>
+          <t>-34.04270, -70.68174</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>167:00:01</t>
+          <t>24:04:23</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -1299,7 +1299,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>LPR20251T02800022</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1312,41 +1312,41 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026/09/04 00:59:11</t>
+          <t>2026/09/05 00:56:11</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-34.0426, -70.68171</t>
+          <t>-33.367244, -70.69677</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-34.04260, -70.68171</t>
+          <t>-33.36724, -70.69677</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026/09/04 08:34:55</t>
+          <t>2026/09/11 22:56:10</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-34.042662, -70.681715</t>
+          <t>-33.367244, -70.69677</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-34.04266, -70.68171</t>
+          <t>-33.36724, -70.69677</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>07:35:44</t>
+          <t>165:59:59</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -1358,7 +1358,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1366,58 +1366,58 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026/09/04 01:04:45</t>
+          <t>2026/09/05 00:57:08</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-33.3672483, -70.6957066</t>
+          <t>-34.579653, -70.961436</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-33.36725, -70.69571</t>
+          <t>-34.57965, -70.96144</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026/09/10 11:40:07</t>
+          <t>2026/09/06 01:37:43</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-33.367095, -70.695535</t>
+          <t>-34.579718, -70.961362</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-33.36709, -70.69554</t>
+          <t>-34.57972, -70.96136</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>154:35:22</t>
+          <t>24:40:35</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>25.32</v>
+        <v>0.01</v>
       </c>
       <c r="M18" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1430,53 +1430,53 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026/09/04 01:11:55</t>
+          <t>2026/09/05 01:04:45</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-33.47614, -70.69841</t>
+          <t>-33.3672483, -70.6957066</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-33.47614, -70.69841</t>
+          <t>-33.36725, -70.69571</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026/09/04 08:43:28</t>
+          <t>2026/09/10 11:40:07</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-33.4762816, -70.69835</t>
+          <t>-33.367095, -70.695535</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-33.47628, -70.69835</t>
+          <t>-33.36709, -70.69554</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>07:31:33</t>
+          <t>130:35:22</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>11.12</v>
+        <v>25.32</v>
       </c>
       <c r="M19" t="n">
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="N19" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1489,57 +1489,57 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026/09/04 01:41:26</t>
+          <t>2026/09/05 01:15:29</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-33.4371233, -70.6294183</t>
+          <t>-33.4761866, -70.6983983</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-33.43712, -70.62942</t>
+          <t>-33.47619, -70.69840</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026/09/04 07:24:53</t>
+          <t>2026/09/05 09:35:05</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-33.4459483, -70.6203349</t>
+          <t>-33.47627, -70.6983233</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-33.44595, -70.62033</t>
+          <t>-33.47627, -70.69832</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>05:43:27</t>
+          <t>08:19:36</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.8</v>
+        <v>0.03</v>
       </c>
       <c r="M20" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="N20" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1548,53 +1548,53 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026/09/04 07:25:02</t>
+          <t>2026/09/05 01:52:42</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-33.4459483, -70.620345</t>
+          <t>-32.7975916, -70.8870383</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-33.44595, -70.62035</t>
+          <t>-32.79759, -70.88704</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026/09/04 09:03:06</t>
+          <t>2026/09/05 07:57:03</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-33.4442883, -70.621585</t>
+          <t>-32.88315, -70.6123616</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-33.44429, -70.62158</t>
+          <t>-32.88315, -70.61236</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>01:38:04</t>
+          <t>06:04:21</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0.27</v>
+        <v>42.04</v>
       </c>
       <c r="M21" t="n">
-        <v>20</v>
+        <v>108</v>
       </c>
       <c r="N21" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1607,44 +1607,44 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026/09/04 07:58:47</t>
+          <t>2026/09/05 07:58:18</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-32.8791849, -70.6087683</t>
+          <t>-32.88312, -70.61235</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-32.87918, -70.60877</t>
+          <t>-32.88312, -70.61235</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026/09/04 10:47:06</t>
+          <t>2026/09/05 08:07:56</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-32.8850833, -70.61119</t>
+          <t>-32.8826383, -70.610755</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-32.88508, -70.61119</t>
+          <t>-32.88264, -70.61075</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>02:48:19</t>
+          <t>00:09:38</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.04</v>
+        <v>0.2</v>
       </c>
       <c r="M22" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N22" t="n">
         <v>11</v>
@@ -1653,66 +1653,66 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026/09/04 08:09:22</t>
+          <t>2026/09/05 08:08:53</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-33.360311, -70.810384</t>
+          <t>-32.88354, -70.6105233</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-33.36031, -70.81038</t>
+          <t>-32.88354, -70.61052</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026/09/04 10:02:40</t>
+          <t>2026/09/05 12:25:44</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-33.360087, -70.810294</t>
+          <t>-32.88288, -70.6123549</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-33.36009, -70.81029</t>
+          <t>-32.88288, -70.61235</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>01:53:18</t>
+          <t>04:16:51</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0.04</v>
+        <v>0.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1725,57 +1725,57 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026/09/04 08:34:12</t>
+          <t>2026/09/05 09:35:14</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-34.2042816, -70.6790583</t>
+          <t>-33.4763216, -70.6983783</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-34.20428, -70.67906</t>
+          <t>-33.47632, -70.69838</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026/09/04 08:45:47</t>
+          <t>2026/09/05 10:06:33</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-34.2052216, -70.6774799</t>
+          <t>-33.3622916, -70.670125</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-34.20522, -70.67748</t>
+          <t>-33.36229, -70.67012</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>00:11:35</t>
+          <t>00:31:19</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0.18</v>
+        <v>18.67</v>
       </c>
       <c r="M24" t="n">
-        <v>16</v>
+        <v>104</v>
       </c>
       <c r="N24" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1784,57 +1784,57 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026/09/04 08:35:55</t>
+          <t>2026/09/05 10:07:01</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-34.042665, -70.681707</t>
+          <t>-33.3621366, -70.6701166</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-34.04266, -70.68171</t>
+          <t>-33.36214, -70.67012</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026/09/04 16:54:01</t>
+          <t>2026/09/05 18:19:44</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-34.04266, -70.681732</t>
+          <t>-33.47629, -70.698265</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-34.04266, -70.68173</t>
+          <t>-33.47629, -70.69827</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>08:18:06</t>
+          <t>08:12:43</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0.12</v>
+        <v>18.06</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1843,57 +1843,57 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026/09/04 08:43:44</t>
+          <t>2026/09/05 12:26:59</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-33.4763116, -70.6983833</t>
+          <t>-32.883165, -70.6123866</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-33.47631, -70.69838</t>
+          <t>-32.88316, -70.61239</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026/09/04 10:16:00</t>
+          <t>2026/09/05 13:46:42</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-33.3623183, -70.6701366</t>
+          <t>-32.7977016, -70.8874016</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-33.36232, -70.67014</t>
+          <t>-32.79770, -70.88740</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>01:32:16</t>
+          <t>01:19:43</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>19.68</v>
+        <v>49.24</v>
       </c>
       <c r="M26" t="n">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="N26" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1902,41 +1902,41 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026/09/04 08:44:08</t>
+          <t>2026/09/05 12:27:22</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-32.838344, -70.95562</t>
+          <t>-33.0873383, -71.3623383</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-32.83834, -70.95562</t>
+          <t>-33.08734, -71.36234</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026/09/04 14:42:08</t>
+          <t>2026/09/05 20:21:01</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-33.367513, -70.695444</t>
+          <t>-33.0873766, -71.36229</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-33.36751, -70.69544</t>
+          <t>-33.08738, -71.36229</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>05:58:00</t>
+          <t>07:53:39</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>64.23999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="M27" t="n">
         <v>6</v>
@@ -1948,7 +1948,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1961,53 +1961,53 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026/09/04 08:45:20</t>
+          <t>2026/09/05 13:31:21</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-34.205165, -70.6802683</t>
+          <t>-32.8313683, -70.6160649</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-34.20517, -70.68027</t>
+          <t>-32.83137, -70.61606</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026/09/04 09:03:44</t>
+          <t>2026/09/05 13:46:31</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-34.2041833, -70.6787916</t>
+          <t>-32.8213499, -70.6154616</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-34.20418, -70.67879</t>
+          <t>-32.82135, -70.61546</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>00:18:24</t>
+          <t>00:15:10</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.18</v>
+        <v>5.66</v>
       </c>
       <c r="M28" t="n">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="N28" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2020,47 +2020,47 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026/09/04 08:46:04</t>
+          <t>2026/09/05 13:46:39</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-34.205485, -70.6775316</t>
+          <t>-32.8214033, -70.6154666</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-34.20549, -70.67753</t>
+          <t>-32.82140, -70.61547</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026/09/04 08:51:56</t>
+          <t>2026/09/05 14:31:32</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-34.2058216, -70.67598</t>
+          <t>-32.8792099, -70.6089166</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-34.20582, -70.67598</t>
+          <t>-32.87921, -70.60892</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>00:05:52</t>
+          <t>00:44:53</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0.15</v>
+        <v>9.83</v>
       </c>
       <c r="M29" t="n">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="N29" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2079,53 +2079,53 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026/09/04 08:46:08</t>
+          <t>2026/09/05 13:47:45</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-34.205405, -70.6775266</t>
+          <t>-32.7975933, -70.88708</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-34.20540, -70.67753</t>
+          <t>-32.79759, -70.88708</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026/09/04 09:09:17</t>
+          <t>2026/09/05 17:01:45</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-34.20574, -70.6760516</t>
+          <t>-32.7554033, -70.724555</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-34.20574, -70.67605</t>
+          <t>-32.75540, -70.72455</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>00:23:09</t>
+          <t>03:14:00</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0.15</v>
+        <v>18.63</v>
       </c>
       <c r="M30" t="n">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="N30" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2138,57 +2138,57 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026/09/04 08:52:30</t>
+          <t>2026/09/05 14:32:20</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-34.2075316, -70.6760083</t>
+          <t>-32.8790733, -70.6093966</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-34.20753, -70.67601</t>
+          <t>-32.87907, -70.60940</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026/09/04 09:28:47</t>
+          <t>2026/09/05 18:38:02</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-34.2055416, -70.6775516</t>
+          <t>-32.8792566, -70.6088116</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-34.20554, -70.67755</t>
+          <t>-32.87926, -70.60881</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>00:36:17</t>
+          <t>04:05:42</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0.37</v>
+        <v>10.8</v>
       </c>
       <c r="M31" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="N31" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2197,57 +2197,57 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026/09/04 09:03:46</t>
+          <t>2026/09/05 17:03:00</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-33.4442899, -70.6216116</t>
+          <t>-32.7519866, -70.7233349</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-33.44429, -70.62161</t>
+          <t>-32.75199, -70.72333</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026/09/04 10:24:14</t>
+          <t>2026/09/05 18:12:38</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-33.3661483, -70.6955366</t>
+          <t>-32.7548899, -70.7276849</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-33.36615, -70.69554</t>
+          <t>-32.75489, -70.72768</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>01:20:28</t>
+          <t>01:09:38</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>13.24</v>
+        <v>1.92</v>
       </c>
       <c r="M32" t="n">
-        <v>112</v>
+        <v>26</v>
       </c>
       <c r="N32" t="n">
-        <v>41</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2256,57 +2256,57 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026/09/04 09:03:52</t>
+          <t>2026/09/05 18:14:17</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-34.2041116, -70.6788799</t>
+          <t>-32.7548933, -70.7280533</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-34.20411, -70.67888</t>
+          <t>-32.75489, -70.72805</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026/09/04 12:15:55</t>
+          <t>2026/09/05 19:09:56</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-34.19012, -70.7093833</t>
+          <t>-32.7977333, -70.8874249</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-34.19012, -70.70938</t>
+          <t>-32.79773, -70.88742</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>03:12:03</t>
+          <t>00:55:39</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.86</v>
+        <v>18.22</v>
       </c>
       <c r="M33" t="n">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="N33" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2315,57 +2315,57 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026/09/04 09:09:53</t>
+          <t>2026/09/05 18:20:59</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-34.2074133, -70.6760033</t>
+          <t>-33.4762383, -70.6983866</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-34.20741, -70.67600</t>
+          <t>-33.47624, -70.69839</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026/09/04 09:28:33</t>
+          <t>2026/09/07 09:06:46</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-34.2052533, -70.677495</t>
+          <t>-33.476265, -70.6983216</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-34.20525, -70.67749</t>
+          <t>-33.47626, -70.69832</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>00:18:40</t>
+          <t>38:45:47</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0.34</v>
+        <v>56.18</v>
       </c>
       <c r="M34" t="n">
-        <v>15</v>
+        <v>118</v>
       </c>
       <c r="N34" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2374,57 +2374,57 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026/09/04 09:28:39</t>
+          <t>2026/09/05 18:38:11</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-34.2053166, -70.6774733</t>
+          <t>-32.8792633, -70.6087649</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-34.20532, -70.67747</t>
+          <t>-32.87926, -70.60876</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026/09/04 09:37:50</t>
+          <t>2026/09/06 09:58:46</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-34.2051783, -70.6775099</t>
+          <t>-32.8813949, -70.611115</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-34.20518, -70.67751</t>
+          <t>-32.88139, -70.61111</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>00:09:11</t>
+          <t>15:20:35</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0.39</v>
+        <v>1.58</v>
       </c>
       <c r="M35" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="N35" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2433,116 +2433,116 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026/09/04 09:29:00</t>
+          <t>2026/09/05 19:11:11</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-34.2053566, -70.6775216</t>
+          <t>-32.7976083, -70.8870683</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-34.20536, -70.67752</t>
+          <t>-32.79761, -70.88707</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026/09/04 10:26:09</t>
+          <t>2026/09/05 22:01:12</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-34.2052283, -70.68034</t>
+          <t>-32.7832499, -70.8550466</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-34.20523, -70.68034</t>
+          <t>-32.78325, -70.85505</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>00:57:09</t>
+          <t>02:50:01</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.11</v>
+        <v>3.87</v>
       </c>
       <c r="M36" t="n">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="N36" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026/09/05 20:21:24</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>-33.0872549, -71.3621933</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-33.08725, -71.36219</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026/09/06 15:23:37</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>-33.0582133, -71.3724133</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>-33.05821, -71.37241</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>19:02:13</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
         <v>5</v>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2026/09/04 09:38:01</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>-34.2053566, -70.6774249</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>-34.20536, -70.67742</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>2026/09/04 10:23:35</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>-34.2052716, -70.6803033</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>-34.20527, -70.68030</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>00:45:34</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>0.29</v>
-      </c>
       <c r="M37" t="n">
-        <v>11</v>
+        <v>86</v>
       </c>
       <c r="N37" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2551,57 +2551,57 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026/09/04 10:02:53</t>
+          <t>2026/09/05 22:02:27</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-33.360088, -70.81028</t>
+          <t>-32.7831599, -70.8549516</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-33.36009, -70.81028</t>
+          <t>-32.78316, -70.85495</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026/09/04 10:33:30</t>
+          <t>2026/09/05 22:13:04</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-33.360391, -70.811058</t>
+          <t>-32.7976933, -70.8873866</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-33.36039, -70.81106</t>
+          <t>-32.79769, -70.88739</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>00:30:37</t>
+          <t>00:10:37</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0.2</v>
+        <v>3.7</v>
       </c>
       <c r="M38" t="n">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="N38" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2610,57 +2610,57 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026/09/04 10:16:23</t>
+          <t>2026/09/05 22:14:03</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-33.3622116, -70.6701683</t>
+          <t>-32.79761, -70.88709</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-33.36221, -70.67017</t>
+          <t>-32.79761, -70.88709</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026/09/04 12:23:59</t>
+          <t>2026/09/06 11:18:46</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>-33.4338966, -70.8107233</t>
+          <t>-32.79573, -70.8201666</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>-33.43390, -70.81072</t>
+          <t>-32.79573, -70.82017</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>02:07:36</t>
+          <t>13:04:43</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>19.94</v>
+        <v>9.68</v>
       </c>
       <c r="M39" t="n">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="N39" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2669,57 +2669,57 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026/09/04 10:23:42</t>
+          <t>2026/09/06 02:35:12</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-34.2051583, -70.6802433</t>
+          <t>-34.579718, -70.961362</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-34.20516, -70.68024</t>
+          <t>-34.57972, -70.96136</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026/09/04 10:54:19</t>
+          <t>2026/09/07 15:17:14</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-34.2042833, -70.6791233</t>
+          <t>-34.579702, -70.961411</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>-34.20428, -70.67912</t>
+          <t>-34.57970, -70.96141</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>00:30:37</t>
+          <t>36:42:02</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0.14</v>
+        <v>0.79</v>
       </c>
       <c r="M40" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N40" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2728,57 +2728,57 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026/09/04 10:25:10</t>
+          <t>2026/09/06 12:05:47</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-33.3672, -70.69557</t>
+          <t>-32.8791933, -70.6088266</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-33.36720, -70.69557</t>
+          <t>-32.87919, -70.60883</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026/09/04 15:17:14</t>
+          <t>2026/09/06 13:37:21</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-33.4361266, -70.6299066</t>
+          <t>-33.5490416, -70.8405516</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-33.43613, -70.62991</t>
+          <t>-33.54904, -70.84055</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>04:52:04</t>
+          <t>01:31:34</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>19.37</v>
+        <v>100.35</v>
       </c>
       <c r="M41" t="n">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="N41" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2787,53 +2787,53 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026/09/04 10:26:17</t>
+          <t>2026/09/06 12:48:02</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-34.2052083, -70.680315</t>
+          <t>-33.59851, -70.52519</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-34.20521, -70.68031</t>
+          <t>-33.59851, -70.52519</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026/09/04 10:33:11</t>
+          <t>2026/09/06 14:32:42</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-34.2053416, -70.6803166</t>
+          <t>-33.693515, -70.3346666</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-34.20534, -70.68032</t>
+          <t>-33.69351, -70.33467</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>00:06:54</t>
+          <t>01:44:40</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0.02</v>
+        <v>28.03</v>
       </c>
       <c r="M42" t="n">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="N42" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -2846,57 +2846,57 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026/09/04 10:33:45</t>
+          <t>2026/09/06 13:38:36</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-34.2054166, -70.6797116</t>
+          <t>-33.548945, -70.8405816</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-34.20542, -70.67971</t>
+          <t>-33.54895, -70.84058</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026/09/04 10:44:11</t>
+          <t>2026/09/06 14:15:50</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-34.2049049, -70.678595</t>
+          <t>-33.4583416, -70.6605216</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-34.20490, -70.67860</t>
+          <t>-33.45834, -70.66052</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>00:10:26</t>
+          <t>00:37:14</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0.51</v>
+        <v>27.47</v>
       </c>
       <c r="M43" t="n">
-        <v>11</v>
+        <v>126</v>
       </c>
       <c r="N43" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2905,57 +2905,57 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026/09/04 10:33:54</t>
+          <t>2026/09/06 14:17:05</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-33.360387, -70.811093</t>
+          <t>-33.4583416, -70.6618449</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-33.36039, -70.81109</t>
+          <t>-33.45834, -70.66184</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026/09/04 10:55:40</t>
+          <t>2026/09/06 17:34:09</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-33.360599, -70.811197</t>
+          <t>-32.84845, -70.59168</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-33.36060, -70.81120</t>
+          <t>-32.84845, -70.59168</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>00:21:46</t>
+          <t>03:17:04</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0.09</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>6</v>
+        <v>136</v>
       </c>
       <c r="N44" t="n">
-        <v>4</v>
+        <v>71</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2964,57 +2964,57 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026/09/04 10:45:26</t>
+          <t>2026/09/06 14:33:57</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-34.2048983, -70.6786316</t>
+          <t>-33.6935366, -70.334655</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-34.20490, -70.67863</t>
+          <t>-33.69354, -70.33465</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026/09/04 11:09:18</t>
+          <t>2026/09/06 15:35:55</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-34.20549, -70.6769449</t>
+          <t>-33.6838933, -70.3390666</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-34.20549, -70.67694</t>
+          <t>-33.68389, -70.33907</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>00:23:52</t>
+          <t>01:01:58</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="M45" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="N45" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3023,57 +3023,57 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026/09/04 10:48:21</t>
+          <t>2026/09/06 15:37:10</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-32.8845033, -70.6111716</t>
+          <t>-33.680965, -70.3387466</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-32.88450, -70.61117</t>
+          <t>-33.68097, -70.33875</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026/09/04 11:08:15</t>
+          <t>2026/09/06 16:02:34</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-32.885, -70.61041</t>
+          <t>-33.5945, -70.3902549</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-32.88500, -70.61041</t>
+          <t>-33.59450, -70.39025</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>00:19:54</t>
+          <t>00:25:24</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0.52</v>
+        <v>13.27</v>
       </c>
       <c r="M46" t="n">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="N46" t="n">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3082,57 +3082,57 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026/09/04 10:54:45</t>
+          <t>2026/09/06 16:03:14</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-34.204295, -70.6790683</t>
+          <t>-33.5938016, -70.39274</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-34.20430, -70.67907</t>
+          <t>-33.59380, -70.39274</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026/09/04 11:33:13</t>
+          <t>2026/09/06 16:32:37</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-34.2050683, -70.6771349</t>
+          <t>-33.5982049, -70.5221333</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-34.20507, -70.67713</t>
+          <t>-33.59820, -70.52213</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>00:38:28</t>
+          <t>00:29:23</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.06</v>
+        <v>14.02</v>
       </c>
       <c r="M47" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="N47" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3141,47 +3141,47 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026/09/04 10:55:54</t>
+          <t>2026/09/06 16:33:52</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-33.360602, -70.811154</t>
+          <t>-33.5983416, -70.52602</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-33.36060, -70.81115</t>
+          <t>-33.59834, -70.52602</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026/09/04 11:09:56</t>
+          <t>2026/09/06 17:38:24</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-33.361199, -70.81185</t>
+          <t>-33.4365083, -70.6289616</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-33.36120, -70.81185</t>
+          <t>-33.43651, -70.62896</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>00:14:02</t>
+          <t>01:04:32</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0.18</v>
+        <v>39.69</v>
       </c>
       <c r="M48" t="n">
-        <v>7</v>
+        <v>109</v>
       </c>
       <c r="N48" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49">
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3200,57 +3200,57 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026/09/04 11:08:23</t>
+          <t>2026/09/06 17:34:58</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-32.8850233, -70.6104466</t>
+          <t>-32.848435, -70.5917433</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-32.88502, -70.61045</t>
+          <t>-32.84844, -70.59174</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026/09/04 12:19:14</t>
+          <t>2026/09/06 18:02:45</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-32.8795316, -70.6078533</t>
+          <t>-32.8792316, -70.608855</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>-32.87953, -70.60785</t>
+          <t>-32.87923, -70.60886</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>01:10:51</t>
+          <t>00:27:47</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.09</v>
+        <v>5.64</v>
       </c>
       <c r="M49" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="N49" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3259,106 +3259,106 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026/09/04 11:10:33</t>
+          <t>2026/09/06 17:38:57</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-34.2057333, -70.6760183</t>
+          <t>-33.4362116, -70.6289783</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-34.20573, -70.67602</t>
+          <t>-33.43621, -70.62898</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026/09/04 11:26:16</t>
+          <t>2026/09/07 06:48:44</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-34.2064416, -70.67559</t>
+          <t>-33.44523, -70.6205066</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>-34.20644, -70.67559</t>
+          <t>-33.44523, -70.62051</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>00:15:43</t>
+          <t>13:09:47</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0.41</v>
+        <v>2.03</v>
       </c>
       <c r="M50" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="N50" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C51" t="n">
+        <v>10</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026/09/06 18:02:52</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-32.8792366, -70.6087966</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-32.87924, -70.60880</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2026/09/07 12:10:06</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>-32.8791583, -70.6088666</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>-32.87916, -70.60887</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>18:07:14</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M51" t="n">
         <v>6</v>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>2026/09/04 11:10:54</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>-33.361201, -70.811853</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>-33.36120, -70.81185</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>2026/09/04 12:39:20</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>-33.361468, -70.810482</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>-33.36147, -70.81048</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>01:28:26</t>
-        </is>
-      </c>
-      <c r="L51" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="M51" t="n">
-        <v>13</v>
-      </c>
       <c r="N51" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3377,57 +3377,57 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026/09/04 11:27:31</t>
+          <t>2026/09/06 21:06:07</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-34.2063816, -70.67567</t>
+          <t>-33.0873016, -71.3623533</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-34.20638, -70.67567</t>
+          <t>-33.08730, -71.36235</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026/09/04 11:58:52</t>
+          <t>2026/09/07 09:25:33</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-34.2056949, -70.676095</t>
+          <t>-33.08734, -71.3622766</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>-34.20569, -70.67610</t>
+          <t>-33.08734, -71.36228</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>00:31:21</t>
+          <t>12:19:26</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.25</v>
+        <v>0.02</v>
       </c>
       <c r="M52" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="N52" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3436,57 +3436,57 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026/09/04 11:33:18</t>
+          <t>2026/09/07 06:26:13</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-34.2050633, -70.6771616</t>
+          <t>-32.870245, -70.6803216</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-34.20506, -70.67716</t>
+          <t>-32.87024, -70.68032</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026/09/04 12:27:13</t>
+          <t>2026/09/07 07:41:35</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-34.0369933, -70.6828033</t>
+          <t>-33.35995, -70.8069466</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>-34.03699, -70.68280</t>
+          <t>-33.35995, -70.80695</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>00:53:55</t>
+          <t>01:15:22</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>24.08</v>
+        <v>73.16</v>
       </c>
       <c r="M53" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N53" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3495,57 +3495,57 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026/09/04 11:42:00</t>
+          <t>2026/09/07 07:41:48</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-34.579628, -70.961385</t>
+          <t>-33.3599366, -70.8071483</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-34.57963, -70.96139</t>
+          <t>-33.35994, -70.80715</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026/09/04 14:10:24</t>
+          <t>2026/09/07 09:29:03</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>-34.579682, -70.961533</t>
+          <t>-33.4558616, -71.3000133</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>-34.57968, -70.96153</t>
+          <t>-33.45586, -71.30001</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>02:28:24</t>
+          <t>01:47:15</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0.28</v>
+        <v>83.28</v>
       </c>
       <c r="M54" t="n">
-        <v>11</v>
+        <v>121</v>
       </c>
       <c r="N54" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3554,57 +3554,57 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026/09/04 12:00:07</t>
+          <t>2026/09/07 09:29:24</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-34.2051883, -70.6772783</t>
+          <t>-33.4562233, -71.3000583</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-34.20519, -70.67728</t>
+          <t>-33.45622, -71.30006</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026/09/04 12:13:17</t>
+          <t>2026/09/07 10:40:17</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-34.19004, -70.7094316</t>
+          <t>-33.45636, -71.3000366</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>-34.19004, -70.70943</t>
+          <t>-33.45636, -71.30004</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>00:13:10</t>
+          <t>01:10:53</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3.67</v>
+        <v>0.02</v>
       </c>
       <c r="M55" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="N55" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3613,47 +3613,47 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026/09/04 12:14:32</t>
+          <t>2026/09/07 10:41:06</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-34.1901333, -70.709375</t>
+          <t>-33.4561933, -71.3000583</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-34.19013, -70.70937</t>
+          <t>-33.45619, -71.30006</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026/09/04 15:05:00</t>
+          <t>2026/09/07 11:59:55</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>-33.087335, -71.3622966</t>
+          <t>-33.5064066, -71.2516466</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>-33.08734, -71.36230</t>
+          <t>-33.50641, -71.25165</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>02:50:28</t>
+          <t>01:18:49</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>187.85</v>
+        <v>7.61</v>
       </c>
       <c r="M56" t="n">
-        <v>136</v>
+        <v>69</v>
       </c>
       <c r="N56" t="n">
-        <v>81</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57">
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -3672,57 +3672,57 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026/09/04 12:16:13</t>
+          <t>2026/09/07 12:00:06</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-34.1901766, -70.7093633</t>
+          <t>-33.5063033, -71.251795</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-34.19018, -70.70936</t>
+          <t>-33.50630, -71.25180</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026/09/04 15:37:58</t>
+          <t>2026/09/07 13:06:05</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>-32.7432533, -70.7329599</t>
+          <t>-33.4558666, -71.3000266</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-32.74325, -70.73296</t>
+          <t>-33.45587, -71.30003</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>03:21:45</t>
+          <t>01:05:59</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>183.65</v>
+        <v>7.54</v>
       </c>
       <c r="M57" t="n">
-        <v>129</v>
+        <v>74</v>
       </c>
       <c r="N57" t="n">
-        <v>66</v>
+        <v>33</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -3731,47 +3731,47 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026/09/04 12:20:29</t>
+          <t>2026/09/07 13:06:22</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-32.87943, -70.6089449</t>
+          <t>-33.456225, -71.3000966</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-32.87943, -70.60894</t>
+          <t>-33.45623, -71.30010</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026/09/04 12:34:11</t>
+          <t>2026/09/07 19:00:44</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>-32.8851883, -70.611225</t>
+          <t>-32.7431866, -70.7330566</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>-32.88519, -70.61123</t>
+          <t>-32.74319, -70.73306</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>00:13:42</t>
+          <t>05:54:22</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0.91</v>
+        <v>150.55</v>
       </c>
       <c r="M58" t="n">
-        <v>38</v>
+        <v>124</v>
       </c>
       <c r="N58" t="n">
-        <v>17</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59">
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3790,57 +3790,57 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026/09/04 12:25:14</t>
+          <t>2026/09/07 13:10:10</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-33.4342933, -70.810605</t>
+          <t>-33.477215, -70.6979716</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-33.43429, -70.81060</t>
+          <t>-33.47722, -70.69797</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026/09/04 13:25:14</t>
+          <t>2026/09/07 13:20:37</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>-33.4560416, -71.3002116</t>
+          <t>-33.47627, -70.6983666</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>-33.45604, -71.30021</t>
+          <t>-33.47627, -70.69837</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>01:00:00</t>
+          <t>00:10:27</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>55.09</v>
+        <v>0.19</v>
       </c>
       <c r="M59" t="n">
-        <v>115</v>
+        <v>24</v>
       </c>
       <c r="N59" t="n">
-        <v>61</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -3849,57 +3849,57 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026/09/04 12:28:28</t>
+          <t>2026/09/07 13:20:53</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>-34.0417083, -70.6819866</t>
+          <t>-33.4762883, -70.6983966</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-34.04171, -70.68199</t>
+          <t>-33.47629, -70.69840</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026/09/04 15:19:53</t>
+          <t>2026/09/07 14:51:18</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>-32.7977333, -70.8874383</t>
+          <t>-33.5389833, -70.6432516</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>-32.79773, -70.88744</t>
+          <t>-33.53898, -70.64325</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>02:51:25</t>
+          <t>01:30:25</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>176.87</v>
+        <v>14.32</v>
       </c>
       <c r="M60" t="n">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="N60" t="n">
-        <v>68</v>
+        <v>33</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3908,57 +3908,57 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026/09/04 12:35:26</t>
+          <t>2026/09/07 13:45:02</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-32.8844316, -70.6111916</t>
+          <t>-34.3459883, -71.1257183</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-32.88443, -70.61119</t>
+          <t>-34.34599, -71.12572</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026/09/04 12:51:14</t>
+          <t>2026/09/07 14:13:02</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>-32.8826433, -70.610755</t>
+          <t>-34.3476749, -71.1277766</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>-32.88264, -70.61075</t>
+          <t>-34.34767, -71.12778</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>00:15:48</t>
+          <t>00:28:00</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="M61" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="N61" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3967,116 +3967,116 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026/09/04 12:39:56</t>
+          <t>2026/09/07 13:46:53</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>-33.361473, -70.81048</t>
+          <t>-34.34603, -71.12569</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-33.36147, -70.81048</t>
+          <t>-34.34603, -71.12569</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026/09/04 13:50:06</t>
+          <t>2026/09/07 14:07:25</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>-33.360643, -70.809636</t>
+          <t>-34.346422, -71.125933</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>-33.36064, -70.80964</t>
+          <t>-34.34642, -71.12593</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>01:10:10</t>
+          <t>00:20:32</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0.79</v>
+        <v>0.17</v>
       </c>
       <c r="M62" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="N62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026/09/04 12:51:44</t>
+          <t>2026/09/07 14:08:20</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-32.8836816, -70.6106666</t>
+          <t>-34.346349, -71.125925</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-32.88368, -70.61067</t>
+          <t>-34.34635, -71.12592</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026/09/04 14:25:07</t>
+          <t>2026/09/07 14:18:02</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>-32.8828883, -70.612345</t>
+          <t>-34.34672, -71.125939</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>-32.88289, -70.61235</t>
+          <t>-34.34672, -71.12594</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>01:33:23</t>
+          <t>00:09:42</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0.85</v>
+        <v>0.09</v>
       </c>
       <c r="M63" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="N63" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4085,44 +4085,44 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026/09/04 13:25:20</t>
+          <t>2026/09/07 14:14:17</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-33.456035, -71.3001716</t>
+          <t>-34.3485233, -71.127835</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-33.45603, -71.30017</t>
+          <t>-34.34852, -71.12784</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026/09/04 15:05:18</t>
+          <t>2026/09/07 14:42:19</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>-33.455895, -71.3000933</t>
+          <t>-34.351345, -71.12937</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>-33.45589, -71.30009</t>
+          <t>-34.35135, -71.12937</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>01:39:58</t>
+          <t>00:28:02</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0.03</v>
+        <v>0.83</v>
       </c>
       <c r="M64" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="N64" t="n">
         <v>9</v>
@@ -4131,188 +4131,188 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026/09/04 13:50:56</t>
+          <t>2026/09/07 14:18:20</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-33.360475, -70.80966599999999</t>
+          <t>-34.346794, -71.125936</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-33.36048, -70.80967</t>
+          <t>-34.34679, -71.12594</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026/09/04 14:02:59</t>
+          <t>2026/09/07 14:24:20</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>-33.360157, -70.80752</t>
+          <t>-34.34633, -71.125927</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>-33.36016, -70.80752</t>
+          <t>-34.34633, -71.12593</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>00:12:03</t>
+          <t>00:06:00</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0.23</v>
+        <v>0.1</v>
       </c>
       <c r="M65" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026/09/04 14:03:59</t>
+          <t>2026/09/07 14:24:28</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>-33.36016, -70.807185</t>
+          <t>-34.042722, -70.681703</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-33.36016, -70.80719</t>
+          <t>-34.04272, -70.68170</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026/09/09 14:27:06</t>
+          <t>2026/09/08 13:25:22</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>-33.359994, -70.807053</t>
+          <t>-34.041819, -70.681668</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80705</t>
+          <t>-34.04182, -70.68167</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>120:23:07</t>
+          <t>23:00:54</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="M66" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C67" t="n">
+        <v>4</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026/09/07 14:24:44</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-34.346277, -71.125924</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-34.34628, -71.12592</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2026/09/07 14:33:43</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>-34.346249, -71.125961</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>-34.34625, -71.12596</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>00:08:59</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M67" t="n">
         <v>3</v>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>2026/09/04 14:10:44</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>-34.579661, -70.961383</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>-34.57966, -70.96138</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>2026/09/04 14:53:15</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>-34.579224, -70.961619</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>-34.57922, -70.96162</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>00:42:31</t>
-        </is>
-      </c>
-      <c r="L67" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="M67" t="n">
-        <v>5</v>
-      </c>
       <c r="N67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4321,57 +4321,57 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026/09/04 14:26:22</t>
+          <t>2026/09/07 14:34:18</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>-32.883145, -70.6123633</t>
+          <t>-34.346318, -71.126003</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-32.88314, -70.61236</t>
+          <t>-34.34632, -71.12600</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026/09/04 14:58:54</t>
+          <t>2026/09/07 14:54:53</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>-32.8792216, -70.6088666</t>
+          <t>-34.346995, -71.126064</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>-32.87922, -70.60887</t>
+          <t>-34.34699, -71.12606</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>00:32:32</t>
+          <t>00:20:35</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.64</v>
+        <v>0.35</v>
       </c>
       <c r="M68" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="N68" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4380,116 +4380,116 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026/09/04 14:53:29</t>
+          <t>2026/09/07 14:43:34</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-34.579325, -70.96167</t>
+          <t>-34.3506066, -71.12932</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-34.57932, -70.96167</t>
+          <t>-34.35061, -71.12932</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026/09/04 15:56:36</t>
+          <t>2026/09/07 14:55:11</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>-34.579679, -70.961433</t>
+          <t>-34.3466316, -71.1265866</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>-34.57968, -70.96143</t>
+          <t>-34.34663, -71.12659</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>01:03:07</t>
+          <t>00:11:37</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M69" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="N69" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026/09/04 14:54:04</t>
+          <t>2026/09/07 14:52:14</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>-33.379638, -70.752649</t>
+          <t>-33.5384016, -70.6430566</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-33.37964, -70.75265</t>
+          <t>-33.53840, -70.64306</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026/09/04 15:00:23</t>
+          <t>2026/09/07 15:20:19</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>-33.379666, -70.752655</t>
+          <t>-33.4762516, -70.69833</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>-33.37967, -70.75266</t>
+          <t>-33.47625, -70.69833</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>00:06:19</t>
+          <t>00:28:05</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>13.35</v>
       </c>
       <c r="M70" t="n">
-        <v>1</v>
+        <v>106</v>
       </c>
       <c r="N70" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4498,116 +4498,116 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026/09/04 14:58:58</t>
+          <t>2026/09/07 14:55:18</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>-32.8792183, -70.6087966</t>
+          <t>-34.346855, -71.126061</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-32.87922, -70.60880</t>
+          <t>-34.34685, -71.12606</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026/09/04 16:16:52</t>
+          <t>2026/09/07 15:12:17</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>-32.8521266, -70.606735</t>
+          <t>-34.34598, -71.125749</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>-32.85213, -70.60674</t>
+          <t>-34.34598, -71.12575</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>01:17:54</t>
+          <t>00:16:59</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>12.88</v>
+        <v>0.23</v>
       </c>
       <c r="M71" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="N71" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026/09/04 15:01:00</t>
+          <t>2026/09/07 14:56:26</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>-33.379666, -70.752655</t>
+          <t>-34.3462733, -71.126005</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-33.37967, -70.75266</t>
+          <t>-34.34627, -71.12601</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026/09/04 15:06:33</t>
+          <t>2026/09/07 15:05:05</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>-33.379713, -70.75275</t>
+          <t>-34.3461549, -71.1255633</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>-33.37971, -70.75275</t>
+          <t>-34.34615, -71.12556</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>00:05:33</t>
+          <t>00:08:39</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="M72" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N72" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -4616,57 +4616,57 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026/09/04 15:05:11</t>
+          <t>2026/09/07 15:06:20</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>-33.0873233, -71.36232</t>
+          <t>-34.3464633, -71.12531</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-33.08732, -71.36232</t>
+          <t>-34.34646, -71.12531</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026/09/04 16:35:49</t>
+          <t>2026/09/07 18:30:43</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>-33.0880316, -71.363945</t>
+          <t>-32.8795316, -70.6081933</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>-33.08803, -71.36395</t>
+          <t>-32.87953, -70.60819</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>01:30:38</t>
+          <t>03:24:23</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0.63</v>
+        <v>217.83</v>
       </c>
       <c r="M73" t="n">
-        <v>13</v>
+        <v>136</v>
       </c>
       <c r="N73" t="n">
-        <v>11</v>
+        <v>71</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -4675,47 +4675,47 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026/09/04 15:06:33</t>
+          <t>2026/09/07 15:12:52</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>-33.4561249, -71.3006266</t>
+          <t>-34.346006, -71.125762</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-33.45612, -71.30063</t>
+          <t>-34.34601, -71.12576</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026/09/04 15:16:44</t>
+          <t>2026/09/08 08:53:32</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>-33.4539316, -71.3014783</t>
+          <t>-34.346557, -71.125393</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>-33.45393, -71.30148</t>
+          <t>-34.34656, -71.12539</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>00:10:11</t>
+          <t>17:40:40</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0.52</v>
+        <v>0.11</v>
       </c>
       <c r="M74" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="N74" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -4734,57 +4734,57 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026/09/04 15:17:59</t>
+          <t>2026/09/07 15:21:34</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>-33.4539333, -71.3027849</t>
+          <t>-33.476185, -70.6984216</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-33.45393, -71.30278</t>
+          <t>-33.47619, -70.69842</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026/09/04 15:30:02</t>
+          <t>2026/09/08 07:45:19</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>-33.4541833, -71.3038533</t>
+          <t>-33.4762716, -70.698355</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>-33.45418, -71.30385</t>
+          <t>-33.47627, -70.69836</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>00:12:03</t>
+          <t>16:23:45</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0.12</v>
+        <v>11.17</v>
       </c>
       <c r="M75" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="N75" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -4793,57 +4793,57 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026/09/04 15:18:29</t>
+          <t>2026/09/07 15:28:53</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-33.4362866, -70.629435</t>
+          <t>-33.366952, -70.685523</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-33.43629, -70.62944</t>
+          <t>-33.36695, -70.68552</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026/09/04 16:27:21</t>
+          <t>2026/09/07 16:36:26</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>-33.4209333, -70.617445</t>
+          <t>-33.367301, -70.696048</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>-33.42093, -70.61745</t>
+          <t>-33.36730, -70.69605</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>01:08:52</t>
+          <t>01:07:33</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="M76" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="N76" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -4852,47 +4852,47 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026/09/04 15:21:08</t>
+          <t>2026/09/07 16:35:07</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>-32.79761, -70.8870633</t>
+          <t>-33.0873233, -71.36235</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88706</t>
+          <t>-33.08732, -71.36235</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026/09/04 18:37:26</t>
+          <t>2026/09/07 20:51:29</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>-32.6608966, -70.71691</t>
+          <t>-33.0872983, -71.3622316</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>-32.66090, -70.71691</t>
+          <t>-33.08730, -71.36223</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>03:16:18</t>
+          <t>04:16:22</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>29.35</v>
+        <v>0.01</v>
       </c>
       <c r="M77" t="n">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="N77" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78">
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -4911,57 +4911,57 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026/09/04 15:23:10</t>
+          <t>2026/09/07 17:27:33</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>-33.360098, -70.80898</t>
+          <t>-32.838365, -70.955536</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-33.36010, -70.80898</t>
+          <t>-32.83837, -70.95554</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026/09/04 15:48:26</t>
+          <t>2026/09/08 12:34:32</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>-33.37969, -70.752779</t>
+          <t>-34.205318, -70.677524</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>-33.37969, -70.75278</t>
+          <t>-34.20532, -70.67752</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>00:25:16</t>
+          <t>19:06:59</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>5.69</v>
+        <v>205.09</v>
       </c>
       <c r="M78" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -4970,47 +4970,47 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026/09/04 15:31:17</t>
+          <t>2026/09/07 18:31:58</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>-33.4541566, -71.3037933</t>
+          <t>-32.8794533, -70.6089166</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-33.45416, -71.30379</t>
+          <t>-32.87945, -70.60892</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026/09/04 15:46:10</t>
+          <t>2026/09/07 19:36:36</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>-33.4539666, -71.3028216</t>
+          <t>-32.7977183, -70.88739</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>-33.45397, -71.30282</t>
+          <t>-32.79772, -70.88739</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>00:14:53</t>
+          <t>01:04:38</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0.09</v>
+        <v>47.17</v>
       </c>
       <c r="M79" t="n">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="N79" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
     </row>
     <row r="80">
@@ -5020,7 +5020,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5029,44 +5029,44 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026/09/04 15:39:13</t>
+          <t>2026/09/07 19:01:08</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>-32.7433633, -70.7327083</t>
+          <t>-32.7433483, -70.7326566</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-32.74336, -70.73271</t>
+          <t>-32.74335, -70.73266</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026/09/04 16:26:40</t>
+          <t>2026/09/07 19:13:22</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>-32.7441833, -70.730365</t>
+          <t>-32.7431783, -70.7296383</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>-32.74418, -70.73037</t>
+          <t>-32.74318, -70.72964</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>00:47:27</t>
+          <t>00:12:14</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0.24</v>
+        <v>0.36</v>
       </c>
       <c r="M80" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N80" t="n">
         <v>9</v>
@@ -5075,7 +5075,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -5088,116 +5088,116 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026/09/04 15:47:25</t>
+          <t>2026/09/07 19:14:37</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>-33.4538683, -71.3023783</t>
+          <t>-32.7432166, -70.729625</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-33.45387, -71.30238</t>
+          <t>-32.74322, -70.72962</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026/09/04 17:08:16</t>
+          <t>2026/09/08 07:25:00</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>-33.4747083, -70.6961166</t>
+          <t>-33.3599433, -70.8069966</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>-33.47471, -70.69612</t>
+          <t>-33.35994, -70.80700</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>01:20:51</t>
+          <t>12:10:23</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>67.94</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="M81" t="n">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="N81" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026/09/04 15:57:10</t>
+          <t>2026/09/07 19:37:51</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>-34.579653, -70.961436</t>
+          <t>-32.7976133, -70.88705</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-34.57965, -70.96144</t>
+          <t>-32.79761, -70.88705</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026/09/06 01:37:43</t>
+          <t>2026/09/07 19:58:39</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>-34.579718, -70.961362</t>
+          <t>-32.7976666, -70.887215</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>-34.57972, -70.96136</t>
+          <t>-32.79767, -70.88721</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>33:40:33</t>
+          <t>00:20:48</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0.01</v>
+        <v>7.86</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5206,57 +5206,57 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026/09/04 16:01:06</t>
+          <t>2026/09/07 19:59:00</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>-33.359945, -70.807106</t>
+          <t>-32.79761, -70.8870333</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-33.35995, -70.80711</t>
+          <t>-32.79761, -70.88703</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026/09/04 22:03:43</t>
+          <t>2026/09/08 07:29:24</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>-32.838471, -70.954864</t>
+          <t>-33.3599616, -70.806975</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>-32.83847, -70.95486</t>
+          <t>-33.35996, -70.80697</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>06:02:37</t>
+          <t>11:30:24</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>60.35</v>
+        <v>104.42</v>
       </c>
       <c r="M83" t="n">
-        <v>2</v>
+        <v>130</v>
       </c>
       <c r="N83" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5265,116 +5265,116 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026/09/04 16:17:32</t>
+          <t>2026/09/07 20:51:37</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>-32.8522233, -70.6075533</t>
+          <t>-33.0872183, -71.36218</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-32.85222, -70.60755</t>
+          <t>-33.08722, -71.36218</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026/09/04 17:03:08</t>
+          <t>2026/09/08 06:44:06</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>-32.879225, -70.6088783</t>
+          <t>-33.0872933, -71.362245</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>-32.87922, -70.60888</t>
+          <t>-33.08729, -71.36225</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>00:45:36</t>
+          <t>09:52:29</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>4.21</v>
+        <v>14.03</v>
       </c>
       <c r="M84" t="n">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="N84" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C85" t="n">
+        <v>2</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026/09/08 09:21:31</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>-34.34731, -71.125642</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-34.34731, -71.12564</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2026/09/08 10:21:02</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>-34.346529, -71.126182</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>-34.34653, -71.12618</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>00:59:31</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M85" t="n">
         <v>6</v>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>2026/09/04 16:27:55</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>-32.743235, -70.72964</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>-32.74323, -70.72964</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>2026/09/06 18:18:51</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>-32.7431899, -70.7296433</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>-32.74319, -70.72964</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>49:50:56</t>
-        </is>
-      </c>
-      <c r="L85" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="M85" t="n">
-        <v>18</v>
-      </c>
       <c r="N85" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5383,57 +5383,57 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026/09/04 16:28:36</t>
+          <t>2026/09/08 10:21:07</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>-33.4211999, -70.6180566</t>
+          <t>-34.346532, -71.126181</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-33.42120, -70.61806</t>
+          <t>-34.34653, -71.12618</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026/09/04 17:27:31</t>
+          <t>2026/09/08 10:51:28</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>-33.42472, -70.6233366</t>
+          <t>-34.346507, -71.125244</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>-33.42472, -70.62334</t>
+          <t>-34.34651, -71.12524</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>00:58:55</t>
+          <t>00:30:21</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0.63</v>
+        <v>0.33</v>
       </c>
       <c r="M86" t="n">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="N86" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5442,57 +5442,57 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026/09/04 16:36:46</t>
+          <t>2026/09/08 10:51:48</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>-33.0882033, -71.364255</t>
+          <t>-34.346526, -71.125237</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-33.08820, -71.36425</t>
+          <t>-34.34653, -71.12524</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026/09/04 18:23:21</t>
+          <t>2026/09/08 12:51:39</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>-33.0873516, -71.3623049</t>
+          <t>-34.347589, -71.127686</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>-33.08735, -71.36230</t>
+          <t>-34.34759, -71.12769</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>01:46:35</t>
+          <t>01:59:51</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.51</v>
+        <v>0.32</v>
       </c>
       <c r="M87" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="N87" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5501,41 +5501,41 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026/09/04 16:54:53</t>
+          <t>2026/09/08 11:12:57</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>-34.042633, -70.681756</t>
+          <t>-34.579665, -70.961414</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-34.04263, -70.68176</t>
+          <t>-34.57966, -70.96141</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026/09/06 00:59:49</t>
+          <t>2026/09/08 12:50:13</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>-34.042702, -70.681741</t>
+          <t>-34.579642, -70.961429</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>-34.04270, -70.68174</t>
+          <t>-34.57964, -70.96143</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>32:04:56</t>
+          <t>01:37:16</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -5547,129 +5547,129 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026/09/04 17:03:13</t>
+          <t>2026/09/08 12:50:16</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>-32.8792333, -70.6088083</t>
+          <t>-34.579664, -70.961403</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-32.87923, -70.60881</t>
+          <t>-34.57966, -70.96140</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026/09/04 17:49:34</t>
+          <t>2026/09/11 22:34:21</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>-32.8202099, -70.6144099</t>
+          <t>-34.579677, -70.96149</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>-32.82021, -70.61441</t>
+          <t>-34.57968, -70.96149</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>00:46:21</t>
+          <t>81:44:05</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>14.27</v>
+        <v>0.03</v>
       </c>
       <c r="M89" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026/09/04 17:09:31</t>
+          <t>2026/09/08 13:03:39</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>-33.47634, -70.6984516</t>
+          <t>-34.348853, -71.127667</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-33.47634, -70.69845</t>
+          <t>-34.34885, -71.12767</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026/09/04 19:22:04</t>
+          <t>2026/09/08 13:11:23</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>-33.3952233, -70.6225633</t>
+          <t>-34.348297, -71.127681</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>-33.39522, -70.62256</t>
+          <t>-34.34830, -71.12768</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>02:12:33</t>
+          <t>00:07:44</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>50.99</v>
+        <v>0.06</v>
       </c>
       <c r="M90" t="n">
-        <v>113</v>
+        <v>3</v>
       </c>
       <c r="N90" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -5678,57 +5678,57 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026/09/04 17:28:46</t>
+          <t>2026/09/08 13:25:32</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>-33.4298916, -70.6266716</t>
+          <t>-34.041832, -70.681694</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-33.42989, -70.62667</t>
+          <t>-34.04183, -70.68169</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026/09/04 17:55:10</t>
+          <t>2026/09/08 15:14:07</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>-33.43754, -70.6287766</t>
+          <t>-34.042664, -70.681724</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>-33.43754, -70.62878</t>
+          <t>-34.04266, -70.68172</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>00:26:24</t>
+          <t>01:48:35</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.93</v>
+        <v>0.15</v>
       </c>
       <c r="M91" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="N91" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -5737,293 +5737,293 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026/09/04 17:50:49</t>
+          <t>2026/09/08 13:31:35</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>-32.820565, -70.6140333</t>
+          <t>-34.348097, -71.127772</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-32.82057, -70.61403</t>
+          <t>-34.34810, -71.12777</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026/09/04 18:33:13</t>
+          <t>2026/09/08 13:46:25</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>-32.8792316, -70.609045</t>
+          <t>-34.346322, -71.1256</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>-32.87923, -70.60904</t>
+          <t>-34.34632, -71.12560</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>00:42:24</t>
+          <t>00:14:50</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>11.83</v>
+        <v>0.35</v>
       </c>
       <c r="M92" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="N92" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026/09/04 17:56:25</t>
+          <t>2026/09/08 13:47:25</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>-33.4363316, -70.628895</t>
+          <t>-34.346558, -71.125262</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-33.43633, -70.62889</t>
+          <t>-34.34656, -71.12526</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026/09/06 09:42:38</t>
+          <t>2026/09/08 13:55:43</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>-33.4359749, -70.6299933</t>
+          <t>-34.345942, -71.125755</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>-33.43597, -70.62999</t>
+          <t>-34.34594, -71.12575</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>39:46:13</t>
+          <t>00:08:18</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>55.39</v>
+        <v>0.08</v>
       </c>
       <c r="M93" t="n">
-        <v>138</v>
+        <v>4</v>
       </c>
       <c r="N93" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026/09/04 18:23:30</t>
+          <t>2026/09/08 13:56:22</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>-33.0873216, -71.362345</t>
+          <t>-34.345962, -71.125764</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-33.08732, -71.36235</t>
+          <t>-34.34596, -71.12576</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026/09/05 12:26:55</t>
+          <t>2026/09/11 23:01:38</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>-33.0873233, -71.3623383</t>
+          <t>-34.34603, -71.125731</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>-33.08732, -71.36234</t>
+          <t>-34.34603, -71.12573</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>18:03:25</t>
+          <t>81:05:16</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="M94" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026/09/04 18:33:44</t>
+          <t>2026/09/08 15:15:01</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>-32.8790849, -70.6094833</t>
+          <t>-34.042664, -70.68175</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-32.87908, -70.60948</t>
+          <t>-34.04266, -70.68175</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026/09/05 13:30:06</t>
+          <t>2026/09/08 15:26:28</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>-32.8321399, -70.6228783</t>
+          <t>-34.042648, -70.681753</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>-32.83214, -70.62288</t>
+          <t>-34.04265, -70.68175</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>18:56:22</t>
+          <t>00:11:27</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="N95" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026/09/04 18:38:41</t>
+          <t>2026/09/08 15:26:45</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>-32.6615966, -70.7172283</t>
+          <t>-34.042645, -70.681745</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-32.66160, -70.71723</t>
+          <t>-34.04265, -70.68175</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026/09/04 19:50:41</t>
+          <t>2026/09/11 22:57:48</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>-32.7977383, -70.8874283</t>
+          <t>-34.042613, -70.681788</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>-32.79774, -70.88743</t>
+          <t>-34.04261, -70.68179</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>01:12:00</t>
+          <t>79:31:03</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>29.32</v>
+        <v>0.01</v>
       </c>
       <c r="M96" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6032,57 +6032,57 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026/09/04 19:23:19</t>
+          <t>2026/09/08 16:19:10</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>-33.3994366, -70.6136916</t>
+          <t>-33.3599583, -70.8070683</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-33.39944, -70.61369</t>
+          <t>-33.35996, -70.80707</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026/09/04 19:56:41</t>
+          <t>2026/09/08 18:49:57</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>-33.4349183, -70.5737733</t>
+          <t>-32.7432316, -70.7328933</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>-33.43492, -70.57377</t>
+          <t>-32.74323, -70.73289</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>00:33:22</t>
+          <t>02:30:47</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>10.36</v>
+        <v>125.82</v>
       </c>
       <c r="M97" t="n">
-        <v>55</v>
+        <v>138</v>
       </c>
       <c r="N97" t="n">
-        <v>20</v>
+        <v>53</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6091,47 +6091,47 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026/09/04 19:51:56</t>
+          <t>2026/09/08 18:06:06</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>-32.7975916, -70.8870383</t>
+          <t>-32.8205016, -70.6143333</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-32.79759, -70.88704</t>
+          <t>-32.82050, -70.61433</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026/09/05 07:57:03</t>
+          <t>2026/09/08 18:42:10</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>-32.88315, -70.6123616</t>
+          <t>-32.7580149, -70.70204</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>-32.88315, -70.61236</t>
+          <t>-32.75801, -70.70204</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>12:05:07</t>
+          <t>00:36:04</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>42.04</v>
+        <v>12.65</v>
       </c>
       <c r="M98" t="n">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="N98" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="99">
@@ -6141,7 +6141,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6150,57 +6150,57 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026/09/04 19:57:56</t>
+          <t>2026/09/08 18:27:43</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>-33.4346516, -70.5738166</t>
+          <t>-33.3621483, -70.6701383</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-33.43465, -70.57382</t>
+          <t>-33.36215, -70.67014</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026/09/04 20:23:31</t>
+          <t>2026/09/08 19:03:48</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>-33.362115, -70.6700899</t>
+          <t>-33.4762116, -70.6982083</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>-33.36212, -70.67009</t>
+          <t>-33.47621, -70.69821</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>00:25:35</t>
+          <t>00:36:05</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>14.53</v>
+        <v>18.07</v>
       </c>
       <c r="M99" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="N99" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6209,57 +6209,57 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026/09/04 20:23:59</t>
+          <t>2026/09/08 18:42:33</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>-33.3621583, -70.6700733</t>
+          <t>-32.7582066, -70.7021599</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-33.36216, -70.67007</t>
+          <t>-32.75821, -70.70216</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026/09/04 21:11:53</t>
+          <t>2026/09/08 19:19:25</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>-33.4768333, -70.6988233</t>
+          <t>-32.8792133, -70.6090199</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>-33.47683, -70.69882</t>
+          <t>-32.87921, -70.60902</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>00:47:54</t>
+          <t>00:36:52</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>17.18</v>
+        <v>25.15</v>
       </c>
       <c r="M100" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="N100" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6268,57 +6268,57 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026/09/04 21:13:08</t>
+          <t>2026/09/08 18:50:27</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>-33.4761199, -70.6980899</t>
+          <t>-32.7433533, -70.7327166</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-33.47612, -70.69809</t>
+          <t>-32.74335, -70.73272</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026/09/05 09:35:05</t>
+          <t>2026/09/08 19:08:01</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>-33.47627, -70.6983233</t>
+          <t>-32.7431883, -70.729675</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>-33.47627, -70.69832</t>
+          <t>-32.74319, -70.72968</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>12:21:57</t>
+          <t>00:17:34</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0.06</v>
+        <v>0.36</v>
       </c>
       <c r="M101" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="N101" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6327,47 +6327,47 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026/09/04 22:03:47</t>
+          <t>2026/09/08 19:05:03</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>-32.838483, -70.954875</t>
+          <t>-33.4762333, -70.6984166</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-32.83848, -70.95488</t>
+          <t>-33.47623, -70.69842</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026/09/06 20:51:33</t>
+          <t>2026/09/09 07:44:57</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>-32.785413, -70.895182</t>
+          <t>-33.4762833, -70.6983599</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>-32.78541, -70.89518</t>
+          <t>-33.47628, -70.69836</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>46:47:46</t>
+          <t>12:39:54</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>37.72</v>
+        <v>11.17</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="103">
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6386,57 +6386,57 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026/09/07 13:06:22</t>
+          <t>2026/09/08 19:09:16</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>-33.456225, -71.3000966</t>
+          <t>-32.743165, -70.7297066</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-33.45623, -71.30010</t>
+          <t>-32.74316, -70.72971</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026/09/07 19:00:44</t>
+          <t>2026/09/09 07:18:24</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>-32.7431866, -70.7330566</t>
+          <t>-33.3599916, -70.8071333</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>-32.74319, -70.73306</t>
+          <t>-33.35999, -70.80713</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>05:54:22</t>
+          <t>12:09:08</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>150.55</v>
+        <v>89.91</v>
       </c>
       <c r="M103" t="n">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="N103" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6445,234 +6445,234 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026/09/07 13:46:53</t>
+          <t>2026/09/08 19:20:40</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>-34.34603, -71.12569</t>
+          <t>-32.8790916, -70.6094466</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-34.34603, -71.12569</t>
+          <t>-32.87909, -70.60945</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026/09/07 14:07:25</t>
+          <t>2026/09/08 19:31:12</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>-34.346422, -71.125933</t>
+          <t>-32.879155, -70.6093066</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>-34.34642, -71.12593</t>
+          <t>-32.87915, -70.60931</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>00:20:32</t>
+          <t>00:10:32</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0.17</v>
+        <v>0.01</v>
       </c>
       <c r="M104" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N104" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026/09/07 14:08:20</t>
+          <t>2026/09/08 19:31:50</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>-34.346349, -71.125925</t>
+          <t>-32.8792316, -70.6088183</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-34.34635, -71.12592</t>
+          <t>-32.87923, -70.60882</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026/09/07 14:18:02</t>
+          <t>2026/09/09 07:06:21</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>-34.34672, -71.125939</t>
+          <t>-32.879205, -70.60888</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>-34.34672, -71.12594</t>
+          <t>-32.87920, -70.60888</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>00:09:42</t>
+          <t>11:34:31</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0.09</v>
+        <v>10.18</v>
       </c>
       <c r="M105" t="n">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="N105" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026/09/07 14:18:20</t>
+          <t>2026/09/09 15:49:12</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>-34.346794, -71.125936</t>
+          <t>-34.2088533, -70.6784016</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-34.34679, -71.12594</t>
+          <t>-34.20885, -70.67840</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026/09/07 14:24:20</t>
+          <t>2026/09/09 16:25:24</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>-34.34633, -71.125927</t>
+          <t>-34.2041083, -70.6790099</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>-34.34633, -71.12593</t>
+          <t>-34.20411, -70.67901</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>00:06:00</t>
+          <t>00:36:12</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0.1</v>
+        <v>1.07</v>
       </c>
       <c r="M106" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="N106" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026/09/07 14:24:44</t>
+          <t>2026/09/09 16:25:31</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>-34.346277, -71.125924</t>
+          <t>-34.2041483, -70.679065</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-34.34628, -71.12592</t>
+          <t>-34.20415, -70.67906</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026/09/07 14:33:43</t>
+          <t>2026/09/09 16:38:53</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>-34.346249, -71.125961</t>
+          <t>-34.2058549, -70.6759933</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>-34.34625, -71.12596</t>
+          <t>-34.20585, -70.67599</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>00:08:59</t>
+          <t>00:13:22</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0.01</v>
+        <v>0.59</v>
       </c>
       <c r="M107" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="N107" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -6681,57 +6681,57 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026/09/07 14:34:18</t>
+          <t>2026/09/09 16:39:54</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>-34.346318, -71.126003</t>
+          <t>-34.2074116, -70.6760316</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-34.34632, -71.12600</t>
+          <t>-34.20741, -70.67603</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026/09/07 14:54:53</t>
+          <t>2026/09/09 17:16:48</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>-34.346995, -71.126064</t>
+          <t>-34.2045433, -70.6795616</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>-34.34699, -71.12606</t>
+          <t>-34.20454, -70.67956</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>00:20:35</t>
+          <t>00:36:54</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0.35</v>
+        <v>1.1</v>
       </c>
       <c r="M108" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="N108" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -6740,57 +6740,57 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026/09/07 14:43:34</t>
+          <t>2026/09/09 17:17:22</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>-34.3506066, -71.12932</t>
+          <t>-34.2051833, -70.68031</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-34.35061, -71.12932</t>
+          <t>-34.20518, -70.68031</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026/09/07 14:55:11</t>
+          <t>2026/09/09 17:43:00</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>-34.3466316, -71.1265866</t>
+          <t>-34.1900883, -70.70946</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>-34.34663, -71.12659</t>
+          <t>-34.19009, -70.70946</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>00:11:37</t>
+          <t>00:25:38</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0.5600000000000001</v>
+        <v>3.38</v>
       </c>
       <c r="M109" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="N109" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -6799,57 +6799,57 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026/09/07 14:55:18</t>
+          <t>2026/09/09 17:43:35</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>-34.346855, -71.126061</t>
+          <t>-34.19014, -70.7094049</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-34.34685, -71.12606</t>
+          <t>-34.19014, -70.70940</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026/09/07 15:12:17</t>
+          <t>2026/09/09 18:37:10</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>-34.34598, -71.125749</t>
+          <t>-34.1790849, -70.70823</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>-34.34598, -71.12575</t>
+          <t>-34.17908, -70.70823</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>00:16:59</t>
+          <t>00:53:35</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0.23</v>
+        <v>1.61</v>
       </c>
       <c r="M110" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="N110" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -6858,57 +6858,57 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026/09/07 14:56:26</t>
+          <t>2026/09/09 18:38:25</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>-34.3462733, -71.126005</t>
+          <t>-34.1796933, -70.7074966</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-34.34627, -71.12601</t>
+          <t>-34.17969, -70.70750</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026/09/07 15:05:05</t>
+          <t>2026/09/10 07:46:05</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>-34.3461549, -71.1255633</t>
+          <t>-34.2070316, -70.6771383</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>-34.34615, -71.12556</t>
+          <t>-34.20703, -70.67714</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>00:08:39</t>
+          <t>13:07:40</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0.04</v>
+        <v>5.68</v>
       </c>
       <c r="M111" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="N111" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -6917,57 +6917,57 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026/09/07 15:06:20</t>
+          <t>2026/09/09 18:48:26</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>-34.3464633, -71.12531</t>
+          <t>-33.4511266, -70.666315</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-34.34646, -71.12531</t>
+          <t>-33.45113, -70.66631</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026/09/07 18:30:43</t>
+          <t>2026/09/09 19:03:26</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>-32.8795316, -70.6081933</t>
+          <t>-33.4507766, -70.6663983</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>-32.87953, -70.60819</t>
+          <t>-33.45078, -70.66640</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>03:24:23</t>
+          <t>00:15:00</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>217.83</v>
+        <v>0.05</v>
       </c>
       <c r="M112" t="n">
-        <v>136</v>
+        <v>9</v>
       </c>
       <c r="N112" t="n">
-        <v>71</v>
+        <v>9</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -6976,57 +6976,57 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026/09/07 15:12:52</t>
+          <t>2026/09/09 19:04:41</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>-34.346006, -71.125762</t>
+          <t>-33.450825, -70.6666066</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-34.34601, -71.12576</t>
+          <t>-33.45083, -70.66661</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026/09/08 08:53:32</t>
+          <t>2026/09/09 19:33:12</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>-34.346557, -71.125393</t>
+          <t>-33.4762216, -70.6982983</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>-34.34656, -71.12539</t>
+          <t>-33.47622, -70.69830</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>17:40:40</t>
+          <t>00:28:31</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0.11</v>
+        <v>7.91</v>
       </c>
       <c r="M113" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="N113" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7035,57 +7035,57 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026/09/07 15:28:53</t>
+          <t>2026/09/09 19:34:28</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>-33.366952, -70.685523</t>
+          <t>-33.4761533, -70.6984083</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-33.36695, -70.68552</t>
+          <t>-33.47615, -70.69841</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026/09/07 16:36:26</t>
+          <t>2026/09/10 07:48:15</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>-33.367301, -70.696048</t>
+          <t>-33.47624, -70.69838</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>-33.36730, -70.69605</t>
+          <t>-33.47624, -70.69838</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>01:07:33</t>
+          <t>12:13:47</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.6</v>
+        <v>11.1</v>
       </c>
       <c r="M114" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="N114" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7094,57 +7094,57 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026/09/07 17:27:33</t>
+          <t>2026/09/10 16:42:50</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>-32.838365, -70.955536</t>
+          <t>-34.20484, -70.677505</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95554</t>
+          <t>-34.20484, -70.67750</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026/09/08 12:34:32</t>
+          <t>2026/09/10 17:35:40</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>-34.205318, -70.677524</t>
+          <t>-34.1796983, -70.7075316</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>-34.20532, -70.67752</t>
+          <t>-34.17970, -70.70753</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>19:06:59</t>
+          <t>00:52:50</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>205.09</v>
+        <v>5.39</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7153,57 +7153,57 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026/09/07 18:31:58</t>
+          <t>2026/09/10 17:36:55</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>-32.8794533, -70.6089166</t>
+          <t>-34.1797233, -70.7073566</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-32.87945, -70.60892</t>
+          <t>-34.17972, -70.70736</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026/09/07 19:36:36</t>
+          <t>2026/09/11 07:34:52</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>-32.7977183, -70.88739</t>
+          <t>-34.18998, -70.7092433</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>-32.79772, -70.88739</t>
+          <t>-34.18998, -70.70924</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>01:04:38</t>
+          <t>13:57:57</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>47.17</v>
+        <v>2.17</v>
       </c>
       <c r="M116" t="n">
-        <v>138</v>
+        <v>25</v>
       </c>
       <c r="N116" t="n">
-        <v>48</v>
+        <v>13</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7212,57 +7212,57 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026/09/07 19:01:08</t>
+          <t>2026/09/10 19:53:35</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>-32.7433483, -70.7326566</t>
+          <t>-32.7976283, -70.8870166</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-32.74335, -70.73266</t>
+          <t>-32.79763, -70.88702</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026/09/07 19:13:22</t>
+          <t>2026/09/11 06:18:20</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>-32.7431783, -70.7296383</t>
+          <t>-33.5398733, -70.7089816</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>-32.74318, -70.72964</t>
+          <t>-33.53987, -70.70898</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>00:12:14</t>
+          <t>10:24:45</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0.36</v>
+        <v>117.06</v>
       </c>
       <c r="M117" t="n">
-        <v>11</v>
+        <v>144</v>
       </c>
       <c r="N117" t="n">
-        <v>9</v>
+        <v>71</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7271,57 +7271,57 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026/09/07 19:14:37</t>
+          <t>2026/09/11 11:08:47</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>-32.7432166, -70.729625</t>
+          <t>-33.3649116, -70.4965666</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>-32.74322, -70.72962</t>
+          <t>-33.36491, -70.49657</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026/09/08 07:25:00</t>
+          <t>2026/09/11 11:23:05</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>-33.3599433, -70.8069966</t>
+          <t>-33.3588366, -70.4849283</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>-33.35994, -70.80700</t>
+          <t>-33.35884, -70.48493</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>12:10:23</t>
+          <t>00:14:18</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>90.84999999999999</v>
+        <v>1.52</v>
       </c>
       <c r="M118" t="n">
-        <v>102</v>
+        <v>39</v>
       </c>
       <c r="N118" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7330,44 +7330,44 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026/09/07 19:37:51</t>
+          <t>2026/09/11 11:24:20</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>-32.7976133, -70.88705</t>
+          <t>-33.3585916, -70.48524</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88705</t>
+          <t>-33.35859, -70.48524</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026/09/07 19:58:39</t>
+          <t>2026/09/11 18:19:57</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>-32.7976666, -70.887215</t>
+          <t>-33.5140783, -70.637485</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>-32.79767, -70.88721</t>
+          <t>-33.51408, -70.63748</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>00:20:48</t>
+          <t>06:55:37</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>7.86</v>
+        <v>33.06</v>
       </c>
       <c r="M119" t="n">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="N119" t="n">
         <v>26</v>
@@ -7376,247 +7376,247 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026/09/07 19:59:00</t>
+          <t>2026/09/11 16:46:08</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>-32.79761, -70.8870333</t>
+          <t>-33.4364066, -70.629565</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88703</t>
+          <t>-33.43641, -70.62956</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026/09/08 07:29:24</t>
+          <t>2026/09/11 22:46:08</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>-33.3599616, -70.806975</t>
+          <t>-33.4364066, -70.629565</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>-33.35996, -70.80697</t>
+          <t>-33.43641, -70.62956</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>11:30:24</t>
+          <t>06:00:00</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>104.42</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026/09/08 09:21:31</t>
+          <t>2026/09/11 17:59:30</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>-34.34731, -71.125642</t>
+          <t>-33.476155, -70.69845</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-34.34731, -71.12564</t>
+          <t>-33.47615, -70.69845</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026/09/08 10:21:02</t>
+          <t>2026/09/11 22:00:12</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>-34.346529, -71.126182</t>
+          <t>-33.476155, -70.69845</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>-34.34653, -71.12618</t>
+          <t>-33.47615, -70.69845</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>00:59:31</t>
+          <t>04:00:42</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026/09/08 10:21:07</t>
+          <t>2026/09/11 18:21:12</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>-34.346532, -71.126181</t>
+          <t>-33.5138849, -70.638245</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>-34.34653, -71.12618</t>
+          <t>-33.51388, -70.63824</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026/09/08 10:51:28</t>
+          <t>2026/09/11 22:57:33</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>-34.346507, -71.125244</t>
+          <t>-33.5138849, -70.638245</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>-34.34651, -71.12524</t>
+          <t>-33.51388, -70.63824</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>00:30:21</t>
+          <t>04:36:21</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026/09/08 10:51:48</t>
+          <t>2026/09/11 19:13:47</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>-34.346526, -71.125237</t>
+          <t>-32.7976, -70.887115</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-34.34653, -71.12524</t>
+          <t>-32.79760, -70.88711</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026/09/08 12:51:39</t>
+          <t>2026/09/11 21:14:47</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>-34.347589, -71.127686</t>
+          <t>-32.7975983, -70.8870416</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>-34.34759, -71.12769</t>
+          <t>-32.79760, -70.88704</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>01:59:51</t>
+          <t>02:01:00</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0.32</v>
+        <v>0.01</v>
       </c>
       <c r="M123" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7625,37 +7625,37 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026/09/08 11:12:57</t>
+          <t>2026/09/11 19:43:56</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>-34.579665, -70.961414</t>
+          <t>-32.8792, -70.608775</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>-34.57966, -70.96141</t>
+          <t>-32.87920, -70.60877</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026/09/08 12:50:13</t>
+          <t>2026/09/11 21:43:56</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>-34.579642, -70.961429</t>
+          <t>-32.8792, -70.608775</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>-34.57964, -70.96143</t>
+          <t>-32.87920, -70.60877</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>01:37:16</t>
+          <t>02:00:00</t>
         </is>
       </c>
       <c r="L124" t="n">
@@ -7671,11 +7671,11 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -7684,1108 +7684,46 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026/09/08 12:50:16</t>
+          <t>2026/09/11 20:01:03</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>-34.579664, -70.961403</t>
+          <t>-33.0872133, -71.3621916</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>-34.57966, -70.96140</t>
+          <t>-33.08721, -71.36219</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026/09/10 23:34:47</t>
+          <t>2026/09/11 22:01:03</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>-34.579677, -70.96149</t>
+          <t>-33.0872133, -71.3621916</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>-34.57968, -70.96149</t>
+          <t>-33.08721, -71.36219</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>58:44:31</t>
+          <t>02:00:00</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
         <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>LPR20251L02790031-SV</t>
-        </is>
-      </c>
-      <c r="C126" t="n">
-        <v>6</v>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>2026/09/08 13:03:39</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>-34.348853, -71.127667</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>-34.34885, -71.12767</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>2026/09/08 13:11:23</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>-34.348297, -71.127681</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>-34.34830, -71.12768</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>00:07:44</t>
-        </is>
-      </c>
-      <c r="L126" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="M126" t="n">
-        <v>3</v>
-      </c>
-      <c r="N126" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>LPR20251H02800016-STL</t>
-        </is>
-      </c>
-      <c r="C127" t="n">
-        <v>1</v>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>2026/09/08 13:25:32</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>-34.041832, -70.681694</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>-34.04183, -70.68169</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>2026/09/08 15:14:07</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>-34.042664, -70.681724</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>-34.04266, -70.68172</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>01:48:35</t>
-        </is>
-      </c>
-      <c r="L127" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="M127" t="n">
-        <v>4</v>
-      </c>
-      <c r="N127" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>LPR20251L02790031-SV</t>
-        </is>
-      </c>
-      <c r="C128" t="n">
-        <v>8</v>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>2026/09/08 13:31:35</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>-34.348097, -71.127772</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>-34.34810, -71.12777</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>2026/09/08 13:46:25</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>-34.346322, -71.1256</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>-34.34632, -71.12560</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>00:14:50</t>
-        </is>
-      </c>
-      <c r="L128" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="M128" t="n">
-        <v>4</v>
-      </c>
-      <c r="N128" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>LPR20251L02790031-SV</t>
-        </is>
-      </c>
-      <c r="C129" t="n">
-        <v>9</v>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>2026/09/08 13:47:25</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>-34.346558, -71.125262</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>-34.34656, -71.12526</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>2026/09/08 13:55:43</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>-34.345942, -71.125755</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>-34.34594, -71.12575</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>00:08:18</t>
-        </is>
-      </c>
-      <c r="L129" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="M129" t="n">
-        <v>4</v>
-      </c>
-      <c r="N129" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>LPR20251L02790031-SV</t>
-        </is>
-      </c>
-      <c r="C130" t="n">
-        <v>10</v>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>2026/09/08 13:56:22</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>-34.345962, -71.125764</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>-34.34596, -71.12576</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>2026/09/10 23:54:17</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>-34.345969, -71.125786</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>-34.34597, -71.12579</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>57:57:55</t>
-        </is>
-      </c>
-      <c r="L130" t="n">
-        <v>0</v>
-      </c>
-      <c r="M130" t="n">
-        <v>0</v>
-      </c>
-      <c r="N130" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>LPR20251H02800016-STL</t>
-        </is>
-      </c>
-      <c r="C131" t="n">
-        <v>2</v>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>2026/09/08 15:15:01</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>-34.042664, -70.68175</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>-34.04266, -70.68175</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>2026/09/08 15:26:28</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>-34.042648, -70.681753</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>-34.04265, -70.68175</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>00:11:27</t>
-        </is>
-      </c>
-      <c r="L131" t="n">
-        <v>0</v>
-      </c>
-      <c r="M131" t="n">
-        <v>3</v>
-      </c>
-      <c r="N131" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>JAC X200 SJTJ-50</t>
-        </is>
-      </c>
-      <c r="C132" t="n">
-        <v>10</v>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>2026/09/08 16:19:10</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>-33.3599583, -70.8070683</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>-33.35996, -70.80707</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>2026/09/08 18:49:57</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>-32.7432316, -70.7328933</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>-32.74323, -70.73289</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>02:30:47</t>
-        </is>
-      </c>
-      <c r="L132" t="n">
-        <v>125.82</v>
-      </c>
-      <c r="M132" t="n">
-        <v>138</v>
-      </c>
-      <c r="N132" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>JAC X200 SJTJ-50</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>11</v>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>2026/09/08 18:50:27</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>-32.7433533, -70.7327166</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>-32.74335, -70.73272</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>2026/09/08 19:08:01</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>-32.7431883, -70.729675</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>-32.74319, -70.72968</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>00:17:34</t>
-        </is>
-      </c>
-      <c r="L133" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="M133" t="n">
-        <v>13</v>
-      </c>
-      <c r="N133" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>JAC X200 SJTJ-50</t>
-        </is>
-      </c>
-      <c r="C134" t="n">
-        <v>12</v>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>2026/09/08 19:09:16</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>-32.743165, -70.7297066</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>-32.74316, -70.72971</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>2026/09/09 07:18:24</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>-33.3599916, -70.8071333</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>-33.35999, -70.80713</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>12:09:08</t>
-        </is>
-      </c>
-      <c r="L134" t="n">
-        <v>89.91</v>
-      </c>
-      <c r="M134" t="n">
-        <v>113</v>
-      </c>
-      <c r="N134" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>SUZUKI CARRY SKDB-52</t>
-        </is>
-      </c>
-      <c r="C135" t="n">
-        <v>14</v>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>2026/09/08 19:31:50</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>-32.8792316, -70.6088183</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>-32.87923, -70.60882</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>2026/09/09 07:06:21</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>-32.879205, -70.60888</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>-32.87920, -70.60888</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>11:34:31</t>
-        </is>
-      </c>
-      <c r="L135" t="n">
-        <v>10.18</v>
-      </c>
-      <c r="M135" t="n">
-        <v>63</v>
-      </c>
-      <c r="N135" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>SLP20250425120-AC01</t>
-        </is>
-      </c>
-      <c r="C136" t="n">
-        <v>1</v>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>2026/09/09 15:24:37</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>-33.359994, -70.807053</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>-33.35999, -70.80705</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>2026/09/10 23:09:54</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>-33.359969, -70.807032</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>-33.35997, -70.80703</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>31:45:17</t>
-        </is>
-      </c>
-      <c r="L136" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="M136" t="n">
-        <v>0</v>
-      </c>
-      <c r="N136" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>OPEL COMBO</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>1</v>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>2026/09/10 11:41:22</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>-33.3671166, -70.695655</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>-33.36712, -70.69566</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>2026/09/10 23:42:06</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>-33.3671166, -70.695655</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>-33.36712, -70.69566</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>12:00:44</t>
-        </is>
-      </c>
-      <c r="L137" t="n">
-        <v>0</v>
-      </c>
-      <c r="M137" t="n">
-        <v>0</v>
-      </c>
-      <c r="N137" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
-        </is>
-      </c>
-      <c r="C138" t="n">
-        <v>14</v>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>2026/09/10 17:36:55</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>-34.1797233, -70.7073566</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>-34.17972, -70.70736</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>2026/09/10 23:37:12</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>-34.1797233, -70.7073566</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>-34.17972, -70.70736</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>06:00:17</t>
-        </is>
-      </c>
-      <c r="L138" t="n">
-        <v>0</v>
-      </c>
-      <c r="M138" t="n">
-        <v>0</v>
-      </c>
-      <c r="N138" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>SUZUKI CARRY SKDB-52</t>
-        </is>
-      </c>
-      <c r="C139" t="n">
-        <v>12</v>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>2026/09/10 17:47:06</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>-32.8792399, -70.6088066</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>-32.87924, -70.60881</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>2026/09/10 23:47:06</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>-32.8792399, -70.6088066</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>-32.87924, -70.60881</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>06:00:00</t>
-        </is>
-      </c>
-      <c r="L139" t="n">
-        <v>0</v>
-      </c>
-      <c r="M139" t="n">
-        <v>0</v>
-      </c>
-      <c r="N139" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
-        </is>
-      </c>
-      <c r="C140" t="n">
-        <v>2</v>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>2026/09/10 19:40:13</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>-33.4373266, -70.6293133</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>-33.43733, -70.62931</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>2026/09/10 23:40:33</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>-33.4373266, -70.6293133</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>-33.43733, -70.62931</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>04:00:20</t>
-        </is>
-      </c>
-      <c r="L140" t="n">
-        <v>0</v>
-      </c>
-      <c r="M140" t="n">
-        <v>0</v>
-      </c>
-      <c r="N140" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
-        </is>
-      </c>
-      <c r="C141" t="n">
-        <v>10</v>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>2026/09/10 19:42:31</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>-33.4761716, -70.698385</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>-33.47617, -70.69839</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>2026/09/10 23:43:06</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>-33.476175, -70.6984333</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>-33.47617, -70.69843</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>04:00:35</t>
-        </is>
-      </c>
-      <c r="L141" t="n">
-        <v>0</v>
-      </c>
-      <c r="M141" t="n">
-        <v>0</v>
-      </c>
-      <c r="N141" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
-        </is>
-      </c>
-      <c r="C142" t="n">
-        <v>19</v>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>2026/09/10 19:53:35</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>-32.7976283, -70.8870166</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>-32.79763, -70.88702</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>2026/09/10 23:54:59</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>-32.7976283, -70.8870166</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>-32.79763, -70.88702</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>04:01:24</t>
-        </is>
-      </c>
-      <c r="L142" t="n">
-        <v>0</v>
-      </c>
-      <c r="M142" t="n">
-        <v>0</v>
-      </c>
-      <c r="N142" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>JAC X200 SJTJ-50</t>
-        </is>
-      </c>
-      <c r="C143" t="n">
-        <v>12</v>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>2026/09/10 20:41:03</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>-32.7431966, -70.7296633</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>-32.74320, -70.72966</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>2026/09/10 22:41:28</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>-32.7431149, -70.7297283</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>-32.74311, -70.72973</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>02:00:25</t>
-        </is>
-      </c>
-      <c r="L143" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="M143" t="n">
-        <v>0</v>
-      </c>
-      <c r="N143" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8837,16 +7775,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1691.29</v>
+        <v>1882.83</v>
       </c>
       <c r="C2" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3">
@@ -8856,13 +7794,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>722.12</v>
+        <v>747.37</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>15</v>
@@ -8875,10 +7813,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>925.05</v>
+        <v>971.65</v>
       </c>
       <c r="C4" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -8894,13 +7832,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1328.95</v>
+        <v>1317.07</v>
       </c>
       <c r="C5" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>138</v>
@@ -8951,13 +7889,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
         <v>5</v>
@@ -8989,16 +7927,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.82</v>
+        <v>1.08</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -9065,10 +8003,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1407.92</v>
+        <v>1431.08</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -9084,10 +8022,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>365.62</v>
+        <v>380.82</v>
       </c>
       <c r="C15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
@@ -9103,16 +8041,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25.32</v>
+        <v>89.06</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17">
@@ -9122,16 +8060,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -9147,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -9160,16 +8098,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1101.1</v>
+        <v>1262.73</v>
       </c>
       <c r="C19" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -855,7 +855,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026/09/11 22:31:27</t>
+          <t>2026/09/11 23:31:54</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>165:59:50</t>
+          <t>167:00:17</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/09/11 22:41:02</t>
+          <t>2026/09/11 23:41:02</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>165:58:56</t>
+          <t>166:58:56</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026/09/11 22:56:10</t>
+          <t>2026/09/11 23:56:10</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>165:59:59</t>
+          <t>166:59:59</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026/09/11 22:34:21</t>
+          <t>2026/09/11 23:34:40</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>81:44:05</t>
+          <t>82:44:24</t>
         </is>
       </c>
       <c r="L89" t="n">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026/09/11 22:57:48</t>
+          <t>2026/09/11 23:57:51</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>79:31:03</t>
+          <t>80:31:06</t>
         </is>
       </c>
       <c r="L96" t="n">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026/09/11 21:14:47</t>
+          <t>2026/09/11 23:14:47</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>02:01:00</t>
+          <t>04:01:00</t>
         </is>
       </c>
       <c r="L123" t="n">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026/09/11 21:43:56</t>
+          <t>2026/09/11 23:43:56</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L124" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,13 +446,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N125"/>
+  <dimension ref="A1:N127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Desde : 2026/09/05 04:00:00   Hasta : 2026/09/12 03:59:59</t>
+          <t>Desde : 2026/09/06 04:00:00   Hasta : 2026/09/13 03:59:59</t>
         </is>
       </c>
     </row>
@@ -545,17 +545,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026/09/05 00:01:19</t>
+          <t>2026/09/06 00:01:38</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-34.346043, -71.125812</t>
+          <t>-34.346093, -71.125792</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-34.34604, -71.12581</t>
+          <t>-34.34609, -71.12579</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -575,11 +575,11 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>61:44:47</t>
+          <t>37:44:28</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="M4" t="n">
         <v>1</v>
@@ -604,7 +604,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026/09/05 00:01:57</t>
+          <t>2026/09/06 00:01:57</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>33:40:41</t>
+          <t>09:40:41</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -663,7 +663,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026/09/05 00:11:38</t>
+          <t>2026/09/06 00:11:51</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -678,26 +678,26 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026/09/11 23:06:39</t>
+          <t>2026/09/12 23:11:38</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-34.205326, -70.677367</t>
+          <t>-34.205371, -70.67735</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-34.20533, -70.67737</t>
+          <t>-34.20537, -70.67735</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>166:55:01</t>
+          <t>166:59:47</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LPR20251T02900038-RTN</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -717,58 +717,58 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026/09/05 00:23:37</t>
+          <t>2026/09/06 00:14:03</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-34.876447, -71.12707</t>
+          <t>-32.79761, -70.88709</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-34.87645, -71.12707</t>
+          <t>-32.79761, -70.88709</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026/09/07 01:24:55</t>
+          <t>2026/09/06 11:18:46</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-34.876432, -71.127131</t>
+          <t>-32.79573, -70.8201666</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-34.87643, -71.12713</t>
+          <t>-32.79573, -70.82017</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>49:01:18</t>
+          <t>11:04:43</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.03</v>
+        <v>9.68</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -776,58 +776,58 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026/09/05 00:25:37</t>
+          <t>2026/09/06 00:21:18</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-33.359994, -70.807041</t>
+          <t>-33.4762066, -70.6984716</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80704</t>
+          <t>-33.47621, -70.69847</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026/09/09 14:27:06</t>
+          <t>2026/09/07 09:06:46</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-33.359994, -70.807053</t>
+          <t>-33.476265, -70.6983216</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80705</t>
+          <t>-33.47626, -70.69832</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>110:01:29</t>
+          <t>32:45:28</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.03</v>
+        <v>56.18</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LPR20251V02900023-LL</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -835,58 +835,58 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026/09/05 00:31:37</t>
+          <t>2026/09/06 00:21:43</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-33.899796, -71.429428</t>
+          <t>-33.0872566, -71.3621933</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-33.89980, -71.42943</t>
+          <t>-33.08726, -71.36219</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026/09/11 23:31:54</t>
+          <t>2026/09/06 15:23:37</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-33.899886, -71.429534</t>
+          <t>-33.0582133, -71.3724133</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-33.89989, -71.42953</t>
+          <t>-33.05821, -71.37241</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>167:00:17</t>
+          <t>15:01:54</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.01</v>
+        <v>5</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>LPR20251T02900038-RTN</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -894,58 +894,58 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026/09/05 00:32:53</t>
+          <t>2026/09/06 00:23:26</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-32.7430849, -70.7297799</t>
+          <t>-34.87659, -71.127088</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-32.74308, -70.72978</t>
+          <t>-34.87659, -71.12709</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/09/06 18:18:51</t>
+          <t>2026/09/07 01:24:55</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-32.7431899, -70.7296433</t>
+          <t>-34.876432, -71.127131</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-32.74319, -70.72964</t>
+          <t>-34.87643, -71.12713</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>41:45:58</t>
+          <t>25:01:29</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.44</v>
+        <v>0.02</v>
       </c>
       <c r="M10" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>LPR20251V02900023-LL</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -953,46 +953,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026/09/05 00:33:21</t>
+          <t>2026/09/06 00:31:38</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-32.779806, -70.979927</t>
+          <t>-33.899796, -71.429428</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-32.77981, -70.97993</t>
+          <t>-33.89980, -71.42943</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026/09/06 20:51:33</t>
+          <t>2026/09/12 22:31:38</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-32.785413, -70.895182</t>
+          <t>-33.899848, -71.429508</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-32.78541, -70.89518</t>
+          <t>-33.89985, -71.42951</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>44:18:12</t>
+          <t>166:00:00</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>30.79</v>
+        <v>0.02</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1004,7 +1004,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1017,53 +1017,53 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026/09/05 00:39:42</t>
+          <t>2026/09/06 00:32:53</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-32.8792316, -70.6088916</t>
+          <t>-32.7430849, -70.7297799</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-32.87923, -70.60889</t>
+          <t>-32.74308, -70.72978</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026/09/05 13:30:06</t>
+          <t>2026/09/06 18:18:51</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-32.8321399, -70.6228783</t>
+          <t>-32.7431899, -70.7296433</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-32.83214, -70.62288</t>
+          <t>-32.74319, -70.72964</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>12:50:24</t>
+          <t>17:45:58</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>8.27</v>
+        <v>0.44</v>
       </c>
       <c r="M12" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="N12" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1076,53 +1076,53 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026/09/05 00:40:53</t>
+          <t>2026/09/06 00:38:11</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-33.087275, -71.3622416</t>
+          <t>-32.8792633, -70.6087649</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-33.08727, -71.36224</t>
+          <t>-32.87926, -70.60876</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026/09/05 12:26:55</t>
+          <t>2026/09/06 09:58:46</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-33.0873233, -71.3623383</t>
+          <t>-32.8813949, -70.611115</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-33.08732, -71.36234</t>
+          <t>-32.88139, -70.61111</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>11:46:02</t>
+          <t>09:20:35</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.02</v>
+        <v>1.58</v>
       </c>
       <c r="M13" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="N13" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LPR20251E02900022</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1135,53 +1135,53 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026/09/05 00:42:06</t>
+          <t>2026/09/06 00:39:39</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-33.36765, -70.697163</t>
+          <t>-33.360041, -70.807078</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-33.36765, -70.69716</t>
+          <t>-33.36004, -70.80708</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/09/11 23:41:02</t>
+          <t>2026/09/09 14:27:06</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-33.36765, -70.697163</t>
+          <t>-33.359994, -70.807053</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-33.36765, -70.69716</t>
+          <t>-33.35999, -70.80705</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>166:58:56</t>
+          <t>85:47:27</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>LPR20251E02900022</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1194,53 +1194,53 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026/09/05 00:46:27</t>
+          <t>2026/09/06 00:42:06</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-34.20537, -70.677421</t>
+          <t>-33.36765, -70.697163</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-34.20537, -70.67742</t>
+          <t>-33.36765, -70.69716</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/09/07 02:49:01</t>
+          <t>2026/09/12 22:41:10</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-34.205421, -70.677247</t>
+          <t>-33.36765, -70.697163</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-34.20542, -70.67725</t>
+          <t>-33.36765, -70.69716</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>50:02:34</t>
+          <t>165:59:04</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1253,41 +1253,41 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026/09/05 00:55:26</t>
+          <t>2026/09/06 00:46:50</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-34.042677, -70.681769</t>
+          <t>-34.205316, -70.677272</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-34.04268, -70.68177</t>
+          <t>-34.20532, -70.67727</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/09/06 00:59:49</t>
+          <t>2026/09/07 02:49:01</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-34.042702, -70.681741</t>
+          <t>-34.205421, -70.677247</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-34.04270, -70.68174</t>
+          <t>-34.20542, -70.67725</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>24:04:23</t>
+          <t>26:02:11</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -1299,7 +1299,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LPR20251T02800022</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1312,37 +1312,37 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026/09/05 00:56:11</t>
+          <t>2026/09/06 00:55:09</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-33.367244, -70.69677</t>
+          <t>-34.042677, -70.681769</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-33.36724, -70.69677</t>
+          <t>-34.04268, -70.68177</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026/09/11 23:56:10</t>
+          <t>2026/09/06 00:59:49</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-33.367244, -70.69677</t>
+          <t>-34.042702, -70.681741</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-33.36724, -70.69677</t>
+          <t>-34.04270, -70.68174</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>166:59:59</t>
+          <t>00:04:40</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -1358,7 +1358,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>LPR20251T02800022</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1371,41 +1371,41 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026/09/05 00:57:08</t>
+          <t>2026/09/06 00:56:11</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-34.579653, -70.961436</t>
+          <t>-33.367244, -70.69677</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-34.57965, -70.96144</t>
+          <t>-33.36724, -70.69677</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026/09/06 01:37:43</t>
+          <t>2026/09/12 22:56:08</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-34.579718, -70.961362</t>
+          <t>-33.367244, -70.69677</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-34.57972, -70.96136</t>
+          <t>-33.36724, -70.69677</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>24:40:35</t>
+          <t>165:59:57</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1417,7 +1417,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1425,58 +1425,58 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026/09/05 01:04:45</t>
+          <t>2026/09/06 00:57:28</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-33.3672483, -70.6957066</t>
+          <t>-34.579653, -70.961436</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-33.36725, -70.69571</t>
+          <t>-34.57965, -70.96144</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026/09/10 11:40:07</t>
+          <t>2026/09/06 01:37:43</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-33.367095, -70.695535</t>
+          <t>-34.579718, -70.961362</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-33.36709, -70.69554</t>
+          <t>-34.57972, -70.96136</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>130:35:22</t>
+          <t>00:40:15</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>25.32</v>
+        <v>0.01</v>
       </c>
       <c r="M19" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1489,112 +1489,112 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026/09/05 01:15:29</t>
+          <t>2026/09/06 01:04:45</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-33.4761866, -70.6983983</t>
+          <t>-33.3672483, -70.6957066</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-33.47619, -70.69840</t>
+          <t>-33.36725, -70.69571</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026/09/05 09:35:05</t>
+          <t>2026/09/10 11:40:07</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-33.47627, -70.6983233</t>
+          <t>-33.367095, -70.695535</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-33.47627, -70.69832</t>
+          <t>-33.36709, -70.69554</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>08:19:36</t>
+          <t>106:35:22</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0.03</v>
+        <v>25.32</v>
       </c>
       <c r="M20" t="n">
-        <v>8</v>
+        <v>116</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026/09/06 01:57:15</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-34.042702, -70.681741</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-34.04270, -70.68174</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026/09/07 09:26:29</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-34.042567, -70.681769</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-34.04257, -70.68177</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>31:29:14</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026/09/05 01:52:42</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>-32.7975916, -70.8870383</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-32.79759, -70.88704</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2026/09/05 07:57:03</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-32.88315, -70.6123616</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>-32.88315, -70.61236</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>06:04:21</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
-        <v>42.04</v>
-      </c>
-      <c r="M21" t="n">
-        <v>108</v>
-      </c>
       <c r="N21" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1607,57 +1607,57 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026/09/05 07:58:18</t>
+          <t>2026/09/06 02:35:12</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-32.88312, -70.61235</t>
+          <t>-34.579718, -70.961362</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-32.88312, -70.61235</t>
+          <t>-34.57972, -70.96136</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026/09/05 08:07:56</t>
+          <t>2026/09/07 15:17:14</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-32.8826383, -70.610755</t>
+          <t>-34.579702, -70.961411</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-32.88264, -70.61075</t>
+          <t>-34.57970, -70.96141</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>00:09:38</t>
+          <t>36:42:02</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0.2</v>
+        <v>0.79</v>
       </c>
       <c r="M22" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1666,53 +1666,53 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026/09/05 08:08:53</t>
+          <t>2026/09/06 09:43:53</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-32.88354, -70.6105233</t>
+          <t>-33.4365366, -70.6295316</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-32.88354, -70.61052</t>
+          <t>-33.43654, -70.62953</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026/09/05 12:25:44</t>
+          <t>2026/09/06 12:47:48</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-32.88288, -70.6123549</t>
+          <t>-33.5984266, -70.525295</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-32.88288, -70.61235</t>
+          <t>-33.59843, -70.52529</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>04:16:51</t>
+          <t>03:03:55</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0.3</v>
+        <v>22.4</v>
       </c>
       <c r="M23" t="n">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="N23" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1725,53 +1725,53 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026/09/05 09:35:14</t>
+          <t>2026/09/06 10:00:01</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-33.4763216, -70.6983783</t>
+          <t>-32.881215, -70.611425</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-33.47632, -70.69838</t>
+          <t>-32.88121, -70.61142</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026/09/05 10:06:33</t>
+          <t>2026/09/06 10:42:57</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-33.3622916, -70.670125</t>
+          <t>-32.829235, -70.6114849</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-33.36229, -70.67012</t>
+          <t>-32.82923, -70.61148</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>00:31:19</t>
+          <t>00:42:56</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>18.67</v>
+        <v>11.52</v>
       </c>
       <c r="M24" t="n">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="N24" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1784,57 +1784,57 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026/09/05 10:07:01</t>
+          <t>2026/09/06 10:43:19</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-33.3621366, -70.6701166</t>
+          <t>-32.8296299, -70.6116466</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-33.36214, -70.67012</t>
+          <t>-32.82963, -70.61165</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026/09/05 18:19:44</t>
+          <t>2026/09/06 11:18:17</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-33.47629, -70.698265</t>
+          <t>-32.8792083, -70.6089216</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-33.47629, -70.69827</t>
+          <t>-32.87921, -70.60892</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>08:12:43</t>
+          <t>00:34:58</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>18.06</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="N25" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1843,57 +1843,57 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026/09/05 12:26:59</t>
+          <t>2026/09/06 11:14:45</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-32.883165, -70.6123866</t>
+          <t>-32.838394, -70.955539</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-32.88316, -70.61239</t>
+          <t>-32.83839, -70.95554</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026/09/05 13:46:42</t>
+          <t>2026/09/06 20:51:33</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-32.7977016, -70.8874016</t>
+          <t>-32.785413, -70.895182</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-32.79770, -70.88740</t>
+          <t>-32.78541, -70.89518</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>01:19:43</t>
+          <t>09:36:48</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>49.24</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1902,41 +1902,41 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026/09/05 12:27:22</t>
+          <t>2026/09/06 11:18:55</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-33.0873383, -71.3623383</t>
+          <t>-32.87904, -70.6094516</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-33.08734, -71.36234</t>
+          <t>-32.87904, -70.60945</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026/09/05 20:21:01</t>
+          <t>2026/09/06 11:30:15</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-33.0873766, -71.36229</t>
+          <t>-32.8792033, -70.6088833</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-33.08738, -71.36229</t>
+          <t>-32.87920, -70.60888</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>07:53:39</t>
+          <t>00:11:20</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="M27" t="n">
         <v>6</v>
@@ -1948,7 +1948,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1961,47 +1961,47 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026/09/05 13:31:21</t>
+          <t>2026/09/06 11:19:05</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-32.8313683, -70.6160649</t>
+          <t>-32.7958166, -70.8201116</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-32.83137, -70.61606</t>
+          <t>-32.79582, -70.82011</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026/09/05 13:46:31</t>
+          <t>2026/09/06 11:35:26</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-32.8213499, -70.6154616</t>
+          <t>-32.7979433, -70.8272549</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-32.82135, -70.61546</t>
+          <t>-32.79794, -70.82725</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>00:15:10</t>
+          <t>00:16:21</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>5.66</v>
+        <v>0.72</v>
       </c>
       <c r="M28" t="n">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="N28" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2020,47 +2020,47 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026/09/05 13:46:39</t>
+          <t>2026/09/06 11:30:20</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-32.8214033, -70.6154666</t>
+          <t>-32.8792066, -70.6088383</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-32.82140, -70.61547</t>
+          <t>-32.87921, -70.60884</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026/09/05 14:31:32</t>
+          <t>2026/09/06 11:54:27</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-32.8792099, -70.6089166</t>
+          <t>-32.87735, -70.6095066</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-32.87921, -70.60892</t>
+          <t>-32.87735, -70.60951</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>00:44:53</t>
+          <t>00:24:07</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>9.83</v>
+        <v>0.85</v>
       </c>
       <c r="M29" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="N29" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2079,53 +2079,53 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026/09/05 13:47:45</t>
+          <t>2026/09/06 11:36:41</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-32.7975933, -70.88708</t>
+          <t>-32.7962016, -70.8278933</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-32.79759, -70.88708</t>
+          <t>-32.79620, -70.82789</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026/09/05 17:01:45</t>
+          <t>2026/09/06 11:54:07</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-32.7554033, -70.724555</t>
+          <t>-32.7677633, -70.8336683</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-32.75540, -70.72455</t>
+          <t>-32.76776, -70.83367</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>03:14:00</t>
+          <t>00:17:26</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>18.63</v>
+        <v>3.5</v>
       </c>
       <c r="M30" t="n">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="N30" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2138,53 +2138,53 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026/09/05 14:32:20</t>
+          <t>2026/09/06 11:54:28</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-32.8790733, -70.6093966</t>
+          <t>-32.7681516, -70.8333683</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-32.87907, -70.60940</t>
+          <t>-32.76815, -70.83337</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026/09/05 18:38:02</t>
+          <t>2026/09/06 12:07:44</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-32.8792566, -70.6088116</t>
+          <t>-32.7977249, -70.8874466</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-32.87926, -70.60881</t>
+          <t>-32.79772, -70.88745</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>04:05:42</t>
+          <t>00:13:16</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>10.8</v>
+        <v>6.26</v>
       </c>
       <c r="M31" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="N31" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2197,53 +2197,53 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026/09/05 17:03:00</t>
+          <t>2026/09/06 11:54:49</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-32.7519866, -70.7233349</t>
+          <t>-32.8774116, -70.6094399</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-32.75199, -70.72333</t>
+          <t>-32.87741, -70.60944</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026/09/05 18:12:38</t>
+          <t>2026/09/06 12:04:32</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-32.7548899, -70.7276849</t>
+          <t>-32.8791933, -70.6088333</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-32.75489, -70.72768</t>
+          <t>-32.87919, -70.60883</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>01:09:38</t>
+          <t>00:09:43</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.92</v>
+        <v>0.88</v>
       </c>
       <c r="M32" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2256,57 +2256,57 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026/09/05 18:14:17</t>
+          <t>2026/09/06 12:05:47</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-32.7548933, -70.7280533</t>
+          <t>-32.8791933, -70.6088266</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-32.75489, -70.72805</t>
+          <t>-32.87919, -70.60883</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026/09/05 19:09:56</t>
+          <t>2026/09/06 13:37:21</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-32.7977333, -70.8874249</t>
+          <t>-33.5490416, -70.8405516</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-32.79773, -70.88742</t>
+          <t>-33.54904, -70.84055</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>00:55:39</t>
+          <t>01:31:34</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>18.22</v>
+        <v>100.35</v>
       </c>
       <c r="M33" t="n">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="N33" t="n">
-        <v>37</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2315,57 +2315,57 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026/09/05 18:20:59</t>
+          <t>2026/09/06 12:08:54</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-33.4762383, -70.6983866</t>
+          <t>-32.79762, -70.8870983</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-33.47624, -70.69839</t>
+          <t>-32.79762, -70.88710</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026/09/07 09:06:46</t>
+          <t>2026/09/06 16:15:53</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-33.476265, -70.6983216</t>
+          <t>-32.7977583, -70.887415</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-33.47626, -70.69832</t>
+          <t>-32.79776, -70.88742</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>38:45:47</t>
+          <t>04:06:59</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>56.18</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>118</v>
+        <v>63</v>
       </c>
       <c r="N34" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2374,53 +2374,53 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026/09/05 18:38:11</t>
+          <t>2026/09/06 12:48:02</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-32.8792633, -70.6087649</t>
+          <t>-33.59851, -70.52519</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-32.87926, -70.60876</t>
+          <t>-33.59851, -70.52519</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026/09/06 09:58:46</t>
+          <t>2026/09/06 14:32:42</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-32.8813949, -70.611115</t>
+          <t>-33.693515, -70.3346666</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-32.88139, -70.61111</t>
+          <t>-33.69351, -70.33467</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>15:20:35</t>
+          <t>01:44:40</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.58</v>
+        <v>28.03</v>
       </c>
       <c r="M35" t="n">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="N35" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2433,57 +2433,57 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026/09/05 19:11:11</t>
+          <t>2026/09/06 13:38:36</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-32.7976083, -70.8870683</t>
+          <t>-33.548945, -70.8405816</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88707</t>
+          <t>-33.54895, -70.84058</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026/09/05 22:01:12</t>
+          <t>2026/09/06 14:15:50</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-32.7832499, -70.8550466</t>
+          <t>-33.4583416, -70.6605216</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-32.78325, -70.85505</t>
+          <t>-33.45834, -70.66052</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>02:50:01</t>
+          <t>00:37:14</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.87</v>
+        <v>27.47</v>
       </c>
       <c r="M36" t="n">
-        <v>57</v>
+        <v>126</v>
       </c>
       <c r="N36" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2492,57 +2492,57 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026/09/05 20:21:24</t>
+          <t>2026/09/06 14:17:05</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-33.0872549, -71.3621933</t>
+          <t>-33.4583416, -70.6618449</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-33.08725, -71.36219</t>
+          <t>-33.45834, -70.66184</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026/09/06 15:23:37</t>
+          <t>2026/09/06 17:34:09</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-33.0582133, -71.3724133</t>
+          <t>-32.84845, -70.59168</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-33.05821, -71.37241</t>
+          <t>-32.84845, -70.59168</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>19:02:13</t>
+          <t>03:17:04</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>5</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="N37" t="n">
-        <v>25</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2551,57 +2551,57 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026/09/05 22:02:27</t>
+          <t>2026/09/06 14:33:57</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-32.7831599, -70.8549516</t>
+          <t>-33.6935366, -70.334655</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-32.78316, -70.85495</t>
+          <t>-33.69354, -70.33465</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026/09/05 22:13:04</t>
+          <t>2026/09/06 15:35:55</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-32.7976933, -70.8873866</t>
+          <t>-33.6838933, -70.3390666</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-32.79769, -70.88739</t>
+          <t>-33.68389, -70.33907</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>00:10:37</t>
+          <t>01:01:58</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.7</v>
+        <v>1.21</v>
       </c>
       <c r="M38" t="n">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="N38" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2610,57 +2610,57 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026/09/05 22:14:03</t>
+          <t>2026/09/06 15:24:01</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88709</t>
+          <t>-33.0586466, -71.37246</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88709</t>
+          <t>-33.05865, -71.37246</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026/09/06 11:18:46</t>
+          <t>2026/09/06 15:39:37</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>-32.79573, -70.8201666</t>
+          <t>-33.0873616, -71.3622666</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>-32.79573, -70.82017</t>
+          <t>-33.08736, -71.36227</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>13:04:43</t>
+          <t>00:15:36</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>9.68</v>
+        <v>4.38</v>
       </c>
       <c r="M39" t="n">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="N39" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2669,57 +2669,57 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026/09/06 02:35:12</t>
+          <t>2026/09/06 15:37:10</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-34.579718, -70.961362</t>
+          <t>-33.680965, -70.3387466</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-34.57972, -70.96136</t>
+          <t>-33.68097, -70.33875</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026/09/07 15:17:14</t>
+          <t>2026/09/06 16:02:34</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-34.579702, -70.961411</t>
+          <t>-33.5945, -70.3902549</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>-34.57970, -70.96141</t>
+          <t>-33.59450, -70.39025</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>36:42:02</t>
+          <t>00:25:24</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0.79</v>
+        <v>13.27</v>
       </c>
       <c r="M40" t="n">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="N40" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026/09/06 12:05:47</t>
+          <t>2026/09/06 15:40:47</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-32.8791933, -70.6088266</t>
+          <t>-33.0872733, -71.3622366</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-32.87919, -70.60883</t>
+          <t>-33.08727, -71.36224</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026/09/06 13:37:21</t>
+          <t>2026/09/06 17:03:51</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-33.5490416, -70.8405516</t>
+          <t>-32.9936133, -71.4735133</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-33.54904, -70.84055</t>
+          <t>-32.99361, -71.47351</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>01:31:34</t>
+          <t>01:23:04</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>100.35</v>
+        <v>25.04</v>
       </c>
       <c r="M41" t="n">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="N41" t="n">
-        <v>75</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42">
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2787,57 +2787,57 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026/09/06 12:48:02</t>
+          <t>2026/09/06 16:03:14</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-33.59851, -70.52519</t>
+          <t>-33.5938016, -70.39274</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-33.59851, -70.52519</t>
+          <t>-33.59380, -70.39274</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026/09/06 14:32:42</t>
+          <t>2026/09/06 16:32:37</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-33.693515, -70.3346666</t>
+          <t>-33.5982049, -70.5221333</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-33.69351, -70.33467</t>
+          <t>-33.59820, -70.52213</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>01:44:40</t>
+          <t>00:29:23</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>28.03</v>
+        <v>14.02</v>
       </c>
       <c r="M42" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="N42" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2846,57 +2846,57 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026/09/06 13:38:36</t>
+          <t>2026/09/06 16:16:21</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-33.548945, -70.8405816</t>
+          <t>-32.7976433, -70.8870716</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-33.54895, -70.84058</t>
+          <t>-32.79764, -70.88707</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026/09/06 14:15:50</t>
+          <t>2026/09/07 08:12:31</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-33.4583416, -70.6605216</t>
+          <t>-34.3522566, -71.1172433</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-33.45834, -70.66052</t>
+          <t>-34.35226, -71.11724</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>00:37:14</t>
+          <t>15:56:10</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>27.47</v>
+        <v>263.06</v>
       </c>
       <c r="M43" t="n">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="N43" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2905,57 +2905,57 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026/09/06 14:17:05</t>
+          <t>2026/09/06 16:33:52</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-33.4583416, -70.6618449</t>
+          <t>-33.5983416, -70.52602</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-33.45834, -70.66184</t>
+          <t>-33.59834, -70.52602</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026/09/06 17:34:09</t>
+          <t>2026/09/06 17:38:24</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-32.84845, -70.59168</t>
+          <t>-33.4365083, -70.6289616</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-32.84845, -70.59168</t>
+          <t>-33.43651, -70.62896</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>03:17:04</t>
+          <t>01:04:32</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>83.43000000000001</v>
+        <v>39.69</v>
       </c>
       <c r="M44" t="n">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="N44" t="n">
-        <v>71</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2964,57 +2964,57 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026/09/06 14:33:57</t>
+          <t>2026/09/06 17:05:06</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-33.6935366, -70.334655</t>
+          <t>-32.9935183, -71.47363</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-33.69354, -70.33465</t>
+          <t>-32.99352, -71.47363</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026/09/06 15:35:55</t>
+          <t>2026/09/06 21:04:52</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-33.6838933, -70.3390666</t>
+          <t>-33.0868833, -71.3618233</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-33.68389, -70.33907</t>
+          <t>-33.08688, -71.36182</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>01:01:58</t>
+          <t>03:59:46</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.21</v>
+        <v>32.39</v>
       </c>
       <c r="M45" t="n">
-        <v>51</v>
+        <v>127</v>
       </c>
       <c r="N45" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3023,47 +3023,47 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026/09/06 15:37:10</t>
+          <t>2026/09/06 17:34:58</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-33.680965, -70.3387466</t>
+          <t>-32.848435, -70.5917433</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-33.68097, -70.33875</t>
+          <t>-32.84844, -70.59174</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026/09/06 16:02:34</t>
+          <t>2026/09/06 18:02:45</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-33.5945, -70.3902549</t>
+          <t>-32.8792316, -70.608855</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-33.59450, -70.39025</t>
+          <t>-32.87923, -70.60886</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>00:25:24</t>
+          <t>00:27:47</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>13.27</v>
+        <v>5.64</v>
       </c>
       <c r="M46" t="n">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="N46" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47">
@@ -3073,7 +3073,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3082,116 +3082,116 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026/09/06 16:03:14</t>
+          <t>2026/09/06 17:38:57</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-33.5938016, -70.39274</t>
+          <t>-33.4362116, -70.6289783</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-33.59380, -70.39274</t>
+          <t>-33.43621, -70.62898</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026/09/06 16:32:37</t>
+          <t>2026/09/07 06:48:44</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-33.5982049, -70.5221333</t>
+          <t>-33.44523, -70.6205066</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-33.59820, -70.52213</t>
+          <t>-33.44523, -70.62051</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>00:29:23</t>
+          <t>13:09:47</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>14.02</v>
+        <v>2.03</v>
       </c>
       <c r="M47" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="N47" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C48" t="n">
+        <v>11</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026/09/06 18:02:52</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>-32.8792366, -70.6087966</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-32.87924, -70.60880</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2026/09/07 12:10:06</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>-32.8791583, -70.6088666</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>-32.87916, -70.60887</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>18:07:14</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M48" t="n">
         <v>6</v>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2026/09/06 16:33:52</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>-33.5983416, -70.52602</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>-33.59834, -70.52602</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>2026/09/06 17:38:24</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>-33.4365083, -70.6289616</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>-33.43651, -70.62896</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>01:04:32</t>
-        </is>
-      </c>
-      <c r="L48" t="n">
-        <v>39.69</v>
-      </c>
-      <c r="M48" t="n">
-        <v>109</v>
-      </c>
       <c r="N48" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3200,116 +3200,116 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026/09/06 17:34:58</t>
+          <t>2026/09/06 18:19:42</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-32.848435, -70.5917433</t>
+          <t>-32.7430733, -70.7297799</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-32.84844, -70.59174</t>
+          <t>-32.74307, -70.72978</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026/09/06 18:02:45</t>
+          <t>2026/09/07 06:14:01</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-32.8792316, -70.608855</t>
+          <t>-32.851755, -70.68455</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>-32.87923, -70.60886</t>
+          <t>-32.85175, -70.68455</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>00:27:47</t>
+          <t>11:54:19</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>5.64</v>
+        <v>15.55</v>
       </c>
       <c r="M49" t="n">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="N49" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026/09/06 21:06:07</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-33.0873016, -71.3623533</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-33.08730, -71.36235</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2026/09/07 09:25:33</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>-33.08734, -71.3622766</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>-33.08734, -71.36228</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>12:19:26</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M50" t="n">
+        <v>8</v>
+      </c>
+      <c r="N50" t="n">
         <v>7</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>2026/09/06 17:38:57</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>-33.4362116, -70.6289783</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>-33.43621, -70.62898</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>2026/09/07 06:48:44</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>-33.44523, -70.6205066</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>-33.44523, -70.62051</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>13:09:47</t>
-        </is>
-      </c>
-      <c r="L50" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="M50" t="n">
-        <v>46</v>
-      </c>
-      <c r="N50" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3318,57 +3318,57 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026/09/06 18:02:52</t>
+          <t>2026/09/06 21:09:11</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-32.8792366, -70.6087966</t>
+          <t>-32.785376, -70.960422</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-32.87924, -70.60880</t>
+          <t>-32.78538, -70.96042</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026/09/07 12:10:06</t>
+          <t>2026/09/07 13:41:17</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>-32.8791583, -70.6088666</t>
+          <t>-33.367342, -70.696031</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>-32.87916, -70.60887</t>
+          <t>-33.36734, -70.69603</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>18:07:14</t>
+          <t>16:32:06</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0.04</v>
+        <v>69.56</v>
       </c>
       <c r="M51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3377,47 +3377,47 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026/09/06 21:06:07</t>
+          <t>2026/09/07 07:41:48</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-33.0873016, -71.3623533</t>
+          <t>-33.3599366, -70.8071483</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-33.08730, -71.36235</t>
+          <t>-33.35994, -70.80715</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026/09/07 09:25:33</t>
+          <t>2026/09/07 09:29:03</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-33.08734, -71.3622766</t>
+          <t>-33.4558616, -71.3000133</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>-33.08734, -71.36228</t>
+          <t>-33.45586, -71.30001</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>12:19:26</t>
+          <t>01:47:15</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0.02</v>
+        <v>83.28</v>
       </c>
       <c r="M52" t="n">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="N52" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53">
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3436,57 +3436,57 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026/09/07 06:26:13</t>
+          <t>2026/09/07 09:29:24</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-32.870245, -70.6803216</t>
+          <t>-33.4562233, -71.3000583</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-32.87024, -70.68032</t>
+          <t>-33.45622, -71.30006</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026/09/07 07:41:35</t>
+          <t>2026/09/07 10:40:17</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-33.35995, -70.8069466</t>
+          <t>-33.45636, -71.3000366</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>-33.35995, -70.80695</t>
+          <t>-33.45636, -71.30004</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>01:15:22</t>
+          <t>01:10:53</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>73.16</v>
+        <v>0.02</v>
       </c>
       <c r="M53" t="n">
-        <v>124</v>
+        <v>6</v>
       </c>
       <c r="N53" t="n">
-        <v>63</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3495,57 +3495,57 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026/09/07 07:41:48</t>
+          <t>2026/09/07 10:01:13</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-33.3599366, -70.8071483</t>
+          <t>-33.4914666, -70.70383</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-33.35994, -70.80715</t>
+          <t>-33.49147, -70.70383</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026/09/07 09:29:03</t>
+          <t>2026/09/07 10:08:41</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>-33.4558616, -71.3000133</t>
+          <t>-33.4936616, -70.7056683</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>-33.45586, -71.30001</t>
+          <t>-33.49366, -70.70567</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>01:47:15</t>
+          <t>00:07:28</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>83.28</v>
+        <v>0.4</v>
       </c>
       <c r="M54" t="n">
-        <v>121</v>
+        <v>12</v>
       </c>
       <c r="N54" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3554,57 +3554,57 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026/09/07 09:29:24</t>
+          <t>2026/09/07 10:08:51</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-33.4562233, -71.3000583</t>
+          <t>-33.4936216, -70.705685</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-33.45622, -71.30006</t>
+          <t>-33.49362, -70.70569</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026/09/07 10:40:17</t>
+          <t>2026/09/07 10:36:07</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-33.45636, -71.3000366</t>
+          <t>-33.476235, -70.6983916</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>-33.45636, -71.30004</t>
+          <t>-33.47624, -70.69839</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>01:10:53</t>
+          <t>00:27:16</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0.02</v>
+        <v>4.35</v>
       </c>
       <c r="M55" t="n">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="N55" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3613,47 +3613,47 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026/09/07 10:41:06</t>
+          <t>2026/09/07 10:36:25</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-33.4561933, -71.3000583</t>
+          <t>-33.4763533, -70.6983616</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-33.45619, -71.30006</t>
+          <t>-33.47635, -70.69836</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026/09/07 11:59:55</t>
+          <t>2026/09/07 13:09:57</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>-33.5064066, -71.2516466</t>
+          <t>-33.4771333, -70.6980616</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>-33.50641, -71.25165</t>
+          <t>-33.47713, -70.69806</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>01:18:49</t>
+          <t>02:33:32</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>7.61</v>
+        <v>10.77</v>
       </c>
       <c r="M56" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="N56" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="57">
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -3672,53 +3672,53 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026/09/07 12:00:06</t>
+          <t>2026/09/07 10:41:06</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-33.5063033, -71.251795</t>
+          <t>-33.4561933, -71.3000583</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-33.50630, -71.25180</t>
+          <t>-33.45619, -71.30006</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026/09/07 13:06:05</t>
+          <t>2026/09/07 11:59:55</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>-33.4558666, -71.3000266</t>
+          <t>-33.5064066, -71.2516466</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-33.45587, -71.30003</t>
+          <t>-33.50641, -71.25165</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>01:05:59</t>
+          <t>01:18:49</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>7.54</v>
+        <v>7.61</v>
       </c>
       <c r="M57" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="N57" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -3731,57 +3731,57 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026/09/07 13:06:22</t>
+          <t>2026/09/07 11:47:17</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-33.456225, -71.3000966</t>
+          <t>-34.3467966, -71.1287383</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-33.45623, -71.30010</t>
+          <t>-34.34680, -71.12874</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026/09/07 19:00:44</t>
+          <t>2026/09/07 12:05:44</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>-32.7431866, -70.7330566</t>
+          <t>-34.3554716, -71.1014416</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>-32.74319, -70.73306</t>
+          <t>-34.35547, -71.10144</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>05:54:22</t>
+          <t>00:18:27</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>150.55</v>
+        <v>2.95</v>
       </c>
       <c r="M58" t="n">
-        <v>124</v>
+        <v>53</v>
       </c>
       <c r="N58" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3790,57 +3790,57 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026/09/07 13:10:10</t>
+          <t>2026/09/07 12:00:06</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-33.477215, -70.6979716</t>
+          <t>-33.5063033, -71.251795</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-33.47722, -70.69797</t>
+          <t>-33.50630, -71.25180</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026/09/07 13:20:37</t>
+          <t>2026/09/07 13:06:05</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>-33.47627, -70.6983666</t>
+          <t>-33.4558666, -71.3000266</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>-33.47627, -70.69837</t>
+          <t>-33.45587, -71.30003</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>00:10:27</t>
+          <t>01:05:59</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0.19</v>
+        <v>7.54</v>
       </c>
       <c r="M59" t="n">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="N59" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -3849,57 +3849,57 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026/09/07 13:20:53</t>
+          <t>2026/09/07 12:06:16</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>-33.4762883, -70.6983966</t>
+          <t>-34.3554033, -71.0988566</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-33.47629, -70.69840</t>
+          <t>-34.35540, -71.09886</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026/09/07 14:51:18</t>
+          <t>2026/09/07 13:15:03</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>-33.5389833, -70.6432516</t>
+          <t>-34.3476, -71.1287766</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>-33.53898, -70.64325</t>
+          <t>-34.34760, -71.12878</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>01:30:25</t>
+          <t>01:08:47</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>14.32</v>
+        <v>3.43</v>
       </c>
       <c r="M60" t="n">
-        <v>105</v>
+        <v>48</v>
       </c>
       <c r="N60" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3908,57 +3908,57 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026/09/07 13:45:02</t>
+          <t>2026/09/07 13:06:22</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-34.3459883, -71.1257183</t>
+          <t>-33.456225, -71.3000966</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-34.34599, -71.12572</t>
+          <t>-33.45623, -71.30010</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026/09/07 14:13:02</t>
+          <t>2026/09/07 19:00:44</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>-34.3476749, -71.1277766</t>
+          <t>-32.7431866, -70.7330566</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>-34.34767, -71.12778</t>
+          <t>-32.74319, -70.73306</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>00:28:00</t>
+          <t>05:54:22</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0.28</v>
+        <v>150.55</v>
       </c>
       <c r="M61" t="n">
-        <v>8</v>
+        <v>124</v>
       </c>
       <c r="N61" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3967,116 +3967,116 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026/09/07 13:46:53</t>
+          <t>2026/09/07 13:10:10</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>-34.34603, -71.12569</t>
+          <t>-33.477215, -70.6979716</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-34.34603, -71.12569</t>
+          <t>-33.47722, -70.69797</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026/09/07 14:07:25</t>
+          <t>2026/09/07 13:20:37</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>-34.346422, -71.125933</t>
+          <t>-33.47627, -70.6983666</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>-34.34642, -71.12593</t>
+          <t>-33.47627, -70.69837</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>00:20:32</t>
+          <t>00:10:27</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="M62" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="N62" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026/09/07 14:08:20</t>
+          <t>2026/09/07 13:16:18</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-34.346349, -71.125925</t>
+          <t>-34.3467849, -71.1287533</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-34.34635, -71.12592</t>
+          <t>-34.34678, -71.12875</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026/09/07 14:18:02</t>
+          <t>2026/09/07 13:35:28</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>-34.34672, -71.125939</t>
+          <t>-34.3457483, -71.1278599</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>-34.34672, -71.12594</t>
+          <t>-34.34575, -71.12786</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>00:09:42</t>
+          <t>00:19:10</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="M63" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N63" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4085,116 +4085,116 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026/09/07 14:14:17</t>
+          <t>2026/09/07 13:20:53</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-34.3485233, -71.127835</t>
+          <t>-33.4762883, -70.6983966</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-34.34852, -71.12784</t>
+          <t>-33.47629, -70.69840</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026/09/07 14:42:19</t>
+          <t>2026/09/07 14:51:18</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>-34.351345, -71.12937</t>
+          <t>-33.5389833, -70.6432516</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>-34.35135, -71.12937</t>
+          <t>-33.53898, -70.64325</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>00:28:02</t>
+          <t>01:30:25</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0.83</v>
+        <v>14.32</v>
       </c>
       <c r="M64" t="n">
-        <v>16</v>
+        <v>105</v>
       </c>
       <c r="N64" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026/09/07 14:18:20</t>
+          <t>2026/09/07 13:35:47</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-34.346794, -71.125936</t>
+          <t>-34.3463166, -71.127895</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-34.34679, -71.12594</t>
+          <t>-34.34632, -71.12789</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026/09/07 14:24:20</t>
+          <t>2026/09/07 13:44:48</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>-34.34633, -71.125927</t>
+          <t>-34.3456866, -71.125985</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>-34.34633, -71.12593</t>
+          <t>-34.34569, -71.12599</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>00:06:00</t>
+          <t>00:09:01</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0.1</v>
+        <v>0.33</v>
       </c>
       <c r="M65" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N65" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4203,47 +4203,47 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026/09/07 14:24:28</t>
+          <t>2026/09/07 13:45:02</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>-34.042722, -70.681703</t>
+          <t>-34.3459883, -71.1257183</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-34.04272, -70.68170</t>
+          <t>-34.34599, -71.12572</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026/09/08 13:25:22</t>
+          <t>2026/09/07 14:13:02</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>-34.041819, -70.681668</t>
+          <t>-34.3476749, -71.1277766</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>-34.04182, -70.68167</t>
+          <t>-34.34767, -71.12778</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>23:00:54</t>
+          <t>00:28:00</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0.88</v>
+        <v>0.28</v>
       </c>
       <c r="M66" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N66" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
@@ -4253,53 +4253,53 @@
         </is>
       </c>
       <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026/09/07 13:46:53</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-34.34603, -71.12569</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-34.34603, -71.12569</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2026/09/07 14:07:25</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>-34.346422, -71.125933</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>-34.34642, -71.12593</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>00:20:32</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="M67" t="n">
         <v>4</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>2026/09/07 14:24:44</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>-34.346277, -71.125924</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>-34.34628, -71.12592</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>2026/09/07 14:33:43</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>-34.346249, -71.125961</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>-34.34625, -71.12596</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>00:08:59</t>
-        </is>
-      </c>
-      <c r="L67" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="M67" t="n">
-        <v>3</v>
       </c>
       <c r="N67" t="n">
         <v>3</v>
@@ -4312,50 +4312,50 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026/09/07 14:34:18</t>
+          <t>2026/09/07 14:08:20</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>-34.346318, -71.126003</t>
+          <t>-34.346349, -71.125925</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-34.34632, -71.12600</t>
+          <t>-34.34635, -71.12592</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026/09/07 14:54:53</t>
+          <t>2026/09/07 14:18:02</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>-34.346995, -71.126064</t>
+          <t>-34.34672, -71.125939</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>-34.34699, -71.12606</t>
+          <t>-34.34672, -71.12594</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>00:20:35</t>
+          <t>00:09:42</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0.35</v>
+        <v>0.09</v>
       </c>
       <c r="M68" t="n">
         <v>3</v>
@@ -4371,7 +4371,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4380,116 +4380,116 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026/09/07 14:43:34</t>
+          <t>2026/09/07 14:14:17</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-34.3506066, -71.12932</t>
+          <t>-34.3485233, -71.127835</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-34.35061, -71.12932</t>
+          <t>-34.34852, -71.12784</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026/09/07 14:55:11</t>
+          <t>2026/09/07 14:42:19</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>-34.3466316, -71.1265866</t>
+          <t>-34.351345, -71.12937</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>-34.34663, -71.12659</t>
+          <t>-34.35135, -71.12937</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>00:11:37</t>
+          <t>00:28:02</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="M69" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N69" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026/09/07 14:52:14</t>
+          <t>2026/09/07 14:18:20</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>-33.5384016, -70.6430566</t>
+          <t>-34.346794, -71.125936</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-33.53840, -70.64306</t>
+          <t>-34.34679, -71.12594</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026/09/07 15:20:19</t>
+          <t>2026/09/07 14:24:20</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>-33.4762516, -70.69833</t>
+          <t>-34.34633, -71.125927</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>-33.47625, -70.69833</t>
+          <t>-34.34633, -71.12593</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>00:28:05</t>
+          <t>00:06:00</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>13.35</v>
+        <v>0.1</v>
       </c>
       <c r="M70" t="n">
-        <v>106</v>
+        <v>2</v>
       </c>
       <c r="N70" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4498,41 +4498,41 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026/09/07 14:55:18</t>
+          <t>2026/09/07 14:24:28</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>-34.346855, -71.126061</t>
+          <t>-34.042722, -70.681703</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-34.34685, -71.12606</t>
+          <t>-34.04272, -70.68170</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026/09/07 15:12:17</t>
+          <t>2026/09/08 13:25:22</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>-34.34598, -71.125749</t>
+          <t>-34.041819, -70.681668</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>-34.34598, -71.12575</t>
+          <t>-34.04182, -70.68167</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>00:16:59</t>
+          <t>23:00:54</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0.23</v>
+        <v>0.88</v>
       </c>
       <c r="M71" t="n">
         <v>5</v>
@@ -4544,70 +4544,70 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026/09/07 14:56:26</t>
+          <t>2026/09/07 14:24:44</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>-34.3462733, -71.126005</t>
+          <t>-34.346277, -71.125924</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-34.34627, -71.12601</t>
+          <t>-34.34628, -71.12592</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026/09/07 15:05:05</t>
+          <t>2026/09/07 14:33:43</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>-34.3461549, -71.1255633</t>
+          <t>-34.346249, -71.125961</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>-34.34615, -71.12556</t>
+          <t>-34.34625, -71.12596</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>00:08:39</t>
+          <t>00:08:59</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="M72" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N72" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -4616,57 +4616,57 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026/09/07 15:06:20</t>
+          <t>2026/09/07 14:34:18</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>-34.3464633, -71.12531</t>
+          <t>-34.346318, -71.126003</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-34.34646, -71.12531</t>
+          <t>-34.34632, -71.12600</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026/09/07 18:30:43</t>
+          <t>2026/09/07 14:54:53</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>-32.8795316, -70.6081933</t>
+          <t>-34.346995, -71.126064</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>-32.87953, -70.60819</t>
+          <t>-34.34699, -71.12606</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>03:24:23</t>
+          <t>00:20:35</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>217.83</v>
+        <v>0.35</v>
       </c>
       <c r="M73" t="n">
-        <v>136</v>
+        <v>3</v>
       </c>
       <c r="N73" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -4675,47 +4675,47 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026/09/07 15:12:52</t>
+          <t>2026/09/07 14:43:34</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>-34.346006, -71.125762</t>
+          <t>-34.3506066, -71.12932</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-34.34601, -71.12576</t>
+          <t>-34.35061, -71.12932</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026/09/08 08:53:32</t>
+          <t>2026/09/07 14:55:11</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>-34.346557, -71.125393</t>
+          <t>-34.3466316, -71.1265866</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>-34.34656, -71.12539</t>
+          <t>-34.34663, -71.12659</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>17:40:40</t>
+          <t>00:11:37</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0.11</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M74" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="N74" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="75">
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -4734,57 +4734,57 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026/09/07 15:21:34</t>
+          <t>2026/09/07 14:52:14</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>-33.476185, -70.6984216</t>
+          <t>-33.5384016, -70.6430566</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-33.47619, -70.69842</t>
+          <t>-33.53840, -70.64306</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026/09/08 07:45:19</t>
+          <t>2026/09/07 15:20:19</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>-33.4762716, -70.698355</t>
+          <t>-33.4762516, -70.69833</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>-33.47627, -70.69836</t>
+          <t>-33.47625, -70.69833</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>16:23:45</t>
+          <t>00:28:05</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>11.17</v>
+        <v>13.35</v>
       </c>
       <c r="M75" t="n">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="N75" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -4793,57 +4793,57 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026/09/07 15:28:53</t>
+          <t>2026/09/07 14:55:18</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-33.366952, -70.685523</t>
+          <t>-34.346855, -71.126061</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-33.36695, -70.68552</t>
+          <t>-34.34685, -71.12606</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026/09/07 16:36:26</t>
+          <t>2026/09/07 15:12:17</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>-33.367301, -70.696048</t>
+          <t>-34.34598, -71.125749</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>-33.36730, -70.69605</t>
+          <t>-34.34598, -71.12575</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>01:07:33</t>
+          <t>00:16:59</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.6</v>
+        <v>0.23</v>
       </c>
       <c r="M76" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N76" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -4852,57 +4852,57 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026/09/07 16:35:07</t>
+          <t>2026/09/07 14:56:26</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>-33.0873233, -71.36235</t>
+          <t>-34.3462733, -71.126005</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-33.08732, -71.36235</t>
+          <t>-34.34627, -71.12601</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026/09/07 20:51:29</t>
+          <t>2026/09/07 15:05:05</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>-33.0872983, -71.3622316</t>
+          <t>-34.3461549, -71.1255633</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>-33.08730, -71.36223</t>
+          <t>-34.34615, -71.12556</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>04:16:22</t>
+          <t>00:08:39</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="M77" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N77" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -4911,57 +4911,57 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026/09/07 17:27:33</t>
+          <t>2026/09/07 15:06:20</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>-32.838365, -70.955536</t>
+          <t>-34.3464633, -71.12531</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95554</t>
+          <t>-34.34646, -71.12531</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026/09/08 12:34:32</t>
+          <t>2026/09/07 18:30:43</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>-34.205318, -70.677524</t>
+          <t>-32.8795316, -70.6081933</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>-34.20532, -70.67752</t>
+          <t>-32.87953, -70.60819</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>19:06:59</t>
+          <t>03:24:23</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>205.09</v>
+        <v>217.83</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -4970,57 +4970,57 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026/09/07 18:31:58</t>
+          <t>2026/09/07 15:12:52</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>-32.8794533, -70.6089166</t>
+          <t>-34.346006, -71.125762</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-32.87945, -70.60892</t>
+          <t>-34.34601, -71.12576</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026/09/07 19:36:36</t>
+          <t>2026/09/08 08:53:32</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>-32.7977183, -70.88739</t>
+          <t>-34.346557, -71.125393</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>-32.79772, -70.88739</t>
+          <t>-34.34656, -71.12539</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>01:04:38</t>
+          <t>17:40:40</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>47.17</v>
+        <v>0.11</v>
       </c>
       <c r="M79" t="n">
-        <v>138</v>
+        <v>4</v>
       </c>
       <c r="N79" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5029,57 +5029,57 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026/09/07 19:01:08</t>
+          <t>2026/09/07 15:18:03</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>-32.7433483, -70.7326566</t>
+          <t>-34.579643, -70.961437</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-32.74335, -70.73266</t>
+          <t>-34.57964, -70.96144</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026/09/07 19:13:22</t>
+          <t>2026/09/08 07:10:43</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>-32.7431783, -70.7296383</t>
+          <t>-34.579698, -70.961429</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>-32.74318, -70.72964</t>
+          <t>-34.57970, -70.96143</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>00:12:14</t>
+          <t>15:52:40</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0.36</v>
+        <v>0.18</v>
       </c>
       <c r="M80" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="N80" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5088,57 +5088,57 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026/09/07 19:14:37</t>
+          <t>2026/09/07 15:21:34</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>-32.7432166, -70.729625</t>
+          <t>-33.476185, -70.6984216</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-32.74322, -70.72962</t>
+          <t>-33.47619, -70.69842</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026/09/08 07:25:00</t>
+          <t>2026/09/08 07:45:19</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>-33.3599433, -70.8069966</t>
+          <t>-33.4762716, -70.698355</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>-33.35994, -70.80700</t>
+          <t>-33.47627, -70.69836</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>12:10:23</t>
+          <t>16:23:45</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>90.84999999999999</v>
+        <v>11.17</v>
       </c>
       <c r="M81" t="n">
-        <v>102</v>
+        <v>39</v>
       </c>
       <c r="N81" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5147,47 +5147,47 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026/09/07 19:37:51</t>
+          <t>2026/09/07 17:27:33</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>-32.7976133, -70.88705</t>
+          <t>-32.838365, -70.955536</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88705</t>
+          <t>-32.83837, -70.95554</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026/09/07 19:58:39</t>
+          <t>2026/09/08 12:34:32</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>-32.7976666, -70.887215</t>
+          <t>-34.205318, -70.677524</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>-32.79767, -70.88721</t>
+          <t>-34.20532, -70.67752</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>00:20:48</t>
+          <t>19:06:59</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>7.86</v>
+        <v>205.09</v>
       </c>
       <c r="M82" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -5197,7 +5197,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5206,57 +5206,57 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026/09/07 19:59:00</t>
+          <t>2026/09/07 18:31:58</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>-32.79761, -70.8870333</t>
+          <t>-32.8794533, -70.6089166</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88703</t>
+          <t>-32.87945, -70.60892</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026/09/08 07:29:24</t>
+          <t>2026/09/07 19:36:36</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>-33.3599616, -70.806975</t>
+          <t>-32.7977183, -70.88739</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>-33.35996, -70.80697</t>
+          <t>-32.79772, -70.88739</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>11:30:24</t>
+          <t>01:04:38</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>104.42</v>
+        <v>47.17</v>
       </c>
       <c r="M83" t="n">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="N83" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5265,57 +5265,57 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026/09/07 20:51:37</t>
+          <t>2026/09/07 19:01:08</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>-33.0872183, -71.36218</t>
+          <t>-32.7433483, -70.7326566</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-33.08722, -71.36218</t>
+          <t>-32.74335, -70.73266</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026/09/08 06:44:06</t>
+          <t>2026/09/07 19:13:22</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>-33.0872933, -71.362245</t>
+          <t>-32.7431783, -70.7296383</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>-33.08729, -71.36225</t>
+          <t>-32.74318, -70.72964</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>09:52:29</t>
+          <t>00:12:14</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>14.03</v>
+        <v>0.36</v>
       </c>
       <c r="M84" t="n">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="N84" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5324,57 +5324,57 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026/09/08 09:21:31</t>
+          <t>2026/09/07 19:14:37</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>-34.34731, -71.125642</t>
+          <t>-32.7432166, -70.729625</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-34.34731, -71.12564</t>
+          <t>-32.74322, -70.72962</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026/09/08 10:21:02</t>
+          <t>2026/09/08 07:25:00</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>-34.346529, -71.126182</t>
+          <t>-33.3599433, -70.8069966</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>-34.34653, -71.12618</t>
+          <t>-33.35994, -70.80700</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>00:59:31</t>
+          <t>12:10:23</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.15</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="M85" t="n">
-        <v>6</v>
+        <v>102</v>
       </c>
       <c r="N85" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5383,57 +5383,57 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026/09/08 10:21:07</t>
+          <t>2026/09/07 19:37:51</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>-34.346532, -71.126181</t>
+          <t>-32.7976133, -70.88705</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-34.34653, -71.12618</t>
+          <t>-32.79761, -70.88705</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026/09/08 10:51:28</t>
+          <t>2026/09/07 19:58:39</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>-34.346507, -71.125244</t>
+          <t>-32.7976666, -70.887215</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>-34.34651, -71.12524</t>
+          <t>-32.79767, -70.88721</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>00:30:21</t>
+          <t>00:20:48</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0.33</v>
+        <v>7.86</v>
       </c>
       <c r="M86" t="n">
-        <v>5</v>
+        <v>82</v>
       </c>
       <c r="N86" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5442,165 +5442,165 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026/09/08 10:51:48</t>
+          <t>2026/09/07 19:59:00</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>-34.346526, -71.125237</t>
+          <t>-32.79761, -70.8870333</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-34.34653, -71.12524</t>
+          <t>-32.79761, -70.88703</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026/09/08 12:51:39</t>
+          <t>2026/09/08 07:29:24</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>-34.347589, -71.127686</t>
+          <t>-33.3599616, -70.806975</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>-34.34759, -71.12769</t>
+          <t>-33.35996, -70.80697</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>01:59:51</t>
+          <t>11:30:24</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0.32</v>
+        <v>104.42</v>
       </c>
       <c r="M87" t="n">
-        <v>4</v>
+        <v>130</v>
       </c>
       <c r="N87" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026/09/08 11:12:57</t>
+          <t>2026/09/07 20:51:37</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>-34.579665, -70.961414</t>
+          <t>-33.0872183, -71.36218</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-34.57966, -70.96141</t>
+          <t>-33.08722, -71.36218</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026/09/08 12:50:13</t>
+          <t>2026/09/08 06:44:06</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>-34.579642, -70.961429</t>
+          <t>-33.0872933, -71.362245</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>-34.57964, -70.96143</t>
+          <t>-33.08729, -71.36225</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>01:37:16</t>
+          <t>09:52:29</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>14.03</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C89" t="n">
+        <v>2</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026/09/08 09:21:31</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-34.34731, -71.125642</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-34.34731, -71.12564</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2026/09/08 10:21:02</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>-34.346529, -71.126182</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>-34.34653, -71.12618</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>00:59:31</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M89" t="n">
+        <v>6</v>
+      </c>
+      <c r="N89" t="n">
         <v>3</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>2026/09/08 12:50:16</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>-34.579664, -70.961403</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>-34.57966, -70.96140</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>2026/09/11 23:34:40</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>-34.579677, -70.96149</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>-34.57968, -70.96149</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>82:44:24</t>
-        </is>
-      </c>
-      <c r="L89" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="M89" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -5610,53 +5610,53 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026/09/08 13:03:39</t>
+          <t>2026/09/08 10:21:07</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>-34.348853, -71.127667</t>
+          <t>-34.346532, -71.126181</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-34.34885, -71.12767</t>
+          <t>-34.34653, -71.12618</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026/09/08 13:11:23</t>
+          <t>2026/09/08 10:51:28</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>-34.348297, -71.127681</t>
+          <t>-34.346507, -71.125244</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>-34.34830, -71.12768</t>
+          <t>-34.34651, -71.12524</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>00:07:44</t>
+          <t>00:30:21</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0.06</v>
+        <v>0.33</v>
       </c>
       <c r="M90" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N90" t="n">
         <v>3</v>
@@ -5665,11 +5665,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -5678,41 +5678,41 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026/09/08 13:25:32</t>
+          <t>2026/09/08 10:51:48</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>-34.041832, -70.681694</t>
+          <t>-34.346526, -71.125237</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-34.04183, -70.68169</t>
+          <t>-34.34653, -71.12524</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026/09/08 15:14:07</t>
+          <t>2026/09/08 12:51:39</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>-34.042664, -70.681724</t>
+          <t>-34.347589, -71.127686</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>-34.04266, -70.68172</t>
+          <t>-34.34759, -71.12769</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>01:48:35</t>
+          <t>01:59:51</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0.15</v>
+        <v>0.32</v>
       </c>
       <c r="M91" t="n">
         <v>4</v>
@@ -5724,70 +5724,70 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026/09/08 13:31:35</t>
+          <t>2026/09/08 11:12:57</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>-34.348097, -71.127772</t>
+          <t>-34.579665, -70.961414</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-34.34810, -71.12777</t>
+          <t>-34.57966, -70.96141</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026/09/08 13:46:25</t>
+          <t>2026/09/08 12:50:13</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>-34.346322, -71.1256</t>
+          <t>-34.579642, -70.961429</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>-34.34632, -71.12560</t>
+          <t>-34.57964, -70.96143</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>00:14:50</t>
+          <t>01:37:16</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -5796,47 +5796,47 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026/09/08 13:47:25</t>
+          <t>2026/09/08 12:50:16</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>-34.346558, -71.125262</t>
+          <t>-34.579664, -70.961403</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-34.34656, -71.12526</t>
+          <t>-34.57966, -70.96140</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026/09/08 13:55:43</t>
+          <t>2026/09/12 01:36:53</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>-34.345942, -71.125755</t>
+          <t>-34.579636, -70.961312</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>-34.34594, -71.12575</t>
+          <t>-34.57964, -70.96131</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>00:08:18</t>
+          <t>84:46:37</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="M93" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N93" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -5846,7 +5846,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -5855,47 +5855,47 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026/09/08 13:56:22</t>
+          <t>2026/09/08 13:03:39</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>-34.345962, -71.125764</t>
+          <t>-34.348853, -71.127667</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-34.34596, -71.12576</t>
+          <t>-34.34885, -71.12767</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026/09/11 23:01:38</t>
+          <t>2026/09/08 13:11:23</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>-34.34603, -71.125731</t>
+          <t>-34.348297, -71.127681</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>-34.34603, -71.12573</t>
+          <t>-34.34830, -71.12768</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>81:05:16</t>
+          <t>00:07:44</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
@@ -5905,53 +5905,53 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026/09/08 15:15:01</t>
+          <t>2026/09/08 13:25:32</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>-34.042664, -70.68175</t>
+          <t>-34.041832, -70.681694</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-34.04266, -70.68175</t>
+          <t>-34.04183, -70.68169</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026/09/08 15:26:28</t>
+          <t>2026/09/08 15:14:07</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>-34.042648, -70.681753</t>
+          <t>-34.042664, -70.681724</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>-34.04265, -70.68175</t>
+          <t>-34.04266, -70.68172</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>00:11:27</t>
+          <t>01:48:35</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="M95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N95" t="n">
         <v>3</v>
@@ -5960,247 +5960,247 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C96" t="n">
+        <v>8</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2026/09/08 13:31:35</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>-34.348097, -71.127772</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-34.34810, -71.12777</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2026/09/08 13:46:25</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>-34.346322, -71.1256</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>-34.34632, -71.12560</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>00:14:50</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M96" t="n">
+        <v>4</v>
+      </c>
+      <c r="N96" t="n">
         <v>3</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>2026/09/08 15:26:45</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>-34.042645, -70.681745</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>-34.04265, -70.68175</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>2026/09/11 23:57:51</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>-34.042613, -70.681788</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>-34.04261, -70.68179</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>80:31:06</t>
-        </is>
-      </c>
-      <c r="L96" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="M96" t="n">
-        <v>0</v>
-      </c>
-      <c r="N96" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026/09/08 16:19:10</t>
+          <t>2026/09/08 13:47:25</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>-33.3599583, -70.8070683</t>
+          <t>-34.346558, -71.125262</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-33.35996, -70.80707</t>
+          <t>-34.34656, -71.12526</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026/09/08 18:49:57</t>
+          <t>2026/09/08 13:55:43</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>-32.7432316, -70.7328933</t>
+          <t>-34.345942, -71.125755</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>-32.74323, -70.73289</t>
+          <t>-34.34594, -71.12575</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>02:30:47</t>
+          <t>00:08:18</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>125.82</v>
+        <v>0.08</v>
       </c>
       <c r="M97" t="n">
-        <v>138</v>
+        <v>4</v>
       </c>
       <c r="N97" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026/09/08 18:06:06</t>
+          <t>2026/09/08 13:56:22</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>-32.8205016, -70.6143333</t>
+          <t>-34.345962, -71.125764</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-32.82050, -70.61433</t>
+          <t>-34.34596, -71.12576</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026/09/08 18:42:10</t>
+          <t>2026/09/12 23:01:33</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>-32.7580149, -70.70204</t>
+          <t>-34.34603, -71.125731</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>-32.75801, -70.70204</t>
+          <t>-34.34603, -71.12573</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>00:36:04</t>
+          <t>105:05:11</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>12.65</v>
+        <v>0.01</v>
       </c>
       <c r="M98" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026/09/08 18:27:43</t>
+          <t>2026/09/08 15:26:45</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>-33.3621483, -70.6701383</t>
+          <t>-34.042645, -70.681745</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-33.36215, -70.67014</t>
+          <t>-34.04265, -70.68175</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026/09/08 19:03:48</t>
+          <t>2026/09/12 22:57:15</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>-33.4762116, -70.6982083</t>
+          <t>-34.042553, -70.68171</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>-33.47621, -70.69821</t>
+          <t>-34.04255, -70.68171</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>00:36:05</t>
+          <t>103:30:30</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>18.07</v>
+        <v>0.02</v>
       </c>
       <c r="M99" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6209,57 +6209,57 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026/09/08 18:42:33</t>
+          <t>2026/09/08 16:19:10</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>-32.7582066, -70.7021599</t>
+          <t>-33.3599583, -70.8070683</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-32.75821, -70.70216</t>
+          <t>-33.35996, -70.80707</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026/09/08 19:19:25</t>
+          <t>2026/09/08 18:49:57</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>-32.8792133, -70.6090199</t>
+          <t>-32.7432316, -70.7328933</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>-32.87921, -70.60902</t>
+          <t>-32.74323, -70.73289</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>00:36:52</t>
+          <t>02:30:47</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>25.15</v>
+        <v>125.82</v>
       </c>
       <c r="M100" t="n">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="N100" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6268,57 +6268,57 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026/09/08 18:50:27</t>
+          <t>2026/09/08 18:27:43</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>-32.7433533, -70.7327166</t>
+          <t>-33.3621483, -70.6701383</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-32.74335, -70.73272</t>
+          <t>-33.36215, -70.67014</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026/09/08 19:08:01</t>
+          <t>2026/09/08 19:03:48</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>-32.7431883, -70.729675</t>
+          <t>-33.4762116, -70.6982083</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>-32.74319, -70.72968</t>
+          <t>-33.47621, -70.69821</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>00:17:34</t>
+          <t>00:36:05</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0.36</v>
+        <v>18.07</v>
       </c>
       <c r="M101" t="n">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="N101" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6327,47 +6327,47 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026/09/08 19:05:03</t>
+          <t>2026/09/08 18:42:33</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>-33.4762333, -70.6984166</t>
+          <t>-32.7582066, -70.7021599</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-33.47623, -70.69842</t>
+          <t>-32.75821, -70.70216</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026/09/09 07:44:57</t>
+          <t>2026/09/08 19:19:25</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>-33.4762833, -70.6983599</t>
+          <t>-32.8792133, -70.6090199</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>-33.47628, -70.69836</t>
+          <t>-32.87921, -70.60902</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>12:39:54</t>
+          <t>00:36:52</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>11.17</v>
+        <v>25.15</v>
       </c>
       <c r="M102" t="n">
-        <v>58</v>
+        <v>105</v>
       </c>
       <c r="N102" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
     </row>
     <row r="103">
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6386,57 +6386,57 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026/09/08 19:09:16</t>
+          <t>2026/09/08 18:50:27</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>-32.743165, -70.7297066</t>
+          <t>-32.7433533, -70.7327166</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-32.74316, -70.72971</t>
+          <t>-32.74335, -70.73272</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026/09/09 07:18:24</t>
+          <t>2026/09/08 19:08:01</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>-33.3599916, -70.8071333</t>
+          <t>-32.7431883, -70.729675</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80713</t>
+          <t>-32.74319, -70.72968</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>12:09:08</t>
+          <t>00:17:34</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>89.91</v>
+        <v>0.36</v>
       </c>
       <c r="M103" t="n">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="N103" t="n">
-        <v>57</v>
+        <v>10</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6445,57 +6445,57 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026/09/08 19:20:40</t>
+          <t>2026/09/08 19:05:03</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>-32.8790916, -70.6094466</t>
+          <t>-33.4762333, -70.6984166</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-32.87909, -70.60945</t>
+          <t>-33.47623, -70.69842</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026/09/08 19:31:12</t>
+          <t>2026/09/09 07:44:57</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>-32.879155, -70.6093066</t>
+          <t>-33.4762833, -70.6983599</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>-32.87915, -70.60931</t>
+          <t>-33.47628, -70.69836</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>00:10:32</t>
+          <t>12:39:54</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0.01</v>
+        <v>11.17</v>
       </c>
       <c r="M104" t="n">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="N104" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6504,57 +6504,57 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026/09/08 19:31:50</t>
+          <t>2026/09/08 19:09:16</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>-32.8792316, -70.6088183</t>
+          <t>-32.743165, -70.7297066</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-32.87923, -70.60882</t>
+          <t>-32.74316, -70.72971</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026/09/09 07:06:21</t>
+          <t>2026/09/09 07:18:24</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>-32.879205, -70.60888</t>
+          <t>-33.3599916, -70.8071333</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>-32.87920, -70.60888</t>
+          <t>-33.35999, -70.80713</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>11:34:31</t>
+          <t>12:09:08</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>10.18</v>
+        <v>89.91</v>
       </c>
       <c r="M105" t="n">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="N105" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6563,57 +6563,57 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026/09/09 15:49:12</t>
+          <t>2026/09/08 19:20:40</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>-34.2088533, -70.6784016</t>
+          <t>-32.8790916, -70.6094466</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-34.20885, -70.67840</t>
+          <t>-32.87909, -70.60945</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026/09/09 16:25:24</t>
+          <t>2026/09/08 19:31:12</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>-34.2041083, -70.6790099</t>
+          <t>-32.879155, -70.6093066</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>-34.20411, -70.67901</t>
+          <t>-32.87915, -70.60931</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>00:36:12</t>
+          <t>00:10:32</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.07</v>
+        <v>0.01</v>
       </c>
       <c r="M106" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="N106" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6622,47 +6622,47 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026/09/09 16:25:31</t>
+          <t>2026/09/08 19:31:50</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>-34.2041483, -70.679065</t>
+          <t>-32.8792316, -70.6088183</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-34.20415, -70.67906</t>
+          <t>-32.87923, -70.60882</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026/09/09 16:38:53</t>
+          <t>2026/09/09 07:06:21</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>-34.2058549, -70.6759933</t>
+          <t>-32.879205, -70.60888</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>-34.20585, -70.67599</t>
+          <t>-32.87920, -70.60888</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>00:13:22</t>
+          <t>11:34:31</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0.59</v>
+        <v>10.18</v>
       </c>
       <c r="M107" t="n">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="N107" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="108">
@@ -6672,7 +6672,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -6681,47 +6681,47 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026/09/09 16:39:54</t>
+          <t>2026/09/09 15:49:12</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>-34.2074116, -70.6760316</t>
+          <t>-34.2088533, -70.6784016</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-34.20741, -70.67603</t>
+          <t>-34.20885, -70.67840</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026/09/09 17:16:48</t>
+          <t>2026/09/09 16:25:24</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>-34.2045433, -70.6795616</t>
+          <t>-34.2041083, -70.6790099</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>-34.20454, -70.67956</t>
+          <t>-34.20411, -70.67901</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>00:36:54</t>
+          <t>00:36:12</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="M108" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="N108" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="109">
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -6740,47 +6740,47 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026/09/09 17:17:22</t>
+          <t>2026/09/09 16:25:31</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>-34.2051833, -70.68031</t>
+          <t>-34.2041483, -70.679065</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-34.20518, -70.68031</t>
+          <t>-34.20415, -70.67906</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026/09/09 17:43:00</t>
+          <t>2026/09/09 16:38:53</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>-34.1900883, -70.70946</t>
+          <t>-34.2058549, -70.6759933</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>-34.19009, -70.70946</t>
+          <t>-34.20585, -70.67599</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>00:25:38</t>
+          <t>00:13:22</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>3.38</v>
+        <v>0.59</v>
       </c>
       <c r="M109" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="N109" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="110">
@@ -6790,7 +6790,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -6799,47 +6799,47 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026/09/09 17:43:35</t>
+          <t>2026/09/09 16:39:54</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>-34.19014, -70.7094049</t>
+          <t>-34.2074116, -70.6760316</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-34.19014, -70.70940</t>
+          <t>-34.20741, -70.67603</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026/09/09 18:37:10</t>
+          <t>2026/09/09 17:16:48</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>-34.1790849, -70.70823</t>
+          <t>-34.2045433, -70.6795616</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>-34.17908, -70.70823</t>
+          <t>-34.20454, -70.67956</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>00:53:35</t>
+          <t>00:36:54</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.61</v>
+        <v>1.1</v>
       </c>
       <c r="M110" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="N110" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="111">
@@ -6849,7 +6849,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -6858,53 +6858,53 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026/09/09 18:38:25</t>
+          <t>2026/09/09 17:17:22</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>-34.1796933, -70.7074966</t>
+          <t>-34.2051833, -70.68031</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-34.17969, -70.70750</t>
+          <t>-34.20518, -70.68031</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026/09/10 07:46:05</t>
+          <t>2026/09/09 17:43:00</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>-34.2070316, -70.6771383</t>
+          <t>-34.1900883, -70.70946</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>-34.20703, -70.67714</t>
+          <t>-34.19009, -70.70946</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>13:07:40</t>
+          <t>00:25:38</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>5.68</v>
+        <v>3.38</v>
       </c>
       <c r="M111" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="N111" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -6917,53 +6917,53 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026/09/09 18:48:26</t>
+          <t>2026/09/09 17:43:35</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>-33.4511266, -70.666315</t>
+          <t>-34.19014, -70.7094049</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-33.45113, -70.66631</t>
+          <t>-34.19014, -70.70940</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026/09/09 19:03:26</t>
+          <t>2026/09/09 18:37:10</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>-33.4507766, -70.6663983</t>
+          <t>-34.1790849, -70.70823</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>-33.45078, -70.66640</t>
+          <t>-34.17908, -70.70823</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>00:15:00</t>
+          <t>00:53:35</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0.05</v>
+        <v>1.61</v>
       </c>
       <c r="M112" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="N112" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -6976,47 +6976,47 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026/09/09 19:04:41</t>
+          <t>2026/09/09 18:38:25</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>-33.450825, -70.6666066</t>
+          <t>-34.1796933, -70.7074966</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-33.45083, -70.66661</t>
+          <t>-34.17969, -70.70750</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026/09/09 19:33:12</t>
+          <t>2026/09/10 07:46:05</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>-33.4762216, -70.6982983</t>
+          <t>-34.2070316, -70.6771383</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>-33.47622, -70.69830</t>
+          <t>-34.20703, -70.67714</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>00:28:31</t>
+          <t>13:07:40</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>7.91</v>
+        <v>5.68</v>
       </c>
       <c r="M113" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="N113" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="114">
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7035,57 +7035,57 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026/09/09 19:34:28</t>
+          <t>2026/09/09 18:48:26</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>-33.4761533, -70.6984083</t>
+          <t>-33.4511266, -70.666315</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-33.47615, -70.69841</t>
+          <t>-33.45113, -70.66631</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026/09/10 07:48:15</t>
+          <t>2026/09/09 19:03:26</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>-33.47624, -70.69838</t>
+          <t>-33.4507766, -70.6663983</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>-33.47624, -70.69838</t>
+          <t>-33.45078, -70.66640</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>12:13:47</t>
+          <t>00:15:00</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>11.1</v>
+        <v>0.05</v>
       </c>
       <c r="M114" t="n">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="N114" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7094,57 +7094,57 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026/09/10 16:42:50</t>
+          <t>2026/09/09 19:04:41</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>-34.20484, -70.677505</t>
+          <t>-33.450825, -70.6666066</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-34.20484, -70.67750</t>
+          <t>-33.45083, -70.66661</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026/09/10 17:35:40</t>
+          <t>2026/09/09 19:33:12</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>-34.1796983, -70.7075316</t>
+          <t>-33.4762216, -70.6982983</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>-34.17970, -70.70753</t>
+          <t>-33.47622, -70.69830</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>00:52:50</t>
+          <t>00:28:31</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>5.39</v>
+        <v>7.91</v>
       </c>
       <c r="M115" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N115" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7153,57 +7153,57 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026/09/10 17:36:55</t>
+          <t>2026/09/09 19:34:28</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>-34.1797233, -70.7073566</t>
+          <t>-33.4761533, -70.6984083</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-34.17972, -70.70736</t>
+          <t>-33.47615, -70.69841</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026/09/11 07:34:52</t>
+          <t>2026/09/10 07:48:15</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>-34.18998, -70.7092433</t>
+          <t>-33.47624, -70.69838</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>-34.18998, -70.70924</t>
+          <t>-33.47624, -70.69838</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>13:57:57</t>
+          <t>12:13:47</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.17</v>
+        <v>11.1</v>
       </c>
       <c r="M116" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="N116" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7212,57 +7212,57 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026/09/10 19:53:35</t>
+          <t>2026/09/10 16:42:50</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>-32.7976283, -70.8870166</t>
+          <t>-34.20484, -70.677505</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-32.79763, -70.88702</t>
+          <t>-34.20484, -70.67750</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026/09/11 06:18:20</t>
+          <t>2026/09/10 17:35:40</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>-33.5398733, -70.7089816</t>
+          <t>-34.1796983, -70.7075316</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>-33.53987, -70.70898</t>
+          <t>-34.17970, -70.70753</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>10:24:45</t>
+          <t>00:52:50</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>117.06</v>
+        <v>5.39</v>
       </c>
       <c r="M117" t="n">
-        <v>144</v>
+        <v>42</v>
       </c>
       <c r="N117" t="n">
-        <v>71</v>
+        <v>18</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7271,57 +7271,57 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026/09/11 11:08:47</t>
+          <t>2026/09/10 17:36:55</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>-33.3649116, -70.4965666</t>
+          <t>-34.1797233, -70.7073566</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>-33.36491, -70.49657</t>
+          <t>-34.17972, -70.70736</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026/09/11 11:23:05</t>
+          <t>2026/09/11 07:34:52</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>-33.3588366, -70.4849283</t>
+          <t>-34.18998, -70.7092433</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>-33.35884, -70.48493</t>
+          <t>-34.18998, -70.70924</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>00:14:18</t>
+          <t>13:57:57</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.52</v>
+        <v>2.17</v>
       </c>
       <c r="M118" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="N118" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7330,175 +7330,175 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026/09/11 11:24:20</t>
+          <t>2026/09/10 19:53:35</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>-33.3585916, -70.48524</t>
+          <t>-32.7976283, -70.8870166</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-33.35859, -70.48524</t>
+          <t>-32.79763, -70.88702</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026/09/11 18:19:57</t>
+          <t>2026/09/11 06:18:20</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>-33.5140783, -70.637485</t>
+          <t>-33.5398733, -70.7089816</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>-33.51408, -70.63748</t>
+          <t>-33.53987, -70.70898</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>06:55:37</t>
+          <t>10:24:45</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>33.06</v>
+        <v>117.06</v>
       </c>
       <c r="M119" t="n">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="N119" t="n">
-        <v>26</v>
+        <v>71</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026/09/11 16:46:08</t>
+          <t>2026/09/11 11:08:47</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>-33.4364066, -70.629565</t>
+          <t>-33.3649116, -70.4965666</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>-33.43641, -70.62956</t>
+          <t>-33.36491, -70.49657</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026/09/11 22:46:08</t>
+          <t>2026/09/11 11:23:05</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>-33.4364066, -70.629565</t>
+          <t>-33.3588366, -70.4849283</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>-33.43641, -70.62956</t>
+          <t>-33.35884, -70.48493</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>06:00:00</t>
+          <t>00:14:18</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026/09/11 17:59:30</t>
+          <t>2026/09/11 11:24:20</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>-33.476155, -70.69845</t>
+          <t>-33.3585916, -70.48524</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-33.47615, -70.69845</t>
+          <t>-33.35859, -70.48524</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026/09/11 22:00:12</t>
+          <t>2026/09/11 18:19:57</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>-33.476155, -70.69845</t>
+          <t>-33.5140783, -70.637485</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>-33.47615, -70.69845</t>
+          <t>-33.51408, -70.63748</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>04:00:42</t>
+          <t>06:55:37</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>33.06</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7507,37 +7507,37 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026/09/11 18:21:12</t>
+          <t>2026/09/11 16:46:08</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>-33.5138849, -70.638245</t>
+          <t>-33.4364066, -70.629565</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>-33.51388, -70.63824</t>
+          <t>-33.43641, -70.62956</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026/09/11 22:57:33</t>
+          <t>2026/09/12 22:46:08</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>-33.5138849, -70.638245</t>
+          <t>-33.4364066, -70.629565</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>-33.51388, -70.63824</t>
+          <t>-33.43641, -70.62956</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>04:36:21</t>
+          <t>30:00:00</t>
         </is>
       </c>
       <c r="L122" t="n">
@@ -7553,70 +7553,70 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026/09/11 19:13:47</t>
+          <t>2026/09/11 18:21:12</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>-32.7976, -70.887115</t>
+          <t>-33.5138849, -70.638245</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-32.79760, -70.88711</t>
+          <t>-33.51388, -70.63824</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026/09/11 23:14:47</t>
+          <t>2026/09/12 08:06:40</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>-32.7975983, -70.8870416</t>
+          <t>-33.4510416, -70.6724666</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>-32.79760, -70.88704</t>
+          <t>-33.45104, -70.67247</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>04:01:00</t>
+          <t>13:45:28</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0.01</v>
+        <v>10.84</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7625,41 +7625,41 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026/09/11 19:43:56</t>
+          <t>2026/09/11 22:12:20</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>-32.8792, -70.608775</t>
+          <t>-32.743195, -70.7296283</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>-32.87920, -70.60877</t>
+          <t>-32.74320, -70.72963</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026/09/11 23:43:56</t>
+          <t>2026/09/12 22:15:01</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>-32.8792, -70.608775</t>
+          <t>-32.74302, -70.7297533</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>-32.87920, -70.60877</t>
+          <t>-32.74302, -70.72975</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>04:00:00</t>
+          <t>24:02:41</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="M124" t="n">
         <v>0</v>
@@ -7671,11 +7671,11 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -7684,37 +7684,37 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026/09/11 20:01:03</t>
+          <t>2026/09/12 12:37:06</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>-33.0872133, -71.3621916</t>
+          <t>-33.3671549, -70.6958183</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>-33.08721, -71.36219</t>
+          <t>-33.36715, -70.69582</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026/09/11 22:01:03</t>
+          <t>2026/09/12 22:37:06</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>-33.0872133, -71.3621916</t>
+          <t>-33.3671549, -70.6958183</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>-33.08721, -71.36219</t>
+          <t>-33.36715, -70.69582</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="L125" t="n">
@@ -7724,6 +7724,124 @@
         <v>0</v>
       </c>
       <c r="N125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>CHANGAN HUNTER TKCS-53</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>3</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>2026/09/12 16:50:39</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>-33.0873299, -71.3623866</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>-33.08733, -71.36239</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>2026/09/12 22:51:25</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>-33.0873299, -71.3623866</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>-33.08733, -71.36239</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>06:00:46</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>MITSUBISHI L200 LVHX-40</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>6</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>2026/09/12 18:27:46</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>-33.476225, -70.6984066</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>-33.47622, -70.69841</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>2026/09/12 22:29:01</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>-33.476225, -70.6984066</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>-33.47622, -70.69841</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>04:01:15</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7775,13 +7893,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1882.83</v>
+        <v>1894.52</v>
       </c>
       <c r="C2" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>144</v>
@@ -7794,7 +7912,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>747.37</v>
+        <v>734.6</v>
       </c>
       <c r="C3" t="n">
         <v>10</v>
@@ -7813,10 +7931,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>971.65</v>
+        <v>974.26</v>
       </c>
       <c r="C4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -7832,13 +7950,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1317.07</v>
+        <v>1317.05</v>
       </c>
       <c r="C5" t="n">
         <v>53</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>138</v>
@@ -7933,7 +8051,7 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
         <v>6</v>
@@ -8003,10 +8121,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1431.08</v>
+        <v>1511.1</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -8041,10 +8159,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>89.06</v>
+        <v>111.37</v>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
@@ -8098,13 +8216,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1262.73</v>
+        <v>1330.47</v>
       </c>
       <c r="C19" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>139</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N127"/>
+  <dimension ref="A1:N128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -973,7 +973,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026/09/12 22:31:38</t>
+          <t>2026/09/12 23:31:38</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>166:00:00</t>
+          <t>167:00:00</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/09/12 22:41:10</t>
+          <t>2026/09/12 23:41:10</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>165:59:04</t>
+          <t>166:59:04</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026/09/12 22:56:08</t>
+          <t>2026/09/12 23:56:08</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>165:59:57</t>
+          <t>166:59:57</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026/09/12 22:57:15</t>
+          <t>2026/09/12 23:57:38</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>103:30:30</t>
+          <t>104:30:53</t>
         </is>
       </c>
       <c r="L99" t="n">
@@ -7842,6 +7842,65 @@
         <v>0</v>
       </c>
       <c r="N127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>CHANGAN HUNTER TGPS-77</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>7</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2026/09/12 21:39:50</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>-32.7976249, -70.8871033</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>-32.79762, -70.88710</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>2026/09/12 23:40:06</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>-32.7976249, -70.8871033</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>-32.79762, -70.88710</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>02:00:16</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7893,13 +7952,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1894.52</v>
+        <v>1894.49</v>
       </c>
       <c r="C2" t="n">
         <v>71</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>144</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,13 +446,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N128"/>
+  <dimension ref="A1:N129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Desde : 2026/09/06 04:00:00   Hasta : 2026/09/13 03:59:59</t>
+          <t>Desde : 2026/09/07 04:00:00   Hasta : 2026/09/14 03:59:59</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026/09/06 00:01:38</t>
+          <t>2026/09/07 00:01:31</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>37:44:28</t>
+          <t>13:44:35</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -591,7 +591,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>LPR20251A02800014-DS</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -599,58 +599,58 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026/09/06 00:01:57</t>
+          <t>2026/09/07 00:12:15</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-33.4363316, -70.628895</t>
+          <t>-34.205461, -70.677261</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-33.43633, -70.62889</t>
+          <t>-34.20546, -70.67726</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026/09/06 09:42:38</t>
+          <t>2026/09/13 23:11:38</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-33.4359749, -70.6299933</t>
+          <t>-34.205371, -70.67735</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-33.43597, -70.62999</t>
+          <t>-34.20537, -70.67735</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>09:40:41</t>
+          <t>166:59:23</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>55.39</v>
+        <v>0.04</v>
       </c>
       <c r="M5" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -658,58 +658,58 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026/09/06 00:11:51</t>
+          <t>2026/09/07 00:16:21</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-34.205312, -70.677304</t>
+          <t>-32.7976433, -70.8870716</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-34.20531, -70.67730</t>
+          <t>-32.79764, -70.88707</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026/09/12 23:11:38</t>
+          <t>2026/09/07 08:12:31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-34.205371, -70.67735</t>
+          <t>-34.3522566, -71.1172433</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-34.20537, -70.67735</t>
+          <t>-34.35226, -71.11724</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>166:59:47</t>
+          <t>07:56:10</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.06</v>
+        <v>263.06</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -722,53 +722,53 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026/09/06 00:14:03</t>
+          <t>2026/09/07 00:20:08</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88709</t>
+          <t>-32.7430733, -70.7297799</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88709</t>
+          <t>-32.74307, -70.72978</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026/09/06 11:18:46</t>
+          <t>2026/09/07 06:14:01</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-32.79573, -70.8201666</t>
+          <t>-32.851755, -70.68455</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-32.79573, -70.82017</t>
+          <t>-32.85175, -70.68455</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>11:04:43</t>
+          <t>05:53:53</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>9.68</v>
+        <v>15.55</v>
       </c>
       <c r="M7" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="N7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>LPR20251T02900038-RTN</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -776,58 +776,58 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026/09/06 00:21:18</t>
+          <t>2026/09/07 00:24:46</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-33.4762066, -70.6984716</t>
+          <t>-34.87659, -71.127088</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-33.47621, -70.69847</t>
+          <t>-34.87659, -71.12709</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026/09/07 09:06:46</t>
+          <t>2026/09/07 01:24:55</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-33.476265, -70.6983216</t>
+          <t>-34.876432, -71.127131</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-33.47626, -70.69832</t>
+          <t>-34.87643, -71.12713</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>32:45:28</t>
+          <t>01:00:09</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>56.18</v>
+        <v>0.02</v>
       </c>
       <c r="M8" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>LPR20251V02900023-LL</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -835,58 +835,58 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026/09/06 00:21:43</t>
+          <t>2026/09/07 00:31:38</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-33.0872566, -71.3621933</t>
+          <t>-33.89982, -71.429438</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-33.08726, -71.36219</t>
+          <t>-33.89982, -71.42944</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026/09/06 15:23:37</t>
+          <t>2026/09/13 22:31:26</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-33.0582133, -71.3724133</t>
+          <t>-33.899848, -71.429508</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-33.05821, -71.37241</t>
+          <t>-33.89985, -71.42951</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>15:01:54</t>
+          <t>165:59:48</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>0.02</v>
       </c>
       <c r="M9" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LPR20251T02900038-RTN</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -894,58 +894,58 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026/09/06 00:23:26</t>
+          <t>2026/09/07 00:32:27</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-34.87659, -71.127088</t>
+          <t>-32.8792366, -70.6087949</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-34.87659, -71.12709</t>
+          <t>-32.87924, -70.60879</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/09/07 01:24:55</t>
+          <t>2026/09/07 12:10:06</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-34.876432, -71.127131</t>
+          <t>-32.8791583, -70.6088666</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-34.87643, -71.12713</t>
+          <t>-32.87916, -70.60887</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>25:01:29</t>
+          <t>11:37:39</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LPR20251V02900023-LL</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -953,58 +953,58 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026/09/06 00:31:38</t>
+          <t>2026/09/07 00:35:43</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-33.899796, -71.429428</t>
+          <t>-34.579718, -70.961362</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-33.89980, -71.42943</t>
+          <t>-34.57972, -70.96136</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026/09/12 23:31:38</t>
+          <t>2026/09/07 15:17:14</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-33.899848, -71.429508</t>
+          <t>-34.579702, -70.961411</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-33.89985, -71.42951</t>
+          <t>-34.57970, -70.96141</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>167:00:00</t>
+          <t>14:41:31</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.02</v>
+        <v>0.79</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1012,58 +1012,58 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026/09/06 00:32:53</t>
+          <t>2026/09/07 00:39:37</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-32.7430849, -70.7297799</t>
+          <t>-33.360041, -70.807078</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-32.74308, -70.72978</t>
+          <t>-33.36004, -70.80708</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026/09/06 18:18:51</t>
+          <t>2026/09/09 14:27:06</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-32.7431899, -70.7296433</t>
+          <t>-33.359994, -70.807053</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-32.74319, -70.72964</t>
+          <t>-33.35999, -70.80705</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>17:45:58</t>
+          <t>61:47:29</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.44</v>
+        <v>0.02</v>
       </c>
       <c r="M12" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>LPR20251E02900022</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1071,58 +1071,58 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026/09/06 00:38:11</t>
+          <t>2026/09/07 00:40:43</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-32.8792633, -70.6087649</t>
+          <t>-33.36765, -70.697163</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-32.87926, -70.60876</t>
+          <t>-33.36765, -70.69716</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026/09/06 09:58:46</t>
+          <t>2026/09/13 22:41:10</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-32.8813949, -70.611115</t>
+          <t>-33.36765, -70.697163</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-32.88139, -70.61111</t>
+          <t>-33.36765, -70.69716</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>09:20:35</t>
+          <t>166:00:27</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1135,53 +1135,53 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026/09/06 00:39:39</t>
+          <t>2026/09/07 00:46:21</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-33.360041, -70.807078</t>
+          <t>-34.205316, -70.677272</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-33.36004, -70.80708</t>
+          <t>-34.20532, -70.67727</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/09/09 14:27:06</t>
+          <t>2026/09/07 02:49:01</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-33.359994, -70.807053</t>
+          <t>-34.205421, -70.677247</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80705</t>
+          <t>-34.20542, -70.67725</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>85:47:27</t>
+          <t>02:02:40</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LPR20251E02900022</t>
+          <t>LPR20251T02800022</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1194,53 +1194,53 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026/09/06 00:42:06</t>
+          <t>2026/09/07 00:56:06</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-33.36765, -70.697163</t>
+          <t>-33.367244, -70.69677</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-33.36765, -70.69716</t>
+          <t>-33.36724, -70.69677</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/09/12 23:41:10</t>
+          <t>2026/09/13 22:56:08</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-33.36765, -70.697163</t>
+          <t>-33.367244, -70.69677</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-33.36765, -70.69716</t>
+          <t>-33.36724, -70.69677</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>166:59:04</t>
+          <t>166:00:02</t>
         </is>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1248,52 +1248,52 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026/09/06 00:46:50</t>
+          <t>2026/09/07 00:56:18</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-34.205316, -70.677272</t>
+          <t>-33.4762, -70.6984416</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-34.20532, -70.67727</t>
+          <t>-33.47620, -70.69844</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/09/07 02:49:01</t>
+          <t>2026/09/07 09:06:46</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-34.205421, -70.677247</t>
+          <t>-33.476265, -70.6983216</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-34.20542, -70.67725</t>
+          <t>-33.47626, -70.69832</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>26:02:11</t>
+          <t>08:10:28</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0.01</v>
+        <v>56.12</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17">
@@ -1312,53 +1312,53 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026/09/06 00:55:09</t>
+          <t>2026/09/07 00:57:15</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-34.042677, -70.681769</t>
+          <t>-34.042702, -70.681741</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-34.04268, -70.68177</t>
+          <t>-34.04270, -70.68174</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026/09/06 00:59:49</t>
+          <t>2026/09/07 09:26:29</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-34.042702, -70.681741</t>
+          <t>-34.042567, -70.681769</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-34.04270, -70.68174</t>
+          <t>-34.04257, -70.68177</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>00:04:40</t>
+          <t>08:29:14</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LPR20251T02800022</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1366,58 +1366,58 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026/09/06 00:56:11</t>
+          <t>2026/09/07 01:04:45</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-33.367244, -70.69677</t>
+          <t>-33.3672483, -70.6957066</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-33.36724, -70.69677</t>
+          <t>-33.36725, -70.69571</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026/09/12 23:56:08</t>
+          <t>2026/09/10 11:40:07</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-33.367244, -70.69677</t>
+          <t>-33.367095, -70.695535</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-33.36724, -70.69677</t>
+          <t>-33.36709, -70.69554</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>166:59:57</t>
+          <t>82:35:22</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>25.32</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1425,58 +1425,58 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026/09/06 00:57:28</t>
+          <t>2026/09/07 01:06:53</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-34.579653, -70.961436</t>
+          <t>-33.0872433, -71.3622583</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-34.57965, -70.96144</t>
+          <t>-33.08724, -71.36226</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026/09/06 01:37:43</t>
+          <t>2026/09/07 09:25:33</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-34.579718, -70.961362</t>
+          <t>-33.08734, -71.3622766</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-34.57972, -70.96136</t>
+          <t>-33.08734, -71.36228</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>00:40:15</t>
+          <t>08:18:40</t>
         </is>
       </c>
       <c r="L19" t="n">
         <v>0.01</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1489,53 +1489,53 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026/09/06 01:04:45</t>
+          <t>2026/09/07 01:38:57</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-33.3672483, -70.6957066</t>
+          <t>-33.4362116, -70.6289783</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-33.36725, -70.69571</t>
+          <t>-33.43621, -70.62898</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026/09/10 11:40:07</t>
+          <t>2026/09/07 06:48:44</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-33.367095, -70.695535</t>
+          <t>-33.44523, -70.6205066</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-33.36709, -70.69554</t>
+          <t>-33.44523, -70.62051</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>106:35:22</t>
+          <t>05:09:47</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>25.32</v>
+        <v>2.03</v>
       </c>
       <c r="M20" t="n">
-        <v>116</v>
+        <v>46</v>
       </c>
       <c r="N20" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>LPR20251T02900038-RTN</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1548,53 +1548,53 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026/09/06 01:57:15</t>
+          <t>2026/09/07 02:22:40</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-34.042702, -70.681741</t>
+          <t>-34.876432, -71.127131</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-34.04270, -70.68174</t>
+          <t>-34.87643, -71.12713</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026/09/07 09:26:29</t>
+          <t>2026/09/09 01:24:54</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-34.042567, -70.681769</t>
+          <t>-34.876565, -71.127273</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-34.04257, -70.68177</t>
+          <t>-34.87656, -71.12727</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>31:29:14</t>
+          <t>47:02:14</t>
         </is>
       </c>
       <c r="L21" t="n">
         <v>0.02</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1602,58 +1602,58 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026/09/06 02:35:12</t>
+          <t>2026/09/07 03:46:28</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-34.579718, -70.961362</t>
+          <t>-34.205421, -70.677247</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-34.57972, -70.96136</t>
+          <t>-34.20542, -70.67725</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026/09/07 15:17:14</t>
+          <t>2026/09/09 02:49:18</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-34.579702, -70.961411</t>
+          <t>-34.205403, -70.677372</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-34.57970, -70.96141</t>
+          <t>-34.20540, -70.67737</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>36:42:02</t>
+          <t>47:02:50</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0.79</v>
+        <v>0.01</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1666,57 +1666,57 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026/09/06 09:43:53</t>
+          <t>2026/09/07 06:15:16</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-33.4365366, -70.6295316</t>
+          <t>-32.8518566, -70.684645</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-33.43654, -70.62953</t>
+          <t>-32.85186, -70.68465</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026/09/06 12:47:48</t>
+          <t>2026/09/07 06:25:12</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-33.5984266, -70.525295</t>
+          <t>-32.8616716, -70.682785</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-33.59843, -70.52529</t>
+          <t>-32.86167, -70.68278</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>03:03:55</t>
+          <t>00:09:56</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>22.4</v>
+        <v>1.12</v>
       </c>
       <c r="M23" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="N23" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1725,57 +1725,57 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026/09/06 10:00:01</t>
+          <t>2026/09/07 06:26:13</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-32.881215, -70.611425</t>
+          <t>-32.870245, -70.6803216</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-32.88121, -70.61142</t>
+          <t>-32.87024, -70.68032</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026/09/06 10:42:57</t>
+          <t>2026/09/07 07:41:35</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-32.829235, -70.6114849</t>
+          <t>-33.35995, -70.8069466</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-32.82923, -70.61148</t>
+          <t>-33.35995, -70.80695</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>00:42:56</t>
+          <t>01:15:22</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>11.52</v>
+        <v>73.16</v>
       </c>
       <c r="M24" t="n">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="N24" t="n">
-        <v>21</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1784,57 +1784,57 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026/09/06 10:43:19</t>
+          <t>2026/09/07 06:49:03</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-32.8296299, -70.6116466</t>
+          <t>-33.4454433, -70.62048</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-32.82963, -70.61165</t>
+          <t>-33.44544, -70.62048</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026/09/06 11:18:17</t>
+          <t>2026/09/07 08:32:41</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-32.8792083, -70.6089216</t>
+          <t>-33.3672766, -70.69572</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-32.87921, -70.60892</t>
+          <t>-33.36728, -70.69572</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>00:34:58</t>
+          <t>01:43:38</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>9.449999999999999</v>
+        <v>14.7</v>
       </c>
       <c r="M25" t="n">
-        <v>56</v>
+        <v>123</v>
       </c>
       <c r="N25" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1843,57 +1843,57 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026/09/06 11:14:45</t>
+          <t>2026/09/07 07:41:48</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-32.838394, -70.955539</t>
+          <t>-33.3599366, -70.8071483</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-32.83839, -70.95554</t>
+          <t>-33.35994, -70.80715</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026/09/06 20:51:33</t>
+          <t>2026/09/07 09:29:03</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-32.785413, -70.895182</t>
+          <t>-33.4558616, -71.3000133</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-32.78541, -70.89518</t>
+          <t>-33.45586, -71.30001</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>09:36:48</t>
+          <t>01:47:15</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>8.789999999999999</v>
+        <v>83.28</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1902,47 +1902,47 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026/09/06 11:18:55</t>
+          <t>2026/09/07 07:51:00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-32.87904, -70.6094516</t>
+          <t>-32.838342, -70.955531</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-32.87904, -70.60945</t>
+          <t>-32.83834, -70.95553</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026/09/06 11:30:15</t>
+          <t>2026/09/07 13:41:17</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-32.8792033, -70.6088833</t>
+          <t>-33.367342, -70.696031</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-32.87920, -70.60888</t>
+          <t>-33.36734, -70.69603</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>00:11:20</t>
+          <t>05:50:17</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.06</v>
+        <v>63.63</v>
       </c>
       <c r="M27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -1961,57 +1961,57 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026/09/06 11:19:05</t>
+          <t>2026/09/07 08:13:46</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-32.7958166, -70.8201116</t>
+          <t>-34.346625, -71.1248716</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-32.79582, -70.82011</t>
+          <t>-34.34663, -71.12487</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026/09/06 11:35:26</t>
+          <t>2026/09/07 08:23:05</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-32.7979433, -70.8272549</t>
+          <t>-34.3462216, -71.1260549</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-32.79794, -70.82725</t>
+          <t>-34.34622, -71.12605</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>00:16:21</t>
+          <t>00:09:19</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.72</v>
+        <v>0.14</v>
       </c>
       <c r="M28" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="N28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2020,53 +2020,53 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026/09/06 11:30:20</t>
+          <t>2026/09/07 08:24:20</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-32.8792066, -70.6088383</t>
+          <t>-34.3471133, -71.1260716</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-32.87921, -70.60884</t>
+          <t>-34.34711, -71.12607</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026/09/06 11:54:27</t>
+          <t>2026/09/07 08:35:59</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-32.87735, -70.6095066</t>
+          <t>-34.3477316, -71.1277883</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-32.87735, -70.60951</t>
+          <t>-34.34773, -71.12779</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>00:24:07</t>
+          <t>00:11:39</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0.85</v>
+        <v>0.33</v>
       </c>
       <c r="M29" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="N29" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2079,47 +2079,47 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026/09/06 11:36:41</t>
+          <t>2026/09/07 08:33:24</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-32.7962016, -70.8278933</t>
+          <t>-33.3672766, -70.69578</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-32.79620, -70.82789</t>
+          <t>-33.36728, -70.69578</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026/09/06 11:54:07</t>
+          <t>2026/09/07 17:09:32</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-32.7677633, -70.8336683</t>
+          <t>-33.398885, -70.6154066</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-32.76776, -70.83367</t>
+          <t>-33.39888, -70.61541</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>00:17:26</t>
+          <t>08:36:08</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.5</v>
+        <v>9.6</v>
       </c>
       <c r="M30" t="n">
-        <v>47</v>
+        <v>107</v>
       </c>
       <c r="N30" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31">
@@ -2138,57 +2138,57 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026/09/06 11:54:28</t>
+          <t>2026/09/07 08:37:14</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-32.7681516, -70.8333683</t>
+          <t>-34.3485866, -71.1278033</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-32.76815, -70.83337</t>
+          <t>-34.34859, -71.12780</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026/09/06 12:07:44</t>
+          <t>2026/09/07 10:50:06</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-32.7977249, -70.8874466</t>
+          <t>-34.3456733, -71.1276716</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-32.79772, -70.88745</t>
+          <t>-34.34567, -71.12767</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>00:13:16</t>
+          <t>02:12:52</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>6.26</v>
+        <v>2.18</v>
       </c>
       <c r="M31" t="n">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="N31" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2197,57 +2197,57 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026/09/06 11:54:49</t>
+          <t>2026/09/07 09:07:02</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-32.8774116, -70.6094399</t>
+          <t>-33.4763083, -70.6983716</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-32.87741, -70.60944</t>
+          <t>-33.47631, -70.69837</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026/09/06 12:04:32</t>
+          <t>2026/09/07 10:00:34</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-32.8791933, -70.6088333</t>
+          <t>-33.4915433, -70.7039133</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-32.87919, -70.60883</t>
+          <t>-33.49154, -70.70391</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>00:09:43</t>
+          <t>00:53:32</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0.88</v>
+        <v>3.16</v>
       </c>
       <c r="M32" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="N32" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2256,116 +2256,116 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026/09/06 12:05:47</t>
+          <t>2026/09/07 09:26:48</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-32.8791933, -70.6088266</t>
+          <t>-33.0873333, -71.3622983</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-32.87919, -70.60883</t>
+          <t>-33.08733, -71.36230</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026/09/06 13:37:21</t>
+          <t>2026/09/07 11:20:40</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-33.5490416, -70.8405516</t>
+          <t>-33.45388, -71.30113</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-33.54904, -70.84055</t>
+          <t>-33.45388, -71.30113</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>01:31:34</t>
+          <t>01:53:52</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>100.35</v>
+        <v>62.66</v>
       </c>
       <c r="M33" t="n">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="N33" t="n">
-        <v>75</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026/09/06 12:08:54</t>
+          <t>2026/09/07 09:26:48</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-32.79762, -70.8870983</t>
+          <t>-34.042559, -70.681776</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-32.79762, -70.88710</t>
+          <t>-34.04256, -70.68178</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026/09/06 16:15:53</t>
+          <t>2026/09/07 14:24:10</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-32.7977583, -70.887415</t>
+          <t>-34.042735, -70.681661</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-32.79776, -70.88742</t>
+          <t>-34.04274, -70.68166</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>04:06:59</t>
+          <t>04:57:22</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8.449999999999999</v>
+        <v>0.03</v>
       </c>
       <c r="M34" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2374,57 +2374,57 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026/09/06 12:48:02</t>
+          <t>2026/09/07 09:29:24</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-33.59851, -70.52519</t>
+          <t>-33.4562233, -71.3000583</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-33.59851, -70.52519</t>
+          <t>-33.45622, -71.30006</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026/09/06 14:32:42</t>
+          <t>2026/09/07 10:40:17</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-33.693515, -70.3346666</t>
+          <t>-33.45636, -71.3000366</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-33.69351, -70.33467</t>
+          <t>-33.45636, -71.30004</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>01:44:40</t>
+          <t>01:10:53</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>28.03</v>
+        <v>0.02</v>
       </c>
       <c r="M35" t="n">
-        <v>69</v>
+        <v>6</v>
       </c>
       <c r="N35" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2433,57 +2433,57 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026/09/06 13:38:36</t>
+          <t>2026/09/07 10:01:13</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-33.548945, -70.8405816</t>
+          <t>-33.4914666, -70.70383</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-33.54895, -70.84058</t>
+          <t>-33.49147, -70.70383</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026/09/06 14:15:50</t>
+          <t>2026/09/07 10:08:41</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-33.4583416, -70.6605216</t>
+          <t>-33.4936616, -70.7056683</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-33.45834, -70.66052</t>
+          <t>-33.49366, -70.70567</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>00:37:14</t>
+          <t>00:07:28</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>27.47</v>
+        <v>0.4</v>
       </c>
       <c r="M36" t="n">
-        <v>126</v>
+        <v>12</v>
       </c>
       <c r="N36" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2492,57 +2492,57 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026/09/06 14:17:05</t>
+          <t>2026/09/07 10:08:51</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-33.4583416, -70.6618449</t>
+          <t>-33.4936216, -70.705685</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-33.45834, -70.66184</t>
+          <t>-33.49362, -70.70569</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026/09/06 17:34:09</t>
+          <t>2026/09/07 10:36:07</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-32.84845, -70.59168</t>
+          <t>-33.476235, -70.6983916</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-32.84845, -70.59168</t>
+          <t>-33.47624, -70.69839</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>03:17:04</t>
+          <t>00:27:16</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>83.43000000000001</v>
+        <v>4.35</v>
       </c>
       <c r="M37" t="n">
-        <v>136</v>
+        <v>67</v>
       </c>
       <c r="N37" t="n">
-        <v>71</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2551,57 +2551,57 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026/09/06 14:33:57</t>
+          <t>2026/09/07 10:36:25</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-33.6935366, -70.334655</t>
+          <t>-33.4763533, -70.6983616</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-33.69354, -70.33465</t>
+          <t>-33.47635, -70.69836</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026/09/06 15:35:55</t>
+          <t>2026/09/07 13:09:57</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-33.6838933, -70.3390666</t>
+          <t>-33.4771333, -70.6980616</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-33.68389, -70.33907</t>
+          <t>-33.47713, -70.69806</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>01:01:58</t>
+          <t>02:33:32</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.21</v>
+        <v>10.77</v>
       </c>
       <c r="M38" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="N38" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2610,53 +2610,53 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026/09/06 15:24:01</t>
+          <t>2026/09/07 10:41:06</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-33.0586466, -71.37246</t>
+          <t>-33.4561933, -71.3000583</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-33.05865, -71.37246</t>
+          <t>-33.45619, -71.30006</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026/09/06 15:39:37</t>
+          <t>2026/09/07 11:59:55</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>-33.0873616, -71.3622666</t>
+          <t>-33.5064066, -71.2516466</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>-33.08736, -71.36227</t>
+          <t>-33.50641, -71.25165</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>00:15:36</t>
+          <t>01:18:49</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.38</v>
+        <v>7.61</v>
       </c>
       <c r="M39" t="n">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="N39" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2669,57 +2669,57 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026/09/06 15:37:10</t>
+          <t>2026/09/07 10:51:21</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-33.680965, -70.3387466</t>
+          <t>-34.3451183, -71.1276366</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-33.68097, -70.33875</t>
+          <t>-34.34512, -71.12764</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026/09/06 16:02:34</t>
+          <t>2026/09/07 10:59:04</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-33.5945, -70.3902549</t>
+          <t>-34.3465466, -71.1251849</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>-33.59450, -70.39025</t>
+          <t>-34.34655, -71.12518</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>00:25:24</t>
+          <t>00:07:43</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>13.27</v>
+        <v>0.31</v>
       </c>
       <c r="M40" t="n">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="N40" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2728,57 +2728,57 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026/09/06 15:40:47</t>
+          <t>2026/09/07 11:00:19</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-33.0872733, -71.3622366</t>
+          <t>-34.3465933, -71.1251816</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-33.08727, -71.36224</t>
+          <t>-34.34659, -71.12518</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026/09/06 17:03:51</t>
+          <t>2026/09/07 11:08:34</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-32.9936133, -71.4735133</t>
+          <t>-34.3456216, -71.12767</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-32.99361, -71.47351</t>
+          <t>-34.34562, -71.12767</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>01:23:04</t>
+          <t>00:08:15</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>25.04</v>
+        <v>0.3</v>
       </c>
       <c r="M41" t="n">
-        <v>106</v>
+        <v>12</v>
       </c>
       <c r="N41" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2787,57 +2787,57 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026/09/06 16:03:14</t>
+          <t>2026/09/07 11:09:49</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-33.5938016, -70.39274</t>
+          <t>-34.3451699, -71.1276666</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-33.59380, -70.39274</t>
+          <t>-34.34517, -71.12767</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026/09/06 16:32:37</t>
+          <t>2026/09/07 11:46:02</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-33.5982049, -70.5221333</t>
+          <t>-34.34755, -71.128765</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-33.59820, -70.52213</t>
+          <t>-34.34755, -71.12877</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>00:29:23</t>
+          <t>00:36:13</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>14.02</v>
+        <v>0.33</v>
       </c>
       <c r="M42" t="n">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="N42" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2846,57 +2846,57 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026/09/06 16:16:21</t>
+          <t>2026/09/07 11:21:55</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-32.7976433, -70.8870716</t>
+          <t>-33.4538883, -71.30263</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-32.79764, -70.88707</t>
+          <t>-33.45389, -71.30263</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026/09/07 08:12:31</t>
+          <t>2026/09/07 11:35:15</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-34.3522566, -71.1172433</t>
+          <t>-33.4540383, -71.3038016</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-34.35226, -71.11724</t>
+          <t>-33.45404, -71.30380</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>15:56:10</t>
+          <t>00:13:20</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>263.06</v>
+        <v>0.12</v>
       </c>
       <c r="M43" t="n">
-        <v>136</v>
+        <v>7</v>
       </c>
       <c r="N43" t="n">
-        <v>69</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2905,57 +2905,57 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026/09/06 16:33:52</t>
+          <t>2026/09/07 11:36:10</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-33.5983416, -70.52602</t>
+          <t>-33.453995, -71.3037966</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-33.59834, -70.52602</t>
+          <t>-33.45399, -71.30380</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026/09/06 17:38:24</t>
+          <t>2026/09/07 14:58:43</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-33.4365083, -70.6289616</t>
+          <t>-33.0483833, -71.6110866</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-33.43651, -70.62896</t>
+          <t>-33.04838, -71.61109</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>01:04:32</t>
+          <t>03:22:33</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>39.69</v>
+        <v>66.77</v>
       </c>
       <c r="M44" t="n">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="N44" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2964,57 +2964,57 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026/09/06 17:05:06</t>
+          <t>2026/09/07 11:47:17</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-32.9935183, -71.47363</t>
+          <t>-34.3467966, -71.1287383</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-32.99352, -71.47363</t>
+          <t>-34.34680, -71.12874</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026/09/06 21:04:52</t>
+          <t>2026/09/07 12:05:44</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-33.0868833, -71.3618233</t>
+          <t>-34.3554716, -71.1014416</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-33.08688, -71.36182</t>
+          <t>-34.35547, -71.10144</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>03:59:46</t>
+          <t>00:18:27</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>32.39</v>
+        <v>2.95</v>
       </c>
       <c r="M45" t="n">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c r="N45" t="n">
-        <v>47</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3023,57 +3023,57 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026/09/06 17:34:58</t>
+          <t>2026/09/07 12:00:06</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-32.848435, -70.5917433</t>
+          <t>-33.5063033, -71.251795</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-32.84844, -70.59174</t>
+          <t>-33.50630, -71.25180</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026/09/06 18:02:45</t>
+          <t>2026/09/07 13:06:05</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-32.8792316, -70.608855</t>
+          <t>-33.4558666, -71.3000266</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-32.87923, -70.60886</t>
+          <t>-33.45587, -71.30003</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>00:27:47</t>
+          <t>01:05:59</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>5.64</v>
+        <v>7.54</v>
       </c>
       <c r="M46" t="n">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="N46" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3082,47 +3082,47 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026/09/06 17:38:57</t>
+          <t>2026/09/07 12:06:16</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-33.4362116, -70.6289783</t>
+          <t>-34.3554033, -71.0988566</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-33.43621, -70.62898</t>
+          <t>-34.35540, -71.09886</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026/09/07 06:48:44</t>
+          <t>2026/09/07 13:15:03</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-33.44523, -70.6205066</t>
+          <t>-34.3476, -71.1287766</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-33.44523, -70.62051</t>
+          <t>-34.34760, -71.12878</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>13:09:47</t>
+          <t>01:08:47</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.03</v>
+        <v>3.43</v>
       </c>
       <c r="M47" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N47" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48">
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3141,47 +3141,47 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026/09/06 18:02:52</t>
+          <t>2026/09/07 12:10:21</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-32.8792366, -70.6087966</t>
+          <t>-32.8791683, -70.6087816</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-32.87924, -70.60880</t>
+          <t>-32.87917, -70.60878</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026/09/07 12:10:06</t>
+          <t>2026/09/07 20:24:57</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-32.8791583, -70.6088666</t>
+          <t>-32.879225, -70.60886</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-32.87916, -70.60887</t>
+          <t>-32.87922, -70.60886</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>18:07:14</t>
+          <t>08:14:36</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0.04</v>
+        <v>15.23</v>
       </c>
       <c r="M48" t="n">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="N48" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49">
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3200,57 +3200,57 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026/09/06 18:19:42</t>
+          <t>2026/09/07 13:06:22</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-32.7430733, -70.7297799</t>
+          <t>-33.456225, -71.3000966</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-32.74307, -70.72978</t>
+          <t>-33.45623, -71.30010</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026/09/07 06:14:01</t>
+          <t>2026/09/07 19:00:44</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-32.851755, -70.68455</t>
+          <t>-32.7431866, -70.7330566</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>-32.85175, -70.68455</t>
+          <t>-32.74319, -70.73306</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>11:54:19</t>
+          <t>05:54:22</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>15.55</v>
+        <v>150.55</v>
       </c>
       <c r="M49" t="n">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="N49" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3259,57 +3259,57 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026/09/06 21:06:07</t>
+          <t>2026/09/07 13:10:10</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-33.0873016, -71.3623533</t>
+          <t>-33.477215, -70.6979716</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-33.08730, -71.36235</t>
+          <t>-33.47722, -70.69797</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026/09/07 09:25:33</t>
+          <t>2026/09/07 13:20:37</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-33.08734, -71.3622766</t>
+          <t>-33.47627, -70.6983666</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>-33.08734, -71.36228</t>
+          <t>-33.47627, -70.69837</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>12:19:26</t>
+          <t>00:10:27</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0.02</v>
+        <v>0.19</v>
       </c>
       <c r="M50" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="N50" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3318,44 +3318,44 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026/09/06 21:09:11</t>
+          <t>2026/09/07 13:16:18</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-32.785376, -70.960422</t>
+          <t>-34.3467849, -71.1287533</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-32.78538, -70.96042</t>
+          <t>-34.34678, -71.12875</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026/09/07 13:41:17</t>
+          <t>2026/09/07 13:35:28</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>-33.367342, -70.696031</t>
+          <t>-34.3457483, -71.1278599</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>-33.36734, -70.69603</t>
+          <t>-34.34575, -71.12786</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>16:32:06</t>
+          <t>00:19:10</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>69.56</v>
+        <v>0.17</v>
       </c>
       <c r="M51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N51" t="n">
         <v>7</v>
@@ -3364,11 +3364,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3377,57 +3377,57 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026/09/07 07:41:48</t>
+          <t>2026/09/07 13:20:53</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-33.3599366, -70.8071483</t>
+          <t>-33.4762883, -70.6983966</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-33.35994, -70.80715</t>
+          <t>-33.47629, -70.69840</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026/09/07 09:29:03</t>
+          <t>2026/09/07 14:51:18</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-33.4558616, -71.3000133</t>
+          <t>-33.5389833, -70.6432516</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>-33.45586, -71.30001</t>
+          <t>-33.53898, -70.64325</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>01:47:15</t>
+          <t>01:30:25</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>83.28</v>
+        <v>14.32</v>
       </c>
       <c r="M52" t="n">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="N52" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3436,53 +3436,53 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026/09/07 09:29:24</t>
+          <t>2026/09/07 13:35:47</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-33.4562233, -71.3000583</t>
+          <t>-34.3463166, -71.127895</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-33.45622, -71.30006</t>
+          <t>-34.34632, -71.12789</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026/09/07 10:40:17</t>
+          <t>2026/09/07 13:44:48</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-33.45636, -71.3000366</t>
+          <t>-34.3456866, -71.125985</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>-33.45636, -71.30004</t>
+          <t>-34.34569, -71.12599</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>01:10:53</t>
+          <t>00:09:01</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0.02</v>
+        <v>0.33</v>
       </c>
       <c r="M53" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N53" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -3495,57 +3495,57 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026/09/07 10:01:13</t>
+          <t>2026/09/07 13:44:01</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-33.4914666, -70.70383</t>
+          <t>-33.368745, -70.698099</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-33.49147, -70.70383</t>
+          <t>-33.36874, -70.69810</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026/09/07 10:08:41</t>
+          <t>2026/09/07 15:18:59</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>-33.4936616, -70.7056683</t>
+          <t>-33.367338, -70.695994</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>-33.49366, -70.70567</t>
+          <t>-33.36734, -70.69599</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>00:07:28</t>
+          <t>01:34:58</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0.4</v>
+        <v>0.26</v>
       </c>
       <c r="M54" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3554,165 +3554,165 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026/09/07 10:08:51</t>
+          <t>2026/09/07 13:45:02</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-33.4936216, -70.705685</t>
+          <t>-34.3459883, -71.1257183</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-33.49362, -70.70569</t>
+          <t>-34.34599, -71.12572</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026/09/07 10:36:07</t>
+          <t>2026/09/07 14:13:02</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-33.476235, -70.6983916</t>
+          <t>-34.3476749, -71.1277766</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>-33.47624, -70.69839</t>
+          <t>-34.34767, -71.12778</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>00:27:16</t>
+          <t>00:28:00</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>4.35</v>
+        <v>0.28</v>
       </c>
       <c r="M55" t="n">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="N55" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C56" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026/09/07 13:46:53</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-34.34603, -71.12569</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-34.34603, -71.12569</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2026/09/07 14:07:25</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>-34.346422, -71.125933</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>-34.34642, -71.12593</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>00:20:32</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="M56" t="n">
         <v>4</v>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2026/09/07 10:36:25</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>-33.4763533, -70.6983616</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>-33.47635, -70.69836</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>2026/09/07 13:09:57</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>-33.4771333, -70.6980616</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>-33.47713, -70.69806</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>02:33:32</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
-        <v>10.77</v>
-      </c>
-      <c r="M56" t="n">
-        <v>61</v>
-      </c>
       <c r="N56" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026/09/07 10:41:06</t>
+          <t>2026/09/07 14:08:20</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-33.4561933, -71.3000583</t>
+          <t>-34.346349, -71.125925</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-33.45619, -71.30006</t>
+          <t>-34.34635, -71.12592</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026/09/07 11:59:55</t>
+          <t>2026/09/07 14:18:02</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>-33.5064066, -71.2516466</t>
+          <t>-34.34672, -71.125939</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-33.50641, -71.25165</t>
+          <t>-34.34672, -71.12594</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>01:18:49</t>
+          <t>00:09:42</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>7.61</v>
+        <v>0.09</v>
       </c>
       <c r="M57" t="n">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="N57" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -3731,116 +3731,116 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026/09/07 11:47:17</t>
+          <t>2026/09/07 14:14:17</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-34.3467966, -71.1287383</t>
+          <t>-34.3485233, -71.127835</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-34.34680, -71.12874</t>
+          <t>-34.34852, -71.12784</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026/09/07 12:05:44</t>
+          <t>2026/09/07 14:42:19</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>-34.3554716, -71.1014416</t>
+          <t>-34.351345, -71.12937</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>-34.35547, -71.10144</t>
+          <t>-34.35135, -71.12937</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>00:18:27</t>
+          <t>00:28:02</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.95</v>
+        <v>0.83</v>
       </c>
       <c r="M58" t="n">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="N58" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026/09/07 12:00:06</t>
+          <t>2026/09/07 14:18:20</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-33.5063033, -71.251795</t>
+          <t>-34.346794, -71.125936</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-33.50630, -71.25180</t>
+          <t>-34.34679, -71.12594</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026/09/07 13:06:05</t>
+          <t>2026/09/07 14:24:20</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>-33.4558666, -71.3000266</t>
+          <t>-34.34633, -71.125927</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>-33.45587, -71.30003</t>
+          <t>-34.34633, -71.12593</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>01:05:59</t>
+          <t>00:06:00</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>7.54</v>
+        <v>0.1</v>
       </c>
       <c r="M59" t="n">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="N59" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -3849,116 +3849,116 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026/09/07 12:06:16</t>
+          <t>2026/09/07 14:24:28</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>-34.3554033, -71.0988566</t>
+          <t>-34.042722, -70.681703</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-34.35540, -71.09886</t>
+          <t>-34.04272, -70.68170</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026/09/07 13:15:03</t>
+          <t>2026/09/08 13:25:22</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>-34.3476, -71.1287766</t>
+          <t>-34.041819, -70.681668</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>-34.34760, -71.12878</t>
+          <t>-34.04182, -70.68167</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>01:08:47</t>
+          <t>23:00:54</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.43</v>
+        <v>0.88</v>
       </c>
       <c r="M60" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="N60" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026/09/07 13:06:22</t>
+          <t>2026/09/07 14:24:44</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-33.456225, -71.3000966</t>
+          <t>-34.346277, -71.125924</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-33.45623, -71.30010</t>
+          <t>-34.34628, -71.12592</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026/09/07 19:00:44</t>
+          <t>2026/09/07 14:33:43</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>-32.7431866, -70.7330566</t>
+          <t>-34.346249, -71.125961</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>-32.74319, -70.73306</t>
+          <t>-34.34625, -71.12596</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>05:54:22</t>
+          <t>00:08:59</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>150.55</v>
+        <v>0.01</v>
       </c>
       <c r="M61" t="n">
-        <v>124</v>
+        <v>3</v>
       </c>
       <c r="N61" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3967,47 +3967,47 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026/09/07 13:10:10</t>
+          <t>2026/09/07 14:34:18</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>-33.477215, -70.6979716</t>
+          <t>-34.346318, -71.126003</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-33.47722, -70.69797</t>
+          <t>-34.34632, -71.12600</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026/09/07 13:20:37</t>
+          <t>2026/09/07 14:54:53</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>-33.47627, -70.6983666</t>
+          <t>-34.346995, -71.126064</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>-33.47627, -70.69837</t>
+          <t>-34.34699, -71.12606</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>00:10:27</t>
+          <t>00:20:35</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="M62" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="N62" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4026,47 +4026,47 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026/09/07 13:16:18</t>
+          <t>2026/09/07 14:43:34</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-34.3467849, -71.1287533</t>
+          <t>-34.3506066, -71.12932</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-34.34678, -71.12875</t>
+          <t>-34.35061, -71.12932</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026/09/07 13:35:28</t>
+          <t>2026/09/07 14:55:11</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>-34.3457483, -71.1278599</t>
+          <t>-34.3466316, -71.1265866</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>-34.34575, -71.12786</t>
+          <t>-34.34663, -71.12659</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>00:19:10</t>
+          <t>00:11:37</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0.17</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M63" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="N63" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="64">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4085,57 +4085,57 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026/09/07 13:20:53</t>
+          <t>2026/09/07 14:52:14</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-33.4762883, -70.6983966</t>
+          <t>-33.5384016, -70.6430566</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-33.47629, -70.69840</t>
+          <t>-33.53840, -70.64306</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026/09/07 14:51:18</t>
+          <t>2026/09/07 15:20:19</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>-33.5389833, -70.6432516</t>
+          <t>-33.4762516, -70.69833</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>-33.53898, -70.64325</t>
+          <t>-33.47625, -70.69833</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>01:30:25</t>
+          <t>00:28:05</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>14.32</v>
+        <v>13.35</v>
       </c>
       <c r="M64" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N64" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4144,47 +4144,47 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026/09/07 13:35:47</t>
+          <t>2026/09/07 14:55:18</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-34.3463166, -71.127895</t>
+          <t>-34.346855, -71.126061</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-34.34632, -71.12789</t>
+          <t>-34.34685, -71.12606</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026/09/07 13:44:48</t>
+          <t>2026/09/07 15:12:17</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>-34.3456866, -71.125985</t>
+          <t>-34.34598, -71.125749</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>-34.34569, -71.12599</t>
+          <t>-34.34598, -71.12575</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>00:09:01</t>
+          <t>00:16:59</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="M65" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="N65" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -4194,7 +4194,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4203,44 +4203,44 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026/09/07 13:45:02</t>
+          <t>2026/09/07 14:56:26</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>-34.3459883, -71.1257183</t>
+          <t>-34.3462733, -71.126005</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-34.34599, -71.12572</t>
+          <t>-34.34627, -71.12601</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026/09/07 14:13:02</t>
+          <t>2026/09/07 15:05:05</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>-34.3476749, -71.1277766</t>
+          <t>-34.3461549, -71.1255633</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>-34.34767, -71.12778</t>
+          <t>-34.34615, -71.12556</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>00:28:00</t>
+          <t>00:08:39</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0.28</v>
+        <v>0.04</v>
       </c>
       <c r="M66" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N66" t="n">
         <v>7</v>
@@ -4249,11 +4249,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4262,116 +4262,116 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026/09/07 13:46:53</t>
+          <t>2026/09/07 14:59:58</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>-34.34603, -71.12569</t>
+          <t>-33.047595, -71.610995</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-34.34603, -71.12569</t>
+          <t>-33.04760, -71.61100</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026/09/07 14:07:25</t>
+          <t>2026/09/07 16:34:50</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>-34.346422, -71.125933</t>
+          <t>-33.0873483, -71.3622616</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>-34.34642, -71.12593</t>
+          <t>-33.08735, -71.36226</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>00:20:32</t>
+          <t>01:34:52</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0.17</v>
+        <v>36.35</v>
       </c>
       <c r="M67" t="n">
-        <v>4</v>
+        <v>122</v>
       </c>
       <c r="N67" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026/09/07 14:08:20</t>
+          <t>2026/09/07 15:06:20</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>-34.346349, -71.125925</t>
+          <t>-34.3464633, -71.12531</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-34.34635, -71.12592</t>
+          <t>-34.34646, -71.12531</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026/09/07 14:18:02</t>
+          <t>2026/09/07 18:30:43</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>-34.34672, -71.125939</t>
+          <t>-32.8795316, -70.6081933</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>-34.34672, -71.12594</t>
+          <t>-32.87953, -70.60819</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>00:09:42</t>
+          <t>03:24:23</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0.09</v>
+        <v>217.83</v>
       </c>
       <c r="M68" t="n">
-        <v>3</v>
+        <v>136</v>
       </c>
       <c r="N68" t="n">
-        <v>3</v>
+        <v>71</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4380,116 +4380,116 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026/09/07 14:14:17</t>
+          <t>2026/09/07 15:12:52</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-34.3485233, -71.127835</t>
+          <t>-34.346006, -71.125762</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-34.34852, -71.12784</t>
+          <t>-34.34601, -71.12576</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026/09/07 14:42:19</t>
+          <t>2026/09/08 08:53:32</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>-34.351345, -71.12937</t>
+          <t>-34.346557, -71.125393</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>-34.35135, -71.12937</t>
+          <t>-34.34656, -71.12539</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>00:28:02</t>
+          <t>17:40:40</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0.83</v>
+        <v>0.11</v>
       </c>
       <c r="M69" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="N69" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C70" t="n">
+        <v>2</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026/09/07 15:18:03</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>-34.579643, -70.961437</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-34.57964, -70.96144</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2026/09/08 07:10:43</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>-34.579698, -70.961429</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>-34.57970, -70.96143</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>15:52:40</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M70" t="n">
+        <v>6</v>
+      </c>
+      <c r="N70" t="n">
         <v>3</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>2026/09/07 14:18:20</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>-34.346794, -71.125936</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>-34.34679, -71.12594</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>2026/09/07 14:24:20</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>-34.34633, -71.125927</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>-34.34633, -71.12593</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>00:06:00</t>
-        </is>
-      </c>
-      <c r="L70" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M70" t="n">
-        <v>2</v>
-      </c>
-      <c r="N70" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4498,116 +4498,116 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026/09/07 14:24:28</t>
+          <t>2026/09/07 15:21:34</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>-34.042722, -70.681703</t>
+          <t>-33.476185, -70.6984216</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-34.04272, -70.68170</t>
+          <t>-33.47619, -70.69842</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026/09/08 13:25:22</t>
+          <t>2026/09/08 07:45:19</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>-34.041819, -70.681668</t>
+          <t>-33.4762716, -70.698355</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>-34.04182, -70.68167</t>
+          <t>-33.47627, -70.69836</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>23:00:54</t>
+          <t>16:23:45</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0.88</v>
+        <v>11.17</v>
       </c>
       <c r="M71" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="N71" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026/09/07 14:24:44</t>
+          <t>2026/09/07 15:28:53</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>-34.346277, -71.125924</t>
+          <t>-33.366952, -70.685523</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-34.34628, -71.12592</t>
+          <t>-33.36695, -70.68552</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026/09/07 14:33:43</t>
+          <t>2026/09/07 16:36:26</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>-34.346249, -71.125961</t>
+          <t>-33.367301, -70.696048</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>-34.34625, -71.12596</t>
+          <t>-33.36730, -70.69605</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>00:08:59</t>
+          <t>01:07:33</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0.01</v>
+        <v>2.6</v>
       </c>
       <c r="M72" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N72" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -4616,57 +4616,57 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026/09/07 14:34:18</t>
+          <t>2026/09/07 16:35:07</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>-34.346318, -71.126003</t>
+          <t>-33.0873233, -71.36235</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-34.34632, -71.12600</t>
+          <t>-33.08732, -71.36235</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026/09/07 14:54:53</t>
+          <t>2026/09/07 20:51:29</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>-34.346995, -71.126064</t>
+          <t>-33.0872983, -71.3622316</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>-34.34699, -71.12606</t>
+          <t>-33.08730, -71.36223</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>00:20:35</t>
+          <t>04:16:22</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0.35</v>
+        <v>0.01</v>
       </c>
       <c r="M73" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N73" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -4675,57 +4675,57 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026/09/07 14:43:34</t>
+          <t>2026/09/07 17:10:47</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>-34.3506066, -71.12932</t>
+          <t>-33.399565, -70.6147666</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-34.35061, -71.12932</t>
+          <t>-33.39957, -70.61477</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026/09/07 14:55:11</t>
+          <t>2026/09/07 17:42:07</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>-34.3466316, -71.1265866</t>
+          <t>-33.4352133, -70.6289483</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>-34.34663, -71.12659</t>
+          <t>-33.43521, -70.62895</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>00:11:37</t>
+          <t>00:31:20</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0.5600000000000001</v>
+        <v>4.71</v>
       </c>
       <c r="M74" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="N74" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -4734,57 +4734,57 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026/09/07 14:52:14</t>
+          <t>2026/09/07 17:27:33</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>-33.5384016, -70.6430566</t>
+          <t>-32.838365, -70.955536</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-33.53840, -70.64306</t>
+          <t>-32.83837, -70.95554</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026/09/07 15:20:19</t>
+          <t>2026/09/08 12:34:32</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>-33.4762516, -70.69833</t>
+          <t>-34.205318, -70.677524</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>-33.47625, -70.69833</t>
+          <t>-34.20532, -70.67752</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>00:28:05</t>
+          <t>19:06:59</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>13.35</v>
+        <v>205.09</v>
       </c>
       <c r="M75" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -4793,57 +4793,57 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026/09/07 14:55:18</t>
+          <t>2026/09/07 17:43:22</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-34.346855, -71.126061</t>
+          <t>-33.4352766, -70.6291383</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-34.34685, -71.12606</t>
+          <t>-33.43528, -70.62914</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026/09/07 15:12:17</t>
+          <t>2026/09/07 17:52:36</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>-34.34598, -71.125749</t>
+          <t>-33.4362933, -70.6296166</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>-34.34598, -71.12575</t>
+          <t>-33.43629, -70.62962</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>00:16:59</t>
+          <t>00:09:14</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0.23</v>
+        <v>0.18</v>
       </c>
       <c r="M76" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="N76" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -4852,47 +4852,47 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026/09/07 14:56:26</t>
+          <t>2026/09/07 17:53:02</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>-34.3462733, -71.126005</t>
+          <t>-33.4367683, -70.6294966</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-34.34627, -71.12601</t>
+          <t>-33.43677, -70.62950</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026/09/07 15:05:05</t>
+          <t>2026/09/08 10:52:21</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>-34.3461549, -71.1255633</t>
+          <t>-33.3665366, -70.6962166</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>-34.34615, -71.12556</t>
+          <t>-33.36654, -70.69622</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>00:08:39</t>
+          <t>16:59:19</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0.04</v>
+        <v>20.07</v>
       </c>
       <c r="M77" t="n">
-        <v>7</v>
+        <v>115</v>
       </c>
       <c r="N77" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="78">
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -4911,57 +4911,57 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026/09/07 15:06:20</t>
+          <t>2026/09/07 18:31:58</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>-34.3464633, -71.12531</t>
+          <t>-32.8794533, -70.6089166</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-34.34646, -71.12531</t>
+          <t>-32.87945, -70.60892</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026/09/07 18:30:43</t>
+          <t>2026/09/07 19:36:36</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>-32.8795316, -70.6081933</t>
+          <t>-32.7977183, -70.88739</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>-32.87953, -70.60819</t>
+          <t>-32.79772, -70.88739</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>03:24:23</t>
+          <t>01:04:38</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>217.83</v>
+        <v>47.17</v>
       </c>
       <c r="M78" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N78" t="n">
-        <v>71</v>
+        <v>48</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -4970,57 +4970,57 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026/09/07 15:12:52</t>
+          <t>2026/09/07 19:01:08</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>-34.346006, -71.125762</t>
+          <t>-32.7433483, -70.7326566</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-34.34601, -71.12576</t>
+          <t>-32.74335, -70.73266</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026/09/08 08:53:32</t>
+          <t>2026/09/07 19:13:22</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>-34.346557, -71.125393</t>
+          <t>-32.7431783, -70.7296383</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>-34.34656, -71.12539</t>
+          <t>-32.74318, -70.72964</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>17:40:40</t>
+          <t>00:12:14</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0.11</v>
+        <v>0.36</v>
       </c>
       <c r="M79" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="N79" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5029,57 +5029,57 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026/09/07 15:18:03</t>
+          <t>2026/09/07 19:14:37</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>-34.579643, -70.961437</t>
+          <t>-32.7432166, -70.729625</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-34.57964, -70.96144</t>
+          <t>-32.74322, -70.72962</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026/09/08 07:10:43</t>
+          <t>2026/09/08 07:25:00</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>-34.579698, -70.961429</t>
+          <t>-33.3599433, -70.8069966</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>-34.57970, -70.96143</t>
+          <t>-33.35994, -70.80700</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>15:52:40</t>
+          <t>12:10:23</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0.18</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="M80" t="n">
-        <v>6</v>
+        <v>102</v>
       </c>
       <c r="N80" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5088,57 +5088,57 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026/09/07 15:21:34</t>
+          <t>2026/09/07 19:37:51</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>-33.476185, -70.6984216</t>
+          <t>-32.7976133, -70.88705</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-33.47619, -70.69842</t>
+          <t>-32.79761, -70.88705</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026/09/08 07:45:19</t>
+          <t>2026/09/07 19:58:39</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>-33.4762716, -70.698355</t>
+          <t>-32.7976666, -70.887215</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>-33.47627, -70.69836</t>
+          <t>-32.79767, -70.88721</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>16:23:45</t>
+          <t>00:20:48</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>11.17</v>
+        <v>7.86</v>
       </c>
       <c r="M81" t="n">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="N81" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5147,57 +5147,57 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026/09/07 17:27:33</t>
+          <t>2026/09/07 19:59:00</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>-32.838365, -70.955536</t>
+          <t>-32.79761, -70.8870333</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95554</t>
+          <t>-32.79761, -70.88703</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026/09/08 12:34:32</t>
+          <t>2026/09/08 07:29:24</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>-34.205318, -70.677524</t>
+          <t>-33.3599616, -70.806975</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>-34.20532, -70.67752</t>
+          <t>-33.35996, -70.80697</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>19:06:59</t>
+          <t>11:30:24</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>205.09</v>
+        <v>104.42</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5206,57 +5206,57 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026/09/07 18:31:58</t>
+          <t>2026/09/07 20:25:08</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>-32.8794533, -70.6089166</t>
+          <t>-32.8792116, -70.6087616</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-32.87945, -70.60892</t>
+          <t>-32.87921, -70.60876</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026/09/07 19:36:36</t>
+          <t>2026/09/08 06:25:15</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>-32.7977183, -70.88739</t>
+          <t>-32.890915, -70.6760283</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>-32.79772, -70.88739</t>
+          <t>-32.89091, -70.67603</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>01:04:38</t>
+          <t>10:00:07</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>47.17</v>
+        <v>8.27</v>
       </c>
       <c r="M83" t="n">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="N83" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5265,116 +5265,116 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026/09/07 19:01:08</t>
+          <t>2026/09/07 20:51:37</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>-32.7433483, -70.7326566</t>
+          <t>-33.0872183, -71.36218</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-32.74335, -70.73266</t>
+          <t>-33.08722, -71.36218</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026/09/07 19:13:22</t>
+          <t>2026/09/08 06:44:06</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>-32.7431783, -70.7296383</t>
+          <t>-33.0872933, -71.362245</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>-32.74318, -70.72964</t>
+          <t>-33.08729, -71.36225</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>00:12:14</t>
+          <t>09:52:29</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0.36</v>
+        <v>14.03</v>
       </c>
       <c r="M84" t="n">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="N84" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C85" t="n">
+        <v>4</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026/09/08 09:56:11</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>-32.885145, -70.6108033</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-32.88515, -70.61080</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2026/09/08 11:56:31</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>-32.8826566, -70.6108616</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>-32.88266, -70.61086</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>02:00:20</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M85" t="n">
+        <v>11</v>
+      </c>
+      <c r="N85" t="n">
         <v>9</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>2026/09/07 19:14:37</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>-32.7432166, -70.729625</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>-32.74322, -70.72962</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>2026/09/08 07:25:00</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>-33.3599433, -70.8069966</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>-33.35994, -70.80700</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>12:10:23</t>
-        </is>
-      </c>
-      <c r="L85" t="n">
-        <v>90.84999999999999</v>
-      </c>
-      <c r="M85" t="n">
-        <v>102</v>
-      </c>
-      <c r="N85" t="n">
-        <v>48</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5383,57 +5383,57 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026/09/07 19:37:51</t>
+          <t>2026/09/08 10:21:07</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>-32.7976133, -70.88705</t>
+          <t>-34.346532, -71.126181</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88705</t>
+          <t>-34.34653, -71.12618</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026/09/07 19:58:39</t>
+          <t>2026/09/08 10:51:28</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>-32.7976666, -70.887215</t>
+          <t>-34.346507, -71.125244</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>-32.79767, -70.88721</t>
+          <t>-34.34651, -71.12524</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>00:20:48</t>
+          <t>00:30:21</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>7.86</v>
+        <v>0.33</v>
       </c>
       <c r="M86" t="n">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="N86" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5442,116 +5442,116 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026/09/07 19:59:00</t>
+          <t>2026/09/08 10:51:48</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>-32.79761, -70.8870333</t>
+          <t>-34.346526, -71.125237</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88703</t>
+          <t>-34.34653, -71.12524</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026/09/08 07:29:24</t>
+          <t>2026/09/08 12:51:39</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>-33.3599616, -70.806975</t>
+          <t>-34.347589, -71.127686</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>-33.35996, -70.80697</t>
+          <t>-34.34759, -71.12769</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>11:30:24</t>
+          <t>01:59:51</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>104.42</v>
+        <v>0.32</v>
       </c>
       <c r="M87" t="n">
-        <v>130</v>
+        <v>4</v>
       </c>
       <c r="N87" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026/09/07 20:51:37</t>
+          <t>2026/09/08 11:12:57</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>-33.0872183, -71.36218</t>
+          <t>-34.579665, -70.961414</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-33.08722, -71.36218</t>
+          <t>-34.57966, -70.96141</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026/09/08 06:44:06</t>
+          <t>2026/09/08 12:50:13</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>-33.0872933, -71.362245</t>
+          <t>-34.579642, -70.961429</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>-33.08729, -71.36225</t>
+          <t>-34.57964, -70.96143</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>09:52:29</t>
+          <t>01:37:16</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>14.03</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5560,53 +5560,53 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026/09/08 09:21:31</t>
+          <t>2026/09/08 11:57:29</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>-34.34731, -71.125642</t>
+          <t>-32.8837916, -70.6108649</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-34.34731, -71.12564</t>
+          <t>-32.88379, -70.61086</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026/09/08 10:21:02</t>
+          <t>2026/09/08 13:19:35</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>-34.346529, -71.126182</t>
+          <t>-32.8831099, -70.6124</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>-34.34653, -71.12618</t>
+          <t>-32.88311, -70.61240</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>00:59:31</t>
+          <t>01:22:06</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.15</v>
+        <v>0.59</v>
       </c>
       <c r="M89" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="N89" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -5614,52 +5614,52 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026/09/08 10:21:07</t>
+          <t>2026/09/08 12:50:16</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>-34.346532, -71.126181</t>
+          <t>-34.579664, -70.961403</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-34.34653, -71.12618</t>
+          <t>-34.57966, -70.96140</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026/09/08 10:51:28</t>
+          <t>2026/09/12 01:36:53</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>-34.346507, -71.125244</t>
+          <t>-34.579636, -70.961312</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>-34.34651, -71.12524</t>
+          <t>-34.57964, -70.96131</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>00:30:21</t>
+          <t>84:46:37</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0.33</v>
+        <v>0.04</v>
       </c>
       <c r="M90" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -5669,7 +5669,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -5678,44 +5678,44 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026/09/08 10:51:48</t>
+          <t>2026/09/08 12:52:39</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>-34.346526, -71.125237</t>
+          <t>-34.347672, -71.127696</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-34.34653, -71.12524</t>
+          <t>-34.34767, -71.12770</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026/09/08 12:51:39</t>
+          <t>2026/09/08 13:02:50</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>-34.347589, -71.127686</t>
+          <t>-34.348743, -71.127672</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>-34.34759, -71.12769</t>
+          <t>-34.34874, -71.12767</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>01:59:51</t>
+          <t>00:10:11</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0.32</v>
+        <v>0.12</v>
       </c>
       <c r="M91" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N91" t="n">
         <v>3</v>
@@ -5724,11 +5724,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -5737,162 +5737,162 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026/09/08 11:12:57</t>
+          <t>2026/09/08 13:03:39</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>-34.579665, -70.961414</t>
+          <t>-34.348853, -71.127667</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-34.57966, -70.96141</t>
+          <t>-34.34885, -71.12767</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026/09/08 12:50:13</t>
+          <t>2026/09/08 13:11:23</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>-34.579642, -70.961429</t>
+          <t>-34.348297, -71.127681</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>-34.57964, -70.96143</t>
+          <t>-34.34830, -71.12768</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>01:37:16</t>
+          <t>00:07:44</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026/09/08 12:50:16</t>
+          <t>2026/09/08 13:19:39</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>-34.579664, -70.961403</t>
+          <t>-32.8830683, -70.6124149</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-34.57966, -70.96140</t>
+          <t>-32.88307, -70.61241</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026/09/12 01:36:53</t>
+          <t>2026/09/08 13:33:06</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>-34.579636, -70.961312</t>
+          <t>-32.8791883, -70.6088416</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>-34.57964, -70.96131</t>
+          <t>-32.87919, -70.60884</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>84:46:37</t>
+          <t>00:13:27</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0.04</v>
+        <v>0.7</v>
       </c>
       <c r="M93" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="N93" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026/09/08 13:03:39</t>
+          <t>2026/09/08 13:25:32</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>-34.348853, -71.127667</t>
+          <t>-34.041832, -70.681694</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-34.34885, -71.12767</t>
+          <t>-34.04183, -70.68169</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026/09/08 13:11:23</t>
+          <t>2026/09/08 15:14:07</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>-34.348297, -71.127681</t>
+          <t>-34.042664, -70.681724</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>-34.34830, -71.12768</t>
+          <t>-34.04266, -70.68172</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>00:07:44</t>
+          <t>01:48:35</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="M94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N94" t="n">
         <v>3</v>
@@ -5901,11 +5901,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -5914,47 +5914,47 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026/09/08 13:25:32</t>
+          <t>2026/09/08 13:33:12</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>-34.041832, -70.681694</t>
+          <t>-32.8791916, -70.6087949</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-34.04183, -70.68169</t>
+          <t>-32.87919, -70.60879</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026/09/08 15:14:07</t>
+          <t>2026/09/08 16:33:23</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>-34.042664, -70.681724</t>
+          <t>-32.8525799, -70.605565</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>-34.04266, -70.68172</t>
+          <t>-32.85258, -70.60556</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>01:48:35</t>
+          <t>03:00:11</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0.15</v>
+        <v>4.13</v>
       </c>
       <c r="M95" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="N95" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="96">
@@ -5964,56 +5964,56 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026/09/08 13:31:35</t>
+          <t>2026/09/08 13:47:25</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>-34.348097, -71.127772</t>
+          <t>-34.346558, -71.125262</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-34.34810, -71.12777</t>
+          <t>-34.34656, -71.12526</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026/09/08 13:46:25</t>
+          <t>2026/09/08 13:55:43</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>-34.346322, -71.1256</t>
+          <t>-34.345942, -71.125755</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>-34.34632, -71.12560</t>
+          <t>-34.34594, -71.12575</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>00:14:50</t>
+          <t>00:08:18</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0.35</v>
+        <v>0.08</v>
       </c>
       <c r="M96" t="n">
         <v>4</v>
       </c>
       <c r="N96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97">
@@ -6023,7 +6023,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6032,57 +6032,57 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026/09/08 13:47:25</t>
+          <t>2026/09/08 13:56:22</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>-34.346558, -71.125262</t>
+          <t>-34.345962, -71.125764</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-34.34656, -71.12526</t>
+          <t>-34.34596, -71.12576</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026/09/08 13:55:43</t>
+          <t>2026/09/13 01:03:52</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>-34.345942, -71.125755</t>
+          <t>-34.345955, -71.125806</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>-34.34594, -71.12575</t>
+          <t>-34.34595, -71.12581</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>00:08:18</t>
+          <t>107:07:30</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="M97" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6091,41 +6091,41 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026/09/08 13:56:22</t>
+          <t>2026/09/08 15:26:45</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>-34.345962, -71.125764</t>
+          <t>-34.042645, -70.681745</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-34.34596, -71.12576</t>
+          <t>-34.04265, -70.68175</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026/09/12 23:01:33</t>
+          <t>2026/09/13 22:57:15</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>-34.34603, -71.125731</t>
+          <t>-34.042553, -70.68171</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>-34.34603, -71.12573</t>
+          <t>-34.04255, -70.68171</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>105:05:11</t>
+          <t>127:30:30</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
@@ -6137,70 +6137,70 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026/09/08 15:26:45</t>
+          <t>2026/09/08 16:34:38</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>-34.042645, -70.681745</t>
+          <t>-32.85218, -70.6075633</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-34.04265, -70.68175</t>
+          <t>-32.85218, -70.60756</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026/09/12 23:57:38</t>
+          <t>2026/09/08 16:53:14</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>-34.042553, -70.68171</t>
+          <t>-32.8324916, -70.6003816</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>-34.04255, -70.68171</t>
+          <t>-32.83249, -70.60038</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>104:30:53</t>
+          <t>00:18:36</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0.02</v>
+        <v>2.76</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6209,57 +6209,57 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026/09/08 16:19:10</t>
+          <t>2026/09/08 16:54:07</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>-33.3599583, -70.8070683</t>
+          <t>-32.8323983, -70.6006216</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-33.35996, -70.80707</t>
+          <t>-32.83240, -70.60062</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026/09/08 18:49:57</t>
+          <t>2026/09/08 17:30:12</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>-32.7432316, -70.7328933</t>
+          <t>-32.87977, -70.6062683</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>-32.74323, -70.73289</t>
+          <t>-32.87977, -70.60627</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>02:30:47</t>
+          <t>00:36:05</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>125.82</v>
+        <v>9.42</v>
       </c>
       <c r="M100" t="n">
-        <v>138</v>
+        <v>47</v>
       </c>
       <c r="N100" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6268,47 +6268,47 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026/09/08 18:27:43</t>
+          <t>2026/09/08 17:30:41</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>-33.3621483, -70.6701383</t>
+          <t>-32.87943, -70.6089433</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-33.36215, -70.67014</t>
+          <t>-32.87943, -70.60894</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026/09/08 19:03:48</t>
+          <t>2026/09/08 18:04:51</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>-33.4762116, -70.6982083</t>
+          <t>-32.820255, -70.6146</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>-33.47621, -70.69821</t>
+          <t>-32.82026, -70.61460</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>00:36:05</t>
+          <t>00:34:10</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>18.07</v>
+        <v>11.94</v>
       </c>
       <c r="M101" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="N101" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="102">
@@ -6318,7 +6318,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6327,57 +6327,57 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026/09/08 18:42:33</t>
+          <t>2026/09/08 18:06:06</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>-32.7582066, -70.7021599</t>
+          <t>-32.8205016, -70.6143333</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-32.75821, -70.70216</t>
+          <t>-32.82050, -70.61433</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026/09/08 19:19:25</t>
+          <t>2026/09/08 18:42:10</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>-32.8792133, -70.6090199</t>
+          <t>-32.7580149, -70.70204</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>-32.87921, -70.60902</t>
+          <t>-32.75801, -70.70204</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>00:36:52</t>
+          <t>00:36:04</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>25.15</v>
+        <v>12.65</v>
       </c>
       <c r="M102" t="n">
-        <v>105</v>
+        <v>61</v>
       </c>
       <c r="N102" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6386,116 +6386,116 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026/09/08 18:50:27</t>
+          <t>2026/09/08 18:42:33</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>-32.7433533, -70.7327166</t>
+          <t>-32.7582066, -70.7021599</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-32.74335, -70.73272</t>
+          <t>-32.75821, -70.70216</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026/09/08 19:08:01</t>
+          <t>2026/09/08 19:19:25</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>-32.7431883, -70.729675</t>
+          <t>-32.8792133, -70.6090199</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>-32.74319, -70.72968</t>
+          <t>-32.87921, -70.60902</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>00:17:34</t>
+          <t>00:36:52</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0.36</v>
+        <v>25.15</v>
       </c>
       <c r="M103" t="n">
-        <v>13</v>
+        <v>105</v>
       </c>
       <c r="N103" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C104" t="n">
+        <v>11</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2026/09/08 18:50:27</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>-32.7433533, -70.7327166</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-32.74335, -70.73272</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2026/09/08 19:08:01</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>-32.7431883, -70.729675</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>-32.74319, -70.72968</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>00:17:34</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M104" t="n">
+        <v>13</v>
+      </c>
+      <c r="N104" t="n">
         <v>10</v>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>2026/09/08 19:05:03</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>-33.4762333, -70.6984166</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>-33.47623, -70.69842</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>2026/09/09 07:44:57</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>-33.4762833, -70.6983599</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>-33.47628, -70.69836</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>12:39:54</t>
-        </is>
-      </c>
-      <c r="L104" t="n">
-        <v>11.17</v>
-      </c>
-      <c r="M104" t="n">
-        <v>58</v>
-      </c>
-      <c r="N104" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6504,57 +6504,57 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026/09/08 19:09:16</t>
+          <t>2026/09/08 19:05:03</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>-32.743165, -70.7297066</t>
+          <t>-33.4762333, -70.6984166</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-32.74316, -70.72971</t>
+          <t>-33.47623, -70.69842</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026/09/09 07:18:24</t>
+          <t>2026/09/09 07:44:57</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>-33.3599916, -70.8071333</t>
+          <t>-33.4762833, -70.6983599</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80713</t>
+          <t>-33.47628, -70.69836</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>12:09:08</t>
+          <t>12:39:54</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>89.91</v>
+        <v>11.17</v>
       </c>
       <c r="M105" t="n">
-        <v>113</v>
+        <v>58</v>
       </c>
       <c r="N105" t="n">
-        <v>57</v>
+        <v>22</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6563,47 +6563,47 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026/09/08 19:20:40</t>
+          <t>2026/09/08 19:09:16</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>-32.8790916, -70.6094466</t>
+          <t>-32.743165, -70.7297066</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-32.87909, -70.60945</t>
+          <t>-32.74316, -70.72971</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026/09/08 19:31:12</t>
+          <t>2026/09/09 07:18:24</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>-32.879155, -70.6093066</t>
+          <t>-33.3599916, -70.8071333</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>-32.87915, -70.60931</t>
+          <t>-33.35999, -70.80713</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>00:10:32</t>
+          <t>12:09:08</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0.01</v>
+        <v>89.91</v>
       </c>
       <c r="M106" t="n">
-        <v>6</v>
+        <v>113</v>
       </c>
       <c r="N106" t="n">
-        <v>6</v>
+        <v>57</v>
       </c>
     </row>
     <row r="107">
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6622,57 +6622,57 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026/09/08 19:31:50</t>
+          <t>2026/09/08 19:20:40</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>-32.8792316, -70.6088183</t>
+          <t>-32.8790916, -70.6094466</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-32.87923, -70.60882</t>
+          <t>-32.87909, -70.60945</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026/09/09 07:06:21</t>
+          <t>2026/09/08 19:31:12</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>-32.879205, -70.60888</t>
+          <t>-32.879155, -70.6093066</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>-32.87920, -70.60888</t>
+          <t>-32.87915, -70.60931</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>11:34:31</t>
+          <t>00:10:32</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>10.18</v>
+        <v>0.01</v>
       </c>
       <c r="M107" t="n">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="N107" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -6681,47 +6681,47 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026/09/09 15:49:12</t>
+          <t>2026/09/08 19:31:50</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>-34.2088533, -70.6784016</t>
+          <t>-32.8792316, -70.6088183</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-34.20885, -70.67840</t>
+          <t>-32.87923, -70.60882</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026/09/09 16:25:24</t>
+          <t>2026/09/09 07:06:21</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>-34.2041083, -70.6790099</t>
+          <t>-32.879205, -70.60888</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>-34.20411, -70.67901</t>
+          <t>-32.87920, -70.60888</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>00:36:12</t>
+          <t>11:34:31</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.07</v>
+        <v>10.18</v>
       </c>
       <c r="M108" t="n">
+        <v>63</v>
+      </c>
+      <c r="N108" t="n">
         <v>27</v>
-      </c>
-      <c r="N108" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="109">
@@ -7317,11 +7317,11 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7330,47 +7330,47 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026/09/10 19:53:35</t>
+          <t>2026/09/11 11:08:47</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>-32.7976283, -70.8870166</t>
+          <t>-33.3649116, -70.4965666</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-32.79763, -70.88702</t>
+          <t>-33.36491, -70.49657</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026/09/11 06:18:20</t>
+          <t>2026/09/11 11:23:05</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>-33.5398733, -70.7089816</t>
+          <t>-33.3588366, -70.4849283</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>-33.53987, -70.70898</t>
+          <t>-33.35884, -70.48493</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>10:24:45</t>
+          <t>00:14:18</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>117.06</v>
+        <v>1.52</v>
       </c>
       <c r="M119" t="n">
-        <v>144</v>
+        <v>39</v>
       </c>
       <c r="N119" t="n">
-        <v>71</v>
+        <v>18</v>
       </c>
     </row>
     <row r="120">
@@ -7380,7 +7380,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7389,47 +7389,47 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026/09/11 11:08:47</t>
+          <t>2026/09/11 11:24:20</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>-33.3649116, -70.4965666</t>
+          <t>-33.3585916, -70.48524</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>-33.36491, -70.49657</t>
+          <t>-33.35859, -70.48524</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026/09/11 11:23:05</t>
+          <t>2026/09/11 18:19:57</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>-33.3588366, -70.4849283</t>
+          <t>-33.5140783, -70.637485</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>-33.35884, -70.48493</t>
+          <t>-33.51408, -70.63748</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>00:14:18</t>
+          <t>06:55:37</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.52</v>
+        <v>33.06</v>
       </c>
       <c r="M120" t="n">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="N120" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="121">
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7448,44 +7448,44 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026/09/11 11:24:20</t>
+          <t>2026/09/11 18:21:12</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>-33.3585916, -70.48524</t>
+          <t>-33.5138849, -70.638245</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-33.35859, -70.48524</t>
+          <t>-33.51388, -70.63824</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026/09/11 18:19:57</t>
+          <t>2026/09/12 08:06:40</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>-33.5140783, -70.637485</t>
+          <t>-33.4510416, -70.6724666</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>-33.51408, -70.63748</t>
+          <t>-33.45104, -70.67247</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>06:55:37</t>
+          <t>13:45:28</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>33.06</v>
+        <v>10.84</v>
       </c>
       <c r="M121" t="n">
-        <v>119</v>
+        <v>60</v>
       </c>
       <c r="N121" t="n">
         <v>26</v>
@@ -7494,11 +7494,11 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7507,37 +7507,37 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026/09/11 16:46:08</t>
+          <t>2026/09/12 02:35:36</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>-33.4364066, -70.629565</t>
+          <t>-34.579636, -70.961312</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>-33.43641, -70.62956</t>
+          <t>-34.57964, -70.96131</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026/09/12 22:46:08</t>
+          <t>2026/09/13 22:34:39</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>-33.4364066, -70.629565</t>
+          <t>-34.579636, -70.961312</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>-33.43641, -70.62956</t>
+          <t>-34.57964, -70.96131</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>30:00:00</t>
+          <t>43:59:03</t>
         </is>
       </c>
       <c r="L122" t="n">
@@ -7557,66 +7557,66 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026/09/11 18:21:12</t>
+          <t>2026/09/12 12:37:06</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>-33.5138849, -70.638245</t>
+          <t>-33.3671549, -70.6958183</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-33.51388, -70.63824</t>
+          <t>-33.36715, -70.69582</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026/09/12 08:06:40</t>
+          <t>2026/09/13 22:37:06</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>-33.4510416, -70.6724666</t>
+          <t>-33.3671549, -70.6958183</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>-33.45104, -70.67247</t>
+          <t>-33.36715, -70.69582</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>13:45:28</t>
+          <t>34:00:00</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>10.84</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7625,41 +7625,41 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026/09/11 22:12:20</t>
+          <t>2026/09/13 11:28:57</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>-32.743195, -70.7296283</t>
+          <t>-32.7975866, -70.8870966</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>-32.74320, -70.72963</t>
+          <t>-32.79759, -70.88710</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026/09/12 22:15:01</t>
+          <t>2026/09/13 21:28:57</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>-32.74302, -70.7297533</t>
+          <t>-32.7975866, -70.8870966</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>-32.74302, -70.72975</t>
+          <t>-32.79759, -70.88710</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>24:02:41</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
         <v>0</v>
@@ -7671,7 +7671,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -7684,41 +7684,41 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026/09/12 12:37:06</t>
+          <t>2026/09/13 14:50:30</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>-33.3671549, -70.6958183</t>
+          <t>-33.476155, -70.6984166</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>-33.36715, -70.69582</t>
+          <t>-33.47615, -70.69842</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026/09/12 22:37:06</t>
+          <t>2026/09/13 22:50:48</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>-33.3671549, -70.6958183</t>
+          <t>-33.47617, -70.6984849</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>-33.36715, -70.69582</t>
+          <t>-33.47617, -70.69848</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>08:00:18</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="M125" t="n">
         <v>0</v>
@@ -7730,11 +7730,11 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -7743,37 +7743,37 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026/09/12 16:50:39</t>
+          <t>2026/09/13 17:24:36</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>-33.0873299, -71.3623866</t>
+          <t>-33.4365983, -70.6295433</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>-33.08733, -71.36239</t>
+          <t>-33.43660, -70.62954</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026/09/12 22:51:25</t>
+          <t>2026/09/13 23:24:36</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>-33.0873299, -71.3623866</t>
+          <t>-33.4365983, -70.6295433</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>-33.08733, -71.36239</t>
+          <t>-33.43660, -70.62954</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>06:00:46</t>
+          <t>06:00:00</t>
         </is>
       </c>
       <c r="L126" t="n">
@@ -7789,11 +7789,11 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -7802,37 +7802,37 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026/09/12 18:27:46</t>
+          <t>2026/09/13 17:38:01</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>-33.476225, -70.6984066</t>
+          <t>-32.8792333, -70.6087783</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>-33.47622, -70.69841</t>
+          <t>-32.87923, -70.60878</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026/09/12 22:29:01</t>
+          <t>2026/09/13 22:44:57</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>-33.476225, -70.6984066</t>
+          <t>-32.8792333, -70.6087783</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>-33.47622, -70.69841</t>
+          <t>-32.87923, -70.60878</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>04:01:15</t>
+          <t>05:06:56</t>
         </is>
       </c>
       <c r="L127" t="n">
@@ -7848,11 +7848,11 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -7861,37 +7861,37 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026/09/12 21:39:50</t>
+          <t>2026/09/13 18:32:25</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>-32.7976249, -70.8871033</t>
+          <t>-33.0872833, -71.3622833</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>-32.79762, -70.88710</t>
+          <t>-33.08728, -71.36228</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026/09/12 23:40:06</t>
+          <t>2026/09/13 22:32:25</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>-32.7976249, -70.8871033</t>
+          <t>-33.0872833, -71.3622833</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>-32.79762, -70.88710</t>
+          <t>-33.08728, -71.36228</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>02:00:16</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L128" t="n">
@@ -7901,6 +7901,65 @@
         <v>0</v>
       </c>
       <c r="N128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>JAC X200 SJTJ-50</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>2026/09/13 18:48:44</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>-32.7431016, -70.729765</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>-32.74310, -70.72977</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>2026/09/13 22:50:22</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>-32.7431016, -70.729765</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>-32.74310, -70.72977</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>04:01:38</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7952,7 +8011,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1894.49</v>
+        <v>1897.17</v>
       </c>
       <c r="C2" t="n">
         <v>71</v>
@@ -7971,7 +8030,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>734.6</v>
+        <v>880.1</v>
       </c>
       <c r="C3" t="n">
         <v>10</v>
@@ -7990,10 +8049,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>974.26</v>
+        <v>915.52</v>
       </c>
       <c r="C4" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -8009,7 +8068,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1317.05</v>
+        <v>1316.64</v>
       </c>
       <c r="C5" t="n">
         <v>53</v>
@@ -8072,7 +8131,7 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
         <v>5</v>
@@ -8091,7 +8150,7 @@
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>6</v>
@@ -8110,7 +8169,7 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>6</v>
@@ -8180,10 +8239,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1511.1</v>
+        <v>1526.1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -8199,16 +8258,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>380.82</v>
+        <v>323.54</v>
       </c>
       <c r="C15" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>138</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16">
@@ -8275,13 +8334,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1330.47</v>
+        <v>1091.16</v>
       </c>
       <c r="C19" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>139</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -855,7 +855,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026/09/13 22:31:26</t>
+          <t>2026/09/13 23:31:38</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>165:59:48</t>
+          <t>167:00:00</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026/09/13 22:41:10</t>
+          <t>2026/09/13 23:41:10</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>166:00:27</t>
+          <t>167:00:27</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/09/13 22:56:08</t>
+          <t>2026/09/13 23:56:08</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>166:00:02</t>
+          <t>167:00:02</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026/09/13 22:57:15</t>
+          <t>2026/09/13 23:57:38</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>127:30:30</t>
+          <t>128:30:53</t>
         </is>
       </c>
       <c r="L98" t="n">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026/09/13 22:34:39</t>
+          <t>2026/09/13 23:34:24</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>43:59:03</t>
+          <t>44:58:48</t>
         </is>
       </c>
       <c r="L122" t="n">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026/09/13 21:28:57</t>
+          <t>2026/09/13 23:28:57</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="L124" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -2243,7 +2243,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2261,48 +2261,48 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-33.0873333, -71.3622983</t>
+          <t>-34.042559, -70.681776</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-33.08733, -71.36230</t>
+          <t>-34.04256, -70.68178</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026/09/07 11:20:40</t>
+          <t>2026/09/07 14:24:10</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-33.45388, -71.30113</t>
+          <t>-34.042735, -70.681661</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-33.45388, -71.30113</t>
+          <t>-34.04274, -70.68166</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>01:53:52</t>
+          <t>04:57:22</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>62.66</v>
+        <v>0.03</v>
       </c>
       <c r="M33" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2320,42 +2320,42 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-34.042559, -70.681776</t>
+          <t>-33.0873333, -71.3622983</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-34.04256, -70.68178</t>
+          <t>-33.08733, -71.36230</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026/09/07 14:24:10</t>
+          <t>2026/09/07 11:20:40</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-34.042735, -70.681661</t>
+          <t>-33.45388, -71.30113</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-34.04274, -70.68166</t>
+          <t>-33.45388, -71.30113</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>04:57:22</t>
+          <t>01:53:52</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0.03</v>
+        <v>62.66</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,13 +446,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N129"/>
+  <dimension ref="A1:N146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Desde : 2026/09/07 04:00:00   Hasta : 2026/09/14 03:59:59</t>
+          <t>Desde : 2026/09/08 04:00:00   Hasta : 2026/09/15 03:59:59</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>LPR20251A02800014-DS</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -545,53 +545,53 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026/09/07 00:01:31</t>
+          <t>2026/09/08 00:12:08</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-34.346093, -71.125792</t>
+          <t>-34.205461, -70.677261</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-34.34609, -71.12579</t>
+          <t>-34.20546, -70.67726</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026/09/07 13:46:06</t>
+          <t>2026/09/14 23:11:58</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-34.345978, -71.125792</t>
+          <t>-34.205357, -70.677307</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-34.34598, -71.12579</t>
+          <t>-34.20536, -70.67731</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>13:44:35</t>
+          <t>166:59:50</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -604,53 +604,53 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026/09/07 00:12:15</t>
+          <t>2026/09/08 00:14:09</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-34.205461, -70.677261</t>
+          <t>-34.345998, -71.125808</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-34.20546, -70.67726</t>
+          <t>-34.34600, -71.12581</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026/09/13 23:11:38</t>
+          <t>2026/09/08 08:53:32</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-34.205371, -70.67735</t>
+          <t>-34.346557, -71.125393</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-34.20537, -70.67735</t>
+          <t>-34.34656, -71.12539</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>166:59:23</t>
+          <t>08:39:23</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -663,53 +663,53 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026/09/07 00:16:21</t>
+          <t>2026/09/08 00:17:41</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-32.7976433, -70.8870716</t>
+          <t>-34.579664, -70.961395</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-32.79764, -70.88707</t>
+          <t>-34.57966, -70.96139</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026/09/07 08:12:31</t>
+          <t>2026/09/08 07:10:43</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-34.3522566, -71.1172433</t>
+          <t>-34.579698, -70.961429</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-34.35226, -71.11724</t>
+          <t>-34.57970, -70.96143</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>07:56:10</t>
+          <t>06:53:02</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>263.06</v>
+        <v>0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>136</v>
+        <v>6</v>
       </c>
       <c r="N6" t="n">
-        <v>69</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>LPR20251T02900038-RTN</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -717,58 +717,58 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026/09/07 00:20:08</t>
+          <t>2026/09/08 00:23:56</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-32.7430733, -70.7297799</t>
+          <t>-34.876432, -71.127131</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-32.74307, -70.72978</t>
+          <t>-34.87643, -71.12713</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026/09/07 06:14:01</t>
+          <t>2026/09/09 01:24:54</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-32.851755, -70.68455</t>
+          <t>-34.876565, -71.127273</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-32.85175, -70.68455</t>
+          <t>-34.87656, -71.12727</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>05:53:53</t>
+          <t>25:00:58</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>15.55</v>
+        <v>0.02</v>
       </c>
       <c r="M7" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LPR20251T02900038-RTN</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -776,58 +776,58 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026/09/07 00:24:46</t>
+          <t>2026/09/08 00:25:08</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-34.87659, -71.127088</t>
+          <t>-32.8792116, -70.6087616</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-34.87659, -71.12709</t>
+          <t>-32.87921, -70.60876</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026/09/07 01:24:55</t>
+          <t>2026/09/08 06:25:15</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-34.876432, -71.127131</t>
+          <t>-32.890915, -70.6760283</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-34.87643, -71.12713</t>
+          <t>-32.89091, -70.67603</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>01:00:09</t>
+          <t>06:00:07</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.02</v>
+        <v>8.27</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LPR20251V02900023-LL</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -835,58 +835,58 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026/09/07 00:31:38</t>
+          <t>2026/09/08 00:25:50</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-33.89982, -71.429438</t>
+          <t>-34.042686, -70.681746</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-33.89982, -71.42944</t>
+          <t>-34.04269, -70.68175</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026/09/13 23:31:38</t>
+          <t>2026/09/08 13:25:22</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-33.899848, -71.429508</t>
+          <t>-34.041819, -70.681668</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-33.89985, -71.42951</t>
+          <t>-34.04182, -70.68167</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>167:00:00</t>
+          <t>12:59:32</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.02</v>
+        <v>0.87</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>LPR20251V02900023-LL</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -894,58 +894,58 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026/09/07 00:32:27</t>
+          <t>2026/09/08 00:31:38</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-32.8792366, -70.6087949</t>
+          <t>-33.89982, -71.429438</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-32.87924, -70.60879</t>
+          <t>-33.89982, -71.42944</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/09/07 12:10:06</t>
+          <t>2026/09/14 22:31:38</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-32.8791583, -70.6088666</t>
+          <t>-33.899867, -71.429399</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-32.87916, -70.60887</t>
+          <t>-33.89987, -71.42940</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>11:37:39</t>
+          <t>166:00:00</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="M10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -953,58 +953,58 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026/09/07 00:35:43</t>
+          <t>2026/09/08 00:39:38</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-34.579718, -70.961362</t>
+          <t>-33.360041, -70.807078</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-34.57972, -70.96136</t>
+          <t>-33.36004, -70.80708</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026/09/07 15:17:14</t>
+          <t>2026/09/09 14:27:06</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-34.579702, -70.961411</t>
+          <t>-33.359994, -70.807053</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-34.57970, -70.96141</t>
+          <t>-33.35999, -70.80705</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>14:41:31</t>
+          <t>37:47:28</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.79</v>
+        <v>0.02</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>LPR20251E02900022</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1017,53 +1017,53 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026/09/07 00:39:37</t>
+          <t>2026/09/08 00:40:43</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-33.360041, -70.807078</t>
+          <t>-33.36765, -70.697163</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-33.36004, -70.80708</t>
+          <t>-33.36765, -70.69716</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026/09/09 14:27:06</t>
+          <t>2026/09/14 22:41:51</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-33.359994, -70.807053</t>
+          <t>-33.36765, -70.697163</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80705</t>
+          <t>-33.36765, -70.69716</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>61:47:29</t>
+          <t>166:01:08</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LPR20251E02900022</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1076,53 +1076,53 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026/09/07 00:40:43</t>
+          <t>2026/09/08 00:46:51</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-33.36765, -70.697163</t>
+          <t>-34.205421, -70.677247</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-33.36765, -70.69716</t>
+          <t>-34.20542, -70.67725</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026/09/13 23:41:10</t>
+          <t>2026/09/09 02:49:18</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-33.36765, -70.697163</t>
+          <t>-34.205403, -70.677372</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-33.36765, -70.69716</t>
+          <t>-34.20540, -70.67737</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>167:00:27</t>
+          <t>26:02:27</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1130,52 +1130,52 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026/09/07 00:46:21</t>
+          <t>2026/09/08 00:51:37</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-34.205316, -70.677272</t>
+          <t>-33.0872183, -71.36218</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-34.20532, -70.67727</t>
+          <t>-33.08722, -71.36218</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/09/07 02:49:01</t>
+          <t>2026/09/08 06:44:06</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-34.205421, -70.677247</t>
+          <t>-33.0872933, -71.362245</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-34.20542, -70.67725</t>
+          <t>-33.08729, -71.36225</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>02:02:40</t>
+          <t>05:52:29</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.01</v>
+        <v>14.03</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026/09/07 00:56:06</t>
+          <t>2026/09/08 00:56:06</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/09/13 23:56:08</t>
+          <t>2026/09/14 22:56:13</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>167:00:02</t>
+          <t>166:00:07</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -1240,7 +1240,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1253,53 +1253,53 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026/09/07 00:56:18</t>
+          <t>2026/09/08 01:04:45</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-33.4762, -70.6984416</t>
+          <t>-33.3672483, -70.6957066</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-33.47620, -70.69844</t>
+          <t>-33.36725, -70.69571</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/09/07 09:06:46</t>
+          <t>2026/09/10 11:40:07</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-33.476265, -70.6983216</t>
+          <t>-33.367095, -70.695535</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-33.47626, -70.69832</t>
+          <t>-33.36709, -70.69554</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>08:10:28</t>
+          <t>58:35:22</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>56.12</v>
+        <v>25.32</v>
       </c>
       <c r="M16" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="N16" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1307,58 +1307,58 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026/09/07 00:57:15</t>
+          <t>2026/09/08 01:15:37</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-34.042702, -70.681741</t>
+          <t>-32.7431466, -70.729705</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-34.04270, -70.68174</t>
+          <t>-32.74315, -70.72970</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026/09/07 09:26:29</t>
+          <t>2026/09/08 07:25:00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-34.042567, -70.681769</t>
+          <t>-33.3599433, -70.8069966</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-34.04257, -70.68177</t>
+          <t>-33.35994, -70.80700</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>08:29:14</t>
+          <t>06:09:23</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0.02</v>
+        <v>90.84</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1371,53 +1371,53 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026/09/07 01:04:45</t>
+          <t>2026/09/08 01:21:38</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-33.3672483, -70.6957066</t>
+          <t>-33.476185, -70.6984216</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-33.36725, -70.69571</t>
+          <t>-33.47619, -70.69842</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026/09/10 11:40:07</t>
+          <t>2026/09/08 07:45:19</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-33.367095, -70.695535</t>
+          <t>-33.4762716, -70.698355</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-33.36709, -70.69554</t>
+          <t>-33.47627, -70.69836</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>82:35:22</t>
+          <t>06:23:41</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>25.32</v>
+        <v>11.17</v>
       </c>
       <c r="M18" t="n">
-        <v>116</v>
+        <v>39</v>
       </c>
       <c r="N18" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1430,47 +1430,47 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026/09/07 01:06:53</t>
+          <t>2026/09/08 01:48:03</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-33.0872433, -71.3622583</t>
+          <t>-32.79761, -70.8870333</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-33.08724, -71.36226</t>
+          <t>-32.79761, -70.88703</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026/09/07 09:25:33</t>
+          <t>2026/09/08 07:29:24</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-33.08734, -71.3622766</t>
+          <t>-33.3599616, -70.806975</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-33.08734, -71.36228</t>
+          <t>-33.35996, -70.80697</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>08:18:40</t>
+          <t>05:41:21</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0.01</v>
+        <v>104.42</v>
       </c>
       <c r="M19" t="n">
-        <v>8</v>
+        <v>130</v>
       </c>
       <c r="N19" t="n">
-        <v>7</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20">
@@ -1489,53 +1489,53 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026/09/07 01:38:57</t>
+          <t>2026/09/08 01:54:08</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-33.4362116, -70.6289783</t>
+          <t>-33.4367683, -70.6294966</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-33.43621, -70.62898</t>
+          <t>-33.43677, -70.62950</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026/09/07 06:48:44</t>
+          <t>2026/09/08 10:52:21</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-33.44523, -70.6205066</t>
+          <t>-33.3665366, -70.6962166</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-33.44523, -70.62051</t>
+          <t>-33.36654, -70.69622</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>05:09:47</t>
+          <t>08:58:13</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.03</v>
+        <v>20.07</v>
       </c>
       <c r="M20" t="n">
-        <v>46</v>
+        <v>115</v>
       </c>
       <c r="N20" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LPR20251T02900038-RTN</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1543,58 +1543,58 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026/09/07 02:22:40</t>
+          <t>2026/09/08 06:26:30</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-34.876432, -71.127131</t>
+          <t>-32.8942116, -70.6761066</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-34.87643, -71.12713</t>
+          <t>-32.89421, -70.67611</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026/09/09 01:24:54</t>
+          <t>2026/09/08 06:59:05</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-34.876565, -71.127273</t>
+          <t>-32.8791666, -70.6088066</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-34.87656, -71.12727</t>
+          <t>-32.87917, -70.60881</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>47:02:14</t>
+          <t>00:32:35</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0.02</v>
+        <v>18.36</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1602,62 +1602,62 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026/09/07 03:46:28</t>
+          <t>2026/09/08 06:45:08</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-34.205421, -70.677247</t>
+          <t>-33.0872633, -71.3623066</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-34.20542, -70.67725</t>
+          <t>-33.08726, -71.36231</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026/09/09 02:49:18</t>
+          <t>2026/09/08 08:37:50</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-34.205403, -70.677372</t>
+          <t>-33.3674749, -70.6960416</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-34.20540, -70.67737</t>
+          <t>-33.36747, -70.69604</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>47:02:50</t>
+          <t>01:52:42</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0.01</v>
+        <v>114.44</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>133</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1666,47 +1666,47 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026/09/07 06:15:16</t>
+          <t>2026/09/08 06:59:10</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-32.8518566, -70.684645</t>
+          <t>-32.8791699, -70.6087816</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-32.85186, -70.68465</t>
+          <t>-32.87917, -70.60878</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026/09/07 06:25:12</t>
+          <t>2026/09/08 09:26:09</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-32.8616716, -70.682785</t>
+          <t>-32.8828116, -70.6107533</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-32.86167, -70.68278</t>
+          <t>-32.88281, -70.61075</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>00:09:56</t>
+          <t>02:26:59</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="M23" t="n">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="N23" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1725,53 +1725,53 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026/09/07 06:26:13</t>
+          <t>2026/09/08 07:25:07</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-32.870245, -70.6803216</t>
+          <t>-33.3599233, -70.80713</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-32.87024, -70.68032</t>
+          <t>-33.35992, -70.80713</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026/09/07 07:41:35</t>
+          <t>2026/09/08 07:35:57</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-33.35995, -70.8069466</t>
+          <t>-33.3604983, -70.80907</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-33.35995, -70.80695</t>
+          <t>-33.36050, -70.80907</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>01:15:22</t>
+          <t>00:10:50</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>73.16</v>
+        <v>0.45</v>
       </c>
       <c r="M24" t="n">
-        <v>124</v>
+        <v>23</v>
       </c>
       <c r="N24" t="n">
-        <v>63</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1784,47 +1784,47 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026/09/07 06:49:03</t>
+          <t>2026/09/08 07:30:39</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-33.4454433, -70.62048</t>
+          <t>-33.3598966, -70.807195</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-33.44544, -70.62048</t>
+          <t>-33.35990, -70.80719</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026/09/07 08:32:41</t>
+          <t>2026/09/08 08:08:44</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-33.3672766, -70.69572</t>
+          <t>-33.361905, -70.8066533</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-33.36728, -70.69572</t>
+          <t>-33.36191, -70.80665</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>01:43:38</t>
+          <t>00:38:05</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>14.7</v>
+        <v>0.26</v>
       </c>
       <c r="M25" t="n">
-        <v>123</v>
+        <v>10</v>
       </c>
       <c r="N25" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1843,57 +1843,57 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026/09/07 07:41:48</t>
+          <t>2026/09/08 07:36:10</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-33.3599366, -70.8071483</t>
+          <t>-33.3605033, -70.8090983</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-33.35994, -70.80715</t>
+          <t>-33.36050, -70.80910</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026/09/07 09:29:03</t>
+          <t>2026/09/08 07:47:06</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-33.4558616, -71.3000133</t>
+          <t>-33.3599566, -70.807025</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-33.45586, -71.30001</t>
+          <t>-33.35996, -70.80702</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>01:47:15</t>
+          <t>00:10:56</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>83.28</v>
+        <v>0.26</v>
       </c>
       <c r="M26" t="n">
-        <v>121</v>
+        <v>12</v>
       </c>
       <c r="N26" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1902,57 +1902,57 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026/09/07 07:51:00</t>
+          <t>2026/09/08 07:45:27</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-32.838342, -70.955531</t>
+          <t>-33.476315, -70.6983983</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-32.83834, -70.95553</t>
+          <t>-33.47631, -70.69840</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026/09/07 13:41:17</t>
+          <t>2026/09/08 09:05:30</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-33.367342, -70.696031</t>
+          <t>-33.3621866, -70.67011</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-33.36734, -70.69603</t>
+          <t>-33.36219, -70.67011</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>05:50:17</t>
+          <t>01:20:03</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>63.63</v>
+        <v>18.14</v>
       </c>
       <c r="M27" t="n">
-        <v>7</v>
+        <v>95</v>
       </c>
       <c r="N27" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1961,57 +1961,57 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026/09/07 08:13:46</t>
+          <t>2026/09/08 07:47:11</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-34.346625, -71.1248716</t>
+          <t>-33.3599733, -70.8071166</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-34.34663, -71.12487</t>
+          <t>-33.35997, -70.80712</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026/09/07 08:23:05</t>
+          <t>2026/09/08 09:25:14</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-34.3462216, -71.1260549</t>
+          <t>-33.50219, -71.2540533</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-34.34622, -71.12605</t>
+          <t>-33.50219, -71.25405</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>00:09:19</t>
+          <t>01:38:03</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.14</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="N28" t="n">
-        <v>9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2020,106 +2020,106 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026/09/07 08:24:20</t>
+          <t>2026/09/08 07:48:57</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-34.3471133, -71.1260716</t>
+          <t>-32.838378, -70.955472</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-34.34711, -71.12607</t>
+          <t>-32.83838, -70.95547</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026/09/07 08:35:59</t>
+          <t>2026/09/08 12:34:32</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-34.3477316, -71.1277883</t>
+          <t>-34.205318, -70.677524</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-34.34773, -71.12779</t>
+          <t>-34.20532, -70.67752</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>00:11:39</t>
+          <t>04:45:35</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0.33</v>
+        <v>157.73</v>
       </c>
       <c r="M29" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026/09/08 08:08:16</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-34.579645, -70.961417</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-34.57964, -70.96142</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026/09/08 11:12:19</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>-34.579516, -70.961464</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>-34.57952, -70.96146</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>03:04:03</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M30" t="n">
+        <v>6</v>
+      </c>
+      <c r="N30" t="n">
         <v>3</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2026/09/07 08:33:24</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>-33.3672766, -70.69578</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>-33.36728, -70.69578</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2026/09/07 17:09:32</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>-33.398885, -70.6154066</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>-33.39888, -70.61541</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>08:36:08</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="M30" t="n">
-        <v>107</v>
-      </c>
-      <c r="N30" t="n">
-        <v>42</v>
       </c>
     </row>
     <row r="31">
@@ -2129,7 +2129,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2138,44 +2138,44 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026/09/07 08:37:14</t>
+          <t>2026/09/08 08:08:54</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-34.3485866, -71.1278033</t>
+          <t>-33.3617616, -70.8065883</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-34.34859, -71.12780</t>
+          <t>-33.36176, -70.80659</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026/09/07 10:50:06</t>
+          <t>2026/09/08 09:18:01</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-34.3456733, -71.1276716</t>
+          <t>-33.3619549, -70.8066866</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-34.34567, -71.12767</t>
+          <t>-33.36195, -70.80669</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>02:12:52</t>
+          <t>01:09:07</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.18</v>
+        <v>1.08</v>
       </c>
       <c r="M31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N31" t="n">
         <v>9</v>
@@ -2184,11 +2184,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2197,53 +2197,53 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026/09/07 09:07:02</t>
+          <t>2026/09/08 08:38:28</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-33.4763083, -70.6983716</t>
+          <t>-33.36745, -70.695995</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-33.47631, -70.69837</t>
+          <t>-33.36745, -70.69599</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026/09/07 10:00:34</t>
+          <t>2026/09/08 09:51:52</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-33.4915433, -70.7039133</t>
+          <t>-33.3672816, -70.6966333</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-33.49154, -70.70391</t>
+          <t>-33.36728, -70.69663</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>00:53:32</t>
+          <t>01:13:24</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.16</v>
+        <v>0.11</v>
       </c>
       <c r="M32" t="n">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="N32" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2256,57 +2256,57 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026/09/07 09:26:48</t>
+          <t>2026/09/08 08:53:53</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-34.042559, -70.681776</t>
+          <t>-34.346686, -71.125357</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-34.04256, -70.68178</t>
+          <t>-34.34669, -71.12536</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026/09/07 14:24:10</t>
+          <t>2026/09/08 09:20:35</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-34.042735, -70.681661</t>
+          <t>-34.347231, -71.12564</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-34.04274, -70.68166</t>
+          <t>-34.34723, -71.12564</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>04:57:22</t>
+          <t>00:26:42</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2315,57 +2315,57 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026/09/07 09:26:48</t>
+          <t>2026/09/08 09:05:40</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-33.0873333, -71.3622983</t>
+          <t>-33.36221, -70.67015</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-33.08733, -71.36230</t>
+          <t>-33.36221, -70.67015</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026/09/07 11:20:40</t>
+          <t>2026/09/08 09:28:13</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-33.45388, -71.30113</t>
+          <t>-33.3672933, -70.6960233</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-33.45388, -71.30113</t>
+          <t>-33.36729, -70.69602</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>01:53:52</t>
+          <t>00:22:33</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>62.66</v>
+        <v>6.28</v>
       </c>
       <c r="M34" t="n">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="N34" t="n">
-        <v>54</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2374,41 +2374,41 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026/09/07 09:29:24</t>
+          <t>2026/09/08 09:18:11</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-33.4562233, -71.3000583</t>
+          <t>-33.3618266, -70.8065583</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-33.45622, -71.30006</t>
+          <t>-33.36183, -70.80656</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026/09/07 10:40:17</t>
+          <t>2026/09/08 10:25:08</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-33.45636, -71.3000366</t>
+          <t>-33.3612233, -70.8067816</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-33.45636, -71.30004</t>
+          <t>-33.36122, -70.80678</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>01:10:53</t>
+          <t>01:06:57</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="M35" t="n">
         <v>6</v>
@@ -2420,7 +2420,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2433,57 +2433,57 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026/09/07 10:01:13</t>
+          <t>2026/09/08 09:21:31</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-33.4914666, -70.70383</t>
+          <t>-34.34731, -71.125642</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-33.49147, -70.70383</t>
+          <t>-34.34731, -71.12564</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026/09/07 10:08:41</t>
+          <t>2026/09/08 10:21:02</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-33.4936616, -70.7056683</t>
+          <t>-34.346529, -71.126182</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-33.49366, -70.70567</t>
+          <t>-34.34653, -71.12618</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>00:07:28</t>
+          <t>00:59:31</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0.4</v>
+        <v>1.15</v>
       </c>
       <c r="M36" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N36" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2492,57 +2492,57 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026/09/07 10:08:51</t>
+          <t>2026/09/08 09:25:22</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-33.4936216, -70.705685</t>
+          <t>-33.5022033, -71.2540949</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-33.49362, -70.70569</t>
+          <t>-33.50220, -71.25409</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026/09/07 10:36:07</t>
+          <t>2026/09/08 09:42:28</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-33.476235, -70.6983916</t>
+          <t>-33.4650766, -71.2937683</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-33.47624, -70.69839</t>
+          <t>-33.46508, -71.29377</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>00:27:16</t>
+          <t>00:17:06</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.35</v>
+        <v>5.92</v>
       </c>
       <c r="M37" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="N37" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2551,57 +2551,57 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026/09/07 10:36:25</t>
+          <t>2026/09/08 09:27:24</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-33.4763533, -70.6983616</t>
+          <t>-32.8837233, -70.6107216</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-33.47635, -70.69836</t>
+          <t>-32.88372, -70.61072</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026/09/07 13:09:57</t>
+          <t>2026/09/08 09:55:11</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-33.4771333, -70.6980616</t>
+          <t>-32.8851833, -70.6109416</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-33.47713, -70.69806</t>
+          <t>-32.88518, -70.61094</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>02:33:32</t>
+          <t>00:27:47</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>10.77</v>
+        <v>1.06</v>
       </c>
       <c r="M38" t="n">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="N38" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2610,57 +2610,57 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026/09/07 10:41:06</t>
+          <t>2026/09/08 09:28:50</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-33.4561933, -71.3000583</t>
+          <t>-33.3672833, -70.6957583</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-33.45619, -71.30006</t>
+          <t>-33.36728, -70.69576</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026/09/07 11:59:55</t>
+          <t>2026/09/08 11:20:46</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>-33.5064066, -71.2516466</t>
+          <t>-34.0115399, -70.7038966</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>-33.50641, -71.25165</t>
+          <t>-34.01154, -70.70390</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>01:18:49</t>
+          <t>01:51:56</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>7.61</v>
+        <v>98.23999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="N39" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2669,57 +2669,57 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026/09/07 10:51:21</t>
+          <t>2026/09/08 09:42:31</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-34.3451183, -71.1276366</t>
+          <t>-33.4650599, -71.293765</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-34.34512, -71.12764</t>
+          <t>-33.46506, -71.29376</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026/09/07 10:59:04</t>
+          <t>2026/09/08 09:57:49</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-34.3465466, -71.1251849</t>
+          <t>-33.455855, -71.3000183</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>-34.34655, -71.12518</t>
+          <t>-33.45585, -71.30002</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>00:07:43</t>
+          <t>00:15:18</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0.31</v>
+        <v>1.41</v>
       </c>
       <c r="M40" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="N40" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2728,57 +2728,57 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026/09/07 11:00:19</t>
+          <t>2026/09/08 09:52:20</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-34.3465933, -71.1251816</t>
+          <t>-33.3672933, -70.6966283</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-34.34659, -71.12518</t>
+          <t>-33.36729, -70.69663</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026/09/07 11:08:34</t>
+          <t>2026/09/08 17:41:52</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-34.3456216, -71.12767</t>
+          <t>-33.0873283, -71.362315</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-34.34562, -71.12767</t>
+          <t>-33.08733, -71.36231</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>00:08:15</t>
+          <t>07:49:32</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0.3</v>
+        <v>122.46</v>
       </c>
       <c r="M41" t="n">
-        <v>12</v>
+        <v>128</v>
       </c>
       <c r="N41" t="n">
-        <v>9</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2787,57 +2787,57 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026/09/07 11:09:49</t>
+          <t>2026/09/08 09:56:11</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-34.3451699, -71.1276666</t>
+          <t>-32.885145, -70.6108033</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-34.34517, -71.12767</t>
+          <t>-32.88515, -70.61080</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026/09/07 11:46:02</t>
+          <t>2026/09/08 11:56:31</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-34.34755, -71.128765</t>
+          <t>-32.8826566, -70.6108616</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-34.34755, -71.12877</t>
+          <t>-32.88266, -70.61086</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>00:36:13</t>
+          <t>02:00:20</t>
         </is>
       </c>
       <c r="L42" t="n">
         <v>0.33</v>
       </c>
       <c r="M42" t="n">
+        <v>11</v>
+      </c>
+      <c r="N42" t="n">
         <v>9</v>
-      </c>
-      <c r="N42" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2846,53 +2846,53 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026/09/07 11:21:55</t>
+          <t>2026/09/08 09:58:12</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-33.4538883, -71.30263</t>
+          <t>-33.4562216, -71.3000783</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-33.45389, -71.30263</t>
+          <t>-33.45622, -71.30008</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026/09/07 11:35:15</t>
+          <t>2026/09/08 11:57:52</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-33.4540383, -71.3038016</t>
+          <t>-33.5027033, -71.2574733</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-33.45404, -71.30380</t>
+          <t>-33.50270, -71.25747</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>00:13:20</t>
+          <t>01:59:40</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0.12</v>
+        <v>6.92</v>
       </c>
       <c r="M43" t="n">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="N43" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -2905,47 +2905,47 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026/09/07 11:36:10</t>
+          <t>2026/09/08 10:21:07</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-33.453995, -71.3037966</t>
+          <t>-34.346532, -71.126181</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-33.45399, -71.30380</t>
+          <t>-34.34653, -71.12618</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026/09/07 14:58:43</t>
+          <t>2026/09/08 10:51:28</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-33.0483833, -71.6110866</t>
+          <t>-34.346507, -71.125244</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-33.04838, -71.61109</t>
+          <t>-34.34651, -71.12524</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>03:22:33</t>
+          <t>00:30:21</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>66.77</v>
+        <v>0.33</v>
       </c>
       <c r="M44" t="n">
-        <v>137</v>
+        <v>5</v>
       </c>
       <c r="N44" t="n">
-        <v>62</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2964,57 +2964,57 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026/09/07 11:47:17</t>
+          <t>2026/09/08 10:26:23</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-34.3467966, -71.1287383</t>
+          <t>-33.3599516, -70.8068483</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-34.34680, -71.12874</t>
+          <t>-33.35995, -70.80685</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026/09/07 12:05:44</t>
+          <t>2026/09/08 18:25:56</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-34.3554716, -71.1014416</t>
+          <t>-32.7888, -70.8305216</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-34.35547, -71.10144</t>
+          <t>-32.78880, -70.83052</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>00:18:27</t>
+          <t>07:59:33</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.95</v>
+        <v>103.1</v>
       </c>
       <c r="M45" t="n">
-        <v>53</v>
+        <v>139</v>
       </c>
       <c r="N45" t="n">
-        <v>21</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3023,57 +3023,57 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026/09/07 12:00:06</t>
+          <t>2026/09/08 10:51:48</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-33.5063033, -71.251795</t>
+          <t>-34.346526, -71.125237</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-33.50630, -71.25180</t>
+          <t>-34.34653, -71.12524</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026/09/07 13:06:05</t>
+          <t>2026/09/08 12:51:39</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-33.4558666, -71.3000266</t>
+          <t>-34.347589, -71.127686</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-33.45587, -71.30003</t>
+          <t>-34.34759, -71.12769</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>01:05:59</t>
+          <t>01:59:51</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>7.54</v>
+        <v>0.32</v>
       </c>
       <c r="M46" t="n">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="N46" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3082,116 +3082,116 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026/09/07 12:06:16</t>
+          <t>2026/09/08 10:52:32</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-34.3554033, -71.0988566</t>
+          <t>-33.3664599, -70.6962766</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-34.35540, -71.09886</t>
+          <t>-33.36646, -70.69628</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026/09/07 13:15:03</t>
+          <t>2026/09/08 15:23:35</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-34.3476, -71.1287766</t>
+          <t>-33.3665383, -70.6962</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-34.34760, -71.12878</t>
+          <t>-33.36654, -70.69620</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>01:08:47</t>
+          <t>04:31:03</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.43</v>
+        <v>0.05</v>
       </c>
       <c r="M47" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="N47" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026/09/07 12:10:21</t>
+          <t>2026/09/08 11:12:57</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-32.8791683, -70.6087816</t>
+          <t>-34.579665, -70.961414</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-32.87917, -70.60878</t>
+          <t>-34.57966, -70.96141</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026/09/07 20:24:57</t>
+          <t>2026/09/08 12:50:13</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-32.879225, -70.60886</t>
+          <t>-34.579642, -70.961429</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-32.87922, -70.60886</t>
+          <t>-34.57964, -70.96143</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>08:14:36</t>
+          <t>01:37:16</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>15.23</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3200,53 +3200,53 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026/09/07 13:06:22</t>
+          <t>2026/09/08 11:20:53</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-33.456225, -71.3000966</t>
+          <t>-34.0115399, -70.7039349</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-33.45623, -71.30010</t>
+          <t>-34.01154, -70.70393</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026/09/07 19:00:44</t>
+          <t>2026/09/08 13:00:07</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-32.7431866, -70.7330566</t>
+          <t>-34.8607133, -71.1691466</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>-32.74319, -70.73306</t>
+          <t>-34.86071, -71.16915</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>05:54:22</t>
+          <t>01:39:14</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>150.55</v>
+        <v>109.93</v>
       </c>
       <c r="M49" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N49" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -3259,57 +3259,57 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026/09/07 13:10:10</t>
+          <t>2026/09/08 11:57:29</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-33.477215, -70.6979716</t>
+          <t>-32.8837916, -70.6108649</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-33.47722, -70.69797</t>
+          <t>-32.88379, -70.61086</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026/09/07 13:20:37</t>
+          <t>2026/09/08 13:19:35</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-33.47627, -70.6983666</t>
+          <t>-32.8831099, -70.6124</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>-33.47627, -70.69837</t>
+          <t>-32.88311, -70.61240</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>00:10:27</t>
+          <t>01:22:06</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0.19</v>
+        <v>0.59</v>
       </c>
       <c r="M50" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="N50" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3318,57 +3318,57 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026/09/07 13:16:18</t>
+          <t>2026/09/08 11:59:07</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-34.3467849, -71.1287533</t>
+          <t>-33.5062633, -71.2518716</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-34.34678, -71.12875</t>
+          <t>-33.50626, -71.25187</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026/09/07 13:35:28</t>
+          <t>2026/09/08 12:54:30</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>-34.3457483, -71.1278599</t>
+          <t>-33.4550833, -71.2989233</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>-34.34575, -71.12786</t>
+          <t>-33.45508, -71.29892</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>00:19:10</t>
+          <t>00:55:23</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0.17</v>
+        <v>7.42</v>
       </c>
       <c r="M51" t="n">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="N51" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3377,57 +3377,57 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026/09/07 13:20:53</t>
+          <t>2026/09/08 12:35:13</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-33.4762883, -70.6983966</t>
+          <t>-34.205318, -70.677524</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-33.47629, -70.69840</t>
+          <t>-34.20532, -70.67752</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026/09/07 14:51:18</t>
+          <t>2026/09/08 12:42:34</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-33.5389833, -70.6432516</t>
+          <t>-34.205285, -70.680347</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>-33.53898, -70.64325</t>
+          <t>-34.20529, -70.68035</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>01:30:25</t>
+          <t>00:07:21</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>14.32</v>
+        <v>0.37</v>
       </c>
       <c r="M52" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3436,116 +3436,116 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026/09/07 13:35:47</t>
+          <t>2026/09/08 12:43:31</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-34.3463166, -71.127895</t>
+          <t>-34.205285, -70.680347</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-34.34632, -71.12789</t>
+          <t>-34.20529, -70.68035</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026/09/07 13:44:48</t>
+          <t>2026/09/09 07:40:56</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-34.3456866, -71.125985</t>
+          <t>-32.836158, -70.951069</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>-34.34569, -71.12599</t>
+          <t>-32.83616, -70.95107</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>00:09:01</t>
+          <t>18:57:25</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0.33</v>
+        <v>160.99</v>
       </c>
       <c r="M53" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N53" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026/09/07 13:44:01</t>
+          <t>2026/09/08 12:50:16</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-33.368745, -70.698099</t>
+          <t>-34.579664, -70.961403</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-33.36874, -70.69810</t>
+          <t>-34.57966, -70.96140</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026/09/07 15:18:59</t>
+          <t>2026/09/12 01:36:53</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>-33.367338, -70.695994</t>
+          <t>-34.579636, -70.961312</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>-33.36734, -70.69599</t>
+          <t>-34.57964, -70.96131</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>01:34:58</t>
+          <t>84:46:37</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3554,57 +3554,57 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026/09/07 13:45:02</t>
+          <t>2026/09/08 12:52:39</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-34.3459883, -71.1257183</t>
+          <t>-34.347672, -71.127696</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-34.34599, -71.12572</t>
+          <t>-34.34767, -71.12770</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026/09/07 14:13:02</t>
+          <t>2026/09/08 13:02:50</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-34.3476749, -71.1277766</t>
+          <t>-34.348743, -71.127672</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>-34.34767, -71.12778</t>
+          <t>-34.34874, -71.12767</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>00:28:00</t>
+          <t>00:10:11</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0.28</v>
+        <v>0.12</v>
       </c>
       <c r="M55" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N55" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3613,165 +3613,165 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026/09/07 13:46:53</t>
+          <t>2026/09/08 12:55:45</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-34.34603, -71.12569</t>
+          <t>-33.4551683, -71.2991466</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-34.34603, -71.12569</t>
+          <t>-33.45517, -71.29915</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026/09/07 14:07:25</t>
+          <t>2026/09/08 15:57:21</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>-34.346422, -71.125933</t>
+          <t>-33.3599533, -70.8070883</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>-34.34642, -71.12593</t>
+          <t>-33.35995, -70.80709</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>00:20:32</t>
+          <t>03:01:36</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0.17</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="M56" t="n">
-        <v>4</v>
+        <v>123</v>
       </c>
       <c r="N56" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026/09/07 14:08:20</t>
+          <t>2026/09/08 13:00:33</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-34.346349, -71.125925</t>
+          <t>-34.860545, -71.1700066</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-34.34635, -71.12592</t>
+          <t>-34.86055, -71.17001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026/09/07 14:18:02</t>
+          <t>2026/09/08 14:59:28</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>-34.34672, -71.125939</t>
+          <t>-34.8772116, -71.126205</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-34.34672, -71.12594</t>
+          <t>-34.87721, -71.12620</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>00:09:42</t>
+          <t>01:58:55</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0.09</v>
+        <v>11.68</v>
       </c>
       <c r="M57" t="n">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="N57" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026/09/07 14:14:17</t>
+          <t>2026/09/08 13:03:39</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-34.3485233, -71.127835</t>
+          <t>-34.348853, -71.127667</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-34.34852, -71.12784</t>
+          <t>-34.34885, -71.12767</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026/09/07 14:42:19</t>
+          <t>2026/09/08 13:11:23</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>-34.351345, -71.12937</t>
+          <t>-34.348297, -71.127681</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>-34.35135, -71.12937</t>
+          <t>-34.34830, -71.12768</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>00:28:02</t>
+          <t>00:07:44</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0.83</v>
+        <v>0.06</v>
       </c>
       <c r="M58" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="N58" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3781,66 +3781,66 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026/09/07 14:18:20</t>
+          <t>2026/09/08 13:11:35</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-34.346794, -71.125936</t>
+          <t>-34.348338, -71.127675</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-34.34679, -71.12594</t>
+          <t>-34.34834, -71.12767</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026/09/07 14:24:20</t>
+          <t>2026/09/08 13:31:02</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>-34.34633, -71.125927</t>
+          <t>-34.348022, -71.127792</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>-34.34633, -71.12593</t>
+          <t>-34.34802, -71.12779</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>00:06:00</t>
+          <t>00:19:27</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0.1</v>
+        <v>0.24</v>
       </c>
       <c r="M59" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -3849,103 +3849,103 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026/09/07 14:24:28</t>
+          <t>2026/09/08 13:19:39</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>-34.042722, -70.681703</t>
+          <t>-32.8830683, -70.6124149</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-34.04272, -70.68170</t>
+          <t>-32.88307, -70.61241</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026/09/08 13:25:22</t>
+          <t>2026/09/08 13:33:06</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>-34.041819, -70.681668</t>
+          <t>-32.8791883, -70.6088416</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>-34.04182, -70.68167</t>
+          <t>-32.87919, -70.60884</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>23:00:54</t>
+          <t>00:13:27</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="M60" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="N60" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026/09/07 14:24:44</t>
+          <t>2026/09/08 13:25:32</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-34.346277, -71.125924</t>
+          <t>-34.041832, -70.681694</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-34.34628, -71.12592</t>
+          <t>-34.04183, -70.68169</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026/09/07 14:33:43</t>
+          <t>2026/09/08 15:14:07</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>-34.346249, -71.125961</t>
+          <t>-34.042664, -70.681724</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>-34.34625, -71.12596</t>
+          <t>-34.04266, -70.68172</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>00:08:59</t>
+          <t>01:48:35</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="M61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N61" t="n">
         <v>3</v>
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3967,44 +3967,44 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026/09/07 14:34:18</t>
+          <t>2026/09/08 13:31:35</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>-34.346318, -71.126003</t>
+          <t>-34.348097, -71.127772</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-34.34632, -71.12600</t>
+          <t>-34.34810, -71.12777</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026/09/07 14:54:53</t>
+          <t>2026/09/08 13:46:25</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>-34.346995, -71.126064</t>
+          <t>-34.346322, -71.1256</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>-34.34699, -71.12606</t>
+          <t>-34.34632, -71.12560</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>00:20:35</t>
+          <t>00:14:50</t>
         </is>
       </c>
       <c r="L62" t="n">
         <v>0.35</v>
       </c>
       <c r="M62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N62" t="n">
         <v>3</v>
@@ -4013,11 +4013,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4026,106 +4026,106 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026/09/07 14:43:34</t>
+          <t>2026/09/08 13:33:12</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-34.3506066, -71.12932</t>
+          <t>-32.8791916, -70.6087949</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-34.35061, -71.12932</t>
+          <t>-32.87919, -70.60879</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026/09/07 14:55:11</t>
+          <t>2026/09/08 16:33:23</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>-34.3466316, -71.1265866</t>
+          <t>-32.8525799, -70.605565</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>-34.34663, -71.12659</t>
+          <t>-32.85258, -70.60556</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>00:11:37</t>
+          <t>03:00:11</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0.5600000000000001</v>
+        <v>4.13</v>
       </c>
       <c r="M63" t="n">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="N63" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026/09/07 14:52:14</t>
+          <t>2026/09/08 13:47:25</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-33.5384016, -70.6430566</t>
+          <t>-34.346558, -71.125262</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-33.53840, -70.64306</t>
+          <t>-34.34656, -71.12526</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026/09/07 15:20:19</t>
+          <t>2026/09/08 13:55:43</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>-33.4762516, -70.69833</t>
+          <t>-34.345942, -71.125755</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>-33.47625, -70.69833</t>
+          <t>-34.34594, -71.12575</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>00:28:05</t>
+          <t>00:08:18</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>13.35</v>
+        <v>0.08</v>
       </c>
       <c r="M64" t="n">
-        <v>106</v>
+        <v>4</v>
       </c>
       <c r="N64" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -4135,66 +4135,66 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026/09/07 14:55:18</t>
+          <t>2026/09/08 13:56:22</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-34.346855, -71.126061</t>
+          <t>-34.345962, -71.125764</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-34.34685, -71.12606</t>
+          <t>-34.34596, -71.12576</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026/09/07 15:12:17</t>
+          <t>2026/09/13 01:03:52</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>-34.34598, -71.125749</t>
+          <t>-34.345955, -71.125806</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>-34.34598, -71.12575</t>
+          <t>-34.34595, -71.12581</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>00:16:59</t>
+          <t>107:07:30</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0.23</v>
+        <v>0.02</v>
       </c>
       <c r="M65" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4203,57 +4203,57 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026/09/07 14:56:26</t>
+          <t>2026/09/08 15:00:43</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>-34.3462733, -71.126005</t>
+          <t>-34.8768566, -71.1267133</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-34.34627, -71.12601</t>
+          <t>-34.87686, -71.12671</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026/09/07 15:05:05</t>
+          <t>2026/09/08 15:10:54</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>-34.3461549, -71.1255633</t>
+          <t>-34.8750616, -71.12836</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>-34.34615, -71.12556</t>
+          <t>-34.87506, -71.12836</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>00:08:39</t>
+          <t>00:10:11</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0.04</v>
+        <v>0.26</v>
       </c>
       <c r="M66" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="N66" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4262,116 +4262,116 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026/09/07 14:59:58</t>
+          <t>2026/09/08 15:11:06</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>-33.047595, -71.610995</t>
+          <t>-34.8750416, -71.128585</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-33.04760, -71.61100</t>
+          <t>-34.87504, -71.12859</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026/09/07 16:34:50</t>
+          <t>2026/09/08 17:27:22</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>-33.0873483, -71.3622616</t>
+          <t>-33.47627, -70.6983683</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>-33.08735, -71.36226</t>
+          <t>-33.47627, -70.69837</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>01:34:52</t>
+          <t>02:16:16</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>36.35</v>
+        <v>176.45</v>
       </c>
       <c r="M67" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="N67" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026/09/07 15:06:20</t>
+          <t>2026/09/08 15:15:01</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>-34.3464633, -71.12531</t>
+          <t>-34.042664, -70.68175</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-34.34646, -71.12531</t>
+          <t>-34.04266, -70.68175</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026/09/07 18:30:43</t>
+          <t>2026/09/08 15:26:28</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>-32.8795316, -70.6081933</t>
+          <t>-34.042648, -70.681753</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>-32.87953, -70.60819</t>
+          <t>-34.04265, -70.68175</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>03:24:23</t>
+          <t>00:11:27</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>217.83</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>136</v>
+        <v>3</v>
       </c>
       <c r="N68" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4380,116 +4380,116 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026/09/07 15:12:52</t>
+          <t>2026/09/08 15:24:24</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-34.346006, -71.125762</t>
+          <t>-33.3666133, -70.6958266</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-34.34601, -71.12576</t>
+          <t>-33.36661, -70.69583</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026/09/08 08:53:32</t>
+          <t>2026/09/08 19:07:48</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>-34.346557, -71.125393</t>
+          <t>-33.4363016, -70.62962</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>-34.34656, -71.12539</t>
+          <t>-33.43630, -70.62962</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>17:40:40</t>
+          <t>03:43:24</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0.11</v>
+        <v>14.34</v>
       </c>
       <c r="M69" t="n">
-        <v>4</v>
+        <v>115</v>
       </c>
       <c r="N69" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026/09/07 15:18:03</t>
+          <t>2026/09/08 15:26:45</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>-34.579643, -70.961437</t>
+          <t>-34.042645, -70.681745</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-34.57964, -70.96144</t>
+          <t>-34.04265, -70.68175</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026/09/08 07:10:43</t>
+          <t>2026/09/14 22:57:17</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>-34.579698, -70.961429</t>
+          <t>-34.042752, -70.681779</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>-34.57970, -70.96143</t>
+          <t>-34.04275, -70.68178</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>15:52:40</t>
+          <t>151:30:32</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0.18</v>
+        <v>0.04</v>
       </c>
       <c r="M70" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026/09/07 15:21:34</t>
+          <t>2026/09/08 15:57:39</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>-33.476185, -70.6984216</t>
+          <t>-33.3599233, -70.8071266</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-33.47619, -70.69842</t>
+          <t>-33.35992, -70.80713</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026/09/08 07:45:19</t>
+          <t>2026/09/08 16:19:04</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>-33.4762716, -70.698355</t>
+          <t>-33.359955, -70.80699</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>-33.47627, -70.69836</t>
+          <t>-33.35995, -70.80699</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>16:23:45</t>
+          <t>00:21:25</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>11.17</v>
+        <v>0.7</v>
       </c>
       <c r="M71" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="N71" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4557,57 +4557,57 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026/09/07 15:28:53</t>
+          <t>2026/09/08 16:19:10</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>-33.366952, -70.685523</t>
+          <t>-33.3599583, -70.8070683</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-33.36695, -70.68552</t>
+          <t>-33.35996, -70.80707</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026/09/07 16:36:26</t>
+          <t>2026/09/08 18:49:57</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>-33.367301, -70.696048</t>
+          <t>-32.7432316, -70.7328933</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>-33.36730, -70.69605</t>
+          <t>-32.74323, -70.73289</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>01:07:33</t>
+          <t>02:30:47</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.6</v>
+        <v>125.82</v>
       </c>
       <c r="M72" t="n">
-        <v>8</v>
+        <v>138</v>
       </c>
       <c r="N72" t="n">
-        <v>8</v>
+        <v>53</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -4616,57 +4616,57 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026/09/07 16:35:07</t>
+          <t>2026/09/08 16:34:38</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>-33.0873233, -71.36235</t>
+          <t>-32.85218, -70.6075633</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-33.08732, -71.36235</t>
+          <t>-32.85218, -70.60756</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026/09/07 20:51:29</t>
+          <t>2026/09/08 16:53:14</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>-33.0872983, -71.3622316</t>
+          <t>-32.8324916, -70.6003816</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>-33.08730, -71.36223</t>
+          <t>-32.83249, -70.60038</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>04:16:22</t>
+          <t>00:18:36</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0.01</v>
+        <v>2.76</v>
       </c>
       <c r="M73" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="N73" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -4675,57 +4675,57 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026/09/07 17:10:47</t>
+          <t>2026/09/08 16:54:07</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>-33.399565, -70.6147666</t>
+          <t>-32.8323983, -70.6006216</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-33.39957, -70.61477</t>
+          <t>-32.83240, -70.60062</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026/09/07 17:42:07</t>
+          <t>2026/09/08 17:30:12</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>-33.4352133, -70.6289483</t>
+          <t>-32.87977, -70.6062683</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>-33.43521, -70.62895</t>
+          <t>-32.87977, -70.60627</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>00:31:20</t>
+          <t>00:36:05</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>4.71</v>
+        <v>9.42</v>
       </c>
       <c r="M74" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="N74" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -4734,57 +4734,57 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026/09/07 17:27:33</t>
+          <t>2026/09/08 17:27:31</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>-32.838365, -70.955536</t>
+          <t>-33.476315, -70.6984066</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95554</t>
+          <t>-33.47631, -70.69841</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026/09/08 12:34:32</t>
+          <t>2026/09/08 18:27:09</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>-34.205318, -70.677524</t>
+          <t>-33.3623583, -70.6701216</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>-34.20532, -70.67752</t>
+          <t>-33.36236, -70.67012</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>19:06:59</t>
+          <t>00:59:38</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>205.09</v>
+        <v>20.47</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -4793,57 +4793,57 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026/09/07 17:43:22</t>
+          <t>2026/09/08 17:30:41</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-33.4352766, -70.6291383</t>
+          <t>-32.87943, -70.6089433</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-33.43528, -70.62914</t>
+          <t>-32.87943, -70.60894</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026/09/07 17:52:36</t>
+          <t>2026/09/08 18:04:51</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>-33.4362933, -70.6296166</t>
+          <t>-32.820255, -70.6146</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>-33.43629, -70.62962</t>
+          <t>-32.82026, -70.61460</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>00:09:14</t>
+          <t>00:34:10</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0.18</v>
+        <v>11.94</v>
       </c>
       <c r="M76" t="n">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="N76" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -4852,57 +4852,57 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026/09/07 17:53:02</t>
+          <t>2026/09/08 17:43:07</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>-33.4367683, -70.6294966</t>
+          <t>-33.0873116, -71.3623416</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-33.43677, -70.62950</t>
+          <t>-33.08731, -71.36234</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026/09/08 10:52:21</t>
+          <t>2026/09/08 19:59:51</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>-33.3665366, -70.6962166</t>
+          <t>-33.0872866, -71.362245</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>-33.36654, -70.69622</t>
+          <t>-33.08729, -71.36225</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>16:59:19</t>
+          <t>02:16:44</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>20.07</v>
+        <v>0.01</v>
       </c>
       <c r="M77" t="n">
-        <v>115</v>
+        <v>7</v>
       </c>
       <c r="N77" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -4911,57 +4911,57 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026/09/07 18:31:58</t>
+          <t>2026/09/08 18:06:06</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>-32.8794533, -70.6089166</t>
+          <t>-32.8205016, -70.6143333</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-32.87945, -70.60892</t>
+          <t>-32.82050, -70.61433</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026/09/07 19:36:36</t>
+          <t>2026/09/08 18:42:10</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>-32.7977183, -70.88739</t>
+          <t>-32.7580149, -70.70204</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>-32.79772, -70.88739</t>
+          <t>-32.75801, -70.70204</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>01:04:38</t>
+          <t>00:36:04</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>47.17</v>
+        <v>12.65</v>
       </c>
       <c r="M78" t="n">
-        <v>138</v>
+        <v>61</v>
       </c>
       <c r="N78" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -4970,53 +4970,53 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026/09/07 19:01:08</t>
+          <t>2026/09/08 18:26:59</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>-32.7433483, -70.7326566</t>
+          <t>-32.7856766, -70.8315833</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-32.74335, -70.73266</t>
+          <t>-32.78568, -70.83158</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026/09/07 19:13:22</t>
+          <t>2026/09/08 18:44:27</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>-32.7431783, -70.7296383</t>
+          <t>-32.79774, -70.8874316</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>-32.74318, -70.72964</t>
+          <t>-32.79774, -70.88743</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>00:12:14</t>
+          <t>00:17:28</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0.36</v>
+        <v>7.43</v>
       </c>
       <c r="M79" t="n">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="N79" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -5029,57 +5029,57 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026/09/07 19:14:37</t>
+          <t>2026/09/08 18:27:43</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>-32.7432166, -70.729625</t>
+          <t>-33.3621483, -70.6701383</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-32.74322, -70.72962</t>
+          <t>-33.36215, -70.67014</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026/09/08 07:25:00</t>
+          <t>2026/09/08 19:03:48</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>-33.3599433, -70.8069966</t>
+          <t>-33.4762116, -70.6982083</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>-33.35994, -70.80700</t>
+          <t>-33.47621, -70.69821</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>12:10:23</t>
+          <t>00:36:05</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>90.84999999999999</v>
+        <v>18.07</v>
       </c>
       <c r="M80" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="N80" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5088,47 +5088,47 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026/09/07 19:37:51</t>
+          <t>2026/09/08 18:42:33</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>-32.7976133, -70.88705</t>
+          <t>-32.7582066, -70.7021599</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88705</t>
+          <t>-32.75821, -70.70216</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026/09/07 19:58:39</t>
+          <t>2026/09/08 19:19:25</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>-32.7976666, -70.887215</t>
+          <t>-32.8792133, -70.6090199</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>-32.79767, -70.88721</t>
+          <t>-32.87921, -70.60902</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>00:20:48</t>
+          <t>00:36:52</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>7.86</v>
+        <v>25.15</v>
       </c>
       <c r="M81" t="n">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="N81" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
     </row>
     <row r="82">
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5147,57 +5147,57 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026/09/07 19:59:00</t>
+          <t>2026/09/08 18:45:39</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>-32.79761, -70.8870333</t>
+          <t>-32.7976366, -70.8870966</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88703</t>
+          <t>-32.79764, -70.88710</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026/09/08 07:29:24</t>
+          <t>2026/09/09 09:59:33</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>-33.3599616, -70.806975</t>
+          <t>-32.7426583, -70.7861166</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>-33.35996, -70.80697</t>
+          <t>-32.74266, -70.78612</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>11:30:24</t>
+          <t>15:13:54</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>104.42</v>
+        <v>11.5</v>
       </c>
       <c r="M82" t="n">
-        <v>130</v>
+        <v>69</v>
       </c>
       <c r="N82" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5206,57 +5206,57 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026/09/07 20:25:08</t>
+          <t>2026/09/08 18:50:27</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>-32.8792116, -70.6087616</t>
+          <t>-32.7433533, -70.7327166</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-32.87921, -70.60876</t>
+          <t>-32.74335, -70.73272</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026/09/08 06:25:15</t>
+          <t>2026/09/08 19:08:01</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>-32.890915, -70.6760283</t>
+          <t>-32.7431883, -70.729675</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>-32.89091, -70.67603</t>
+          <t>-32.74319, -70.72968</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>10:00:07</t>
+          <t>00:17:34</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>8.27</v>
+        <v>0.36</v>
       </c>
       <c r="M83" t="n">
-        <v>129</v>
+        <v>13</v>
       </c>
       <c r="N83" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5265,53 +5265,53 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026/09/07 20:51:37</t>
+          <t>2026/09/08 19:05:03</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>-33.0872183, -71.36218</t>
+          <t>-33.4762333, -70.6984166</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-33.08722, -71.36218</t>
+          <t>-33.47623, -70.69842</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026/09/08 06:44:06</t>
+          <t>2026/09/09 07:44:57</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>-33.0872933, -71.362245</t>
+          <t>-33.4762833, -70.6983599</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>-33.08729, -71.36225</t>
+          <t>-33.47628, -70.69836</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>09:52:29</t>
+          <t>12:39:54</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>14.03</v>
+        <v>11.17</v>
       </c>
       <c r="M84" t="n">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="N84" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -5324,57 +5324,57 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026/09/08 09:56:11</t>
+          <t>2026/09/08 19:08:52</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>-32.885145, -70.6108033</t>
+          <t>-33.4365933, -70.62956</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-32.88515, -70.61080</t>
+          <t>-33.43659, -70.62956</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026/09/08 11:56:31</t>
+          <t>2026/09/09 08:59:52</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>-32.8826566, -70.6108616</t>
+          <t>-33.3672266, -70.6955733</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>-32.88266, -70.61086</t>
+          <t>-33.36723, -70.69557</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>02:00:20</t>
+          <t>13:51:00</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0.33</v>
+        <v>13.63</v>
       </c>
       <c r="M85" t="n">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="N85" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5383,57 +5383,57 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026/09/08 10:21:07</t>
+          <t>2026/09/08 19:09:16</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>-34.346532, -71.126181</t>
+          <t>-32.743165, -70.7297066</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-34.34653, -71.12618</t>
+          <t>-32.74316, -70.72971</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026/09/08 10:51:28</t>
+          <t>2026/09/09 07:18:24</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>-34.346507, -71.125244</t>
+          <t>-33.3599916, -70.8071333</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>-34.34651, -71.12524</t>
+          <t>-33.35999, -70.80713</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>00:30:21</t>
+          <t>12:09:08</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0.33</v>
+        <v>89.91</v>
       </c>
       <c r="M86" t="n">
-        <v>5</v>
+        <v>113</v>
       </c>
       <c r="N86" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5442,116 +5442,116 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026/09/08 10:51:48</t>
+          <t>2026/09/08 19:20:40</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>-34.346526, -71.125237</t>
+          <t>-32.8790916, -70.6094466</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-34.34653, -71.12524</t>
+          <t>-32.87909, -70.60945</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026/09/08 12:51:39</t>
+          <t>2026/09/08 19:31:12</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>-34.347589, -71.127686</t>
+          <t>-32.879155, -70.6093066</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>-34.34759, -71.12769</t>
+          <t>-32.87915, -70.60931</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>01:59:51</t>
+          <t>00:10:32</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0.32</v>
+        <v>0.01</v>
       </c>
       <c r="M87" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N87" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026/09/08 11:12:57</t>
+          <t>2026/09/08 19:31:50</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>-34.579665, -70.961414</t>
+          <t>-32.8792316, -70.6088183</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-34.57966, -70.96141</t>
+          <t>-32.87923, -70.60882</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026/09/08 12:50:13</t>
+          <t>2026/09/09 07:06:21</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>-34.579642, -70.961429</t>
+          <t>-32.879205, -70.60888</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>-34.57964, -70.96143</t>
+          <t>-32.87920, -70.60888</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>01:37:16</t>
+          <t>11:34:31</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>10.18</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5560,116 +5560,116 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026/09/08 11:57:29</t>
+          <t>2026/09/08 20:00:05</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>-32.8837916, -70.6108649</t>
+          <t>-33.0872083, -71.3621816</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-32.88379, -70.61086</t>
+          <t>-33.08721, -71.36218</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026/09/08 13:19:35</t>
+          <t>2026/09/09 09:55:26</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>-32.8831099, -70.6124</t>
+          <t>-34.2042699, -70.67912</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>-32.88311, -70.61240</t>
+          <t>-34.20427, -70.67912</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>01:22:06</t>
+          <t>13:55:21</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0.59</v>
+        <v>192.25</v>
       </c>
       <c r="M89" t="n">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="N89" t="n">
-        <v>10</v>
+        <v>74</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026/09/08 12:50:16</t>
+          <t>2026/09/09 15:22:22</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>-34.579664, -70.961403</t>
+          <t>-32.771205, -70.834705</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-34.57966, -70.96140</t>
+          <t>-32.77121, -70.83470</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026/09/12 01:36:53</t>
+          <t>2026/09/09 18:35:49</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>-34.579636, -70.961312</t>
+          <t>-32.7977016, -70.88739</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>-34.57964, -70.96131</t>
+          <t>-32.79770, -70.88739</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>84:46:37</t>
+          <t>03:13:27</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0.04</v>
+        <v>6</v>
       </c>
       <c r="M90" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="N90" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -5678,116 +5678,116 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026/09/08 12:52:39</t>
+          <t>2026/09/09 15:49:12</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>-34.347672, -71.127696</t>
+          <t>-34.2088533, -70.6784016</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-34.34767, -71.12770</t>
+          <t>-34.20885, -70.67840</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026/09/08 13:02:50</t>
+          <t>2026/09/09 16:25:24</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>-34.348743, -71.127672</t>
+          <t>-34.2041083, -70.6790099</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>-34.34874, -71.12767</t>
+          <t>-34.20411, -70.67901</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>00:10:11</t>
+          <t>00:36:12</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0.12</v>
+        <v>1.07</v>
       </c>
       <c r="M91" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="N91" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026/09/08 13:03:39</t>
+          <t>2026/09/09 16:25:31</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>-34.348853, -71.127667</t>
+          <t>-34.2041483, -70.679065</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-34.34885, -71.12767</t>
+          <t>-34.20415, -70.67906</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026/09/08 13:11:23</t>
+          <t>2026/09/09 16:38:53</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>-34.348297, -71.127681</t>
+          <t>-34.2058549, -70.6759933</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>-34.34830, -71.12768</t>
+          <t>-34.20585, -70.67599</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>00:07:44</t>
+          <t>00:13:22</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0.06</v>
+        <v>0.59</v>
       </c>
       <c r="M92" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="N92" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -5796,57 +5796,57 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026/09/08 13:19:39</t>
+          <t>2026/09/09 16:39:54</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>-32.8830683, -70.6124149</t>
+          <t>-34.2074116, -70.6760316</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-32.88307, -70.61241</t>
+          <t>-34.20741, -70.67603</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026/09/08 13:33:06</t>
+          <t>2026/09/09 17:16:48</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>-32.8791883, -70.6088416</t>
+          <t>-34.2045433, -70.6795616</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>-32.87919, -70.60884</t>
+          <t>-34.20454, -70.67956</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>00:13:27</t>
+          <t>00:36:54</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="M93" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="N93" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -5855,57 +5855,57 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026/09/08 13:25:32</t>
+          <t>2026/09/09 17:17:22</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>-34.041832, -70.681694</t>
+          <t>-34.2051833, -70.68031</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-34.04183, -70.68169</t>
+          <t>-34.20518, -70.68031</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026/09/08 15:14:07</t>
+          <t>2026/09/09 17:43:00</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>-34.042664, -70.681724</t>
+          <t>-34.1900883, -70.70946</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>-34.04266, -70.68172</t>
+          <t>-34.19009, -70.70946</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>01:48:35</t>
+          <t>00:25:38</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0.15</v>
+        <v>3.38</v>
       </c>
       <c r="M94" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="N94" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -5914,53 +5914,53 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026/09/08 13:33:12</t>
+          <t>2026/09/09 17:43:35</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>-32.8791916, -70.6087949</t>
+          <t>-34.19014, -70.7094049</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-32.87919, -70.60879</t>
+          <t>-34.19014, -70.70940</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026/09/08 16:33:23</t>
+          <t>2026/09/09 18:37:10</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>-32.8525799, -70.605565</t>
+          <t>-34.1790849, -70.70823</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>-32.85258, -70.60556</t>
+          <t>-34.17908, -70.70823</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>03:00:11</t>
+          <t>00:53:35</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>4.13</v>
+        <v>1.61</v>
       </c>
       <c r="M95" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="N95" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -5968,180 +5968,180 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026/09/08 13:47:25</t>
+          <t>2026/09/09 18:37:04</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>-34.346558, -71.125262</t>
+          <t>-32.79759, -70.8870866</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-34.34656, -71.12526</t>
+          <t>-32.79759, -70.88709</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026/09/08 13:55:43</t>
+          <t>2026/09/10 06:57:22</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>-34.345942, -71.125755</t>
+          <t>-34.0003899, -70.7020416</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>-34.34594, -71.12575</t>
+          <t>-34.00039, -70.70204</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>00:08:18</t>
+          <t>12:20:18</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0.08</v>
+        <v>169.77</v>
       </c>
       <c r="M96" t="n">
-        <v>4</v>
+        <v>127</v>
       </c>
       <c r="N96" t="n">
-        <v>4</v>
+        <v>74</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026/09/08 13:56:22</t>
+          <t>2026/09/09 18:38:25</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>-34.345962, -71.125764</t>
+          <t>-34.1796933, -70.7074966</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-34.34596, -71.12576</t>
+          <t>-34.17969, -70.70750</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026/09/13 01:03:52</t>
+          <t>2026/09/10 07:46:05</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>-34.345955, -71.125806</t>
+          <t>-34.2070316, -70.6771383</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>-34.34595, -71.12581</t>
+          <t>-34.20703, -70.67714</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>107:07:30</t>
+          <t>13:07:40</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0.02</v>
+        <v>5.68</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026/09/08 15:26:45</t>
+          <t>2026/09/09 19:04:41</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>-34.042645, -70.681745</t>
+          <t>-33.450825, -70.6666066</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-34.04265, -70.68175</t>
+          <t>-33.45083, -70.66661</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026/09/13 23:57:38</t>
+          <t>2026/09/09 19:33:12</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>-34.042553, -70.68171</t>
+          <t>-33.4762216, -70.6982983</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>-34.04255, -70.68171</t>
+          <t>-33.47622, -70.69830</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>128:30:53</t>
+          <t>00:28:31</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0.02</v>
+        <v>7.91</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6150,57 +6150,57 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026/09/08 16:34:38</t>
+          <t>2026/09/09 19:34:28</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>-32.85218, -70.6075633</t>
+          <t>-33.4761533, -70.6984083</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-32.85218, -70.60756</t>
+          <t>-33.47615, -70.69841</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026/09/08 16:53:14</t>
+          <t>2026/09/10 07:48:15</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>-32.8324916, -70.6003816</t>
+          <t>-33.47624, -70.69838</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>-32.83249, -70.60038</t>
+          <t>-33.47624, -70.69838</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>00:18:36</t>
+          <t>12:13:47</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.76</v>
+        <v>11.1</v>
       </c>
       <c r="M99" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="N99" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6209,53 +6209,53 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026/09/08 16:54:07</t>
+          <t>2026/09/09 21:27:13</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>-32.8323983, -70.6006216</t>
+          <t>-33.4366466, -70.6296616</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-32.83240, -70.60062</t>
+          <t>-33.43665, -70.62966</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026/09/08 17:30:12</t>
+          <t>2026/09/10 10:08:43</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>-32.87977, -70.6062683</t>
+          <t>-33.367265, -70.695655</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>-32.87977, -70.60627</t>
+          <t>-33.36727, -70.69566</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>00:36:05</t>
+          <t>12:41:30</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>9.42</v>
+        <v>13.52</v>
       </c>
       <c r="M100" t="n">
-        <v>47</v>
+        <v>127</v>
       </c>
       <c r="N100" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -6268,53 +6268,53 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026/09/08 17:30:41</t>
+          <t>2026/09/10 11:40:03</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>-32.87943, -70.6089433</t>
+          <t>-34.20491, -70.677375</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-32.87943, -70.60894</t>
+          <t>-34.20491, -70.67737</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026/09/08 18:04:51</t>
+          <t>2026/09/10 12:18:09</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>-32.820255, -70.6146</t>
+          <t>-34.1899899, -70.7092549</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>-32.82026, -70.61460</t>
+          <t>-34.18999, -70.70925</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>00:34:10</t>
+          <t>00:38:06</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>11.94</v>
+        <v>3.79</v>
       </c>
       <c r="M101" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="N101" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -6327,53 +6327,53 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026/09/08 18:06:06</t>
+          <t>2026/09/10 12:18:20</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>-32.8205016, -70.6143333</t>
+          <t>-34.1899766, -70.7092516</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-32.82050, -70.61433</t>
+          <t>-34.18998, -70.70925</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026/09/08 18:42:10</t>
+          <t>2026/09/10 13:24:06</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>-32.7580149, -70.70204</t>
+          <t>-34.2042616, -70.6787766</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>-32.75801, -70.70204</t>
+          <t>-34.20426, -70.67878</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>00:36:04</t>
+          <t>01:05:46</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>12.65</v>
+        <v>4.31</v>
       </c>
       <c r="M102" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="N102" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -6386,57 +6386,57 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026/09/08 18:42:33</t>
+          <t>2026/09/10 13:25:21</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>-32.7582066, -70.7021599</t>
+          <t>-34.204295, -70.6790766</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-32.75821, -70.70216</t>
+          <t>-34.20430, -70.67908</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026/09/08 19:19:25</t>
+          <t>2026/09/10 13:33:17</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>-32.8792133, -70.6090199</t>
+          <t>-34.2053283, -70.6768866</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>-32.87921, -70.60902</t>
+          <t>-34.20533, -70.67689</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>00:36:52</t>
+          <t>00:07:56</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>25.15</v>
+        <v>0.26</v>
       </c>
       <c r="M103" t="n">
-        <v>105</v>
+        <v>9</v>
       </c>
       <c r="N103" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6445,57 +6445,57 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026/09/08 18:50:27</t>
+          <t>2026/09/10 13:33:28</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>-32.7433533, -70.7327166</t>
+          <t>-34.2053633, -70.6768999</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-32.74335, -70.73272</t>
+          <t>-34.20536, -70.67690</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026/09/08 19:08:01</t>
+          <t>2026/09/10 14:32:58</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>-32.7431883, -70.729675</t>
+          <t>-34.2049866, -70.6772683</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>-32.74319, -70.72968</t>
+          <t>-34.20499, -70.67727</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>00:17:34</t>
+          <t>00:59:30</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0.36</v>
+        <v>0.05</v>
       </c>
       <c r="M104" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="N104" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6504,57 +6504,57 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026/09/08 19:05:03</t>
+          <t>2026/09/10 14:33:12</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>-33.4762333, -70.6984166</t>
+          <t>-34.204925, -70.677335</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-33.47623, -70.69842</t>
+          <t>-34.20493, -70.67733</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026/09/09 07:44:57</t>
+          <t>2026/09/10 15:03:01</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>-33.4762833, -70.6983599</t>
+          <t>-34.2041233, -70.6775366</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>-33.47628, -70.69836</t>
+          <t>-34.20412, -70.67754</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>12:39:54</t>
+          <t>00:29:49</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>11.17</v>
+        <v>0.1</v>
       </c>
       <c r="M105" t="n">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="N105" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6563,57 +6563,57 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026/09/08 19:09:16</t>
+          <t>2026/09/10 15:04:16</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>-32.743165, -70.7297066</t>
+          <t>-34.2045366, -70.6775933</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-32.74316, -70.72971</t>
+          <t>-34.20454, -70.67759</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026/09/09 07:18:24</t>
+          <t>2026/09/10 15:11:00</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>-33.3599916, -70.8071333</t>
+          <t>-34.204355, -70.67778</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80713</t>
+          <t>-34.20435, -70.67778</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>12:09:08</t>
+          <t>00:06:44</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>89.91</v>
+        <v>0.06</v>
       </c>
       <c r="M106" t="n">
-        <v>113</v>
+        <v>7</v>
       </c>
       <c r="N106" t="n">
-        <v>57</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6622,57 +6622,57 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026/09/08 19:20:40</t>
+          <t>2026/09/10 15:11:27</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>-32.8790916, -70.6094466</t>
+          <t>-34.2044533, -70.6778866</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-32.87909, -70.60945</t>
+          <t>-34.20445, -70.67789</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026/09/08 19:31:12</t>
+          <t>2026/09/10 16:17:28</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>-32.879155, -70.6093066</t>
+          <t>-34.2043233, -70.678935</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>-32.87915, -70.60931</t>
+          <t>-34.20432, -70.67893</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>00:10:32</t>
+          <t>01:06:01</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="M107" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N107" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -6681,47 +6681,47 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026/09/08 19:31:50</t>
+          <t>2026/09/10 16:18:00</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>-32.8792316, -70.6088183</t>
+          <t>-34.20419, -70.678245</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-32.87923, -70.60882</t>
+          <t>-34.20419, -70.67825</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026/09/09 07:06:21</t>
+          <t>2026/09/10 16:57:51</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>-32.879205, -70.60888</t>
+          <t>-34.2042549, -70.6782116</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>-32.87920, -70.60888</t>
+          <t>-34.20425, -70.67821</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>11:34:31</t>
+          <t>00:39:51</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>10.18</v>
+        <v>0.35</v>
       </c>
       <c r="M108" t="n">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="N108" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109">
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -6740,57 +6740,57 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026/09/09 16:25:31</t>
+          <t>2026/09/10 16:42:50</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>-34.2041483, -70.679065</t>
+          <t>-34.20484, -70.677505</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-34.20415, -70.67906</t>
+          <t>-34.20484, -70.67750</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026/09/09 16:38:53</t>
+          <t>2026/09/10 17:35:40</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>-34.2058549, -70.6759933</t>
+          <t>-34.1796983, -70.7075316</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>-34.20585, -70.67599</t>
+          <t>-34.17970, -70.70753</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>00:13:22</t>
+          <t>00:52:50</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0.59</v>
+        <v>5.39</v>
       </c>
       <c r="M109" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="N109" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -6799,47 +6799,47 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026/09/09 16:39:54</t>
+          <t>2026/09/10 16:59:06</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>-34.2074116, -70.6760316</t>
+          <t>-34.20424, -70.67818</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-34.20741, -70.67603</t>
+          <t>-34.20424, -70.67818</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026/09/09 17:16:48</t>
+          <t>2026/09/10 19:52:20</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>-34.2045433, -70.6795616</t>
+          <t>-32.797765, -70.8873916</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>-34.20454, -70.67956</t>
+          <t>-32.79776, -70.88739</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>00:36:54</t>
+          <t>02:53:14</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.1</v>
+        <v>196.18</v>
       </c>
       <c r="M110" t="n">
-        <v>16</v>
+        <v>133</v>
       </c>
       <c r="N110" t="n">
-        <v>9</v>
+        <v>71</v>
       </c>
     </row>
     <row r="111">
@@ -6849,7 +6849,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -6858,57 +6858,57 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026/09/09 17:17:22</t>
+          <t>2026/09/10 17:36:55</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>-34.2051833, -70.68031</t>
+          <t>-34.1797233, -70.7073566</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-34.20518, -70.68031</t>
+          <t>-34.17972, -70.70736</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026/09/09 17:43:00</t>
+          <t>2026/09/11 07:34:52</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>-34.1900883, -70.70946</t>
+          <t>-34.18998, -70.7092433</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>-34.19009, -70.70946</t>
+          <t>-34.18998, -70.70924</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>00:25:38</t>
+          <t>13:57:57</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>3.38</v>
+        <v>2.17</v>
       </c>
       <c r="M111" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="N111" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -6917,57 +6917,57 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026/09/09 17:43:35</t>
+          <t>2026/09/10 19:53:35</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>-34.19014, -70.7094049</t>
+          <t>-32.7976283, -70.8870166</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-34.19014, -70.70940</t>
+          <t>-32.79763, -70.88702</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026/09/09 18:37:10</t>
+          <t>2026/09/11 06:18:20</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>-34.1790849, -70.70823</t>
+          <t>-33.5398733, -70.7089816</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>-34.17908, -70.70823</t>
+          <t>-33.53987, -70.70898</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>00:53:35</t>
+          <t>10:24:45</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.61</v>
+        <v>117.06</v>
       </c>
       <c r="M112" t="n">
-        <v>30</v>
+        <v>144</v>
       </c>
       <c r="N112" t="n">
-        <v>15</v>
+        <v>71</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -6976,57 +6976,57 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026/09/09 18:38:25</t>
+          <t>2026/09/11 03:46:43</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>-34.1796933, -70.7074966</t>
+          <t>-34.205533, -70.677237</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-34.17969, -70.70750</t>
+          <t>-34.20553, -70.67724</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026/09/10 07:46:05</t>
+          <t>2026/09/14 12:35:00</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>-34.2070316, -70.6771383</t>
+          <t>-34.204249, -70.679129</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>-34.20703, -70.67714</t>
+          <t>-34.20425, -70.67913</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>13:07:40</t>
+          <t>80:48:17</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>5.68</v>
+        <v>0.35</v>
       </c>
       <c r="M113" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="N113" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7035,57 +7035,57 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026/09/09 18:48:26</t>
+          <t>2026/09/11 11:08:47</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>-33.4511266, -70.666315</t>
+          <t>-33.3649116, -70.4965666</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-33.45113, -70.66631</t>
+          <t>-33.36491, -70.49657</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026/09/09 19:03:26</t>
+          <t>2026/09/11 11:23:05</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>-33.4507766, -70.6663983</t>
+          <t>-33.3588366, -70.4849283</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>-33.45078, -70.66640</t>
+          <t>-33.35884, -70.48493</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>00:15:00</t>
+          <t>00:14:18</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0.05</v>
+        <v>1.52</v>
       </c>
       <c r="M114" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="N114" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7094,57 +7094,57 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026/09/09 19:04:41</t>
+          <t>2026/09/11 11:24:20</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>-33.450825, -70.6666066</t>
+          <t>-33.3585916, -70.48524</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-33.45083, -70.66661</t>
+          <t>-33.35859, -70.48524</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026/09/09 19:33:12</t>
+          <t>2026/09/11 18:19:57</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>-33.4762216, -70.6982983</t>
+          <t>-33.5140783, -70.637485</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>-33.47622, -70.69830</t>
+          <t>-33.51408, -70.63748</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>00:28:31</t>
+          <t>06:55:37</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>7.91</v>
+        <v>33.06</v>
       </c>
       <c r="M115" t="n">
-        <v>50</v>
+        <v>119</v>
       </c>
       <c r="N115" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7153,57 +7153,57 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026/09/09 19:34:28</t>
+          <t>2026/09/11 16:46:08</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>-33.4761533, -70.6984083</t>
+          <t>-33.4364066, -70.629565</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-33.47615, -70.69841</t>
+          <t>-33.43641, -70.62956</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026/09/10 07:48:15</t>
+          <t>2026/09/13 05:17:42</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>-33.47624, -70.69838</t>
+          <t>-33.3689316, -70.5006183</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>-33.47624, -70.69838</t>
+          <t>-33.36893, -70.50062</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>12:13:47</t>
+          <t>36:31:34</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>11.1</v>
+        <v>16.8</v>
       </c>
       <c r="M116" t="n">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="N116" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7212,106 +7212,106 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026/09/10 16:42:50</t>
+          <t>2026/09/11 18:21:12</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>-34.20484, -70.677505</t>
+          <t>-33.5138849, -70.638245</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-34.20484, -70.67750</t>
+          <t>-33.51388, -70.63824</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026/09/10 17:35:40</t>
+          <t>2026/09/12 08:06:40</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>-34.1796983, -70.7075316</t>
+          <t>-33.4510416, -70.6724666</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>-34.17970, -70.70753</t>
+          <t>-33.45104, -70.67247</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>00:52:50</t>
+          <t>13:45:28</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>5.39</v>
+        <v>10.84</v>
       </c>
       <c r="M117" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="N117" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026/09/10 17:36:55</t>
+          <t>2026/09/12 02:35:36</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>-34.1797233, -70.7073566</t>
+          <t>-34.579636, -70.961312</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>-34.17972, -70.70736</t>
+          <t>-34.57964, -70.96131</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026/09/11 07:34:52</t>
+          <t>2026/09/14 22:34:21</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>-34.18998, -70.7092433</t>
+          <t>-34.579612, -70.961482</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>-34.18998, -70.70924</t>
+          <t>-34.57961, -70.96148</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>13:57:57</t>
+          <t>67:58:45</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.17</v>
+        <v>0.02</v>
       </c>
       <c r="M118" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -7325,121 +7325,121 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026/09/11 11:08:47</t>
+          <t>2026/09/12 12:37:06</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>-33.3649116, -70.4965666</t>
+          <t>-33.3671549, -70.6958183</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-33.36491, -70.49657</t>
+          <t>-33.36715, -70.69582</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026/09/11 11:23:05</t>
+          <t>2026/09/14 22:37:06</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>-33.3588366, -70.4849283</t>
+          <t>-33.3671549, -70.6958183</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>-33.35884, -70.48493</t>
+          <t>-33.36715, -70.69582</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>00:14:18</t>
+          <t>58:00:00</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C120" t="n">
+        <v>1</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2026/09/14 09:15:37</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>-33.359979, -70.807019</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-33.35998, -70.80702</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2026/09/14 09:39:49</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>-33.359046, -70.808866</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>-33.35905, -70.80887</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>00:24:12</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M120" t="n">
+        <v>4</v>
+      </c>
+      <c r="N120" t="n">
         <v>3</v>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>2026/09/11 11:24:20</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>-33.3585916, -70.48524</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>-33.35859, -70.48524</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>2026/09/11 18:19:57</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>-33.5140783, -70.637485</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>-33.51408, -70.63748</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>06:55:37</t>
-        </is>
-      </c>
-      <c r="L120" t="n">
-        <v>33.06</v>
-      </c>
-      <c r="M120" t="n">
-        <v>119</v>
-      </c>
-      <c r="N120" t="n">
-        <v>26</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7448,57 +7448,57 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026/09/11 18:21:12</t>
+          <t>2026/09/14 09:40:19</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>-33.5138849, -70.638245</t>
+          <t>-33.359059, -70.808908</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-33.51388, -70.63824</t>
+          <t>-33.35906, -70.80891</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026/09/12 08:06:40</t>
+          <t>2026/09/14 09:45:34</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>-33.4510416, -70.6724666</t>
+          <t>-33.359118, -70.808881</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>-33.45104, -70.67247</t>
+          <t>-33.35912, -70.80888</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>13:45:28</t>
+          <t>00:05:15</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>10.84</v>
+        <v>0.02</v>
       </c>
       <c r="M121" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="N121" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7507,57 +7507,57 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026/09/12 02:35:36</t>
+          <t>2026/09/14 09:46:19</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>-34.579636, -70.961312</t>
+          <t>-33.359147, -70.808861</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>-34.57964, -70.96131</t>
+          <t>-33.35915, -70.80886</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026/09/13 23:34:24</t>
+          <t>2026/09/14 09:59:57</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>-34.579636, -70.961312</t>
+          <t>-33.359251, -70.808957</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>-34.57964, -70.96131</t>
+          <t>-33.35925, -70.80896</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>44:58:48</t>
+          <t>00:13:38</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7566,53 +7566,53 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026/09/12 12:37:06</t>
+          <t>2026/09/14 10:00:14</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>-33.3671549, -70.6958183</t>
+          <t>-33.359242, -70.808944</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-33.36715, -70.69582</t>
+          <t>-33.35924, -70.80894</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026/09/13 22:37:06</t>
+          <t>2026/09/14 10:13:49</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>-33.3671549, -70.6958183</t>
+          <t>-33.359262, -70.808948</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>-33.36715, -70.69582</t>
+          <t>-33.35926, -70.80895</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>34:00:00</t>
+          <t>00:13:35</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -7625,57 +7625,57 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026/09/13 11:28:57</t>
+          <t>2026/09/14 10:13:50</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>-32.7975866, -70.8870966</t>
+          <t>-33.359263, -70.808938</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>-32.79759, -70.88710</t>
+          <t>-33.35926, -70.80894</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026/09/13 23:28:57</t>
+          <t>2026/09/14 10:45:28</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>-32.7975866, -70.8870966</t>
+          <t>-33.358778, -70.809257</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>-32.79759, -70.88710</t>
+          <t>-33.35878, -70.80926</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>00:31:38</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -7684,116 +7684,116 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026/09/13 14:50:30</t>
+          <t>2026/09/14 10:45:43</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>-33.476155, -70.6984166</t>
+          <t>-33.358818, -70.809306</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>-33.47615, -70.69842</t>
+          <t>-33.35882, -70.80931</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026/09/13 22:50:48</t>
+          <t>2026/09/14 11:03:16</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>-33.47617, -70.6984849</t>
+          <t>-33.3595, -70.809294</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>-33.47617, -70.69848</t>
+          <t>-33.35950, -70.80929</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>08:00:18</t>
+          <t>00:17:33</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026/09/13 17:24:36</t>
+          <t>2026/09/14 11:03:51</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>-33.4365983, -70.6295433</t>
+          <t>-33.359668, -70.809279</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>-33.43660, -70.62954</t>
+          <t>-33.35967, -70.80928</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026/09/13 23:24:36</t>
+          <t>2026/09/14 11:20:24</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>-33.4365983, -70.6295433</t>
+          <t>-33.359963, -70.809211</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>-33.43660, -70.62954</t>
+          <t>-33.35996, -70.80921</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>06:00:00</t>
+          <t>00:16:33</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -7802,164 +7802,1167 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026/09/13 17:38:01</t>
+          <t>2026/09/14 11:21:21</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>-32.8792333, -70.6087783</t>
+          <t>-33.359963, -70.809207</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>-32.87923, -70.60878</t>
+          <t>-33.35996, -70.80921</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026/09/13 22:44:57</t>
+          <t>2026/09/14 11:50:36</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>-32.8792333, -70.6087783</t>
+          <t>-33.360141, -70.809355</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>-32.87923, -70.60878</t>
+          <t>-33.36014, -70.80935</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>05:06:56</t>
+          <t>00:29:15</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026/09/13 18:32:25</t>
+          <t>2026/09/14 11:50:45</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>-33.0872833, -71.3622833</t>
+          <t>-33.360136, -70.809362</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>-33.08728, -71.36228</t>
+          <t>-33.36014, -70.80936</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026/09/13 22:32:25</t>
+          <t>2026/09/14 13:23:27</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>-33.0872833, -71.3622833</t>
+          <t>-33.360305, -70.809096</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>-33.08728, -71.36228</t>
+          <t>-33.36030, -70.80910</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>04:00:00</t>
+          <t>01:32:42</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
+          <t>SLP20250425120-AC01</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>10</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>2026/09/14 13:24:09</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>-33.360305, -70.809106</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>-33.36030, -70.80911</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>2026/09/14 13:44:12</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>-33.360371, -70.809155</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>-33.36037, -70.80916</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>00:20:03</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M129" t="n">
+        <v>7</v>
+      </c>
+      <c r="N129" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>SLP20250425120-AC01</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>11</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>2026/09/14 13:45:13</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>-33.36037, -70.809184</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>-33.36037, -70.80918</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>2026/09/14 14:16:43</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>-33.360378, -70.809173</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>-33.36038, -70.80917</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>00:31:30</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M130" t="n">
+        <v>11</v>
+      </c>
+      <c r="N130" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>SLP20250425120-AC01</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>12</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>2026/09/14 14:17:12</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>-33.360402, -70.809186</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>-33.36040, -70.80919</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>2026/09/14 14:31:15</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>-33.360054, -70.810257</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>-33.36005, -70.81026</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>00:14:03</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M131" t="n">
+        <v>6</v>
+      </c>
+      <c r="N131" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>SLP20250425120-AC01</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>13</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>2026/09/14 14:31:43</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>-33.360053, -70.81027</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>-33.36005, -70.81027</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>2026/09/14 14:47:08</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>-33.360014, -70.810408</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>-33.36001, -70.81041</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>00:15:25</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M132" t="n">
+        <v>5</v>
+      </c>
+      <c r="N132" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>SLP20250425120-AC01</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>14</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>2026/09/14 14:47:28</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>-33.360026, -70.810414</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>-33.36003, -70.81041</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>2026/09/14 14:59:03</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>-33.360332, -70.810543</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>-33.36033, -70.81054</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>00:11:35</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M133" t="n">
+        <v>6</v>
+      </c>
+      <c r="N133" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>SLP20250425120-AC01</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>15</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>2026/09/14 15:00:04</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>-33.36039, -70.810625</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>-33.36039, -70.81063</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>2026/09/14 15:15:01</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>-33.36049, -70.81058</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>-33.36049, -70.81058</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>00:14:57</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M134" t="n">
+        <v>5</v>
+      </c>
+      <c r="N134" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>SLP20250425120-AC01</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>16</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>2026/09/14 15:15:58</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>-33.36049, -70.810578</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>-33.36049, -70.81058</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>2026/09/14 15:31:57</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>-33.360534, -70.810545</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>-33.36053, -70.81055</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>00:15:59</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M135" t="n">
+        <v>5</v>
+      </c>
+      <c r="N135" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>SLP20250425120-AC01</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>17</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>2026/09/14 15:32:33</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>-33.360545, -70.810617</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-33.36055, -70.81062</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>2026/09/14 15:48:20</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>-33.36093, -70.810673</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>-33.36093, -70.81067</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>00:15:47</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M136" t="n">
+        <v>6</v>
+      </c>
+      <c r="N136" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>SLP20250425120-AC01</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>18</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>2026/09/14 15:48:42</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>-33.360935, -70.81067</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>-33.36093, -70.81067</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>2026/09/14 16:02:09</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>-33.360886, -70.810733</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>-33.36089, -70.81073</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>00:13:27</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M137" t="n">
+        <v>4</v>
+      </c>
+      <c r="N137" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>SLP20250425120-AC01</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>19</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>2026/09/14 16:02:12</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>-33.360881, -70.810735</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>-33.36088, -70.81073</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>2026/09/14 16:26:01</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>-33.360059, -70.807151</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>-33.36006, -70.80715</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>00:23:49</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="M138" t="n">
+        <v>5</v>
+      </c>
+      <c r="N138" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>SLP20250425120-AC01</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>20</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>2026/09/14 16:27:00</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>-33.359993, -70.807059</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>-33.35999, -70.80706</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>2026/09/14 23:28:01</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>-33.359993, -70.807059</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>-33.35999, -70.80706</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>07:01:01</t>
+        </is>
+      </c>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>SLP20250627045-AC02</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>2</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>2026/09/14 16:43:22</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>-34.205438, -70.677304</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>-34.20544, -70.67730</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>2026/09/14 22:45:08</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>-34.205426, -70.677323</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>-34.20543, -70.67732</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>06:01:46</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>MITSUBISHI L200 PHZF-89</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>4</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>2026/09/14 17:51:38</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>-33.4363, -70.6294366</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>-33.43630, -70.62944</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>2026/09/14 21:51:38</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>-33.4363, -70.6294366</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>-33.43630, -70.62944</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>04:00:00</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>CHANGAN HUNTER TKCS-53</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>13</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>2026/09/14 18:16:13</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>-34.1678416, -70.7329633</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>-34.16784, -70.73296</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>2026/09/14 22:00:52</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>-34.1677933, -70.7330183</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>-34.16779, -70.73302</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>03:44:39</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
           <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
-      <c r="C129" t="n">
-        <v>1</v>
-      </c>
-      <c r="D129" t="inlineStr">
+      <c r="C143" t="n">
+        <v>11</v>
+      </c>
+      <c r="D143" t="inlineStr">
         <is>
           <t>Paradas</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>2026/09/13 18:48:44</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>-32.7431016, -70.729765</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>-32.74310, -70.72977</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>2026/09/13 22:50:22</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>-32.7431016, -70.729765</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>-32.74310, -70.72977</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>04:01:38</t>
-        </is>
-      </c>
-      <c r="L129" t="n">
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>2026/09/14 18:19:50</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>-34.1677166, -70.73301</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>-34.16772, -70.73301</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>2026/09/14 22:19:50</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>-34.1677166, -70.73301</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>-34.16772, -70.73301</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>04:00:00</t>
+        </is>
+      </c>
+      <c r="L143" t="n">
         <v>0</v>
       </c>
-      <c r="M129" t="n">
+      <c r="M143" t="n">
         <v>0</v>
       </c>
-      <c r="N129" t="n">
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>CHANGAN HUNTER TGPS-77</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>11</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>2026/09/14 18:34:07</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>-32.7976266, -70.8871433</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>-32.79763, -70.88714</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>2026/09/14 22:34:07</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>-32.7976266, -70.8871433</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>-32.79763, -70.88714</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>04:00:00</t>
+        </is>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>SUZUKI CARRY SKDB-52</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>14</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>2026/09/14 19:11:20</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>-32.8791966, -70.6087816</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>-32.87920, -70.60878</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>2026/09/14 23:11:20</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>-32.8791966, -70.6087816</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>-32.87920, -70.60878</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>04:00:00</t>
+        </is>
+      </c>
+      <c r="L145" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>MITSUBISHI L200 LVHX-40</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>11</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>2026/09/14 19:40:48</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>-33.4761633, -70.6983933</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>-33.47616, -70.69839</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>2026/09/14 21:41:40</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>-33.4761633, -70.6983933</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>-33.47616, -70.69839</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>02:00:52</t>
+        </is>
+      </c>
+      <c r="L146" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0</v>
+      </c>
+      <c r="N146" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8011,10 +9014,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1897.17</v>
+        <v>1653.28</v>
       </c>
       <c r="C2" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -8030,7 +9033,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>880.1</v>
+        <v>895.8</v>
       </c>
       <c r="C3" t="n">
         <v>10</v>
@@ -8049,16 +9052,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>915.52</v>
+        <v>1001.7</v>
       </c>
       <c r="C4" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5">
@@ -8068,10 +9071,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1316.64</v>
+        <v>1188.2</v>
       </c>
       <c r="C5" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -8131,7 +9134,7 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>5</v>
@@ -8144,13 +9147,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.37</v>
+        <v>2.51</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
         <v>6</v>
@@ -8163,10 +9166,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.08</v>
+        <v>0.29</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>3</v>
@@ -8207,7 +9210,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -8239,10 +9242,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1526.1</v>
+        <v>1533.72</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -8258,10 +9261,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>323.54</v>
+        <v>324.44</v>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
@@ -8296,16 +9299,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -8315,16 +9318,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
         <v>4</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -8334,10 +9337,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1091.16</v>
+        <v>1297.15</v>
       </c>
       <c r="C19" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -914,7 +914,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/09/14 22:31:38</t>
+          <t>2026/09/14 23:31:38</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>166:00:00</t>
+          <t>167:00:00</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026/09/14 22:41:51</t>
+          <t>2026/09/14 23:41:51</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>166:01:08</t>
+          <t>167:01:08</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/09/14 22:56:13</t>
+          <t>2026/09/14 23:56:13</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>166:00:07</t>
+          <t>167:00:07</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026/09/14 22:57:17</t>
+          <t>2026/09/14 23:57:39</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>151:30:32</t>
+          <t>152:30:54</t>
         </is>
       </c>
       <c r="L70" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026/09/14 22:34:21</t>
+          <t>2026/09/14 23:34:38</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>67:58:45</t>
+          <t>68:59:02</t>
         </is>
       </c>
       <c r="L118" t="n">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026/09/14 22:45:08</t>
+          <t>2026/09/14 23:45:08</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>06:01:46</t>
+          <t>07:01:46</t>
         </is>
       </c>
       <c r="L140" t="n">
@@ -8643,7 +8643,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026/09/14 21:51:38</t>
+          <t>2026/09/14 23:51:38</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>04:00:00</t>
+          <t>06:00:00</t>
         </is>
       </c>
       <c r="L141" t="n">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026/09/14 21:41:40</t>
+          <t>2026/09/14 23:41:40</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>02:00:52</t>
+          <t>04:00:52</t>
         </is>
       </c>
       <c r="L146" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -796,7 +796,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026/09/15 22:57:39</t>
+          <t>2026/09/15 23:57:15</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>166:29:38</t>
+          <t>167:29:14</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026/09/15 21:47:19</t>
+          <t>2026/09/15 23:47:19</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9307,7 +9307,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>04:00:00</t>
+          <t>06:00:00</t>
         </is>
       </c>
       <c r="L152" t="n">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026/09/15 21:53:13</t>
+          <t>2026/09/15 23:53:13</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>04:01:06</t>
+          <t>06:01:06</t>
         </is>
       </c>
       <c r="L153" t="n">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026/09/15 21:55:56</t>
+          <t>2026/09/15 23:55:56</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>04:00:00</t>
+          <t>06:00:00</t>
         </is>
       </c>
       <c r="L154" t="n">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026/09/15 21:59:55</t>
+          <t>2026/09/15 23:59:55</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>02:00:08</t>
+          <t>04:00:08</t>
         </is>
       </c>
       <c r="L158" t="n">
@@ -9859,7 +9859,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>586.8099999999999</v>
+        <v>593.63</v>
       </c>
       <c r="C3" t="n">
         <v>10</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N165"/>
+  <dimension ref="A1:N166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026/09/16 22:46:35</t>
+          <t>2026/09/16 23:46:08</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>30:39:43</t>
+          <t>31:39:16</t>
         </is>
       </c>
       <c r="L140" t="n">
@@ -9469,7 +9469,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026/09/16 21:54:00</t>
+          <t>2026/09/16 23:54:00</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>06:00:03</t>
+          <t>08:00:03</t>
         </is>
       </c>
       <c r="L155" t="n">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026/09/16 21:37:48</t>
+          <t>2026/09/16 23:37:48</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>04:00:04</t>
+          <t>06:00:04</t>
         </is>
       </c>
       <c r="L160" t="n">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026/09/16 21:45:51</t>
+          <t>2026/09/16 23:45:51</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>02:00:52</t>
+          <t>04:00:52</t>
         </is>
       </c>
       <c r="L163" t="n">
@@ -10059,32 +10059,91 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026/09/16 23:21:06</t>
+          <t>2026/09/16 23:19:53</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>-33.5079416, -70.6288266</t>
+          <t>-33.5078883, -70.6289333</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>-33.50794, -70.62883</t>
+          <t>-33.50789, -70.62893</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>00:53:49</t>
+          <t>00:52:36</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>12.14</v>
+        <v>12.13</v>
       </c>
       <c r="M165" t="n">
         <v>83</v>
       </c>
       <c r="N165" t="n">
         <v>29</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>OPEL COMBO</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>9</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>2026/09/16 23:21:06</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>-33.5079416, -70.6288266</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>-33.50794, -70.62883</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>2026/09/16 23:43:06</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>-33.51385, -70.6382499</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>-33.51385, -70.63825</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>00:22:00</t>
+        </is>
+      </c>
+      <c r="L166" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M166" t="n">
+        <v>18</v>
+      </c>
+      <c r="N166" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -10401,10 +10460,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>184.09</v>
+        <v>185.68</v>
       </c>
       <c r="C16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -7640,7 +7640,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026/09/17 22:23:58</t>
+          <t>2026/09/17 23:24:20</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>55:07:04</t>
+          <t>56:07:26</t>
         </is>
       </c>
       <c r="L124" t="n">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026/09/17 22:46:23</t>
+          <t>2026/09/17 23:46:38</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>54:39:31</t>
+          <t>55:39:46</t>
         </is>
       </c>
       <c r="L130" t="n">
@@ -9469,7 +9469,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026/09/17 21:33:04</t>
+          <t>2026/09/17 23:33:04</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>03:35:56</t>
+          <t>05:35:56</t>
         </is>
       </c>
       <c r="L155" t="n">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026/09/17 21:31:13</t>
+          <t>2026/09/17 23:31:13</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>02:01:00</t>
+          <t>04:01:00</t>
         </is>
       </c>
       <c r="L158" t="n">
@@ -9918,7 +9918,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>635.0599999999999</v>
+        <v>636.86</v>
       </c>
       <c r="C3" t="n">
         <v>15</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N163"/>
+  <dimension ref="A1:N161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/09/18 22:42:12</t>
+          <t>2026/09/18 23:42:12</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>166:01:10</t>
+          <t>167:01:10</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026/09/18 22:56:13</t>
+          <t>2026/09/18 23:56:13</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>166:00:03</t>
+          <t>167:00:03</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026/09/18 22:22:57</t>
+          <t>2026/09/18 23:22:59</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>83:22:34</t>
+          <t>84:22:36</t>
         </is>
       </c>
       <c r="L108" t="n">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026/09/18 22:23:57</t>
+          <t>2026/09/18 23:24:20</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>79:07:03</t>
+          <t>80:07:26</t>
         </is>
       </c>
       <c r="L121" t="n">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026/09/18 21:16:39</t>
+          <t>2026/09/18 23:16:39</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>26:52:42</t>
+          <t>28:52:42</t>
         </is>
       </c>
       <c r="L153" t="n">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026/09/18 22:46:31</t>
+          <t>2026/09/18 23:46:15</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>19:00:13</t>
+          <t>19:59:57</t>
         </is>
       </c>
       <c r="L158" t="n">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026/09/18 21:25:59</t>
+          <t>2026/09/18 23:25:59</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="L159" t="n">
@@ -9736,11 +9736,11 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -9749,37 +9749,37 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026/09/18 17:57:23</t>
+          <t>2026/09/18 19:47:53</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>-33.4584983, -70.6632966</t>
+          <t>-32.7976083, -70.8870616</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>-33.45850, -70.66330</t>
+          <t>-32.79761, -70.88706</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026/09/18 21:57:25</t>
+          <t>2026/09/18 23:48:02</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>-33.4584983, -70.6632966</t>
+          <t>-32.7976083, -70.8870616</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>-33.45850, -70.66330</t>
+          <t>-32.79761, -70.88706</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>04:00:02</t>
+          <t>04:00:09</t>
         </is>
       </c>
       <c r="L160" t="n">
@@ -9795,11 +9795,11 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -9808,37 +9808,37 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026/09/18 19:47:53</t>
+          <t>2026/09/18 19:53:11</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>-32.7976083, -70.8870616</t>
+          <t>-33.0871666, -71.3621533</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88706</t>
+          <t>-33.08717, -71.36215</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026/09/18 21:48:02</t>
+          <t>2026/09/18 23:53:11</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>-32.7976083, -70.8870616</t>
+          <t>-33.0871666, -71.3621533</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88706</t>
+          <t>-33.08717, -71.36215</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>02:00:09</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L161" t="n">
@@ -9848,124 +9848,6 @@
         <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
-        </is>
-      </c>
-      <c r="C162" t="n">
-        <v>3</v>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>2026/09/18 19:53:11</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>-33.0871666, -71.3621533</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>-33.08717, -71.36215</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>2026/09/18 21:53:11</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>-33.0871666, -71.3621533</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>-33.08717, -71.36215</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>02:00:00</t>
-        </is>
-      </c>
-      <c r="L162" t="n">
-        <v>0</v>
-      </c>
-      <c r="M162" t="n">
-        <v>0</v>
-      </c>
-      <c r="N162" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
-        </is>
-      </c>
-      <c r="C163" t="n">
-        <v>2</v>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>2026/09/18 21:22:13</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>-32.841563, -70.936737</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>-32.84156, -70.93674</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>2026/09/18 22:16:03</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>-32.841698, -70.936857</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>-32.84170, -70.93686</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>00:53:50</t>
-        </is>
-      </c>
-      <c r="L163" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="M163" t="n">
-        <v>0</v>
-      </c>
-      <c r="N163" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10036,13 +9918,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>477</v>
+        <v>478.82</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>18</v>
@@ -10340,13 +10222,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>935.5700000000001</v>
+        <v>1000.2</v>
       </c>
       <c r="C19" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>136</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,13 +446,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N161"/>
+  <dimension ref="A1:N167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Desde : 2026/09/12 04:00:00   Hasta : 2026/09/19 03:59:59</t>
+          <t>Desde : 2026/09/13 04:00:00   Hasta : 2026/09/20 03:59:59</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -545,41 +545,41 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026/09/12 00:00:05</t>
+          <t>2026/09/13 00:01:38</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-33.359951, -70.806969</t>
+          <t>-34.34603, -71.125731</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-33.35995, -70.80697</t>
+          <t>-34.34603, -71.12573</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026/09/14 08:18:02</t>
+          <t>2026/09/13 01:03:52</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-33.359979, -70.807019</t>
+          <t>-34.345955, -71.125806</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-33.35998, -70.80702</t>
+          <t>-34.34595, -71.12581</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>56:17:57</t>
+          <t>01:02:14</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -591,7 +591,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>LPR20251A02800014-DS</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -599,58 +599,58 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026/09/12 00:00:12</t>
+          <t>2026/09/13 00:11:29</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-33.476155, -70.69845</t>
+          <t>-34.205371, -70.67735</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-33.47615, -70.69845</t>
+          <t>-34.20537, -70.67735</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026/09/12 08:50:52</t>
+          <t>2026/09/15 10:03:09</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-33.362175, -70.67011</t>
+          <t>-34.205533, -70.677314</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-33.36218, -70.67011</t>
+          <t>-34.20553, -70.67731</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>08:50:40</t>
+          <t>57:51:40</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>18.67</v>
+        <v>0.09</v>
       </c>
       <c r="M5" t="n">
-        <v>112</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -658,58 +658,58 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026/09/12 00:01:03</t>
+          <t>2026/09/13 00:13:39</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-33.0872133, -71.3621916</t>
+          <t>-33.359948, -70.807046</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-33.08721, -71.36219</t>
+          <t>-33.35995, -70.80705</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026/09/12 09:01:50</t>
+          <t>2026/09/14 08:18:02</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-33.0873299, -71.3623266</t>
+          <t>-33.359979, -70.807019</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-33.08733, -71.36233</t>
+          <t>-33.35998, -70.80702</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>09:00:47</t>
+          <t>32:04:23</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="M6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -717,58 +717,58 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026/09/12 00:01:46</t>
+          <t>2026/09/13 00:15:01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-34.34603, -71.125731</t>
+          <t>-32.74302, -70.7297533</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-34.34603, -71.12573</t>
+          <t>-32.74302, -70.72975</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026/09/13 01:03:52</t>
+          <t>2026/09/13 18:47:29</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-34.345955, -71.125806</t>
+          <t>-32.7430249, -70.72984</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-34.34595, -71.12581</t>
+          <t>-32.74302, -70.72984</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>25:02:06</t>
+          <t>18:32:28</t>
         </is>
       </c>
       <c r="L7" t="n">
         <v>0.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>LPR20251T02900038-RTN</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -781,44 +781,44 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026/09/12 00:06:39</t>
+          <t>2026/09/13 00:22:29</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-34.205326, -70.677367</t>
+          <t>-34.876381, -71.127181</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-34.20533, -70.67737</t>
+          <t>-34.87638, -71.12718</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026/09/15 10:03:09</t>
+          <t>2026/09/15 10:02:56</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-34.205533, -70.677314</t>
+          <t>-34.876431, -71.127382</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-34.20553, -70.67731</t>
+          <t>-34.87643, -71.12738</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>81:56:30</t>
+          <t>57:40:27</t>
         </is>
       </c>
       <c r="L8" t="n">
         <v>0.1</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
@@ -827,7 +827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -840,53 +840,53 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026/09/12 00:15:01</t>
+          <t>2026/09/13 00:29:01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-32.74302, -70.7297533</t>
+          <t>-33.476225, -70.6984066</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-32.74302, -70.72975</t>
+          <t>-33.47622, -70.69841</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026/09/13 18:47:29</t>
+          <t>2026/09/13 11:50:02</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-32.7430249, -70.72984</t>
+          <t>-33.517245, -70.7148749</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-32.74302, -70.72984</t>
+          <t>-33.51725, -70.71487</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>42:32:28</t>
+          <t>11:21:01</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.01</v>
+        <v>6.64</v>
       </c>
       <c r="M9" t="n">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>LPR20251V02900023-LL</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -899,53 +899,53 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026/09/12 00:21:43</t>
+          <t>2026/09/13 00:31:30</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-32.857668, -70.900525</t>
+          <t>-33.899848, -71.429508</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-32.85767, -70.90053</t>
+          <t>-33.89985, -71.42951</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/09/13 11:43:30</t>
+          <t>2026/09/15 10:03:23</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-33.459345, -70.541998</t>
+          <t>-33.899292, -71.42915</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-33.45934, -70.54200</t>
+          <t>-33.89929, -71.42915</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>35:21:47</t>
+          <t>57:31:53</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>89.75</v>
+        <v>0.17</v>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LPR20251T02900038-RTN</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -953,58 +953,58 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026/09/12 00:23:20</t>
+          <t>2026/09/13 00:34:39</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-34.876381, -71.127181</t>
+          <t>-34.579636, -70.961312</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-34.87638, -71.12718</t>
+          <t>-34.57964, -70.96131</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026/09/15 10:02:56</t>
+          <t>2026/09/15 10:02:30</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-34.876431, -71.127382</t>
+          <t>-34.579551, -70.961433</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-34.87643, -71.12738</t>
+          <t>-34.57955, -70.96143</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>81:39:36</t>
+          <t>57:27:51</t>
         </is>
       </c>
       <c r="L11" t="n">
         <v>0.1</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LPR20251V02900023-LL</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1017,53 +1017,53 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026/09/12 00:31:56</t>
+          <t>2026/09/13 00:37:06</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-33.899886, -71.429534</t>
+          <t>-33.3671549, -70.6958183</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-33.89989, -71.42953</t>
+          <t>-33.36715, -70.69582</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026/09/15 10:03:23</t>
+          <t>2026/09/15 19:34:29</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-33.899292, -71.42915</t>
+          <t>-33.5138966, -70.6381783</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-33.89929, -71.42915</t>
+          <t>-33.51390, -70.63818</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>81:31:27</t>
+          <t>66:57:23</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.17</v>
+        <v>21.73</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>LPR20251E02900022</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1076,53 +1076,53 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026/09/12 00:35:51</t>
+          <t>2026/09/13 00:41:10</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-34.579677, -70.96149</t>
+          <t>-33.36765, -70.697163</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-34.57968, -70.96149</t>
+          <t>-33.36765, -70.69716</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026/09/12 01:36:53</t>
+          <t>2026/09/19 22:42:12</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-34.579636, -70.961312</t>
+          <t>-33.36765, -70.697163</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-34.57964, -70.96131</t>
+          <t>-33.36765, -70.69716</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>01:01:02</t>
+          <t>166:01:02</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LPR20251E02900022</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1130,58 +1130,58 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026/09/12 00:41:02</t>
+          <t>2026/09/13 00:46:08</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-33.36765, -70.697163</t>
+          <t>-33.4364066, -70.629565</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-33.36765, -70.69716</t>
+          <t>-33.43641, -70.62956</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/09/18 23:42:12</t>
+          <t>2026/09/13 05:17:42</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-33.36765, -70.697163</t>
+          <t>-33.3689316, -70.5006183</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-33.36765, -70.69716</t>
+          <t>-33.36893, -70.50062</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>167:01:10</t>
+          <t>04:31:34</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>16.8</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>128</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1194,53 +1194,53 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026/09/12 00:46:08</t>
+          <t>2026/09/13 00:47:19</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-33.4364066, -70.629565</t>
+          <t>-34.205533, -70.677237</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-33.43641, -70.62956</t>
+          <t>-34.20553, -70.67724</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/09/13 05:17:42</t>
+          <t>2026/09/14 12:35:00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-33.3689316, -70.5006183</t>
+          <t>-34.204249, -70.679129</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-33.36893, -70.50062</t>
+          <t>-34.20425, -70.67913</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>28:31:34</t>
+          <t>35:47:41</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>16.8</v>
+        <v>0.35</v>
       </c>
       <c r="M15" t="n">
-        <v>128</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1253,47 +1253,47 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026/09/12 00:47:00</t>
+          <t>2026/09/13 00:51:25</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-34.205533, -70.677237</t>
+          <t>-33.0873299, -71.3623866</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-34.20553, -70.67724</t>
+          <t>-33.08733, -71.36239</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/09/14 12:35:00</t>
+          <t>2026/09/13 09:13:18</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-34.204249, -70.679129</t>
+          <t>-33.087335, -71.362245</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-34.20425, -70.67913</t>
+          <t>-33.08734, -71.36225</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>59:48:00</t>
+          <t>08:21:53</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0.35</v>
+        <v>0.04</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026/09/12 00:56:10</t>
+          <t>2026/09/13 00:56:08</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026/09/18 23:56:13</t>
+          <t>2026/09/19 22:56:13</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>167:00:03</t>
+          <t>166:00:05</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -1358,7 +1358,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1366,58 +1366,58 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026/09/12 00:57:33</t>
+          <t>2026/09/13 00:57:17</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-33.5138849, -70.638245</t>
+          <t>-34.042553, -70.68171</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-33.51388, -70.63824</t>
+          <t>-34.04255, -70.68171</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026/09/12 08:06:40</t>
+          <t>2026/09/16 00:59:49</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-33.4510416, -70.6724666</t>
+          <t>-34.042668, -70.681568</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-33.45104, -70.67247</t>
+          <t>-34.04267, -70.68157</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>07:09:07</t>
+          <t>72:02:32</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>10.84</v>
+        <v>0.04</v>
       </c>
       <c r="M18" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1425,52 +1425,52 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026/09/12 00:59:09</t>
+          <t>2026/09/13 01:06:35</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-34.042613, -70.681788</t>
+          <t>-32.87918, -70.6088116</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-34.04261, -70.68179</t>
+          <t>-32.87918, -70.60881</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026/09/16 00:59:49</t>
+          <t>2026/09/13 11:56:40</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-34.042668, -70.681568</t>
+          <t>-32.8792, -70.6088916</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-34.04267, -70.68157</t>
+          <t>-32.87920, -70.60889</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>96:00:40</t>
+          <t>10:50:05</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0.05</v>
+        <v>1.92</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -1489,112 +1489,112 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026/09/12 01:14:47</t>
+          <t>2026/09/13 01:40:06</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-32.7975983, -70.8870416</t>
+          <t>-32.7976249, -70.8871033</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-32.79760, -70.88704</t>
+          <t>-32.79762, -70.88710</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026/09/12 08:35:20</t>
+          <t>2026/09/13 09:58:37</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-32.882925, -70.6123566</t>
+          <t>-32.79572, -70.8201616</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-32.88293, -70.61236</t>
+          <t>-32.79572, -70.82016</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>07:20:33</t>
+          <t>08:18:31</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>41.78</v>
+        <v>9.57</v>
       </c>
       <c r="M20" t="n">
-        <v>111</v>
+        <v>66</v>
       </c>
       <c r="N20" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026/09/13 02:01:16</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-34.345955, -71.125806</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-34.34595, -71.12581</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026/09/15 10:01:43</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-34.346013, -71.12574</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-34.34601, -71.12574</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>56:00:27</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2</v>
+      </c>
+      <c r="N21" t="n">
         <v>1</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026/09/12 01:43:56</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>-32.8792, -70.608775</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-32.87920, -70.60877</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2026/09/12 09:11:14</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-32.887265, -70.613435</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>-32.88726, -70.61343</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>07:27:18</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
-        <v>17.41</v>
-      </c>
-      <c r="M21" t="n">
-        <v>86</v>
-      </c>
-      <c r="N21" t="n">
-        <v>26</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1607,57 +1607,57 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026/09/12 02:35:36</t>
+          <t>2026/09/13 05:18:01</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-34.579636, -70.961312</t>
+          <t>-33.3687366, -70.5006866</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-34.57964, -70.96131</t>
+          <t>-33.36874, -70.50069</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026/09/15 10:02:30</t>
+          <t>2026/09/13 07:00:10</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-34.579551, -70.961433</t>
+          <t>-33.3609633, -70.2530549</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-34.57955, -70.96143</t>
+          <t>-33.36096, -70.25305</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>79:26:54</t>
+          <t>01:42:09</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0.1</v>
+        <v>40.18</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1666,57 +1666,57 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026/09/12 08:07:55</t>
+          <t>2026/09/13 07:01:25</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-33.4500566, -70.6683966</t>
+          <t>-33.36056, -70.25361</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-33.45006, -70.66840</t>
+          <t>-33.36056, -70.25361</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026/09/12 12:35:54</t>
+          <t>2026/09/13 07:25:20</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-33.3672083, -70.6955866</t>
+          <t>-33.35739, -70.252945</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-33.36721, -70.69559</t>
+          <t>-33.35739, -70.25294</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>04:27:59</t>
+          <t>00:23:55</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>11.46</v>
+        <v>0.91</v>
       </c>
       <c r="M23" t="n">
-        <v>116</v>
+        <v>14</v>
       </c>
       <c r="N23" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1725,57 +1725,57 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026/09/12 08:35:31</t>
+          <t>2026/09/13 07:26:35</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-32.8831566, -70.6124033</t>
+          <t>-33.3573883, -70.2529416</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-32.88316, -70.61240</t>
+          <t>-33.35739, -70.25294</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026/09/12 12:59:19</t>
+          <t>2026/09/13 16:52:38</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-32.7977466, -70.887385</t>
+          <t>-33.368945, -70.5006416</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-32.79775, -70.88738</t>
+          <t>-33.36894, -70.50064</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>04:23:48</t>
+          <t>09:26:03</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>42.14</v>
+        <v>40.77</v>
       </c>
       <c r="M24" t="n">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="N24" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1784,47 +1784,47 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026/09/12 08:51:05</t>
+          <t>2026/09/13 08:05:04</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-33.362205, -70.6701433</t>
+          <t>-32.838385, -70.95554</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-33.36221, -70.67014</t>
+          <t>-32.83839, -70.95554</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026/09/12 09:47:13</t>
+          <t>2026/09/13 11:43:30</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-33.578365, -70.6311933</t>
+          <t>-33.459345, -70.541998</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-33.57836, -70.63119</t>
+          <t>-33.45934, -70.54200</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>00:56:08</t>
+          <t>03:38:26</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>33.81</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1843,57 +1843,57 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026/09/12 09:02:13</t>
+          <t>2026/09/13 09:14:33</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-33.0871766, -71.3621933</t>
+          <t>-33.0873416, -71.36223</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-33.08718, -71.36219</t>
+          <t>-33.08734, -71.36223</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026/09/12 16:01:16</t>
+          <t>2026/09/13 09:21:31</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-33.0932983, -71.356795</t>
+          <t>-33.0873233, -71.3622499</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-33.09330, -71.35680</t>
+          <t>-33.08732, -71.36225</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>06:59:03</t>
+          <t>00:06:58</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="N26" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1902,57 +1902,57 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026/09/12 09:11:32</t>
+          <t>2026/09/13 09:21:45</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-32.8874416, -70.61326</t>
+          <t>-33.0873149, -71.3623049</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-32.88744, -70.61326</t>
+          <t>-33.08731, -71.36230</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026/09/12 09:32:31</t>
+          <t>2026/09/13 11:41:19</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-32.8874316, -70.6133416</t>
+          <t>-33.0987699, -71.3302799</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-32.88743, -70.61334</t>
+          <t>-33.09877, -71.33028</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>00:20:59</t>
+          <t>02:19:34</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.53</v>
+        <v>4</v>
       </c>
       <c r="M27" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N27" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1961,57 +1961,57 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026/09/12 09:33:46</t>
+          <t>2026/09/13 09:58:49</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-32.887455, -70.6132666</t>
+          <t>-32.7958466, -70.820085</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-32.88746, -70.61327</t>
+          <t>-32.79585, -70.82009</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026/09/12 09:47:26</t>
+          <t>2026/09/13 10:14:42</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-32.861565, -70.6080116</t>
+          <t>-32.797895, -70.8268716</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-32.86156, -70.60801</t>
+          <t>-32.79789, -70.82687</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>00:13:40</t>
+          <t>00:15:53</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.22</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="N28" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2020,57 +2020,57 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026/09/12 09:47:29</t>
+          <t>2026/09/13 10:15:57</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-32.86157, -70.6080083</t>
+          <t>-32.7980049, -70.8270616</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-32.86157, -70.60801</t>
+          <t>-32.79800, -70.82706</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026/09/12 10:06:58</t>
+          <t>2026/09/13 10:35:48</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-32.8791933, -70.6089133</t>
+          <t>-32.7678066, -70.8336466</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-32.87919, -70.60891</t>
+          <t>-32.76781, -70.83365</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>00:19:29</t>
+          <t>00:19:51</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.88</v>
+        <v>3.72</v>
       </c>
       <c r="M29" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N29" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2079,53 +2079,53 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026/09/12 09:48:28</t>
+          <t>2026/09/13 10:36:11</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-33.5778133, -70.6310833</t>
+          <t>-32.7680966, -70.8334233</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-33.57781, -70.63108</t>
+          <t>-32.76810, -70.83342</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026/09/12 14:08:52</t>
+          <t>2026/09/13 10:55:01</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-33.4763083, -70.6983183</t>
+          <t>-32.79773, -70.8874333</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-33.47631, -70.69832</t>
+          <t>-32.79773, -70.88743</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>04:20:24</t>
+          <t>00:18:50</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>18.6</v>
+        <v>6.27</v>
       </c>
       <c r="M30" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="N30" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2138,57 +2138,57 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026/09/12 10:07:59</t>
+          <t>2026/09/13 10:56:13</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-32.8790299, -70.6094716</t>
+          <t>-32.7976, -70.8870866</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-32.87903, -70.60947</t>
+          <t>-32.79760, -70.88709</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026/09/12 13:24:44</t>
+          <t>2026/09/13 11:28:36</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-32.8790349, -70.60949</t>
+          <t>-32.7976916, -70.8874383</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-32.87903, -70.60949</t>
+          <t>-32.79769, -70.88744</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>03:16:45</t>
+          <t>00:32:23</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0.02</v>
+        <v>11.04</v>
       </c>
       <c r="M31" t="n">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="N31" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2197,57 +2197,57 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026/09/12 12:37:06</t>
+          <t>2026/09/13 11:28:57</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-33.3671549, -70.6958183</t>
+          <t>-32.7975866, -70.8870966</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-33.36715, -70.69582</t>
+          <t>-32.79759, -70.88710</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026/09/15 19:34:29</t>
+          <t>2026/09/14 06:44:50</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-33.5138966, -70.6381783</t>
+          <t>-32.8518633, -70.6846683</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-33.51390, -70.63818</t>
+          <t>-32.85186, -70.68467</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>78:57:23</t>
+          <t>19:15:53</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>21.73</v>
+        <v>29.13</v>
       </c>
       <c r="M32" t="n">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="N32" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2256,57 +2256,57 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026/09/12 13:00:23</t>
+          <t>2026/09/13 11:41:26</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-32.7976466, -70.8871033</t>
+          <t>-33.0988, -71.3301983</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-32.79765, -70.88710</t>
+          <t>-33.09880, -71.33020</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026/09/12 13:11:01</t>
+          <t>2026/09/13 13:16:25</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-32.797785, -70.8875183</t>
+          <t>-33.08699, -71.3619633</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-32.79778, -70.88752</t>
+          <t>-33.08699, -71.36196</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>00:10:38</t>
+          <t>01:34:59</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0.38</v>
+        <v>4</v>
       </c>
       <c r="M33" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="N33" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2315,57 +2315,57 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026/09/12 13:11:14</t>
+          <t>2026/09/13 11:43:41</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-32.79765, -70.8870999</t>
+          <t>-33.459367, -70.542</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-32.79765, -70.88710</t>
+          <t>-33.45937, -70.54200</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026/09/12 15:41:56</t>
+          <t>2026/09/14 13:27:48</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-32.7562366, -70.7225383</t>
+          <t>-32.840288, -70.964465</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-32.75624, -70.72254</t>
+          <t>-32.84029, -70.96447</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>02:30:42</t>
+          <t>25:44:07</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>18.68</v>
+        <v>207.11</v>
       </c>
       <c r="M34" t="n">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="N34" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2374,47 +2374,47 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026/09/12 13:25:18</t>
+          <t>2026/09/13 11:51:17</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-32.8792599, -70.6087566</t>
+          <t>-33.517435, -70.7149666</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-32.87926, -70.60876</t>
+          <t>-33.51743, -70.71497</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026/09/12 13:57:43</t>
+          <t>2026/09/13 14:49:15</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-32.85552, -70.6255766</t>
+          <t>-33.4762766, -70.6982966</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-32.85552, -70.62558</t>
+          <t>-33.47628, -70.69830</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>00:32:25</t>
+          <t>02:57:58</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="M35" t="n">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="N35" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36">
@@ -2424,7 +2424,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2433,57 +2433,57 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026/09/12 13:58:58</t>
+          <t>2026/09/13 11:57:38</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-32.8555283, -70.625745</t>
+          <t>-32.8791983, -70.6088133</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-32.85553, -70.62574</t>
+          <t>-32.87920, -70.60881</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026/09/12 14:49:15</t>
+          <t>2026/09/13 17:26:51</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-32.8793599, -70.6089033</t>
+          <t>-32.8792216, -70.6089233</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-32.87936, -70.60890</t>
+          <t>-32.87922, -70.60892</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>00:50:17</t>
+          <t>05:29:13</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>15.2</v>
+        <v>0.01</v>
       </c>
       <c r="M36" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="N36" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2492,57 +2492,57 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026/09/12 14:09:21</t>
+          <t>2026/09/13 13:17:10</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-33.4763699, -70.6983633</t>
+          <t>-33.0873149, -71.3623266</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-33.47637, -70.69836</t>
+          <t>-33.08731, -71.36233</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026/09/12 14:52:10</t>
+          <t>2026/09/13 16:34:39</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-33.4402016, -70.6554916</t>
+          <t>-33.0873533, -71.3623133</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-33.44020, -70.65549</t>
+          <t>-33.08735, -71.36231</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>00:42:49</t>
+          <t>03:17:29</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>14.53</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="N37" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2551,57 +2551,57 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026/09/12 14:49:31</t>
+          <t>2026/09/13 14:50:30</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-32.8792549, -70.6087983</t>
+          <t>-33.476155, -70.6984166</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-32.87925, -70.60880</t>
+          <t>-33.47615, -70.69842</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026/09/12 15:12:24</t>
+          <t>2026/09/14 08:51:23</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-32.8792599, -70.6088533</t>
+          <t>-33.3750449, -70.63351</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-32.87926, -70.60885</t>
+          <t>-33.37504, -70.63351</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>00:22:53</t>
+          <t>18:00:53</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0.01</v>
+        <v>31.32</v>
       </c>
       <c r="M38" t="n">
-        <v>7</v>
+        <v>104</v>
       </c>
       <c r="N38" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2610,57 +2610,57 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026/09/12 14:53:11</t>
+          <t>2026/09/13 16:35:17</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-33.440545, -70.65729</t>
+          <t>-33.087325, -71.3623383</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-33.44055, -70.65729</t>
+          <t>-33.08732, -71.36234</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026/09/12 15:19:35</t>
+          <t>2026/09/13 18:32:21</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>-33.3621966, -70.6701483</t>
+          <t>-33.0873033, -71.3622983</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>-33.36220, -70.67015</t>
+          <t>-33.08730, -71.36230</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>00:26:24</t>
+          <t>01:57:04</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>13.2</v>
+        <v>0.02</v>
       </c>
       <c r="M39" t="n">
-        <v>105</v>
+        <v>6</v>
       </c>
       <c r="N39" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2669,53 +2669,53 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026/09/12 15:12:44</t>
+          <t>2026/09/13 16:53:09</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-32.87929, -70.608745</t>
+          <t>-33.3687733, -70.5006933</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-32.87929, -70.60874</t>
+          <t>-33.36877, -70.50069</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026/09/12 17:08:20</t>
+          <t>2026/09/13 17:23:33</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-32.7482499, -70.7279733</t>
+          <t>-33.436265, -70.6296016</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>-32.74825, -70.72797</t>
+          <t>-33.43626, -70.62960</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>01:55:36</t>
+          <t>00:30:24</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>29.07</v>
+        <v>18.08</v>
       </c>
       <c r="M40" t="n">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="N40" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -2728,57 +2728,57 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026/09/12 15:20:30</t>
+          <t>2026/09/13 17:24:36</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-33.3622249, -70.6701683</t>
+          <t>-33.4365983, -70.6295433</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-33.36222, -70.67017</t>
+          <t>-33.43660, -70.62954</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026/09/12 18:26:31</t>
+          <t>2026/09/14 06:22:46</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-33.47687, -70.6988516</t>
+          <t>-33.445395, -70.6204733</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-33.47687, -70.69885</t>
+          <t>-33.44539, -70.62047</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>03:06:01</t>
+          <t>12:58:10</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>17.99</v>
+        <v>1.87</v>
       </c>
       <c r="M41" t="n">
-        <v>107</v>
+        <v>28</v>
       </c>
       <c r="N41" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2787,57 +2787,57 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026/09/12 15:43:11</t>
+          <t>2026/09/13 17:27:13</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-32.7563583, -70.7225883</t>
+          <t>-32.87916, -70.6092899</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-32.75636, -70.72259</t>
+          <t>-32.87916, -70.60929</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026/09/12 16:49:07</t>
+          <t>2026/09/13 17:37:38</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-32.75818, -70.70285</t>
+          <t>-32.87915, -70.6092933</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-32.75818, -70.70285</t>
+          <t>-32.87915, -70.60929</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>01:05:56</t>
+          <t>00:10:25</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="N42" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2846,57 +2846,57 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026/09/12 16:02:31</t>
+          <t>2026/09/13 17:38:01</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-33.0945233, -71.35311</t>
+          <t>-32.8792333, -70.6087783</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-33.09452, -71.35311</t>
+          <t>-32.87923, -70.60878</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026/09/12 16:49:24</t>
+          <t>2026/09/14 07:06:02</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-33.08735, -71.3623066</t>
+          <t>-32.8829916, -70.6123416</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-33.08735, -71.36231</t>
+          <t>-32.88299, -70.61234</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>00:46:53</t>
+          <t>13:28:01</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M43" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N43" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2905,44 +2905,44 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026/09/12 16:49:19</t>
+          <t>2026/09/13 18:32:25</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-32.758195, -70.7029133</t>
+          <t>-33.0872833, -71.3622833</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-32.75820, -70.70291</t>
+          <t>-33.08728, -71.36228</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026/09/12 17:22:39</t>
+          <t>2026/09/14 06:37:38</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-32.7908766, -70.630895</t>
+          <t>-33.0873216, -71.3622833</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-32.79088, -70.63089</t>
+          <t>-33.08732, -71.36228</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>00:33:20</t>
+          <t>12:05:13</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>9.699999999999999</v>
+        <v>14.02</v>
       </c>
       <c r="M44" t="n">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="N44" t="n">
         <v>27</v>
@@ -2951,11 +2951,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2964,57 +2964,57 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026/09/12 16:50:39</t>
+          <t>2026/09/13 18:48:44</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-33.0873299, -71.3623866</t>
+          <t>-32.7431016, -70.729765</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-33.08733, -71.36239</t>
+          <t>-32.74310, -70.72977</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026/09/13 09:13:18</t>
+          <t>2026/09/14 07:39:59</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-33.087335, -71.362245</t>
+          <t>-33.3672566, -70.6966966</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-33.08734, -71.36225</t>
+          <t>-33.36726, -70.69670</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>16:22:39</t>
+          <t>12:51:15</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0.04</v>
+        <v>79.02</v>
       </c>
       <c r="M45" t="n">
-        <v>8</v>
+        <v>123</v>
       </c>
       <c r="N45" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3023,57 +3023,57 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026/09/12 17:08:46</t>
+          <t>2026/09/14 08:24:48</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-32.7482366, -70.7281266</t>
+          <t>-33.3599933, -70.8071616</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-32.74824, -70.72813</t>
+          <t>-33.35999, -70.80716</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026/09/12 23:06:09</t>
+          <t>2026/09/14 09:19:05</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-32.8793466, -70.6089133</t>
+          <t>-33.359835, -70.8077249</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-32.87935, -70.60891</t>
+          <t>-33.35983, -70.80772</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>05:57:23</t>
+          <t>00:54:17</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>25.95</v>
+        <v>0.13</v>
       </c>
       <c r="M46" t="n">
-        <v>95</v>
+        <v>7</v>
       </c>
       <c r="N46" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3082,57 +3082,57 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026/09/12 17:23:54</t>
+          <t>2026/09/14 09:15:37</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-32.7910916, -70.6309966</t>
+          <t>-33.359979, -70.807019</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-32.79109, -70.63100</t>
+          <t>-33.35998, -70.80702</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026/09/12 21:38:35</t>
+          <t>2026/09/14 09:39:49</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-32.7976916, -70.8873583</t>
+          <t>-33.359046, -70.808866</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-32.79769, -70.88736</t>
+          <t>-33.35905, -70.80887</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>04:14:41</t>
+          <t>00:24:12</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>34.21</v>
+        <v>0.33</v>
       </c>
       <c r="M47" t="n">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="N47" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3141,57 +3141,57 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026/09/12 18:27:46</t>
+          <t>2026/09/14 09:20:20</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-33.476225, -70.6984066</t>
+          <t>-33.3595949, -70.8077433</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-33.47622, -70.69841</t>
+          <t>-33.35959, -70.80774</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026/09/13 11:50:02</t>
+          <t>2026/09/14 09:32:17</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-33.517245, -70.7148749</t>
+          <t>-33.3599183, -70.80715</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-33.51725, -70.71487</t>
+          <t>-33.35992, -70.80715</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>17:22:16</t>
+          <t>00:11:57</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>6.64</v>
+        <v>0.2</v>
       </c>
       <c r="M48" t="n">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="N48" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3200,57 +3200,57 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026/09/12 21:39:50</t>
+          <t>2026/09/14 09:32:23</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-32.7976249, -70.8871033</t>
+          <t>-33.3599, -70.8071099</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-32.79762, -70.88710</t>
+          <t>-33.35990, -70.80711</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026/09/13 09:58:37</t>
+          <t>2026/09/14 10:00:35</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-32.79572, -70.8201616</t>
+          <t>-33.4821399, -70.7653766</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>-32.79572, -70.82016</t>
+          <t>-33.48214, -70.76538</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>12:18:47</t>
+          <t>00:28:12</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>9.57</v>
+        <v>19.22</v>
       </c>
       <c r="M49" t="n">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="N49" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3259,175 +3259,175 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026/09/12 23:06:35</t>
+          <t>2026/09/14 09:40:19</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-32.87918, -70.6088116</t>
+          <t>-33.359059, -70.808908</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-32.87918, -70.60881</t>
+          <t>-33.35906, -70.80891</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026/09/13 11:56:40</t>
+          <t>2026/09/14 09:45:34</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-32.8792, -70.6088916</t>
+          <t>-33.359118, -70.808881</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>-32.87920, -70.60889</t>
+          <t>-33.35912, -70.80888</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>12:50:05</t>
+          <t>00:05:15</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.92</v>
+        <v>0.02</v>
       </c>
       <c r="M50" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="N50" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C51" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026/09/14 09:46:19</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-33.359147, -70.808861</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-33.35915, -70.80886</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2026/09/14 09:59:57</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>-33.359251, -70.808957</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>-33.35925, -70.80896</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>00:13:38</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M51" t="n">
         <v>2</v>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>2026/09/13 07:01:25</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>-33.36056, -70.25361</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>-33.36056, -70.25361</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>2026/09/13 07:25:20</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>-33.35739, -70.252945</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>-33.35739, -70.25294</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>00:23:55</t>
-        </is>
-      </c>
-      <c r="L51" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="M51" t="n">
-        <v>14</v>
-      </c>
       <c r="N51" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026/09/13 07:26:35</t>
+          <t>2026/09/14 10:00:14</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-33.3573883, -70.2529416</t>
+          <t>-33.359242, -70.808944</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-33.35739, -70.25294</t>
+          <t>-33.35924, -70.80894</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026/09/13 16:52:38</t>
+          <t>2026/09/14 10:13:49</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-33.368945, -70.5006416</t>
+          <t>-33.359262, -70.808948</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>-33.36894, -70.50064</t>
+          <t>-33.35926, -70.80895</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>09:26:03</t>
+          <t>00:13:35</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>40.77</v>
+        <v>0.01</v>
       </c>
       <c r="M52" t="n">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="N52" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3436,53 +3436,53 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026/09/13 16:35:17</t>
+          <t>2026/09/14 10:01:50</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-33.087325, -71.3623383</t>
+          <t>-33.48218, -70.7648666</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-33.08732, -71.36234</t>
+          <t>-33.48218, -70.76487</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026/09/13 18:32:21</t>
+          <t>2026/09/14 11:18:55</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-33.0873033, -71.3622983</t>
+          <t>-34.19005, -70.7093683</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>-33.08730, -71.36230</t>
+          <t>-34.19005, -70.70937</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>01:57:04</t>
+          <t>01:17:05</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0.02</v>
+        <v>86.11</v>
       </c>
       <c r="M53" t="n">
-        <v>6</v>
+        <v>120</v>
       </c>
       <c r="N53" t="n">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -3495,53 +3495,53 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026/09/13 16:53:09</t>
+          <t>2026/09/14 10:04:13</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-33.3687733, -70.5006933</t>
+          <t>-33.5502066, -70.8422299</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-33.36877, -70.50069</t>
+          <t>-33.55021, -70.84223</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026/09/13 17:23:33</t>
+          <t>2026/09/14 12:03:30</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>-33.436265, -70.6296016</t>
+          <t>-33.548995, -70.83941</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>-33.43626, -70.62960</t>
+          <t>-33.54899, -70.83941</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>00:30:24</t>
+          <t>01:59:17</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>18.08</v>
+        <v>0.29</v>
       </c>
       <c r="M54" t="n">
-        <v>121</v>
+        <v>26</v>
       </c>
       <c r="N54" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -3549,58 +3549,58 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026/09/13 17:24:36</t>
+          <t>2026/09/14 10:13:50</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-33.4365983, -70.6295433</t>
+          <t>-33.359263, -70.808938</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-33.43660, -70.62954</t>
+          <t>-33.35926, -70.80894</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026/09/14 06:22:46</t>
+          <t>2026/09/14 10:45:28</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-33.445395, -70.6204733</t>
+          <t>-33.358778, -70.809257</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>-33.44539, -70.62047</t>
+          <t>-33.35878, -70.80926</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>12:58:10</t>
+          <t>00:31:38</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.87</v>
+        <v>0.1</v>
       </c>
       <c r="M55" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="N55" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -3608,62 +3608,62 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026/09/13 18:32:25</t>
+          <t>2026/09/14 10:45:43</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-33.0872833, -71.3622833</t>
+          <t>-33.358818, -70.809306</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-33.08728, -71.36228</t>
+          <t>-33.35882, -70.80931</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026/09/14 06:37:38</t>
+          <t>2026/09/14 11:03:16</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>-33.0873216, -71.3622833</t>
+          <t>-33.3595, -70.809294</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>-33.08732, -71.36228</t>
+          <t>-33.35950, -70.80929</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>12:05:13</t>
+          <t>00:17:33</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>14.02</v>
+        <v>0.09</v>
       </c>
       <c r="M56" t="n">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="N56" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -3672,57 +3672,57 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026/09/14 08:00:11</t>
+          <t>2026/09/14 10:50:54</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-33.36732, -70.69606</t>
+          <t>-33.5496883, -70.8414916</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-33.36732, -70.69606</t>
+          <t>-33.54969, -70.84149</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026/09/14 08:24:41</t>
+          <t>2026/09/14 11:37:22</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>-33.35995, -70.80715</t>
+          <t>-33.5489766, -70.8403816</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-33.35995, -70.80715</t>
+          <t>-33.54898, -70.84038</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>00:24:30</t>
+          <t>00:46:28</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>14.72</v>
+        <v>0.13</v>
       </c>
       <c r="M57" t="n">
-        <v>109</v>
+        <v>11</v>
       </c>
       <c r="N57" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -3731,57 +3731,57 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026/09/14 08:24:48</t>
+          <t>2026/09/14 11:03:51</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-33.3599933, -70.8071616</t>
+          <t>-33.359668, -70.809279</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80716</t>
+          <t>-33.35967, -70.80928</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026/09/14 09:19:05</t>
+          <t>2026/09/14 11:20:24</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>-33.359835, -70.8077249</t>
+          <t>-33.359963, -70.809211</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>-33.35983, -70.80772</t>
+          <t>-33.35996, -70.80921</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>00:54:17</t>
+          <t>00:16:33</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="M58" t="n">
         <v>7</v>
       </c>
       <c r="N58" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3790,116 +3790,116 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026/09/14 09:15:37</t>
+          <t>2026/09/14 11:19:44</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-33.359979, -70.807019</t>
+          <t>-34.190025, -70.7091799</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-33.35998, -70.80702</t>
+          <t>-34.19002, -70.70918</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026/09/14 09:39:49</t>
+          <t>2026/09/14 12:11:45</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>-33.359046, -70.808866</t>
+          <t>-34.2042816, -70.6791433</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>-33.35905, -70.80887</t>
+          <t>-34.20428, -70.67914</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>00:24:12</t>
+          <t>00:52:01</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0.33</v>
+        <v>3.56</v>
       </c>
       <c r="M59" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="N59" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C60" t="n">
+        <v>8</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026/09/14 11:21:21</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>-33.359963, -70.809207</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-33.35996, -70.80921</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2026/09/14 11:50:36</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>-33.360141, -70.809355</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>-33.36014, -70.80935</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>00:29:15</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M60" t="n">
         <v>4</v>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>2026/09/14 09:20:20</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>-33.3595949, -70.8077433</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>-33.35959, -70.80774</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>2026/09/14 09:32:17</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>-33.3599183, -70.80715</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>-33.35992, -70.80715</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>00:11:57</t>
-        </is>
-      </c>
-      <c r="L60" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M60" t="n">
-        <v>13</v>
-      </c>
       <c r="N60" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3908,57 +3908,57 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026/09/14 09:32:23</t>
+          <t>2026/09/14 11:38:27</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-33.3599, -70.8071099</t>
+          <t>-33.5491766, -70.8384849</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-33.35990, -70.80711</t>
+          <t>-33.54918, -70.83848</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026/09/14 10:00:35</t>
+          <t>2026/09/14 11:46:27</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>-33.4821399, -70.7653766</t>
+          <t>-33.5494416, -70.8411483</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>-33.48214, -70.76538</t>
+          <t>-33.54944, -70.84115</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>00:28:12</t>
+          <t>00:08:00</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>19.22</v>
+        <v>0.25</v>
       </c>
       <c r="M61" t="n">
-        <v>102</v>
+        <v>11</v>
       </c>
       <c r="N61" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3967,47 +3967,47 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026/09/14 09:40:19</t>
+          <t>2026/09/14 11:46:56</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>-33.359059, -70.808908</t>
+          <t>-33.5497716, -70.8415533</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-33.35906, -70.80891</t>
+          <t>-33.54977, -70.84155</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026/09/14 09:45:34</t>
+          <t>2026/09/14 13:00:07</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>-33.359118, -70.808881</t>
+          <t>-33.5521966, -70.8414633</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>-33.35912, -70.80888</t>
+          <t>-33.55220, -70.84146</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>00:05:15</t>
+          <t>01:13:11</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0.02</v>
+        <v>0.89</v>
       </c>
       <c r="M62" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="N62" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63">
@@ -4017,115 +4017,115 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026/09/14 09:46:19</t>
+          <t>2026/09/14 11:50:45</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-33.359147, -70.808861</t>
+          <t>-33.360136, -70.809362</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-33.35915, -70.80886</t>
+          <t>-33.36014, -70.80936</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026/09/14 09:59:57</t>
+          <t>2026/09/14 13:23:27</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>-33.359251, -70.808957</t>
+          <t>-33.360305, -70.809096</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>-33.35925, -70.80896</t>
+          <t>-33.36030, -70.80910</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>00:13:38</t>
+          <t>01:32:42</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="M63" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N63" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026/09/14 10:00:14</t>
+          <t>2026/09/14 12:04:45</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-33.359242, -70.808944</t>
+          <t>-33.549175, -70.8384433</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-33.35924, -70.80894</t>
+          <t>-33.54917, -70.83844</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026/09/14 10:13:49</t>
+          <t>2026/09/14 12:20:46</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>-33.359262, -70.808948</t>
+          <t>-33.5495016, -70.8413883</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>-33.35926, -70.80895</t>
+          <t>-33.54950, -70.84139</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>00:13:35</t>
+          <t>00:16:01</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0.01</v>
+        <v>0.32</v>
       </c>
       <c r="M64" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="N64" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65">
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4144,171 +4144,171 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026/09/14 10:01:50</t>
+          <t>2026/09/14 12:12:21</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-33.48218, -70.7648666</t>
+          <t>-34.2042916, -70.6790833</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-33.48218, -70.76487</t>
+          <t>-34.20429, -70.67908</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026/09/14 11:18:55</t>
+          <t>2026/09/14 16:47:22</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>-34.19005, -70.7093683</t>
+          <t>-34.205585, -70.6775883</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>-34.19005, -70.70937</t>
+          <t>-34.20558, -70.67759</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>01:17:05</t>
+          <t>04:35:01</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>86.11</v>
+        <v>0.22</v>
       </c>
       <c r="M65" t="n">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="N65" t="n">
-        <v>69</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026/09/14 10:13:50</t>
+          <t>2026/09/14 12:22:01</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>-33.359263, -70.808938</t>
+          <t>-33.5498933, -70.841675</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-33.35926, -70.80894</t>
+          <t>-33.54989, -70.84167</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026/09/14 10:45:28</t>
+          <t>2026/09/14 13:05:57</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>-33.358778, -70.809257</t>
+          <t>-33.47624, -70.6983116</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>-33.35878, -70.80926</t>
+          <t>-33.47624, -70.69831</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>00:31:38</t>
+          <t>00:43:56</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0.1</v>
+        <v>22.74</v>
       </c>
       <c r="M66" t="n">
-        <v>3</v>
+        <v>121</v>
       </c>
       <c r="N66" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026/09/14 10:45:43</t>
+          <t>2026/09/14 13:01:22</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>-33.358818, -70.809306</t>
+          <t>-33.55268, -70.8369083</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-33.35882, -70.80931</t>
+          <t>-33.55268, -70.83691</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026/09/14 11:03:16</t>
+          <t>2026/09/14 14:43:10</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>-33.3595, -70.809294</t>
+          <t>-32.8792016, -70.6088399</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>-33.35950, -70.80929</t>
+          <t>-32.87920, -70.60884</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>00:17:33</t>
+          <t>01:41:48</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0.09</v>
+        <v>98.89</v>
       </c>
       <c r="M67" t="n">
-        <v>4</v>
+        <v>126</v>
       </c>
       <c r="N67" t="n">
-        <v>4</v>
+        <v>74</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -4321,112 +4321,112 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026/09/14 11:03:51</t>
+          <t>2026/09/14 13:06:06</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>-33.359668, -70.809279</t>
+          <t>-33.4763, -70.698355</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-33.35967, -70.80928</t>
+          <t>-33.47630, -70.69836</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026/09/14 11:20:24</t>
+          <t>2026/09/14 14:13:50</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>-33.359963, -70.809211</t>
+          <t>-33.4770916, -70.6980166</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>-33.35996, -70.80921</t>
+          <t>-33.47709, -70.69802</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>00:16:33</t>
+          <t>01:07:44</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0.06</v>
+        <v>0.17</v>
       </c>
       <c r="M68" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="N68" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C69" t="n">
+        <v>10</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026/09/14 13:24:09</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>-33.360305, -70.809106</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-33.36030, -70.80911</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2026/09/14 13:44:12</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>-33.360371, -70.809155</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>-33.36037, -70.80916</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>00:20:03</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M69" t="n">
         <v>7</v>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>2026/09/14 11:19:44</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>-34.190025, -70.7091799</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>-34.19002, -70.70918</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>2026/09/14 12:11:45</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>-34.2042816, -70.6791433</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>-34.20428, -70.67914</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>00:52:01</t>
-        </is>
-      </c>
-      <c r="L69" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="M69" t="n">
-        <v>26</v>
-      </c>
       <c r="N69" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -4434,58 +4434,58 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026/09/14 11:21:21</t>
+          <t>2026/09/14 13:34:10</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>-33.359963, -70.809207</t>
+          <t>-34.2043016, -70.6790783</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-33.35996, -70.80921</t>
+          <t>-34.20430, -70.67908</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026/09/14 11:50:36</t>
+          <t>2026/09/14 13:40:52</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>-33.360141, -70.809355</t>
+          <t>-34.2040266, -70.67722</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>-33.36014, -70.80935</t>
+          <t>-34.20403, -70.67722</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>00:29:15</t>
+          <t>00:06:42</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0.04</v>
+        <v>0.25</v>
       </c>
       <c r="M70" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="N70" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -4498,57 +4498,57 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026/09/14 11:50:45</t>
+          <t>2026/09/14 13:41:08</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>-33.360136, -70.809362</t>
+          <t>-34.2042383, -70.6771999</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-33.36014, -70.80936</t>
+          <t>-34.20424, -70.67720</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026/09/14 13:23:27</t>
+          <t>2026/09/14 14:36:33</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>-33.360305, -70.809096</t>
+          <t>-34.204215, -70.6772283</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>-33.36030, -70.80910</t>
+          <t>-34.20421, -70.67723</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>01:32:42</t>
+          <t>00:55:25</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N71" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4557,57 +4557,57 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026/09/14 12:12:21</t>
+          <t>2026/09/14 13:45:13</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>-34.2042916, -70.6790833</t>
+          <t>-33.36037, -70.809184</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-34.20429, -70.67908</t>
+          <t>-33.36037, -70.80918</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026/09/14 16:47:22</t>
+          <t>2026/09/14 14:16:43</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>-34.205585, -70.6775883</t>
+          <t>-33.360378, -70.809173</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>-34.20558, -70.67759</t>
+          <t>-33.36038, -70.80917</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>04:35:01</t>
+          <t>00:31:30</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0.22</v>
+        <v>0.04</v>
       </c>
       <c r="M72" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N72" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -4616,47 +4616,47 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026/09/14 13:07:01</t>
+          <t>2026/09/14 14:14:04</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>-34.20428, -70.6772116</t>
+          <t>-33.4772483, -70.69788</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-34.20428, -70.67721</t>
+          <t>-33.47725, -70.69788</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026/09/14 13:33:58</t>
+          <t>2026/09/14 14:22:33</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>-34.204285, -70.6791416</t>
+          <t>-33.476235, -70.6982633</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>-34.20428, -70.67914</t>
+          <t>-33.47624, -70.69826</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>00:26:57</t>
+          <t>00:08:29</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="M73" t="n">
+        <v>18</v>
+      </c>
+      <c r="N73" t="n">
         <v>11</v>
-      </c>
-      <c r="N73" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="74">
@@ -4666,7 +4666,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -4675,44 +4675,44 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026/09/14 13:24:09</t>
+          <t>2026/09/14 14:17:12</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>-33.360305, -70.809106</t>
+          <t>-33.360402, -70.809186</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-33.36030, -70.80911</t>
+          <t>-33.36040, -70.80919</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026/09/14 13:44:12</t>
+          <t>2026/09/14 14:31:15</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>-33.360371, -70.809155</t>
+          <t>-33.360054, -70.810257</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>-33.36037, -70.80916</t>
+          <t>-33.36005, -70.81026</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>00:20:03</t>
+          <t>00:14:03</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0.03</v>
+        <v>0.15</v>
       </c>
       <c r="M74" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N74" t="n">
         <v>4</v>
@@ -4721,11 +4721,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -4734,116 +4734,116 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026/09/14 13:34:10</t>
+          <t>2026/09/14 14:23:48</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>-34.2043016, -70.6790783</t>
+          <t>-33.47616, -70.6984066</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-34.20430, -70.67908</t>
+          <t>-33.47616, -70.69841</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026/09/14 13:40:52</t>
+          <t>2026/09/14 18:17:52</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>-34.2040266, -70.67722</t>
+          <t>-33.4516699, -70.6921</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>-34.20403, -70.67722</t>
+          <t>-33.45167, -70.69210</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>00:06:42</t>
+          <t>03:54:04</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0.25</v>
+        <v>3.86</v>
       </c>
       <c r="M75" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="N75" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026/09/14 13:41:08</t>
+          <t>2026/09/14 14:31:43</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-34.2042383, -70.6771999</t>
+          <t>-33.360053, -70.81027</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-34.20424, -70.67720</t>
+          <t>-33.36005, -70.81027</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026/09/14 14:36:33</t>
+          <t>2026/09/14 14:47:08</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>-34.204215, -70.6772283</t>
+          <t>-33.360014, -70.810408</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>-34.20421, -70.67723</t>
+          <t>-33.36001, -70.81041</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>00:55:25</t>
+          <t>00:15:25</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="M76" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N76" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -4852,57 +4852,57 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026/09/14 13:45:13</t>
+          <t>2026/09/14 14:36:58</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>-33.36037, -70.809184</t>
+          <t>-34.204085, -70.6772483</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-33.36037, -70.80918</t>
+          <t>-34.20408, -70.67725</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026/09/14 14:16:43</t>
+          <t>2026/09/14 16:16:04</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>-33.360378, -70.809173</t>
+          <t>-34.2053699, -70.6802083</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>-33.36038, -70.80917</t>
+          <t>-34.20537, -70.68021</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>00:31:30</t>
+          <t>01:39:06</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0.04</v>
+        <v>2.14</v>
       </c>
       <c r="M77" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N77" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -4911,47 +4911,47 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026/09/14 14:14:04</t>
+          <t>2026/09/14 14:43:19</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>-33.4772483, -70.69788</t>
+          <t>-32.8792033, -70.6087766</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-33.47725, -70.69788</t>
+          <t>-32.87920, -70.60878</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026/09/14 14:22:33</t>
+          <t>2026/09/14 17:05:42</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>-33.476235, -70.6982633</t>
+          <t>-32.8790866, -70.6093483</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>-33.47624, -70.69826</t>
+          <t>-32.87909, -70.60935</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>00:08:29</t>
+          <t>02:22:23</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0.2</v>
+        <v>0.06</v>
       </c>
       <c r="M78" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="N78" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -4970,41 +4970,41 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026/09/14 14:17:12</t>
+          <t>2026/09/14 14:47:28</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>-33.360402, -70.809186</t>
+          <t>-33.360026, -70.810414</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-33.36040, -70.80919</t>
+          <t>-33.36003, -70.81041</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026/09/14 14:31:15</t>
+          <t>2026/09/14 14:59:03</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>-33.360054, -70.810257</t>
+          <t>-33.360332, -70.810543</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>-33.36005, -70.81026</t>
+          <t>-33.36033, -70.81054</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>00:14:03</t>
+          <t>00:11:35</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="M79" t="n">
         <v>6</v>
@@ -5016,129 +5016,129 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026/09/14 14:23:48</t>
+          <t>2026/09/14 15:00:04</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>-33.47616, -70.6984066</t>
+          <t>-33.36039, -70.810625</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-33.47616, -70.69841</t>
+          <t>-33.36039, -70.81063</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026/09/14 18:17:52</t>
+          <t>2026/09/14 15:15:01</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>-33.4516699, -70.6921</t>
+          <t>-33.36049, -70.81058</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>-33.45167, -70.69210</t>
+          <t>-33.36049, -70.81058</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>03:54:04</t>
+          <t>00:14:57</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>3.86</v>
+        <v>0.03</v>
       </c>
       <c r="M80" t="n">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="N80" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026/09/14 14:31:43</t>
+          <t>2026/09/14 15:07:38</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>-33.360053, -70.81027</t>
+          <t>-32.8831666, -70.6123933</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-33.36005, -70.81027</t>
+          <t>-32.88317, -70.61239</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026/09/14 14:47:08</t>
+          <t>2026/09/14 16:02:46</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>-33.360014, -70.810408</t>
+          <t>-32.7567516, -70.7343816</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>-33.36001, -70.81041</t>
+          <t>-32.75675, -70.73438</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>00:15:25</t>
+          <t>00:55:08</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0.03</v>
+        <v>24.62</v>
       </c>
       <c r="M81" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="N81" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5147,47 +5147,47 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026/09/14 14:36:58</t>
+          <t>2026/09/14 15:15:58</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>-34.204085, -70.6772483</t>
+          <t>-33.36049, -70.810578</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-34.20408, -70.67725</t>
+          <t>-33.36049, -70.81058</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026/09/14 16:16:04</t>
+          <t>2026/09/14 15:31:57</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>-34.2053699, -70.6802083</t>
+          <t>-33.360534, -70.810545</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>-34.20537, -70.68021</t>
+          <t>-33.36053, -70.81055</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>01:39:06</t>
+          <t>00:15:59</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.14</v>
+        <v>0.02</v>
       </c>
       <c r="M82" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="N82" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
@@ -5197,7 +5197,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5206,41 +5206,41 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026/09/14 14:47:28</t>
+          <t>2026/09/14 15:32:33</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>-33.360026, -70.810414</t>
+          <t>-33.360545, -70.810617</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-33.36003, -70.81041</t>
+          <t>-33.36055, -70.81062</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026/09/14 14:59:03</t>
+          <t>2026/09/14 15:48:20</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>-33.360332, -70.810543</t>
+          <t>-33.36093, -70.810673</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>-33.36033, -70.81054</t>
+          <t>-33.36093, -70.81067</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>00:11:35</t>
+          <t>00:15:47</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="M83" t="n">
         <v>6</v>
@@ -5256,7 +5256,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5265,47 +5265,47 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026/09/14 15:00:04</t>
+          <t>2026/09/14 15:48:42</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>-33.36039, -70.810625</t>
+          <t>-33.360935, -70.81067</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-33.36039, -70.81063</t>
+          <t>-33.36093, -70.81067</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026/09/14 15:15:01</t>
+          <t>2026/09/14 16:02:09</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>-33.36049, -70.81058</t>
+          <t>-33.360886, -70.810733</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>-33.36049, -70.81058</t>
+          <t>-33.36089, -70.81073</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>00:14:57</t>
+          <t>00:13:27</t>
         </is>
       </c>
       <c r="L84" t="n">
         <v>0.03</v>
       </c>
       <c r="M84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
@@ -5315,7 +5315,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5324,57 +5324,57 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026/09/14 15:15:58</t>
+          <t>2026/09/14 16:02:12</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>-33.36049, -70.810578</t>
+          <t>-33.360881, -70.810735</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-33.36049, -70.81058</t>
+          <t>-33.36088, -70.81073</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026/09/14 15:31:57</t>
+          <t>2026/09/14 16:26:01</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>-33.360534, -70.810545</t>
+          <t>-33.360059, -70.807151</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>-33.36053, -70.81055</t>
+          <t>-33.36006, -70.80715</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>00:15:59</t>
+          <t>00:23:49</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0.02</v>
+        <v>0.47</v>
       </c>
       <c r="M85" t="n">
         <v>5</v>
       </c>
       <c r="N85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5383,106 +5383,106 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026/09/14 15:32:33</t>
+          <t>2026/09/14 16:04:01</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>-33.360545, -70.810617</t>
+          <t>-32.7585233, -70.7292216</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-33.36055, -70.81062</t>
+          <t>-32.75852, -70.72922</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026/09/14 15:48:20</t>
+          <t>2026/09/14 16:42:10</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>-33.36093, -70.810673</t>
+          <t>-32.7878099, -70.8308433</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>-33.36093, -70.81067</t>
+          <t>-32.78781, -70.83084</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>00:15:47</t>
+          <t>00:38:09</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0.06</v>
+        <v>15.79</v>
       </c>
       <c r="M86" t="n">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="N86" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C87" t="n">
+        <v>11</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026/09/14 16:17:19</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>-34.2053633, -70.6802166</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-34.20536, -70.68022</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2026/09/14 17:15:48</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>-34.1900583, -70.7093216</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>-34.19006, -70.70932</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>00:58:29</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="M87" t="n">
+        <v>31</v>
+      </c>
+      <c r="N87" t="n">
         <v>18</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>2026/09/14 15:48:42</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>-33.360935, -70.81067</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>-33.36093, -70.81067</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>2026/09/14 16:02:09</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>-33.360886, -70.810733</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>-33.36089, -70.81073</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>00:13:27</t>
-        </is>
-      </c>
-      <c r="L87" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="M87" t="n">
-        <v>4</v>
-      </c>
-      <c r="N87" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="88">
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5501,57 +5501,57 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026/09/14 16:02:12</t>
+          <t>2026/09/14 16:27:00</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>-33.360881, -70.810735</t>
+          <t>-33.359993, -70.807059</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-33.36088, -70.81073</t>
+          <t>-33.35999, -70.80706</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026/09/14 16:26:01</t>
+          <t>2026/09/15 06:52:44</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>-33.360059, -70.807151</t>
+          <t>-33.36023, -70.810913</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>-33.36006, -70.80715</t>
+          <t>-33.36023, -70.81091</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>00:23:49</t>
+          <t>14:25:44</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="M88" t="n">
         <v>5</v>
       </c>
       <c r="N88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5560,57 +5560,57 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026/09/14 16:17:19</t>
+          <t>2026/09/14 16:42:38</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>-34.2053633, -70.6802166</t>
+          <t>-32.7856783, -70.8315683</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-34.20536, -70.68022</t>
+          <t>-32.78568, -70.83157</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026/09/14 17:15:48</t>
+          <t>2026/09/14 17:23:00</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>-34.1900583, -70.7093216</t>
+          <t>-32.79774, -70.887445</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>-34.19006, -70.70932</t>
+          <t>-32.79774, -70.88744</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>00:58:29</t>
+          <t>00:40:22</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>3.38</v>
+        <v>15.19</v>
       </c>
       <c r="M89" t="n">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="N89" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5619,53 +5619,53 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026/09/14 16:27:00</t>
+          <t>2026/09/14 16:43:22</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>-33.359993, -70.807059</t>
+          <t>-34.205438, -70.677304</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80706</t>
+          <t>-34.20544, -70.67730</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026/09/15 06:52:44</t>
+          <t>2026/09/15 10:02:31</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>-33.36023, -70.810913</t>
+          <t>-34.205402, -70.677286</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>-33.36023, -70.81091</t>
+          <t>-34.20540, -70.67729</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>14:25:44</t>
+          <t>17:19:09</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0.43</v>
+        <v>0.05</v>
       </c>
       <c r="M90" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="N90" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -5678,57 +5678,57 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026/09/14 16:42:38</t>
+          <t>2026/09/14 16:48:37</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>-32.7856783, -70.8315683</t>
+          <t>-34.20541, -70.6801299</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-32.78568, -70.83157</t>
+          <t>-34.20541, -70.68013</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026/09/14 17:23:00</t>
+          <t>2026/09/14 17:15:28</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>-32.79774, -70.887445</t>
+          <t>-34.1900633, -70.70941</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>-32.79774, -70.88744</t>
+          <t>-34.19006, -70.70941</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>00:40:22</t>
+          <t>00:26:51</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>15.19</v>
+        <v>3.41</v>
       </c>
       <c r="M91" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="N91" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -5737,47 +5737,47 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026/09/14 16:43:22</t>
+          <t>2026/09/14 17:06:10</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>-34.205438, -70.677304</t>
+          <t>-32.8792083, -70.6087883</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-34.20544, -70.67730</t>
+          <t>-32.87921, -70.60879</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026/09/15 10:02:31</t>
+          <t>2026/09/14 17:30:09</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>-34.205402, -70.677286</t>
+          <t>-32.8792216, -70.6088283</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>-34.20540, -70.67729</t>
+          <t>-32.87922, -70.60883</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>17:19:09</t>
+          <t>00:23:59</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0.05</v>
+        <v>1.72</v>
       </c>
       <c r="M92" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="N92" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93">
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -5796,57 +5796,57 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026/09/14 16:48:37</t>
+          <t>2026/09/14 17:15:54</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>-34.20541, -70.6801299</t>
+          <t>-34.1899233, -70.7092266</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-34.20541, -70.68013</t>
+          <t>-34.18992, -70.70923</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026/09/14 17:15:28</t>
+          <t>2026/09/14 18:19:27</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>-34.1900633, -70.70941</t>
+          <t>-34.16789, -70.7330566</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>-34.19006, -70.70941</t>
+          <t>-34.16789, -70.73306</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>00:26:51</t>
+          <t>01:03:33</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.41</v>
+        <v>4.09</v>
       </c>
       <c r="M93" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="N93" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -5855,116 +5855,116 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026/09/14 17:11:36</t>
+          <t>2026/09/14 17:16:28</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>-32.840309, -70.964359</t>
+          <t>-34.190155, -70.7094066</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-32.84031, -70.96436</t>
+          <t>-34.19015, -70.70941</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026/09/14 17:18:20</t>
+          <t>2026/09/14 18:14:58</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>-32.841129, -70.959156</t>
+          <t>-34.1676766, -70.734485</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>-32.84113, -70.95916</t>
+          <t>-34.16768, -70.73449</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>00:06:44</t>
+          <t>00:58:30</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0.49</v>
+        <v>3.92</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C95" t="n">
+        <v>3</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2026/09/14 17:19:01</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>-32.841129, -70.959156</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-32.84113, -70.95916</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2026/09/15 09:53:30</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>-32.840526, -70.964542</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>-32.84053, -70.96454</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>16:34:29</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="M95" t="n">
         <v>10</v>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>2026/09/14 17:15:54</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>-34.1899233, -70.7092266</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>-34.18992, -70.70923</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>2026/09/14 18:19:27</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>-34.16789, -70.7330566</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>-34.16789, -70.73306</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>01:03:33</t>
-        </is>
-      </c>
-      <c r="L95" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="M95" t="n">
-        <v>60</v>
-      </c>
       <c r="N95" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -5973,57 +5973,57 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026/09/14 17:16:28</t>
+          <t>2026/09/14 17:23:23</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>-34.190155, -70.7094066</t>
+          <t>-32.7976266, -70.88709</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-34.19015, -70.70941</t>
+          <t>-32.79763, -70.88709</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026/09/14 18:14:58</t>
+          <t>2026/09/14 18:33:02</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>-34.1676766, -70.734485</t>
+          <t>-32.7977033, -70.8874266</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>-34.16768, -70.73449</t>
+          <t>-32.79770, -70.88743</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>00:58:30</t>
+          <t>01:09:39</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>3.92</v>
+        <v>7.71</v>
       </c>
       <c r="M96" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="N96" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6032,116 +6032,116 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026/09/14 17:19:01</t>
+          <t>2026/09/14 17:30:14</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>-32.841129, -70.959156</t>
+          <t>-32.8792266, -70.6088066</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-32.84113, -70.95916</t>
+          <t>-32.87923, -70.60881</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026/09/15 09:53:30</t>
+          <t>2026/09/14 17:58:23</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>-32.840526, -70.964542</t>
+          <t>-32.83263, -70.5999416</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>-32.84053, -70.96454</t>
+          <t>-32.83263, -70.59994</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>16:34:29</t>
+          <t>00:28:09</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.76</v>
+        <v>8.98</v>
       </c>
       <c r="M97" t="n">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="N97" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C98" t="n">
+        <v>12</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2026/09/14 17:59:05</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>-32.8323616, -70.6008849</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-32.83236, -70.60088</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2026/09/14 18:28:51</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>-32.832405, -70.6010316</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>-32.83241, -70.60103</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>00:29:46</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M98" t="n">
         <v>10</v>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>2026/09/14 17:23:23</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>-32.7976266, -70.88709</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>-32.79763, -70.88709</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>2026/09/14 18:33:02</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>-32.7977033, -70.8874266</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>-32.79770, -70.88743</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>01:09:39</t>
-        </is>
-      </c>
-      <c r="L98" t="n">
-        <v>7.71</v>
-      </c>
-      <c r="M98" t="n">
-        <v>63</v>
-      </c>
       <c r="N98" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6150,57 +6150,57 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026/09/14 17:59:05</t>
+          <t>2026/09/14 18:16:13</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>-32.8323616, -70.6008849</t>
+          <t>-34.1678416, -70.7329633</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-32.83236, -70.60088</t>
+          <t>-34.16784, -70.73296</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026/09/14 18:28:51</t>
+          <t>2026/09/15 07:20:47</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>-32.832405, -70.6010316</t>
+          <t>-34.2053666, -70.6806116</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>-32.83241, -70.60103</t>
+          <t>-34.20537, -70.68061</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>00:29:46</t>
+          <t>13:04:34</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0.01</v>
+        <v>7.33</v>
       </c>
       <c r="M99" t="n">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="N99" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6209,57 +6209,57 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026/09/14 18:16:13</t>
+          <t>2026/09/14 18:19:07</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>-34.1678416, -70.7329633</t>
+          <t>-33.4519016, -70.692385</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-34.16784, -70.73296</t>
+          <t>-33.45190, -70.69239</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026/09/15 07:20:47</t>
+          <t>2026/09/14 19:39:33</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>-34.2053666, -70.6806116</t>
+          <t>-33.4768133, -70.6988516</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>-34.20537, -70.68061</t>
+          <t>-33.47681, -70.69885</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>13:04:34</t>
+          <t>01:20:26</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>7.33</v>
+        <v>8.65</v>
       </c>
       <c r="M100" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N100" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6268,57 +6268,57 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026/09/14 18:19:07</t>
+          <t>2026/09/14 18:19:50</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>-33.4519016, -70.692385</t>
+          <t>-34.1677166, -70.73301</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-33.45190, -70.69239</t>
+          <t>-34.16772, -70.73301</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026/09/14 19:39:33</t>
+          <t>2026/09/15 07:25:56</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>-33.4768133, -70.6988516</t>
+          <t>-34.2042699, -70.6791216</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>-33.47681, -70.69885</t>
+          <t>-34.20427, -70.67912</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>01:20:26</t>
+          <t>13:06:06</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>8.65</v>
+        <v>8.84</v>
       </c>
       <c r="M101" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="N101" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6327,57 +6327,57 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026/09/14 18:19:50</t>
+          <t>2026/09/14 18:30:06</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>-34.1677166, -70.73301</t>
+          <t>-32.8345233, -70.601925</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-34.16772, -70.73301</t>
+          <t>-32.83452, -70.60192</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026/09/15 07:25:56</t>
+          <t>2026/09/14 19:10:12</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>-34.2042699, -70.6791216</t>
+          <t>-32.8794316, -70.6088699</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>-34.20427, -70.67912</t>
+          <t>-32.87943, -70.60887</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>13:06:06</t>
+          <t>00:40:06</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>8.84</v>
+        <v>9.43</v>
       </c>
       <c r="M102" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="N102" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6386,57 +6386,57 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026/09/14 18:30:06</t>
+          <t>2026/09/14 18:34:07</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>-32.8345233, -70.601925</t>
+          <t>-32.7976266, -70.8871433</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-32.83452, -70.60192</t>
+          <t>-32.79763, -70.88714</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026/09/14 19:10:12</t>
+          <t>2026/09/15 07:25:33</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>-32.8794316, -70.6088699</t>
+          <t>-33.3576799, -70.7042766</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>-32.87943, -70.60887</t>
+          <t>-33.35768, -70.70428</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>00:40:06</t>
+          <t>12:51:26</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>9.43</v>
+        <v>90.48</v>
       </c>
       <c r="M103" t="n">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="N103" t="n">
-        <v>21</v>
+        <v>64</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6445,57 +6445,57 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026/09/14 18:34:07</t>
+          <t>2026/09/14 19:11:20</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>-32.7976266, -70.8871433</t>
+          <t>-32.8791966, -70.6087816</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-32.79763, -70.88714</t>
+          <t>-32.87920, -70.60878</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026/09/15 07:25:33</t>
+          <t>2026/09/15 07:02:36</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>-33.3576799, -70.7042766</t>
+          <t>-32.8791783, -70.608865</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>-33.35768, -70.70428</t>
+          <t>-32.87918, -70.60886</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>12:51:26</t>
+          <t>11:51:16</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>90.48</v>
+        <v>10.19</v>
       </c>
       <c r="M104" t="n">
-        <v>116</v>
+        <v>58</v>
       </c>
       <c r="N104" t="n">
-        <v>64</v>
+        <v>25</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6504,57 +6504,57 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026/09/14 19:11:20</t>
+          <t>2026/09/14 19:40:48</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>-32.8791966, -70.6087816</t>
+          <t>-33.4761633, -70.6983933</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-32.87920, -70.60878</t>
+          <t>-33.47616, -70.69839</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026/09/15 07:02:36</t>
+          <t>2026/09/15 07:40:41</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>-32.8791783, -70.608865</t>
+          <t>-33.4762616, -70.6983483</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>-32.87918, -70.60886</t>
+          <t>-33.47626, -70.69835</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>11:51:16</t>
+          <t>11:59:53</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>10.19</v>
+        <v>11.06</v>
       </c>
       <c r="M105" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="N105" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6563,57 +6563,57 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026/09/14 19:40:48</t>
+          <t>2026/09/15 08:25:47</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>-33.4761633, -70.6983933</t>
+          <t>-33.36106, -70.811306</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-33.47616, -70.69839</t>
+          <t>-33.36106, -70.81131</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026/09/15 07:40:41</t>
+          <t>2026/09/15 10:08:00</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>-33.4762616, -70.6983483</t>
+          <t>-33.361512, -70.812445</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>-33.47626, -70.69835</t>
+          <t>-33.36151, -70.81244</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>11:59:53</t>
+          <t>01:42:13</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>11.06</v>
+        <v>0.31</v>
       </c>
       <c r="M106" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="N106" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>LPR20251T02900038-RTN</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6622,53 +6622,53 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026/09/15 08:25:47</t>
+          <t>2026/09/15 11:00:23</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>-33.36106, -70.811306</t>
+          <t>-34.876431, -71.127382</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-33.36106, -70.81131</t>
+          <t>-34.87643, -71.12738</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026/09/15 10:08:00</t>
+          <t>2026/09/19 23:23:09</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>-33.361512, -70.812445</t>
+          <t>-34.876469, -71.127312</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>-33.36151, -70.81244</t>
+          <t>-34.87647, -71.12731</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>01:42:13</t>
+          <t>108:22:46</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="M107" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>LPR20251T02900038-RTN</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -6676,52 +6676,52 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026/09/15 11:00:23</t>
+          <t>2026/09/15 11:00:28</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>-34.876431, -71.127382</t>
+          <t>-34.579551, -70.961433</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-34.87643, -71.12738</t>
+          <t>-34.57955, -70.96143</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026/09/18 23:22:59</t>
+          <t>2026/09/18 01:36:53</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>-34.876469, -71.127312</t>
+          <t>-34.579158, -70.961193</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>-34.87647, -71.12731</t>
+          <t>-34.57916, -70.96119</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>84:22:36</t>
+          <t>62:36:25</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0.28</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -7463,22 +7463,22 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026/09/18 23:24:20</t>
+          <t>2026/09/19 23:05:44</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>-33.36, -70.80706</t>
+          <t>-33.360022, -70.807071</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>-33.36000, -70.80706</t>
+          <t>-33.36002, -70.80707</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>80:07:26</t>
+          <t>103:48:50</t>
         </is>
       </c>
       <c r="L121" t="n">
@@ -8438,11 +8438,11 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8451,57 +8451,57 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026/09/16 13:21:00</t>
+          <t>2026/09/16 01:57:22</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>-33.360032, -70.806896</t>
+          <t>-34.042668, -70.681568</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>-33.36003, -70.80690</t>
+          <t>-34.04267, -70.68157</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026/09/16 13:56:57</t>
+          <t>2026/09/19 00:59:47</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>-33.368802, -70.698116</t>
+          <t>-34.042614, -70.681587</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>-33.36880, -70.69812</t>
+          <t>-34.04261, -70.68159</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>00:35:57</t>
+          <t>71:02:25</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>10.16</v>
+        <v>0.05</v>
       </c>
       <c r="M138" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N138" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8510,47 +8510,47 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026/09/16 13:59:04</t>
+          <t>2026/09/16 09:57:52</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>-33.367261, -70.696725</t>
+          <t>-33.4605666, -70.6524483</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>-33.36726, -70.69673</t>
+          <t>-33.46057, -70.65245</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026/09/16 15:27:39</t>
+          <t>2026/09/16 17:23:39</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>-33.44286, -70.696072</t>
+          <t>-33.463985, -70.651095</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>-33.44286, -70.69607</t>
+          <t>-33.46399, -70.65109</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>01:28:35</t>
+          <t>07:25:47</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>8.41</v>
+        <v>3.27</v>
       </c>
       <c r="M139" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="N139" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="140">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -8569,57 +8569,57 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026/09/16 15:28:13</t>
+          <t>2026/09/16 13:21:00</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>-33.442853, -70.69607</t>
+          <t>-33.360032, -70.806896</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>-33.44285, -70.69607</t>
+          <t>-33.36003, -70.80690</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026/09/17 12:24:19</t>
+          <t>2026/09/16 13:56:57</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>-32.838265, -70.954773</t>
+          <t>-33.368802, -70.698116</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>-32.83826, -70.95477</t>
+          <t>-33.36880, -70.69812</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>20:56:06</t>
+          <t>00:35:57</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>74.41</v>
+        <v>10.16</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8628,57 +8628,57 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026/09/16 15:36:32</t>
+          <t>2026/09/16 13:59:04</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>-33.5135016, -70.7452933</t>
+          <t>-33.367261, -70.696725</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>-33.51350, -70.74529</t>
+          <t>-33.36726, -70.69673</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026/09/16 16:07:52</t>
+          <t>2026/09/16 15:27:39</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>-33.4763066, -70.6983533</t>
+          <t>-33.44286, -70.696072</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>-33.47631, -70.69835</t>
+          <t>-33.44286, -70.69607</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>00:31:20</t>
+          <t>01:28:35</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>8.619999999999999</v>
+        <v>8.41</v>
       </c>
       <c r="M141" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="N141" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -8687,47 +8687,47 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026/09/16 16:08:03</t>
+          <t>2026/09/16 15:28:13</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>-33.4763316, -70.6983966</t>
+          <t>-33.442853, -70.69607</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>-33.47633, -70.69840</t>
+          <t>-33.44285, -70.69607</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026/09/16 17:01:40</t>
+          <t>2026/09/17 12:24:19</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>-33.3622683, -70.6701466</t>
+          <t>-32.838265, -70.954773</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>-33.36227, -70.67015</t>
+          <t>-32.83826, -70.95477</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>00:53:37</t>
+          <t>20:56:06</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>18.7</v>
+        <v>74.41</v>
       </c>
       <c r="M142" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -8737,7 +8737,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -8746,57 +8746,57 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026/09/16 17:02:55</t>
+          <t>2026/09/16 15:36:32</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>-33.362175, -70.6701283</t>
+          <t>-33.5135016, -70.7452933</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>-33.36218, -70.67013</t>
+          <t>-33.51350, -70.74529</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026/09/16 19:43:44</t>
+          <t>2026/09/16 16:07:52</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>-33.47613, -70.6981416</t>
+          <t>-33.4763066, -70.6983533</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>-33.47613, -70.69814</t>
+          <t>-33.47631, -70.69835</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>02:40:49</t>
+          <t>00:31:20</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>23.41</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="M143" t="n">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="N143" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -8805,57 +8805,57 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026/09/16 17:37:07</t>
+          <t>2026/09/16 16:08:03</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>-33.4605383, -70.6524433</t>
+          <t>-33.4763316, -70.6983966</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>-33.46054, -70.65244</t>
+          <t>-33.47633, -70.69840</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026/09/16 19:12:11</t>
+          <t>2026/09/16 17:01:40</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>-33.5140633, -70.6373683</t>
+          <t>-33.3622683, -70.6701466</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>-33.51406, -70.63737</t>
+          <t>-33.36227, -70.67015</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>01:35:04</t>
+          <t>00:53:37</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>7.39</v>
+        <v>18.7</v>
       </c>
       <c r="M144" t="n">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="N144" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -8864,47 +8864,47 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026/09/16 19:13:26</t>
+          <t>2026/09/16 17:02:55</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>-33.5138833, -70.6382266</t>
+          <t>-33.362175, -70.6701283</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>-33.51388, -70.63823</t>
+          <t>-33.36218, -70.67013</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026/09/16 19:35:31</t>
+          <t>2026/09/16 19:43:44</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>-33.5075233, -70.62587</t>
+          <t>-33.47613, -70.6981416</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>-33.50752, -70.62587</t>
+          <t>-33.47613, -70.69814</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>00:22:05</t>
+          <t>02:40:49</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>2.91</v>
+        <v>23.41</v>
       </c>
       <c r="M145" t="n">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="N145" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="146">
@@ -8914,7 +8914,7 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -8923,57 +8923,57 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026/09/16 19:36:46</t>
+          <t>2026/09/16 17:24:32</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>-33.5072899, -70.6273433</t>
+          <t>-33.46409, -70.6517799</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>-33.50729, -70.62734</t>
+          <t>-33.46409, -70.65178</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026/09/16 21:06:17</t>
+          <t>2026/09/16 17:35:52</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>-33.50709, -70.6273566</t>
+          <t>-33.4605966, -70.6524183</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>-33.50709, -70.62736</t>
+          <t>-33.46060, -70.65242</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>01:29:31</t>
+          <t>00:11:20</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="N146" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -8982,47 +8982,47 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026/09/16 19:44:59</t>
+          <t>2026/09/16 17:37:07</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>-33.476185, -70.6983883</t>
+          <t>-33.4605383, -70.6524433</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>-33.47619, -70.69839</t>
+          <t>-33.46054, -70.65244</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026/09/17 09:01:36</t>
+          <t>2026/09/16 19:12:11</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>-33.362145, -70.67013</t>
+          <t>-33.5140633, -70.6373683</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>-33.36214, -70.67013</t>
+          <t>-33.51406, -70.63737</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>13:16:37</t>
+          <t>01:35:04</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>23.54</v>
+        <v>7.39</v>
       </c>
       <c r="M147" t="n">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="N147" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="148">
@@ -9032,7 +9032,7 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9041,47 +9041,47 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026/09/16 21:06:55</t>
+          <t>2026/09/16 19:13:26</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>-33.50715, -70.6273616</t>
+          <t>-33.5138833, -70.6382266</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>-33.50715, -70.62736</t>
+          <t>-33.51388, -70.63823</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026/09/16 22:26:02</t>
+          <t>2026/09/16 19:35:31</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>-33.5290116, -70.7016866</t>
+          <t>-33.5075233, -70.62587</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>-33.52901, -70.70169</t>
+          <t>-33.50752, -70.62587</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>01:19:07</t>
+          <t>00:22:05</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>16.06</v>
+        <v>2.91</v>
       </c>
       <c r="M148" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N148" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="149">
@@ -9091,7 +9091,7 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9100,57 +9100,57 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026/09/16 22:27:17</t>
+          <t>2026/09/16 19:36:46</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>-33.528555, -70.7014516</t>
+          <t>-33.5072899, -70.6273433</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>-33.52855, -70.70145</t>
+          <t>-33.50729, -70.62734</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026/09/16 23:19:53</t>
+          <t>2026/09/16 21:06:17</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>-33.5078883, -70.6289333</t>
+          <t>-33.50709, -70.6273566</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>-33.50789, -70.62893</t>
+          <t>-33.50709, -70.62736</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>00:52:36</t>
+          <t>01:29:31</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>12.13</v>
+        <v>0.1</v>
       </c>
       <c r="M149" t="n">
-        <v>83</v>
+        <v>5</v>
       </c>
       <c r="N149" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9159,47 +9159,47 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026/09/16 23:21:06</t>
+          <t>2026/09/16 19:44:59</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>-33.5079416, -70.6288266</t>
+          <t>-33.476185, -70.6983883</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>-33.50794, -70.62883</t>
+          <t>-33.47619, -70.69839</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026/09/16 23:41:53</t>
+          <t>2026/09/17 09:01:36</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>-33.5140666, -70.6374033</t>
+          <t>-33.362145, -70.67013</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>-33.51407, -70.63740</t>
+          <t>-33.36214, -70.67013</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>00:20:47</t>
+          <t>13:16:37</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>1.51</v>
+        <v>23.54</v>
       </c>
       <c r="M150" t="n">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="N150" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="151">
@@ -9209,7 +9209,7 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9218,283 +9218,283 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026/09/16 23:43:06</t>
+          <t>2026/09/16 21:06:55</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>-33.51385, -70.6382499</t>
+          <t>-33.50715, -70.6273616</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>-33.51385, -70.63825</t>
+          <t>-33.50715, -70.62736</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026/09/17 13:13:21</t>
+          <t>2026/09/16 22:26:02</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>-33.4613033, -70.65244</t>
+          <t>-33.5290116, -70.7016866</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>-33.46130, -70.65244</t>
+          <t>-33.52901, -70.70169</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>13:30:15</t>
+          <t>01:19:07</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>8.06</v>
+        <v>16.06</v>
       </c>
       <c r="M151" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="N151" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026/09/17 12:24:20</t>
+          <t>2026/09/16 22:27:17</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>-32.838265, -70.954773</t>
+          <t>-33.528555, -70.7014516</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>-32.83826, -70.95477</t>
+          <t>-33.52855, -70.70145</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026/09/17 12:29:33</t>
+          <t>2026/09/16 23:19:53</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>-32.838305, -70.954774</t>
+          <t>-33.5078883, -70.6289333</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>-32.83830, -70.95477</t>
+          <t>-33.50789, -70.62893</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>00:05:13</t>
+          <t>00:52:36</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>12.13</v>
       </c>
       <c r="M152" t="n">
-        <v>2</v>
+        <v>83</v>
       </c>
       <c r="N152" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026/09/17 18:23:57</t>
+          <t>2026/09/16 23:21:06</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>-33.4761483, -70.6985083</t>
+          <t>-33.5079416, -70.6288266</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>-33.47615, -70.69851</t>
+          <t>-33.50794, -70.62883</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026/09/18 23:16:39</t>
+          <t>2026/09/16 23:41:53</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>-33.47617, -70.6984399</t>
+          <t>-33.5140666, -70.6374033</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>-33.47617, -70.69844</t>
+          <t>-33.51407, -70.63740</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>28:52:42</t>
+          <t>00:20:47</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0.01</v>
+        <v>1.51</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026/09/17 18:58:34</t>
+          <t>2026/09/16 23:43:06</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>-33.4363449, -70.6293183</t>
+          <t>-33.51385, -70.6382499</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>-33.43634, -70.62932</t>
+          <t>-33.51385, -70.63825</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026/09/18 22:58:34</t>
+          <t>2026/09/17 13:13:21</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>-33.4363449, -70.6293183</t>
+          <t>-33.4613033, -70.65244</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>-33.43634, -70.62932</t>
+          <t>-33.46130, -70.65244</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>28:00:00</t>
+          <t>13:30:15</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>8.06</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026/09/17 19:33:53</t>
+          <t>2026/09/17 12:24:20</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>-32.743135, -70.7296099</t>
+          <t>-32.838265, -70.954773</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>-32.74314, -70.72961</t>
+          <t>-32.83826, -70.95477</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026/09/17 20:07:18</t>
+          <t>2026/09/17 12:29:33</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>-32.743165, -70.7329116</t>
+          <t>-32.838305, -70.954774</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>-32.74316, -70.73291</t>
+          <t>-32.83830, -70.95477</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>00:33:25</t>
+          <t>00:05:13</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="N155" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="156">
@@ -9504,56 +9504,56 @@
         </is>
       </c>
       <c r="C156" t="n">
+        <v>12</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>2026/09/17 19:33:53</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>-32.743135, -70.7296099</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>-32.74314, -70.72961</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>2026/09/17 20:07:18</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>-32.743165, -70.7329116</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>-32.74316, -70.73291</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>00:33:25</t>
+        </is>
+      </c>
+      <c r="L156" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="M156" t="n">
+        <v>26</v>
+      </c>
+      <c r="N156" t="n">
         <v>13</v>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>2026/09/17 20:07:30</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>-32.7432499, -70.7326533</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>-32.74325, -70.73265</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>2026/09/17 20:53:41</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>-32.7431399, -70.7296316</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>-32.74314, -70.72963</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>00:46:11</t>
-        </is>
-      </c>
-      <c r="L156" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="M156" t="n">
-        <v>14</v>
-      </c>
-      <c r="N156" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="157">
@@ -9563,180 +9563,180 @@
         </is>
       </c>
       <c r="C157" t="n">
+        <v>13</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>2026/09/17 20:07:30</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>-32.7432499, -70.7326533</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>-32.74325, -70.73265</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>2026/09/17 20:53:41</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>-32.7431399, -70.7296316</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>-32.74314, -70.72963</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>00:46:11</t>
+        </is>
+      </c>
+      <c r="L157" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M157" t="n">
         <v>14</v>
       </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>2026/09/17 20:54:56</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>-32.7431183, -70.7296483</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>-32.74312, -70.72965</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>2026/09/18 23:06:06</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>-32.7430049, -70.72982</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>-32.74300, -70.72982</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>26:11:10</t>
-        </is>
-      </c>
-      <c r="L157" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="M157" t="n">
-        <v>0</v>
-      </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026/09/18 03:46:18</t>
+          <t>2026/09/17 20:54:56</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>-34.205247, -70.677394</t>
+          <t>-32.7431183, -70.7296483</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>-34.20525, -70.67739</t>
+          <t>-32.74312, -70.72965</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026/09/18 23:46:15</t>
+          <t>2026/09/19 08:12:02</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>-34.205247, -70.677394</t>
+          <t>-32.7430733, -70.7297516</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>-34.20525, -70.67739</t>
+          <t>-32.74307, -70.72975</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>19:59:57</t>
+          <t>35:17:06</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C159" t="n">
+        <v>1</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>2026/09/18 03:46:18</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>-34.205247, -70.677394</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>-34.20525, -70.67739</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>2026/09/19 02:49:09</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>-34.205209, -70.677496</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>-34.20521, -70.67750</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>23:02:51</t>
+        </is>
+      </c>
+      <c r="L159" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M159" t="n">
         <v>2</v>
       </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>2026/09/18 11:25:59</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>-33.5139349, -70.6383516</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>-33.51393, -70.63835</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>2026/09/18 23:25:59</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>-33.5139349, -70.6383516</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>-33.51393, -70.63835</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="L159" t="n">
-        <v>0</v>
-      </c>
-      <c r="M159" t="n">
-        <v>0</v>
-      </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -9749,37 +9749,37 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026/09/18 19:47:53</t>
+          <t>2026/09/18 11:25:59</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>-32.7976083, -70.8870616</t>
+          <t>-33.5139349, -70.6383516</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88706</t>
+          <t>-33.51393, -70.63835</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026/09/18 23:48:02</t>
+          <t>2026/09/19 23:25:59</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>-32.7976083, -70.8870616</t>
+          <t>-33.5139349, -70.6383516</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88706</t>
+          <t>-33.51393, -70.63835</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>04:00:09</t>
+          <t>36:00:00</t>
         </is>
       </c>
       <c r="L160" t="n">
@@ -9795,59 +9795,413 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
+          <t>CHANGAN HUNTER TKCL-70</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>2</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>2026/09/18 21:22:13</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>-32.841563, -70.936737</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>-32.84156, -70.93674</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>2026/09/18 23:32:42</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>-32.841764, -70.936873</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>-32.84176, -70.93687</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>02:10:29</t>
+        </is>
+      </c>
+      <c r="L161" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M161" t="n">
+        <v>4</v>
+      </c>
+      <c r="N161" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>CHANGAN HUNTER TGPS-77</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>1</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>2026/09/19 11:58:11</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>-32.7976033, -70.8870833</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>-32.79760, -70.88708</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>2026/09/19 21:58:11</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>-32.7976033, -70.8870833</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>-32.79760, -70.88708</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="L162" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>JAC X200 SJTJ-50</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>5</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>2026/09/19 18:55:10</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>-32.7432466, -70.7296366</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>-32.74325, -70.72964</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>2026/09/19 23:05:53</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>-32.7430783, -70.7297883</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>-32.74308, -70.72979</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>04:10:43</t>
+        </is>
+      </c>
+      <c r="L163" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
           <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
-      <c r="C161" t="n">
+      <c r="C164" t="n">
+        <v>4</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>2026/09/19 19:33:18</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>-33.0872333, -71.3621783</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>-33.08723, -71.36218</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>2026/09/19 21:33:18</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>-33.0872333, -71.3621783</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>-33.08723, -71.36218</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>02:00:00</t>
+        </is>
+      </c>
+      <c r="L164" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>MITSUBISHI L200 PHZF-89</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
         <v>3</v>
       </c>
-      <c r="D161" t="inlineStr">
+      <c r="D165" t="inlineStr">
         <is>
           <t>Paradas</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>2026/09/18 19:53:11</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>-33.0871666, -71.3621533</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>-33.08717, -71.36215</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>2026/09/18 23:53:11</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>-33.0871666, -71.3621533</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>-33.08717, -71.36215</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>04:00:00</t>
-        </is>
-      </c>
-      <c r="L161" t="n">
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>2026/09/19 20:05:50</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>-33.4359966, -70.628935</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>-33.43600, -70.62893</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>2026/09/19 22:05:50</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>-33.4359966, -70.628935</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>-33.43600, -70.62893</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>02:00:00</t>
+        </is>
+      </c>
+      <c r="L165" t="n">
         <v>0</v>
       </c>
-      <c r="M161" t="n">
+      <c r="M165" t="n">
         <v>0</v>
       </c>
-      <c r="N161" t="n">
+      <c r="N165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>MITSUBISHI L200 LVHX-40</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>3</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>2026/09/19 21:27:10</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>-33.4761283, -70.6984816</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>-33.47613, -70.69848</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>2026/09/19 23:27:10</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>-33.4761283, -70.6984816</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>-33.47613, -70.69848</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>02:00:00</t>
+        </is>
+      </c>
+      <c r="L166" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" t="n">
+        <v>0</v>
+      </c>
+      <c r="N166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>SUZUKI CARRY SKDB-52</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>5</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>2026/09/19 22:11:21</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>-32.7386433, -70.718895</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>-32.73864, -70.71890</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>2026/09/19 22:50:02</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>-32.7386433, -70.718895</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>-32.73864, -70.71890</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>00:38:41</t>
+        </is>
+      </c>
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9899,10 +10253,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1028.09</v>
+        <v>891.41</v>
       </c>
       <c r="C2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -9918,13 +10272,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>478.82</v>
+        <v>470.64</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>18</v>
@@ -9937,10 +10291,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>685.29</v>
+        <v>693.25</v>
       </c>
       <c r="C4" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -9956,10 +10310,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>493.64</v>
+        <v>723.71</v>
       </c>
       <c r="C5" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -9975,16 +10329,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -10013,16 +10367,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -10051,16 +10405,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -10114,7 +10468,7 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -10127,10 +10481,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>820.02</v>
+        <v>709.89</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -10146,10 +10500,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>236.53</v>
+        <v>380.42</v>
       </c>
       <c r="C15" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
@@ -10165,16 +10519,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>115.33</v>
+        <v>93.03</v>
       </c>
       <c r="C16" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17">
@@ -10209,7 +10563,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
         <v>19</v>
@@ -10222,13 +10576,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1000.2</v>
+        <v>979.05</v>
       </c>
       <c r="C19" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>136</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026/09/19 22:42:12</t>
+          <t>2026/09/19 23:42:12</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>166:01:02</t>
+          <t>167:01:02</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026/09/19 22:56:13</t>
+          <t>2026/09/19 23:56:13</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>166:00:05</t>
+          <t>167:00:05</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026/09/19 21:58:11</t>
+          <t>2026/09/19 23:58:11</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="L162" t="n">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026/09/19 21:33:18</t>
+          <t>2026/09/19 23:33:18</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L164" t="n">
@@ -10272,7 +10272,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>470.64</v>
+        <v>472.52</v>
       </c>
       <c r="C3" t="n">
         <v>18</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -1032,7 +1032,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026/09/20 22:40:44</t>
+          <t>2026/09/20 23:40:44</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>165:59:34</t>
+          <t>166:59:34</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026/09/20 22:56:09</t>
+          <t>2026/09/20 23:56:09</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>166:00:01</t>
+          <t>167:00:01</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026/09/20 22:22:38</t>
+          <t>2026/09/20 23:23:15</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>131:22:15</t>
+          <t>132:22:52</t>
         </is>
       </c>
       <c r="L115" t="n">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026/09/20 21:33:18</t>
+          <t>2026/09/20 23:33:18</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>26:00:00</t>
+          <t>28:00:00</t>
         </is>
       </c>
       <c r="L160" t="n">
@@ -10059,7 +10059,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026/09/20 21:30:21</t>
+          <t>2026/09/20 23:30:21</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>02:00:37</t>
+          <t>04:00:37</t>
         </is>
       </c>
       <c r="L165" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/09/21 22:40:44</t>
+          <t>2026/09/21 23:40:44</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>165:58:53</t>
+          <t>166:58:53</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/09/21 22:56:09</t>
+          <t>2026/09/21 23:56:09</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>165:59:56</t>
+          <t>166:59:56</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026/09/21 22:23:31</t>
+          <t>2026/09/21 23:22:38</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>155:23:08</t>
+          <t>156:22:15</t>
         </is>
       </c>
       <c r="L52" t="n">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026/09/21 22:32:56</t>
+          <t>2026/09/21 23:32:29</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>31:00:24</t>
+          <t>31:59:57</t>
         </is>
       </c>
       <c r="L159" t="n">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026/09/21 21:49:51</t>
+          <t>2026/09/21 23:49:51</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>12:00:28</t>
+          <t>14:00:28</t>
         </is>
       </c>
       <c r="L161" t="n">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026/09/21 21:23:01</t>
+          <t>2026/09/21 23:23:01</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L172" t="n">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026/09/21 21:39:42</t>
+          <t>2026/09/21 23:39:42</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L173" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -796,7 +796,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026/09/22 22:56:11</t>
+          <t>2026/09/22 23:56:11</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>166:50:43</t>
+          <t>167:50:43</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026/09/22 21:49:51</t>
+          <t>2026/09/22 23:49:51</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>36:00:28</t>
+          <t>38:00:28</t>
         </is>
       </c>
       <c r="L120" t="n">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026/09/22 22:22:51</t>
+          <t>2026/09/22 23:23:07</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>20:00:24</t>
+          <t>21:00:40</t>
         </is>
       </c>
       <c r="L133" t="n">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026/09/22 21:39:43</t>
+          <t>2026/09/22 23:39:43</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>05:25:27</t>
+          <t>07:25:27</t>
         </is>
       </c>
       <c r="L158" t="n">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026/09/22 22:32:25</t>
+          <t>2026/09/22 23:32:25</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>06:01:37</t>
+          <t>07:01:37</t>
         </is>
       </c>
       <c r="L159" t="n">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026/09/22 21:36:09</t>
+          <t>2026/09/22 23:36:09</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>04:00:00</t>
+          <t>06:00:00</t>
         </is>
       </c>
       <c r="L160" t="n">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026/09/22 21:57:54</t>
+          <t>2026/09/22 23:57:54</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>02:01:09</t>
+          <t>04:01:09</t>
         </is>
       </c>
       <c r="L162" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026/09/23 22:56:11</t>
+          <t>2026/09/23 23:56:11</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>166:48:13</t>
+          <t>167:48:13</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026/09/23 22:22:55</t>
+          <t>2026/09/23 23:22:52</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>44:00:28</t>
+          <t>45:00:25</t>
         </is>
       </c>
       <c r="L109" t="n">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026/09/23 22:57:17</t>
+          <t>2026/09/23 23:57:09</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>32:56:22</t>
+          <t>33:56:14</t>
         </is>
       </c>
       <c r="L128" t="n">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026/09/23 22:51:55</t>
+          <t>2026/09/23 23:51:55</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>11:01:00</t>
+          <t>12:01:00</t>
         </is>
       </c>
       <c r="L143" t="n">
@@ -8997,7 +8997,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026/09/23 22:58:36</t>
+          <t>2026/09/23 23:58:37</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>08:01:13</t>
+          <t>09:01:14</t>
         </is>
       </c>
       <c r="L147" t="n">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026/09/23 21:15:34</t>
+          <t>2026/09/23 23:15:34</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>06:00:20</t>
+          <t>08:00:20</t>
         </is>
       </c>
       <c r="L149" t="n">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026/09/23 21:14:09</t>
+          <t>2026/09/23 23:14:09</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L154" t="n">
@@ -9469,7 +9469,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026/09/23 21:22:13</t>
+          <t>2026/09/23 23:22:13</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>02:00:22</t>
+          <t>04:00:22</t>
         </is>
       </c>
       <c r="L155" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -619,7 +619,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026/09/24 22:57:32</t>
+          <t>2026/09/24 23:57:32</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>166:49:34</t>
+          <t>167:49:34</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026/09/24 22:57:38</t>
+          <t>2026/09/24 23:57:15</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>56:56:43</t>
+          <t>57:56:20</t>
         </is>
       </c>
       <c r="L113" t="n">
@@ -8997,7 +8997,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026/09/24 22:42:20</t>
+          <t>2026/09/24 23:42:20</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>08:24:42</t>
+          <t>09:24:42</t>
         </is>
       </c>
       <c r="L147" t="n">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026/09/24 21:31:32</t>
+          <t>2026/09/24 23:31:32</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9307,7 +9307,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>04:00:00</t>
+          <t>06:00:00</t>
         </is>
       </c>
       <c r="L152" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N154"/>
+  <dimension ref="A1:N169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4780,11 +4780,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -4793,57 +4793,57 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026/09/21 14:54:07</t>
+          <t>2026/09/21 14:51:44</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-33.437215, -70.6287866</t>
+          <t>-34.2042833, -70.6789066</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-33.43722, -70.62879</t>
+          <t>-34.20428, -70.67891</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026/09/21 18:22:22</t>
+          <t>2026/09/21 16:56:47</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>-33.46673, -70.607075</t>
+          <t>-34.1679249, -70.732985</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>-33.46673, -70.60707</t>
+          <t>-34.16792, -70.73298</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>03:28:15</t>
+          <t>02:05:03</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>5.24</v>
+        <v>7.6</v>
       </c>
       <c r="M76" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="N76" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -4852,57 +4852,57 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026/09/21 15:01:35</t>
+          <t>2026/09/21 14:54:07</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>-32.7976116, -70.8870599</t>
+          <t>-33.437215, -70.6287866</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88706</t>
+          <t>-33.43722, -70.62879</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026/09/21 16:31:34</t>
+          <t>2026/09/21 18:22:22</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>-32.7856583, -70.8316066</t>
+          <t>-33.46673, -70.607075</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>-32.78566, -70.83161</t>
+          <t>-33.46673, -70.60707</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>01:29:59</t>
+          <t>03:28:15</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>7.63</v>
+        <v>5.24</v>
       </c>
       <c r="M77" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="N77" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -4911,47 +4911,47 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026/09/21 15:01:41</t>
+          <t>2026/09/21 15:01:35</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>-32.8832016, -70.610845</t>
+          <t>-32.7976116, -70.8870599</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-32.88320, -70.61084</t>
+          <t>-32.79761, -70.88706</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026/09/21 15:24:58</t>
+          <t>2026/09/21 16:31:34</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>-32.8792133, -70.6088483</t>
+          <t>-32.7856583, -70.8316066</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>-32.87921, -70.60885</t>
+          <t>-32.78566, -70.83161</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>00:23:17</t>
+          <t>01:29:59</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.5</v>
+        <v>7.63</v>
       </c>
       <c r="M78" t="n">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="N78" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -4970,47 +4970,47 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026/09/21 15:25:03</t>
+          <t>2026/09/21 15:01:41</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>-32.8792333, -70.6088083</t>
+          <t>-32.8832016, -70.610845</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-32.87923, -70.60881</t>
+          <t>-32.88320, -70.61084</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026/09/21 15:53:13</t>
+          <t>2026/09/21 15:24:58</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>-32.8520599, -70.6068466</t>
+          <t>-32.8792133, -70.6088483</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>-32.85206, -70.60685</t>
+          <t>-32.87921, -70.60885</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>00:28:10</t>
+          <t>00:23:17</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>4.32</v>
+        <v>1.5</v>
       </c>
       <c r="M79" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="N79" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80">
@@ -5020,7 +5020,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5029,57 +5029,57 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026/09/21 15:53:38</t>
+          <t>2026/09/21 15:25:03</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>-32.8521933, -70.607595</t>
+          <t>-32.8792333, -70.6088083</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-32.85219, -70.60760</t>
+          <t>-32.87923, -70.60881</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026/09/21 16:51:07</t>
+          <t>2026/09/21 15:53:13</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>-32.87923, -70.6088683</t>
+          <t>-32.8520599, -70.6068466</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>-32.87923, -70.60887</t>
+          <t>-32.85206, -70.60685</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>00:57:29</t>
+          <t>00:28:10</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>4.26</v>
+        <v>4.32</v>
       </c>
       <c r="M80" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="N80" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5088,44 +5088,44 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026/09/21 16:30:07</t>
+          <t>2026/09/21 15:53:38</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>-33.409245, -70.6780766</t>
+          <t>-32.8521933, -70.607595</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-33.40924, -70.67808</t>
+          <t>-32.85219, -70.60760</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026/09/21 17:30:41</t>
+          <t>2026/09/21 16:51:07</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>-33.476315, -70.6983616</t>
+          <t>-32.87923, -70.6088683</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>-33.47631, -70.69836</t>
+          <t>-32.87923, -70.60887</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>01:00:34</t>
+          <t>00:57:29</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>12.14</v>
+        <v>4.26</v>
       </c>
       <c r="M81" t="n">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="N81" t="n">
         <v>17</v>
@@ -5134,11 +5134,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5147,47 +5147,47 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026/09/21 16:31:50</t>
+          <t>2026/09/21 16:30:07</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>-32.7856916, -70.83158</t>
+          <t>-33.409245, -70.6780766</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-32.78569, -70.83158</t>
+          <t>-33.40924, -70.67808</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026/09/21 16:47:52</t>
+          <t>2026/09/21 17:30:41</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>-32.797745, -70.8874683</t>
+          <t>-33.476315, -70.6983616</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>-32.79774, -70.88747</t>
+          <t>-33.47631, -70.69836</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>00:16:02</t>
+          <t>01:00:34</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>7.42</v>
+        <v>12.14</v>
       </c>
       <c r="M82" t="n">
         <v>64</v>
       </c>
       <c r="N82" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="83">
@@ -5197,7 +5197,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5206,57 +5206,57 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026/09/21 16:48:26</t>
+          <t>2026/09/21 16:31:50</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>-32.7976116, -70.8870983</t>
+          <t>-32.7856916, -70.83158</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88710</t>
+          <t>-32.78569, -70.83158</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026/09/21 19:11:12</t>
+          <t>2026/09/21 16:47:52</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>-32.7977149, -70.8873983</t>
+          <t>-32.797745, -70.8874683</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>-32.79771, -70.88740</t>
+          <t>-32.79774, -70.88747</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>02:22:46</t>
+          <t>00:16:02</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>7.44</v>
+        <v>7.42</v>
       </c>
       <c r="M83" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="N83" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5265,47 +5265,47 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026/09/21 16:51:11</t>
+          <t>2026/09/21 16:48:26</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>-32.879245, -70.6088383</t>
+          <t>-32.7976116, -70.8870983</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-32.87924, -70.60884</t>
+          <t>-32.79761, -70.88710</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026/09/21 17:21:52</t>
+          <t>2026/09/21 19:11:12</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>-32.8293683, -70.6115916</t>
+          <t>-32.7977149, -70.8873983</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>-32.82937, -70.61159</t>
+          <t>-32.79771, -70.88740</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>00:30:41</t>
+          <t>02:22:46</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>9.720000000000001</v>
+        <v>7.44</v>
       </c>
       <c r="M84" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="N84" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="85">
@@ -5315,7 +5315,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5324,57 +5324,57 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026/09/21 17:22:06</t>
+          <t>2026/09/21 16:51:11</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>-32.8296, -70.6116483</t>
+          <t>-32.879245, -70.6088383</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-32.82960, -70.61165</t>
+          <t>-32.87924, -70.60884</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026/09/21 18:23:53</t>
+          <t>2026/09/21 17:21:52</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>-32.8292716, -70.6114966</t>
+          <t>-32.8293683, -70.6115916</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>-32.82927, -70.61150</t>
+          <t>-32.82937, -70.61159</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>01:01:47</t>
+          <t>00:30:41</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.27</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="M85" t="n">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="N85" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5383,57 +5383,57 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026/09/21 17:30:52</t>
+          <t>2026/09/21 16:58:00</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>-33.4763583, -70.6984033</t>
+          <t>-34.1677383, -70.7330166</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-33.47636, -70.69840</t>
+          <t>-34.16774, -70.73302</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026/09/21 18:37:59</t>
+          <t>2026/09/22 07:32:37</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>-33.4762916, -70.698285</t>
+          <t>-34.2042766, -70.6791333</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>-33.47629, -70.69828</t>
+          <t>-34.20428, -70.67913</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>01:07:07</t>
+          <t>14:34:37</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>11.02</v>
+        <v>7.64</v>
       </c>
       <c r="M86" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="N86" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5442,57 +5442,57 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026/09/21 18:02:18</t>
+          <t>2026/09/21 17:22:06</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>-33.0873416, -71.36233</t>
+          <t>-32.8296, -70.6116483</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-33.08734, -71.36233</t>
+          <t>-32.82960, -70.61165</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026/09/21 19:39:27</t>
+          <t>2026/09/21 18:23:53</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>-33.0872666, -71.36224</t>
+          <t>-32.8292716, -70.6114966</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>-33.08727, -71.36224</t>
+          <t>-32.82927, -70.61150</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>01:37:09</t>
+          <t>01:01:47</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0.01</v>
+        <v>1.27</v>
       </c>
       <c r="M87" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="N87" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5501,57 +5501,57 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026/09/21 18:23:02</t>
+          <t>2026/09/21 17:30:52</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>-33.4667166, -70.6070683</t>
+          <t>-33.4763583, -70.6984033</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-33.46672, -70.60707</t>
+          <t>-33.47636, -70.69840</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026/09/21 20:08:11</t>
+          <t>2026/09/21 18:37:59</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>-33.4362316, -70.6295633</t>
+          <t>-33.4762916, -70.698285</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>-33.43623, -70.62956</t>
+          <t>-33.47629, -70.69828</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>01:45:09</t>
+          <t>01:07:07</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>5.45</v>
+        <v>11.02</v>
       </c>
       <c r="M88" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="N88" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5560,57 +5560,57 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026/09/21 18:24:02</t>
+          <t>2026/09/21 18:02:18</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>-32.8296183, -70.6116416</t>
+          <t>-33.0873416, -71.36233</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-32.82962, -70.61164</t>
+          <t>-33.08734, -71.36233</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026/09/21 19:22:37</t>
+          <t>2026/09/21 19:39:27</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>-32.8792183, -70.608845</t>
+          <t>-33.0872666, -71.36224</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>-32.87922, -70.60885</t>
+          <t>-33.08727, -71.36224</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>00:58:35</t>
+          <t>01:37:09</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>14.21</v>
+        <v>0.01</v>
       </c>
       <c r="M89" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="N89" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5619,57 +5619,57 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026/09/21 18:39:14</t>
+          <t>2026/09/21 18:23:02</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>-33.4761433, -70.6985049</t>
+          <t>-33.4667166, -70.6070683</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-33.47614, -70.69850</t>
+          <t>-33.46672, -70.60707</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026/09/22 07:43:44</t>
+          <t>2026/09/21 20:08:11</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>-33.4762799, -70.6983683</t>
+          <t>-33.4362316, -70.6295633</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>-33.47628, -70.69837</t>
+          <t>-33.43623, -70.62956</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>13:04:30</t>
+          <t>01:45:09</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>11.12</v>
+        <v>5.45</v>
       </c>
       <c r="M90" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="N90" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -5678,57 +5678,57 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026/09/21 19:12:06</t>
+          <t>2026/09/21 18:24:02</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>-32.7976416, -70.8871583</t>
+          <t>-32.8296183, -70.6116416</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-32.79764, -70.88716</t>
+          <t>-32.82962, -70.61164</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026/09/22 06:56:15</t>
+          <t>2026/09/21 19:22:37</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>-33.9264483, -70.7179816</t>
+          <t>-32.8792183, -70.608845</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>-33.92645, -70.71798</t>
+          <t>-32.87922, -70.60885</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>11:44:09</t>
+          <t>00:58:35</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>161.14</v>
+        <v>14.21</v>
       </c>
       <c r="M91" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="N91" t="n">
-        <v>77</v>
+        <v>18</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -5737,116 +5737,116 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026/09/21 19:23:01</t>
+          <t>2026/09/21 18:39:14</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>-32.879235, -70.6087766</t>
+          <t>-33.4761433, -70.6985049</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-32.87924, -70.60878</t>
+          <t>-33.47614, -70.69850</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026/09/22 08:24:51</t>
+          <t>2026/09/22 07:43:44</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>-33.92794, -70.7170816</t>
+          <t>-33.4762799, -70.6983683</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>-33.92794, -70.71708</t>
+          <t>-33.47628, -70.69837</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>13:01:50</t>
+          <t>13:04:30</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>139.2</v>
+        <v>11.12</v>
       </c>
       <c r="M92" t="n">
-        <v>134</v>
+        <v>46</v>
       </c>
       <c r="N92" t="n">
-        <v>82</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026/09/21 19:39:42</t>
+          <t>2026/09/21 19:12:06</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>-33.0871716, -71.3621683</t>
+          <t>-32.7976416, -70.8871583</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-33.08717, -71.36217</t>
+          <t>-32.79764, -70.88716</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026/09/22 07:14:57</t>
+          <t>2026/09/22 06:56:15</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>-33.0871716, -71.3621683</t>
+          <t>-33.9264483, -70.7179816</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>-33.08717, -71.36217</t>
+          <t>-33.92645, -70.71798</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>11:35:15</t>
+          <t>11:44:09</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>161.14</v>
       </c>
       <c r="M93" t="n">
-        <v>3</v>
+        <v>123</v>
       </c>
       <c r="N93" t="n">
-        <v>3</v>
+        <v>77</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -5855,57 +5855,57 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026/09/21 20:09:26</t>
+          <t>2026/09/21 19:23:01</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>-33.43729, -70.6293783</t>
+          <t>-32.879235, -70.6087766</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-33.43729, -70.62938</t>
+          <t>-32.87924, -70.60878</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026/09/22 11:17:27</t>
+          <t>2026/09/22 08:24:51</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>-33.3661816, -70.6954966</t>
+          <t>-33.92794, -70.7170816</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>-33.36618, -70.69550</t>
+          <t>-33.92794, -70.71708</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>15:08:01</t>
+          <t>13:01:50</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>13.32</v>
+        <v>139.2</v>
       </c>
       <c r="M94" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="N94" t="n">
-        <v>48</v>
+        <v>82</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>LPR20251T02900038-RTN</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -5914,57 +5914,57 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026/09/22 02:22:27</t>
+          <t>2026/09/21 19:39:42</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>-34.876437, -71.127341</t>
+          <t>-33.0871716, -71.3621683</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-34.87644, -71.12734</t>
+          <t>-33.08717, -71.36217</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026/09/24 23:23:48</t>
+          <t>2026/09/22 07:14:57</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>-34.876578, -71.127348</t>
+          <t>-33.0871716, -71.3621683</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>-34.87658, -71.12735</t>
+          <t>-33.08717, -71.36217</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>69:01:21</t>
+          <t>11:35:15</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -5973,106 +5973,106 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026/09/22 08:12:26</t>
+          <t>2026/09/21 20:09:26</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>-34.204213, -70.679123</t>
+          <t>-33.43729, -70.6293783</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-34.20421, -70.67912</t>
+          <t>-33.43729, -70.62938</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026/09/22 08:24:22</t>
+          <t>2026/09/22 11:17:27</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>-34.20517, -70.680279</t>
+          <t>-33.3661816, -70.6954966</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>-34.20517, -70.68028</t>
+          <t>-33.36618, -70.69550</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>00:11:56</t>
+          <t>15:08:01</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0.15</v>
+        <v>13.32</v>
       </c>
       <c r="M96" t="n">
-        <v>3</v>
+        <v>129</v>
       </c>
       <c r="N96" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>LPR20251T02900038-RTN</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026/09/22 08:25:22</t>
+          <t>2026/09/22 02:22:27</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>-34.205261, -70.680364</t>
+          <t>-34.876437, -71.127341</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-34.20526, -70.68036</t>
+          <t>-34.87644, -71.12734</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026/09/22 09:36:52</t>
+          <t>2026/09/24 23:23:48</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>-34.206349, -70.673762</t>
+          <t>-34.876578, -71.127348</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>-34.20635, -70.67376</t>
+          <t>-34.87658, -71.12735</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>01:11:30</t>
+          <t>69:01:21</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0.67</v>
+        <v>0.02</v>
       </c>
       <c r="M97" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6091,37 +6091,37 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026/09/22 09:37:18</t>
+          <t>2026/09/22 08:12:26</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>-34.20635, -70.673665</t>
+          <t>-34.204213, -70.679123</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-34.20635, -70.67366</t>
+          <t>-34.20421, -70.67912</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026/09/22 10:03:28</t>
+          <t>2026/09/22 08:24:22</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>-34.206951, -70.675011</t>
+          <t>-34.20517, -70.680279</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>-34.20695, -70.67501</t>
+          <t>-34.20517, -70.68028</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>00:26:10</t>
+          <t>00:11:56</t>
         </is>
       </c>
       <c r="L98" t="n">
@@ -6137,60 +6137,60 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026/09/22 09:42:54</t>
+          <t>2026/09/22 08:25:22</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>-34.0420849, -70.6798033</t>
+          <t>-34.205261, -70.680364</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-34.04208, -70.67980</t>
+          <t>-34.20526, -70.68036</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026/09/22 09:53:34</t>
+          <t>2026/09/22 09:36:52</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>-34.0427966, -70.6797049</t>
+          <t>-34.206349, -70.673762</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>-34.04280, -70.67970</t>
+          <t>-34.20635, -70.67376</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>00:10:40</t>
+          <t>01:11:30</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0.08</v>
+        <v>0.67</v>
       </c>
       <c r="M99" t="n">
         <v>4</v>
       </c>
       <c r="N99" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
@@ -6200,7 +6200,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6209,44 +6209,44 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026/09/22 10:04:18</t>
+          <t>2026/09/22 09:37:18</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>-34.20696, -70.675017</t>
+          <t>-34.20635, -70.673665</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-34.20696, -70.67502</t>
+          <t>-34.20635, -70.67366</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026/09/22 10:22:53</t>
+          <t>2026/09/22 10:03:28</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>-34.208863, -70.678383</t>
+          <t>-34.206951, -70.675011</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>-34.20886, -70.67838</t>
+          <t>-34.20695, -70.67501</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>00:18:35</t>
+          <t>00:26:10</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0.39</v>
+        <v>0.15</v>
       </c>
       <c r="M100" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N100" t="n">
         <v>3</v>
@@ -6255,11 +6255,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6268,44 +6268,44 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026/09/22 10:23:18</t>
+          <t>2026/09/22 09:42:54</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>-34.208862, -70.67839</t>
+          <t>-34.0420849, -70.6798033</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-34.20886, -70.67839</t>
+          <t>-34.04208, -70.67980</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026/09/22 10:29:46</t>
+          <t>2026/09/22 09:53:34</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>-34.208866, -70.67837</t>
+          <t>-34.0427966, -70.6797049</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>-34.20887, -70.67837</t>
+          <t>-34.04280, -70.67970</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>00:06:28</t>
+          <t>00:10:40</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="M101" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N101" t="n">
         <v>4</v>
@@ -6318,53 +6318,53 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026/09/22 10:30:18</t>
+          <t>2026/09/22 10:04:18</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>-34.208867, -70.678371</t>
+          <t>-34.20696, -70.675017</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-34.20887, -70.67837</t>
+          <t>-34.20696, -70.67502</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026/09/22 10:36:36</t>
+          <t>2026/09/22 10:22:53</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>-34.208815, -70.678375</t>
+          <t>-34.208863, -70.678383</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>-34.20882, -70.67838</t>
+          <t>-34.20886, -70.67838</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>00:06:18</t>
+          <t>00:18:35</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0.01</v>
+        <v>0.39</v>
       </c>
       <c r="M102" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N102" t="n">
         <v>3</v>
@@ -6377,56 +6377,56 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026/09/22 10:37:18</t>
+          <t>2026/09/22 10:23:18</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>-34.208824, -70.678362</t>
+          <t>-34.208862, -70.67839</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-34.20882, -70.67836</t>
+          <t>-34.20886, -70.67839</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026/09/22 10:59:41</t>
+          <t>2026/09/22 10:29:46</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>-34.204207, -70.678857</t>
+          <t>-34.208866, -70.67837</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>-34.20421, -70.67886</t>
+          <t>-34.20887, -70.67837</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>00:22:23</t>
+          <t>00:06:28</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0.78</v>
+        <v>0.01</v>
       </c>
       <c r="M103" t="n">
+        <v>5</v>
+      </c>
+      <c r="N103" t="n">
         <v>4</v>
-      </c>
-      <c r="N103" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -6436,53 +6436,53 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026/09/22 10:59:52</t>
+          <t>2026/09/22 10:30:18</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>-34.204187, -70.67891</t>
+          <t>-34.208867, -70.678371</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-34.20419, -70.67891</t>
+          <t>-34.20887, -70.67837</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026/09/22 12:58:54</t>
+          <t>2026/09/22 10:36:36</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>-34.205263, -70.680228</t>
+          <t>-34.208815, -70.678375</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>-34.20526, -70.68023</t>
+          <t>-34.20882, -70.67838</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>01:59:02</t>
+          <t>00:06:18</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0.21</v>
+        <v>0.01</v>
       </c>
       <c r="M104" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N104" t="n">
         <v>3</v>
@@ -6491,54 +6491,54 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026/09/22 11:34:29</t>
+          <t>2026/09/22 10:37:18</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>-34.34645, -71.1253</t>
+          <t>-34.208824, -70.678362</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-34.34645, -71.12530</t>
+          <t>-34.20882, -70.67836</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026/09/22 11:56:25</t>
+          <t>2026/09/22 10:59:41</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>-34.34642, -71.125439</t>
+          <t>-34.204207, -70.678857</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>-34.34642, -71.12544</t>
+          <t>-34.20421, -70.67886</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>00:21:56</t>
+          <t>00:22:23</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0.04</v>
+        <v>0.78</v>
       </c>
       <c r="M105" t="n">
         <v>4</v>
@@ -6550,11 +6550,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6563,41 +6563,41 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026/09/22 11:57:05</t>
+          <t>2026/09/22 10:59:52</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>-34.346398, -71.125448</t>
+          <t>-34.204187, -70.67891</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-34.34640, -71.12545</t>
+          <t>-34.20419, -70.67891</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026/09/22 13:04:46</t>
+          <t>2026/09/22 12:58:54</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>-34.346413, -71.126384</t>
+          <t>-34.205263, -70.680228</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>-34.34641, -71.12638</t>
+          <t>-34.20526, -70.68023</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>01:07:41</t>
+          <t>01:59:02</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0.51</v>
+        <v>0.21</v>
       </c>
       <c r="M106" t="n">
         <v>4</v>
@@ -6609,11 +6609,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6622,44 +6622,44 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026/09/22 12:59:21</t>
+          <t>2026/09/22 11:34:29</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>-34.205292, -70.68013</t>
+          <t>-34.34645, -71.1253</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-34.20529, -70.68013</t>
+          <t>-34.34645, -71.12530</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026/09/22 13:14:03</t>
+          <t>2026/09/22 11:56:25</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>-34.205283, -70.680057</t>
+          <t>-34.34642, -71.125439</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>-34.20528, -70.68006</t>
+          <t>-34.34642, -71.12544</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>00:14:42</t>
+          <t>00:21:56</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="M107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N107" t="n">
         <v>3</v>
@@ -6668,11 +6668,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -6681,47 +6681,47 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026/09/22 13:14:46</t>
+          <t>2026/09/22 11:42:35</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>-34.205275, -70.680078</t>
+          <t>-34.2052, -70.68011</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-34.20528, -70.68008</t>
+          <t>-34.20520, -70.68011</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026/09/22 13:38:55</t>
+          <t>2026/09/22 11:59:52</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>-34.205547, -70.67683</t>
+          <t>-34.1900366, -70.7093033</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>-34.20555, -70.67683</t>
+          <t>-34.19004, -70.70930</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>00:24:09</t>
+          <t>00:17:17</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0.39</v>
+        <v>3.39</v>
       </c>
       <c r="M108" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="N108" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="109">
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -6740,44 +6740,44 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026/09/22 13:14:58</t>
+          <t>2026/09/22 11:57:05</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>-34.347007, -71.126925</t>
+          <t>-34.346398, -71.125448</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-34.34701, -71.12692</t>
+          <t>-34.34640, -71.12545</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026/09/22 13:26:25</t>
+          <t>2026/09/22 13:04:46</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>-34.348226, -71.126971</t>
+          <t>-34.346413, -71.126384</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>-34.34823, -71.12697</t>
+          <t>-34.34641, -71.12638</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>00:11:27</t>
+          <t>01:07:41</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0.14</v>
+        <v>0.51</v>
       </c>
       <c r="M109" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N109" t="n">
         <v>3</v>
@@ -6786,11 +6786,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -6799,57 +6799,57 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026/09/22 13:27:25</t>
+          <t>2026/09/22 12:00:05</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>-34.348284, -71.126962</t>
+          <t>-34.1899583, -70.70929</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-34.34828, -71.12696</t>
+          <t>-34.18996, -70.70929</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026/09/22 13:41:55</t>
+          <t>2026/09/22 12:53:30</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>-34.346289, -71.125643</t>
+          <t>-34.2042999, -70.6791933</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>-34.34629, -71.12564</t>
+          <t>-34.20430, -70.67919</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>00:14:30</t>
+          <t>00:53:25</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0.33</v>
+        <v>3.56</v>
       </c>
       <c r="M110" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="N110" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -6858,103 +6858,103 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026/09/22 13:39:18</t>
+          <t>2026/09/22 12:54:25</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>-34.205565, -70.67666</t>
+          <t>-34.205185, -70.6801283</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-34.20556, -70.67666</t>
+          <t>-34.20519, -70.68013</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026/09/22 14:03:28</t>
+          <t>2026/09/22 13:33:19</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>-34.205287, -70.680091</t>
+          <t>-34.2055783, -70.677475</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>-34.20529, -70.68009</t>
+          <t>-34.20558, -70.67748</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>00:24:10</t>
+          <t>00:38:54</t>
         </is>
       </c>
       <c r="L111" t="n">
         <v>0.37</v>
       </c>
       <c r="M111" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="N111" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026/09/22 13:42:55</t>
+          <t>2026/09/22 12:59:21</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>-34.346547, -71.12528</t>
+          <t>-34.205292, -70.68013</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-34.34655, -71.12528</t>
+          <t>-34.20529, -70.68013</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026/09/22 15:15:30</t>
+          <t>2026/09/22 13:14:03</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>-34.345964, -71.125758</t>
+          <t>-34.205283, -70.680057</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>-34.34596, -71.12576</t>
+          <t>-34.20528, -70.68006</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>01:32:35</t>
+          <t>00:14:42</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0.16</v>
+        <v>0.01</v>
       </c>
       <c r="M112" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N112" t="n">
         <v>3</v>
@@ -6963,113 +6963,113 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026/09/22 14:00:55</t>
+          <t>2026/09/22 13:14:46</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>-34.042682, -70.681748</t>
+          <t>-34.205275, -70.680078</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-34.04268, -70.68175</t>
+          <t>-34.20528, -70.68008</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026/09/24 23:57:15</t>
+          <t>2026/09/22 13:38:55</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>-34.042504, -70.681533</t>
+          <t>-34.205547, -70.67683</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>-34.04250, -70.68153</t>
+          <t>-34.20555, -70.67683</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>57:56:20</t>
+          <t>00:24:09</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0.05</v>
+        <v>0.39</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026/09/22 14:04:18</t>
+          <t>2026/09/22 13:14:58</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>-34.205283, -70.68009</t>
+          <t>-34.347007, -71.126925</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-34.20528, -70.68009</t>
+          <t>-34.34701, -71.12692</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026/09/22 14:21:15</t>
+          <t>2026/09/22 13:26:25</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>-34.205278, -70.680101</t>
+          <t>-34.348226, -71.126971</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>-34.20528, -70.68010</t>
+          <t>-34.34823, -71.12697</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>00:16:57</t>
+          <t>00:11:27</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0.01</v>
+        <v>0.14</v>
       </c>
       <c r="M114" t="n">
         <v>3</v>
@@ -7081,11 +7081,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7094,116 +7094,116 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026/09/22 14:08:54</t>
+          <t>2026/09/22 13:27:25</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>-34.2055366, -70.676625</t>
+          <t>-34.348284, -71.126962</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-34.20554, -70.67663</t>
+          <t>-34.34828, -71.12696</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026/09/22 14:21:21</t>
+          <t>2026/09/22 13:41:55</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>-34.2051366, -70.6775233</t>
+          <t>-34.346289, -71.125643</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>-34.20514, -70.67752</t>
+          <t>-34.34629, -71.12564</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>00:12:27</t>
+          <t>00:14:30</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0.1</v>
+        <v>0.33</v>
       </c>
       <c r="M115" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N115" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026/09/22 14:21:19</t>
+          <t>2026/09/22 13:33:45</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>-34.205284, -70.680111</t>
+          <t>-34.2055266, -70.6765999</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-34.20528, -70.68011</t>
+          <t>-34.20553, -70.67660</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026/09/22 15:42:35</t>
+          <t>2026/09/22 14:07:50</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>-34.205281, -70.680094</t>
+          <t>-34.2053883, -70.6800999</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>-34.20528, -70.68009</t>
+          <t>-34.20539, -70.68010</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>01:21:16</t>
+          <t>00:34:05</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0.02</v>
+        <v>0.84</v>
       </c>
       <c r="M116" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="N116" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7212,57 +7212,57 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026/09/22 14:22:36</t>
+          <t>2026/09/22 13:39:18</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>-34.2043133, -70.6790683</t>
+          <t>-34.205565, -70.67666</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-34.20431, -70.67907</t>
+          <t>-34.20556, -70.67666</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026/09/22 14:43:21</t>
+          <t>2026/09/22 14:03:28</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>-34.2065066, -70.67392</t>
+          <t>-34.205287, -70.680091</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>-34.20651, -70.67392</t>
+          <t>-34.20529, -70.68009</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>00:20:45</t>
+          <t>00:24:10</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0.79</v>
+        <v>0.37</v>
       </c>
       <c r="M117" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="N117" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7271,175 +7271,175 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026/09/22 14:43:51</t>
+          <t>2026/09/22 13:42:55</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>-34.2070549, -70.6749516</t>
+          <t>-34.346547, -71.12528</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>-34.20705, -70.67495</t>
+          <t>-34.34655, -71.12528</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026/09/22 15:15:44</t>
+          <t>2026/09/22 15:15:30</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>-34.2042683, -70.6788383</t>
+          <t>-34.345964, -71.125758</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>-34.20427, -70.67884</t>
+          <t>-34.34596, -71.12576</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>00:31:53</t>
+          <t>01:32:35</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0.61</v>
+        <v>0.16</v>
       </c>
       <c r="M118" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="N118" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026/09/22 15:15:37</t>
+          <t>2026/09/22 14:00:55</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>-34.345967, -71.12576</t>
+          <t>-34.042682, -70.681748</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-34.34597, -71.12576</t>
+          <t>-34.04268, -70.68175</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026/09/23 08:39:27</t>
+          <t>2026/09/24 23:57:15</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>-34.346894, -71.125631</t>
+          <t>-34.042504, -70.681533</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>-34.34689, -71.12563</t>
+          <t>-34.04250, -70.68153</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>17:23:50</t>
+          <t>57:56:20</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0.18</v>
+        <v>0.05</v>
       </c>
       <c r="M119" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026/09/22 15:15:58</t>
+          <t>2026/09/22 14:04:18</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>-34.20431, -70.6790883</t>
+          <t>-34.205283, -70.68009</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>-34.20431, -70.67909</t>
+          <t>-34.20528, -70.68009</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026/09/22 17:13:29</t>
+          <t>2026/09/22 14:21:15</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>-34.1917016, -70.709965</t>
+          <t>-34.205278, -70.680101</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>-34.19170, -70.70996</t>
+          <t>-34.20528, -70.68010</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>01:57:31</t>
+          <t>00:16:57</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>3.34</v>
+        <v>0.01</v>
       </c>
       <c r="M120" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="N120" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7448,57 +7448,57 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026/09/22 15:43:02</t>
+          <t>2026/09/22 14:08:06</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>-34.205312, -70.680106</t>
+          <t>-34.205325, -70.680145</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-34.20531, -70.68011</t>
+          <t>-34.20533, -70.68014</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026/09/22 16:29:48</t>
+          <t>2026/09/22 14:32:19</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>-34.205468, -70.677413</t>
+          <t>-34.2062216, -70.6739366</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>-34.20547, -70.67741</t>
+          <t>-34.20622, -70.67394</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>00:46:46</t>
+          <t>00:24:13</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0.31</v>
+        <v>0.59</v>
       </c>
       <c r="M121" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N121" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7507,116 +7507,116 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026/09/22 16:01:33</t>
+          <t>2026/09/22 14:08:54</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>-32.8831633, -70.6123783</t>
+          <t>-34.2055366, -70.676625</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>-32.88316, -70.61238</t>
+          <t>-34.20554, -70.67663</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026/09/22 16:13:01</t>
+          <t>2026/09/22 14:21:21</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>-32.8823833, -70.6120583</t>
+          <t>-34.2051366, -70.6775233</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>-32.88238, -70.61206</t>
+          <t>-34.20514, -70.67752</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>00:11:28</t>
+          <t>00:12:27</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="M122" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="N122" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026/09/22 16:06:10</t>
+          <t>2026/09/22 14:21:19</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>-33.3622, -70.6701283</t>
+          <t>-34.205284, -70.680111</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-33.36220, -70.67013</t>
+          <t>-34.20528, -70.68011</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026/09/22 16:37:23</t>
+          <t>2026/09/22 15:42:35</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>-33.3532766, -70.6698133</t>
+          <t>-34.205281, -70.680094</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>-33.35328, -70.66981</t>
+          <t>-34.20528, -70.68009</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>00:31:13</t>
+          <t>01:21:16</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.18</v>
+        <v>0.02</v>
       </c>
       <c r="M123" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="N123" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7625,57 +7625,57 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026/09/22 16:14:16</t>
+          <t>2026/09/22 14:22:36</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>-32.8794133, -70.6088816</t>
+          <t>-34.2043133, -70.6790683</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>-32.87941, -70.60888</t>
+          <t>-34.20431, -70.67907</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026/09/23 09:25:13</t>
+          <t>2026/09/22 14:43:21</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>-32.8843333, -70.6130366</t>
+          <t>-34.2065066, -70.67392</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>-32.88433, -70.61304</t>
+          <t>-34.20651, -70.67392</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>17:10:57</t>
+          <t>00:20:45</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="M124" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="N124" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -7684,175 +7684,175 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026/09/22 16:30:48</t>
+          <t>2026/09/22 14:33:34</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>-34.205453, -70.677307</t>
+          <t>-34.2063166, -70.6738783</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>-34.20545, -70.67731</t>
+          <t>-34.20632, -70.67388</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026/09/23 11:13:11</t>
+          <t>2026/09/22 14:39:58</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>-34.204275, -70.67867</t>
+          <t>-34.2065166, -70.673925</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>-34.20428, -70.67867</t>
+          <t>-34.20652, -70.67392</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>18:42:23</t>
+          <t>00:06:24</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0.23</v>
+        <v>0.04</v>
       </c>
       <c r="M125" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N125" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C126" t="n">
+        <v>14</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>2026/09/22 14:41:13</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>-34.2069716, -70.6750733</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>-34.20697, -70.67507</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>2026/09/22 14:57:28</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>-34.2084233, -70.67758</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>-34.20842, -70.67758</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>00:16:15</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M126" t="n">
         <v>11</v>
       </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>2026/09/22 16:37:38</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>-33.353245, -70.6697983</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>-33.35325, -70.66980</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>2026/09/22 16:59:07</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>-33.3623633, -70.6701316</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>-33.36236, -70.67013</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>00:21:29</t>
-        </is>
-      </c>
-      <c r="L126" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="M126" t="n">
-        <v>22</v>
-      </c>
       <c r="N126" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C127" t="n">
+        <v>11</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>2026/09/22 14:43:51</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>-34.2070549, -70.6749516</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>-34.20705, -70.67495</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>2026/09/22 15:15:44</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>-34.2042683, -70.6788383</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>-34.20427, -70.67884</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>00:31:53</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M127" t="n">
         <v>12</v>
       </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>2026/09/22 16:59:32</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>-33.3622083, -70.6701349</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>-33.36221, -70.67013</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>2026/09/22 18:38:41</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>-33.4762516, -70.6983599</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>-33.47625, -70.69836</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>01:39:09</t>
-        </is>
-      </c>
-      <c r="L127" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="M127" t="n">
-        <v>108</v>
-      </c>
       <c r="N127" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -7861,57 +7861,57 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026/09/22 17:14:44</t>
+          <t>2026/09/22 14:58:43</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>-34.191225, -70.70989</t>
+          <t>-34.2088333, -70.6783066</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>-34.19123, -70.70989</t>
+          <t>-34.20883, -70.67831</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026/09/22 17:35:00</t>
+          <t>2026/09/22 15:21:51</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>-34.167885, -70.73306</t>
+          <t>-34.2055383, -70.676695</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>-34.16788, -70.73306</t>
+          <t>-34.20554, -70.67669</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>00:20:16</t>
+          <t>00:23:08</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>4.19</v>
+        <v>0.48</v>
       </c>
       <c r="M128" t="n">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="N128" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -7920,57 +7920,57 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026/09/22 17:36:09</t>
+          <t>2026/09/22 15:15:37</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>-34.1677383, -70.73303</t>
+          <t>-34.345967, -71.12576</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>-34.16774, -70.73303</t>
+          <t>-34.34597, -71.12576</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026/09/23 07:36:14</t>
+          <t>2026/09/23 08:39:27</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>-34.2042699, -70.6791416</t>
+          <t>-34.346894, -71.125631</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>-34.20427, -70.67914</t>
+          <t>-34.34689, -71.12563</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>14:00:05</t>
+          <t>17:23:50</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>7.56</v>
+        <v>0.18</v>
       </c>
       <c r="M129" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="N129" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -7979,57 +7979,57 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026/09/22 18:39:56</t>
+          <t>2026/09/22 15:15:58</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>-33.4761133, -70.6985049</t>
+          <t>-34.20431, -70.6790883</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>-33.47611, -70.69850</t>
+          <t>-34.20431, -70.67909</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026/09/23 08:56:03</t>
+          <t>2026/09/22 17:13:29</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>-33.3623133, -70.6701033</t>
+          <t>-34.1917016, -70.709965</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>-33.36231, -70.67010</t>
+          <t>-34.19170, -70.70996</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>14:16:07</t>
+          <t>01:57:31</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>18.71</v>
+        <v>3.34</v>
       </c>
       <c r="M130" t="n">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="N130" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8038,57 +8038,57 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026/09/23 08:39:46</t>
+          <t>2026/09/22 15:22:55</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>-34.346866, -71.12567</t>
+          <t>-34.2053466, -70.6802216</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>-34.34687, -71.12567</t>
+          <t>-34.20535, -70.68022</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026/09/23 09:51:53</t>
+          <t>2026/09/22 15:35:53</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>-34.347209, -71.12573</t>
+          <t>-34.2053333, -70.6803533</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>-34.34721, -71.12573</t>
+          <t>-34.20533, -70.68035</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>01:12:07</t>
+          <t>00:12:58</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0.33</v>
+        <v>0.58</v>
       </c>
       <c r="M131" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="N131" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8097,47 +8097,47 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026/09/23 11:04:04</t>
+          <t>2026/09/22 15:36:03</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>-33.360175, -70.807263</t>
+          <t>-34.2053316, -70.680195</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>-33.36017, -70.80726</t>
+          <t>-34.20533, -70.68019</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026/09/23 14:22:54</t>
+          <t>2026/09/22 15:49:03</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>-33.360909, -70.804812</t>
+          <t>-34.2034616, -70.6782916</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>-33.36091, -70.80481</t>
+          <t>-34.20346, -70.67829</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>03:18:50</t>
+          <t>00:13:00</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0.24</v>
+        <v>0.29</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133">
@@ -8147,7 +8147,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8156,44 +8156,44 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026/09/23 11:23:52</t>
+          <t>2026/09/22 15:43:02</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>-34.205473, -70.677304</t>
+          <t>-34.205312, -70.680106</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>-34.20547, -70.67730</t>
+          <t>-34.20531, -70.68011</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026/09/23 11:42:51</t>
+          <t>2026/09/22 16:29:48</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>-34.205071, -70.68017</t>
+          <t>-34.205468, -70.677413</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>-34.20507, -70.68017</t>
+          <t>-34.20547, -70.67741</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>00:18:59</t>
+          <t>00:46:46</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0.39</v>
+        <v>0.31</v>
       </c>
       <c r="M133" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N133" t="n">
         <v>3</v>
@@ -8202,188 +8202,188 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026/09/23 11:43:10</t>
+          <t>2026/09/22 15:50:09</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>-34.205153, -70.680117</t>
+          <t>-34.2034566, -70.6784233</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>-34.20515, -70.68012</t>
+          <t>-34.20346, -70.67842</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026/09/23 12:59:00</t>
+          <t>2026/09/22 17:29:03</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>-34.205237, -70.680109</t>
+          <t>-34.1678716, -70.7330333</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>-34.20524, -70.68011</t>
+          <t>-34.16787, -70.73303</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>01:15:50</t>
+          <t>01:38:54</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0.02</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="M134" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="N134" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026/09/23 11:50:55</t>
+          <t>2026/09/22 16:01:33</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>-34.345954, -71.125788</t>
+          <t>-32.8831633, -70.6123783</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>-34.34595, -71.12579</t>
+          <t>-32.88316, -70.61238</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026/09/24 11:13:19</t>
+          <t>2026/09/22 16:13:01</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>-34.346426, -71.125197</t>
+          <t>-32.8823833, -70.6120583</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>-34.34643, -71.12520</t>
+          <t>-32.88238, -70.61206</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>23:22:24</t>
+          <t>00:11:28</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="M135" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="N135" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026/09/23 12:59:11</t>
+          <t>2026/09/22 16:06:10</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>-34.205247, -70.680103</t>
+          <t>-33.3622, -70.6701283</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>-34.20525, -70.68010</t>
+          <t>-33.36220, -70.67013</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026/09/23 13:10:45</t>
+          <t>2026/09/22 16:37:23</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>-34.205284, -70.680106</t>
+          <t>-33.3532766, -70.6698133</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>-34.20528, -70.68011</t>
+          <t>-33.35328, -70.66981</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>00:11:34</t>
+          <t>00:31:13</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0.01</v>
+        <v>1.18</v>
       </c>
       <c r="M136" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N136" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8392,44 +8392,44 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026/09/23 14:16:58</t>
+          <t>2026/09/22 16:14:16</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>-34.2052916, -70.6802883</t>
+          <t>-32.8794133, -70.6088816</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>-34.20529, -70.68029</t>
+          <t>-32.87941, -70.60888</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026/09/23 14:37:23</t>
+          <t>2026/09/23 09:25:13</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>-34.206435, -70.6737383</t>
+          <t>-32.8843333, -70.6130366</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>-34.20643, -70.67374</t>
+          <t>-32.88433, -70.61304</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>00:20:25</t>
+          <t>17:10:57</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="M137" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="N137" t="n">
         <v>12</v>
@@ -8438,11 +8438,11 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8451,57 +8451,57 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026/09/23 14:37:27</t>
+          <t>2026/09/22 16:30:48</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>-34.2064416, -70.6737533</t>
+          <t>-34.205453, -70.677307</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>-34.20644, -70.67375</t>
+          <t>-34.20545, -70.67731</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026/09/23 15:10:37</t>
+          <t>2026/09/23 11:13:11</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>-34.2063866, -70.6737133</t>
+          <t>-34.204275, -70.67867</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>-34.20639, -70.67371</t>
+          <t>-34.20428, -70.67867</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>00:33:10</t>
+          <t>18:42:23</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>1.35</v>
+        <v>0.23</v>
       </c>
       <c r="M138" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="N138" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8510,106 +8510,106 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026/09/23 15:10:42</t>
+          <t>2026/09/22 16:37:38</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>-34.2064283, -70.6737516</t>
+          <t>-33.353245, -70.6697983</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>-34.20643, -70.67375</t>
+          <t>-33.35325, -70.66980</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026/09/23 15:37:17</t>
+          <t>2026/09/22 16:59:07</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>-34.2088683, -70.678425</t>
+          <t>-33.3623633, -70.6701316</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>-34.20887, -70.67843</t>
+          <t>-33.36236, -70.67013</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>00:26:35</t>
+          <t>00:21:29</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0.51</v>
+        <v>2.68</v>
       </c>
       <c r="M139" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="N139" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026/09/23 15:15:14</t>
+          <t>2026/09/22 16:59:32</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>-33.3671916, -70.6958816</t>
+          <t>-33.3622083, -70.6701349</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>-33.36719, -70.69588</t>
+          <t>-33.36221, -70.67013</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026/09/24 23:15:34</t>
+          <t>2026/09/22 18:38:41</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>-33.3671916, -70.6958816</t>
+          <t>-33.4762516, -70.6983599</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>-33.36719, -70.69588</t>
+          <t>-33.47625, -70.69836</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>32:00:20</t>
+          <t>01:39:09</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>21.59</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="141">
@@ -8619,7 +8619,7 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8628,53 +8628,53 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026/09/23 15:38:11</t>
+          <t>2026/09/22 17:14:44</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>-34.2088583, -70.67846</t>
+          <t>-34.191225, -70.70989</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>-34.20886, -70.67846</t>
+          <t>-34.19123, -70.70989</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026/09/23 16:38:40</t>
+          <t>2026/09/22 17:35:00</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>-34.167865, -70.7330533</t>
+          <t>-34.167885, -70.73306</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>-34.16786, -70.73305</t>
+          <t>-34.16788, -70.73306</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>01:00:29</t>
+          <t>00:20:16</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>8.35</v>
+        <v>4.19</v>
       </c>
       <c r="M141" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N141" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -8687,57 +8687,57 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026/09/23 16:39:55</t>
+          <t>2026/09/22 17:30:18</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>-34.1677683, -70.7330216</t>
+          <t>-34.1676883, -70.7329933</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>-34.16777, -70.73302</t>
+          <t>-34.16769, -70.73299</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026/09/24 07:33:51</t>
+          <t>2026/09/23 07:27:58</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>-34.2064066, -70.6737083</t>
+          <t>-34.2052533, -70.6823733</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>-34.20641, -70.67371</t>
+          <t>-34.20525, -70.68237</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>14:53:56</t>
+          <t>13:57:40</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>8.15</v>
+        <v>7.25</v>
       </c>
       <c r="M142" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="N142" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -8746,116 +8746,116 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026/09/23 17:36:46</t>
+          <t>2026/09/22 17:36:09</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>-32.83989, -70.961898</t>
+          <t>-34.1677383, -70.73303</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>-32.83989, -70.96190</t>
+          <t>-34.16774, -70.73303</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026/09/24 11:26:33</t>
+          <t>2026/09/23 07:36:14</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>-33.360146, -70.806869</t>
+          <t>-34.2042699, -70.6791416</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>-33.36015, -70.80687</t>
+          <t>-34.20427, -70.67914</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>17:49:47</t>
+          <t>14:00:05</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>61.8</v>
+        <v>7.56</v>
       </c>
       <c r="M143" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026/09/23 20:13:52</t>
+          <t>2026/09/22 18:39:56</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>-33.4361833, -70.6295283</t>
+          <t>-33.4761133, -70.6985049</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>-33.43618, -70.62953</t>
+          <t>-33.47611, -70.69850</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026/09/24 22:13:52</t>
+          <t>2026/09/23 08:56:03</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>-33.4361833, -70.6295283</t>
+          <t>-33.3623133, -70.6701033</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>-33.43618, -70.62953</t>
+          <t>-33.36231, -70.67010</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>26:00:00</t>
+          <t>14:16:07</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>18.71</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -8864,41 +8864,41 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026/09/24 13:21:48</t>
+          <t>2026/09/23 08:39:46</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>-34.206341, -70.673913</t>
+          <t>-34.346866, -71.12567</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>-34.20634, -70.67391</t>
+          <t>-34.34687, -71.12567</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026/09/24 14:17:13</t>
+          <t>2026/09/23 09:51:53</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>-34.205473, -70.677302</t>
+          <t>-34.347209, -71.12573</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>-34.20547, -70.67730</t>
+          <t>-34.34721, -71.12573</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>00:55:25</t>
+          <t>01:12:07</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="M145" t="n">
         <v>4</v>
@@ -8910,129 +8910,129 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026/09/24 13:27:02</t>
+          <t>2026/09/23 11:04:04</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>-34.346514, -71.125324</t>
+          <t>-33.360175, -70.807263</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>-34.34651, -71.12532</t>
+          <t>-33.36017, -70.80726</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026/09/24 15:14:47</t>
+          <t>2026/09/23 14:22:54</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>-34.346198, -71.125541</t>
+          <t>-33.360909, -70.804812</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>-34.34620, -71.12554</t>
+          <t>-33.36091, -70.80481</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>01:47:45</t>
+          <t>03:18:50</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0.04</v>
+        <v>0.24</v>
       </c>
       <c r="M146" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026/09/24 14:17:38</t>
+          <t>2026/09/23 11:23:52</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>-34.205446, -70.677348</t>
+          <t>-34.205473, -70.677304</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>-34.20545, -70.67735</t>
+          <t>-34.20547, -70.67730</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026/09/24 23:42:20</t>
+          <t>2026/09/23 11:42:51</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>-34.205382, -70.677293</t>
+          <t>-34.205071, -70.68017</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>-34.20538, -70.67729</t>
+          <t>-34.20507, -70.68017</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>09:24:42</t>
+          <t>00:18:59</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0.02</v>
+        <v>0.39</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9041,47 +9041,47 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026/09/24 14:36:58</t>
+          <t>2026/09/23 11:43:10</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>-32.879235, -70.60878</t>
+          <t>-34.205153, -70.680117</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>-32.87924, -70.60878</t>
+          <t>-34.20515, -70.68012</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026/09/24 22:36:58</t>
+          <t>2026/09/23 12:59:00</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>-32.879235, -70.60878</t>
+          <t>-34.205237, -70.680109</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>-32.87924, -70.60878</t>
+          <t>-34.20524, -70.68011</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>01:15:50</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="149">
@@ -9091,7 +9091,7 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9100,47 +9100,47 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026/09/24 15:15:47</t>
+          <t>2026/09/23 11:50:55</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>-34.345945, -71.125747</t>
+          <t>-34.345954, -71.125788</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>-34.34595, -71.12575</t>
+          <t>-34.34595, -71.12579</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026/09/24 23:17:44</t>
+          <t>2026/09/24 11:13:19</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>-34.345997, -71.125783</t>
+          <t>-34.346426, -71.125197</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>-34.34600, -71.12578</t>
+          <t>-34.34643, -71.12520</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>08:01:57</t>
+          <t>23:22:24</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150">
@@ -9150,7 +9150,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9159,37 +9159,37 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026/09/24 15:23:54</t>
+          <t>2026/09/23 12:59:11</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>-34.205297, -70.680202</t>
+          <t>-34.205247, -70.680103</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>-34.20530, -70.68020</t>
+          <t>-34.20525, -70.68010</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026/09/24 15:30:47</t>
+          <t>2026/09/23 13:10:45</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>-34.205297, -70.680211</t>
+          <t>-34.205284, -70.680106</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>-34.20530, -70.68021</t>
+          <t>-34.20528, -70.68011</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>00:06:53</t>
+          <t>00:11:34</t>
         </is>
       </c>
       <c r="L150" t="n">
@@ -9205,11 +9205,11 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9218,47 +9218,47 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026/09/24 15:31:46</t>
+          <t>2026/09/23 14:16:58</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>-34.20527, -70.680189</t>
+          <t>-34.2052916, -70.6802883</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>-34.20527, -70.68019</t>
+          <t>-34.20529, -70.68029</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026/09/24 15:48:25</t>
+          <t>2026/09/23 14:37:23</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>-34.20548, -70.677407</t>
+          <t>-34.206435, -70.6737383</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>-34.20548, -70.67741</t>
+          <t>-34.20643, -70.67374</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>00:16:39</t>
+          <t>00:20:25</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0.34</v>
+        <v>0.7</v>
       </c>
       <c r="M151" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="N151" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="152">
@@ -9268,125 +9268,125 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026/09/24 17:31:32</t>
+          <t>2026/09/23 14:37:27</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>-34.16782, -70.73301</t>
+          <t>-34.2064416, -70.6737533</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>-34.16782, -70.73301</t>
+          <t>-34.20644, -70.67375</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026/09/24 23:31:32</t>
+          <t>2026/09/23 15:10:37</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>-34.16782, -70.73301</t>
+          <t>-34.2063866, -70.6737133</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>-34.16782, -70.73301</t>
+          <t>-34.20639, -70.67371</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>06:00:00</t>
+          <t>00:33:10</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M152" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026/09/24 18:35:15</t>
+          <t>2026/09/23 15:10:42</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>-33.4762016, -70.6984316</t>
+          <t>-34.2064283, -70.6737516</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>-33.47620, -70.69843</t>
+          <t>-34.20643, -70.67375</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026/09/24 22:35:53</t>
+          <t>2026/09/23 15:37:17</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>-33.4762016, -70.6984316</t>
+          <t>-34.2088683, -70.678425</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>-33.47620, -70.69843</t>
+          <t>-34.20887, -70.67843</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>04:00:38</t>
+          <t>00:26:35</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9395,37 +9395,37 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026/09/24 18:39:20</t>
+          <t>2026/09/23 15:15:14</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>-32.797605, -70.887025</t>
+          <t>-33.3671916, -70.6958816</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>-32.79760, -70.88702</t>
+          <t>-33.36719, -70.69588</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026/09/24 22:39:20</t>
+          <t>2026/09/24 23:15:34</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>-32.797605, -70.887025</t>
+          <t>-33.3671916, -70.6958816</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>-32.79760, -70.88702</t>
+          <t>-33.36719, -70.69588</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>04:00:00</t>
+          <t>32:00:20</t>
         </is>
       </c>
       <c r="L154" t="n">
@@ -9435,6 +9435,891 @@
         <v>0</v>
       </c>
       <c r="N154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>CHANGAN HUNTER TKCS-53</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>18</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>2026/09/23 15:38:11</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>-34.2088583, -70.67846</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>-34.20886, -70.67846</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>2026/09/23 16:38:40</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>-34.167865, -70.7330533</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>-34.16786, -70.73305</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>01:00:29</t>
+        </is>
+      </c>
+      <c r="L155" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="M155" t="n">
+        <v>57</v>
+      </c>
+      <c r="N155" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>CHANGAN HUNTER TKCS-53</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>19</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>2026/09/23 16:39:55</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>-34.1677683, -70.7330216</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>-34.16777, -70.73302</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>2026/09/24 07:33:51</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>-34.2064066, -70.6737083</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>-34.20641, -70.67371</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>14:53:56</t>
+        </is>
+      </c>
+      <c r="L156" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="M156" t="n">
+        <v>70</v>
+      </c>
+      <c r="N156" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>CHANGAN HUNTER TKCL-70</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>5</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>2026/09/23 17:36:46</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>-32.83989, -70.961898</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>-32.83989, -70.96190</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>2026/09/24 11:26:33</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>-33.360146, -70.806869</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>-33.36015, -70.80687</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>17:49:47</t>
+        </is>
+      </c>
+      <c r="L157" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="M157" t="n">
+        <v>1</v>
+      </c>
+      <c r="N157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>MITSUBISHI L200 PHZF-89</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>5</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>2026/09/23 20:13:52</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>-33.4361833, -70.6295283</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>-33.43618, -70.62953</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>2026/09/24 22:13:52</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>-33.4361833, -70.6295283</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>-33.43618, -70.62953</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>26:00:00</t>
+        </is>
+      </c>
+      <c r="L158" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>LPR20251A02800014-DS</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>3</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>2026/09/24 13:21:48</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>-34.206341, -70.673913</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>-34.20634, -70.67391</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>2026/09/24 14:17:13</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>-34.205473, -70.677302</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>-34.20547, -70.67730</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>00:55:25</t>
+        </is>
+      </c>
+      <c r="L159" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="M159" t="n">
+        <v>4</v>
+      </c>
+      <c r="N159" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>LPR20251L02790031-SV</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>6</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>2026/09/24 13:27:02</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>-34.346514, -71.125324</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>-34.34651, -71.12532</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>2026/09/24 15:14:47</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>-34.346198, -71.125541</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>-34.34620, -71.12554</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>01:47:45</t>
+        </is>
+      </c>
+      <c r="L160" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M160" t="n">
+        <v>3</v>
+      </c>
+      <c r="N160" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>LPR20251A02800014-DS</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>4</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>2026/09/24 14:17:38</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>-34.205446, -70.677348</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>-34.20545, -70.67735</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>2026/09/24 23:42:20</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>-34.205382, -70.677293</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>-34.20538, -70.67729</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>09:24:42</t>
+        </is>
+      </c>
+      <c r="L161" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>SUZUKI CARRY SKDB-52</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>5</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>2026/09/24 14:36:58</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>-32.879235, -70.60878</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>-32.87924, -70.60878</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>2026/09/24 22:36:58</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>-32.879235, -70.60878</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>-32.87924, -70.60878</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="L162" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>LPR20251L02790031-SV</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>7</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>2026/09/24 15:15:47</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>-34.345945, -71.125747</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>-34.34595, -71.12575</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>2026/09/24 23:17:44</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>-34.345997, -71.125783</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>-34.34600, -71.12578</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>08:01:57</t>
+        </is>
+      </c>
+      <c r="L163" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>SLP20250627045-AC02</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>6</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>2026/09/24 15:23:54</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>-34.205297, -70.680202</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>-34.20530, -70.68020</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>2026/09/24 15:30:47</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>-34.205297, -70.680211</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>-34.20530, -70.68021</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>00:06:53</t>
+        </is>
+      </c>
+      <c r="L164" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M164" t="n">
+        <v>3</v>
+      </c>
+      <c r="N164" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>SLP20250627045-AC02</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>7</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>2026/09/24 15:31:46</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>-34.20527, -70.680189</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>-34.20527, -70.68019</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>2026/09/24 15:48:25</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>-34.20548, -70.677407</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>-34.20548, -70.67741</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>00:16:39</t>
+        </is>
+      </c>
+      <c r="L165" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M165" t="n">
+        <v>4</v>
+      </c>
+      <c r="N165" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>CHANGAN HUNTER TKCS-53</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>13</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>2026/09/24 17:31:32</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>-34.16782, -70.73301</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>-34.16782, -70.73301</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>2026/09/24 23:31:32</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>-34.16782, -70.73301</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>-34.16782, -70.73301</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>06:00:00</t>
+        </is>
+      </c>
+      <c r="L166" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" t="n">
+        <v>0</v>
+      </c>
+      <c r="N166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>JAC X200 SJTJ-50</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>13</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>2026/09/24 17:39:32</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>-34.1677816, -70.7330016</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>-34.16778, -70.73300</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>2026/09/24 22:35:42</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>-34.1677816, -70.7330016</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>-34.16778, -70.73300</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>04:56:10</t>
+        </is>
+      </c>
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>MITSUBISHI L200 LVHX-40</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>12</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>2026/09/24 18:35:15</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>-33.4762016, -70.6984316</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>-33.47620, -70.69843</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>2026/09/24 22:35:53</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>-33.4762016, -70.6984316</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>-33.47620, -70.69843</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>04:00:38</t>
+        </is>
+      </c>
+      <c r="L168" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0</v>
+      </c>
+      <c r="N168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>CHANGAN HUNTER TGPS-77</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>7</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>2026/09/24 18:39:20</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>-32.797605, -70.887025</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>-32.79760, -70.88702</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>2026/09/24 22:39:20</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>-32.797605, -70.887025</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>-32.79760, -70.88702</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>04:00:00</t>
+        </is>
+      </c>
+      <c r="L169" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9543,13 +10428,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>354.27</v>
+        <v>560.23</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>122</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/09/25 22:57:32</t>
+          <t>2026/09/25 23:57:32</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>166:01:19</t>
+          <t>167:01:19</t>
         </is>
       </c>
       <c r="L14" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,13 +446,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N167"/>
+  <dimension ref="A1:N169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Desde : 2026/09/19 04:00:00   Hasta : 2026/09/26 03:59:59</t>
+          <t>Desde : 2026/09/20 04:00:00   Hasta : 2026/09/27 03:59:59</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -540,58 +540,58 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026/09/19 00:01:01</t>
+          <t>2026/09/20 00:01:34</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-32.9190466, -70.6749433</t>
+          <t>-34.346082, -71.125752</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-32.91905, -70.67494</t>
+          <t>-34.34608, -71.12575</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026/09/19 00:10:17</t>
+          <t>2026/09/21 10:32:33</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-32.8791933, -70.6088866</t>
+          <t>-34.346007, -71.125915</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-32.87919, -70.60889</t>
+          <t>-34.34601, -71.12592</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>00:09:16</t>
+          <t>34:30:59</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>10.2</v>
+        <v>0.04</v>
       </c>
       <c r="M4" t="n">
-        <v>127</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>76</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -599,111 +599,111 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026/09/19 00:01:40</t>
+          <t>2026/09/20 00:05:50</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-34.346082, -71.125752</t>
+          <t>-33.4359966, -70.628935</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-34.34608, -71.12575</t>
+          <t>-33.43600, -70.62893</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026/09/21 10:32:33</t>
+          <t>2026/09/20 13:25:35</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-34.346007, -71.125915</t>
+          <t>-33.4284833, -70.6480883</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-34.34601, -71.12592</t>
+          <t>-33.42848, -70.64809</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>58:30:53</t>
+          <t>13:19:45</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.04</v>
+        <v>3.98</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026/09/19 00:10:31</t>
+          <t>2026/09/20 00:05:50</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-32.879205, -70.608805</t>
+          <t>-33.360022, -70.807071</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-32.87920, -70.60881</t>
+          <t>-33.36002, -70.80707</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026/09/19 18:16:59</t>
+          <t>2026/09/20 14:35:06</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-32.8825783, -70.6119566</t>
+          <t>-33.360046, -70.807163</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-32.88258, -70.61196</t>
+          <t>-33.36005, -70.80716</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>18:06:28</t>
+          <t>14:29:16</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.48</v>
+        <v>0.03</v>
       </c>
       <c r="M6" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -717,52 +717,52 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026/09/19 00:11:48</t>
+          <t>2026/09/20 00:11:23</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-34.205017, -70.677254</t>
+          <t>-34.20547, -70.677435</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-34.20502, -70.67725</t>
+          <t>-34.20547, -70.67744</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026/09/19 01:13:48</t>
+          <t>2026/09/20 01:13:53</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-34.20547, -70.677435</t>
+          <t>-34.205315, -70.677233</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-34.20547, -70.67744</t>
+          <t>-34.20531, -70.67723</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>01:02:00</t>
+          <t>01:02:30</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -781,7 +781,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026/09/19 00:23:11</t>
+          <t>2026/09/20 00:22:33</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>73:01:50</t>
+          <t>49:02:28</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -827,7 +827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>LPR20251V02900023-LL</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -840,53 +840,53 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026/09/19 00:23:55</t>
+          <t>2026/09/20 00:31:15</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-33.36, -70.80706</t>
+          <t>-33.899723, -71.429709</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-33.36000, -70.80706</t>
+          <t>-33.89972, -71.42971</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026/09/20 14:35:06</t>
+          <t>2026/09/20 01:33:55</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-33.360046, -70.807163</t>
+          <t>-33.900235, -71.429753</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-33.36005, -70.80716</t>
+          <t>-33.90024, -71.42975</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>38:11:11</t>
+          <t>01:02:40</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LPR20251V02900023-LL</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -894,58 +894,58 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026/09/19 00:31:22</t>
+          <t>2026/09/20 00:34:38</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-33.899832, -71.429443</t>
+          <t>-34.579423, -70.961482</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-33.89983, -71.42944</t>
+          <t>-34.57942, -70.96148</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/09/19 01:33:50</t>
+          <t>2026/09/20 02:36:43</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-33.899723, -71.429709</t>
+          <t>-34.579863, -70.961835</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-33.89972, -71.42971</t>
+          <t>-34.57986, -70.96183</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>01:02:28</t>
+          <t>02:02:05</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>LPR20251E02900022</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -953,58 +953,58 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026/09/19 00:34:38</t>
+          <t>2026/09/20 00:42:12</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-34.579158, -70.961193</t>
+          <t>-33.36765, -70.697163</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-34.57916, -70.96119</t>
+          <t>-33.36765, -70.69716</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026/09/19 01:36:51</t>
+          <t>2026/09/22 09:43:01</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-34.579423, -70.961482</t>
+          <t>-33.36765, -70.697163</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-34.57942, -70.96148</t>
+          <t>-33.36765, -70.69716</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>01:02:13</t>
+          <t>57:00:49</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LPR20251E02900022</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1017,53 +1017,53 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026/09/19 00:42:12</t>
+          <t>2026/09/20 00:46:40</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-33.36765, -70.697163</t>
+          <t>-34.205209, -70.677496</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-33.36765, -70.69716</t>
+          <t>-34.20521, -70.67750</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026/09/22 09:43:01</t>
+          <t>2026/09/21 02:49:07</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-33.36765, -70.697163</t>
+          <t>-34.205421, -70.676645</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-33.36765, -70.69716</t>
+          <t>-34.20542, -70.67664</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>81:00:49</t>
+          <t>26:02:27</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1071,52 +1071,52 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026/09/19 00:46:16</t>
+          <t>2026/09/20 00:50:02</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-34.205247, -70.677394</t>
+          <t>-32.7386433, -70.718895</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-34.20525, -70.67739</t>
+          <t>-32.73864, -70.71890</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026/09/19 02:49:09</t>
+          <t>2026/09/20 02:36:59</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-34.205209, -70.677496</t>
+          <t>-32.8436366, -70.6006199</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-34.20521, -70.67750</t>
+          <t>-32.84364, -70.60062</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>02:02:53</t>
+          <t>01:46:57</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.01</v>
+        <v>19.82</v>
       </c>
       <c r="M13" t="n">
-        <v>2</v>
+        <v>92</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026/09/19 00:56:13</t>
+          <t>2026/09/20 00:56:13</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/09/25 23:57:32</t>
+          <t>2026/09/26 22:56:06</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>167:01:19</t>
+          <t>165:59:53</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -1181,7 +1181,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1189,58 +1189,58 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026/09/19 00:58:34</t>
+          <t>2026/09/20 00:59:08</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-33.4363449, -70.6293183</t>
+          <t>-34.042614, -70.681587</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-33.43634, -70.62932</t>
+          <t>-34.04261, -70.68159</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/09/19 13:12:49</t>
+          <t>2026/09/21 00:59:51</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-33.3825016, -71.2317016</t>
+          <t>-34.042788, -70.681593</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-33.38250, -71.23170</t>
+          <t>-34.04279, -70.68159</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>12:14:15</t>
+          <t>24:00:43</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>68.27</v>
+        <v>0.02</v>
       </c>
       <c r="M15" t="n">
-        <v>132</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1253,53 +1253,53 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026/09/19 00:59:08</t>
+          <t>2026/09/20 01:05:53</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-34.042665, -70.681601</t>
+          <t>-32.7430783, -70.7297883</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-34.04266, -70.68160</t>
+          <t>-32.74308, -70.72979</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/09/19 00:59:47</t>
+          <t>2026/09/20 17:45:53</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-34.042614, -70.681587</t>
+          <t>-32.7432, -70.7296849</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-34.04261, -70.68159</t>
+          <t>-32.74320, -70.72968</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>00:00:39</t>
+          <t>16:40:00</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0.01</v>
+        <v>0.87</v>
       </c>
       <c r="M16" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="N16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1312,47 +1312,47 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026/09/19 01:06:06</t>
+          <t>2026/09/20 01:25:59</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-32.7430049, -70.72982</t>
+          <t>-33.5139349, -70.6383516</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-32.74300, -70.72982</t>
+          <t>-33.51393, -70.63835</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026/09/19 08:12:02</t>
+          <t>2026/09/20 12:07:39</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-32.7430733, -70.7297516</t>
+          <t>-33.51081, -70.637165</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-32.74307, -70.72975</t>
+          <t>-33.51081, -70.63716</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>07:05:56</t>
+          <t>10:41:40</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0.02</v>
+        <v>1.62</v>
       </c>
       <c r="M17" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -1371,53 +1371,53 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026/09/19 01:16:39</t>
+          <t>2026/09/20 01:27:10</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-33.47617, -70.6984399</t>
+          <t>-33.4761283, -70.6984816</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-33.47617, -70.69844</t>
+          <t>-33.47613, -70.69848</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026/09/19 13:51:24</t>
+          <t>2026/09/20 10:00:00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-33.4763066, -70.6983233</t>
+          <t>-33.5087033, -70.7730866</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-33.47631, -70.69832</t>
+          <t>-33.50870, -70.77309</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>12:34:45</t>
+          <t>08:32:50</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0.03</v>
+        <v>13.9</v>
       </c>
       <c r="M18" t="n">
-        <v>7</v>
+        <v>103</v>
       </c>
       <c r="N18" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1430,47 +1430,47 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026/09/19 01:25:59</t>
+          <t>2026/09/20 01:33:18</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-33.5139349, -70.6383516</t>
+          <t>-33.0872333, -71.3621783</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-33.51393, -70.63835</t>
+          <t>-33.08723, -71.36218</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026/09/20 12:07:39</t>
+          <t>2026/09/21 08:30:55</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-33.51081, -70.637165</t>
+          <t>-33.0873366, -71.3622766</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-33.51081, -70.63716</t>
+          <t>-33.08734, -71.36228</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>34:41:40</t>
+          <t>30:57:37</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.62</v>
+        <v>0.05</v>
       </c>
       <c r="M19" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="N19" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -1489,27 +1489,27 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026/09/19 01:48:02</t>
+          <t>2026/09/20 01:58:11</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-32.7976083, -70.8870616</t>
+          <t>-32.7976033, -70.8870833</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88706</t>
+          <t>-32.79760, -70.88708</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026/09/19 11:57:50</t>
+          <t>2026/09/20 11:13:04</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-32.7977233, -70.8874433</t>
+          <t>-32.7977216, -70.8874416</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1519,82 +1519,82 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>10:09:48</t>
+          <t>09:14:53</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>13.09</v>
+        <v>15.25</v>
       </c>
       <c r="M20" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="N20" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>LPR20251A02800014-DS</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026/09/19 01:53:11</t>
+          <t>2026/09/20 02:11:21</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-33.0871666, -71.3621533</t>
+          <t>-34.205315, -70.677233</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-33.08717, -71.36215</t>
+          <t>-34.20531, -70.67723</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026/09/19 10:29:22</t>
+          <t>2026/09/21 01:14:18</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-33.0904899, -71.3605866</t>
+          <t>-34.204699, -70.676845</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-33.09049, -71.36059</t>
+          <t>-34.20470, -70.67685</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>08:36:11</t>
+          <t>23:02:57</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0.62</v>
+        <v>0.08</v>
       </c>
       <c r="M21" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>LPR20251V02900023-LL</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1607,53 +1607,53 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026/09/19 01:57:39</t>
+          <t>2026/09/20 02:31:39</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-34.042614, -70.681587</t>
+          <t>-33.900235, -71.429753</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-34.04261, -70.68159</t>
+          <t>-33.90024, -71.42975</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026/09/21 00:59:51</t>
+          <t>2026/09/21 01:33:54</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-34.042788, -70.681593</t>
+          <t>-33.899764, -71.429673</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-34.04279, -70.68159</t>
+          <t>-33.89976, -71.42967</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>47:02:12</t>
+          <t>23:02:15</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1661,111 +1661,111 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026/09/19 02:11:26</t>
+          <t>2026/09/20 02:38:14</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-34.20547, -70.677435</t>
+          <t>-32.8434483, -70.6010999</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-34.20547, -70.67744</t>
+          <t>-32.84345, -70.60110</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026/09/20 01:13:53</t>
+          <t>2026/09/20 03:11:17</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-34.205315, -70.677233</t>
+          <t>-32.8792016, -70.6088983</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-34.20531, -70.67723</t>
+          <t>-32.87920, -70.60890</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>23:02:27</t>
+          <t>00:33:03</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0.03</v>
+        <v>5.58</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LPR20251V02900023-LL</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026/09/19 02:31:21</t>
+          <t>2026/09/20 03:11:26</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-33.899723, -71.429709</t>
+          <t>-32.8792166, -70.608815</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-33.89972, -71.42971</t>
+          <t>-32.87922, -70.60882</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026/09/20 01:33:55</t>
+          <t>2026/09/20 10:18:21</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-33.900235, -71.429753</t>
+          <t>-33.5517716, -70.8447049</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-33.90024, -71.42975</t>
+          <t>-33.55177, -70.84470</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>23:02:34</t>
+          <t>07:06:55</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0.06</v>
+        <v>103.56</v>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
+        <v>140</v>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25">
@@ -1784,53 +1784,53 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026/09/19 02:35:12</t>
+          <t>2026/09/20 03:35:04</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-34.579423, -70.961482</t>
+          <t>-34.579863, -70.961835</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-34.57942, -70.96148</t>
+          <t>-34.57986, -70.96183</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026/09/20 02:36:43</t>
+          <t>2026/09/21 01:36:50</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-34.579863, -70.961835</t>
+          <t>-34.579897, -70.961631</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-34.57986, -70.96183</t>
+          <t>-34.57990, -70.96163</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>24:01:31</t>
+          <t>22:01:46</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="M25" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="N25" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1838,62 +1838,62 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026/09/19 03:46:54</t>
+          <t>2026/09/20 10:00:29</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-34.205209, -70.677496</t>
+          <t>-33.5087133, -70.7730616</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-34.20521, -70.67750</t>
+          <t>-33.50871, -70.77306</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026/09/21 02:49:07</t>
+          <t>2026/09/20 17:09:26</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-34.205421, -70.676645</t>
+          <t>-33.4580083, -70.7010683</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-34.20542, -70.67664</t>
+          <t>-33.45801, -70.70107</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>47:02:13</t>
+          <t>07:08:57</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0.09</v>
+        <v>10.5</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1902,57 +1902,57 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026/09/19 08:13:06</t>
+          <t>2026/09/20 10:19:36</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-32.74301, -70.7295966</t>
+          <t>-33.5517566, -70.8447033</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-32.74301, -70.72960</t>
+          <t>-33.55176, -70.84470</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026/09/19 08:22:38</t>
+          <t>2026/09/20 11:02:50</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-32.742655, -70.7271883</t>
+          <t>-33.5496066, -70.8425433</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-32.74265, -70.72719</t>
+          <t>-33.54961, -70.84254</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>00:09:32</t>
+          <t>00:43:14</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.28</v>
+        <v>3.71</v>
       </c>
       <c r="M27" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="N27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1961,57 +1961,57 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026/09/19 08:23:53</t>
+          <t>2026/09/20 11:04:05</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-32.7423249, -70.7270716</t>
+          <t>-33.5491583, -70.841735</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-32.74232, -70.72707</t>
+          <t>-33.54916, -70.84173</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026/09/19 08:38:56</t>
+          <t>2026/09/20 12:25:00</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-32.7140966, -70.7476716</t>
+          <t>-32.8792116, -70.6088783</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-32.71410, -70.74767</t>
+          <t>-32.87921, -70.60888</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>00:15:03</t>
+          <t>01:20:55</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.51</v>
+        <v>101.96</v>
       </c>
       <c r="M28" t="n">
-        <v>58</v>
+        <v>127</v>
       </c>
       <c r="N28" t="n">
-        <v>26</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2020,57 +2020,57 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026/09/19 08:40:11</t>
+          <t>2026/09/20 11:13:35</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-32.7140433, -70.7475983</t>
+          <t>-32.7976383, -70.8871716</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-32.71404, -70.74760</t>
+          <t>-32.79764, -70.88717</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026/09/19 09:45:05</t>
+          <t>2026/09/20 15:08:23</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-32.5609366, -70.7150499</t>
+          <t>-32.79777, -70.8874366</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-32.56094, -70.71505</t>
+          <t>-32.79777, -70.88744</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>01:04:54</t>
+          <t>03:54:48</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>19.75</v>
+        <v>44.32</v>
       </c>
       <c r="M29" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="N29" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2079,57 +2079,57 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026/09/19 09:45:13</t>
+          <t>2026/09/20 12:08:17</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-32.5608733, -70.7151633</t>
+          <t>-33.510875, -70.6370716</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-32.56087, -70.71516</t>
+          <t>-33.51087, -70.63707</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026/09/19 18:53:55</t>
+          <t>2026/09/20 12:27:02</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-32.7412333, -70.7290283</t>
+          <t>-33.5110683, -70.6376316</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-32.74123, -70.72903</t>
+          <t>-33.51107, -70.63763</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>09:08:42</t>
+          <t>00:18:45</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>205.46</v>
+        <v>0.09</v>
       </c>
       <c r="M30" t="n">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="N30" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2138,57 +2138,57 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026/09/19 10:29:55</t>
+          <t>2026/09/20 12:10:22</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-33.090865, -71.3610499</t>
+          <t>-32.838357, -70.955582</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-33.09087, -71.36105</t>
+          <t>-32.83836, -70.95558</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026/09/19 10:41:53</t>
+          <t>2026/09/21 13:47:49</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-33.0868266, -71.3617183</t>
+          <t>-33.367937, -70.695106</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-33.08683, -71.36172</t>
+          <t>-33.36794, -70.69511</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>00:11:58</t>
+          <t>25:37:27</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0.6</v>
+        <v>78.31</v>
       </c>
       <c r="M31" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2197,57 +2197,57 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026/09/19 10:42:48</t>
+          <t>2026/09/20 12:25:06</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-33.0873433, -71.362275</t>
+          <t>-32.8792216, -70.6088283</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-33.08734, -71.36227</t>
+          <t>-32.87922, -70.60883</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026/09/19 11:18:23</t>
+          <t>2026/09/21 11:05:36</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-33.08691, -71.3618516</t>
+          <t>-32.7556383, -70.7397133</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-33.08691, -71.36185</t>
+          <t>-32.75564, -70.73971</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>00:35:35</t>
+          <t>22:40:30</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>9.35</v>
+        <v>21.73</v>
       </c>
       <c r="M32" t="n">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="N32" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2256,57 +2256,57 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026/09/19 11:18:53</t>
+          <t>2026/09/20 12:28:17</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-33.0873166, -71.3623266</t>
+          <t>-33.5064116, -70.63851</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-33.08732, -71.36233</t>
+          <t>-33.50641, -70.63851</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026/09/19 19:33:12</t>
+          <t>2026/09/20 13:03:51</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-33.0872833, -71.362215</t>
+          <t>-33.5140933, -70.6374333</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-33.08728, -71.36222</t>
+          <t>-33.51409, -70.63743</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>08:14:19</t>
+          <t>00:35:34</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0.02</v>
+        <v>1.87</v>
       </c>
       <c r="M33" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="N33" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2315,57 +2315,57 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026/09/19 11:58:11</t>
+          <t>2026/09/20 13:05:06</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-32.7976033, -70.8870833</t>
+          <t>-33.5138749, -70.6383083</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-32.79760, -70.88708</t>
+          <t>-33.51387, -70.63831</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026/09/20 11:13:04</t>
+          <t>2026/09/21 09:48:08</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-32.7977216, -70.8874416</t>
+          <t>-33.3671683, -70.6955583</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-32.79772, -70.88744</t>
+          <t>-33.36717, -70.69556</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>23:14:53</t>
+          <t>20:43:02</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>15.25</v>
+        <v>20.5</v>
       </c>
       <c r="M34" t="n">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="N34" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2374,57 +2374,57 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026/09/19 12:34:54</t>
+          <t>2026/09/20 13:26:50</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-32.83836, -70.955543</t>
+          <t>-33.4298516, -70.6486516</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-32.83836, -70.95554</t>
+          <t>-33.42985, -70.64865</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026/09/19 12:36:45</t>
+          <t>2026/09/20 14:28:01</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-32.838403, -70.954848</t>
+          <t>-33.4288433, -70.5788783</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-32.83840, -70.95485</t>
+          <t>-33.42884, -70.57888</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>00:01:51</t>
+          <t>01:01:11</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0.19</v>
+        <v>10.66</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2433,57 +2433,57 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026/09/19 12:37:43</t>
+          <t>2026/09/20 14:29:10</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-32.838403, -70.954848</t>
+          <t>-33.4296166, -70.5783916</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-32.83840, -70.95485</t>
+          <t>-33.42962, -70.57839</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026/09/21 13:47:49</t>
+          <t>2026/09/20 16:18:09</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-33.367937, -70.695106</t>
+          <t>-33.4362733, -70.6295616</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-33.36794, -70.69511</t>
+          <t>-33.43627, -70.62956</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>49:10:06</t>
+          <t>01:48:59</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>82.88</v>
+        <v>6.49</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2492,53 +2492,53 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026/09/19 13:14:04</t>
+          <t>2026/09/20 15:08:53</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-33.3824649, -71.2315433</t>
+          <t>-32.79765, -70.8871266</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-33.38246, -71.23154</t>
+          <t>-32.79765, -70.88713</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026/09/19 19:19:15</t>
+          <t>2026/09/20 16:41:09</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-33.4396833, -70.8128499</t>
+          <t>-32.7977516, -70.8874299</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-33.43968, -70.81285</t>
+          <t>-32.79775, -70.88743</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>06:05:11</t>
+          <t>01:32:16</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>46.61</v>
+        <v>12.39</v>
       </c>
       <c r="M37" t="n">
-        <v>128</v>
+        <v>66</v>
       </c>
       <c r="N37" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2546,62 +2546,62 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026/09/19 13:51:36</t>
+          <t>2026/09/20 15:32:32</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-33.4763499, -70.6983583</t>
+          <t>-33.360046, -70.807163</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-33.47635, -70.69836</t>
+          <t>-33.36005, -70.80716</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026/09/19 14:25:56</t>
+          <t>2026/09/26 22:50:57</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-33.464275, -70.7084933</t>
+          <t>-33.360042, -70.807029</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-33.46428, -70.70849</t>
+          <t>-33.36004, -70.80703</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>00:34:20</t>
+          <t>151:18:25</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.53</v>
+        <v>0.06</v>
       </c>
       <c r="M38" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2610,57 +2610,57 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026/09/19 14:26:23</t>
+          <t>2026/09/20 16:19:01</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-33.4642766, -70.708315</t>
+          <t>-33.436395, -70.62956</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-33.46428, -70.70831</t>
+          <t>-33.43639, -70.62956</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026/09/19 21:25:54</t>
+          <t>2026/09/21 06:18:44</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>-33.4762566, -70.69828</t>
+          <t>-33.4449966, -70.619575</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>-33.47626, -70.69828</t>
+          <t>-33.44500, -70.61957</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>06:59:31</t>
+          <t>13:59:43</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.1</v>
+        <v>1.82</v>
       </c>
       <c r="M39" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N39" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2669,57 +2669,57 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026/09/19 18:18:14</t>
+          <t>2026/09/20 16:41:34</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-32.8832049, -70.6123416</t>
+          <t>-32.7976233, -70.88709</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-32.88320, -70.61234</t>
+          <t>-32.79762, -70.88709</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026/09/19 18:36:51</t>
+          <t>2026/09/20 19:28:29</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-32.8824016, -70.6119899</t>
+          <t>-32.7977166, -70.8873633</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>-32.88240, -70.61199</t>
+          <t>-32.79772, -70.88736</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>00:18:37</t>
+          <t>02:46:55</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0.6899999999999999</v>
+        <v>40.53</v>
       </c>
       <c r="M40" t="n">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="N40" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026/09/19 18:38:06</t>
+          <t>2026/09/20 17:10:41</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-32.8794316, -70.608835</t>
+          <t>-33.4575833, -70.7012149</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-32.87943, -70.60883</t>
+          <t>-33.45758, -70.70121</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026/09/19 19:14:57</t>
+          <t>2026/09/20 23:12:51</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-32.8437949, -70.5976883</t>
+          <t>-33.47623, -70.698295</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-32.84379, -70.59769</t>
+          <t>-33.47623, -70.69830</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>00:36:51</t>
+          <t>06:02:10</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>6.61</v>
+        <v>18.25</v>
       </c>
       <c r="M41" t="n">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="N41" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42">
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2787,44 +2787,44 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026/09/19 18:55:10</t>
+          <t>2026/09/20 17:47:05</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-32.7432466, -70.7296366</t>
+          <t>-32.74311, -70.7297766</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-32.74325, -70.72964</t>
+          <t>-32.74311, -70.72978</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026/09/20 17:45:53</t>
+          <t>2026/09/20 19:12:44</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-32.7432, -70.7296849</t>
+          <t>-32.7430783, -70.7297333</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-32.74320, -70.72968</t>
+          <t>-32.74308, -70.72973</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>22:50:43</t>
+          <t>01:25:39</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0.9</v>
+        <v>0.01</v>
       </c>
       <c r="M42" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="N42" t="n">
         <v>9</v>
@@ -2833,11 +2833,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2846,57 +2846,57 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026/09/19 19:16:07</t>
+          <t>2026/09/20 19:13:13</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-32.84321, -70.6019916</t>
+          <t>-32.7431166, -70.729705</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-32.84321, -70.60199</t>
+          <t>-32.74312, -70.72970</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026/09/19 22:10:31</t>
+          <t>2026/09/21 06:42:10</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-32.7385033, -70.7198449</t>
+          <t>-32.8417366, -70.9368466</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-32.73850, -70.71984</t>
+          <t>-32.84174, -70.93685</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>02:54:24</t>
+          <t>11:28:57</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>60.65</v>
+        <v>35.66</v>
       </c>
       <c r="M43" t="n">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="N43" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2905,57 +2905,57 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026/09/19 19:20:30</t>
+          <t>2026/09/20 19:29:44</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-33.4344633, -70.8104549</t>
+          <t>-32.79759, -70.88704</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-33.43446, -70.81045</t>
+          <t>-32.79759, -70.88704</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026/09/19 20:05:26</t>
+          <t>2026/09/21 07:01:02</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-33.4361849, -70.6288799</t>
+          <t>-32.742505, -70.7863866</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-33.43618, -70.62888</t>
+          <t>-32.74251, -70.78639</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>00:44:56</t>
+          <t>11:31:18</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>29</v>
+        <v>11.6</v>
       </c>
       <c r="M44" t="n">
-        <v>128</v>
+        <v>67</v>
       </c>
       <c r="N44" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2964,57 +2964,57 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026/09/19 19:33:18</t>
+          <t>2026/09/20 23:14:03</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-33.0872333, -71.3621783</t>
+          <t>-33.4760783, -70.6984983</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-33.08723, -71.36218</t>
+          <t>-33.47608, -70.69850</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026/09/21 08:30:55</t>
+          <t>2026/09/21 07:45:23</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-33.0873366, -71.3622766</t>
+          <t>-33.4762683, -70.6983366</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-33.08734, -71.36228</t>
+          <t>-33.47627, -70.69834</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>36:57:37</t>
+          <t>08:31:20</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0.05</v>
+        <v>11.16</v>
       </c>
       <c r="M45" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="N45" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3023,57 +3023,57 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026/09/19 20:05:50</t>
+          <t>2026/09/21 01:57:37</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-33.4359966, -70.628935</t>
+          <t>-34.042788, -70.681593</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-33.43600, -70.62893</t>
+          <t>-34.04279, -70.68159</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026/09/20 13:25:35</t>
+          <t>2026/09/22 00:59:45</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-33.4284833, -70.6480883</t>
+          <t>-34.042546, -70.681506</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-33.42848, -70.64809</t>
+          <t>-34.04255, -70.68151</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>17:19:45</t>
+          <t>23:02:08</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.98</v>
+        <v>0.03</v>
       </c>
       <c r="M46" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="N46" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>LPR20251A02800014-DS</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3082,57 +3082,57 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026/09/19 21:27:10</t>
+          <t>2026/09/21 02:11:38</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-33.4761283, -70.6984816</t>
+          <t>-34.204699, -70.676845</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-33.47613, -70.69848</t>
+          <t>-34.20470, -70.67685</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026/09/20 10:00:00</t>
+          <t>2026/09/24 01:13:58</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-33.5087033, -70.7730866</t>
+          <t>-34.205163, -70.677135</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-33.50870, -70.77309</t>
+          <t>-34.20516, -70.67714</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>12:32:50</t>
+          <t>71:02:20</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>13.9</v>
+        <v>0.16</v>
       </c>
       <c r="M47" t="n">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="N47" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>LPR20251V02900023-LL</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3141,53 +3141,53 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026/09/19 22:11:21</t>
+          <t>2026/09/21 02:31:44</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-32.7386433, -70.718895</t>
+          <t>-33.899764, -71.429673</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-32.73864, -70.71890</t>
+          <t>-33.89976, -71.42967</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026/09/20 02:36:59</t>
+          <t>2026/09/23 01:33:50</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-32.8436366, -70.6006199</t>
+          <t>-33.899801, -71.429488</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-32.84364, -70.60062</t>
+          <t>-33.89980, -71.42949</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>04:25:38</t>
+          <t>47:02:06</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>19.82</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>92</v>
+        <v>7</v>
       </c>
       <c r="N48" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -3195,121 +3195,121 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026/09/20 02:11:21</t>
+          <t>2026/09/21 03:46:55</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-34.205315, -70.677233</t>
+          <t>-34.205421, -70.676645</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-34.20531, -70.67723</t>
+          <t>-34.20542, -70.67664</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026/09/21 01:14:18</t>
+          <t>2026/09/22 02:48:54</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-34.204699, -70.676845</t>
+          <t>-34.205312, -70.677285</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>-34.20470, -70.67685</t>
+          <t>-34.20531, -70.67728</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>23:02:57</t>
+          <t>23:01:59</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026/09/20 12:28:17</t>
+          <t>2026/09/21 09:39:54</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-33.5064116, -70.63851</t>
+          <t>-32.7460133, -70.724655</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-33.50641, -70.63851</t>
+          <t>-32.74601, -70.72465</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026/09/20 13:03:51</t>
+          <t>2026/09/21 09:56:12</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-33.5140933, -70.6374333</t>
+          <t>-32.74595, -70.7245833</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>-33.51409, -70.63743</t>
+          <t>-32.74595, -70.72458</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>00:35:34</t>
+          <t>00:16:18</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.87</v>
+        <v>0.03</v>
       </c>
       <c r="M50" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="N50" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3318,47 +3318,47 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026/09/20 13:05:06</t>
+          <t>2026/09/21 10:02:32</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-33.5138749, -70.6383083</t>
+          <t>-32.7458116, -70.7246516</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-33.51387, -70.63831</t>
+          <t>-32.74581, -70.72465</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026/09/21 09:48:08</t>
+          <t>2026/09/21 10:26:47</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>-33.3671683, -70.6955583</t>
+          <t>-32.7466066, -70.7223566</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>-33.36717, -70.69556</t>
+          <t>-32.74661, -70.72236</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>20:43:02</t>
+          <t>00:24:15</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>20.5</v>
+        <v>0.64</v>
       </c>
       <c r="M51" t="n">
-        <v>101</v>
+        <v>14</v>
       </c>
       <c r="N51" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52">
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3377,57 +3377,57 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026/09/20 16:41:34</t>
+          <t>2026/09/21 10:26:53</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-32.7976233, -70.88709</t>
+          <t>-32.7465666, -70.7223633</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-32.79762, -70.88709</t>
+          <t>-32.74657, -70.72236</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026/09/20 19:28:29</t>
+          <t>2026/09/21 10:47:51</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-32.7977166, -70.8873633</t>
+          <t>-32.7557566, -70.7220016</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>-32.79772, -70.88736</t>
+          <t>-32.75576, -70.72200</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>02:46:55</t>
+          <t>00:20:58</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>40.53</v>
+        <v>1.65</v>
       </c>
       <c r="M52" t="n">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="N52" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3436,57 +3436,57 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026/09/20 19:29:44</t>
+          <t>2026/09/21 10:41:46</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-32.79759, -70.88704</t>
+          <t>-34.345974, -71.125771</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-32.79759, -70.88704</t>
+          <t>-34.34597, -71.12577</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026/09/21 07:01:02</t>
+          <t>2026/09/21 11:16:57</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-32.742505, -70.7863866</t>
+          <t>-34.348243, -71.127659</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>-32.74251, -70.78639</t>
+          <t>-34.34824, -71.12766</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>11:31:18</t>
+          <t>00:35:11</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>11.6</v>
+        <v>0.7</v>
       </c>
       <c r="M53" t="n">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="N53" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LPR20251V02900023-LL</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3495,57 +3495,57 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026/09/21 02:31:44</t>
+          <t>2026/09/21 10:49:06</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-33.899764, -71.429673</t>
+          <t>-32.75533, -70.723645</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-33.89976, -71.42967</t>
+          <t>-32.75533, -70.72365</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026/09/23 01:33:50</t>
+          <t>2026/09/21 10:59:41</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>-33.899801, -71.429488</t>
+          <t>-32.757515, -70.7369016</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>-33.89980, -71.42949</t>
+          <t>-32.75751, -70.73690</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>47:02:06</t>
+          <t>00:10:35</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.44</v>
       </c>
       <c r="M54" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="N54" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3554,47 +3554,47 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026/09/21 03:46:55</t>
+          <t>2026/09/21 10:58:12</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-34.205421, -70.676645</t>
+          <t>-34.2053533, -70.6802216</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-34.20542, -70.67664</t>
+          <t>-34.20535, -70.68022</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026/09/22 02:48:54</t>
+          <t>2026/09/21 11:32:45</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-34.205312, -70.677285</t>
+          <t>-34.2078066, -70.6790816</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>-34.20531, -70.67728</t>
+          <t>-34.20781, -70.67908</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>23:01:59</t>
+          <t>00:34:33</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0.06</v>
+        <v>1.34</v>
       </c>
       <c r="M55" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="N55" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56">
@@ -3604,125 +3604,125 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026/09/21 09:39:54</t>
+          <t>2026/09/21 11:00:56</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-32.7460133, -70.724655</t>
+          <t>-32.7546883, -70.741175</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-32.74601, -70.72465</t>
+          <t>-32.75469, -70.74117</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026/09/21 09:56:12</t>
+          <t>2026/09/21 11:42:00</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>-32.74595, -70.7245833</t>
+          <t>-32.795735, -70.8201816</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>-32.74595, -70.72458</t>
+          <t>-32.79574, -70.82018</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>00:16:18</t>
+          <t>00:41:04</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0.03</v>
+        <v>14.61</v>
       </c>
       <c r="M56" t="n">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="N56" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026/09/21 09:56:18</t>
+          <t>2026/09/21 11:17:44</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-32.745895, -70.724575</t>
+          <t>-34.348188, -71.127655</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-32.74589, -70.72458</t>
+          <t>-34.34819, -71.12766</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026/09/21 10:01:54</t>
+          <t>2026/09/21 11:27:14</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>-32.7458516, -70.7246616</t>
+          <t>-34.347861, -71.127635</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-32.74585, -70.72466</t>
+          <t>-34.34786, -71.12763</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>00:05:36</t>
+          <t>00:09:30</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="M57" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N57" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -3731,57 +3731,57 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026/09/21 10:02:32</t>
+          <t>2026/09/21 11:27:54</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-32.7458116, -70.7246516</t>
+          <t>-34.347666, -71.127633</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-32.74581, -70.72465</t>
+          <t>-34.34767, -71.12763</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026/09/21 10:26:47</t>
+          <t>2026/09/21 12:10:45</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>-32.7466066, -70.7223566</t>
+          <t>-34.345983, -71.12569</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>-32.74661, -70.72236</t>
+          <t>-34.34598, -71.12569</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>00:24:15</t>
+          <t>00:42:51</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0.64</v>
+        <v>0.27</v>
       </c>
       <c r="M58" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="N58" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3790,57 +3790,57 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026/09/21 10:26:53</t>
+          <t>2026/09/21 11:31:52</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-32.7465666, -70.7223633</t>
+          <t>-33.4678366, -70.711765</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-32.74657, -70.72236</t>
+          <t>-33.46784, -70.71176</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026/09/21 10:47:51</t>
+          <t>2026/09/21 12:50:08</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>-32.7557566, -70.7220016</t>
+          <t>-33.4762616, -70.6982733</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>-32.75576, -70.72200</t>
+          <t>-33.47626, -70.69827</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>00:20:58</t>
+          <t>01:18:16</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.65</v>
+        <v>3.23</v>
       </c>
       <c r="M59" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="N59" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -3849,47 +3849,47 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026/09/21 10:41:46</t>
+          <t>2026/09/21 11:34:00</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>-34.345974, -71.125771</t>
+          <t>-34.2070416, -70.67714</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-34.34597, -71.12577</t>
+          <t>-34.20704, -70.67714</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026/09/21 11:16:57</t>
+          <t>2026/09/21 11:58:43</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>-34.348243, -71.127659</t>
+          <t>-34.1900099, -70.7093266</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>-34.34824, -71.12766</t>
+          <t>-34.19001, -70.70933</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>00:35:11</t>
+          <t>00:24:43</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0.7</v>
+        <v>3.93</v>
       </c>
       <c r="M60" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="N60" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61">
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3908,57 +3908,57 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026/09/21 10:49:06</t>
+          <t>2026/09/21 11:43:15</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-32.75533, -70.723645</t>
+          <t>-32.7958333, -70.820115</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-32.75533, -70.72365</t>
+          <t>-32.79583, -70.82012</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026/09/21 10:59:41</t>
+          <t>2026/09/21 13:12:25</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>-32.757515, -70.7369016</t>
+          <t>-32.75696, -70.733815</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>-32.75751, -70.73690</t>
+          <t>-32.75696, -70.73382</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>00:10:35</t>
+          <t>01:29:10</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.44</v>
+        <v>15.34</v>
       </c>
       <c r="M61" t="n">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="N61" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3967,47 +3967,47 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026/09/21 11:00:56</t>
+          <t>2026/09/21 11:59:58</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>-32.7546883, -70.741175</t>
+          <t>-34.19012, -70.70941</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-32.75469, -70.74117</t>
+          <t>-34.19012, -70.70941</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026/09/21 11:42:00</t>
+          <t>2026/09/21 12:51:42</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>-32.795735, -70.8201816</t>
+          <t>-34.205315, -70.6803433</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>-32.79574, -70.82018</t>
+          <t>-34.20531, -70.68034</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>00:41:04</t>
+          <t>00:51:44</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>14.61</v>
+        <v>3.37</v>
       </c>
       <c r="M62" t="n">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="N62" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="63">
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4026,41 +4026,41 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026/09/21 11:17:44</t>
+          <t>2026/09/21 12:10:58</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-34.348188, -71.127655</t>
+          <t>-34.345963, -71.12571</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-34.34819, -71.12766</t>
+          <t>-34.34596, -71.12571</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026/09/21 11:27:14</t>
+          <t>2026/09/22 11:01:43</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>-34.347861, -71.127635</t>
+          <t>-34.346207, -71.12551</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>-34.34786, -71.12763</t>
+          <t>-34.34621, -71.12551</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>00:09:30</t>
+          <t>22:50:45</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="M63" t="n">
         <v>3</v>
@@ -4072,11 +4072,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4085,53 +4085,53 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026/09/21 11:27:54</t>
+          <t>2026/09/21 12:50:39</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-34.347666, -71.127633</t>
+          <t>-33.4763016, -70.6983899</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-34.34767, -71.12763</t>
+          <t>-33.47630, -70.69839</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026/09/21 12:10:45</t>
+          <t>2026/09/21 16:29:37</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>-34.345983, -71.12569</t>
+          <t>-33.4092366, -70.6780866</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>-34.34598, -71.12569</t>
+          <t>-33.40924, -70.67809</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>00:42:51</t>
+          <t>03:38:58</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0.27</v>
+        <v>11.45</v>
       </c>
       <c r="M64" t="n">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="N64" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -4144,57 +4144,57 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026/09/21 11:31:52</t>
+          <t>2026/09/21 12:52:22</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-33.4678366, -70.711765</t>
+          <t>-34.2041316, -70.67902</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-33.46784, -70.71176</t>
+          <t>-34.20413, -70.67902</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026/09/21 12:50:08</t>
+          <t>2026/09/21 13:36:54</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>-33.4762616, -70.6982733</t>
+          <t>-34.20752, -70.6759233</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>-33.47626, -70.69827</t>
+          <t>-34.20752, -70.67592</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>01:18:16</t>
+          <t>00:44:32</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.23</v>
+        <v>0.53</v>
       </c>
       <c r="M65" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="N65" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4203,116 +4203,116 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026/09/21 11:43:15</t>
+          <t>2026/09/21 13:02:58</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>-32.7958333, -70.820115</t>
+          <t>-34.2064133, -70.6737666</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-32.79583, -70.82012</t>
+          <t>-34.20641, -70.67377</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026/09/21 13:12:25</t>
+          <t>2026/09/21 13:28:08</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>-32.75696, -70.733815</t>
+          <t>-34.2069733, -70.67487</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>-32.75696, -70.73382</t>
+          <t>-34.20697, -70.67487</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>01:29:10</t>
+          <t>00:25:10</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>15.34</v>
+        <v>0.12</v>
       </c>
       <c r="M66" t="n">
-        <v>79</v>
+        <v>3</v>
       </c>
       <c r="N66" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026/09/21 12:10:58</t>
+          <t>2026/09/21 13:13:40</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>-34.345963, -71.12571</t>
+          <t>-32.7571049, -70.7338066</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-34.34596, -71.12571</t>
+          <t>-32.75710, -70.73381</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026/09/22 11:01:43</t>
+          <t>2026/09/21 15:00:20</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>-34.346207, -71.12551</t>
+          <t>-32.79772, -70.8873733</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>-34.34621, -71.12551</t>
+          <t>-32.79772, -70.88737</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>22:50:45</t>
+          <t>01:46:40</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0.06</v>
+        <v>17.26</v>
       </c>
       <c r="M67" t="n">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="N67" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4321,57 +4321,57 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026/09/21 12:50:39</t>
+          <t>2026/09/21 13:28:29</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>-33.4763016, -70.6983899</t>
+          <t>-34.2069483, -70.6750266</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-33.47630, -70.69839</t>
+          <t>-34.20695, -70.67503</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026/09/21 16:29:37</t>
+          <t>2026/09/21 14:51:40</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>-33.4092366, -70.6780866</t>
+          <t>-34.2042733, -70.6788433</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>-33.40924, -70.67809</t>
+          <t>-34.20427, -70.67884</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>03:38:58</t>
+          <t>01:23:11</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>11.45</v>
+        <v>0.61</v>
       </c>
       <c r="M68" t="n">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="N68" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4380,47 +4380,47 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026/09/21 13:13:40</t>
+          <t>2026/09/21 13:37:31</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-32.7571049, -70.7338066</t>
+          <t>-34.2070683, -70.6749683</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-32.75710, -70.73381</t>
+          <t>-34.20707, -70.67497</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026/09/21 15:00:20</t>
+          <t>2026/09/21 14:01:38</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>-32.79772, -70.8873733</t>
+          <t>-34.2041049, -70.67894</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>-32.79772, -70.88737</t>
+          <t>-34.20410, -70.67894</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>01:46:40</t>
+          <t>00:24:07</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>17.26</v>
+        <v>1.32</v>
       </c>
       <c r="M69" t="n">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="N69" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70">
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4439,53 +4439,53 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026/09/21 13:37:31</t>
+          <t>2026/09/21 14:01:42</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>-34.2070683, -70.6749683</t>
+          <t>-34.20411, -70.6789666</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-34.20707, -70.67497</t>
+          <t>-34.20411, -70.67897</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026/09/21 14:01:38</t>
+          <t>2026/09/21 18:01:54</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>-34.2041049, -70.67894</t>
+          <t>-33.0873633, -71.3623049</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>-34.20410, -70.67894</t>
+          <t>-33.08736, -71.36230</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>00:24:07</t>
+          <t>04:00:12</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.32</v>
+        <v>203.99</v>
       </c>
       <c r="M70" t="n">
-        <v>25</v>
+        <v>142</v>
       </c>
       <c r="N70" t="n">
-        <v>13</v>
+        <v>85</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -4498,47 +4498,47 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026/09/21 14:01:42</t>
+          <t>2026/09/21 14:14:12</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>-34.20411, -70.6789666</t>
+          <t>-32.8845783, -70.61139</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-34.20411, -70.67897</t>
+          <t>-32.88458, -70.61139</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026/09/21 18:01:54</t>
+          <t>2026/09/21 14:35:36</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>-33.0873633, -71.3623049</t>
+          <t>-32.885225, -70.6111833</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>-33.08736, -71.36230</t>
+          <t>-32.88522, -70.61118</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>04:00:12</t>
+          <t>00:21:24</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>203.99</v>
+        <v>0.99</v>
       </c>
       <c r="M71" t="n">
-        <v>142</v>
+        <v>23</v>
       </c>
       <c r="N71" t="n">
-        <v>85</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72">
@@ -4548,7 +4548,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4557,57 +4557,57 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026/09/21 14:14:12</t>
+          <t>2026/09/21 14:36:51</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>-32.8845783, -70.61139</t>
+          <t>-32.8844966, -70.6112</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-32.88458, -70.61139</t>
+          <t>-32.88450, -70.61120</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026/09/21 14:35:36</t>
+          <t>2026/09/21 15:00:26</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>-32.885225, -70.6111833</t>
+          <t>-32.8831183, -70.61084</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>-32.88522, -70.61118</t>
+          <t>-32.88312, -70.61084</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>00:21:24</t>
+          <t>00:23:35</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0.99</v>
+        <v>0.86</v>
       </c>
       <c r="M72" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N72" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -4616,47 +4616,47 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026/09/21 14:36:51</t>
+          <t>2026/09/21 14:51:44</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>-32.8844966, -70.6112</t>
+          <t>-34.2042833, -70.6789066</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-32.88450, -70.61120</t>
+          <t>-34.20428, -70.67891</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026/09/21 15:00:26</t>
+          <t>2026/09/21 16:56:47</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>-32.8831183, -70.61084</t>
+          <t>-34.1679249, -70.732985</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>-32.88312, -70.61084</t>
+          <t>-34.16792, -70.73298</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>00:23:35</t>
+          <t>02:05:03</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0.86</v>
+        <v>7.6</v>
       </c>
       <c r="M73" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="N73" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74">
@@ -5842,7 +5842,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -5855,57 +5855,57 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026/09/22 01:57:15</t>
+          <t>2026/09/22 02:34:52</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>-34.042546, -70.681506</t>
+          <t>-34.580059, -70.961183</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-34.04255, -70.68151</t>
+          <t>-34.58006, -70.96118</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026/09/22 14:00:30</t>
+          <t>2026/09/23 01:37:53</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>-34.042727, -70.681625</t>
+          <t>-34.57985, -70.961438</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>-34.04273, -70.68162</t>
+          <t>-34.57985, -70.96144</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>12:03:15</t>
+          <t>23:03:01</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="M94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -5914,47 +5914,47 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026/09/22 02:34:52</t>
+          <t>2026/09/22 08:04:36</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>-34.580059, -70.961183</t>
+          <t>-34.204283, -70.67889</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-34.58006, -70.96118</t>
+          <t>-34.20428, -70.67889</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026/09/23 01:37:53</t>
+          <t>2026/09/22 08:11:36</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>-34.57985, -70.961438</t>
+          <t>-34.204069, -70.678925</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>-34.57985, -70.96144</t>
+          <t>-34.20407, -70.67893</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>23:03:01</t>
+          <t>00:07:00</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="M95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -7199,11 +7199,11 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7212,116 +7212,116 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026/09/22 14:04:18</t>
+          <t>2026/09/22 14:00:55</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>-34.205283, -70.68009</t>
+          <t>-34.042682, -70.681748</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-34.20528, -70.68009</t>
+          <t>-34.04268, -70.68175</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026/09/22 14:21:15</t>
+          <t>2026/09/25 00:59:47</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>-34.205278, -70.680101</t>
+          <t>-34.042755, -70.681629</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>-34.20528, -70.68010</t>
+          <t>-34.04275, -70.68163</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>00:16:57</t>
+          <t>58:58:52</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="M117" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026/09/22 14:08:06</t>
+          <t>2026/09/22 14:04:18</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>-34.205325, -70.680145</t>
+          <t>-34.205283, -70.68009</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>-34.20533, -70.68014</t>
+          <t>-34.20528, -70.68009</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026/09/22 14:32:19</t>
+          <t>2026/09/22 14:21:15</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>-34.2062216, -70.6739366</t>
+          <t>-34.205278, -70.680101</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>-34.20622, -70.67394</t>
+          <t>-34.20528, -70.68010</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>00:24:13</t>
+          <t>00:16:57</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0.59</v>
+        <v>0.01</v>
       </c>
       <c r="M118" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N118" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7330,175 +7330,175 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026/09/22 14:08:54</t>
+          <t>2026/09/22 14:08:06</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>-34.2055366, -70.676625</t>
+          <t>-34.205325, -70.680145</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-34.20554, -70.67663</t>
+          <t>-34.20533, -70.68014</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026/09/22 14:21:21</t>
+          <t>2026/09/22 14:32:19</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>-34.2051366, -70.6775233</t>
+          <t>-34.2062216, -70.6739366</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>-34.20514, -70.67752</t>
+          <t>-34.20622, -70.67394</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>00:12:27</t>
+          <t>00:24:13</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0.1</v>
+        <v>0.59</v>
       </c>
       <c r="M119" t="n">
         <v>9</v>
       </c>
       <c r="N119" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026/09/22 14:21:19</t>
+          <t>2026/09/22 14:08:54</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>-34.205284, -70.680111</t>
+          <t>-34.2055366, -70.676625</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>-34.20528, -70.68011</t>
+          <t>-34.20554, -70.67663</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026/09/22 15:42:35</t>
+          <t>2026/09/22 14:21:21</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>-34.205281, -70.680094</t>
+          <t>-34.2051366, -70.6775233</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>-34.20528, -70.68009</t>
+          <t>-34.20514, -70.67752</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>01:21:16</t>
+          <t>00:12:27</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="M120" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N120" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026/09/22 14:22:36</t>
+          <t>2026/09/22 14:21:19</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>-34.2043133, -70.6790683</t>
+          <t>-34.205284, -70.680111</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-34.20431, -70.67907</t>
+          <t>-34.20528, -70.68011</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026/09/22 14:43:21</t>
+          <t>2026/09/22 15:42:35</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>-34.2065066, -70.67392</t>
+          <t>-34.205281, -70.680094</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>-34.20651, -70.67392</t>
+          <t>-34.20528, -70.68009</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>00:20:45</t>
+          <t>01:21:16</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0.79</v>
+        <v>0.02</v>
       </c>
       <c r="M121" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="N121" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7507,47 +7507,47 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026/09/22 14:33:34</t>
+          <t>2026/09/22 14:22:36</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>-34.2063166, -70.6738783</t>
+          <t>-34.2043133, -70.6790683</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>-34.20632, -70.67388</t>
+          <t>-34.20431, -70.67907</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026/09/22 14:39:58</t>
+          <t>2026/09/22 14:43:21</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>-34.2065166, -70.673925</t>
+          <t>-34.2065066, -70.67392</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>-34.20652, -70.67392</t>
+          <t>-34.20651, -70.67392</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>00:06:24</t>
+          <t>00:20:45</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0.04</v>
+        <v>0.79</v>
       </c>
       <c r="M122" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="N122" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="123">
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7566,116 +7566,116 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026/09/22 14:41:13</t>
+          <t>2026/09/22 14:33:34</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>-34.2069716, -70.6750733</t>
+          <t>-34.2063166, -70.6738783</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-34.20697, -70.67507</t>
+          <t>-34.20632, -70.67388</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026/09/22 14:57:28</t>
+          <t>2026/09/22 14:39:58</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>-34.2084233, -70.67758</t>
+          <t>-34.2065166, -70.673925</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>-34.20842, -70.67758</t>
+          <t>-34.20652, -70.67392</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>00:16:15</t>
+          <t>00:06:24</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0.31</v>
+        <v>0.04</v>
       </c>
       <c r="M123" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="N123" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C124" t="n">
+        <v>14</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>2026/09/22 14:41:13</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>-34.2069716, -70.6750733</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>-34.20697, -70.67507</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>2026/09/22 14:57:28</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>-34.2084233, -70.67758</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>-34.20842, -70.67758</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>00:16:15</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M124" t="n">
         <v>11</v>
       </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>2026/09/22 14:43:51</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>-34.2070549, -70.6749516</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>-34.20705, -70.67495</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>2026/09/22 15:15:44</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>-34.2042683, -70.6788383</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>-34.20427, -70.67884</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>00:31:53</t>
-        </is>
-      </c>
-      <c r="L124" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="M124" t="n">
-        <v>12</v>
-      </c>
       <c r="N124" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -7684,57 +7684,57 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026/09/22 14:58:43</t>
+          <t>2026/09/22 14:43:51</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>-34.2088333, -70.6783066</t>
+          <t>-34.2070549, -70.6749516</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>-34.20883, -70.67831</t>
+          <t>-34.20705, -70.67495</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026/09/22 15:21:51</t>
+          <t>2026/09/22 15:15:44</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>-34.2055383, -70.676695</t>
+          <t>-34.2042683, -70.6788383</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>-34.20554, -70.67669</t>
+          <t>-34.20427, -70.67884</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>00:23:08</t>
+          <t>00:31:53</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0.48</v>
+        <v>0.61</v>
       </c>
       <c r="M125" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="N125" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -7743,57 +7743,57 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026/09/22 15:15:37</t>
+          <t>2026/09/22 14:58:43</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>-34.345967, -71.12576</t>
+          <t>-34.2088333, -70.6783066</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>-34.34597, -71.12576</t>
+          <t>-34.20883, -70.67831</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026/09/23 08:39:27</t>
+          <t>2026/09/22 15:21:51</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>-34.346894, -71.125631</t>
+          <t>-34.2055383, -70.676695</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>-34.34689, -71.12563</t>
+          <t>-34.20554, -70.67669</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>17:23:50</t>
+          <t>00:23:08</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0.18</v>
+        <v>0.48</v>
       </c>
       <c r="M126" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="N126" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -7802,57 +7802,57 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026/09/22 15:15:58</t>
+          <t>2026/09/22 15:15:37</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>-34.20431, -70.6790883</t>
+          <t>-34.345967, -71.12576</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>-34.20431, -70.67909</t>
+          <t>-34.34597, -71.12576</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026/09/22 17:13:29</t>
+          <t>2026/09/23 08:39:27</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>-34.1917016, -70.709965</t>
+          <t>-34.346894, -71.125631</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>-34.19170, -70.70996</t>
+          <t>-34.34689, -71.12563</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>01:57:31</t>
+          <t>17:23:50</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>3.34</v>
+        <v>0.18</v>
       </c>
       <c r="M127" t="n">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="N127" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -7861,47 +7861,47 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026/09/22 15:22:55</t>
+          <t>2026/09/22 15:15:58</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>-34.2053466, -70.6802216</t>
+          <t>-34.20431, -70.6790883</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>-34.20535, -70.68022</t>
+          <t>-34.20431, -70.67909</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026/09/22 15:35:53</t>
+          <t>2026/09/22 17:13:29</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>-34.2053333, -70.6803533</t>
+          <t>-34.1917016, -70.709965</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>-34.20533, -70.68035</t>
+          <t>-34.19170, -70.70996</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>00:12:58</t>
+          <t>01:57:31</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0.58</v>
+        <v>3.34</v>
       </c>
       <c r="M128" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="N128" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="129">
@@ -7911,7 +7911,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -7920,57 +7920,57 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026/09/22 15:36:03</t>
+          <t>2026/09/22 15:22:55</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>-34.2053316, -70.680195</t>
+          <t>-34.2053466, -70.6802216</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>-34.20533, -70.68019</t>
+          <t>-34.20535, -70.68022</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026/09/22 15:49:03</t>
+          <t>2026/09/22 15:35:53</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>-34.2034616, -70.6782916</t>
+          <t>-34.2053333, -70.6803533</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>-34.20346, -70.67829</t>
+          <t>-34.20533, -70.68035</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>00:13:00</t>
+          <t>00:12:58</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0.29</v>
+        <v>0.58</v>
       </c>
       <c r="M129" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="N129" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -7979,57 +7979,57 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026/09/22 15:43:02</t>
+          <t>2026/09/22 15:36:03</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>-34.205312, -70.680106</t>
+          <t>-34.2053316, -70.680195</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>-34.20531, -70.68011</t>
+          <t>-34.20533, -70.68019</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026/09/22 16:29:48</t>
+          <t>2026/09/22 15:49:03</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>-34.205468, -70.677413</t>
+          <t>-34.2034616, -70.6782916</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>-34.20547, -70.67741</t>
+          <t>-34.20346, -70.67829</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>00:46:46</t>
+          <t>00:13:00</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="M130" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N130" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8038,116 +8038,116 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026/09/22 15:50:09</t>
+          <t>2026/09/22 15:43:02</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>-34.2034566, -70.6784233</t>
+          <t>-34.205312, -70.680106</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>-34.20346, -70.67842</t>
+          <t>-34.20531, -70.68011</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026/09/22 17:29:03</t>
+          <t>2026/09/22 16:29:48</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>-34.1678716, -70.7330333</t>
+          <t>-34.205468, -70.677413</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>-34.16787, -70.73303</t>
+          <t>-34.20547, -70.67741</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>01:38:54</t>
+          <t>00:46:46</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>9.210000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="M131" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="N131" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C132" t="n">
+        <v>18</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>2026/09/22 15:50:09</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>-34.2034566, -70.6784233</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>-34.20346, -70.67842</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>2026/09/22 17:29:03</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>-34.1678716, -70.7330333</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>-34.16787, -70.73303</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>01:38:54</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="M132" t="n">
+        <v>40</v>
+      </c>
+      <c r="N132" t="n">
         <v>16</v>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>2026/09/22 16:01:33</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>-32.8831633, -70.6123783</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>-32.88316, -70.61238</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>2026/09/22 16:13:01</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>-32.8823833, -70.6120583</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>-32.88238, -70.61206</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>00:11:28</t>
-        </is>
-      </c>
-      <c r="L132" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="M132" t="n">
-        <v>23</v>
-      </c>
-      <c r="N132" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8156,57 +8156,57 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026/09/22 16:06:10</t>
+          <t>2026/09/22 16:01:33</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>-33.3622, -70.6701283</t>
+          <t>-32.8831633, -70.6123783</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>-33.36220, -70.67013</t>
+          <t>-32.88316, -70.61238</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026/09/22 16:37:23</t>
+          <t>2026/09/22 16:13:01</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>-33.3532766, -70.6698133</t>
+          <t>-32.8823833, -70.6120583</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>-33.35328, -70.66981</t>
+          <t>-32.88238, -70.61206</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>00:31:13</t>
+          <t>00:11:28</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.18</v>
+        <v>0.13</v>
       </c>
       <c r="M133" t="n">
+        <v>23</v>
+      </c>
+      <c r="N133" t="n">
         <v>14</v>
-      </c>
-      <c r="N133" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8215,53 +8215,53 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026/09/22 16:14:16</t>
+          <t>2026/09/22 16:06:10</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>-32.8794133, -70.6088816</t>
+          <t>-33.3622, -70.6701283</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>-32.87941, -70.60888</t>
+          <t>-33.36220, -70.67013</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026/09/23 09:25:13</t>
+          <t>2026/09/22 16:37:23</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>-32.8843333, -70.6130366</t>
+          <t>-33.3532766, -70.6698133</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>-32.88433, -70.61304</t>
+          <t>-33.35328, -70.66981</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>17:10:57</t>
+          <t>00:31:13</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0.8</v>
+        <v>1.18</v>
       </c>
       <c r="M134" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="N134" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -8274,57 +8274,57 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026/09/22 16:30:48</t>
+          <t>2026/09/22 16:14:16</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>-34.205453, -70.677307</t>
+          <t>-32.8794133, -70.6088816</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>-34.20545, -70.67731</t>
+          <t>-32.87941, -70.60888</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026/09/23 11:13:11</t>
+          <t>2026/09/23 09:25:13</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>-34.204275, -70.67867</t>
+          <t>-32.8843333, -70.6130366</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>-34.20428, -70.67867</t>
+          <t>-32.88433, -70.61304</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>18:42:23</t>
+          <t>17:10:57</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0.23</v>
+        <v>0.8</v>
       </c>
       <c r="M135" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="N135" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8333,47 +8333,47 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026/09/22 16:37:38</t>
+          <t>2026/09/22 16:30:48</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>-33.353245, -70.6697983</t>
+          <t>-34.205453, -70.677307</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>-33.35325, -70.66980</t>
+          <t>-34.20545, -70.67731</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026/09/22 16:59:07</t>
+          <t>2026/09/23 11:13:11</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>-33.3623633, -70.6701316</t>
+          <t>-34.204275, -70.67867</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>-33.36236, -70.67013</t>
+          <t>-34.20428, -70.67867</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>00:21:29</t>
+          <t>18:42:23</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2.68</v>
+        <v>0.23</v>
       </c>
       <c r="M136" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="N136" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="137">
@@ -8383,66 +8383,66 @@
         </is>
       </c>
       <c r="C137" t="n">
+        <v>11</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>2026/09/22 16:37:38</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>-33.353245, -70.6697983</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>-33.35325, -70.66980</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>2026/09/22 16:59:07</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>-33.3623633, -70.6701316</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>-33.36236, -70.67013</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>00:21:29</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="M137" t="n">
+        <v>22</v>
+      </c>
+      <c r="N137" t="n">
         <v>12</v>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>2026/09/22 16:59:32</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>-33.3622083, -70.6701349</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>-33.36221, -70.67013</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>2026/09/22 18:38:41</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>-33.4762516, -70.6983599</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>-33.47625, -70.69836</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>01:39:09</t>
-        </is>
-      </c>
-      <c r="L137" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="M137" t="n">
-        <v>108</v>
-      </c>
-      <c r="N137" t="n">
-        <v>28</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8451,44 +8451,44 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026/09/22 17:14:44</t>
+          <t>2026/09/22 16:59:32</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>-34.191225, -70.70989</t>
+          <t>-33.3622083, -70.6701349</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>-34.19123, -70.70989</t>
+          <t>-33.36221, -70.67013</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026/09/22 17:35:00</t>
+          <t>2026/09/22 18:38:41</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>-34.167885, -70.73306</t>
+          <t>-33.4762516, -70.6983599</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>-34.16788, -70.73306</t>
+          <t>-33.47625, -70.69836</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>00:20:16</t>
+          <t>01:39:09</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>4.19</v>
+        <v>21.59</v>
       </c>
       <c r="M138" t="n">
-        <v>63</v>
+        <v>108</v>
       </c>
       <c r="N138" t="n">
         <v>28</v>
@@ -8497,11 +8497,11 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8510,57 +8510,57 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026/09/22 17:30:18</t>
+          <t>2026/09/22 17:14:44</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>-34.1676883, -70.7329933</t>
+          <t>-34.191225, -70.70989</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>-34.16769, -70.73299</t>
+          <t>-34.19123, -70.70989</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026/09/23 07:27:58</t>
+          <t>2026/09/22 17:35:00</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>-34.2052533, -70.6823733</t>
+          <t>-34.167885, -70.73306</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>-34.20525, -70.68237</t>
+          <t>-34.16788, -70.73306</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>13:57:40</t>
+          <t>00:20:16</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>7.25</v>
+        <v>4.19</v>
       </c>
       <c r="M139" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="N139" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -8569,57 +8569,57 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026/09/22 17:36:09</t>
+          <t>2026/09/22 17:30:18</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>-34.1677383, -70.73303</t>
+          <t>-34.1676883, -70.7329933</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>-34.16774, -70.73303</t>
+          <t>-34.16769, -70.73299</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026/09/23 07:36:14</t>
+          <t>2026/09/23 07:27:58</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>-34.2042699, -70.6791416</t>
+          <t>-34.2052533, -70.6823733</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>-34.20427, -70.67914</t>
+          <t>-34.20525, -70.68237</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>14:00:05</t>
+          <t>13:57:40</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>7.56</v>
+        <v>7.25</v>
       </c>
       <c r="M140" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N140" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8628,57 +8628,57 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026/09/22 18:39:56</t>
+          <t>2026/09/22 17:36:09</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>-33.4761133, -70.6985049</t>
+          <t>-34.1677383, -70.73303</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>-33.47611, -70.69850</t>
+          <t>-34.16774, -70.73303</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026/09/23 08:56:03</t>
+          <t>2026/09/23 07:36:14</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>-33.3623133, -70.6701033</t>
+          <t>-34.2042699, -70.6791416</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>-33.36231, -70.67010</t>
+          <t>-34.20427, -70.67914</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>14:16:07</t>
+          <t>14:00:05</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>18.71</v>
+        <v>7.56</v>
       </c>
       <c r="M141" t="n">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="N141" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -8687,112 +8687,112 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026/09/23 08:39:46</t>
+          <t>2026/09/22 18:39:56</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>-34.346866, -71.12567</t>
+          <t>-33.4761133, -70.6985049</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>-34.34687, -71.12567</t>
+          <t>-33.47611, -70.69850</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026/09/23 09:51:53</t>
+          <t>2026/09/23 08:56:03</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>-34.347209, -71.12573</t>
+          <t>-33.3623133, -70.6701033</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>-34.34721, -71.12573</t>
+          <t>-33.36231, -70.67010</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>01:12:07</t>
+          <t>14:16:07</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0.33</v>
+        <v>18.71</v>
       </c>
       <c r="M142" t="n">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="N142" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>2026/09/23 08:39:46</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>-34.346866, -71.12567</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>-34.34687, -71.12567</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>2026/09/23 09:51:53</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>-34.347209, -71.12573</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>-34.34721, -71.12573</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>01:12:07</t>
+        </is>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M143" t="n">
+        <v>4</v>
+      </c>
+      <c r="N143" t="n">
         <v>3</v>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>2026/09/23 11:04:04</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>-33.360175, -70.807263</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>-33.36017, -70.80726</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>2026/09/23 14:22:54</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>-33.360909, -70.804812</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>-33.36091, -70.80481</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>03:18:50</t>
-        </is>
-      </c>
-      <c r="L143" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="M143" t="n">
-        <v>0</v>
-      </c>
-      <c r="N143" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -8805,53 +8805,53 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026/09/23 11:23:52</t>
+          <t>2026/09/23 10:36:28</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>-34.205473, -70.677304</t>
+          <t>-33.360171, -70.806817</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>-34.20547, -70.67730</t>
+          <t>-33.36017, -70.80682</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026/09/23 11:42:51</t>
+          <t>2026/09/23 11:03:21</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>-34.205071, -70.68017</t>
+          <t>-33.360175, -70.807263</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>-34.20507, -70.68017</t>
+          <t>-33.36017, -70.80726</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>00:18:59</t>
+          <t>00:26:53</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0.39</v>
+        <v>0.15</v>
       </c>
       <c r="M144" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -8859,108 +8859,108 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026/09/23 11:43:10</t>
+          <t>2026/09/23 11:04:04</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>-34.205153, -70.680117</t>
+          <t>-33.360175, -70.807263</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>-34.20515, -70.68012</t>
+          <t>-33.36017, -70.80726</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026/09/23 12:59:00</t>
+          <t>2026/09/23 14:22:54</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>-34.205237, -70.680109</t>
+          <t>-33.360909, -70.804812</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>-34.20524, -70.68011</t>
+          <t>-33.36091, -70.80481</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>01:15:50</t>
+          <t>03:18:50</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0.02</v>
+        <v>0.24</v>
       </c>
       <c r="M145" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026/09/23 11:50:55</t>
+          <t>2026/09/23 11:23:52</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>-34.345954, -71.125788</t>
+          <t>-34.205473, -70.677304</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>-34.34595, -71.12579</t>
+          <t>-34.20547, -70.67730</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026/09/24 11:13:19</t>
+          <t>2026/09/23 11:42:51</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>-34.346426, -71.125197</t>
+          <t>-34.205071, -70.68017</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>-34.34643, -71.12520</t>
+          <t>-34.20507, -70.68017</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>23:22:24</t>
+          <t>00:18:59</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0.1</v>
+        <v>0.39</v>
       </c>
       <c r="M146" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N146" t="n">
         <v>3</v>
@@ -8973,53 +8973,53 @@
         </is>
       </c>
       <c r="C147" t="n">
+        <v>3</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>2026/09/23 11:43:10</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>-34.205153, -70.680117</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>-34.20515, -70.68012</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>2026/09/23 12:59:00</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>-34.205237, -70.680109</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>-34.20524, -70.68011</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>01:15:50</t>
+        </is>
+      </c>
+      <c r="L147" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M147" t="n">
         <v>4</v>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>2026/09/23 12:59:11</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>-34.205247, -70.680103</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>-34.20525, -70.68010</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>2026/09/23 13:10:45</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>-34.205284, -70.680106</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>-34.20528, -70.68011</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>00:11:34</t>
-        </is>
-      </c>
-      <c r="L147" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="M147" t="n">
-        <v>3</v>
       </c>
       <c r="N147" t="n">
         <v>3</v>
@@ -9028,66 +9028,66 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026/09/23 14:16:58</t>
+          <t>2026/09/23 11:50:55</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>-34.2052916, -70.6802883</t>
+          <t>-34.345954, -71.125788</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>-34.20529, -70.68029</t>
+          <t>-34.34595, -71.12579</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026/09/23 14:37:23</t>
+          <t>2026/09/24 11:13:19</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>-34.206435, -70.6737383</t>
+          <t>-34.346426, -71.125197</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>-34.20643, -70.67374</t>
+          <t>-34.34643, -71.12520</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>00:20:25</t>
+          <t>23:22:24</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="M148" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="N148" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -9095,52 +9095,52 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026/09/23 14:23:01</t>
+          <t>2026/09/23 12:59:11</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>-33.360909, -70.804812</t>
+          <t>-34.205247, -70.680103</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>-33.36091, -70.80481</t>
+          <t>-34.20525, -70.68010</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026/09/23 17:36:03</t>
+          <t>2026/09/23 13:10:45</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>-32.83989, -70.961898</t>
+          <t>-34.205284, -70.680106</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>-32.83989, -70.96190</t>
+          <t>-34.20528, -70.68011</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>03:13:02</t>
+          <t>00:11:34</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>60.55</v>
+        <v>0.01</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150">
@@ -9150,7 +9150,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9159,57 +9159,57 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026/09/23 14:37:27</t>
+          <t>2026/09/23 14:16:58</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>-34.2064416, -70.6737533</t>
+          <t>-34.2052916, -70.6802883</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>-34.20644, -70.67375</t>
+          <t>-34.20529, -70.68029</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026/09/23 15:10:37</t>
+          <t>2026/09/23 14:37:23</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>-34.2063866, -70.6737133</t>
+          <t>-34.206435, -70.6737383</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>-34.20639, -70.67371</t>
+          <t>-34.20643, -70.67374</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>00:33:10</t>
+          <t>00:20:25</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>1.35</v>
+        <v>0.7</v>
       </c>
       <c r="M150" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N150" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9218,106 +9218,106 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026/09/23 15:10:42</t>
+          <t>2026/09/23 14:23:01</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>-34.2064283, -70.6737516</t>
+          <t>-33.360909, -70.804812</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>-34.20643, -70.67375</t>
+          <t>-33.36091, -70.80481</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026/09/23 15:37:17</t>
+          <t>2026/09/23 17:36:03</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>-34.2088683, -70.678425</t>
+          <t>-32.83989, -70.961898</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>-34.20887, -70.67843</t>
+          <t>-32.83989, -70.96190</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>00:26:35</t>
+          <t>03:13:02</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0.51</v>
+        <v>60.55</v>
       </c>
       <c r="M151" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026/09/23 15:15:14</t>
+          <t>2026/09/23 14:37:27</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>-33.3671916, -70.6958816</t>
+          <t>-34.2064416, -70.6737533</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>-33.36719, -70.69588</t>
+          <t>-34.20644, -70.67375</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026/09/25 23:15:34</t>
+          <t>2026/09/23 15:10:37</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>-33.3671916, -70.6958816</t>
+          <t>-34.2063866, -70.6737133</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>-33.36719, -70.69588</t>
+          <t>-34.20639, -70.67371</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>56:00:20</t>
+          <t>00:33:10</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M152" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="153">
@@ -9327,7 +9327,7 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9336,116 +9336,116 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026/09/23 15:38:11</t>
+          <t>2026/09/23 15:10:42</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>-34.2088583, -70.67846</t>
+          <t>-34.2064283, -70.6737516</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>-34.20886, -70.67846</t>
+          <t>-34.20643, -70.67375</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026/09/23 16:38:40</t>
+          <t>2026/09/23 15:37:17</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>-34.167865, -70.7330533</t>
+          <t>-34.2088683, -70.678425</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>-34.16786, -70.73305</t>
+          <t>-34.20887, -70.67843</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>01:00:29</t>
+          <t>00:26:35</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>8.35</v>
+        <v>0.51</v>
       </c>
       <c r="M153" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="N153" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026/09/23 16:39:55</t>
+          <t>2026/09/23 15:15:14</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>-34.1677683, -70.7330216</t>
+          <t>-33.3671916, -70.6958816</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>-34.16777, -70.73302</t>
+          <t>-33.36719, -70.69588</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026/09/24 07:33:51</t>
+          <t>2026/09/26 23:15:34</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>-34.2064066, -70.6737083</t>
+          <t>-33.3671916, -70.6958816</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>-34.20641, -70.67371</t>
+          <t>-33.36719, -70.69588</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>14:53:56</t>
+          <t>80:00:20</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>8.15</v>
+        <v>0</v>
       </c>
       <c r="M154" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9454,57 +9454,57 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026/09/23 17:36:46</t>
+          <t>2026/09/23 15:38:11</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>-32.83989, -70.961898</t>
+          <t>-34.2088583, -70.67846</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>-32.83989, -70.96190</t>
+          <t>-34.20886, -70.67846</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026/09/24 11:26:33</t>
+          <t>2026/09/23 16:38:40</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>-33.360146, -70.806869</t>
+          <t>-34.167865, -70.7330533</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>-33.36015, -70.80687</t>
+          <t>-34.16786, -70.73305</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>17:49:47</t>
+          <t>01:00:29</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>61.8</v>
+        <v>8.35</v>
       </c>
       <c r="M155" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9513,57 +9513,57 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026/09/24 10:27:55</t>
+          <t>2026/09/23 16:39:55</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>-34.205423, -70.677214</t>
+          <t>-34.1677683, -70.7330216</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>-34.20542, -70.67721</t>
+          <t>-34.16777, -70.73302</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026/09/24 13:20:48</t>
+          <t>2026/09/24 07:33:51</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>-34.206143, -70.674138</t>
+          <t>-34.2064066, -70.6737083</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>-34.20614, -70.67414</t>
+          <t>-34.20641, -70.67371</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>02:52:53</t>
+          <t>14:53:56</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0.4</v>
+        <v>8.15</v>
       </c>
       <c r="M156" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="N156" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -9572,106 +9572,106 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026/09/24 13:21:48</t>
+          <t>2026/09/23 17:36:46</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>-34.206341, -70.673913</t>
+          <t>-32.83989, -70.961898</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>-34.20634, -70.67391</t>
+          <t>-32.83989, -70.96190</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026/09/24 14:17:13</t>
+          <t>2026/09/24 11:26:33</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>-34.205473, -70.677302</t>
+          <t>-33.360146, -70.806869</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>-34.20547, -70.67730</t>
+          <t>-33.36015, -70.80687</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>00:55:25</t>
+          <t>17:49:47</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0.37</v>
+        <v>61.8</v>
       </c>
       <c r="M157" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N157" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>LPR20251A02800014-DS</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026/09/24 13:27:02</t>
+          <t>2026/09/24 10:27:55</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>-34.346514, -71.125324</t>
+          <t>-34.205423, -70.677214</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>-34.34651, -71.12532</t>
+          <t>-34.20542, -70.67721</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026/09/24 15:14:47</t>
+          <t>2026/09/24 13:20:48</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>-34.346198, -71.125541</t>
+          <t>-34.206143, -70.674138</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>-34.34620, -71.12554</t>
+          <t>-34.20614, -70.67414</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>01:47:45</t>
+          <t>02:52:53</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0.04</v>
+        <v>0.4</v>
       </c>
       <c r="M158" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N158" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="159">
@@ -9681,62 +9681,62 @@
         </is>
       </c>
       <c r="C159" t="n">
+        <v>3</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>2026/09/24 13:21:48</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>-34.206341, -70.673913</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>-34.20634, -70.67391</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>2026/09/24 14:17:13</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>-34.205473, -70.677302</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>-34.20547, -70.67730</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>00:55:25</t>
+        </is>
+      </c>
+      <c r="L159" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="M159" t="n">
         <v>4</v>
       </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>2026/09/24 14:17:38</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>-34.205446, -70.677348</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>-34.20545, -70.67735</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>2026/09/25 23:11:06</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>-34.205372, -70.677301</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>-34.20537, -70.67730</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>32:53:28</t>
-        </is>
-      </c>
-      <c r="L159" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="M159" t="n">
-        <v>0</v>
-      </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -9749,41 +9749,41 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026/09/24 15:23:54</t>
+          <t>2026/09/24 13:27:02</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>-34.205297, -70.680202</t>
+          <t>-34.346514, -71.125324</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>-34.20530, -70.68020</t>
+          <t>-34.34651, -71.12532</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026/09/24 15:30:47</t>
+          <t>2026/09/24 15:14:47</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>-34.205297, -70.680211</t>
+          <t>-34.346198, -71.125541</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>-34.20530, -70.68021</t>
+          <t>-34.34620, -71.12554</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>00:06:53</t>
+          <t>01:47:45</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="M160" t="n">
         <v>3</v>
@@ -9795,60 +9795,60 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>LPR20251A02800014-DS</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026/09/24 15:31:46</t>
+          <t>2026/09/24 14:17:38</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>-34.20527, -70.680189</t>
+          <t>-34.205446, -70.677348</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>-34.20527, -70.68019</t>
+          <t>-34.20545, -70.67735</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026/09/24 15:48:25</t>
+          <t>2026/09/26 23:11:38</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>-34.20548, -70.677407</t>
+          <t>-34.205388, -70.677352</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>-34.20548, -70.67741</t>
+          <t>-34.20539, -70.67735</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>00:16:39</t>
+          <t>56:54:00</t>
         </is>
       </c>
       <c r="L161" t="n">
-        <v>0.34</v>
+        <v>0.03</v>
       </c>
       <c r="M161" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -9858,7 +9858,7 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -9867,116 +9867,116 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026/09/25 10:57:32</t>
+          <t>2026/09/24 15:23:54</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>-34.205444, -70.677298</t>
+          <t>-34.205297, -70.680202</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>-34.20544, -70.67730</t>
+          <t>-34.20530, -70.68020</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026/09/25 23:03:51</t>
+          <t>2026/09/24 15:30:47</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>-34.205393, -70.677304</t>
+          <t>-34.205297, -70.680211</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>-34.20539, -70.67730</t>
+          <t>-34.20530, -70.68021</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>12:06:19</t>
+          <t>00:06:53</t>
         </is>
       </c>
       <c r="L162" t="n">
         <v>0.01</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C163" t="n">
+        <v>7</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>2026/09/24 15:31:46</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>-34.20527, -70.680189</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>-34.20527, -70.68019</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>2026/09/24 15:48:25</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>-34.20548, -70.677407</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>-34.20548, -70.67741</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>00:16:39</t>
+        </is>
+      </c>
+      <c r="L163" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M163" t="n">
         <v>4</v>
       </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>2026/09/25 15:13:11</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>-33.4364116, -70.62956</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>-33.43641, -70.62956</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>2026/09/25 23:13:11</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>-33.4364116, -70.62956</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>-33.43641, -70.62956</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="L163" t="n">
-        <v>0</v>
-      </c>
-      <c r="M163" t="n">
-        <v>0</v>
-      </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -9985,41 +9985,41 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026/09/25 15:44:19</t>
+          <t>2026/09/25 10:57:32</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>-33.0873266, -71.3623483</t>
+          <t>-34.205444, -70.677298</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>-33.08733, -71.36235</t>
+          <t>-34.20544, -70.67730</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026/09/25 23:22:42</t>
+          <t>2026/09/26 22:46:17</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>-33.087235, -71.3621816</t>
+          <t>-34.205469, -70.677165</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>-33.08723, -71.36218</t>
+          <t>-34.20547, -70.67717</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>07:38:23</t>
+          <t>35:48:45</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="M164" t="n">
         <v>0</v>
@@ -10031,11 +10031,11 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10044,41 +10044,41 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026/09/25 16:21:18</t>
+          <t>2026/09/25 15:13:11</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>-32.7430816, -70.7298016</t>
+          <t>-33.4364116, -70.62956</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>-32.74308, -70.72980</t>
+          <t>-33.43641, -70.62956</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026/09/25 23:02:22</t>
+          <t>2026/09/26 23:13:11</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>-32.7430533, -70.729815</t>
+          <t>-33.4364116, -70.62956</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>-32.74305, -70.72982</t>
+          <t>-33.43641, -70.62956</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>06:41:04</t>
+          <t>32:00:00</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="M165" t="n">
         <v>0</v>
@@ -10090,11 +10090,11 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10103,41 +10103,41 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026/09/25 21:05:47</t>
+          <t>2026/09/25 16:21:18</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>-32.879215, -70.6087933</t>
+          <t>-32.7430816, -70.7298016</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>-32.87922, -70.60879</t>
+          <t>-32.74308, -70.72980</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026/09/25 23:05:47</t>
+          <t>2026/09/26 23:02:22</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>-32.879215, -70.6087933</t>
+          <t>-32.7430533, -70.729815</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>-32.87922, -70.60879</t>
+          <t>-32.74305, -70.72982</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>30:41:04</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="M166" t="n">
         <v>0</v>
@@ -10149,11 +10149,11 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10162,46 +10162,164 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026/09/25 21:24:28</t>
+          <t>2026/09/26 12:42:42</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>-33.4760983, -70.69852</t>
+          <t>-33.0873166, -71.3623233</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>-33.47610, -70.69852</t>
+          <t>-33.08732, -71.36232</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026/09/25 23:25:00</t>
+          <t>2026/09/26 23:01:00</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>-33.4760983, -70.69852</t>
+          <t>-33.087215, -71.362245</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>-33.47610, -70.69852</t>
+          <t>-33.08722, -71.36225</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>02:00:32</t>
+          <t>10:18:18</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="M167" t="n">
         <v>0</v>
       </c>
       <c r="N167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>SUZUKI CARRY SKDB-52</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>12</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>2026/09/26 18:33:58</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>-32.87922, -70.6088133</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>-32.87922, -70.60881</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>2026/09/26 22:33:58</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>-32.87922, -70.6088133</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>-32.87922, -70.60881</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>04:00:00</t>
+        </is>
+      </c>
+      <c r="L168" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0</v>
+      </c>
+      <c r="N168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>MITSUBISHI L200 LVHX-40</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>8</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>2026/09/26 18:42:13</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>-33.4761033, -70.698495</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>-33.47610, -70.69849</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>2026/09/26 22:42:13</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>-33.4761033, -70.698495</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>-33.47610, -70.69849</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>04:00:00</t>
+        </is>
+      </c>
+      <c r="L169" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10253,16 +10371,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1182.99</v>
+        <v>1509.36</v>
       </c>
       <c r="C2" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3">
@@ -10272,7 +10390,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>630.9299999999999</v>
+        <v>641.46</v>
       </c>
       <c r="C3" t="n">
         <v>15</v>
@@ -10291,10 +10409,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>909.71</v>
+        <v>911.66</v>
       </c>
       <c r="C4" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
@@ -10310,10 +10428,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>782.29</v>
+        <v>552.24</v>
       </c>
       <c r="C5" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -10329,10 +10447,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
         <v>4</v>
@@ -10370,10 +10488,10 @@
         <v>0.03</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -10405,10 +10523,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
@@ -10481,10 +10599,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1270.56</v>
+        <v>1334.63</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -10500,10 +10618,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>337.47</v>
+        <v>193.58</v>
       </c>
       <c r="C15" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
@@ -10563,7 +10681,7 @@
         <v>23</v>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
         <v>8</v>
@@ -10576,10 +10694,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1006.74</v>
+        <v>975.39</v>
       </c>
       <c r="C19" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D19" t="n">
         <v>2</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/09/26 22:56:06</t>
+          <t>2026/09/26 23:56:06</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>165:59:53</t>
+          <t>166:59:53</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026/09/26 22:50:57</t>
+          <t>2026/09/26 23:50:31</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>151:18:25</t>
+          <t>152:17:59</t>
         </is>
       </c>
       <c r="L38" t="n">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026/09/26 22:46:17</t>
+          <t>2026/09/26 23:46:41</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>35:48:45</t>
+          <t>36:49:09</t>
         </is>
       </c>
       <c r="L164" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -914,7 +914,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/09/27 22:50:57</t>
+          <t>2026/09/27 23:50:29</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>166:18:24</t>
+          <t>167:17:56</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/09/27 22:56:06</t>
+          <t>2026/09/27 23:56:06</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>165:59:57</t>
+          <t>166:59:57</t>
         </is>
       </c>
       <c r="L14" t="n">

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N162"/>
+  <dimension ref="A1:N165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -855,7 +855,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026/09/28 19:51:36</t>
+          <t>2026/09/28 23:51:14</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>163:19:03</t>
+          <t>167:18:41</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/09/28 19:56:10</t>
+          <t>2026/09/28 23:56:10</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>163:00:01</t>
+          <t>167:00:01</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026/09/28 19:22:30</t>
+          <t>2026/09/28 23:22:33</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>161:00:03</t>
+          <t>165:00:06</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026/09/28 19:43:31</t>
+          <t>2026/09/28 23:43:31</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>153:00:56</t>
+          <t>157:00:56</t>
         </is>
       </c>
       <c r="L53" t="n">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026/09/28 19:15:34</t>
+          <t>2026/09/28 23:15:34</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>124:00:20</t>
+          <t>128:00:20</t>
         </is>
       </c>
       <c r="L143" t="n">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026/09/28 19:46:21</t>
+          <t>2026/09/28 23:46:48</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>16:00:06</t>
+          <t>20:00:33</t>
         </is>
       </c>
       <c r="L159" t="n">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026/09/28 18:33:38</t>
+          <t>2026/09/28 22:33:38</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>06:00:00</t>
         </is>
       </c>
       <c r="L160" t="n">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026/09/28 18:34:03</t>
+          <t>2026/09/28 22:34:03</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>02:00:00</t>
+          <t>06:00:00</t>
         </is>
       </c>
       <c r="L161" t="n">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026/09/28 19:21:37</t>
+          <t>2026/09/28 23:21:37</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>00:49:41</t>
+          <t>04:49:41</t>
         </is>
       </c>
       <c r="L162" t="n">
@@ -9907,6 +9907,183 @@
         <v>0</v>
       </c>
       <c r="N162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>CHANGAN HUNTER TGPS-77</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>9</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>2026/09/28 19:08:50</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>-32.7975783, -70.8870583</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>-32.79758, -70.88706</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>2026/09/28 22:31:01</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>-32.7975783, -70.8870583</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>-32.79758, -70.88706</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>03:22:11</t>
+        </is>
+      </c>
+      <c r="L163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>MITSUBISHI L200 LVHX-40</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>14</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>2026/09/28 20:29:38</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>-33.4761233, -70.6985033</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>-33.47612, -70.69850</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>2026/09/28 22:29:38</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>-33.4761233, -70.6985033</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>-33.47612, -70.69850</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>02:00:00</t>
+        </is>
+      </c>
+      <c r="L164" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>SUZUKI CARRY SKDB-52</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>12</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>2026/09/28 20:41:53</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>-32.8791716, -70.6088033</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>-32.87917, -70.60880</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>2026/09/28 22:41:53</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>-32.8791716, -70.6088033</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>-32.87917, -70.60880</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>02:00:00</t>
+        </is>
+      </c>
+      <c r="L165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0</v>
+      </c>
+      <c r="N165" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9958,13 +10135,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1611.09</v>
+        <v>1611.06</v>
       </c>
       <c r="C2" t="n">
         <v>57</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>146</v>
@@ -10186,13 +10363,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1304.26</v>
+        <v>1322.27</v>
       </c>
       <c r="C14" t="n">
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>128</v>
@@ -10281,13 +10458,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>725.65</v>
+        <v>736.84</v>
       </c>
       <c r="C19" t="n">
         <v>75</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>134</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,13 +446,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N142"/>
+  <dimension ref="A1:N133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Desde : 2026/09/23 04:00:00   Hasta : 2026/09/30 03:59:59</t>
+          <t>Desde : 2026/09/24 04:00:00   Hasta : 2026/10/01 03:59:59</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -540,52 +540,52 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026/09/23 00:05:27</t>
+          <t>2026/09/24 00:05:48</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-34.042629, -70.681718</t>
+          <t>-32.79762, -70.887105</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-34.04263, -70.68172</t>
+          <t>-32.79762, -70.88711</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026/09/25 00:59:47</t>
+          <t>2026/09/24 07:51:00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-34.042755, -70.681629</t>
+          <t>-33.3672399, -70.6965616</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-34.04275, -70.68163</t>
+          <t>-33.36724, -70.69656</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>48:54:20</t>
+          <t>07:45:12</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.07000000000000001</v>
+        <v>92.41</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
@@ -604,17 +604,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026/09/23 00:11:36</t>
+          <t>2026/09/24 00:11:22</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-34.205407, -70.677292</t>
+          <t>-34.205566, -70.677323</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-34.20541, -70.67729</t>
+          <t>-34.20557, -70.67732</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -634,11 +634,11 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>25:02:22</t>
+          <t>01:02:36</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="M5" t="n">
         <v>7</v>
@@ -650,7 +650,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -663,47 +663,47 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026/09/23 00:17:28</t>
+          <t>2026/09/24 00:13:52</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-34.345995, -71.125727</t>
+          <t>-33.4361833, -70.6295283</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-34.34600, -71.12573</t>
+          <t>-33.43618, -70.62953</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026/09/23 08:39:27</t>
+          <t>2026/09/25 07:13:15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-34.346894, -71.125631</t>
+          <t>-33.4461766, -70.6193216</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-34.34689, -71.12563</t>
+          <t>-33.44618, -70.61932</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>08:21:59</t>
+          <t>30:59:23</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.18</v>
+        <v>2.19</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -722,7 +722,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026/09/23 00:22:44</t>
+          <t>2026/09/24 00:22:58</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -737,26 +737,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026/09/29 23:23:19</t>
+          <t>2026/09/30 01:24:53</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-34.876401, -71.12726</t>
+          <t>-34.876425, -71.127141</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-34.87640, -71.12726</t>
+          <t>-34.87642, -71.12714</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>167:00:35</t>
+          <t>145:01:55</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>LPR20251V02900023-LL</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -776,58 +776,58 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026/09/23 00:26:40</t>
+          <t>2026/09/24 00:31:38</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-34.1676883, -70.7329933</t>
+          <t>-33.899801, -71.429488</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-34.16769, -70.73299</t>
+          <t>-33.89980, -71.42949</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026/09/23 07:27:58</t>
+          <t>2026/09/25 01:34:09</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-34.2052533, -70.6823733</t>
+          <t>-33.899779, -71.42949</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-34.20525, -70.68237</t>
+          <t>-33.89978, -71.42949</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>07:01:18</t>
+          <t>25:02:31</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>7.25</v>
+        <v>0.02</v>
       </c>
       <c r="M8" t="n">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -840,53 +840,53 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026/09/23 00:27:39</t>
+          <t>2026/09/24 00:33:55</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-33.4365033, -70.629035</t>
+          <t>-33.360003, -70.807038</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-33.43650, -70.62904</t>
+          <t>-33.36000, -70.80704</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026/09/23 06:03:27</t>
+          <t>2026/09/30 11:49:06</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-33.4462, -70.6250433</t>
+          <t>-33.359523, -70.80683</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-33.44620, -70.62504</t>
+          <t>-33.35952, -70.80683</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>05:35:48</t>
+          <t>155:15:11</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.46</v>
+        <v>0.1</v>
       </c>
       <c r="M9" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="N9" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LPR20251V02900023-LL</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -894,58 +894,58 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026/09/23 00:31:22</t>
+          <t>2026/09/24 00:34:27</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-33.899554, -71.429312</t>
+          <t>-34.57985, -70.961438</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-33.89955, -71.42931</t>
+          <t>-34.57985, -70.96144</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/09/23 01:33:50</t>
+          <t>2026/09/28 01:38:35</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-33.899801, -71.429488</t>
+          <t>-34.579561, -70.961474</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-33.89980, -71.42949</t>
+          <t>-34.57956, -70.96147</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>01:02:28</t>
+          <t>97:04:08</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="M10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -958,53 +958,53 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026/09/23 00:32:25</t>
+          <t>2026/09/24 00:37:43</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-34.20544, -70.677285</t>
+          <t>-34.167765, -70.7330316</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-34.20544, -70.67728</t>
+          <t>-34.16777, -70.73303</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026/09/23 11:13:11</t>
+          <t>2026/09/24 07:25:03</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-34.204275, -70.67867</t>
+          <t>-34.2042466, -70.67914</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-34.20428, -70.67867</t>
+          <t>-34.20425, -70.67914</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>10:40:46</t>
+          <t>06:47:20</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.23</v>
+        <v>7.61</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1012,58 +1012,58 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026/09/23 00:32:32</t>
+          <t>2026/09/24 00:40:00</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-33.360046, -70.807163</t>
+          <t>-34.1677683, -70.7330216</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-33.36005, -70.80716</t>
+          <t>-34.16777, -70.73302</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026/09/29 23:51:15</t>
+          <t>2026/09/24 07:33:51</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-33.35999, -70.807059</t>
+          <t>-34.2064066, -70.6737083</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80706</t>
+          <t>-34.20641, -70.67371</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>167:18:43</t>
+          <t>06:53:51</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.07000000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>LPR20251E02900022</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1076,53 +1076,53 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026/09/23 00:34:53</t>
+          <t>2026/09/24 00:43:02</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-34.580059, -70.961183</t>
+          <t>-33.366736, -70.696931</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-34.58006, -70.96118</t>
+          <t>-33.36674, -70.69693</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026/09/23 01:37:53</t>
+          <t>2026/09/30 23:43:56</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-34.57985, -70.961438</t>
+          <t>-33.36746, -70.69652</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-34.57985, -70.96144</t>
+          <t>-33.36746, -70.69652</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>01:03:00</t>
+          <t>167:00:54</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1130,58 +1130,58 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026/09/23 00:40:02</t>
+          <t>2026/09/24 00:51:55</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-33.4761133, -70.6985049</t>
+          <t>-34.345954, -71.125788</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-33.47611, -70.69850</t>
+          <t>-34.34595, -71.12579</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/09/23 08:56:03</t>
+          <t>2026/09/24 11:13:19</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-33.3623133, -70.6701033</t>
+          <t>-34.346426, -71.125197</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-33.36231, -70.67010</t>
+          <t>-34.34643, -71.12520</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>08:16:01</t>
+          <t>10:21:24</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>18.71</v>
+        <v>0.1</v>
       </c>
       <c r="M14" t="n">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LPR20251E02900022</t>
+          <t>LPR20251T02800022</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1194,53 +1194,53 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026/09/23 00:43:01</t>
+          <t>2026/09/24 00:56:11</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-33.366736, -70.696931</t>
+          <t>-33.367244, -70.69677</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-33.36674, -70.69693</t>
+          <t>-33.36724, -70.69677</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/09/29 23:43:31</t>
+          <t>2026/09/30 23:35:40</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-33.36746, -70.69652</t>
+          <t>-33.367244, -70.69677</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-33.36746, -70.69652</t>
+          <t>-33.36724, -70.69677</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>167:00:30</t>
+          <t>166:39:29</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LPR20251T02800022</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1248,58 +1248,58 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026/09/23 00:56:11</t>
+          <t>2026/09/24 00:58:36</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-33.367244, -70.69677</t>
+          <t>-34.20544, -70.677291</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-33.36724, -70.69677</t>
+          <t>-34.20544, -70.67729</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/09/29 23:56:10</t>
+          <t>2026/09/24 07:43:39</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-33.367244, -70.69677</t>
+          <t>-34.205371, -70.680097</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-33.36724, -70.69677</t>
+          <t>-34.20537, -70.68010</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>166:59:59</t>
+          <t>06:45:03</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1307,52 +1307,52 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026/09/23 01:36:09</t>
+          <t>2026/09/24 00:59:08</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-34.1677383, -70.73303</t>
+          <t>-34.042704, -70.681722</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-34.16774, -70.73303</t>
+          <t>-34.04270, -70.68172</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026/09/23 07:36:14</t>
+          <t>2026/09/25 00:59:47</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-34.2042699, -70.6791416</t>
+          <t>-34.042755, -70.681629</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-34.20427, -70.67914</t>
+          <t>-34.04275, -70.68163</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>06:00:05</t>
+          <t>24:00:39</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>7.56</v>
+        <v>0.06</v>
       </c>
       <c r="M17" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1371,47 +1371,47 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026/09/23 01:39:43</t>
+          <t>2026/09/24 01:14:09</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-32.8792549, -70.6087333</t>
+          <t>-32.879225, -70.6087533</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-32.87925, -70.60873</t>
+          <t>-32.87922, -70.60875</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026/09/23 09:25:13</t>
+          <t>2026/09/24 10:12:55</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-32.8843333, -70.6130366</t>
+          <t>-32.8853, -70.6115766</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-32.88433, -70.61304</t>
+          <t>-32.88530, -70.61158</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>07:45:30</t>
+          <t>08:58:46</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="M18" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="N18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
@@ -1430,53 +1430,53 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026/09/23 01:49:51</t>
+          <t>2026/09/24 01:15:34</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-33.3670883, -70.695945</t>
+          <t>-33.3671916, -70.6958816</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-33.36709, -70.69594</t>
+          <t>-33.36719, -70.69588</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026/09/23 10:55:24</t>
+          <t>2026/09/30 12:09:06</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-33.4484066, -70.7433416</t>
+          <t>-33.3507416, -70.6959183</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-33.44841, -70.74334</t>
+          <t>-33.35074, -70.69592</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>09:05:33</t>
+          <t>154:53:32</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.18</v>
+        <v>5.16</v>
       </c>
       <c r="M19" t="n">
-        <v>116</v>
+        <v>55</v>
       </c>
       <c r="N19" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1489,53 +1489,53 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026/09/23 01:57:54</t>
+          <t>2026/09/24 01:22:13</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-32.7976166, -70.88707</t>
+          <t>-33.47611, -70.6984816</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-32.79762, -70.88707</t>
+          <t>-33.47611, -70.69848</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026/09/23 08:00:37</t>
+          <t>2026/09/24 07:43:29</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-33.3673983, -70.6959983</t>
+          <t>-33.47625, -70.6982899</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-33.36740, -70.69600</t>
+          <t>-33.47625, -70.69829</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>06:02:43</t>
+          <t>06:21:16</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>92.58</v>
+        <v>11.16</v>
       </c>
       <c r="M20" t="n">
-        <v>121</v>
+        <v>59</v>
       </c>
       <c r="N20" t="n">
-        <v>59</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LPR20251V02900023-LL</t>
+          <t>LPR20251A02800014-DS</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1548,53 +1548,53 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026/09/23 02:31:21</t>
+          <t>2026/09/24 02:11:38</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-33.899801, -71.429488</t>
+          <t>-34.205163, -70.677135</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-33.89980, -71.42949</t>
+          <t>-34.20516, -70.67714</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026/09/25 01:34:09</t>
+          <t>2026/09/24 10:27:41</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-33.899779, -71.42949</t>
+          <t>-34.205424, -70.677213</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-33.89978, -71.42949</t>
+          <t>-34.20542, -70.67721</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>47:02:48</t>
+          <t>08:16:03</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="M21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1602,58 +1602,58 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026/09/23 02:34:25</t>
+          <t>2026/09/24 07:26:03</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-34.57985, -70.961438</t>
+          <t>-34.20527, -70.6800733</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-34.57985, -70.96144</t>
+          <t>-34.20527, -70.68007</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026/09/28 01:38:35</t>
+          <t>2026/09/24 07:46:51</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-34.579561, -70.961474</t>
+          <t>-34.2053083, -70.6801166</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-34.57956, -70.96147</t>
+          <t>-34.20531, -70.68012</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>119:04:10</t>
+          <t>00:20:48</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0.09</v>
+        <v>0.49</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1666,53 +1666,53 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026/09/23 06:04:42</t>
+          <t>2026/09/24 07:34:10</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-33.44527, -70.6199016</t>
+          <t>-34.206395, -70.673705</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-33.44527, -70.61990</t>
+          <t>-34.20640, -70.67370</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026/09/23 08:20:16</t>
+          <t>2026/09/24 08:21:39</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-33.366095, -70.6954866</t>
+          <t>-34.206395, -70.673705</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-33.36610, -70.69549</t>
+          <t>-34.20640, -70.67370</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>02:15:34</t>
+          <t>00:47:29</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>13.69</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>111</v>
+        <v>7</v>
       </c>
       <c r="N23" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1725,57 +1725,57 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026/09/23 07:29:13</t>
+          <t>2026/09/24 07:43:51</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-34.2053466, -70.680535</t>
+          <t>-33.4763183, -70.6983683</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-34.20535, -70.68054</t>
+          <t>-33.47632, -70.69837</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026/09/23 07:58:23</t>
+          <t>2026/09/24 09:17:47</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-34.2055949, -70.6771566</t>
+          <t>-33.3623316, -70.6701233</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-34.20559, -70.67716</t>
+          <t>-33.36233, -70.67012</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>00:29:10</t>
+          <t>01:33:56</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0.32</v>
+        <v>20.42</v>
       </c>
       <c r="M24" t="n">
-        <v>15</v>
+        <v>112</v>
       </c>
       <c r="N24" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1784,44 +1784,44 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026/09/23 07:31:36</t>
+          <t>2026/09/24 07:43:58</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-32.838368, -70.955489</t>
+          <t>-34.205304, -70.680147</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95549</t>
+          <t>-34.20530, -70.68015</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026/09/23 09:59:07</t>
+          <t>2026/09/24 08:22:55</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-33.360633, -70.806185</t>
+          <t>-34.20633, -70.673777</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-33.36063, -70.80618</t>
+          <t>-34.20633, -70.67378</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>02:27:31</t>
+          <t>00:38:57</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>62.16</v>
+        <v>0.74</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
         <v>3</v>
@@ -1830,11 +1830,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1843,47 +1843,47 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026/09/23 07:36:30</t>
+          <t>2026/09/24 07:44:12</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-34.204265, -70.6789633</t>
+          <t>-32.838355, -70.955539</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-34.20426, -70.67896</t>
+          <t>-32.83835, -70.95554</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026/09/23 08:16:27</t>
+          <t>2026/09/24 11:26:33</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-34.205675, -70.6760483</t>
+          <t>-33.360146, -70.806869</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-34.20567, -70.67605</t>
+          <t>-33.36015, -70.80687</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>00:39:57</t>
+          <t>03:42:21</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0.9399999999999999</v>
+        <v>60.81</v>
       </c>
       <c r="M26" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1902,47 +1902,47 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026/09/23 07:58:41</t>
+          <t>2026/09/24 07:47:04</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-34.2055683, -70.676595</t>
+          <t>-34.205235, -70.68009</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-34.20557, -70.67660</t>
+          <t>-34.20524, -70.68009</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026/09/23 08:07:06</t>
+          <t>2026/09/24 09:55:04</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-34.205175, -70.675445</t>
+          <t>-34.2053116, -70.68014</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-34.20517, -70.67544</t>
+          <t>-34.20531, -70.68014</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>00:08:25</t>
+          <t>02:08:00</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.13</v>
+        <v>0.53</v>
       </c>
       <c r="M27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
@@ -1961,57 +1961,57 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026/09/23 08:01:52</t>
+          <t>2026/09/24 07:51:28</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-33.3673666, -70.6960266</t>
+          <t>-33.3672199, -70.6966966</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-33.36737, -70.69603</t>
+          <t>-33.36722, -70.69670</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026/09/23 11:40:54</t>
+          <t>2026/09/24 10:52:41</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-33.3688216, -70.6982483</t>
+          <t>-33.3699699, -70.6707849</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-33.36882, -70.69825</t>
+          <t>-33.36997, -70.67078</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>03:39:02</t>
+          <t>03:01:13</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.68</v>
+        <v>2.76</v>
       </c>
       <c r="M28" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="N28" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2020,53 +2020,53 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026/09/23 08:08:18</t>
+          <t>2026/09/24 08:22:19</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-34.2063066, -70.6736933</t>
+          <t>-34.2070116, -70.6749866</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-34.20631, -70.67369</t>
+          <t>-34.20701, -70.67499</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026/09/23 08:29:30</t>
+          <t>2026/09/24 09:04:22</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-34.2056783, -70.6760583</t>
+          <t>-34.2088366, -70.6784283</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-34.20568, -70.67606</t>
+          <t>-34.20884, -70.67843</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>00:21:12</t>
+          <t>00:42:03</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0.45</v>
+        <v>0.38</v>
       </c>
       <c r="M29" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="N29" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2074,62 +2074,62 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026/09/23 08:17:21</t>
+          <t>2026/09/24 08:22:58</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-34.2042699, -70.6789183</t>
+          <t>-34.206332, -70.673789</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-34.20427, -70.67892</t>
+          <t>-34.20633, -70.67379</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026/09/23 08:45:05</t>
+          <t>2026/09/24 09:18:58</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-34.2063716, -70.6737066</t>
+          <t>-34.206352, -70.673854</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-34.20637, -70.67371</t>
+          <t>-34.20635, -70.67385</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>00:27:44</t>
+          <t>00:56:00</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0.62</v>
+        <v>0.01</v>
       </c>
       <c r="M30" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2138,57 +2138,57 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026/09/23 08:21:31</t>
+          <t>2026/09/24 09:04:26</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-33.3670916, -70.6955016</t>
+          <t>-34.2088316, -70.6784433</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-33.36709, -70.69550</t>
+          <t>-34.20883, -70.67844</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026/09/23 17:22:48</t>
+          <t>2026/09/24 09:45:03</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-33.4362966, -70.629605</t>
+          <t>-34.2052816, -70.6803766</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-33.43630, -70.62960</t>
+          <t>-34.20528, -70.68038</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>09:01:17</t>
+          <t>00:40:37</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>19.41</v>
+        <v>0.9</v>
       </c>
       <c r="M31" t="n">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="N31" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2197,57 +2197,57 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026/09/23 08:30:37</t>
+          <t>2026/09/24 09:18:16</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-34.2042283, -70.6788816</t>
+          <t>-33.3621233, -70.6701516</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-34.20423, -70.67888</t>
+          <t>-33.36212, -70.67015</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026/09/23 08:48:20</t>
+          <t>2026/09/24 10:28:35</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-34.2042666, -70.6788916</t>
+          <t>-34.011455, -70.7037066</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-34.20427, -70.67889</t>
+          <t>-34.01145, -70.70371</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>00:17:43</t>
+          <t>01:10:19</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>78.36</v>
       </c>
       <c r="M32" t="n">
-        <v>14</v>
+        <v>123</v>
       </c>
       <c r="N32" t="n">
-        <v>10</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2256,41 +2256,41 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026/09/23 08:39:46</t>
+          <t>2026/09/24 09:19:42</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-34.346866, -71.12567</t>
+          <t>-34.206354, -70.673854</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-34.34687, -71.12567</t>
+          <t>-34.20635, -70.67385</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026/09/23 09:51:53</t>
+          <t>2026/09/24 14:29:35</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-34.347209, -71.12573</t>
+          <t>-34.205377, -70.680129</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-34.34721, -71.12573</t>
+          <t>-34.20538, -70.68013</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>01:12:07</t>
+          <t>05:09:53</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0.33</v>
+        <v>0.88</v>
       </c>
       <c r="M33" t="n">
         <v>4</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2315,41 +2315,41 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026/09/23 08:45:11</t>
+          <t>2026/09/24 09:45:07</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-34.2064033, -70.6737416</t>
+          <t>-34.205275, -70.6803683</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-34.20640, -70.67374</t>
+          <t>-34.20528, -70.68037</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026/09/23 09:08:19</t>
+          <t>2026/09/24 11:09:51</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-34.2052916, -70.6803566</t>
+          <t>-34.2063616, -70.67374</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-34.20529, -70.68036</t>
+          <t>-34.20636, -70.67374</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>00:23:08</t>
+          <t>01:24:44</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0.84</v>
+        <v>0.98</v>
       </c>
       <c r="M34" t="n">
         <v>15</v>
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2374,53 +2374,53 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026/09/23 08:48:27</t>
+          <t>2026/09/24 09:55:09</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-34.2042766, -70.678985</t>
+          <t>-34.2052516, -70.680095</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-34.20428, -70.67898</t>
+          <t>-34.20525, -70.68009</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026/09/23 09:24:48</t>
+          <t>2026/09/24 10:56:59</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-34.2052, -70.6774916</t>
+          <t>-34.2053333, -70.6774466</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-34.20520, -70.67749</t>
+          <t>-34.20533, -70.67745</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>00:36:21</t>
+          <t>01:01:50</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="M35" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="N35" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2433,57 +2433,57 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026/09/23 08:56:24</t>
+          <t>2026/09/24 10:13:39</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-33.3621766, -70.67012</t>
+          <t>-32.8846149, -70.611565</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-33.36218, -70.67012</t>
+          <t>-32.88461, -70.61156</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026/09/23 10:04:20</t>
+          <t>2026/09/24 11:58:06</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-33.42365, -70.6125366</t>
+          <t>-32.8829483, -70.61251</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-33.42365, -70.61254</t>
+          <t>-32.88295, -70.61251</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>01:07:56</t>
+          <t>01:44:27</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>10.84</v>
+        <v>0.7</v>
       </c>
       <c r="M36" t="n">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="N36" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>LPR20251A02800014-DS</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2492,57 +2492,57 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026/09/23 09:09:34</t>
+          <t>2026/09/24 10:27:55</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-34.2052683, -70.6803433</t>
+          <t>-34.205423, -70.677214</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-34.20527, -70.68034</t>
+          <t>-34.20542, -70.67721</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026/09/23 09:19:48</t>
+          <t>2026/09/24 13:20:48</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-34.206345, -70.6737</t>
+          <t>-34.206143, -70.674138</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-34.20634, -70.67370</t>
+          <t>-34.20614, -70.67414</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>00:10:14</t>
+          <t>02:52:53</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="M37" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="N37" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2551,57 +2551,57 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026/09/23 09:19:54</t>
+          <t>2026/09/24 10:29:50</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-34.2064016, -70.6737416</t>
+          <t>-34.01146, -70.7037266</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-34.20640, -70.67374</t>
+          <t>-34.01146, -70.70373</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026/09/23 09:28:43</t>
+          <t>2026/09/24 11:45:10</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-34.2085916, -70.6779166</t>
+          <t>-34.2052449, -70.6775066</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-34.20859, -70.67792</t>
+          <t>-34.20524, -70.67751</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>00:08:49</t>
+          <t>01:15:20</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0.46</v>
+        <v>26.25</v>
       </c>
       <c r="M38" t="n">
-        <v>13</v>
+        <v>117</v>
       </c>
       <c r="N38" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2610,57 +2610,57 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026/09/23 09:24:59</t>
+          <t>2026/09/24 10:53:38</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-34.2053166, -70.6775083</t>
+          <t>-33.370745, -70.6707466</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-34.20532, -70.67751</t>
+          <t>-33.37074, -70.67075</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026/09/23 09:41:49</t>
+          <t>2026/09/24 11:18:54</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>-34.2058166, -70.675975</t>
+          <t>-33.3674449, -70.6960183</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>-34.20582, -70.67597</t>
+          <t>-33.36744, -70.69602</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>00:16:50</t>
+          <t>00:25:16</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0.17</v>
+        <v>4.72</v>
       </c>
       <c r="M39" t="n">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="N39" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2669,57 +2669,57 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026/09/23 09:26:28</t>
+          <t>2026/09/24 10:58:14</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-32.884975, -70.6121833</t>
+          <t>-34.20534, -70.6773049</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-32.88497, -70.61218</t>
+          <t>-34.20534, -70.67730</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026/09/23 10:01:36</t>
+          <t>2026/09/24 11:08:07</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-32.8828816, -70.6121583</t>
+          <t>-34.2053133, -70.6801816</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>-32.88288, -70.61216</t>
+          <t>-34.20531, -70.68018</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>00:35:08</t>
+          <t>00:09:53</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0.79</v>
+        <v>0.35</v>
       </c>
       <c r="M40" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="N40" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2728,57 +2728,57 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026/09/23 09:29:01</t>
+          <t>2026/09/24 11:08:17</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-34.2088133, -70.6784133</t>
+          <t>-34.20522, -70.6801133</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-34.20881, -70.67841</t>
+          <t>-34.20522, -70.68011</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026/09/23 09:53:38</t>
+          <t>2026/09/24 12:00:39</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-34.2074583, -70.6758316</t>
+          <t>-34.1900716, -70.7093933</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-34.20746, -70.67583</t>
+          <t>-34.19007, -70.70939</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>00:24:37</t>
+          <t>00:52:22</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0.29</v>
+        <v>3.4</v>
       </c>
       <c r="M41" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="N41" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2787,47 +2787,47 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026/09/23 09:42:46</t>
+          <t>2026/09/24 11:10:01</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-34.20732, -70.67604</t>
+          <t>-34.2063966, -70.6737783</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-34.20732, -70.67604</t>
+          <t>-34.20640, -70.67378</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026/09/23 10:32:43</t>
+          <t>2026/09/24 11:24:22</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-34.2055299, -70.676665</t>
+          <t>-34.20812, -70.677075</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-34.20553, -70.67666</t>
+          <t>-34.20812, -70.67708</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>00:49:57</t>
+          <t>00:14:21</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="M42" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N42" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
@@ -2837,66 +2837,66 @@
         </is>
       </c>
       <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026/09/24 11:14:09</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-34.346408, -71.125193</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-34.34641, -71.12519</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026/09/24 11:26:27</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>-34.346422, -71.125393</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>-34.34642, -71.12539</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>00:12:18</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M43" t="n">
         <v>3</v>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2026/09/23 09:51:55</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>-34.347212, -71.125722</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>-34.34721, -71.12572</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>2026/09/23 10:50:37</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>-34.346896, -71.125699</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>-34.34690, -71.12570</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>00:58:42</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="M43" t="n">
-        <v>4</v>
-      </c>
       <c r="N43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2905,57 +2905,57 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026/09/23 09:54:04</t>
+          <t>2026/09/24 11:19:12</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-34.2069716, -70.6749183</t>
+          <t>-33.3673749, -70.6959866</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-34.20697, -70.67492</t>
+          <t>-33.36737, -70.69599</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026/09/23 10:19:23</t>
+          <t>2026/09/24 14:48:45</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-34.2043433, -70.6792783</t>
+          <t>-32.8825533, -70.61196</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-34.20434, -70.67928</t>
+          <t>-32.88255, -70.61196</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>00:25:19</t>
+          <t>03:29:33</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0.77</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>19</v>
+        <v>124</v>
       </c>
       <c r="N44" t="n">
-        <v>14</v>
+        <v>71</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2964,53 +2964,53 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026/09/23 10:00:24</t>
+          <t>2026/09/24 11:24:56</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-33.360635, -70.806185</t>
+          <t>-34.2088116, -70.6784266</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-33.36064, -70.80618</t>
+          <t>-34.20881, -70.67843</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026/09/23 10:21:47</t>
+          <t>2026/09/24 12:00:04</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-33.362095, -70.806694</t>
+          <t>-34.190125, -70.709515</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-33.36209, -70.80669</t>
+          <t>-34.19013, -70.70951</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>00:21:23</t>
+          <t>00:35:08</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0.17</v>
+        <v>4.23</v>
       </c>
       <c r="M45" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="N45" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -3023,57 +3023,57 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026/09/23 10:02:48</t>
+          <t>2026/09/24 11:27:15</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-32.8835466, -70.61218</t>
+          <t>-34.346401, -71.12545</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-32.88355, -70.61218</t>
+          <t>-34.34640, -71.12545</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026/09/23 10:21:41</t>
+          <t>2026/09/24 11:51:02</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-32.883145, -70.6126066</t>
+          <t>-34.347171, -71.125732</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-32.88314, -70.61261</t>
+          <t>-34.34717, -71.12573</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>00:18:53</t>
+          <t>00:23:47</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0.39</v>
+        <v>0.27</v>
       </c>
       <c r="M46" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="N46" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3082,57 +3082,57 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026/09/23 10:05:35</t>
+          <t>2026/09/24 11:27:18</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-33.4248183, -70.6137816</t>
+          <t>-33.360146, -70.806869</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-33.42482, -70.61378</t>
+          <t>-33.36015, -70.80687</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026/09/23 10:45:18</t>
+          <t>2026/09/24 15:03:06</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-33.4349633, -70.6496466</t>
+          <t>-33.36052, -70.809028</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-33.43496, -70.64965</t>
+          <t>-33.36052, -70.80903</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>00:39:43</t>
+          <t>03:35:48</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>4.17</v>
+        <v>14.13</v>
       </c>
       <c r="M47" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3141,53 +3141,53 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026/09/23 10:20:09</t>
+          <t>2026/09/24 11:45:36</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-34.2053516, -70.6803683</t>
+          <t>-34.205295, -70.6775266</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-34.20535, -70.68037</t>
+          <t>-34.20529, -70.67753</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026/09/23 10:55:37</t>
+          <t>2026/09/24 11:55:39</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-34.2044683, -70.67844</t>
+          <t>-34.20835, -70.677595</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-34.20447, -70.67844</t>
+          <t>-34.20835, -70.67759</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>00:35:28</t>
+          <t>00:10:03</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0.25</v>
+        <v>0.54</v>
       </c>
       <c r="M48" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="N48" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -3195,62 +3195,62 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026/09/23 10:21:49</t>
+          <t>2026/09/24 11:51:43</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-32.8831666, -70.6123983</t>
+          <t>-34.347182, -71.125748</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-32.88317, -70.61240</t>
+          <t>-34.34718, -71.12575</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026/09/23 10:36:36</t>
+          <t>2026/09/24 11:59:43</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-32.8825566, -70.6117983</t>
+          <t>-34.347233, -71.125745</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>-32.88256, -70.61180</t>
+          <t>-34.34723, -71.12574</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>00:14:47</t>
+          <t>00:08:00</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="M49" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="N49" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3259,53 +3259,53 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026/09/23 10:33:23</t>
+          <t>2026/09/24 11:56:54</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-34.20558, -70.6772233</t>
+          <t>-34.2080283, -70.6775933</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-34.20558, -70.67722</t>
+          <t>-34.20803, -70.67759</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026/09/23 11:35:18</t>
+          <t>2026/09/24 12:26:11</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-34.205515, -70.67757</t>
+          <t>-34.20666, -70.6759283</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>-34.20551, -70.67757</t>
+          <t>-34.20666, -70.67593</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>01:01:55</t>
+          <t>00:29:17</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0.03</v>
+        <v>0.33</v>
       </c>
       <c r="M50" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="N50" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -3318,57 +3318,57 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026/09/23 10:36:28</t>
+          <t>2026/09/24 11:59:21</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-33.360171, -70.806817</t>
+          <t>-32.8824283, -70.6119</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-33.36017, -70.80682</t>
+          <t>-32.88243, -70.61190</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026/09/23 11:03:21</t>
+          <t>2026/09/24 12:05:50</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>-33.360175, -70.807263</t>
+          <t>-32.8851266, -70.6110783</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>-33.36017, -70.80726</t>
+          <t>-32.88513, -70.61108</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>00:26:53</t>
+          <t>00:06:29</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0.15</v>
+        <v>0.45</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3377,116 +3377,116 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026/09/23 10:37:49</t>
+          <t>2026/09/24 12:00:32</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-32.88382, -70.6118083</t>
+          <t>-34.1900033, -70.7093533</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-32.88382, -70.61181</t>
+          <t>-34.19000, -70.70935</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026/09/23 11:08:09</t>
+          <t>2026/09/24 12:52:52</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-32.882395, -70.6115666</t>
+          <t>-34.2057333, -70.6761616</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>-32.88240, -70.61157</t>
+          <t>-34.20573, -70.67616</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>00:30:20</t>
+          <t>00:52:20</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.65</v>
+        <v>3.77</v>
       </c>
       <c r="M52" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="N52" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C53" t="n">
+        <v>5</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026/09/24 12:00:43</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-34.347249, -71.125753</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-34.34725, -71.12575</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2026/09/24 12:27:44</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>-34.346725, -71.125178</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>-34.34672, -71.12518</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>00:27:01</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M53" t="n">
         <v>4</v>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>2026/09/23 10:46:33</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>-33.4355183, -70.6499533</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>-33.43552, -70.64995</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>2026/09/23 13:23:04</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>-33.8997566, -71.426385</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>-33.89976, -71.42638</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>02:36:31</t>
-        </is>
-      </c>
-      <c r="L53" t="n">
-        <v>132.53</v>
-      </c>
-      <c r="M53" t="n">
-        <v>124</v>
-      </c>
       <c r="N53" t="n">
-        <v>61</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3495,57 +3495,57 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026/09/23 10:51:04</t>
+          <t>2026/09/24 12:00:59</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-34.346864, -71.125704</t>
+          <t>-34.1902266, -70.7093466</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-34.34686, -71.12570</t>
+          <t>-34.19023, -70.70935</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026/09/23 11:50:22</t>
+          <t>2026/09/24 13:00:57</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>-34.345945, -71.125749</t>
+          <t>-34.2054666, -70.6774233</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>-34.34595, -71.12575</t>
+          <t>-34.20547, -70.67742</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>00:59:18</t>
+          <t>00:59:58</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0.73</v>
+        <v>3.64</v>
       </c>
       <c r="M54" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="N54" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3554,57 +3554,57 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026/09/23 10:56:06</t>
+          <t>2026/09/24 12:07:05</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-33.4485116, -70.7433816</t>
+          <t>-32.8844783, -70.6110616</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-33.44851, -70.74338</t>
+          <t>-32.88448, -70.61106</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026/09/23 11:58:43</t>
+          <t>2026/09/24 12:43:54</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-33.367245, -70.6955833</t>
+          <t>-32.8333516, -70.5945266</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>-33.36724, -70.69558</t>
+          <t>-32.83335, -70.59453</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>01:02:37</t>
+          <t>00:36:49</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>35.13</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="M55" t="n">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="N55" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3613,106 +3613,106 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026/09/23 10:56:45</t>
+          <t>2026/09/24 12:26:25</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-34.2055483, -70.6765883</t>
+          <t>-34.2073449, -70.6760033</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-34.20555, -70.67659</t>
+          <t>-34.20734, -70.67600</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026/09/23 11:29:15</t>
+          <t>2026/09/24 13:07:45</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>-34.20514, -70.6774249</t>
+          <t>-34.0418483, -70.6818516</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>-34.20514, -70.67742</t>
+          <t>-34.04185, -70.68185</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>00:32:30</t>
+          <t>00:41:20</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0.09</v>
+        <v>24.96</v>
       </c>
       <c r="M56" t="n">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="N56" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026/09/23 11:04:04</t>
+          <t>2026/09/24 12:27:52</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-33.360175, -70.807263</t>
+          <t>-34.346677, -71.125204</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-33.36017, -70.80726</t>
+          <t>-34.34668, -71.12520</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026/09/23 14:22:54</t>
+          <t>2026/09/24 13:26:27</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>-33.360909, -70.804812</t>
+          <t>-34.346532, -71.125169</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-33.36091, -70.80481</t>
+          <t>-34.34653, -71.12517</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>03:18:50</t>
+          <t>00:58:35</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0.24</v>
+        <v>0.02</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -3731,57 +3731,57 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026/09/23 11:09:24</t>
+          <t>2026/09/24 12:44:38</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-32.8836983, -70.6115683</t>
+          <t>-32.8334383, -70.5942483</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-32.88370, -70.61157</t>
+          <t>-32.83344, -70.59425</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026/09/23 11:44:00</t>
+          <t>2026/09/24 14:36:46</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>-32.8824349, -70.6118483</t>
+          <t>-32.8792233, -70.6089283</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>-32.88243, -70.61185</t>
+          <t>-32.87922, -70.60893</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>00:34:36</t>
+          <t>01:52:08</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0.18</v>
+        <v>44.55</v>
       </c>
       <c r="M58" t="n">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="N58" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3790,57 +3790,57 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026/09/23 11:14:10</t>
+          <t>2026/09/24 12:53:34</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-34.204153, -70.678915</t>
+          <t>-34.20706, -70.67719</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-34.20415, -70.67892</t>
+          <t>-34.20706, -70.67719</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026/09/23 11:23:10</t>
+          <t>2026/09/24 13:45:39</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>-34.205433, -70.677347</t>
+          <t>-34.20565, -70.6762066</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>-34.20543, -70.67735</t>
+          <t>-34.20565, -70.67621</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>00:09:00</t>
+          <t>00:52:05</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="M59" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N59" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -3849,57 +3849,57 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026/09/23 11:23:52</t>
+          <t>2026/09/24 13:02:12</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>-34.205473, -70.677304</t>
+          <t>-34.2054616, -70.677315</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-34.20547, -70.67730</t>
+          <t>-34.20546, -70.67731</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026/09/23 11:42:51</t>
+          <t>2026/09/24 13:14:52</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>-34.205071, -70.68017</t>
+          <t>-34.2051383, -70.6755883</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>-34.20507, -70.68017</t>
+          <t>-34.20514, -70.67559</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>00:18:59</t>
+          <t>00:12:40</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="M60" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="N60" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3908,47 +3908,47 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026/09/23 11:29:59</t>
+          <t>2026/09/24 13:09:00</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-34.2042583, -70.6791466</t>
+          <t>-34.0429066, -70.6816716</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-34.20426, -70.67915</t>
+          <t>-34.04291, -70.68167</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026/09/23 11:58:48</t>
+          <t>2026/09/24 13:22:41</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>-34.190065, -70.709465</t>
+          <t>-34.0421883, -70.680195</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>-34.19006, -70.70946</t>
+          <t>-34.04219, -70.68019</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>00:28:49</t>
+          <t>00:13:41</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.51</v>
+        <v>0.46</v>
       </c>
       <c r="M61" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="N61" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62">
@@ -3958,180 +3958,180 @@
         </is>
       </c>
       <c r="C62" t="n">
+        <v>9</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026/09/24 13:15:52</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-34.2063016, -70.6737599</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-34.20630, -70.67376</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2026/09/24 14:20:09</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>-34.20539, -70.6801583</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>-34.20539, -70.68016</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>01:04:17</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M62" t="n">
+        <v>14</v>
+      </c>
+      <c r="N62" t="n">
         <v>10</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>2026/09/23 11:36:35</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>-34.2042716, -70.6790466</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>-34.20427, -70.67905</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>2026/09/23 13:06:13</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>-34.2052583, -70.6803049</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>-34.20526, -70.68030</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>01:29:38</t>
-        </is>
-      </c>
-      <c r="L62" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="M62" t="n">
-        <v>34</v>
-      </c>
-      <c r="N62" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>LPR20251A02800014-DS</t>
         </is>
       </c>
       <c r="C63" t="n">
+        <v>4</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026/09/24 13:21:48</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-34.206341, -70.673913</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-34.20634, -70.67391</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2026/09/24 14:17:13</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>-34.205473, -70.677302</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>-34.20547, -70.67730</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>00:55:25</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="M63" t="n">
+        <v>4</v>
+      </c>
+      <c r="N63" t="n">
         <v>3</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>2026/09/23 11:41:03</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>-33.3687966, -70.6981033</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>-33.36880, -70.69810</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>2026/09/23 11:54:46</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>-33.3676133, -70.6962899</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>-33.36761, -70.69629</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>00:13:43</t>
-        </is>
-      </c>
-      <c r="L63" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M63" t="n">
-        <v>26</v>
-      </c>
-      <c r="N63" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026/09/23 11:43:10</t>
+          <t>2026/09/24 13:23:20</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-34.205153, -70.680117</t>
+          <t>-34.0422916, -70.6801799</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-34.20515, -70.68012</t>
+          <t>-34.04229, -70.68018</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026/09/23 12:59:00</t>
+          <t>2026/09/24 13:45:09</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>-34.205237, -70.680109</t>
+          <t>-34.0421183, -70.6801349</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>-34.20524, -70.68011</t>
+          <t>-34.04212, -70.68013</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>01:15:50</t>
+          <t>00:21:49</t>
         </is>
       </c>
       <c r="L64" t="n">
         <v>0.02</v>
       </c>
       <c r="M64" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N64" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -4139,121 +4139,121 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026/09/23 11:45:15</t>
+          <t>2026/09/24 13:27:02</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-32.8831366, -70.6123533</t>
+          <t>-34.346514, -71.125324</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-32.88314, -70.61235</t>
+          <t>-34.34651, -71.12532</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026/09/23 11:53:45</t>
+          <t>2026/09/24 15:14:47</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>-32.8791733, -70.6088949</t>
+          <t>-34.346198, -71.125541</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>-32.87917, -70.60889</t>
+          <t>-34.34620, -71.12554</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>00:08:30</t>
+          <t>01:47:45</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0.6</v>
+        <v>0.04</v>
       </c>
       <c r="M65" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="N65" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026/09/23 11:50:55</t>
+          <t>2026/09/24 13:45:56</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>-34.345954, -71.125788</t>
+          <t>-34.2055733, -70.676615</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-34.34595, -71.12579</t>
+          <t>-34.20557, -70.67661</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026/09/24 11:13:19</t>
+          <t>2026/09/24 15:52:53</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>-34.346426, -71.125197</t>
+          <t>-34.2041066, -70.67899</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>-34.34643, -71.12520</t>
+          <t>-34.20411, -70.67899</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>23:22:24</t>
+          <t>02:06:57</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0.1</v>
+        <v>0.27</v>
       </c>
       <c r="M66" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="N66" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4262,116 +4262,116 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026/09/23 11:55:00</t>
+          <t>2026/09/24 13:46:16</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>-32.8791916, -70.608815</t>
+          <t>-34.0449666, -70.6801866</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-32.87919, -70.60882</t>
+          <t>-34.04497, -70.68019</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026/09/23 13:35:40</t>
+          <t>2026/09/24 15:29:22</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>-32.7869766, -70.6097683</t>
+          <t>-33.4762716, -70.6983483</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>-32.78698, -70.60977</t>
+          <t>-33.47627, -70.69835</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>01:40:40</t>
+          <t>01:43:06</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>46.89</v>
+        <v>69.28</v>
       </c>
       <c r="M67" t="n">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="N67" t="n">
-        <v>27</v>
+        <v>64</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>LPR20251A02800014-DS</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026/09/23 11:55:36</t>
+          <t>2026/09/24 14:17:38</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>-33.36738, -70.6960316</t>
+          <t>-34.205446, -70.677348</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-33.36738, -70.69603</t>
+          <t>-34.20545, -70.67735</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026/09/23 15:43:01</t>
+          <t>2026/09/27 01:13:50</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>-32.787305, -70.8310549</t>
+          <t>-34.205678, -70.676839</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>-32.78731, -70.83105</t>
+          <t>-34.20568, -70.67684</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>03:47:25</t>
+          <t>58:56:12</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>91.70999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="M68" t="n">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="N68" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4380,57 +4380,57 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026/09/23 11:59:14</t>
+          <t>2026/09/24 14:20:46</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-34.1899833, -70.7093283</t>
+          <t>-34.2051566, -70.6801299</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-34.18998, -70.70933</t>
+          <t>-34.20516, -70.68013</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026/09/23 13:02:25</t>
+          <t>2026/09/24 14:28:24</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>-34.2053616, -70.6803733</t>
+          <t>-34.2051333, -70.680145</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>-34.20536, -70.68037</t>
+          <t>-34.20513, -70.68014</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>01:03:11</t>
+          <t>00:07:38</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>4.31</v>
+        <v>0.01</v>
       </c>
       <c r="M69" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="N69" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4439,47 +4439,47 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026/09/23 11:59:58</t>
+          <t>2026/09/24 14:28:40</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>-33.367265, -70.6959266</t>
+          <t>-34.2052466, -70.6801016</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-33.36727, -70.69593</t>
+          <t>-34.20525, -70.68010</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026/09/23 14:25:51</t>
+          <t>2026/09/24 16:14:21</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>-33.3649799, -70.676045</t>
+          <t>-34.2052116, -70.6775099</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>-33.36498, -70.67605</t>
+          <t>-34.20521, -70.67751</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>02:25:53</t>
+          <t>01:45:41</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>24.81</v>
+        <v>0.35</v>
       </c>
       <c r="M70" t="n">
-        <v>125</v>
+        <v>13</v>
       </c>
       <c r="N70" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71">
@@ -4493,49 +4493,49 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026/09/23 12:59:11</t>
+          <t>2026/09/24 14:30:12</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>-34.205247, -70.680103</t>
+          <t>-34.205252, -70.680165</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-34.20525, -70.68010</t>
+          <t>-34.20525, -70.68017</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026/09/23 13:10:45</t>
+          <t>2026/09/24 15:15:27</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>-34.205284, -70.680106</t>
+          <t>-34.205258, -70.680072</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>-34.20528, -70.68011</t>
+          <t>-34.20526, -70.68007</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>00:11:34</t>
+          <t>00:45:15</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0.01</v>
+        <v>0.58</v>
       </c>
       <c r="M71" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N71" t="n">
         <v>3</v>
@@ -4544,11 +4544,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4557,57 +4557,57 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026/09/23 13:02:42</t>
+          <t>2026/09/24 14:36:58</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>-34.2053516, -70.6803816</t>
+          <t>-32.879235, -70.60878</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-34.20535, -70.68038</t>
+          <t>-32.87924, -70.60878</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026/09/23 13:17:54</t>
+          <t>2026/09/25 07:47:56</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>-34.2055916, -70.6769066</t>
+          <t>-32.8529266, -70.62402</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>-34.20559, -70.67691</t>
+          <t>-32.85293, -70.62402</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>00:15:12</t>
+          <t>17:10:58</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0.32</v>
+        <v>6.41</v>
       </c>
       <c r="M72" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="N72" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -4616,57 +4616,57 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026/09/23 13:06:47</t>
+          <t>2026/09/24 14:50:00</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>-34.2053866, -70.6802433</t>
+          <t>-32.88321, -70.6124516</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-34.20539, -70.68024</t>
+          <t>-32.88321, -70.61245</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026/09/23 13:37:25</t>
+          <t>2026/09/24 17:50:05</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>-34.20516, -70.6802816</t>
+          <t>-32.788285, -70.8306849</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>-34.20516, -70.68028</t>
+          <t>-32.78829, -70.83068</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>00:30:38</t>
+          <t>03:00:05</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.26</v>
+        <v>40.44</v>
       </c>
       <c r="M73" t="n">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="N73" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -4675,57 +4675,57 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026/09/23 13:11:10</t>
+          <t>2026/09/24 15:03:08</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>-34.205291, -70.680109</t>
+          <t>-33.36052, -70.809029</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-34.20529, -70.68011</t>
+          <t>-33.36052, -70.80903</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026/09/23 14:56:23</t>
+          <t>2026/09/25 07:07:07</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>-34.205515, -70.677515</t>
+          <t>-32.839517, -70.956188</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>-34.20551, -70.67751</t>
+          <t>-32.83952, -70.95619</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>01:45:13</t>
+          <t>16:03:59</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0.26</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="M74" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="N74" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -4734,175 +4734,175 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026/09/23 13:18:09</t>
+          <t>2026/09/24 15:15:47</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>-34.2055983, -70.6764983</t>
+          <t>-34.345945, -71.125747</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-34.20560, -70.67650</t>
+          <t>-34.34595, -71.12575</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026/09/23 13:44:56</t>
+          <t>2026/09/25 12:48:30</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>-34.2064083, -70.6737349</t>
+          <t>-34.346461, -71.126063</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>-34.20641, -70.67373</t>
+          <t>-34.34646, -71.12606</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>00:26:47</t>
+          <t>21:32:43</t>
         </is>
       </c>
       <c r="L75" t="n">
         <v>0.34</v>
       </c>
       <c r="M75" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="N75" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C76" t="n">
+        <v>6</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026/09/24 15:15:58</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>-34.20526, -70.680089</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-34.20526, -70.68009</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2026/09/24 15:23:37</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>-34.205254, -70.680188</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>-34.20525, -70.68019</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>00:07:39</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M76" t="n">
         <v>5</v>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>2026/09/23 13:23:09</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>-33.89976, -71.4264633</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>-33.89976, -71.42646</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>2026/09/23 14:28:34</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>-33.8988133, -71.4273783</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>-33.89881, -71.42738</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>01:05:25</t>
-        </is>
-      </c>
-      <c r="L76" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="M76" t="n">
-        <v>19</v>
-      </c>
       <c r="N76" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026/09/23 13:36:47</t>
+          <t>2026/09/24 15:23:54</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>-32.7866349, -70.60921</t>
+          <t>-34.205297, -70.680202</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-32.78663, -70.60921</t>
+          <t>-34.20530, -70.68020</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026/09/23 14:04:06</t>
+          <t>2026/09/24 15:30:47</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>-32.8365016, -70.5986049</t>
+          <t>-34.205297, -70.680211</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>-32.83650, -70.59860</t>
+          <t>-34.20530, -70.68021</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>00:27:19</t>
+          <t>00:06:53</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>7.95</v>
+        <v>0.01</v>
       </c>
       <c r="M77" t="n">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="N77" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -4911,57 +4911,57 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026/09/23 13:37:56</t>
+          <t>2026/09/24 15:29:57</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>-34.205315, -70.68016</t>
+          <t>-33.4763316, -70.698415</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-34.20531, -70.68016</t>
+          <t>-33.47633, -70.69841</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026/09/23 13:55:15</t>
+          <t>2026/09/24 16:57:52</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>-34.20559, -70.6777349</t>
+          <t>-33.362385, -70.6701316</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>-34.20559, -70.67773</t>
+          <t>-33.36239, -70.67013</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>00:17:19</t>
+          <t>01:27:55</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0.23</v>
+        <v>25.05</v>
       </c>
       <c r="M78" t="n">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="N78" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -4970,116 +4970,116 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026/09/23 13:45:01</t>
+          <t>2026/09/24 15:31:46</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>-34.2064249, -70.6737766</t>
+          <t>-34.20527, -70.680189</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-34.20642, -70.67378</t>
+          <t>-34.20527, -70.68019</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026/09/23 14:15:43</t>
+          <t>2026/09/24 15:48:25</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>-34.2052733, -70.6802966</t>
+          <t>-34.20548, -70.677407</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>-34.20527, -70.68030</t>
+          <t>-34.20548, -70.67741</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>00:30:42</t>
+          <t>00:16:39</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.14</v>
+        <v>0.34</v>
       </c>
       <c r="M79" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="N79" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026/09/23 13:56:35</t>
+          <t>2026/09/24 15:49:07</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>-34.2054966, -70.67737</t>
+          <t>-34.20545, -70.677304</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-34.20550, -70.67737</t>
+          <t>-34.20545, -70.67730</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026/09/23 14:49:28</t>
+          <t>2026/09/25 07:48:22</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>-34.2075266, -70.6758866</t>
+          <t>-34.205362, -70.677228</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>-34.20753, -70.67589</t>
+          <t>-34.20536, -70.67723</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>00:52:53</t>
+          <t>15:59:15</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0.34</v>
+        <v>0.03</v>
       </c>
       <c r="M80" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="N80" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5088,57 +5088,57 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026/09/23 14:04:41</t>
+          <t>2026/09/24 15:54:08</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>-32.8368583, -70.59747</t>
+          <t>-34.2041649, -70.67908</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-32.83686, -70.59747</t>
+          <t>-34.20416, -70.67908</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026/09/23 14:29:53</t>
+          <t>2026/09/24 16:22:20</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>-32.879225, -70.60894</t>
+          <t>-34.2056733, -70.67627</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>-32.87922, -70.60894</t>
+          <t>-34.20567, -70.67627</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>00:25:12</t>
+          <t>00:28:12</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>7.13</v>
+        <v>1.91</v>
       </c>
       <c r="M81" t="n">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="N81" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5147,57 +5147,57 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026/09/23 14:16:58</t>
+          <t>2026/09/24 16:14:29</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>-34.2052916, -70.6802883</t>
+          <t>-34.2053283, -70.6775299</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-34.20529, -70.68029</t>
+          <t>-34.20533, -70.67753</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026/09/23 14:37:23</t>
+          <t>2026/09/24 16:40:42</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>-34.206435, -70.6737383</t>
+          <t>-34.205365, -70.6774516</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>-34.20643, -70.67374</t>
+          <t>-34.20537, -70.67745</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>00:20:25</t>
+          <t>00:26:13</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="M82" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="N82" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5206,57 +5206,57 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026/09/23 14:23:01</t>
+          <t>2026/09/24 16:23:35</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>-33.360909, -70.804812</t>
+          <t>-34.20516, -70.6774983</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-33.36091, -70.80481</t>
+          <t>-34.20516, -70.67750</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026/09/23 17:36:03</t>
+          <t>2026/09/24 16:29:57</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>-32.83989, -70.961898</t>
+          <t>-34.2041116, -70.6790016</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>-32.83989, -70.96190</t>
+          <t>-34.20411, -70.67900</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>03:13:02</t>
+          <t>00:06:22</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>60.55</v>
+        <v>0.18</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5265,57 +5265,57 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026/09/23 14:27:06</t>
+          <t>2026/09/24 16:30:02</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>-33.365015, -70.6769933</t>
+          <t>-34.2041433, -70.6790466</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-33.36501, -70.67699</t>
+          <t>-34.20414, -70.67905</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026/09/23 15:13:59</t>
+          <t>2026/09/24 17:30:49</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>-33.3672116, -70.6955683</t>
+          <t>-34.1679133, -70.7330449</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>-33.36721, -70.69557</t>
+          <t>-34.16791, -70.73304</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>00:46:53</t>
+          <t>01:00:47</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>4.68</v>
+        <v>7.58</v>
       </c>
       <c r="M84" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="N84" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5324,57 +5324,57 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026/09/23 14:28:40</t>
+          <t>2026/09/24 16:41:57</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>-33.898795, -71.42753</t>
+          <t>-34.2055249, -70.6774249</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-33.89879, -71.42753</t>
+          <t>-34.20552, -70.67742</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026/09/23 14:51:52</t>
+          <t>2026/09/24 17:38:55</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>-33.8995466, -71.4297466</t>
+          <t>-34.1678783, -70.73303</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>-33.89955, -71.42975</t>
+          <t>-34.16788, -70.73303</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>00:23:12</t>
+          <t>00:56:58</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0.39</v>
+        <v>7.7</v>
       </c>
       <c r="M85" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="N85" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5383,47 +5383,47 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026/09/23 14:31:07</t>
+          <t>2026/09/24 16:58:26</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>-32.8791016, -70.6093999</t>
+          <t>-33.36221, -70.6701216</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-32.87910, -70.60940</t>
+          <t>-33.36221, -70.67012</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026/09/23 19:14:00</t>
+          <t>2026/09/24 18:34:00</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>-32.8792166, -70.6088116</t>
+          <t>-33.4761983, -70.6981583</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>-32.87922, -70.60881</t>
+          <t>-33.47620, -70.69816</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>04:42:53</t>
+          <t>01:35:34</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.74</v>
+        <v>17.6</v>
       </c>
       <c r="M86" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="N86" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="87">
@@ -5433,7 +5433,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5442,47 +5442,47 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026/09/23 14:37:27</t>
+          <t>2026/09/24 17:31:32</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>-34.2064416, -70.6737533</t>
+          <t>-34.16782, -70.73301</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-34.20644, -70.67375</t>
+          <t>-34.16782, -70.73301</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026/09/23 15:10:37</t>
+          <t>2026/09/25 07:15:02</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>-34.2063866, -70.6737133</t>
+          <t>-34.1679016, -70.7330383</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>-34.20639, -70.67371</t>
+          <t>-34.16790, -70.73304</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>00:33:10</t>
+          <t>13:43:30</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.35</v>
+        <v>0.04</v>
       </c>
       <c r="M87" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="N87" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88">
@@ -5501,57 +5501,57 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026/09/23 14:50:43</t>
+          <t>2026/09/24 17:39:32</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>-34.2076033, -70.6760233</t>
+          <t>-34.1677816, -70.7330016</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-34.20760, -70.67602</t>
+          <t>-34.16778, -70.73300</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026/09/23 15:02:34</t>
+          <t>2026/09/25 07:39:02</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>-34.205155, -70.6775416</t>
+          <t>-34.2053049, -70.6801799</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>-34.20515, -70.67754</t>
+          <t>-34.20530, -70.68018</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>00:11:51</t>
+          <t>13:59:30</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0.37</v>
+        <v>7.58</v>
       </c>
       <c r="M88" t="n">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="N88" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5560,53 +5560,53 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026/09/23 14:51:57</t>
+          <t>2026/09/24 17:50:54</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>-33.89955, -71.4298233</t>
+          <t>-32.7855033, -70.8316366</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-33.89955, -71.42982</t>
+          <t>-32.78550, -70.83164</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026/09/23 15:12:17</t>
+          <t>2026/09/24 18:06:45</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>-33.9000766, -71.4297083</t>
+          <t>-32.7977349, -70.8874299</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>-33.90008, -71.42971</t>
+          <t>-32.79773, -70.88743</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>00:20:20</t>
+          <t>00:15:51</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0.07000000000000001</v>
+        <v>7.36</v>
       </c>
       <c r="M89" t="n">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="N89" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -5619,57 +5619,57 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026/09/23 14:57:23</t>
+          <t>2026/09/24 18:07:19</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>-34.20544, -70.677291</t>
+          <t>-32.79763, -70.8870999</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-34.20544, -70.67729</t>
+          <t>-32.79763, -70.88710</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026/09/24 07:43:39</t>
+          <t>2026/09/24 18:38:29</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>-34.205371, -70.680097</t>
+          <t>-32.7977266, -70.887315</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>-34.20537, -70.68010</t>
+          <t>-32.79773, -70.88732</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>16:46:16</t>
+          <t>00:31:10</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
       <c r="M90" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="N90" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -5678,57 +5678,57 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026/09/23 15:03:49</t>
+          <t>2026/09/24 18:35:15</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>-34.2043083, -70.679075</t>
+          <t>-33.4762016, -70.6984316</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-34.20431, -70.67907</t>
+          <t>-33.47620, -70.69843</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026/09/23 15:43:12</t>
+          <t>2026/09/25 07:45:24</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>-34.2051666, -70.6801249</t>
+          <t>-33.4762749, -70.6983349</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>-34.20517, -70.68012</t>
+          <t>-33.47627, -70.69833</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>00:39:23</t>
+          <t>13:10:09</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0.14</v>
+        <v>11.15</v>
       </c>
       <c r="M91" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="N91" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -5737,175 +5737,175 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026/09/23 15:10:42</t>
+          <t>2026/09/24 18:39:20</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>-34.2064283, -70.6737516</t>
+          <t>-32.797605, -70.887025</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-34.20643, -70.67375</t>
+          <t>-32.79760, -70.88702</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026/09/23 15:37:17</t>
+          <t>2026/09/25 07:11:23</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>-34.2088683, -70.678425</t>
+          <t>-32.88316, -70.6124083</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>-34.20887, -70.67843</t>
+          <t>-32.88316, -70.61241</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>00:26:35</t>
+          <t>12:32:03</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0.51</v>
+        <v>41.76</v>
       </c>
       <c r="M92" t="n">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="N92" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026/09/23 15:13:32</t>
+          <t>2026/09/25 08:11:06</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>-33.900335, -71.4303616</t>
+          <t>-34.205344, -70.677493</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-33.90033, -71.43036</t>
+          <t>-34.20534, -70.67749</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026/09/23 15:20:39</t>
+          <t>2026/09/25 08:22:32</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>-33.9000516, -71.4296933</t>
+          <t>-34.205442, -70.677361</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>-33.90005, -71.42969</t>
+          <t>-34.20544, -70.67736</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>00:07:07</t>
+          <t>00:11:26</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="M93" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N93" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026/09/23 15:15:14</t>
+          <t>2026/09/25 09:56:56</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>-33.3671916, -70.6958816</t>
+          <t>-33.3670249, -70.695565</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-33.36719, -70.69588</t>
+          <t>-33.36702, -70.69557</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026/09/29 23:15:34</t>
+          <t>2026/09/25 14:29:28</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>-33.3671916, -70.6958816</t>
+          <t>-33.38888, -70.6165516</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>-33.36719, -70.69588</t>
+          <t>-33.38888, -70.61655</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>152:00:20</t>
+          <t>04:32:32</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>29.4</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -5914,57 +5914,57 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026/09/23 15:21:54</t>
+          <t>2026/09/25 12:49:21</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>-33.9002216, -71.429375</t>
+          <t>-34.346311, -71.12606</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-33.90022, -71.42937</t>
+          <t>-34.34631, -71.12606</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026/09/23 16:22:44</t>
+          <t>2026/09/25 13:24:08</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>-33.7728216, -71.247475</t>
+          <t>-34.347549, -71.126086</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>-33.77282, -71.24747</t>
+          <t>-34.34755, -71.12609</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>01:00:50</t>
+          <t>00:34:47</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>27.62</v>
+        <v>1.01</v>
       </c>
       <c r="M95" t="n">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="N95" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -5973,57 +5973,57 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026/09/23 15:38:11</t>
+          <t>2026/09/25 14:02:54</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>-34.2088583, -70.67846</t>
+          <t>-32.8782316, -70.6034333</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-34.20886, -70.67846</t>
+          <t>-32.87823, -70.60343</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026/09/23 16:38:40</t>
+          <t>2026/09/25 14:38:11</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>-34.167865, -70.7330533</t>
+          <t>-32.8792216, -70.608805</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>-34.16786, -70.73305</t>
+          <t>-32.87922, -70.60881</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>01:00:29</t>
+          <t>00:35:17</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>8.35</v>
+        <v>0.74</v>
       </c>
       <c r="M96" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="N96" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6032,57 +6032,57 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026/09/23 15:43:24</t>
+          <t>2026/09/25 14:14:26</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>-34.2053016, -70.680095</t>
+          <t>-34.347204, -71.126365</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-34.20530, -70.68009</t>
+          <t>-34.34720, -71.12637</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026/09/23 16:37:01</t>
+          <t>2026/09/25 14:24:26</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>-34.167725, -70.7345633</t>
+          <t>-34.346286, -71.126098</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>-34.16772, -70.73456</t>
+          <t>-34.34629, -71.12610</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>00:53:37</t>
+          <t>00:10:00</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>7.12</v>
+        <v>0.17</v>
       </c>
       <c r="M97" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="N97" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6091,116 +6091,116 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026/09/23 15:43:43</t>
+          <t>2026/09/25 14:19:02</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>-32.7855083, -70.8316516</t>
+          <t>-33.360681, -70.809045</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-32.78551, -70.83165</t>
+          <t>-33.36068, -70.80904</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026/09/23 16:02:55</t>
+          <t>2026/09/26 14:27:18</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>-32.7977233, -70.8873916</t>
+          <t>-32.838367, -70.955473</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>-32.79772, -70.88739</t>
+          <t>-32.83837, -70.95547</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>00:19:12</t>
+          <t>24:08:16</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>7.35</v>
+        <v>133.78</v>
       </c>
       <c r="M98" t="n">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="N98" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026/09/23 16:04:10</t>
+          <t>2026/09/25 14:24:51</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>-32.79762, -70.887105</t>
+          <t>-34.346253, -71.125985</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-32.79762, -70.88711</t>
+          <t>-34.34625, -71.12599</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026/09/24 07:51:00</t>
+          <t>2026/09/25 15:07:34</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>-33.3672399, -70.6965616</t>
+          <t>-34.346117, -71.125698</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>-33.36724, -70.69656</t>
+          <t>-34.34612, -71.12570</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>15:46:50</t>
+          <t>00:42:43</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>92.41</v>
+        <v>0.03</v>
       </c>
       <c r="M99" t="n">
-        <v>130</v>
+        <v>2</v>
       </c>
       <c r="N99" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6209,57 +6209,57 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026/09/23 16:22:53</t>
+          <t>2026/09/25 14:30:37</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>-33.7726333, -71.24735</t>
+          <t>-33.3887316, -70.6166066</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-33.77263, -71.24735</t>
+          <t>-33.38873, -70.61661</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026/09/23 17:46:12</t>
+          <t>2026/09/25 15:12:26</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>-33.362375, -70.6701633</t>
+          <t>-33.4362633, -70.6295983</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>-33.36238, -70.67016</t>
+          <t>-33.43626, -70.62960</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>01:23:19</t>
+          <t>00:41:49</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>91.45</v>
+        <v>6.71</v>
       </c>
       <c r="M100" t="n">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="N100" t="n">
-        <v>74</v>
+        <v>23</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6268,57 +6268,57 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026/09/23 16:38:19</t>
+          <t>2026/09/25 14:38:15</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>-34.1678983, -70.7332416</t>
+          <t>-32.8792316, -70.6087616</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-34.16790, -70.73324</t>
+          <t>-32.87923, -70.60876</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026/09/24 07:25:03</t>
+          <t>2026/09/25 16:51:32</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>-34.2042466, -70.67914</t>
+          <t>-33.43344, -70.6504999</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>-34.20425, -70.67914</t>
+          <t>-33.43344, -70.65050</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>14:46:44</t>
+          <t>02:13:17</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>7.64</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="M101" t="n">
-        <v>56</v>
+        <v>122</v>
       </c>
       <c r="N101" t="n">
-        <v>18</v>
+        <v>53</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6327,57 +6327,57 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026/09/23 16:39:55</t>
+          <t>2026/09/25 15:13:11</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>-34.1677683, -70.7330216</t>
+          <t>-33.4364116, -70.62956</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-34.16777, -70.73302</t>
+          <t>-33.43641, -70.62956</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026/09/24 07:33:51</t>
+          <t>2026/09/28 06:11:55</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>-34.2064066, -70.6737083</t>
+          <t>-33.4452, -70.6199333</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>-34.20641, -70.67371</t>
+          <t>-33.44520, -70.61993</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>14:53:56</t>
+          <t>62:58:44</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>8.15</v>
+        <v>1.8</v>
       </c>
       <c r="M102" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="N102" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6386,57 +6386,57 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026/09/23 17:24:03</t>
+          <t>2026/09/25 16:52:47</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>-33.43728, -70.6294083</t>
+          <t>-33.434, -70.6501766</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-33.43728, -70.62941</t>
+          <t>-33.43400, -70.65018</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026/09/23 18:34:58</t>
+          <t>2026/09/25 19:28:53</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>-33.466715, -70.607045</t>
+          <t>-33.4347966, -70.6499983</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>-33.46672, -70.60704</t>
+          <t>-33.43480, -70.65000</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>01:10:55</t>
+          <t>02:36:06</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>5.1</v>
+        <v>0.12</v>
       </c>
       <c r="M103" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="N103" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6445,53 +6445,53 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026/09/23 17:36:46</t>
+          <t>2026/09/25 19:29:50</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>-32.83989, -70.961898</t>
+          <t>-33.4350916, -70.650465</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-32.83989, -70.96190</t>
+          <t>-33.43509, -70.65046</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026/09/24 11:26:33</t>
+          <t>2026/09/25 19:58:34</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>-33.360146, -70.806869</t>
+          <t>-33.4239633, -70.6725666</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>-33.36015, -70.80687</t>
+          <t>-33.42396, -70.67257</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>17:49:47</t>
+          <t>00:28:44</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>61.8</v>
+        <v>2.82</v>
       </c>
       <c r="M104" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -6504,57 +6504,57 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026/09/23 17:47:27</t>
+          <t>2026/09/25 19:59:49</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>-33.3618699, -70.6701616</t>
+          <t>-33.42366, -70.672645</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-33.36187, -70.67016</t>
+          <t>-33.42366, -70.67265</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026/09/23 19:20:36</t>
+          <t>2026/09/25 21:05:37</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>-33.4762583, -70.6982866</t>
+          <t>-32.8792216, -70.6088833</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>-33.47626, -70.69829</t>
+          <t>-32.87922, -70.60888</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>01:33:09</t>
+          <t>01:05:48</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>17.2</v>
+        <v>74.63</v>
       </c>
       <c r="M105" t="n">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="N105" t="n">
-        <v>25</v>
+        <v>73</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6563,47 +6563,47 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026/09/23 18:35:19</t>
+          <t>2026/09/25 20:45:59</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>-33.4667083, -70.6070283</t>
+          <t>-32.79762, -70.8870866</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-33.46671, -70.60703</t>
+          <t>-32.79762, -70.88709</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026/09/23 20:13:08</t>
+          <t>2026/09/25 21:37:31</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>-33.43611, -70.62983</t>
+          <t>-32.7685433, -70.8329983</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>-33.43611, -70.62983</t>
+          <t>-32.76854, -70.83300</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>01:37:49</t>
+          <t>00:51:32</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>5.43</v>
+        <v>6.41</v>
       </c>
       <c r="M106" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="N106" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="107">
@@ -6622,57 +6622,57 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026/09/23 19:14:09</t>
+          <t>2026/09/25 21:05:47</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>-32.879225, -70.6087533</t>
+          <t>-32.879215, -70.6087933</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-32.87922, -70.60875</t>
+          <t>-32.87922, -70.60879</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026/09/24 10:12:55</t>
+          <t>2026/09/26 08:55:03</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>-32.8853, -70.6115766</t>
+          <t>-32.84833, -70.5919733</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>-32.88530, -70.61158</t>
+          <t>-32.84833, -70.59197</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>14:58:46</t>
+          <t>11:49:16</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0.95</v>
+        <v>5.62</v>
       </c>
       <c r="M107" t="n">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="N107" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -6681,57 +6681,57 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026/09/23 19:21:51</t>
+          <t>2026/09/25 21:38:46</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>-33.47611, -70.6984816</t>
+          <t>-32.7686416, -70.8332483</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-33.47611, -70.69848</t>
+          <t>-32.76864, -70.83325</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026/09/24 07:43:29</t>
+          <t>2026/09/25 22:04:08</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>-33.47625, -70.6982899</t>
+          <t>-32.7977249, -70.8874783</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>-33.47625, -70.69829</t>
+          <t>-32.79772, -70.88748</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>12:21:38</t>
+          <t>00:25:22</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>11.16</v>
+        <v>6.23</v>
       </c>
       <c r="M108" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N108" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -6740,53 +6740,53 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026/09/23 20:13:52</t>
+          <t>2026/09/25 22:04:34</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>-33.4361833, -70.6295283</t>
+          <t>-32.7976133, -70.887115</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-33.43618, -70.62953</t>
+          <t>-32.79761, -70.88711</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026/09/25 07:13:15</t>
+          <t>2026/09/26 07:10:51</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>-33.4461766, -70.6193216</t>
+          <t>-32.7977, -70.887445</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>-33.44618, -70.61932</t>
+          <t>-32.79770, -70.88744</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>34:59:23</t>
+          <t>09:06:17</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.19</v>
+        <v>12.84</v>
       </c>
       <c r="M109" t="n">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="N109" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -6794,62 +6794,62 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026/09/24 02:11:38</t>
+          <t>2026/09/27 01:57:23</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>-34.205163, -70.677135</t>
+          <t>-34.042474, -70.681749</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-34.20516, -70.67714</t>
+          <t>-34.04247, -70.68175</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026/09/24 10:27:41</t>
+          <t>2026/09/28 00:59:54</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>-34.205424, -70.677213</t>
+          <t>-34.041867, -70.681404</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>-34.20542, -70.67721</t>
+          <t>-34.04187, -70.68140</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>08:16:03</t>
+          <t>23:02:31</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>LPR20251A02800014-DS</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -6858,175 +6858,175 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026/09/24 08:22:58</t>
+          <t>2026/09/27 02:11:15</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>-34.206332, -70.673789</t>
+          <t>-34.205678, -70.676839</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-34.20633, -70.67379</t>
+          <t>-34.20568, -70.67684</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026/09/24 09:18:58</t>
+          <t>2026/09/30 23:12:08</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>-34.206352, -70.673854</t>
+          <t>-34.205405, -70.677267</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>-34.20635, -70.67385</t>
+          <t>-34.20540, -70.67727</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>00:56:00</t>
+          <t>93:00:53</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="M111" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026/09/24 10:27:55</t>
+          <t>2026/09/28 03:46:15</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>-34.205423, -70.677214</t>
+          <t>-34.205603, -70.67714</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-34.20542, -70.67721</t>
+          <t>-34.20560, -70.67714</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026/09/24 13:20:48</t>
+          <t>2026/09/30 03:49:09</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>-34.206143, -70.674138</t>
+          <t>-34.205447, -70.677137</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>-34.20614, -70.67414</t>
+          <t>-34.20545, -70.67714</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>02:52:53</t>
+          <t>48:02:54</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0.4</v>
+        <v>0.06</v>
       </c>
       <c r="M112" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N112" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026/09/24 11:51:43</t>
+          <t>2026/09/28 20:29:38</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>-34.347182, -71.125748</t>
+          <t>-33.4761233, -70.6985033</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-34.34718, -71.12575</t>
+          <t>-33.47612, -70.69850</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026/09/24 11:59:43</t>
+          <t>2026/09/29 06:59:56</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>-34.347233, -71.125745</t>
+          <t>-33.4761833, -70.6984333</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>-34.34723, -71.12574</t>
+          <t>-33.47618, -70.69843</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>00:08:00</t>
+          <t>10:30:18</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="M113" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N113" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7035,175 +7035,175 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026/09/24 13:21:48</t>
+          <t>2026/09/29 14:14:22</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>-34.206341, -70.673913</t>
+          <t>-34.2042933, -70.6790483</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-34.20634, -70.67391</t>
+          <t>-34.20429, -70.67905</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026/09/24 14:17:13</t>
+          <t>2026/09/29 14:45:35</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>-34.205473, -70.677302</t>
+          <t>-34.2063833, -70.6736816</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>-34.20547, -70.67730</t>
+          <t>-34.20638, -70.67368</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>00:55:25</t>
+          <t>00:31:13</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0.37</v>
+        <v>0.65</v>
       </c>
       <c r="M114" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="N114" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026/09/24 13:27:02</t>
+          <t>2026/09/29 14:45:41</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>-34.346514, -71.125324</t>
+          <t>-34.2064566, -70.6737749</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-34.34651, -71.12532</t>
+          <t>-34.20646, -70.67377</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026/09/24 15:14:47</t>
+          <t>2026/09/29 15:02:34</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>-34.346198, -71.125541</t>
+          <t>-34.2088516, -70.6784083</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>-34.34620, -71.12554</t>
+          <t>-34.20885, -70.67841</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>01:47:45</t>
+          <t>00:16:53</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0.04</v>
+        <v>0.5</v>
       </c>
       <c r="M115" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="N115" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026/09/24 14:17:38</t>
+          <t>2026/09/29 15:02:41</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>-34.205446, -70.677348</t>
+          <t>-34.2088366, -70.6784433</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-34.20545, -70.67735</t>
+          <t>-34.20884, -70.67844</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026/09/27 01:13:50</t>
+          <t>2026/09/29 15:10:24</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>-34.205678, -70.676839</t>
+          <t>-34.2055783, -70.6765233</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>-34.20568, -70.67684</t>
+          <t>-34.20558, -70.67652</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>58:56:12</t>
+          <t>00:07:43</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0.08</v>
+        <v>0.54</v>
       </c>
       <c r="M116" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="N116" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7212,57 +7212,57 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026/09/24 14:30:12</t>
+          <t>2026/09/29 15:10:33</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>-34.205252, -70.680165</t>
+          <t>-34.2055833, -70.6766683</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-34.20525, -70.68017</t>
+          <t>-34.20558, -70.67667</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026/09/24 15:15:27</t>
+          <t>2026/09/29 15:17:16</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>-34.205258, -70.680072</t>
+          <t>-34.2053283, -70.6803716</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>-34.20526, -70.68007</t>
+          <t>-34.20533, -70.68037</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>00:45:15</t>
+          <t>00:06:43</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0.58</v>
+        <v>0.34</v>
       </c>
       <c r="M117" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="N117" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7271,57 +7271,57 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026/09/24 15:15:47</t>
+          <t>2026/09/29 15:17:21</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>-34.345945, -71.125747</t>
+          <t>-34.2052983, -70.6803616</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>-34.34595, -71.12575</t>
+          <t>-34.20530, -70.68036</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026/09/25 12:48:30</t>
+          <t>2026/09/29 15:36:24</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>-34.346461, -71.126063</t>
+          <t>-34.20408, -70.6772316</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>-34.34646, -71.12606</t>
+          <t>-34.20408, -70.67723</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>21:32:43</t>
+          <t>00:19:03</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0.34</v>
+        <v>0.4</v>
       </c>
       <c r="M118" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="N118" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7330,175 +7330,175 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026/09/24 15:15:58</t>
+          <t>2026/09/29 15:36:37</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>-34.20526, -70.680089</t>
+          <t>-34.2044066, -70.677265</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-34.20526, -70.68009</t>
+          <t>-34.20441, -70.67727</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026/09/24 15:23:37</t>
+          <t>2026/09/29 16:07:01</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>-34.205254, -70.680188</t>
+          <t>-34.207595, -70.6760166</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>-34.20525, -70.68019</t>
+          <t>-34.20759, -70.67602</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>00:07:39</t>
+          <t>00:30:24</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0.02</v>
+        <v>0.4</v>
       </c>
       <c r="M119" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="N119" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026/09/24 15:23:54</t>
+          <t>2026/09/29 16:08:16</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>-34.205297, -70.680202</t>
+          <t>-34.2074249, -70.676</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>-34.20530, -70.68020</t>
+          <t>-34.20742, -70.67600</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026/09/24 15:30:47</t>
+          <t>2026/09/29 17:17:11</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>-34.205297, -70.680211</t>
+          <t>-34.1677016, -70.7344666</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>-34.20530, -70.68021</t>
+          <t>-34.16770, -70.73447</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>00:06:53</t>
+          <t>01:08:55</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0.01</v>
+        <v>7.83</v>
       </c>
       <c r="M120" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="N120" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026/09/24 15:49:07</t>
+          <t>2026/09/29 17:18:26</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>-34.20545, -70.677304</t>
+          <t>-34.1678883, -70.7331966</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-34.20545, -70.67730</t>
+          <t>-34.16789, -70.73320</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026/09/25 07:48:22</t>
+          <t>2026/09/30 07:57:11</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>-34.205362, -70.677228</t>
+          <t>-34.20535, -70.680375</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>-34.20536, -70.67723</t>
+          <t>-34.20535, -70.68037</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>15:59:15</t>
+          <t>14:38:45</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0.03</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="M121" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="N121" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7507,470 +7507,470 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026/09/24 18:39:20</t>
+          <t>2026/09/29 18:09:06</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>-32.797605, -70.887025</t>
+          <t>-32.843495, -70.6010066</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>-32.79760, -70.88702</t>
+          <t>-32.84349, -70.60101</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026/09/25 07:11:23</t>
+          <t>2026/09/29 21:21:27</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>-32.88316, -70.6124083</t>
+          <t>-32.8791733, -70.60882</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>-32.88316, -70.61241</t>
+          <t>-32.87917, -70.60882</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>12:32:03</t>
+          <t>03:12:21</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>41.76</v>
+        <v>5.63</v>
       </c>
       <c r="M122" t="n">
-        <v>110</v>
+        <v>52</v>
       </c>
       <c r="N122" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>LPR20251V02900023-LL</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026/09/25 02:31:48</t>
+          <t>2026/09/29 21:21:37</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>-33.899779, -71.42949</t>
+          <t>-32.8791833, -70.6087983</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-33.89978, -71.42949</t>
+          <t>-32.87918, -70.60880</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026/09/26 01:52:03</t>
+          <t>2026/09/30 09:29:12</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>-33.89996, -71.429414</t>
+          <t>-32.8830983, -70.6123566</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>-33.89996, -71.42941</t>
+          <t>-32.88310, -70.61236</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>23:20:15</t>
+          <t>12:07:35</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0.09</v>
+        <v>14.03</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026/09/25 08:23:09</t>
+          <t>2026/09/30 12:35:25</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>-34.205444, -70.677355</t>
+          <t>-33.364985, -70.6766933</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>-34.20544, -70.67736</t>
+          <t>-33.36498, -70.67669</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026/09/25 08:43:01</t>
+          <t>2026/09/30 13:07:33</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>-34.2054, -70.677412</t>
+          <t>-33.3671433, -70.6956466</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>-34.20540, -70.67741</t>
+          <t>-33.36714, -70.69565</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>00:19:52</t>
+          <t>00:32:08</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0.05</v>
+        <v>4.63</v>
       </c>
       <c r="M124" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="N124" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026/09/25 20:18:25</t>
+          <t>2026/09/30 12:45:37</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>-32.7995383, -70.9086633</t>
+          <t>-33.359523, -70.80683</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>-32.79954, -70.90866</t>
+          <t>-33.35952, -70.80683</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026/09/25 20:45:43</t>
+          <t>2026/09/30 23:43:47</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>-32.7977316, -70.8874233</t>
+          <t>-33.359986, -70.807021</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>-32.79773, -70.88742</t>
+          <t>-33.35999, -70.80702</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>00:27:18</t>
+          <t>10:58:10</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.66</v>
+        <v>0.05</v>
       </c>
       <c r="M125" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026/09/25 20:45:59</t>
+          <t>2026/09/30 13:08:48</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>-32.79762, -70.8870866</t>
+          <t>-33.36717, -70.6958566</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>-32.79762, -70.88709</t>
+          <t>-33.36717, -70.69586</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026/09/25 21:37:31</t>
+          <t>2026/09/30 23:09:04</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>-32.7685433, -70.8329983</t>
+          <t>-33.36717, -70.6958566</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>-32.76854, -70.83300</t>
+          <t>-33.36717, -70.69586</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>00:51:32</t>
+          <t>10:00:16</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>6.41</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026/09/25 21:38:46</t>
+          <t>2026/09/30 17:05:50</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>-32.7686416, -70.8332483</t>
+          <t>-34.167845, -70.7330049</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>-32.76864, -70.83325</t>
+          <t>-34.16784, -70.73300</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026/09/25 22:04:08</t>
+          <t>2026/09/30 23:05:50</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>-32.7977249, -70.8874783</t>
+          <t>-34.167845, -70.7330049</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>-32.79772, -70.88748</t>
+          <t>-34.16784, -70.73300</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>00:25:22</t>
+          <t>06:00:00</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026/09/25 22:04:34</t>
+          <t>2026/09/30 17:06:57</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>-32.7976133, -70.887115</t>
+          <t>-34.1678933, -70.7330433</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88711</t>
+          <t>-34.16789, -70.73304</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026/09/26 07:10:51</t>
+          <t>2026/09/30 23:07:08</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>-32.7977, -70.887445</t>
+          <t>-34.1678933, -70.7330433</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>-32.79770, -70.88744</t>
+          <t>-34.16789, -70.73304</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>09:06:17</t>
+          <t>06:00:11</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>12.84</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026/09/27 01:57:23</t>
+          <t>2026/09/30 17:09:42</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>-34.042474, -70.681749</t>
+          <t>-34.1679316, -70.7330566</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>-34.04247, -70.68175</t>
+          <t>-34.16793, -70.73306</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026/09/28 00:59:54</t>
+          <t>2026/09/30 23:18:09</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>-34.041867, -70.681404</t>
+          <t>-34.1678466, -70.7330116</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>-34.04187, -70.68140</t>
+          <t>-34.16785, -70.73301</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>23:02:31</t>
+          <t>06:08:27</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="M129" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -7979,41 +7979,41 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026/09/28 03:46:15</t>
+          <t>2026/09/30 17:33:08</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>-34.205603, -70.67714</t>
+          <t>-33.4365083, -70.6295716</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>-34.20560, -70.67714</t>
+          <t>-33.43651, -70.62957</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026/09/29 23:12:52</t>
+          <t>2026/09/30 23:33:08</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>-34.205421, -70.677329</t>
+          <t>-33.4365083, -70.6295716</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>-34.20542, -70.67733</t>
+          <t>-33.43651, -70.62957</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>43:26:37</t>
+          <t>06:00:00</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
         <v>0</v>
@@ -8025,54 +8025,54 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026/09/28 16:34:03</t>
+          <t>2026/09/30 18:24:29</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>-33.436445, -70.6295783</t>
+          <t>-32.837145, -70.96704</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>-33.43644, -70.62958</t>
+          <t>-32.83714, -70.96704</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026/09/29 22:34:03</t>
+          <t>2026/09/30 20:02:04</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>-33.436445, -70.6295783</t>
+          <t>-32.838387, -70.955454</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>-33.43644, -70.62958</t>
+          <t>-32.83839, -70.95545</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>30:00:00</t>
+          <t>01:37:35</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M131" t="n">
         <v>0</v>
@@ -8088,645 +8088,114 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026/09/28 18:40:07</t>
+          <t>2026/09/30 18:58:52</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>-33.3621466, -70.6701</t>
+          <t>-33.47613, -70.6984866</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>-33.36215, -70.67010</t>
+          <t>-33.47613, -70.69849</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026/09/28 20:28:27</t>
+          <t>2026/09/30 22:58:58</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>-33.4762116, -70.6982766</t>
+          <t>-33.47613, -70.6984866</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>-33.47621, -70.69828</t>
+          <t>-33.47613, -70.69849</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>01:48:20</t>
+          <t>04:00:06</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>18.05</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026/09/28 20:29:38</t>
+          <t>2026/09/30 19:01:38</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>-33.4761233, -70.6985033</t>
+          <t>-32.8792366, -70.6087549</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>-33.47612, -70.69850</t>
+          <t>-32.87924, -70.60875</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026/09/29 06:59:56</t>
+          <t>2026/09/30 23:01:38</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>-33.4761833, -70.6984333</t>
+          <t>-32.8792366, -70.6087549</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>-33.47618, -70.69843</t>
+          <t>-32.87924, -70.60875</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>10:30:18</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>LPR20251L02790031-SV</t>
-        </is>
-      </c>
-      <c r="C134" t="n">
-        <v>1</v>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>2026/09/29 11:06:31</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>-34.346928, -71.125346</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>-34.34693, -71.12535</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>2026/09/29 15:34:47</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>-34.346197, -71.125629</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>-34.34620, -71.12563</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>04:28:16</t>
-        </is>
-      </c>
-      <c r="L134" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M134" t="n">
-        <v>4</v>
-      </c>
-      <c r="N134" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>LPR20251L02790031-SV</t>
-        </is>
-      </c>
-      <c r="C135" t="n">
-        <v>2</v>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>2026/09/29 15:35:46</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>-34.345979, -71.125753</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>-34.34598, -71.12575</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>2026/09/29 23:34:45</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>-34.346, -71.12575</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>-34.34600, -71.12575</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>07:58:59</t>
-        </is>
-      </c>
-      <c r="L135" t="n">
-        <v>0</v>
-      </c>
-      <c r="M135" t="n">
-        <v>0</v>
-      </c>
-      <c r="N135" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
-        </is>
-      </c>
-      <c r="C136" t="n">
-        <v>21</v>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>2026/09/29 16:08:16</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>-34.2074249, -70.676</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>-34.20742, -70.67600</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>2026/09/29 17:17:11</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>-34.1677016, -70.7344666</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>-34.16770, -70.73447</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>01:08:55</t>
-        </is>
-      </c>
-      <c r="L136" t="n">
-        <v>7.83</v>
-      </c>
-      <c r="M136" t="n">
-        <v>54</v>
-      </c>
-      <c r="N136" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>JAC X200 SJTJ-50</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>12</v>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>2026/09/29 17:14:42</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>-34.1677733, -70.7330083</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>-34.16777, -70.73301</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>2026/09/29 23:14:42</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>-34.1677733, -70.7330083</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>-34.16777, -70.73301</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>06:00:00</t>
-        </is>
-      </c>
-      <c r="L137" t="n">
-        <v>0</v>
-      </c>
-      <c r="M137" t="n">
-        <v>0</v>
-      </c>
-      <c r="N137" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
-        </is>
-      </c>
-      <c r="C138" t="n">
-        <v>22</v>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>2026/09/29 17:18:26</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>-34.1678883, -70.7331966</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>-34.16789, -70.73320</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>2026/09/29 23:19:54</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>-34.1678783, -70.7330383</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>-34.16788, -70.73304</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>06:01:28</t>
-        </is>
-      </c>
-      <c r="L138" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="M138" t="n">
-        <v>0</v>
-      </c>
-      <c r="N138" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
-        </is>
-      </c>
-      <c r="C139" t="n">
-        <v>8</v>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>2026/09/29 17:23:17</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>-34.167845, -70.733015</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>-34.16784, -70.73301</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>2026/09/29 23:26:21</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>-34.167845, -70.733015</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>-34.16784, -70.73301</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>06:03:04</t>
-        </is>
-      </c>
-      <c r="L139" t="n">
-        <v>0</v>
-      </c>
-      <c r="M139" t="n">
-        <v>0</v>
-      </c>
-      <c r="N139" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>SUZUKI CARRY SKDB-52</t>
-        </is>
-      </c>
-      <c r="C140" t="n">
-        <v>13</v>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>2026/09/29 18:09:06</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>-32.843495, -70.6010066</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>-32.84349, -70.60101</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>2026/09/29 21:21:27</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>-32.8791733, -70.60882</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>-32.87917, -70.60882</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>03:12:21</t>
-        </is>
-      </c>
-      <c r="L140" t="n">
-        <v>5.63</v>
-      </c>
-      <c r="M140" t="n">
-        <v>52</v>
-      </c>
-      <c r="N140" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
-        </is>
-      </c>
-      <c r="C141" t="n">
-        <v>12</v>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>2026/09/29 18:38:35</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>-33.47615, -70.6984816</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>-33.47615, -70.69848</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>2026/09/29 22:38:35</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>-33.47615, -70.6984816</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>-33.47615, -70.69848</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>04:00:00</t>
-        </is>
-      </c>
-      <c r="L141" t="n">
-        <v>0</v>
-      </c>
-      <c r="M141" t="n">
-        <v>0</v>
-      </c>
-      <c r="N141" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>SUZUKI CARRY SKDB-52</t>
-        </is>
-      </c>
-      <c r="C142" t="n">
-        <v>14</v>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Paradas</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>2026/09/29 21:21:37</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>-32.8791833, -70.6087983</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>-32.87918, -70.60880</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>2026/09/29 23:21:37</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>-32.8791833, -70.6087983</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>-32.87918, -70.60880</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>02:00:00</t>
-        </is>
-      </c>
-      <c r="L142" t="n">
-        <v>0</v>
-      </c>
-      <c r="M142" t="n">
-        <v>0</v>
-      </c>
-      <c r="N142" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8778,10 +8247,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1405.95</v>
+        <v>1254.29</v>
       </c>
       <c r="C2" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -8797,7 +8266,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>613.13</v>
+        <v>558.46</v>
       </c>
       <c r="C3" t="n">
         <v>18</v>
@@ -8816,10 +8285,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>586.23</v>
+        <v>579.85</v>
       </c>
       <c r="C4" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -8835,10 +8304,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>798.62</v>
+        <v>812.45</v>
       </c>
       <c r="C5" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -8854,7 +8323,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
@@ -8911,16 +8380,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.79</v>
+        <v>3.41</v>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -8974,7 +8443,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -8987,16 +8456,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -9006,10 +8475,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1183.45</v>
+        <v>1161.37</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -9025,7 +8494,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>129.42</v>
+        <v>115.56</v>
       </c>
       <c r="C15" t="n">
         <v>13</v>
@@ -9044,16 +8513,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>90.8</v>
+        <v>13.6</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>129</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17">
@@ -9063,16 +8532,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18">
@@ -9082,13 +8551,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.45</v>
+        <v>4.35</v>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
         <v>20</v>
@@ -9101,10 +8570,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>646</v>
+        <v>612.21</v>
       </c>
       <c r="C19" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,13 +446,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N133"/>
+  <dimension ref="A1:N134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Desde : 2026/09/24 04:00:00   Hasta : 2026/10/01 03:59:59</t>
+          <t>Desde : 2026/09/25 04:00:00   Hasta : 2026/10/02 03:59:59</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -545,53 +545,53 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026/09/24 00:05:48</t>
+          <t>2026/09/25 00:13:52</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-32.79762, -70.887105</t>
+          <t>-33.4361833, -70.6295283</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-32.79762, -70.88711</t>
+          <t>-33.43618, -70.62953</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026/09/24 07:51:00</t>
+          <t>2026/09/25 07:13:15</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-33.3672399, -70.6965616</t>
+          <t>-33.4461766, -70.6193216</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-33.36724, -70.69656</t>
+          <t>-33.44618, -70.61932</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>07:45:12</t>
+          <t>06:59:23</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>92.41</v>
+        <v>2.19</v>
       </c>
       <c r="M4" t="n">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="N4" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -604,53 +604,53 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026/09/24 00:11:22</t>
+          <t>2026/09/25 00:17:44</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-34.205566, -70.677323</t>
+          <t>-34.345997, -71.125783</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-34.20557, -70.67732</t>
+          <t>-34.34600, -71.12578</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026/09/24 01:13:58</t>
+          <t>2026/09/25 12:48:30</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-34.205163, -70.677135</t>
+          <t>-34.346461, -71.126063</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-34.20516, -70.67714</t>
+          <t>-34.34646, -71.12606</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>01:02:36</t>
+          <t>12:30:46</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.05</v>
+        <v>0.34</v>
       </c>
       <c r="M5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>LPR20251T02900038-RTN</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -658,58 +658,58 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026/09/24 00:13:52</t>
+          <t>2026/09/25 00:24:07</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-33.4361833, -70.6295283</t>
+          <t>-34.876578, -71.127348</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-33.43618, -70.62953</t>
+          <t>-34.87658, -71.12735</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026/09/25 07:13:15</t>
+          <t>2026/09/30 01:24:53</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-33.4461766, -70.6193216</t>
+          <t>-34.876425, -71.127141</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-33.44618, -70.61932</t>
+          <t>-34.87642, -71.12714</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>30:59:23</t>
+          <t>121:00:46</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.19</v>
+        <v>0.04</v>
       </c>
       <c r="M6" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LPR20251T02900038-RTN</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -717,52 +717,52 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026/09/24 00:22:58</t>
+          <t>2026/09/25 00:24:55</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-34.876437, -71.127341</t>
+          <t>-33.359986, -70.807048</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-34.87644, -71.12734</t>
+          <t>-33.35999, -70.80705</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026/09/30 01:24:53</t>
+          <t>2026/09/30 11:49:06</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-34.876425, -71.127141</t>
+          <t>-33.359523, -70.80683</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-34.87642, -71.12714</t>
+          <t>-33.35952, -70.80683</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>145:01:55</t>
+          <t>131:24:11</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8">
@@ -781,17 +781,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026/09/24 00:31:38</t>
+          <t>2026/09/25 00:31:22</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-33.899801, -71.429488</t>
+          <t>-33.899816, -71.429365</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-33.89980, -71.42949</t>
+          <t>-33.89982, -71.42937</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>25:02:31</t>
+          <t>01:02:47</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="M8" t="n">
         <v>2</v>
@@ -827,7 +827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -835,58 +835,58 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026/09/24 00:33:55</t>
+          <t>2026/09/25 00:34:54</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-33.360003, -70.807038</t>
+          <t>-34.57985, -70.961438</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-33.36000, -70.80704</t>
+          <t>-34.57985, -70.96144</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026/09/30 11:49:06</t>
+          <t>2026/09/28 01:38:35</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-33.359523, -70.80683</t>
+          <t>-34.579561, -70.961474</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-33.35952, -70.80683</t>
+          <t>-34.57956, -70.96147</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>155:15:11</t>
+          <t>73:03:41</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="M9" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -894,58 +894,58 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026/09/24 00:34:27</t>
+          <t>2026/09/25 00:35:53</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-34.57985, -70.961438</t>
+          <t>-33.4762016, -70.6984316</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-34.57985, -70.96144</t>
+          <t>-33.47620, -70.69843</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/09/28 01:38:35</t>
+          <t>2026/09/25 07:45:24</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-34.579561, -70.961474</t>
+          <t>-33.4762749, -70.6983349</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-34.57956, -70.96147</t>
+          <t>-33.47627, -70.69833</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>97:04:08</t>
+          <t>07:09:31</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.09</v>
+        <v>11.15</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -958,53 +958,53 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026/09/24 00:37:43</t>
+          <t>2026/09/25 00:36:58</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-34.167765, -70.7330316</t>
+          <t>-32.879235, -70.60878</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-34.16777, -70.73303</t>
+          <t>-32.87924, -70.60878</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026/09/24 07:25:03</t>
+          <t>2026/09/25 07:47:56</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-34.2042466, -70.67914</t>
+          <t>-32.8529266, -70.62402</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-34.20425, -70.67914</t>
+          <t>-32.85293, -70.62402</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>06:47:20</t>
+          <t>07:10:58</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>7.61</v>
+        <v>6.41</v>
       </c>
       <c r="M11" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="N11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1017,53 +1017,53 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026/09/24 00:40:00</t>
+          <t>2026/09/25 00:39:20</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-34.1677683, -70.7330216</t>
+          <t>-32.797605, -70.887025</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-34.16777, -70.73302</t>
+          <t>-32.79760, -70.88702</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026/09/24 07:33:51</t>
+          <t>2026/09/25 07:11:23</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-34.2064066, -70.6737083</t>
+          <t>-32.88316, -70.6124083</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-34.20641, -70.67371</t>
+          <t>-32.88316, -70.61241</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>06:53:51</t>
+          <t>06:32:03</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>8.15</v>
+        <v>41.76</v>
       </c>
       <c r="M12" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="N12" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LPR20251E02900022</t>
+          <t>LPR20251A02800014-DS</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1076,53 +1076,53 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026/09/24 00:43:02</t>
+          <t>2026/09/25 00:42:20</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-33.366736, -70.696931</t>
+          <t>-34.205382, -70.677293</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-33.36674, -70.69693</t>
+          <t>-34.20538, -70.67729</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026/09/30 23:43:56</t>
+          <t>2026/09/27 01:13:50</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-33.36746, -70.69652</t>
+          <t>-34.205678, -70.676839</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-33.36746, -70.69652</t>
+          <t>-34.20568, -70.67684</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>167:00:54</t>
+          <t>48:31:30</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>LPR20251E02900022</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1135,44 +1135,44 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026/09/24 00:51:55</t>
+          <t>2026/09/25 00:43:29</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-34.345954, -71.125788</t>
+          <t>-33.366736, -70.696931</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-34.34595, -71.12579</t>
+          <t>-33.36674, -70.69693</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/09/24 11:13:19</t>
+          <t>2026/10/01 23:43:56</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-34.346426, -71.125197</t>
+          <t>-33.36746, -70.69652</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-34.34643, -71.12520</t>
+          <t>-33.36746, -70.69652</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>10:21:24</t>
+          <t>167:00:27</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
         <v>3</v>
@@ -1181,7 +1181,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LPR20251T02800022</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1194,53 +1194,53 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026/09/24 00:56:11</t>
+          <t>2026/09/25 00:50:08</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-33.367244, -70.69677</t>
+          <t>-34.20545, -70.677304</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-33.36724, -70.69677</t>
+          <t>-34.20545, -70.67730</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/09/30 23:35:40</t>
+          <t>2026/09/25 07:48:22</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-33.367244, -70.69677</t>
+          <t>-34.205362, -70.677228</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-33.36724, -70.69677</t>
+          <t>-34.20536, -70.67723</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>166:39:29</t>
+          <t>06:58:14</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>LPR20251T02800022</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1248,52 +1248,52 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026/09/24 00:58:36</t>
+          <t>2026/09/25 00:57:32</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-34.20544, -70.677291</t>
+          <t>-33.367244, -70.69677</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-34.20544, -70.67729</t>
+          <t>-33.36724, -70.69677</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/09/24 07:43:39</t>
+          <t>2026/10/01 23:35:40</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-34.205371, -70.680097</t>
+          <t>-33.367244, -70.69677</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-34.20537, -70.68010</t>
+          <t>-33.36724, -70.69677</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>06:45:03</t>
+          <t>166:38:08</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1312,17 +1312,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026/09/24 00:59:08</t>
+          <t>2026/09/25 00:59:07</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-34.042704, -70.681722</t>
+          <t>-34.042504, -70.681533</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-34.04270, -70.68172</t>
+          <t>-34.04250, -70.68153</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1342,11 +1342,11 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>24:00:39</t>
+          <t>00:00:40</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -1358,7 +1358,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1371,53 +1371,53 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026/09/24 01:14:09</t>
+          <t>2026/09/25 01:15:34</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-32.879225, -70.6087533</t>
+          <t>-33.3671916, -70.6958816</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-32.87922, -70.60875</t>
+          <t>-33.36719, -70.69588</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026/09/24 10:12:55</t>
+          <t>2026/09/30 12:09:06</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-32.8853, -70.6115766</t>
+          <t>-33.3507416, -70.6959183</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-32.88530, -70.61158</t>
+          <t>-33.35074, -70.69592</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>08:58:46</t>
+          <t>130:53:32</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0.95</v>
+        <v>5.16</v>
       </c>
       <c r="M18" t="n">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="N18" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1430,53 +1430,53 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026/09/24 01:15:34</t>
+          <t>2026/09/25 01:31:32</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-33.3671916, -70.6958816</t>
+          <t>-34.16782, -70.73301</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-33.36719, -70.69588</t>
+          <t>-34.16782, -70.73301</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026/09/30 12:09:06</t>
+          <t>2026/09/25 07:15:02</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-33.3507416, -70.6959183</t>
+          <t>-34.1679016, -70.7330383</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-33.35074, -70.69592</t>
+          <t>-34.16790, -70.73304</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>154:53:32</t>
+          <t>05:43:30</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.16</v>
+        <v>0.04</v>
       </c>
       <c r="M19" t="n">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="N19" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1489,53 +1489,53 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026/09/24 01:22:13</t>
+          <t>2026/09/25 01:36:48</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-33.47611, -70.6984816</t>
+          <t>-34.1677816, -70.7330016</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-33.47611, -70.69848</t>
+          <t>-34.16778, -70.73300</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026/09/24 07:43:29</t>
+          <t>2026/09/25 07:39:02</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-33.47625, -70.6982899</t>
+          <t>-34.2053049, -70.6801799</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-33.47625, -70.69829</t>
+          <t>-34.20530, -70.68018</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>06:21:16</t>
+          <t>06:02:14</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>11.16</v>
+        <v>7.58</v>
       </c>
       <c r="M20" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="N20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1548,41 +1548,41 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026/09/24 02:11:38</t>
+          <t>2026/09/25 01:57:14</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-34.205163, -70.677135</t>
+          <t>-34.042755, -70.681629</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-34.20516, -70.67714</t>
+          <t>-34.04275, -70.68163</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026/09/24 10:27:41</t>
+          <t>2026/09/26 00:59:56</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-34.205424, -70.677213</t>
+          <t>-34.042857, -70.681747</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-34.20542, -70.67721</t>
+          <t>-34.04286, -70.68175</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>08:16:03</t>
+          <t>23:02:42</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -1594,7 +1594,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>LPR20251V02900023-LL</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1602,62 +1602,62 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026/09/24 07:26:03</t>
+          <t>2026/09/25 02:31:48</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-34.20527, -70.6800733</t>
+          <t>-33.899779, -71.42949</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-34.20527, -70.68007</t>
+          <t>-33.89978, -71.42949</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026/09/24 07:46:51</t>
+          <t>2026/09/26 01:52:03</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-34.2053083, -70.6801166</t>
+          <t>-33.89996, -71.429414</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-34.20531, -70.68012</t>
+          <t>-33.89996, -71.42941</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>00:20:48</t>
+          <t>23:20:15</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0.49</v>
+        <v>0.09</v>
       </c>
       <c r="M22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1666,53 +1666,53 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026/09/24 07:34:10</t>
+          <t>2026/09/25 06:56:23</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-34.206395, -70.673705</t>
+          <t>-32.838367, -70.955507</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-34.20640, -70.67370</t>
+          <t>-32.83837, -70.95551</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026/09/24 08:21:39</t>
+          <t>2026/09/25 07:07:07</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-34.206395, -70.673705</t>
+          <t>-32.839517, -70.956188</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-34.20640, -70.67370</t>
+          <t>-32.83952, -70.95619</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>00:47:29</t>
+          <t>00:10:44</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="M23" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="N23" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1725,53 +1725,53 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026/09/24 07:43:51</t>
+          <t>2026/09/25 07:12:38</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-33.4763183, -70.6983683</t>
+          <t>-32.8831616, -70.6124266</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-33.47632, -70.69837</t>
+          <t>-32.88316, -70.61243</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026/09/24 09:17:47</t>
+          <t>2026/09/25 13:01:53</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-33.3623316, -70.6701233</t>
+          <t>-32.756715, -70.7345333</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-33.36233, -70.67012</t>
+          <t>-32.75671, -70.73453</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>01:33:56</t>
+          <t>05:49:15</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>20.42</v>
+        <v>24.62</v>
       </c>
       <c r="M24" t="n">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="N24" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1784,57 +1784,57 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026/09/24 07:43:58</t>
+          <t>2026/09/25 07:14:30</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-34.205304, -70.680147</t>
+          <t>-33.44648, -70.6208016</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-34.20530, -70.68015</t>
+          <t>-33.44648, -70.62080</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026/09/24 08:22:55</t>
+          <t>2026/09/25 09:56:13</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-34.20633, -70.673777</t>
+          <t>-33.3661266, -70.6955216</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-34.20633, -70.67378</t>
+          <t>-33.36613, -70.69552</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>00:38:57</t>
+          <t>02:41:43</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0.74</v>
+        <v>13.39</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1843,47 +1843,47 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026/09/24 07:44:12</t>
+          <t>2026/09/25 07:16:17</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-32.838355, -70.955539</t>
+          <t>-34.1678983, -70.7330049</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-32.83835, -70.95554</t>
+          <t>-34.16790, -70.73300</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026/09/24 11:26:33</t>
+          <t>2026/09/25 07:41:57</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-33.360146, -70.806869</t>
+          <t>-34.2052916, -70.68031</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-33.36015, -70.80687</t>
+          <t>-34.20529, -70.68031</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>03:42:21</t>
+          <t>00:25:40</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>60.81</v>
+        <v>7.44</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1902,44 +1902,44 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026/09/24 07:47:04</t>
+          <t>2026/09/25 07:40:17</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-34.205235, -70.68009</t>
+          <t>-34.2052766, -70.6801349</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-34.20524, -70.68009</t>
+          <t>-34.20528, -70.68013</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026/09/24 09:55:04</t>
+          <t>2026/09/25 07:46:36</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-34.2053116, -70.68014</t>
+          <t>-34.2055183, -70.6775416</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-34.20531, -70.68014</t>
+          <t>-34.20552, -70.67754</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>02:08:00</t>
+          <t>00:06:19</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.53</v>
+        <v>0.26</v>
       </c>
       <c r="M27" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="N27" t="n">
         <v>9</v>
@@ -1948,11 +1948,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1961,57 +1961,57 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026/09/24 07:51:28</t>
+          <t>2026/09/25 07:42:41</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-33.3672199, -70.6966966</t>
+          <t>-34.204085, -70.678975</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-33.36722, -70.69670</t>
+          <t>-34.20408, -70.67897</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026/09/24 10:52:41</t>
+          <t>2026/09/25 09:15:43</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-33.3699699, -70.6707849</t>
+          <t>-34.2051666, -70.6775016</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-33.36997, -70.67078</t>
+          <t>-34.20517, -70.67750</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>03:01:13</t>
+          <t>01:33:02</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.76</v>
+        <v>0.18</v>
       </c>
       <c r="M28" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="N28" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2020,53 +2020,53 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026/09/24 08:22:19</t>
+          <t>2026/09/25 07:46:01</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-34.2070116, -70.6749866</t>
+          <t>-33.4763216, -70.6983966</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-34.20701, -70.67499</t>
+          <t>-33.47632, -70.69840</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026/09/24 09:04:22</t>
+          <t>2026/09/25 09:29:53</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-34.2088366, -70.6784283</t>
+          <t>-33.360285, -70.8090433</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-34.20884, -70.67843</t>
+          <t>-33.36028, -70.80904</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>00:42:03</t>
+          <t>01:43:52</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0.38</v>
+        <v>37.1</v>
       </c>
       <c r="M29" t="n">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="N29" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2074,121 +2074,121 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026/09/24 08:22:58</t>
+          <t>2026/09/25 07:46:49</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-34.206332, -70.673789</t>
+          <t>-34.20529, -70.6775133</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-34.20633, -70.67379</t>
+          <t>-34.20529, -70.67751</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026/09/24 09:18:58</t>
+          <t>2026/09/25 10:39:55</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-34.206352, -70.673854</t>
+          <t>-34.2052816, -70.6775066</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-34.20635, -70.67385</t>
+          <t>-34.20528, -70.67751</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>00:56:00</t>
+          <t>02:53:06</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026/09/25 07:48:28</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-34.205327, -70.677293</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-34.20533, -70.67729</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026/09/25 08:10:06</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>-34.205121, -70.677514</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>-34.20512, -70.67751</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>00:21:38</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M31" t="n">
         <v>4</v>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>2026/09/24 09:04:26</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>-34.2088316, -70.6784433</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>-34.20883, -70.67844</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2026/09/24 09:45:03</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>-34.2052816, -70.6803766</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>-34.20528, -70.68038</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>00:40:37</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M31" t="n">
-        <v>17</v>
-      </c>
       <c r="N31" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2197,47 +2197,47 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026/09/24 09:18:16</t>
+          <t>2026/09/25 07:49:11</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-33.3621233, -70.6701516</t>
+          <t>-32.853015, -70.6241333</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-33.36212, -70.67015</t>
+          <t>-32.85301, -70.62413</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026/09/24 10:28:35</t>
+          <t>2026/09/25 08:12:47</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-34.011455, -70.7037066</t>
+          <t>-32.882485, -70.6119416</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-34.01145, -70.70371</t>
+          <t>-32.88249, -70.61194</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>01:10:19</t>
+          <t>00:23:36</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>78.36</v>
+        <v>5.59</v>
       </c>
       <c r="M32" t="n">
-        <v>123</v>
+        <v>46</v>
       </c>
       <c r="N32" t="n">
-        <v>68</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33">
@@ -2247,66 +2247,66 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026/09/24 09:19:42</t>
+          <t>2026/09/25 08:11:06</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-34.206354, -70.673854</t>
+          <t>-34.205344, -70.677493</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-34.20635, -70.67385</t>
+          <t>-34.20534, -70.67749</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026/09/24 14:29:35</t>
+          <t>2026/09/25 08:22:32</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-34.205377, -70.680129</t>
+          <t>-34.205442, -70.677361</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-34.20538, -70.68013</t>
+          <t>-34.20544, -70.67736</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>05:09:53</t>
+          <t>00:11:26</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0.88</v>
+        <v>0.03</v>
       </c>
       <c r="M33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2315,53 +2315,53 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026/09/24 09:45:07</t>
+          <t>2026/09/25 08:14:02</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-34.205275, -70.6803683</t>
+          <t>-32.8831133, -70.6123516</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-34.20528, -70.68037</t>
+          <t>-32.88311, -70.61235</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026/09/24 11:09:51</t>
+          <t>2026/09/25 08:31:14</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-34.2063616, -70.67374</t>
+          <t>-32.88338, -70.612335</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-34.20636, -70.67374</t>
+          <t>-32.88338, -70.61234</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>01:24:44</t>
+          <t>00:17:12</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0.98</v>
+        <v>0.13</v>
       </c>
       <c r="M34" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N34" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -2369,52 +2369,52 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026/09/24 09:55:09</t>
+          <t>2026/09/25 08:23:09</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-34.2052516, -70.680095</t>
+          <t>-34.205444, -70.677355</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-34.20525, -70.68009</t>
+          <t>-34.20544, -70.67736</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026/09/24 10:56:59</t>
+          <t>2026/09/25 08:43:01</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-34.2053333, -70.6774466</t>
+          <t>-34.2054, -70.677412</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-34.20533, -70.67745</t>
+          <t>-34.20540, -70.67741</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>01:01:50</t>
+          <t>00:19:52</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0.26</v>
+        <v>0.05</v>
       </c>
       <c r="M35" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="N35" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2424,7 +2424,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2433,44 +2433,44 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026/09/24 10:13:39</t>
+          <t>2026/09/25 08:31:17</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-32.8846149, -70.611565</t>
+          <t>-32.8833933, -70.6123333</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-32.88461, -70.61156</t>
+          <t>-32.88339, -70.61233</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026/09/24 11:58:06</t>
+          <t>2026/09/25 08:55:10</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-32.8829483, -70.61251</t>
+          <t>-32.8824283, -70.6115533</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-32.88295, -70.61251</t>
+          <t>-32.88243, -70.61155</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>01:44:27</t>
+          <t>00:23:53</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0.7</v>
+        <v>0.17</v>
       </c>
       <c r="M36" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N36" t="n">
         <v>13</v>
@@ -2479,11 +2479,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2492,57 +2492,57 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026/09/24 10:27:55</t>
+          <t>2026/09/25 08:43:07</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-34.205423, -70.677214</t>
+          <t>-34.205387, -70.677402</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-34.20542, -70.67721</t>
+          <t>-34.20539, -70.67740</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026/09/24 13:20:48</t>
+          <t>2026/09/25 10:57:25</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-34.206143, -70.674138</t>
+          <t>-34.205452, -70.677288</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-34.20614, -70.67414</t>
+          <t>-34.20545, -70.67729</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>02:52:53</t>
+          <t>02:14:18</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0.4</v>
+        <v>0.63</v>
       </c>
       <c r="M37" t="n">
         <v>4</v>
       </c>
       <c r="N37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2551,116 +2551,116 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026/09/24 10:29:50</t>
+          <t>2026/09/25 08:55:35</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-34.01146, -70.7037266</t>
+          <t>-32.8836966, -70.6115766</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-34.01146, -70.70373</t>
+          <t>-32.88370, -70.61158</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026/09/24 11:45:10</t>
+          <t>2026/09/25 10:14:17</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-34.2052449, -70.6775066</t>
+          <t>-32.8829033, -70.6123849</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-34.20524, -70.67751</t>
+          <t>-32.88290, -70.61238</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>01:15:20</t>
+          <t>01:18:42</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>26.25</v>
+        <v>0.25</v>
       </c>
       <c r="M38" t="n">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="N38" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026/09/25 09:10:07</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-33.36015, -70.80746</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-33.36015, -70.80746</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026/09/25 09:16:12</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>-33.360659, -70.809035</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>-33.36066, -70.80903</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>00:06:05</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M39" t="n">
+        <v>9</v>
+      </c>
+      <c r="N39" t="n">
         <v>3</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2026/09/24 10:53:38</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>-33.370745, -70.6707466</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>-33.37074, -70.67075</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>2026/09/24 11:18:54</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>-33.3674449, -70.6960183</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>-33.36744, -70.69602</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>00:25:16</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="M39" t="n">
-        <v>57</v>
-      </c>
-      <c r="N39" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2669,57 +2669,57 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026/09/24 10:58:14</t>
+          <t>2026/09/25 09:15:48</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-34.20534, -70.6773049</t>
+          <t>-34.2052183, -70.6774933</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-34.20534, -70.67730</t>
+          <t>-34.20522, -70.67749</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026/09/24 11:08:07</t>
+          <t>2026/09/25 09:38:39</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-34.2053133, -70.6801816</t>
+          <t>-34.2052066, -70.6774916</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>-34.20531, -70.68018</t>
+          <t>-34.20521, -70.67749</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>00:09:53</t>
+          <t>00:22:51</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0.35</v>
+        <v>0.41</v>
       </c>
       <c r="M40" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2728,57 +2728,57 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026/09/24 11:08:17</t>
+          <t>2026/09/25 09:16:13</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-34.20522, -70.6801133</t>
+          <t>-33.360659, -70.809035</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-34.20522, -70.68011</t>
+          <t>-33.36066, -70.80903</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026/09/24 12:00:39</t>
+          <t>2026/09/25 13:15:39</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-34.1900716, -70.7093933</t>
+          <t>-33.360197, -70.806776</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-34.19007, -70.70939</t>
+          <t>-33.36020, -70.80678</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>00:52:22</t>
+          <t>03:59:26</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.4</v>
+        <v>0.36</v>
       </c>
       <c r="M41" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2787,57 +2787,57 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026/09/24 11:10:01</t>
+          <t>2026/09/25 09:30:04</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-34.2063966, -70.6737783</t>
+          <t>-33.3606283, -70.8090366</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-34.20640, -70.67378</t>
+          <t>-33.36063, -70.80904</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026/09/24 11:24:22</t>
+          <t>2026/09/25 10:20:27</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-34.20812, -70.677075</t>
+          <t>-33.36129, -70.8068783</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-34.20812, -70.67708</t>
+          <t>-33.36129, -70.80688</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>00:14:21</t>
+          <t>00:50:23</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0.36</v>
+        <v>0.48</v>
       </c>
       <c r="M42" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N42" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2846,57 +2846,57 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026/09/24 11:14:09</t>
+          <t>2026/09/25 09:38:45</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-34.346408, -71.125193</t>
+          <t>-34.2052383, -70.6775033</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-34.34641, -71.12519</t>
+          <t>-34.20524, -70.67750</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026/09/24 11:26:27</t>
+          <t>2026/09/25 10:12:29</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-34.346422, -71.125393</t>
+          <t>-34.2056983, -70.6760549</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-34.34642, -71.12539</t>
+          <t>-34.20570, -70.67605</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>00:12:18</t>
+          <t>00:33:44</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="M43" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N43" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2905,47 +2905,47 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026/09/24 11:19:12</t>
+          <t>2026/09/25 09:56:56</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-33.3673749, -70.6959866</t>
+          <t>-33.3670249, -70.695565</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-33.36737, -70.69599</t>
+          <t>-33.36702, -70.69557</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026/09/24 14:48:45</t>
+          <t>2026/09/25 14:29:28</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-32.8825533, -70.61196</t>
+          <t>-33.38888, -70.6165516</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-32.88255, -70.61196</t>
+          <t>-33.38888, -70.61655</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>03:29:33</t>
+          <t>04:32:32</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>65.59999999999999</v>
+        <v>29.4</v>
       </c>
       <c r="M44" t="n">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="N44" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45">
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2964,57 +2964,57 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026/09/24 11:24:56</t>
+          <t>2026/09/25 10:13:03</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-34.2088116, -70.6784266</t>
+          <t>-34.2055083, -70.6765966</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-34.20881, -70.67843</t>
+          <t>-34.20551, -70.67660</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026/09/24 12:00:04</t>
+          <t>2026/09/25 10:22:58</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-34.190125, -70.709515</t>
+          <t>-34.20407, -70.6789766</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-34.19013, -70.70951</t>
+          <t>-34.20407, -70.67898</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>00:35:08</t>
+          <t>00:09:55</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>4.23</v>
+        <v>0.28</v>
       </c>
       <c r="M45" t="n">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="N45" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3023,57 +3023,57 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026/09/24 11:27:15</t>
+          <t>2026/09/25 10:14:26</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-34.346401, -71.12545</t>
+          <t>-32.8831366, -70.6123683</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-34.34640, -71.12545</t>
+          <t>-32.88314, -70.61237</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026/09/24 11:51:02</t>
+          <t>2026/09/25 13:33:38</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-34.347171, -71.125732</t>
+          <t>-32.8792283, -70.6088366</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-34.34717, -71.12573</t>
+          <t>-32.87923, -70.60884</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>00:23:47</t>
+          <t>03:19:12</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0.27</v>
+        <v>1.33</v>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="N46" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3082,57 +3082,57 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026/09/24 11:27:18</t>
+          <t>2026/09/25 10:20:33</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-33.360146, -70.806869</t>
+          <t>-33.3612916, -70.80684</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-33.36015, -70.80687</t>
+          <t>-33.36129, -70.80684</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026/09/24 15:03:06</t>
+          <t>2026/09/25 10:28:52</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-33.36052, -70.809028</t>
+          <t>-33.3613233, -70.80687</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-33.36052, -70.80903</t>
+          <t>-33.36132, -70.80687</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>03:35:48</t>
+          <t>00:08:19</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>14.13</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3141,116 +3141,116 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026/09/24 11:45:36</t>
+          <t>2026/09/25 10:23:03</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-34.205295, -70.6775266</t>
+          <t>-34.20411, -70.6790299</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-34.20529, -70.67753</t>
+          <t>-34.20411, -70.67903</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026/09/24 11:55:39</t>
+          <t>2026/09/25 11:10:43</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-34.20835, -70.677595</t>
+          <t>-34.2050716, -70.6802133</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-34.20835, -70.67759</t>
+          <t>-34.20507, -70.68021</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>00:10:03</t>
+          <t>00:47:40</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0.54</v>
+        <v>0.15</v>
       </c>
       <c r="M48" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="N48" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026/09/24 11:51:43</t>
+          <t>2026/09/25 10:29:06</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-34.347182, -71.125748</t>
+          <t>-33.361305, -70.8071349</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-34.34718, -71.12575</t>
+          <t>-33.36131, -70.80713</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026/09/24 11:59:43</t>
+          <t>2026/09/25 11:09:05</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-34.347233, -71.125745</t>
+          <t>-33.3613366, -70.807175</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>-34.34723, -71.12574</t>
+          <t>-33.36134, -70.80718</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>00:08:00</t>
+          <t>00:39:59</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="M49" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N49" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3259,44 +3259,44 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026/09/24 11:56:54</t>
+          <t>2026/09/25 10:39:59</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-34.2080283, -70.6775933</t>
+          <t>-34.2052416, -70.6775216</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-34.20803, -70.67759</t>
+          <t>-34.20524, -70.67752</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026/09/24 12:26:11</t>
+          <t>2026/09/25 11:16:02</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-34.20666, -70.6759283</t>
+          <t>-34.2050766, -70.6801466</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>-34.20666, -70.67593</t>
+          <t>-34.20508, -70.68015</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>00:29:17</t>
+          <t>00:36:03</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="M50" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="N50" t="n">
         <v>10</v>
@@ -3305,11 +3305,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3318,57 +3318,57 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026/09/24 11:59:21</t>
+          <t>2026/09/25 10:57:32</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-32.8824283, -70.6119</t>
+          <t>-34.205444, -70.677298</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-32.88243, -70.61190</t>
+          <t>-34.20544, -70.67730</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026/09/24 12:05:50</t>
+          <t>2026/09/28 02:48:55</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>-32.8851266, -70.6110783</t>
+          <t>-34.205603, -70.67714</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>-32.88513, -70.61108</t>
+          <t>-34.20560, -70.67714</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>00:06:29</t>
+          <t>63:51:23</t>
         </is>
       </c>
       <c r="L51" t="n">
         <v>0.45</v>
       </c>
       <c r="M51" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="N51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3377,57 +3377,57 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026/09/24 12:00:32</t>
+          <t>2026/09/25 11:10:20</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-34.1900033, -70.7093533</t>
+          <t>-33.36163, -70.8071633</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-34.19000, -70.70935</t>
+          <t>-33.36163, -70.80716</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026/09/24 12:52:52</t>
+          <t>2026/09/25 11:35:23</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-34.2057333, -70.6761616</t>
+          <t>-33.3622033, -70.8090666</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>-34.20573, -70.67616</t>
+          <t>-33.36220, -70.80907</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>00:52:20</t>
+          <t>00:25:03</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.77</v>
+        <v>1.82</v>
       </c>
       <c r="M52" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="N52" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3436,47 +3436,47 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026/09/24 12:00:43</t>
+          <t>2026/09/25 11:10:55</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-34.347249, -71.125753</t>
+          <t>-34.2053033, -70.6804233</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-34.34725, -71.12575</t>
+          <t>-34.20530, -70.68042</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026/09/24 12:27:44</t>
+          <t>2026/09/25 11:50:16</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-34.346725, -71.125178</t>
+          <t>-34.205275, -70.6803666</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>-34.34672, -71.12518</t>
+          <t>-34.20528, -70.68037</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>00:27:01</t>
+          <t>00:39:21</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0.35</v>
+        <v>0.01</v>
       </c>
       <c r="M53" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N53" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3495,57 +3495,57 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026/09/24 12:00:59</t>
+          <t>2026/09/25 11:16:08</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-34.1902266, -70.7093466</t>
+          <t>-34.2051783, -70.6801566</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-34.19023, -70.70935</t>
+          <t>-34.20518, -70.68016</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026/09/24 13:00:57</t>
+          <t>2026/09/25 13:43:55</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>-34.2054666, -70.6774233</t>
+          <t>-32.8417516, -70.9368433</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>-34.20547, -70.67742</t>
+          <t>-32.84175, -70.93684</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>00:59:58</t>
+          <t>02:27:47</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.64</v>
+        <v>176.03</v>
       </c>
       <c r="M54" t="n">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="N54" t="n">
-        <v>17</v>
+        <v>77</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3554,57 +3554,57 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026/09/24 12:07:05</t>
+          <t>2026/09/25 11:35:34</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-32.8844783, -70.6110616</t>
+          <t>-33.3617599, -70.8090833</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-32.88448, -70.61106</t>
+          <t>-33.36176, -70.80908</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026/09/24 12:43:54</t>
+          <t>2026/09/25 13:19:56</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-32.8333516, -70.5945266</t>
+          <t>-33.4762933, -70.6983383</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>-32.83335, -70.59453</t>
+          <t>-33.47629, -70.69834</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>00:36:49</t>
+          <t>01:44:22</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>8.960000000000001</v>
+        <v>33.99</v>
       </c>
       <c r="M55" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="N55" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3613,47 +3613,47 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026/09/24 12:26:25</t>
+          <t>2026/09/25 11:51:21</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-34.2073449, -70.6760033</t>
+          <t>-34.2041199, -70.6790516</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-34.20734, -70.67600</t>
+          <t>-34.20412, -70.67905</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026/09/24 13:07:45</t>
+          <t>2026/09/25 13:57:03</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>-34.0418483, -70.6818516</t>
+          <t>-33.4314616, -71.0321983</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>-34.04185, -70.68185</t>
+          <t>-33.43146, -71.03220</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>00:41:20</t>
+          <t>02:05:42</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>24.96</v>
+        <v>130.2</v>
       </c>
       <c r="M56" t="n">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="N56" t="n">
-        <v>44</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57">
@@ -3663,53 +3663,53 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026/09/24 12:27:52</t>
+          <t>2026/09/25 12:49:21</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-34.346677, -71.125204</t>
+          <t>-34.346311, -71.12606</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-34.34668, -71.12520</t>
+          <t>-34.34631, -71.12606</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026/09/24 13:26:27</t>
+          <t>2026/09/25 13:24:08</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>-34.346532, -71.125169</t>
+          <t>-34.347549, -71.126086</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-34.34653, -71.12517</t>
+          <t>-34.34755, -71.12609</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>00:58:35</t>
+          <t>00:34:47</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0.02</v>
+        <v>1.01</v>
       </c>
       <c r="M57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N57" t="n">
         <v>3</v>
@@ -3718,11 +3718,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -3731,57 +3731,57 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026/09/24 12:44:38</t>
+          <t>2026/09/25 13:03:08</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-32.8334383, -70.5942483</t>
+          <t>-32.7584083, -70.729305</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-32.83344, -70.59425</t>
+          <t>-32.75841, -70.72930</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026/09/24 14:36:46</t>
+          <t>2026/09/25 13:33:38</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>-32.8792233, -70.6089283</t>
+          <t>-32.797745, -70.88742</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>-32.87922, -70.60893</t>
+          <t>-32.79774, -70.88742</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>01:52:08</t>
+          <t>00:30:30</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>44.55</v>
+        <v>17.68</v>
       </c>
       <c r="M58" t="n">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="N58" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3790,57 +3790,57 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026/09/24 12:53:34</t>
+          <t>2026/09/25 13:20:03</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-34.20706, -70.67719</t>
+          <t>-33.4763466, -70.6983866</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-34.20706, -70.67719</t>
+          <t>-33.47635, -70.69839</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026/09/24 13:45:39</t>
+          <t>2026/09/25 14:55:34</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>-34.20565, -70.6762066</t>
+          <t>-33.4112849, -70.6370083</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>-34.20565, -70.67621</t>
+          <t>-33.41128, -70.63701</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>00:52:05</t>
+          <t>01:35:31</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0.19</v>
+        <v>16.04</v>
       </c>
       <c r="M59" t="n">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="N59" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -3849,57 +3849,57 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026/09/24 13:02:12</t>
+          <t>2026/09/25 13:24:57</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>-34.2054616, -70.677315</t>
+          <t>-34.347751, -71.126117</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-34.20546, -70.67731</t>
+          <t>-34.34775, -71.12612</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026/09/24 13:14:52</t>
+          <t>2026/09/25 14:02:25</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>-34.2051383, -70.6755883</t>
+          <t>-34.346422, -71.126335</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>-34.20514, -70.67559</t>
+          <t>-34.34642, -71.12633</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>00:12:40</t>
+          <t>00:37:28</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0.3</v>
+        <v>0.86</v>
       </c>
       <c r="M60" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="N60" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3908,57 +3908,57 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026/09/24 13:09:00</t>
+          <t>2026/09/25 13:33:43</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-34.0429066, -70.6816716</t>
+          <t>-32.8792233, -70.6087716</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-34.04291, -70.68167</t>
+          <t>-32.87922, -70.60877</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026/09/24 13:22:41</t>
+          <t>2026/09/25 14:01:39</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>-34.0421883, -70.680195</t>
+          <t>-32.8800916, -70.6035233</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>-34.04219, -70.68019</t>
+          <t>-32.88009, -70.60352</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>00:13:41</t>
+          <t>00:27:56</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0.46</v>
+        <v>0.53</v>
       </c>
       <c r="M61" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="N61" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3967,57 +3967,57 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026/09/24 13:15:52</t>
+          <t>2026/09/25 13:34:34</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>-34.2063016, -70.6737599</t>
+          <t>-32.7976266, -70.8870866</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-34.20630, -70.67376</t>
+          <t>-32.79763, -70.88709</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026/09/24 14:20:09</t>
+          <t>2026/09/25 15:27:44</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>-34.20539, -70.6801583</t>
+          <t>-32.744875, -70.7906449</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>-34.20539, -70.68016</t>
+          <t>-32.74488, -70.79064</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>01:04:17</t>
+          <t>01:53:10</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0.83</v>
+        <v>11.13</v>
       </c>
       <c r="M62" t="n">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="N62" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4026,57 +4026,57 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026/09/24 13:21:48</t>
+          <t>2026/09/25 13:44:07</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-34.206341, -70.673913</t>
+          <t>-32.8416366, -70.93678</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-34.20634, -70.67391</t>
+          <t>-32.84164, -70.93678</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026/09/24 14:17:13</t>
+          <t>2026/09/25 14:48:45</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>-34.205473, -70.677302</t>
+          <t>-32.7432249, -70.7330266</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>-34.20547, -70.67730</t>
+          <t>-32.74322, -70.73303</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>00:55:25</t>
+          <t>01:04:38</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0.37</v>
+        <v>36.79</v>
       </c>
       <c r="M63" t="n">
-        <v>4</v>
+        <v>118</v>
       </c>
       <c r="N63" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4085,116 +4085,116 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026/09/24 13:23:20</t>
+          <t>2026/09/25 13:58:18</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-34.0422916, -70.6801799</t>
+          <t>-33.425675, -71.0393433</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-34.04229, -70.68018</t>
+          <t>-33.42567, -71.03934</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026/09/24 13:45:09</t>
+          <t>2026/09/25 15:44:04</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>-34.0421183, -70.6801349</t>
+          <t>-33.08735, -71.3622916</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>-34.04212, -70.68013</t>
+          <t>-33.08735, -71.36229</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>00:21:49</t>
+          <t>01:45:46</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0.02</v>
+        <v>75.14</v>
       </c>
       <c r="M64" t="n">
-        <v>7</v>
+        <v>123</v>
       </c>
       <c r="N64" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026/09/24 13:27:02</t>
+          <t>2026/09/25 14:02:54</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-34.346514, -71.125324</t>
+          <t>-32.8782316, -70.6034333</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-34.34651, -71.12532</t>
+          <t>-32.87823, -70.60343</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026/09/24 15:14:47</t>
+          <t>2026/09/25 14:38:11</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>-34.346198, -71.125541</t>
+          <t>-32.8792216, -70.608805</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>-34.34620, -71.12554</t>
+          <t>-32.87922, -70.60881</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>01:47:45</t>
+          <t>00:35:17</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0.04</v>
+        <v>0.74</v>
       </c>
       <c r="M65" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="N65" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4203,57 +4203,57 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026/09/24 13:45:56</t>
+          <t>2026/09/25 14:03:25</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>-34.2055733, -70.676615</t>
+          <t>-34.346671, -71.126341</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-34.20557, -70.67661</t>
+          <t>-34.34667, -71.12634</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026/09/24 15:52:53</t>
+          <t>2026/09/25 14:13:25</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>-34.2041066, -70.67899</t>
+          <t>-34.34698, -71.126362</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>-34.20411, -70.67899</t>
+          <t>-34.34698, -71.12636</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>02:06:57</t>
+          <t>00:10:00</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0.27</v>
+        <v>0.04</v>
       </c>
       <c r="M66" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="N66" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4262,53 +4262,53 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026/09/24 13:46:16</t>
+          <t>2026/09/25 14:08:55</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>-34.0449666, -70.6801866</t>
+          <t>-33.360181, -70.806779</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-34.04497, -70.68019</t>
+          <t>-33.36018, -70.80678</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026/09/24 15:29:22</t>
+          <t>2026/09/25 14:17:50</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>-33.4762716, -70.6983483</t>
+          <t>-33.36014, -70.806867</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>-33.47627, -70.69835</t>
+          <t>-33.36014, -70.80687</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>01:43:06</t>
+          <t>00:08:55</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>69.28</v>
+        <v>0.01</v>
       </c>
       <c r="M67" t="n">
-        <v>113</v>
+        <v>8</v>
       </c>
       <c r="N67" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -4316,62 +4316,62 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026/09/24 14:17:38</t>
+          <t>2026/09/25 14:14:26</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>-34.205446, -70.677348</t>
+          <t>-34.347204, -71.126365</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-34.20545, -70.67735</t>
+          <t>-34.34720, -71.12637</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026/09/27 01:13:50</t>
+          <t>2026/09/25 14:24:26</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>-34.205678, -70.676839</t>
+          <t>-34.346286, -71.126098</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>-34.20568, -70.67684</t>
+          <t>-34.34629, -71.12610</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>58:56:12</t>
+          <t>00:10:00</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0.08</v>
+        <v>0.17</v>
       </c>
       <c r="M68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4380,116 +4380,116 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026/09/24 14:20:46</t>
+          <t>2026/09/25 14:19:02</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-34.2051566, -70.6801299</t>
+          <t>-33.360681, -70.809045</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-34.20516, -70.68013</t>
+          <t>-33.36068, -70.80904</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026/09/24 14:28:24</t>
+          <t>2026/09/26 14:27:18</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>-34.2051333, -70.680145</t>
+          <t>-32.838367, -70.955473</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>-34.20513, -70.68014</t>
+          <t>-32.83837, -70.95547</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>00:07:38</t>
+          <t>24:08:16</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0.01</v>
+        <v>133.78</v>
       </c>
       <c r="M69" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N69" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026/09/24 14:28:40</t>
+          <t>2026/09/25 14:24:51</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>-34.2052466, -70.6801016</t>
+          <t>-34.346253, -71.125985</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-34.20525, -70.68010</t>
+          <t>-34.34625, -71.12599</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026/09/24 16:14:21</t>
+          <t>2026/09/25 15:07:34</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>-34.2052116, -70.6775099</t>
+          <t>-34.346117, -71.125698</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>-34.20521, -70.67751</t>
+          <t>-34.34612, -71.12570</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>01:45:41</t>
+          <t>00:42:43</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0.35</v>
+        <v>0.03</v>
       </c>
       <c r="M70" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="N70" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4498,47 +4498,47 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026/09/24 14:30:12</t>
+          <t>2026/09/25 14:30:37</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>-34.205252, -70.680165</t>
+          <t>-33.3887316, -70.6166066</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-34.20525, -70.68017</t>
+          <t>-33.38873, -70.61661</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026/09/24 15:15:27</t>
+          <t>2026/09/25 15:12:26</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>-34.205258, -70.680072</t>
+          <t>-33.4362633, -70.6295983</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>-34.20526, -70.68007</t>
+          <t>-33.43626, -70.62960</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>00:45:15</t>
+          <t>00:41:49</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0.58</v>
+        <v>6.71</v>
       </c>
       <c r="M71" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="N71" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="72">
@@ -4548,7 +4548,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4557,57 +4557,57 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026/09/24 14:36:58</t>
+          <t>2026/09/25 14:38:15</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>-32.879235, -70.60878</t>
+          <t>-32.8792316, -70.6087616</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-32.87924, -70.60878</t>
+          <t>-32.87923, -70.60876</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026/09/25 07:47:56</t>
+          <t>2026/09/25 16:51:32</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>-32.8529266, -70.62402</t>
+          <t>-33.43344, -70.6504999</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>-32.85293, -70.62402</t>
+          <t>-33.43344, -70.65050</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>17:10:58</t>
+          <t>02:13:17</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>6.41</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="M72" t="n">
-        <v>38</v>
+        <v>122</v>
       </c>
       <c r="N72" t="n">
-        <v>16</v>
+        <v>53</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -4616,57 +4616,57 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026/09/24 14:50:00</t>
+          <t>2026/09/25 14:50:00</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>-32.88321, -70.6124516</t>
+          <t>-32.7433566, -70.73271</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-32.88321, -70.61245</t>
+          <t>-32.74336, -70.73271</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026/09/24 17:50:05</t>
+          <t>2026/09/25 16:20:13</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>-32.788285, -70.8306849</t>
+          <t>-32.743235, -70.7297366</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>-32.78829, -70.83068</t>
+          <t>-32.74323, -70.72974</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>03:00:05</t>
+          <t>01:30:13</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>40.44</v>
+        <v>1.12</v>
       </c>
       <c r="M73" t="n">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="N73" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -4675,47 +4675,47 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026/09/24 15:03:08</t>
+          <t>2026/09/25 14:56:49</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>-33.36052, -70.809029</t>
+          <t>-33.410875, -70.6388583</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-33.36052, -70.80903</t>
+          <t>-33.41087, -70.63886</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026/09/25 07:07:07</t>
+          <t>2026/09/25 16:54:48</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>-32.839517, -70.956188</t>
+          <t>-33.3624316, -70.6701516</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>-32.83952, -70.95619</t>
+          <t>-33.36243, -70.67015</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>16:03:59</t>
+          <t>01:57:59</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>75.34999999999999</v>
+        <v>31.01</v>
       </c>
       <c r="M74" t="n">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="N74" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="75">
@@ -4725,66 +4725,66 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026/09/24 15:15:47</t>
+          <t>2026/09/25 15:08:34</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>-34.345945, -71.125747</t>
+          <t>-34.345986, -71.125724</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-34.34595, -71.12575</t>
+          <t>-34.34599, -71.12572</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026/09/25 12:48:30</t>
+          <t>2026/09/27 01:04:06</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>-34.346461, -71.126063</t>
+          <t>-34.346003, -71.125758</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>-34.34646, -71.12606</t>
+          <t>-34.34600, -71.12576</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>21:32:43</t>
+          <t>33:55:32</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0.34</v>
+        <v>0.01</v>
       </c>
       <c r="M75" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -4793,112 +4793,112 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026/09/24 15:15:58</t>
+          <t>2026/09/25 15:13:11</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-34.20526, -70.680089</t>
+          <t>-33.4364116, -70.62956</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-34.20526, -70.68009</t>
+          <t>-33.43641, -70.62956</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026/09/24 15:23:37</t>
+          <t>2026/09/28 06:11:55</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>-34.205254, -70.680188</t>
+          <t>-33.4452, -70.6199333</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>-34.20525, -70.68019</t>
+          <t>-33.44520, -70.61993</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>00:07:39</t>
+          <t>62:58:44</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0.02</v>
+        <v>1.8</v>
       </c>
       <c r="M76" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="N76" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026/09/24 15:23:54</t>
+          <t>2026/09/25 15:28:59</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>-34.205297, -70.680202</t>
+          <t>-32.7442583, -70.7893699</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-34.20530, -70.68020</t>
+          <t>-32.74426, -70.78937</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026/09/24 15:30:47</t>
+          <t>2026/09/25 16:18:52</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>-34.205297, -70.680211</t>
+          <t>-32.74662, -70.6616616</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>-34.20530, -70.68021</t>
+          <t>-32.74662, -70.66166</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>00:06:53</t>
+          <t>00:49:53</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0.01</v>
+        <v>16.22</v>
       </c>
       <c r="M77" t="n">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="N77" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -4911,57 +4911,57 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026/09/24 15:29:57</t>
+          <t>2026/09/25 15:44:19</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>-33.4763316, -70.698415</t>
+          <t>-33.0873266, -71.3623483</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-33.47633, -70.69841</t>
+          <t>-33.08733, -71.36235</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026/09/24 16:57:52</t>
+          <t>2026/09/26 11:29:39</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>-33.362385, -70.6701316</t>
+          <t>-33.0873483, -71.36227</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>-33.36239, -70.67013</t>
+          <t>-33.08735, -71.36227</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>01:27:55</t>
+          <t>19:45:20</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>25.05</v>
+        <v>0.08</v>
       </c>
       <c r="M78" t="n">
-        <v>87</v>
+        <v>9</v>
       </c>
       <c r="N78" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -4970,175 +4970,175 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026/09/24 15:31:46</t>
+          <t>2026/09/25 16:19:09</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>-34.20527, -70.680189</t>
+          <t>-32.74662, -70.6616449</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-34.20527, -70.68019</t>
+          <t>-32.74662, -70.66164</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026/09/24 15:48:25</t>
+          <t>2026/09/25 19:08:06</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>-34.20548, -70.677407</t>
+          <t>-32.7906433, -70.8730199</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>-34.20548, -70.67741</t>
+          <t>-32.79064, -70.87302</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>00:16:39</t>
+          <t>02:48:57</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0.34</v>
+        <v>25.38</v>
       </c>
       <c r="M79" t="n">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="N79" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026/09/24 15:49:07</t>
+          <t>2026/09/25 16:21:18</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>-34.20545, -70.677304</t>
+          <t>-32.7430816, -70.7298016</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-34.20545, -70.67730</t>
+          <t>-32.74308, -70.72980</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026/09/25 07:48:22</t>
+          <t>2026/09/27 12:25:39</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>-34.205362, -70.677228</t>
+          <t>-32.6228783, -70.7205266</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>-34.20536, -70.67723</t>
+          <t>-32.62288, -70.72053</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>15:59:15</t>
+          <t>44:04:21</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0.03</v>
+        <v>15.06</v>
       </c>
       <c r="M80" t="n">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="N80" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C81" t="n">
+        <v>10</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026/09/25 16:52:47</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-33.434, -70.6501766</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-33.43400, -70.65018</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2026/09/25 19:28:53</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>-33.4347966, -70.6499983</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>-33.43480, -70.65000</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>02:36:06</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M81" t="n">
+        <v>13</v>
+      </c>
+      <c r="N81" t="n">
         <v>11</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>2026/09/24 15:54:08</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>-34.2041649, -70.67908</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>-34.20416, -70.67908</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>2026/09/24 16:22:20</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>-34.2056733, -70.67627</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>-34.20567, -70.67627</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>00:28:12</t>
-        </is>
-      </c>
-      <c r="L81" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="M81" t="n">
-        <v>24</v>
-      </c>
-      <c r="N81" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5147,57 +5147,57 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026/09/24 16:14:29</t>
+          <t>2026/09/25 16:55:19</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>-34.2053283, -70.6775299</t>
+          <t>-33.3623199, -70.6701466</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-34.20533, -70.67753</t>
+          <t>-33.36232, -70.67015</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026/09/24 16:40:42</t>
+          <t>2026/09/25 18:33:07</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>-34.205365, -70.6774516</t>
+          <t>-33.45174, -70.6920966</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>-34.20537, -70.67745</t>
+          <t>-33.45174, -70.69210</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>00:26:13</t>
+          <t>01:37:48</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0.01</v>
+        <v>14.44</v>
       </c>
       <c r="M82" t="n">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="N82" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5206,57 +5206,57 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026/09/24 16:23:35</t>
+          <t>2026/09/25 18:34:22</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>-34.20516, -70.6774983</t>
+          <t>-33.4518933, -70.6923633</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-34.20516, -70.67750</t>
+          <t>-33.45189, -70.69236</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026/09/24 16:29:57</t>
+          <t>2026/09/25 19:36:29</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>-34.2041116, -70.6790016</t>
+          <t>-33.4762866, -70.698275</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>-34.20411, -70.67900</t>
+          <t>-33.47629, -70.69827</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>00:06:22</t>
+          <t>01:02:07</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0.18</v>
+        <v>3.74</v>
       </c>
       <c r="M83" t="n">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="N83" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5265,57 +5265,57 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026/09/24 16:30:02</t>
+          <t>2026/09/25 19:09:21</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>-34.2041433, -70.6790466</t>
+          <t>-32.7911066, -70.8728983</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-34.20414, -70.67905</t>
+          <t>-32.79111, -70.87290</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026/09/24 17:30:49</t>
+          <t>2026/09/25 19:25:41</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>-34.1679133, -70.7330449</t>
+          <t>-32.7977383, -70.8873616</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>-34.16791, -70.73304</t>
+          <t>-32.79774, -70.88736</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>01:00:47</t>
+          <t>00:16:20</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>7.58</v>
+        <v>1.76</v>
       </c>
       <c r="M84" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="N84" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5324,57 +5324,57 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026/09/24 16:41:57</t>
+          <t>2026/09/25 19:26:56</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>-34.2055249, -70.6774249</t>
+          <t>-32.79761, -70.8870466</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-34.20552, -70.67742</t>
+          <t>-32.79761, -70.88705</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026/09/24 17:38:55</t>
+          <t>2026/09/25 20:17:10</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>-34.1678783, -70.73303</t>
+          <t>-32.7995983, -70.9088316</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>-34.16788, -70.73303</t>
+          <t>-32.79960, -70.90883</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>00:56:58</t>
+          <t>00:50:14</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>7.7</v>
+        <v>2.7</v>
       </c>
       <c r="M85" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N85" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5383,57 +5383,57 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026/09/24 16:58:26</t>
+          <t>2026/09/25 19:29:50</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>-33.36221, -70.6701216</t>
+          <t>-33.4350916, -70.650465</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-33.36221, -70.67012</t>
+          <t>-33.43509, -70.65046</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026/09/24 18:34:00</t>
+          <t>2026/09/25 19:58:34</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>-33.4761983, -70.6981583</t>
+          <t>-33.4239633, -70.6725666</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>-33.47620, -70.69816</t>
+          <t>-33.42396, -70.67257</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>01:35:34</t>
+          <t>00:28:44</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>17.6</v>
+        <v>2.82</v>
       </c>
       <c r="M86" t="n">
         <v>55</v>
       </c>
       <c r="N86" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5442,57 +5442,57 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026/09/24 17:31:32</t>
+          <t>2026/09/25 19:37:44</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>-34.16782, -70.73301</t>
+          <t>-33.4761383, -70.69849</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-34.16782, -70.73301</t>
+          <t>-33.47614, -70.69849</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026/09/25 07:15:02</t>
+          <t>2026/09/25 21:23:13</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>-34.1679016, -70.7330383</t>
+          <t>-33.4762133, -70.6983833</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>-34.16790, -70.73304</t>
+          <t>-33.47621, -70.69838</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>13:43:30</t>
+          <t>01:45:29</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0.04</v>
+        <v>51.01</v>
       </c>
       <c r="M87" t="n">
-        <v>8</v>
+        <v>97</v>
       </c>
       <c r="N87" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5501,47 +5501,47 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026/09/24 17:39:32</t>
+          <t>2026/09/25 19:59:49</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>-34.1677816, -70.7330016</t>
+          <t>-33.42366, -70.672645</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-34.16778, -70.73300</t>
+          <t>-33.42366, -70.67265</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026/09/25 07:39:02</t>
+          <t>2026/09/25 21:05:37</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>-34.2053049, -70.6801799</t>
+          <t>-32.8792216, -70.6088833</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>-34.20530, -70.68018</t>
+          <t>-32.87922, -70.60888</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>13:59:30</t>
+          <t>01:05:48</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>7.58</v>
+        <v>74.63</v>
       </c>
       <c r="M88" t="n">
-        <v>63</v>
+        <v>129</v>
       </c>
       <c r="N88" t="n">
-        <v>23</v>
+        <v>73</v>
       </c>
     </row>
     <row r="89">
@@ -5551,7 +5551,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5560,47 +5560,47 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026/09/24 17:50:54</t>
+          <t>2026/09/25 20:18:25</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>-32.7855033, -70.8316366</t>
+          <t>-32.7995383, -70.9086633</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-32.78550, -70.83164</t>
+          <t>-32.79954, -70.90866</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026/09/24 18:06:45</t>
+          <t>2026/09/25 20:45:43</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>-32.7977349, -70.8874299</t>
+          <t>-32.7977316, -70.8874233</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>-32.79773, -70.88743</t>
+          <t>-32.79773, -70.88742</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>00:15:51</t>
+          <t>00:27:18</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>7.36</v>
+        <v>2.66</v>
       </c>
       <c r="M89" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="N89" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="90">
@@ -5610,7 +5610,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5619,53 +5619,53 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026/09/24 18:07:19</t>
+          <t>2026/09/25 20:45:59</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>-32.79763, -70.8870999</t>
+          <t>-32.79762, -70.8870866</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-32.79763, -70.88710</t>
+          <t>-32.79762, -70.88709</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026/09/24 18:38:29</t>
+          <t>2026/09/25 21:37:31</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>-32.7977266, -70.887315</t>
+          <t>-32.7685433, -70.8329983</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>-32.79773, -70.88732</t>
+          <t>-32.76854, -70.83300</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>00:31:10</t>
+          <t>00:51:32</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0.39</v>
+        <v>6.41</v>
       </c>
       <c r="M90" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="N90" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -5678,175 +5678,175 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026/09/24 18:35:15</t>
+          <t>2026/09/25 21:05:47</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>-33.4762016, -70.6984316</t>
+          <t>-32.879215, -70.6087933</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-33.47620, -70.69843</t>
+          <t>-32.87922, -70.60879</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026/09/25 07:45:24</t>
+          <t>2026/09/26 08:55:03</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>-33.4762749, -70.6983349</t>
+          <t>-32.84833, -70.5919733</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>-33.47627, -70.69833</t>
+          <t>-32.84833, -70.59197</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>13:10:09</t>
+          <t>11:49:16</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>11.15</v>
+        <v>5.62</v>
       </c>
       <c r="M91" t="n">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="N91" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C92" t="n">
+        <v>13</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2026/09/25 21:24:28</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>-33.4760983, -70.69852</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-33.47610, -70.69852</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2026/09/26 08:25:09</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>-33.4762483, -70.6983149</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>-33.47625, -70.69831</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>11:00:41</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M92" t="n">
         <v>8</v>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>2026/09/24 18:39:20</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>-32.797605, -70.887025</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>-32.79760, -70.88702</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>2026/09/25 07:11:23</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>-32.88316, -70.6124083</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>-32.88316, -70.61241</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>12:32:03</t>
-        </is>
-      </c>
-      <c r="L92" t="n">
-        <v>41.76</v>
-      </c>
-      <c r="M92" t="n">
-        <v>110</v>
-      </c>
       <c r="N92" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026/09/25 08:11:06</t>
+          <t>2026/09/25 21:38:46</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>-34.205344, -70.677493</t>
+          <t>-32.7686416, -70.8332483</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-34.20534, -70.67749</t>
+          <t>-32.76864, -70.83325</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026/09/25 08:22:32</t>
+          <t>2026/09/25 22:04:08</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>-34.205442, -70.677361</t>
+          <t>-32.7977249, -70.8874783</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>-34.20544, -70.67736</t>
+          <t>-32.79772, -70.88748</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>00:11:26</t>
+          <t>00:25:22</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0.03</v>
+        <v>6.23</v>
       </c>
       <c r="M93" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="N93" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -5855,53 +5855,53 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026/09/25 09:56:56</t>
+          <t>2026/09/25 22:04:34</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>-33.3670249, -70.695565</t>
+          <t>-32.7976133, -70.887115</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-33.36702, -70.69557</t>
+          <t>-32.79761, -70.88711</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026/09/25 14:29:28</t>
+          <t>2026/09/26 07:10:51</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>-33.38888, -70.6165516</t>
+          <t>-32.7977, -70.887445</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>-33.38888, -70.61655</t>
+          <t>-32.79770, -70.88744</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>04:32:32</t>
+          <t>09:06:17</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>29.4</v>
+        <v>12.84</v>
       </c>
       <c r="M94" t="n">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="N94" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -5914,57 +5914,57 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026/09/25 12:49:21</t>
+          <t>2026/09/27 01:57:23</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>-34.346311, -71.12606</t>
+          <t>-34.042474, -70.681749</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-34.34631, -71.12606</t>
+          <t>-34.04247, -70.68175</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026/09/25 13:24:08</t>
+          <t>2026/09/28 00:59:54</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>-34.347549, -71.126086</t>
+          <t>-34.041867, -70.681404</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>-34.34755, -71.12609</t>
+          <t>-34.04187, -70.68140</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>00:34:47</t>
+          <t>23:02:31</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M95" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="N95" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>LPR20251A02800014-DS</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -5973,57 +5973,57 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026/09/25 14:02:54</t>
+          <t>2026/09/27 02:11:15</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>-32.8782316, -70.6034333</t>
+          <t>-34.205678, -70.676839</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-32.87823, -70.60343</t>
+          <t>-34.20568, -70.67684</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026/09/25 14:38:11</t>
+          <t>2026/10/01 23:12:00</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>-32.8792216, -70.608805</t>
+          <t>-34.205394, -70.677257</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>-32.87922, -70.60881</t>
+          <t>-34.20539, -70.67726</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>00:35:17</t>
+          <t>117:00:45</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0.74</v>
+        <v>0.13</v>
       </c>
       <c r="M96" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6032,57 +6032,57 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026/09/25 14:14:26</t>
+          <t>2026/09/28 16:47:18</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>-34.347204, -71.126365</t>
+          <t>-32.7432949, -70.7327983</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-34.34720, -71.12637</t>
+          <t>-32.74329, -70.73280</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026/09/25 14:24:26</t>
+          <t>2026/09/28 18:30:41</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>-34.346286, -71.126098</t>
+          <t>-32.7431733, -70.7296533</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>-34.34629, -71.12610</t>
+          <t>-32.74317, -70.72965</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>00:10:00</t>
+          <t>01:43:23</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0.17</v>
+        <v>0.79</v>
       </c>
       <c r="M97" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="N97" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6091,175 +6091,175 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026/09/25 14:19:02</t>
+          <t>2026/09/28 18:31:56</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>-33.360681, -70.809045</t>
+          <t>-32.74321, -70.7296183</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-33.36068, -70.80904</t>
+          <t>-32.74321, -70.72962</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026/09/26 14:27:18</t>
+          <t>2026/09/29 07:16:48</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>-32.838367, -70.955473</t>
+          <t>-33.4821416, -70.7653783</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95547</t>
+          <t>-33.48214, -70.76538</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>24:08:16</t>
+          <t>12:44:52</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>133.78</v>
+        <v>96.23999999999999</v>
       </c>
       <c r="M98" t="n">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="N98" t="n">
-        <v>8</v>
+        <v>63</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026/09/25 14:24:51</t>
+          <t>2026/09/28 20:29:38</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>-34.346253, -71.125985</t>
+          <t>-33.4761233, -70.6985033</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-34.34625, -71.12599</t>
+          <t>-33.47612, -70.69850</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026/09/25 15:07:34</t>
+          <t>2026/09/29 06:59:56</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>-34.346117, -71.125698</t>
+          <t>-33.4761833, -70.6984333</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>-34.34612, -71.12570</t>
+          <t>-33.47618, -70.69843</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>00:42:43</t>
+          <t>10:30:18</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="M99" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="N99" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C100" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2026/09/29 11:06:31</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>-34.346928, -71.125346</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-34.34693, -71.12535</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2026/09/29 15:34:47</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>-34.346197, -71.125629</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>-34.34620, -71.12563</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>04:28:16</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M100" t="n">
+        <v>4</v>
+      </c>
+      <c r="N100" t="n">
         <v>3</v>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>2026/09/25 14:30:37</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>-33.3887316, -70.6166066</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>-33.38873, -70.61661</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>2026/09/25 15:12:26</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>-33.4362633, -70.6295983</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>-33.43626, -70.62960</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>00:41:49</t>
-        </is>
-      </c>
-      <c r="L100" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="M100" t="n">
-        <v>50</v>
-      </c>
-      <c r="N100" t="n">
-        <v>23</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6268,57 +6268,57 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026/09/25 14:38:15</t>
+          <t>2026/09/29 12:00:42</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>-32.8792316, -70.6087616</t>
+          <t>-34.1899616, -70.70926</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-32.87923, -70.60876</t>
+          <t>-34.18996, -70.70926</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026/09/25 16:51:32</t>
+          <t>2026/09/29 13:41:59</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>-33.43344, -70.6504999</t>
+          <t>-34.2053933, -70.6808299</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>-33.43344, -70.65050</t>
+          <t>-34.20539, -70.68083</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>02:13:17</t>
+          <t>01:41:17</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>83.56999999999999</v>
+        <v>3.33</v>
       </c>
       <c r="M101" t="n">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="N101" t="n">
-        <v>53</v>
+        <v>24</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6327,57 +6327,57 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026/09/25 15:13:11</t>
+          <t>2026/09/29 13:43:14</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>-33.4364116, -70.62956</t>
+          <t>-34.2053833, -70.68031</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-33.43641, -70.62956</t>
+          <t>-34.20538, -70.68031</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026/09/28 06:11:55</t>
+          <t>2026/09/29 13:53:13</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>-33.4452, -70.6199333</t>
+          <t>-34.2053633, -70.6802916</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>-33.44520, -70.61993</t>
+          <t>-34.20536, -70.68029</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>62:58:44</t>
+          <t>00:09:59</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="N102" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6386,57 +6386,57 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026/09/25 16:52:47</t>
+          <t>2026/09/29 13:54:28</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>-33.434, -70.6501766</t>
+          <t>-34.20521, -70.680225</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-33.43400, -70.65018</t>
+          <t>-34.20521, -70.68022</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026/09/25 19:28:53</t>
+          <t>2026/09/29 14:13:33</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>-33.4347966, -70.6499983</t>
+          <t>-34.2051133, -70.6801616</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>-33.43480, -70.65000</t>
+          <t>-34.20511, -70.68016</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>02:36:06</t>
+          <t>00:19:05</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0.12</v>
+        <v>0.01</v>
       </c>
       <c r="M103" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N103" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6445,57 +6445,57 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026/09/25 19:29:50</t>
+          <t>2026/09/29 14:14:22</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>-33.4350916, -70.650465</t>
+          <t>-34.2042933, -70.6790483</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-33.43509, -70.65046</t>
+          <t>-34.20429, -70.67905</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026/09/25 19:58:34</t>
+          <t>2026/09/29 14:45:35</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>-33.4239633, -70.6725666</t>
+          <t>-34.2063833, -70.6736816</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>-33.42396, -70.67257</t>
+          <t>-34.20638, -70.67368</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>00:28:44</t>
+          <t>00:31:13</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.82</v>
+        <v>0.65</v>
       </c>
       <c r="M104" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="N104" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6504,57 +6504,57 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026/09/25 19:59:49</t>
+          <t>2026/09/29 14:45:41</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>-33.42366, -70.672645</t>
+          <t>-34.2064566, -70.6737749</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-33.42366, -70.67265</t>
+          <t>-34.20646, -70.67377</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026/09/25 21:05:37</t>
+          <t>2026/09/29 15:02:34</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>-32.8792216, -70.6088833</t>
+          <t>-34.2088516, -70.6784083</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>-32.87922, -70.60888</t>
+          <t>-34.20885, -70.67841</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>01:05:48</t>
+          <t>00:16:53</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>74.63</v>
+        <v>0.5</v>
       </c>
       <c r="M105" t="n">
-        <v>129</v>
+        <v>12</v>
       </c>
       <c r="N105" t="n">
-        <v>73</v>
+        <v>12</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6563,57 +6563,57 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026/09/25 20:45:59</t>
+          <t>2026/09/29 15:02:41</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>-32.79762, -70.8870866</t>
+          <t>-34.2088366, -70.6784433</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-32.79762, -70.88709</t>
+          <t>-34.20884, -70.67844</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026/09/25 21:37:31</t>
+          <t>2026/09/29 15:10:24</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>-32.7685433, -70.8329983</t>
+          <t>-34.2055783, -70.6765233</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>-32.76854, -70.83300</t>
+          <t>-34.20558, -70.67652</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>00:51:32</t>
+          <t>00:07:43</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>6.41</v>
+        <v>0.54</v>
       </c>
       <c r="M106" t="n">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="N106" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6622,57 +6622,57 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026/09/25 21:05:47</t>
+          <t>2026/09/29 15:10:33</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>-32.879215, -70.6087933</t>
+          <t>-34.2055833, -70.6766683</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-32.87922, -70.60879</t>
+          <t>-34.20558, -70.67667</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026/09/26 08:55:03</t>
+          <t>2026/09/29 15:17:16</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>-32.84833, -70.5919733</t>
+          <t>-34.2053283, -70.6803716</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>-32.84833, -70.59197</t>
+          <t>-34.20533, -70.68037</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>11:49:16</t>
+          <t>00:06:43</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>5.62</v>
+        <v>0.34</v>
       </c>
       <c r="M107" t="n">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="N107" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -6681,53 +6681,53 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026/09/25 21:38:46</t>
+          <t>2026/09/29 15:17:21</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>-32.7686416, -70.8332483</t>
+          <t>-34.2052983, -70.6803616</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-32.76864, -70.83325</t>
+          <t>-34.20530, -70.68036</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026/09/25 22:04:08</t>
+          <t>2026/09/29 15:36:24</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>-32.7977249, -70.8874783</t>
+          <t>-34.20408, -70.6772316</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>-32.79772, -70.88748</t>
+          <t>-34.20408, -70.67723</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>00:25:22</t>
+          <t>00:19:03</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>6.23</v>
+        <v>0.4</v>
       </c>
       <c r="M108" t="n">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="N108" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -6740,57 +6740,57 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026/09/25 22:04:34</t>
+          <t>2026/09/29 15:31:53</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>-32.7976133, -70.887115</t>
+          <t>-34.04247, -70.6816733</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-32.79761, -70.88711</t>
+          <t>-34.04247, -70.68167</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026/09/26 07:10:51</t>
+          <t>2026/09/29 17:14:04</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>-32.7977, -70.887445</t>
+          <t>-34.16791, -70.7331566</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>-32.79770, -70.88744</t>
+          <t>-34.16791, -70.73316</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>09:06:17</t>
+          <t>01:42:11</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>12.84</v>
+        <v>18.53</v>
       </c>
       <c r="M109" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="N109" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -6799,175 +6799,175 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026/09/27 01:57:23</t>
+          <t>2026/09/29 15:36:37</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>-34.042474, -70.681749</t>
+          <t>-34.2044066, -70.677265</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-34.04247, -70.68175</t>
+          <t>-34.20441, -70.67727</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026/09/28 00:59:54</t>
+          <t>2026/09/29 16:07:01</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>-34.041867, -70.681404</t>
+          <t>-34.207595, -70.6760166</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>-34.04187, -70.68140</t>
+          <t>-34.20759, -70.67602</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>23:02:31</t>
+          <t>00:30:24</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="M110" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="N110" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026/09/27 02:11:15</t>
+          <t>2026/09/29 16:08:16</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>-34.205678, -70.676839</t>
+          <t>-34.2074249, -70.676</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-34.20568, -70.67684</t>
+          <t>-34.20742, -70.67600</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026/09/30 23:12:08</t>
+          <t>2026/09/29 17:17:11</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>-34.205405, -70.677267</t>
+          <t>-34.1677016, -70.7344666</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>-34.20540, -70.67727</t>
+          <t>-34.16770, -70.73447</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>93:00:53</t>
+          <t>01:08:55</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0.09</v>
+        <v>7.83</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026/09/28 03:46:15</t>
+          <t>2026/09/29 17:14:42</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>-34.205603, -70.67714</t>
+          <t>-34.1677733, -70.7330083</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-34.20560, -70.67714</t>
+          <t>-34.16777, -70.73301</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026/09/30 03:49:09</t>
+          <t>2026/09/30 07:45:52</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>-34.205447, -70.677137</t>
+          <t>-34.041345, -70.6800983</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>-34.20545, -70.67714</t>
+          <t>-34.04134, -70.68010</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>48:02:54</t>
+          <t>14:31:10</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0.06</v>
+        <v>18.84</v>
       </c>
       <c r="M112" t="n">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="N112" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -6976,57 +6976,57 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026/09/28 20:29:38</t>
+          <t>2026/09/29 17:18:26</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>-33.4761233, -70.6985033</t>
+          <t>-34.1678883, -70.7331966</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-33.47612, -70.69850</t>
+          <t>-34.16789, -70.73320</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026/09/29 06:59:56</t>
+          <t>2026/09/30 07:57:11</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>-33.4761833, -70.6984333</t>
+          <t>-34.20535, -70.680375</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>-33.47618, -70.69843</t>
+          <t>-34.20535, -70.68037</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>10:30:18</t>
+          <t>14:38:45</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0.02</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="M113" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="N113" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7035,57 +7035,57 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026/09/29 14:14:22</t>
+          <t>2026/09/29 21:21:37</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>-34.2042933, -70.6790483</t>
+          <t>-32.8791833, -70.6087983</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-34.20429, -70.67905</t>
+          <t>-32.87918, -70.60880</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026/09/29 14:45:35</t>
+          <t>2026/09/30 09:29:12</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>-34.2063833, -70.6736816</t>
+          <t>-32.8830983, -70.6123566</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>-34.20638, -70.67368</t>
+          <t>-32.88310, -70.61236</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>00:31:13</t>
+          <t>12:07:35</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0.65</v>
+        <v>14.03</v>
       </c>
       <c r="M114" t="n">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="N114" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7094,175 +7094,175 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026/09/29 14:45:41</t>
+          <t>2026/09/30 04:46:48</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>-34.2064566, -70.6737749</t>
+          <t>-34.205447, -70.677137</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-34.20646, -70.67377</t>
+          <t>-34.20545, -70.67714</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026/09/29 15:02:34</t>
+          <t>2026/10/01 08:01:11</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>-34.2088516, -70.6784083</t>
+          <t>-34.204273, -70.678813</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>-34.20885, -70.67841</t>
+          <t>-34.20427, -70.67881</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>00:16:53</t>
+          <t>27:14:23</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0.5</v>
+        <v>0.23</v>
       </c>
       <c r="M115" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="N115" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C116" t="n">
+        <v>2</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Recorridos</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2026/09/30 12:35:25</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>-33.364985, -70.6766933</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-33.36498, -70.67669</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2026/09/30 13:07:33</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>-33.3671433, -70.6956466</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>-33.36714, -70.69565</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>00:32:08</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="M116" t="n">
+        <v>46</v>
+      </c>
+      <c r="N116" t="n">
         <v>17</v>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Recorridos</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>2026/09/29 15:02:41</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>-34.2088366, -70.6784433</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>-34.20884, -70.67844</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>2026/09/29 15:10:24</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>-34.2055783, -70.6765233</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>-34.20558, -70.67652</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>00:07:43</t>
-        </is>
-      </c>
-      <c r="L116" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="M116" t="n">
-        <v>16</v>
-      </c>
-      <c r="N116" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026/09/29 15:10:33</t>
+          <t>2026/09/30 12:45:37</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>-34.2055833, -70.6766683</t>
+          <t>-33.359523, -70.80683</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-34.20558, -70.67667</t>
+          <t>-33.35952, -70.80683</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026/09/29 15:17:16</t>
+          <t>2026/10/01 23:13:21</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>-34.2053283, -70.6803716</t>
+          <t>-33.360027, -70.80704</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>-34.20533, -70.68037</t>
+          <t>-33.36003, -70.80704</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>00:06:43</t>
+          <t>34:27:44</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0.34</v>
+        <v>0.08</v>
       </c>
       <c r="M117" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7271,116 +7271,116 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026/09/29 15:17:21</t>
+          <t>2026/09/30 13:08:48</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>-34.2052983, -70.6803616</t>
+          <t>-33.36717, -70.6958566</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>-34.20530, -70.68036</t>
+          <t>-33.36717, -70.69586</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026/09/29 15:36:24</t>
+          <t>2026/10/01 12:44:50</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>-34.20408, -70.6772316</t>
+          <t>-33.40172, -70.7491433</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>-34.20408, -70.67723</t>
+          <t>-33.40172, -70.74914</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>00:19:03</t>
+          <t>23:36:02</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0.4</v>
+        <v>29.79</v>
       </c>
       <c r="M118" t="n">
-        <v>13</v>
+        <v>129</v>
       </c>
       <c r="N118" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026/09/29 15:36:37</t>
+          <t>2026/10/01 08:35:14</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>-34.2044066, -70.677265</t>
+          <t>-34.204158, -70.678905</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-34.20441, -70.67727</t>
+          <t>-34.20416, -70.67891</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026/09/29 16:07:01</t>
+          <t>2026/10/01 08:41:50</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>-34.207595, -70.6760166</t>
+          <t>-34.204154, -70.678888</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>-34.20759, -70.67602</t>
+          <t>-34.20415, -70.67889</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>00:30:24</t>
+          <t>00:06:36</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0.4</v>
+        <v>0.02</v>
       </c>
       <c r="M119" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="N119" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7389,293 +7389,293 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026/09/29 16:08:16</t>
+          <t>2026/10/01 08:42:13</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>-34.2074249, -70.676</t>
+          <t>-34.204184, -70.678915</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>-34.20742, -70.67600</t>
+          <t>-34.20418, -70.67892</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026/09/29 17:17:11</t>
+          <t>2026/10/01 09:54:13</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>-34.1677016, -70.7344666</t>
+          <t>-34.042757, -70.681707</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>-34.16770, -70.73447</t>
+          <t>-34.04276, -70.68171</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>01:08:55</t>
+          <t>01:12:00</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>7.83</v>
+        <v>23.48</v>
       </c>
       <c r="M120" t="n">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="N120" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>OPEL COMBO</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026/09/29 17:18:26</t>
+          <t>2026/10/01 13:25:31</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>-34.1678883, -70.7331966</t>
+          <t>-33.3671533, -70.6959633</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-34.16789, -70.73320</t>
+          <t>-33.36715, -70.69596</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026/09/30 07:57:11</t>
+          <t>2026/10/01 23:25:36</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>-34.20535, -70.680375</t>
+          <t>-33.3671533, -70.6959633</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>-34.20535, -70.68037</t>
+          <t>-33.36715, -70.69596</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>14:38:45</t>
+          <t>10:00:05</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>8.029999999999999</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026/09/29 18:09:06</t>
+          <t>2026/10/01 15:35:22</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>-32.843495, -70.6010066</t>
+          <t>-34.345993, -71.125785</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>-32.84349, -70.60101</t>
+          <t>-34.34599, -71.12578</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026/09/29 21:21:27</t>
+          <t>2026/10/01 23:34:21</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>-32.8791733, -70.60882</t>
+          <t>-34.345993, -71.125785</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>-32.87917, -70.60882</t>
+          <t>-34.34599, -71.12578</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>03:12:21</t>
+          <t>07:58:59</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026/09/29 21:21:37</t>
+          <t>2026/10/01 15:54:54</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>-32.8791833, -70.6087983</t>
+          <t>-34.042203, -70.681725</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-32.87918, -70.60880</t>
+          <t>-34.04220, -70.68173</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026/09/30 09:29:12</t>
+          <t>2026/10/01 16:06:11</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>-32.8830983, -70.6123566</t>
+          <t>-34.042224, -70.681724</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>-32.88310, -70.61236</t>
+          <t>-34.04222, -70.68172</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>12:07:35</t>
+          <t>00:11:17</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>14.03</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>83</v>
+        <v>3</v>
       </c>
       <c r="N123" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026/09/30 12:35:25</t>
+          <t>2026/10/01 16:06:54</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>-33.364985, -70.6766933</t>
+          <t>-34.042238, -70.68172</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>-33.36498, -70.67669</t>
+          <t>-34.04224, -70.68172</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026/09/30 13:07:33</t>
+          <t>2026/10/01 23:24:23</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>-33.3671433, -70.6956466</t>
+          <t>-34.042238, -70.68172</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>-33.36714, -70.69565</t>
+          <t>-34.04224, -70.68172</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>00:32:08</t>
+          <t>07:17:29</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -7684,41 +7684,41 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026/09/30 12:45:37</t>
+          <t>2026/10/01 17:19:44</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>-33.359523, -70.80683</t>
+          <t>-34.1676916, -70.7329816</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>-33.35952, -70.80683</t>
+          <t>-34.16769, -70.73298</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026/09/30 23:43:47</t>
+          <t>2026/10/01 23:19:44</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>-33.359986, -70.807021</t>
+          <t>-34.1676916, -70.7329816</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80702</t>
+          <t>-34.16769, -70.73298</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>10:58:10</t>
+          <t>06:00:00</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
         <v>0</v>
@@ -7730,11 +7730,11 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>OPEL COMBO</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -7743,37 +7743,37 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026/09/30 13:08:48</t>
+          <t>2026/10/01 17:25:54</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>-33.36717, -70.6958566</t>
+          <t>-34.1677633, -70.733025</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>-33.36717, -70.69586</t>
+          <t>-34.16776, -70.73302</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026/09/30 23:09:04</t>
+          <t>2026/10/01 23:25:54</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>-33.36717, -70.6958566</t>
+          <t>-34.1677633, -70.733025</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>-33.36717, -70.69586</t>
+          <t>-34.16776, -70.73302</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>10:00:16</t>
+          <t>06:00:00</t>
         </is>
       </c>
       <c r="L126" t="n">
@@ -7789,54 +7789,54 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TKCL-70</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026/09/30 17:05:50</t>
+          <t>2026/10/01 18:11:24</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>-34.167845, -70.7330049</t>
+          <t>-32.840503, -70.959778</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>-34.16784, -70.73300</t>
+          <t>-32.84050, -70.95978</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026/09/30 23:05:50</t>
+          <t>2026/10/01 20:00:14</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>-34.167845, -70.7330049</t>
+          <t>-32.83836, -70.95554</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>-34.16784, -70.73300</t>
+          <t>-32.83836, -70.95554</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>06:00:00</t>
+          <t>01:48:50</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>11.55</v>
       </c>
       <c r="M127" t="n">
         <v>0</v>
@@ -7848,129 +7848,129 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026/09/30 17:06:57</t>
+          <t>2026/10/01 18:13:13</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>-34.1678933, -70.7330433</t>
+          <t>-32.8837266, -70.6115666</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>-34.16789, -70.73304</t>
+          <t>-32.88373, -70.61157</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026/09/30 23:07:08</t>
+          <t>2026/10/01 18:25:12</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>-34.1678933, -70.7330433</t>
+          <t>-32.8834233, -70.6129166</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>-34.16789, -70.73304</t>
+          <t>-32.88342, -70.61292</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>06:00:11</t>
+          <t>00:11:59</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026/09/30 17:09:42</t>
+          <t>2026/10/01 18:26:27</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>-34.1679316, -70.7330566</t>
+          <t>-32.8827683, -70.6122316</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>-34.16793, -70.73306</t>
+          <t>-32.88277, -70.61223</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026/09/30 23:18:09</t>
+          <t>2026/10/01 18:38:44</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>-34.1678466, -70.7330116</t>
+          <t>-32.8827333, -70.6121833</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>-34.16785, -70.73301</t>
+          <t>-32.88273, -70.61218</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>06:08:27</t>
+          <t>00:12:17</t>
         </is>
       </c>
       <c r="L129" t="n">
         <v>0.01</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -7979,37 +7979,37 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026/09/30 17:33:08</t>
+          <t>2026/10/01 18:27:27</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>-33.4365083, -70.6295716</t>
+          <t>-33.4761066, -70.69849</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>-33.43651, -70.62957</t>
+          <t>-33.47611, -70.69849</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026/09/30 23:33:08</t>
+          <t>2026/10/01 22:27:31</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>-33.4365083, -70.6295716</t>
+          <t>-33.4761066, -70.69849</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>-33.43651, -70.62957</t>
+          <t>-33.47611, -70.69849</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>06:00:00</t>
+          <t>04:00:04</t>
         </is>
       </c>
       <c r="L130" t="n">
@@ -8025,11 +8025,11 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8038,57 +8038,57 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026/09/30 18:24:29</t>
+          <t>2026/10/01 18:39:59</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>-32.837145, -70.96704</t>
+          <t>-32.8824766, -70.6119316</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>-32.83714, -70.96704</t>
+          <t>-32.88248, -70.61193</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026/09/30 20:02:04</t>
+          <t>2026/10/01 18:47:30</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>-32.838387, -70.955454</t>
+          <t>-32.8791983, -70.6088099</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>-32.83839, -70.95545</t>
+          <t>-32.87920, -70.60881</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>01:37:35</t>
+          <t>00:07:31</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.31</v>
+        <v>0.48</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8097,37 +8097,37 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026/09/30 18:58:52</t>
+          <t>2026/10/01 18:47:38</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>-33.47613, -70.6984866</t>
+          <t>-32.8792, -70.60876</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>-33.47613, -70.69849</t>
+          <t>-32.87920, -70.60876</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026/09/30 22:58:58</t>
+          <t>2026/10/01 22:47:38</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>-33.47613, -70.6984866</t>
+          <t>-32.8792, -70.60876</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>-33.47613, -70.69849</t>
+          <t>-32.87920, -70.60876</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>04:00:06</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="L132" t="n">
@@ -8143,11 +8143,11 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8156,46 +8156,105 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026/09/30 19:01:38</t>
+          <t>2026/10/01 19:46:19</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>-32.8792366, -70.6087549</t>
+          <t>-33.0873, -71.3623033</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>-32.87924, -70.60875</t>
+          <t>-33.08730, -71.36230</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026/09/30 23:01:38</t>
+          <t>2026/10/01 23:47:46</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>-32.8792366, -70.6087549</t>
+          <t>-33.08722, -71.362225</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>-32.87924, -70.60875</t>
+          <t>-33.08722, -71.36222</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>04:00:00</t>
+          <t>04:01:27</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="M133" t="n">
         <v>0</v>
       </c>
       <c r="N133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>MITSUBISHI L200 PHZF-89</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>6</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Paradas</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>2026/10/01 21:04:14</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>-33.4363983, -70.6289216</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>-33.43640, -70.62892</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>2026/10/01 23:08:36</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>-33.4364866, -70.6289466</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>-33.43649, -70.62895</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>02:04:22</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8247,10 +8306,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1254.29</v>
+        <v>1101.09</v>
       </c>
       <c r="C2" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -8266,10 +8325,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>558.46</v>
+        <v>567.96</v>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -8285,16 +8344,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>579.85</v>
+        <v>765.64</v>
       </c>
       <c r="C4" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5">
@@ -8304,10 +8363,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>812.45</v>
+        <v>824.66</v>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -8323,16 +8382,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -8367,7 +8426,7 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
         <v>25</v>
@@ -8380,13 +8439,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.41</v>
+        <v>3.03</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
         <v>19</v>
@@ -8405,7 +8464,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -8475,10 +8534,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1161.37</v>
+        <v>1120.08</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -8494,16 +8553,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>115.56</v>
+        <v>324.03</v>
       </c>
       <c r="C15" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16">
@@ -8513,16 +8572,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13.6</v>
+        <v>53.45</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>55</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17">
@@ -8532,7 +8591,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -8551,16 +8610,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.35</v>
+        <v>25.24</v>
       </c>
       <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="n">
         <v>9</v>
       </c>
-      <c r="D18" t="n">
-        <v>7</v>
-      </c>
       <c r="E18" t="n">
-        <v>20</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19">
@@ -8570,10 +8629,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>612.21</v>
+        <v>630.62</v>
       </c>
       <c r="C19" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>

--- a/REPORTE DE RECORRIDO.xlsx
+++ b/REPORTE DE RECORRIDO.xlsx
@@ -446,13 +446,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N134"/>
+  <dimension ref="A1:N133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Desde : 2026/09/25 04:00:00   Hasta : 2026/10/02 03:59:59</t>
+          <t>Desde : 2026/09/26 04:00:00   Hasta : 2026/10/03 03:59:59</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>SLP20250627045-AC02</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -545,53 +545,53 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026/09/25 00:13:52</t>
+          <t>2026/09/26 00:03:51</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-33.4361833, -70.6295283</t>
+          <t>-34.205393, -70.677304</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-33.43618, -70.62953</t>
+          <t>-34.20539, -70.67730</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026/09/25 07:13:15</t>
+          <t>2026/09/28 02:48:55</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-33.4461766, -70.6193216</t>
+          <t>-34.205603, -70.67714</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-33.44618, -70.61932</t>
+          <t>-34.20560, -70.67714</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>06:59:23</t>
+          <t>50:45:04</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.19</v>
+        <v>0.45</v>
       </c>
       <c r="M4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="N4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LPR20251L02790031-SV</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -604,53 +604,53 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026/09/25 00:17:44</t>
+          <t>2026/09/26 00:04:34</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-34.345997, -71.125783</t>
+          <t>-32.7976133, -70.887115</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-34.34600, -71.12578</t>
+          <t>-32.79761, -70.88711</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026/09/25 12:48:30</t>
+          <t>2026/09/26 07:10:51</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-34.346461, -71.126063</t>
+          <t>-32.7977, -70.887445</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-34.34646, -71.12606</t>
+          <t>-32.79770, -70.88744</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>12:30:46</t>
+          <t>07:06:17</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.34</v>
+        <v>12.84</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>108</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LPR20251T02900038-RTN</t>
+          <t>LPR20251A02800014-DS</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -663,53 +663,53 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026/09/25 00:24:07</t>
+          <t>2026/09/26 00:11:25</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-34.876578, -71.127348</t>
+          <t>-34.205372, -70.677301</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-34.87658, -71.12735</t>
+          <t>-34.20537, -70.67730</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026/09/30 01:24:53</t>
+          <t>2026/09/27 01:13:50</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-34.876425, -71.127141</t>
+          <t>-34.205678, -70.676839</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-34.87642, -71.12714</t>
+          <t>-34.20568, -70.67684</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>121:00:46</t>
+          <t>25:02:25</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SLP20250425120-AC01</t>
+          <t>LPR20251L02790031-SV</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -717,58 +717,58 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026/09/25 00:24:55</t>
+          <t>2026/09/26 00:11:48</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-33.359986, -70.807048</t>
+          <t>-34.346003, -71.125772</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-33.35999, -70.80705</t>
+          <t>-34.34600, -71.12577</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026/09/30 11:49:06</t>
+          <t>2026/09/27 01:04:06</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-33.359523, -70.80683</t>
+          <t>-34.346003, -71.125758</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-33.35952, -70.80683</t>
+          <t>-34.34600, -71.12576</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>131:24:11</t>
+          <t>24:52:18</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LPR20251V02900023-LL</t>
+          <t>LPR20251T02900038-RTN</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -781,53 +781,53 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026/09/25 00:31:22</t>
+          <t>2026/09/26 00:23:09</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-33.899816, -71.429365</t>
+          <t>-34.876578, -71.127348</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-33.89982, -71.42937</t>
+          <t>-34.87658, -71.12735</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026/09/25 01:34:09</t>
+          <t>2026/09/30 01:24:53</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-33.899779, -71.42949</t>
+          <t>-34.876425, -71.127141</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-33.89978, -71.42949</t>
+          <t>-34.87642, -71.12714</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>01:02:47</t>
+          <t>97:01:44</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LPR20251P02790030-ALD</t>
+          <t>LPR20251V02900023-LL</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -840,53 +840,53 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026/09/25 00:34:54</t>
+          <t>2026/09/26 00:32:40</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-34.57985, -70.961438</t>
+          <t>-33.899779, -71.42949</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-34.57985, -70.96144</t>
+          <t>-33.89978, -71.42949</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026/09/28 01:38:35</t>
+          <t>2026/09/26 01:52:03</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-34.579561, -70.961474</t>
+          <t>-33.89996, -71.429414</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-34.57956, -70.96147</t>
+          <t>-33.89996, -71.42941</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>73:03:41</t>
+          <t>01:19:23</t>
         </is>
       </c>
       <c r="L9" t="n">
         <v>0.09</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>LPR20251P02790030-ALD</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -894,58 +894,58 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Recorridos</t>
+          <t>Paradas</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026/09/25 00:35:53</t>
+          <t>2026/09/26 00:35:58</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-33.4762016, -70.6984316</t>
+          <t>-34.579697, -70.961386</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-33.47620, -70.69843</t>
+          <t>-34.57970, -70.96139</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/09/25 07:45:24</t>
+          <t>2026/09/28 01:38:35</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-33.4762749, -70.6983349</t>
+          <t>-34.579561, -70.961474</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-33.47627, -70.69833</t>
+          <t>-34.57956, -70.96147</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>07:09:31</t>
+          <t>49:02:37</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>11.15</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>LPR20251E02900022</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -958,53 +958,53 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026/09/25 00:36:58</t>
+          <t>2026/09/26 00:43:29</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-32.879235, -70.60878</t>
+          <t>-33.366736, -70.696931</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-32.87924, -70.60878</t>
+          <t>-33.36674, -70.69693</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026/09/25 07:47:56</t>
+          <t>2026/10/02 12:29:26</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-32.8529266, -70.62402</t>
+          <t>-32.888105, -70.619573</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-32.85293, -70.62402</t>
+          <t>-32.88811, -70.61957</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>07:10:58</t>
+          <t>155:45:57</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>6.41</v>
+        <v>61.3</v>
       </c>
       <c r="M11" t="n">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="N11" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>SLP20250425120-AC01</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1017,53 +1017,53 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026/09/25 00:39:20</t>
+          <t>2026/09/26 00:50:41</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-32.797605, -70.887025</t>
+          <t>-33.360042, -70.807029</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-32.79760, -70.88702</t>
+          <t>-33.36004, -70.80703</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026/09/25 07:11:23</t>
+          <t>2026/09/30 11:49:06</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-32.88316, -70.6124083</t>
+          <t>-33.359523, -70.80683</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-32.88316, -70.61241</t>
+          <t>-33.35952, -70.80683</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>06:32:03</t>
+          <t>106:58:25</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>41.76</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="N12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LPR20251A02800014-DS</t>
+          <t>LPR20251T02800022</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1076,53 +1076,53 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026/09/25 00:42:20</t>
+          <t>2026/09/26 00:57:32</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-34.205382, -70.677293</t>
+          <t>-33.367244, -70.69677</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-34.20538, -70.67729</t>
+          <t>-33.36724, -70.69677</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026/09/27 01:13:50</t>
+          <t>2026/10/02 10:50:40</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-34.205678, -70.676839</t>
+          <t>-33.367347, -70.696408</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-34.20568, -70.67684</t>
+          <t>-33.36735, -70.69641</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>48:31:30</t>
+          <t>153:53:08</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="M13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LPR20251E02900022</t>
+          <t>LPR20251H02800016-STL</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1135,53 +1135,53 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026/09/25 00:43:29</t>
+          <t>2026/09/26 00:59:14</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-33.366736, -70.696931</t>
+          <t>-34.042755, -70.681629</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-33.36674, -70.69693</t>
+          <t>-34.04275, -70.68163</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026/10/01 23:43:56</t>
+          <t>2026/09/26 00:59:56</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-33.36746, -70.69652</t>
+          <t>-34.042857, -70.681747</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-33.36746, -70.69652</t>
+          <t>-34.04286, -70.68175</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>167:00:27</t>
+          <t>00:00:42</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>JAC X200 SJTJ-50</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1189,58 +1189,58 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026/09/25 00:50:08</t>
+          <t>2026/09/26 01:02:22</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-34.20545, -70.677304</t>
+          <t>-32.7430533, -70.729815</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-34.20545, -70.67730</t>
+          <t>-32.74305, -70.72982</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026/09/25 07:48:22</t>
+          <t>2026/09/27 12:25:39</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-34.205362, -70.677228</t>
+          <t>-32.6228783, -70.7205266</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-34.20536, -70.67723</t>
+          <t>-32.62288, -70.72053</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>06:58:14</t>
+          <t>35:23:17</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.03</v>
+        <v>15.05</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LPR20251T02800022</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1248,58 +1248,58 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026/09/25 00:57:32</t>
+          <t>2026/09/26 01:05:47</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-33.367244, -70.69677</t>
+          <t>-32.879215, -70.6087933</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-33.36724, -70.69677</t>
+          <t>-32.87922, -70.60879</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026/10/01 23:35:40</t>
+          <t>2026/09/26 08:55:03</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-33.367244, -70.69677</t>
+          <t>-32.84833, -70.5919733</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-33.36724, -70.69677</t>
+          <t>-32.84833, -70.59197</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>166:38:08</t>
+          <t>07:49:16</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LPR20251H02800016-STL</t>
+          <t>MITSUBISHI L200 PHZF-89</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1307,52 +1307,52 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026/09/25 00:59:07</t>
+          <t>2026/09/26 01:13:11</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-34.042504, -70.681533</t>
+          <t>-33.4364116, -70.62956</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-34.04250, -70.68153</t>
+          <t>-33.43641, -70.62956</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026/09/25 00:59:47</t>
+          <t>2026/09/28 06:11:55</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-34.042755, -70.681629</t>
+          <t>-33.4452, -70.6199333</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-34.04275, -70.68163</t>
+          <t>-33.44520, -70.61993</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>00:00:40</t>
+          <t>52:58:44</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0.03</v>
+        <v>1.8</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026/09/25 01:15:34</t>
+          <t>2026/09/26 01:15:34</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>130:53:32</t>
+          <t>106:53:32</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -1430,53 +1430,53 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026/09/25 01:31:32</t>
+          <t>2026/09/26 01:22:42</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-34.16782, -70.73301</t>
+          <t>-33.087235, -71.3621816</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-34.16782, -70.73301</t>
+          <t>-33.08723, -71.36218</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026/09/25 07:15:02</t>
+          <t>2026/09/26 11:29:39</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-34.1679016, -70.7330383</t>
+          <t>-33.0873483, -71.36227</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-34.16790, -70.73304</t>
+          <t>-33.08735, -71.36227</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>05:43:30</t>
+          <t>10:06:57</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="M19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1489,47 +1489,47 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026/09/25 01:36:48</t>
+          <t>2026/09/26 01:25:00</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-34.1677816, -70.7330016</t>
+          <t>-33.4760983, -70.69852</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-34.16778, -70.73300</t>
+          <t>-33.47610, -70.69852</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026/09/25 07:39:02</t>
+          <t>2026/09/26 08:25:09</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-34.2053049, -70.6801799</t>
+          <t>-33.4762483, -70.6983149</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-34.20530, -70.68018</t>
+          <t>-33.47625, -70.69831</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>06:02:14</t>
+          <t>07:00:09</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>7.58</v>
+        <v>0.03</v>
       </c>
       <c r="M20" t="n">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="N20" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -1548,47 +1548,47 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026/09/25 01:57:14</t>
+          <t>2026/09/26 01:57:21</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-34.042755, -70.681629</t>
+          <t>-34.042857, -70.681747</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-34.04275, -70.68163</t>
+          <t>-34.04286, -70.68175</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026/09/26 00:59:56</t>
+          <t>2026/09/27 00:59:51</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-34.042857, -70.681747</t>
+          <t>-34.042474, -70.681749</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-34.04286, -70.68175</t>
+          <t>-34.04247, -70.68175</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>23:02:42</t>
+          <t>23:02:30</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -1607,41 +1607,41 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026/09/25 02:31:48</t>
+          <t>2026/09/26 02:01:31</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-33.899779, -71.42949</t>
+          <t>-33.89996, -71.429414</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-33.89978, -71.42949</t>
+          <t>-33.89996, -71.42941</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026/09/26 01:52:03</t>
+          <t>2026/09/29 01:33:54</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-33.89996, -71.429414</t>
+          <t>-33.899862, -71.429485</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-33.89996, -71.42941</t>
+          <t>-33.89986, -71.42948</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>23:20:15</t>
+          <t>71:32:23</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -1653,11 +1653,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCL-70</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1666,53 +1666,53 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026/09/25 06:56:23</t>
+          <t>2026/09/26 07:11:07</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-32.838367, -70.955507</t>
+          <t>-32.7975816, -70.8870833</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-32.83837, -70.95551</t>
+          <t>-32.79758, -70.88708</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026/09/25 07:07:07</t>
+          <t>2026/09/26 09:49:16</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-32.839517, -70.956188</t>
+          <t>-33.0869066, -71.361845</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-32.83952, -70.95619</t>
+          <t>-33.08691, -71.36185</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>00:10:44</t>
+          <t>02:38:09</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0.14</v>
+        <v>99.08</v>
       </c>
       <c r="M23" t="n">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="N23" t="n">
-        <v>31</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TGPS-77</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1725,53 +1725,53 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026/09/25 07:12:38</t>
+          <t>2026/09/26 08:25:17</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-32.8831616, -70.6124266</t>
+          <t>-33.4763016, -70.6983683</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-32.88316, -70.61243</t>
+          <t>-33.47630, -70.69837</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026/09/25 13:01:53</t>
+          <t>2026/09/26 09:12:14</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-32.756715, -70.7345333</t>
+          <t>-33.3621333, -70.6701183</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-32.75671, -70.73453</t>
+          <t>-33.36213, -70.67012</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>05:49:15</t>
+          <t>00:46:57</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>24.62</v>
+        <v>18.76</v>
       </c>
       <c r="M24" t="n">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="N24" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 PHZF-89</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1784,57 +1784,57 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026/09/25 07:14:30</t>
+          <t>2026/09/26 08:55:34</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-33.44648, -70.6208016</t>
+          <t>-32.848355, -70.5919233</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-33.44648, -70.62080</t>
+          <t>-32.84835, -70.59192</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026/09/25 09:56:13</t>
+          <t>2026/09/26 09:33:48</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-33.3661266, -70.6955216</t>
+          <t>-32.8792, -70.6088916</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-33.36613, -70.69552</t>
+          <t>-32.87920, -70.60889</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>02:41:43</t>
+          <t>00:38:14</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>13.39</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>124</v>
+        <v>62</v>
       </c>
       <c r="N25" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1843,57 +1843,57 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026/09/25 07:16:17</t>
+          <t>2026/09/26 09:12:28</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-34.1678983, -70.7330049</t>
+          <t>-33.3621549, -70.67016</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-34.16790, -70.73300</t>
+          <t>-33.36215, -70.67016</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026/09/25 07:41:57</t>
+          <t>2026/09/26 12:35:42</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-34.2052916, -70.68031</t>
+          <t>-33.370445, -70.6707016</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-34.20529, -70.68031</t>
+          <t>-33.37044, -70.67070</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>00:25:40</t>
+          <t>03:23:14</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>7.44</v>
+        <v>1.74</v>
       </c>
       <c r="M26" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="N26" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1902,53 +1902,53 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026/09/25 07:40:17</t>
+          <t>2026/09/26 09:33:54</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-34.2052766, -70.6801349</t>
+          <t>-32.8792083, -70.608835</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-34.20528, -70.68013</t>
+          <t>-32.87921, -70.60883</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026/09/25 07:46:36</t>
+          <t>2026/09/26 09:51:32</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-34.2055183, -70.6775416</t>
+          <t>-32.852215, -70.607595</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-34.20552, -70.67754</t>
+          <t>-32.85222, -70.60760</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>00:06:19</t>
+          <t>00:17:38</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.26</v>
+        <v>4.3</v>
       </c>
       <c r="M27" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="N27" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CHANGAN HUNTER TKCS-53</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1961,57 +1961,57 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026/09/25 07:42:41</t>
+          <t>2026/09/26 09:50:31</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-34.204085, -70.678975</t>
+          <t>-33.08729, -71.3623216</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-34.20408, -70.67897</t>
+          <t>-33.08729, -71.36232</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026/09/25 09:15:43</t>
+          <t>2026/09/26 11:37:02</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-34.2051666, -70.6775016</t>
+          <t>-32.805725, -70.8246949</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-34.20517, -70.67750</t>
+          <t>-32.80573, -70.82469</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>01:33:02</t>
+          <t>01:46:31</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.18</v>
+        <v>86.91</v>
       </c>
       <c r="M28" t="n">
-        <v>12</v>
+        <v>146</v>
       </c>
       <c r="N28" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MITSUBISHI L200 LVHX-40</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2020,57 +2020,57 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026/09/25 07:46:01</t>
+          <t>2026/09/26 09:51:53</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-33.4763216, -70.6983966</t>
+          <t>-32.85219, -70.6075549</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-33.47632, -70.69840</t>
+          <t>-32.85219, -70.60755</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026/09/25 09:29:53</t>
+          <t>2026/09/26 10:13:25</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-33.360285, -70.8090433</t>
+          <t>-32.8522649, -70.6076816</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-33.36028, -70.80904</t>
+          <t>-32.85226, -70.60768</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>01:43:52</t>
+          <t>00:21:32</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>37.1</v>
+        <v>0.02</v>
       </c>
       <c r="M29" t="n">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="N29" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JAC X200 SJTJ-50</t>
+          <t>SUZUKI CARRY SKDB-52</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2079,53 +2079,53 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026/09/25 07:46:49</t>
+          <t>2026/09/26 10:13:36</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-34.20529, -70.6775133</t>
+          <t>-32.8522083, -70.6075433</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-34.20529, -70.67751</t>
+          <t>-32.85221, -70.60754</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026/09/25 10:39:55</t>
+          <t>2026/09/26 12:12:22</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-34.2052816, -70.6775066</t>
+          <t>-32.8792216, -70.60896</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-34.20528, -70.67751</t>
+          <t>-32.87922, -70.60896</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>02:53:06</t>
+          <t>01:58:46</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="M30" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="N30" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2138,57 +2138,57 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026/09/25 07:48:28</t>
+          <t>2026/09/26 11:29:49</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-34.205327, -70.677293</t>
+          <t>-33.08735, -71.3623016</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-34.20533, -70.67729</t>
+          <t>-33.08735, -71.36230</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026/09/25 08:10:06</t>
+          <t>2026/09/26 12:08:57</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-34.205121, -70.677514</t>
+          <t>-33.0443716, -71.3764083</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-34.20512, -70.67751</t>
+          <t>-33.04437, -71.37641</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>00:21:38</t>
+          <t>00:39:08</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0.45</v>
+        <v>6.47</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="N31" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SUZUKI CARRY SKDB-52</t>
+          <t>CHANGAN HUNTER TGPS-77</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2197,53 +2197,53 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026/09/25 07:49:11</t>
+          <t>2026/09/26 11:38:17</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-32.853015, -70.6241333</t>
+          <t>-32.8057499, -70.8247083</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-32.85301, -70.62413</t>
+          <t>-32.80575, -70.82471</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026/09/25 08:12:47</t>
+          <t>2026/09/26 12:46:02</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-32.882485, -70.6119416</t>
+          <t>-32.79175, -70.872745</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-32.88249, -70.61194</t>
+          <t>-32.79175, -70.87274</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>00:23:36</t>
+          <t>01:07:45</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>5.59</v>
+        <v>33.98</v>
       </c>
       <c r="M32" t="n">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="N32" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>CHANGAN HUNTER TKCS-53</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2251,52 +2251,52 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026/09/25 08:11:06</t>
+          <t>2026/09/26 12:10:12</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-34.205344, -70.677493</t>
+          <t>-33.0444033, -71.3744016</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-34.20534, -70.67749</t>
+          <t>-33.04440, -71.37440</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026/09/25 08:22:32</t>
+          <t>2026/09/26 12:42:15</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-34.205442, -70.677361</t>
+          <t>-33.08736, -71.362275</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-34.20544, -70.67736</t>
+          <t>-33.08736, -71.36227</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>00:11:26</t>
+          <t>00:32:03</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0.03</v>
+        <v>5.99</v>
       </c>
       <c r="M33" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="N33" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34">
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2315,53 +2315,53 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026/09/25 08:14:02</t>
+          <t>2026/09/26 12:13:37</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-32.8831133, -70.6123516</t>
+          <t>-32.8792216, -70.6088633</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-32.88311, -70.61235</t>
+          <t>-32.87922, -70.60886</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026/09/25 08:31:14</t>
+          <t>2026/09/26 12:56:24</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-32.88338, -70.612335</t>
+          <t>-32.8293666, -70.6115466</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-32.88338, -70.61234</t>
+          <t>-32.82937, -70.61155</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>00:17:12</t>
+          <t>00:42:47</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0.13</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="N34" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SLP20250627045-AC02</t>
+          <t>MITSUBISHI L200 LVHX-40</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -2369,58 +2369,58 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Paradas</t>
+          <t>Recorridos</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026/09/25 08:23:09</t>
+          <t>2026/09/26 12:36:01</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <